--- a/Projekttagebuch.xlsx
+++ b/Projekttagebuch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\projects\GW.Demo.Maui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F399F19-C071-46D5-B28E-BDC2F95E2415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CE483E-9C59-4B4D-9496-8649B2DDA058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
   <si>
     <t>Framework:</t>
   </si>
@@ -219,6 +219,46 @@
   </si>
   <si>
     <t>84</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Durch den Einsatz von CarouselView, der sich als sinnvoll erwiesen hat, wurde die Swipe-Funktionalität bereits mit den Screeens implementiert. Eine sinnhafte Trennung ist nicht möglich.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/dotnet/maui/fundamentals/shell/flyout
+https://learn.microsoft.com/en-us/shows/on-dotnet/enhance-dotnet-maui-desktop-apps-with-the-menu-bar
+https://stackoverflow.com/questions/73886700/net-maui-flyout-as-a-regular-sidebar
+https://www.youtube.com/watch?v=b77dEArbk9E
+ChatGPT, CoPilot
+https://medium.com/@cristian_lopes/net-maui-flyout-navigation-tab-navigation-ca62913c98fa</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Menü-Commands feuern nicht, mühsam, Video und AI haben geholfen.
+Um das mit Commands zu machen, musste ich dann noch weiter rumzangeln. Richtiges VM haben wir so einmal nicht.</t>
+  </si>
+  <si>
+    <t>Binding von PositionView ist trotz expliziter Implementation falsch. Lösung ist VM im Control explizit. Problem lässt sich schlecht formulieren/suchen, Fehlermeldung ('CoordinateText' property not found on '0', target property: 'Microsoft.Maui.Controls.Label.Text') nur bedingt hilfreich. Allerdings viel Community-Support dazu (WPF/MAUI)). Zeigt aber auch, dass das generell eine Schwachstelle des Ansatzes ist.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/dotnet/maui/platform-integration/device/geolocation
+https://thinkgeo.com/blog/maui-geolocation
+https://stackoverflow.com/questions/33805067/how-to-resolve-a-binding-expression-path-error-in-wpf
+https://learn.microsoft.com/en-us/answers/questions/319101/binding-property-not-found
+https://www.reddit.com/r/csharp/comments/1b8r4mk/having_trouble_getting_maui_data_bindings_to_work/
+https://learn.microsoft.com/en-us/dotnet/maui/fundamentals/data-binding/basic-bindings
+https://wpf-tutorial.com/am/41/data-binding/debugging-data-bindings/
+https://csharpforums.net/threads/binding-failures.9253/
+https://stackoverflow.com/questions/41574642/refresh-or-update-content-page-every-few-seconds-automatically
+https://www.syncfusion.com/blogs/post/timer-app-maui-radialgauge-timepicker
+https://learn.microsoft.com/en-us/dotnet/api/microsoft.maui.dispatching.idispatchertimer</t>
+  </si>
+  <si>
+    <t>82</t>
   </si>
 </sst>
 </file>
@@ -463,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -609,6 +649,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2099,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B477CBB-721B-4C42-B1E4-90FB6F775FFA}">
-  <dimension ref="B2:AC213"/>
+  <dimension ref="B2:AC216"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4.7109375" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="4.7109375" style="1"/>
@@ -2749,33 +2792,35 @@
     <row r="27" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="44"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="41"/>
+      <c r="D27" s="41" t="s">
+        <v>54</v>
+      </c>
       <c r="E27" s="42"/>
       <c r="F27" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G27" s="6"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="48"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="34"/>
       <c r="AC27" s="11"/>
     </row>
     <row r="28" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2785,27 +2830,27 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="50"/>
-      <c r="AA28" s="50"/>
-      <c r="AB28" s="51"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="36"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="36"/>
+      <c r="Z28" s="36"/>
+      <c r="AA28" s="36"/>
+      <c r="AB28" s="37"/>
       <c r="AC28" s="11"/>
     </row>
     <row r="29" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2815,27 +2860,27 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="50"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="50"/>
-      <c r="AA29" s="50"/>
-      <c r="AB29" s="51"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
+      <c r="Q29" s="36"/>
+      <c r="R29" s="36"/>
+      <c r="S29" s="36"/>
+      <c r="T29" s="36"/>
+      <c r="U29" s="36"/>
+      <c r="V29" s="36"/>
+      <c r="W29" s="36"/>
+      <c r="X29" s="36"/>
+      <c r="Y29" s="36"/>
+      <c r="Z29" s="36"/>
+      <c r="AA29" s="36"/>
+      <c r="AB29" s="37"/>
       <c r="AC29" s="11"/>
     </row>
     <row r="30" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2845,27 +2890,27 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="50"/>
-      <c r="W30" s="50"/>
-      <c r="X30" s="50"/>
-      <c r="Y30" s="50"/>
-      <c r="Z30" s="50"/>
-      <c r="AA30" s="50"/>
-      <c r="AB30" s="51"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="36"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="36"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
+      <c r="X30" s="36"/>
+      <c r="Y30" s="36"/>
+      <c r="Z30" s="36"/>
+      <c r="AA30" s="36"/>
+      <c r="AB30" s="37"/>
       <c r="AC30" s="11"/>
     </row>
     <row r="31" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2875,27 +2920,27 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="50"/>
-      <c r="V31" s="50"/>
-      <c r="W31" s="50"/>
-      <c r="X31" s="50"/>
-      <c r="Y31" s="50"/>
-      <c r="Z31" s="50"/>
-      <c r="AA31" s="50"/>
-      <c r="AB31" s="51"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="36"/>
+      <c r="V31" s="36"/>
+      <c r="W31" s="36"/>
+      <c r="X31" s="36"/>
+      <c r="Y31" s="36"/>
+      <c r="Z31" s="36"/>
+      <c r="AA31" s="36"/>
+      <c r="AB31" s="37"/>
       <c r="AC31" s="11"/>
     </row>
     <row r="32" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2905,27 +2950,27 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50"/>
-      <c r="S32" s="50"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="50"/>
-      <c r="V32" s="50"/>
-      <c r="W32" s="50"/>
-      <c r="X32" s="50"/>
-      <c r="Y32" s="50"/>
-      <c r="Z32" s="50"/>
-      <c r="AA32" s="50"/>
-      <c r="AB32" s="51"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="36"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="P32" s="36"/>
+      <c r="Q32" s="36"/>
+      <c r="R32" s="36"/>
+      <c r="S32" s="36"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="36"/>
+      <c r="V32" s="36"/>
+      <c r="W32" s="36"/>
+      <c r="X32" s="36"/>
+      <c r="Y32" s="36"/>
+      <c r="Z32" s="36"/>
+      <c r="AA32" s="36"/>
+      <c r="AB32" s="37"/>
       <c r="AC32" s="11"/>
     </row>
     <row r="33" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2935,27 +2980,27 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="53"/>
-      <c r="W33" s="53"/>
-      <c r="X33" s="53"/>
-      <c r="Y33" s="53"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="53"/>
-      <c r="AB33" s="54"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="39"/>
+      <c r="Q33" s="39"/>
+      <c r="R33" s="39"/>
+      <c r="S33" s="39"/>
+      <c r="T33" s="39"/>
+      <c r="U33" s="39"/>
+      <c r="V33" s="39"/>
+      <c r="W33" s="39"/>
+      <c r="X33" s="39"/>
+      <c r="Y33" s="39"/>
+      <c r="Z33" s="39"/>
+      <c r="AA33" s="39"/>
+      <c r="AB33" s="40"/>
       <c r="AC33" s="11"/>
     </row>
     <row r="34" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2997,27 +3042,29 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="47"/>
-      <c r="V35" s="47"/>
-      <c r="W35" s="47"/>
-      <c r="X35" s="47"/>
-      <c r="Y35" s="47"/>
-      <c r="Z35" s="47"/>
-      <c r="AA35" s="47"/>
-      <c r="AB35" s="48"/>
+      <c r="H35" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="33"/>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="34"/>
       <c r="AC35" s="11"/>
     </row>
     <row r="36" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3027,27 +3074,27 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="50"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
-      <c r="Y36" s="50"/>
-      <c r="Z36" s="50"/>
-      <c r="AA36" s="50"/>
-      <c r="AB36" s="51"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="36"/>
+      <c r="Z36" s="36"/>
+      <c r="AA36" s="36"/>
+      <c r="AB36" s="37"/>
       <c r="AC36" s="11"/>
     </row>
     <row r="37" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3057,27 +3104,27 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="50"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="51"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="36"/>
+      <c r="R37" s="36"/>
+      <c r="S37" s="36"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="36"/>
+      <c r="V37" s="36"/>
+      <c r="W37" s="36"/>
+      <c r="X37" s="36"/>
+      <c r="Y37" s="36"/>
+      <c r="Z37" s="36"/>
+      <c r="AA37" s="36"/>
+      <c r="AB37" s="37"/>
       <c r="AC37" s="11"/>
     </row>
     <row r="38" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3087,27 +3134,27 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50"/>
-      <c r="S38" s="50"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="50"/>
-      <c r="Y38" s="50"/>
-      <c r="Z38" s="50"/>
-      <c r="AA38" s="50"/>
-      <c r="AB38" s="51"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="36"/>
+      <c r="V38" s="36"/>
+      <c r="W38" s="36"/>
+      <c r="X38" s="36"/>
+      <c r="Y38" s="36"/>
+      <c r="Z38" s="36"/>
+      <c r="AA38" s="36"/>
+      <c r="AB38" s="37"/>
       <c r="AC38" s="11"/>
     </row>
     <row r="39" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3117,27 +3164,27 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50"/>
-      <c r="Y39" s="50"/>
-      <c r="Z39" s="50"/>
-      <c r="AA39" s="50"/>
-      <c r="AB39" s="51"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="36"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36"/>
+      <c r="Q39" s="36"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="36"/>
+      <c r="W39" s="36"/>
+      <c r="X39" s="36"/>
+      <c r="Y39" s="36"/>
+      <c r="Z39" s="36"/>
+      <c r="AA39" s="36"/>
+      <c r="AB39" s="37"/>
       <c r="AC39" s="11"/>
     </row>
     <row r="40" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3147,27 +3194,27 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="50"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="50"/>
-      <c r="O40" s="50"/>
-      <c r="P40" s="50"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="50"/>
-      <c r="S40" s="50"/>
-      <c r="T40" s="50"/>
-      <c r="U40" s="50"/>
-      <c r="V40" s="50"/>
-      <c r="W40" s="50"/>
-      <c r="X40" s="50"/>
-      <c r="Y40" s="50"/>
-      <c r="Z40" s="50"/>
-      <c r="AA40" s="50"/>
-      <c r="AB40" s="51"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+      <c r="U40" s="36"/>
+      <c r="V40" s="36"/>
+      <c r="W40" s="36"/>
+      <c r="X40" s="36"/>
+      <c r="Y40" s="36"/>
+      <c r="Z40" s="36"/>
+      <c r="AA40" s="36"/>
+      <c r="AB40" s="37"/>
       <c r="AC40" s="11"/>
     </row>
     <row r="41" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3177,27 +3224,27 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="53"/>
-      <c r="N41" s="53"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="53"/>
-      <c r="Q41" s="53"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="53"/>
-      <c r="T41" s="53"/>
-      <c r="U41" s="53"/>
-      <c r="V41" s="53"/>
-      <c r="W41" s="53"/>
-      <c r="X41" s="53"/>
-      <c r="Y41" s="53"/>
-      <c r="Z41" s="53"/>
-      <c r="AA41" s="53"/>
-      <c r="AB41" s="54"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
+      <c r="R41" s="39"/>
+      <c r="S41" s="39"/>
+      <c r="T41" s="39"/>
+      <c r="U41" s="39"/>
+      <c r="V41" s="39"/>
+      <c r="W41" s="39"/>
+      <c r="X41" s="39"/>
+      <c r="Y41" s="39"/>
+      <c r="Z41" s="39"/>
+      <c r="AA41" s="39"/>
+      <c r="AB41" s="40"/>
       <c r="AC41" s="11"/>
     </row>
     <row r="42" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3299,33 +3346,37 @@
     <row r="46" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="44"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="41"/>
+      <c r="D46" s="41" t="s">
+        <v>57</v>
+      </c>
       <c r="E46" s="42"/>
       <c r="F46" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G46" s="6"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
-      <c r="L46" s="47"/>
-      <c r="M46" s="47"/>
-      <c r="N46" s="47"/>
-      <c r="O46" s="47"/>
-      <c r="P46" s="47"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="47"/>
-      <c r="V46" s="47"/>
-      <c r="W46" s="47"/>
-      <c r="X46" s="47"/>
-      <c r="Y46" s="47"/>
-      <c r="Z46" s="47"/>
-      <c r="AA46" s="47"/>
-      <c r="AB46" s="48"/>
+      <c r="H46" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="33"/>
+      <c r="AA46" s="33"/>
+      <c r="AB46" s="34"/>
       <c r="AC46" s="11"/>
     </row>
     <row r="47" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3335,27 +3386,27 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="50"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="50"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50"/>
-      <c r="S47" s="50"/>
-      <c r="T47" s="50"/>
-      <c r="U47" s="50"/>
-      <c r="V47" s="50"/>
-      <c r="W47" s="50"/>
-      <c r="X47" s="50"/>
-      <c r="Y47" s="50"/>
-      <c r="Z47" s="50"/>
-      <c r="AA47" s="50"/>
-      <c r="AB47" s="51"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="36"/>
+      <c r="P47" s="36"/>
+      <c r="Q47" s="36"/>
+      <c r="R47" s="36"/>
+      <c r="S47" s="36"/>
+      <c r="T47" s="36"/>
+      <c r="U47" s="36"/>
+      <c r="V47" s="36"/>
+      <c r="W47" s="36"/>
+      <c r="X47" s="36"/>
+      <c r="Y47" s="36"/>
+      <c r="Z47" s="36"/>
+      <c r="AA47" s="36"/>
+      <c r="AB47" s="37"/>
       <c r="AC47" s="11"/>
     </row>
     <row r="48" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3365,27 +3416,27 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="50"/>
-      <c r="J48" s="50"/>
-      <c r="K48" s="50"/>
-      <c r="L48" s="50"/>
-      <c r="M48" s="50"/>
-      <c r="N48" s="50"/>
-      <c r="O48" s="50"/>
-      <c r="P48" s="50"/>
-      <c r="Q48" s="50"/>
-      <c r="R48" s="50"/>
-      <c r="S48" s="50"/>
-      <c r="T48" s="50"/>
-      <c r="U48" s="50"/>
-      <c r="V48" s="50"/>
-      <c r="W48" s="50"/>
-      <c r="X48" s="50"/>
-      <c r="Y48" s="50"/>
-      <c r="Z48" s="50"/>
-      <c r="AA48" s="50"/>
-      <c r="AB48" s="51"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="36"/>
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="36"/>
+      <c r="P48" s="36"/>
+      <c r="Q48" s="36"/>
+      <c r="R48" s="36"/>
+      <c r="S48" s="36"/>
+      <c r="T48" s="36"/>
+      <c r="U48" s="36"/>
+      <c r="V48" s="36"/>
+      <c r="W48" s="36"/>
+      <c r="X48" s="36"/>
+      <c r="Y48" s="36"/>
+      <c r="Z48" s="36"/>
+      <c r="AA48" s="36"/>
+      <c r="AB48" s="37"/>
       <c r="AC48" s="11"/>
     </row>
     <row r="49" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3395,27 +3446,27 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="50"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="50"/>
-      <c r="P49" s="50"/>
-      <c r="Q49" s="50"/>
-      <c r="R49" s="50"/>
-      <c r="S49" s="50"/>
-      <c r="T49" s="50"/>
-      <c r="U49" s="50"/>
-      <c r="V49" s="50"/>
-      <c r="W49" s="50"/>
-      <c r="X49" s="50"/>
-      <c r="Y49" s="50"/>
-      <c r="Z49" s="50"/>
-      <c r="AA49" s="50"/>
-      <c r="AB49" s="51"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="36"/>
+      <c r="M49" s="36"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="36"/>
+      <c r="P49" s="36"/>
+      <c r="Q49" s="36"/>
+      <c r="R49" s="36"/>
+      <c r="S49" s="36"/>
+      <c r="T49" s="36"/>
+      <c r="U49" s="36"/>
+      <c r="V49" s="36"/>
+      <c r="W49" s="36"/>
+      <c r="X49" s="36"/>
+      <c r="Y49" s="36"/>
+      <c r="Z49" s="36"/>
+      <c r="AA49" s="36"/>
+      <c r="AB49" s="37"/>
       <c r="AC49" s="11"/>
     </row>
     <row r="50" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3425,27 +3476,27 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="50"/>
-      <c r="K50" s="50"/>
-      <c r="L50" s="50"/>
-      <c r="M50" s="50"/>
-      <c r="N50" s="50"/>
-      <c r="O50" s="50"/>
-      <c r="P50" s="50"/>
-      <c r="Q50" s="50"/>
-      <c r="R50" s="50"/>
-      <c r="S50" s="50"/>
-      <c r="T50" s="50"/>
-      <c r="U50" s="50"/>
-      <c r="V50" s="50"/>
-      <c r="W50" s="50"/>
-      <c r="X50" s="50"/>
-      <c r="Y50" s="50"/>
-      <c r="Z50" s="50"/>
-      <c r="AA50" s="50"/>
-      <c r="AB50" s="51"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="36"/>
+      <c r="O50" s="36"/>
+      <c r="P50" s="36"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="36"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36"/>
+      <c r="U50" s="36"/>
+      <c r="V50" s="36"/>
+      <c r="W50" s="36"/>
+      <c r="X50" s="36"/>
+      <c r="Y50" s="36"/>
+      <c r="Z50" s="36"/>
+      <c r="AA50" s="36"/>
+      <c r="AB50" s="37"/>
       <c r="AC50" s="11"/>
     </row>
     <row r="51" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3455,27 +3506,27 @@
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="50"/>
-      <c r="J51" s="50"/>
-      <c r="K51" s="50"/>
-      <c r="L51" s="50"/>
-      <c r="M51" s="50"/>
-      <c r="N51" s="50"/>
-      <c r="O51" s="50"/>
-      <c r="P51" s="50"/>
-      <c r="Q51" s="50"/>
-      <c r="R51" s="50"/>
-      <c r="S51" s="50"/>
-      <c r="T51" s="50"/>
-      <c r="U51" s="50"/>
-      <c r="V51" s="50"/>
-      <c r="W51" s="50"/>
-      <c r="X51" s="50"/>
-      <c r="Y51" s="50"/>
-      <c r="Z51" s="50"/>
-      <c r="AA51" s="50"/>
-      <c r="AB51" s="51"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="36"/>
+      <c r="J51" s="36"/>
+      <c r="K51" s="36"/>
+      <c r="L51" s="36"/>
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="36"/>
+      <c r="P51" s="36"/>
+      <c r="Q51" s="36"/>
+      <c r="R51" s="36"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36"/>
+      <c r="U51" s="36"/>
+      <c r="V51" s="36"/>
+      <c r="W51" s="36"/>
+      <c r="X51" s="36"/>
+      <c r="Y51" s="36"/>
+      <c r="Z51" s="36"/>
+      <c r="AA51" s="36"/>
+      <c r="AB51" s="37"/>
       <c r="AC51" s="11"/>
     </row>
     <row r="52" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3485,27 +3536,27 @@
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="53"/>
-      <c r="J52" s="53"/>
-      <c r="K52" s="53"/>
-      <c r="L52" s="53"/>
-      <c r="M52" s="53"/>
-      <c r="N52" s="53"/>
-      <c r="O52" s="53"/>
-      <c r="P52" s="53"/>
-      <c r="Q52" s="53"/>
-      <c r="R52" s="53"/>
-      <c r="S52" s="53"/>
-      <c r="T52" s="53"/>
-      <c r="U52" s="53"/>
-      <c r="V52" s="53"/>
-      <c r="W52" s="53"/>
-      <c r="X52" s="53"/>
-      <c r="Y52" s="53"/>
-      <c r="Z52" s="53"/>
-      <c r="AA52" s="53"/>
-      <c r="AB52" s="54"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="39"/>
+      <c r="M52" s="39"/>
+      <c r="N52" s="39"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="39"/>
+      <c r="S52" s="39"/>
+      <c r="T52" s="39"/>
+      <c r="U52" s="39"/>
+      <c r="V52" s="39"/>
+      <c r="W52" s="39"/>
+      <c r="X52" s="39"/>
+      <c r="Y52" s="39"/>
+      <c r="Z52" s="39"/>
+      <c r="AA52" s="39"/>
+      <c r="AB52" s="40"/>
       <c r="AC52" s="11"/>
     </row>
     <row r="53" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3547,27 +3598,29 @@
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="47"/>
-      <c r="J54" s="47"/>
-      <c r="K54" s="47"/>
-      <c r="L54" s="47"/>
-      <c r="M54" s="47"/>
-      <c r="N54" s="47"/>
-      <c r="O54" s="47"/>
-      <c r="P54" s="47"/>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47"/>
-      <c r="S54" s="47"/>
-      <c r="T54" s="47"/>
-      <c r="U54" s="47"/>
-      <c r="V54" s="47"/>
-      <c r="W54" s="47"/>
-      <c r="X54" s="47"/>
-      <c r="Y54" s="47"/>
-      <c r="Z54" s="47"/>
-      <c r="AA54" s="47"/>
-      <c r="AB54" s="48"/>
+      <c r="H54" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="33"/>
+      <c r="M54" s="33"/>
+      <c r="N54" s="33"/>
+      <c r="O54" s="33"/>
+      <c r="P54" s="33"/>
+      <c r="Q54" s="33"/>
+      <c r="R54" s="33"/>
+      <c r="S54" s="33"/>
+      <c r="T54" s="33"/>
+      <c r="U54" s="33"/>
+      <c r="V54" s="33"/>
+      <c r="W54" s="33"/>
+      <c r="X54" s="33"/>
+      <c r="Y54" s="33"/>
+      <c r="Z54" s="33"/>
+      <c r="AA54" s="33"/>
+      <c r="AB54" s="34"/>
       <c r="AC54" s="11"/>
     </row>
     <row r="55" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3577,27 +3630,27 @@
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="50"/>
-      <c r="J55" s="50"/>
-      <c r="K55" s="50"/>
-      <c r="L55" s="50"/>
-      <c r="M55" s="50"/>
-      <c r="N55" s="50"/>
-      <c r="O55" s="50"/>
-      <c r="P55" s="50"/>
-      <c r="Q55" s="50"/>
-      <c r="R55" s="50"/>
-      <c r="S55" s="50"/>
-      <c r="T55" s="50"/>
-      <c r="U55" s="50"/>
-      <c r="V55" s="50"/>
-      <c r="W55" s="50"/>
-      <c r="X55" s="50"/>
-      <c r="Y55" s="50"/>
-      <c r="Z55" s="50"/>
-      <c r="AA55" s="50"/>
-      <c r="AB55" s="51"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
+      <c r="L55" s="36"/>
+      <c r="M55" s="36"/>
+      <c r="N55" s="36"/>
+      <c r="O55" s="36"/>
+      <c r="P55" s="36"/>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="36"/>
+      <c r="S55" s="36"/>
+      <c r="T55" s="36"/>
+      <c r="U55" s="36"/>
+      <c r="V55" s="36"/>
+      <c r="W55" s="36"/>
+      <c r="X55" s="36"/>
+      <c r="Y55" s="36"/>
+      <c r="Z55" s="36"/>
+      <c r="AA55" s="36"/>
+      <c r="AB55" s="37"/>
       <c r="AC55" s="11"/>
     </row>
     <row r="56" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3607,27 +3660,27 @@
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="50"/>
-      <c r="L56" s="50"/>
-      <c r="M56" s="50"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="50"/>
-      <c r="P56" s="50"/>
-      <c r="Q56" s="50"/>
-      <c r="R56" s="50"/>
-      <c r="S56" s="50"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="50"/>
-      <c r="V56" s="50"/>
-      <c r="W56" s="50"/>
-      <c r="X56" s="50"/>
-      <c r="Y56" s="50"/>
-      <c r="Z56" s="50"/>
-      <c r="AA56" s="50"/>
-      <c r="AB56" s="51"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="36"/>
+      <c r="P56" s="36"/>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="36"/>
+      <c r="S56" s="36"/>
+      <c r="T56" s="36"/>
+      <c r="U56" s="36"/>
+      <c r="V56" s="36"/>
+      <c r="W56" s="36"/>
+      <c r="X56" s="36"/>
+      <c r="Y56" s="36"/>
+      <c r="Z56" s="36"/>
+      <c r="AA56" s="36"/>
+      <c r="AB56" s="37"/>
       <c r="AC56" s="11"/>
     </row>
     <row r="57" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3637,27 +3690,27 @@
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="50"/>
-      <c r="J57" s="50"/>
-      <c r="K57" s="50"/>
-      <c r="L57" s="50"/>
-      <c r="M57" s="50"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="50"/>
-      <c r="P57" s="50"/>
-      <c r="Q57" s="50"/>
-      <c r="R57" s="50"/>
-      <c r="S57" s="50"/>
-      <c r="T57" s="50"/>
-      <c r="U57" s="50"/>
-      <c r="V57" s="50"/>
-      <c r="W57" s="50"/>
-      <c r="X57" s="50"/>
-      <c r="Y57" s="50"/>
-      <c r="Z57" s="50"/>
-      <c r="AA57" s="50"/>
-      <c r="AB57" s="51"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="36"/>
+      <c r="K57" s="36"/>
+      <c r="L57" s="36"/>
+      <c r="M57" s="36"/>
+      <c r="N57" s="36"/>
+      <c r="O57" s="36"/>
+      <c r="P57" s="36"/>
+      <c r="Q57" s="36"/>
+      <c r="R57" s="36"/>
+      <c r="S57" s="36"/>
+      <c r="T57" s="36"/>
+      <c r="U57" s="36"/>
+      <c r="V57" s="36"/>
+      <c r="W57" s="36"/>
+      <c r="X57" s="36"/>
+      <c r="Y57" s="36"/>
+      <c r="Z57" s="36"/>
+      <c r="AA57" s="36"/>
+      <c r="AB57" s="37"/>
       <c r="AC57" s="11"/>
     </row>
     <row r="58" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3667,27 +3720,27 @@
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
-      <c r="K58" s="50"/>
-      <c r="L58" s="50"/>
-      <c r="M58" s="50"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="50"/>
-      <c r="P58" s="50"/>
-      <c r="Q58" s="50"/>
-      <c r="R58" s="50"/>
-      <c r="S58" s="50"/>
-      <c r="T58" s="50"/>
-      <c r="U58" s="50"/>
-      <c r="V58" s="50"/>
-      <c r="W58" s="50"/>
-      <c r="X58" s="50"/>
-      <c r="Y58" s="50"/>
-      <c r="Z58" s="50"/>
-      <c r="AA58" s="50"/>
-      <c r="AB58" s="51"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
+      <c r="K58" s="36"/>
+      <c r="L58" s="36"/>
+      <c r="M58" s="36"/>
+      <c r="N58" s="36"/>
+      <c r="O58" s="36"/>
+      <c r="P58" s="36"/>
+      <c r="Q58" s="36"/>
+      <c r="R58" s="36"/>
+      <c r="S58" s="36"/>
+      <c r="T58" s="36"/>
+      <c r="U58" s="36"/>
+      <c r="V58" s="36"/>
+      <c r="W58" s="36"/>
+      <c r="X58" s="36"/>
+      <c r="Y58" s="36"/>
+      <c r="Z58" s="36"/>
+      <c r="AA58" s="36"/>
+      <c r="AB58" s="37"/>
       <c r="AC58" s="11"/>
     </row>
     <row r="59" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3697,27 +3750,27 @@
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="50"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="50"/>
-      <c r="M59" s="50"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="50"/>
-      <c r="Q59" s="50"/>
-      <c r="R59" s="50"/>
-      <c r="S59" s="50"/>
-      <c r="T59" s="50"/>
-      <c r="U59" s="50"/>
-      <c r="V59" s="50"/>
-      <c r="W59" s="50"/>
-      <c r="X59" s="50"/>
-      <c r="Y59" s="50"/>
-      <c r="Z59" s="50"/>
-      <c r="AA59" s="50"/>
-      <c r="AB59" s="51"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36"/>
+      <c r="O59" s="36"/>
+      <c r="P59" s="36"/>
+      <c r="Q59" s="36"/>
+      <c r="R59" s="36"/>
+      <c r="S59" s="36"/>
+      <c r="T59" s="36"/>
+      <c r="U59" s="36"/>
+      <c r="V59" s="36"/>
+      <c r="W59" s="36"/>
+      <c r="X59" s="36"/>
+      <c r="Y59" s="36"/>
+      <c r="Z59" s="36"/>
+      <c r="AA59" s="36"/>
+      <c r="AB59" s="37"/>
       <c r="AC59" s="11"/>
     </row>
     <row r="60" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3727,27 +3780,27 @@
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="53"/>
-      <c r="J60" s="53"/>
-      <c r="K60" s="53"/>
-      <c r="L60" s="53"/>
-      <c r="M60" s="53"/>
-      <c r="N60" s="53"/>
-      <c r="O60" s="53"/>
-      <c r="P60" s="53"/>
-      <c r="Q60" s="53"/>
-      <c r="R60" s="53"/>
-      <c r="S60" s="53"/>
-      <c r="T60" s="53"/>
-      <c r="U60" s="53"/>
-      <c r="V60" s="53"/>
-      <c r="W60" s="53"/>
-      <c r="X60" s="53"/>
-      <c r="Y60" s="53"/>
-      <c r="Z60" s="53"/>
-      <c r="AA60" s="53"/>
-      <c r="AB60" s="54"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+      <c r="L60" s="39"/>
+      <c r="M60" s="39"/>
+      <c r="N60" s="39"/>
+      <c r="O60" s="39"/>
+      <c r="P60" s="39"/>
+      <c r="Q60" s="39"/>
+      <c r="R60" s="39"/>
+      <c r="S60" s="39"/>
+      <c r="T60" s="39"/>
+      <c r="U60" s="39"/>
+      <c r="V60" s="39"/>
+      <c r="W60" s="39"/>
+      <c r="X60" s="39"/>
+      <c r="Y60" s="39"/>
+      <c r="Z60" s="39"/>
+      <c r="AA60" s="39"/>
+      <c r="AB60" s="40"/>
       <c r="AC60" s="11"/>
     </row>
     <row r="61" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3849,33 +3902,37 @@
     <row r="65" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="44"/>
       <c r="C65" s="5"/>
-      <c r="D65" s="41"/>
+      <c r="D65" s="41" t="s">
+        <v>61</v>
+      </c>
       <c r="E65" s="42"/>
       <c r="F65" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G65" s="6"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="47"/>
-      <c r="J65" s="47"/>
-      <c r="K65" s="47"/>
-      <c r="L65" s="47"/>
-      <c r="M65" s="47"/>
-      <c r="N65" s="47"/>
-      <c r="O65" s="47"/>
-      <c r="P65" s="47"/>
-      <c r="Q65" s="47"/>
-      <c r="R65" s="47"/>
-      <c r="S65" s="47"/>
-      <c r="T65" s="47"/>
-      <c r="U65" s="47"/>
-      <c r="V65" s="47"/>
-      <c r="W65" s="47"/>
-      <c r="X65" s="47"/>
-      <c r="Y65" s="47"/>
-      <c r="Z65" s="47"/>
-      <c r="AA65" s="47"/>
-      <c r="AB65" s="48"/>
+      <c r="H65" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="I65" s="33"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
+      <c r="M65" s="33"/>
+      <c r="N65" s="33"/>
+      <c r="O65" s="33"/>
+      <c r="P65" s="33"/>
+      <c r="Q65" s="33"/>
+      <c r="R65" s="33"/>
+      <c r="S65" s="33"/>
+      <c r="T65" s="33"/>
+      <c r="U65" s="33"/>
+      <c r="V65" s="33"/>
+      <c r="W65" s="33"/>
+      <c r="X65" s="33"/>
+      <c r="Y65" s="33"/>
+      <c r="Z65" s="33"/>
+      <c r="AA65" s="33"/>
+      <c r="AB65" s="34"/>
       <c r="AC65" s="11"/>
     </row>
     <row r="66" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3885,27 +3942,27 @@
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
-      <c r="H66" s="49"/>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="50"/>
-      <c r="M66" s="50"/>
-      <c r="N66" s="50"/>
-      <c r="O66" s="50"/>
-      <c r="P66" s="50"/>
-      <c r="Q66" s="50"/>
-      <c r="R66" s="50"/>
-      <c r="S66" s="50"/>
-      <c r="T66" s="50"/>
-      <c r="U66" s="50"/>
-      <c r="V66" s="50"/>
-      <c r="W66" s="50"/>
-      <c r="X66" s="50"/>
-      <c r="Y66" s="50"/>
-      <c r="Z66" s="50"/>
-      <c r="AA66" s="50"/>
-      <c r="AB66" s="51"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="66"/>
+      <c r="J66" s="66"/>
+      <c r="K66" s="66"/>
+      <c r="L66" s="66"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="66"/>
+      <c r="O66" s="66"/>
+      <c r="P66" s="66"/>
+      <c r="Q66" s="66"/>
+      <c r="R66" s="66"/>
+      <c r="S66" s="66"/>
+      <c r="T66" s="66"/>
+      <c r="U66" s="66"/>
+      <c r="V66" s="66"/>
+      <c r="W66" s="66"/>
+      <c r="X66" s="66"/>
+      <c r="Y66" s="66"/>
+      <c r="Z66" s="66"/>
+      <c r="AA66" s="66"/>
+      <c r="AB66" s="37"/>
       <c r="AC66" s="11"/>
     </row>
     <row r="67" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3915,27 +3972,27 @@
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
-      <c r="H67" s="49"/>
-      <c r="I67" s="50"/>
-      <c r="J67" s="50"/>
-      <c r="K67" s="50"/>
-      <c r="L67" s="50"/>
-      <c r="M67" s="50"/>
-      <c r="N67" s="50"/>
-      <c r="O67" s="50"/>
-      <c r="P67" s="50"/>
-      <c r="Q67" s="50"/>
-      <c r="R67" s="50"/>
-      <c r="S67" s="50"/>
-      <c r="T67" s="50"/>
-      <c r="U67" s="50"/>
-      <c r="V67" s="50"/>
-      <c r="W67" s="50"/>
-      <c r="X67" s="50"/>
-      <c r="Y67" s="50"/>
-      <c r="Z67" s="50"/>
-      <c r="AA67" s="50"/>
-      <c r="AB67" s="51"/>
+      <c r="H67" s="35"/>
+      <c r="I67" s="66"/>
+      <c r="J67" s="66"/>
+      <c r="K67" s="66"/>
+      <c r="L67" s="66"/>
+      <c r="M67" s="66"/>
+      <c r="N67" s="66"/>
+      <c r="O67" s="66"/>
+      <c r="P67" s="66"/>
+      <c r="Q67" s="66"/>
+      <c r="R67" s="66"/>
+      <c r="S67" s="66"/>
+      <c r="T67" s="66"/>
+      <c r="U67" s="66"/>
+      <c r="V67" s="66"/>
+      <c r="W67" s="66"/>
+      <c r="X67" s="66"/>
+      <c r="Y67" s="66"/>
+      <c r="Z67" s="66"/>
+      <c r="AA67" s="66"/>
+      <c r="AB67" s="37"/>
       <c r="AC67" s="11"/>
     </row>
     <row r="68" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3945,27 +4002,27 @@
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="50"/>
-      <c r="J68" s="50"/>
-      <c r="K68" s="50"/>
-      <c r="L68" s="50"/>
-      <c r="M68" s="50"/>
-      <c r="N68" s="50"/>
-      <c r="O68" s="50"/>
-      <c r="P68" s="50"/>
-      <c r="Q68" s="50"/>
-      <c r="R68" s="50"/>
-      <c r="S68" s="50"/>
-      <c r="T68" s="50"/>
-      <c r="U68" s="50"/>
-      <c r="V68" s="50"/>
-      <c r="W68" s="50"/>
-      <c r="X68" s="50"/>
-      <c r="Y68" s="50"/>
-      <c r="Z68" s="50"/>
-      <c r="AA68" s="50"/>
-      <c r="AB68" s="51"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="66"/>
+      <c r="J68" s="66"/>
+      <c r="K68" s="66"/>
+      <c r="L68" s="66"/>
+      <c r="M68" s="66"/>
+      <c r="N68" s="66"/>
+      <c r="O68" s="66"/>
+      <c r="P68" s="66"/>
+      <c r="Q68" s="66"/>
+      <c r="R68" s="66"/>
+      <c r="S68" s="66"/>
+      <c r="T68" s="66"/>
+      <c r="U68" s="66"/>
+      <c r="V68" s="66"/>
+      <c r="W68" s="66"/>
+      <c r="X68" s="66"/>
+      <c r="Y68" s="66"/>
+      <c r="Z68" s="66"/>
+      <c r="AA68" s="66"/>
+      <c r="AB68" s="37"/>
       <c r="AC68" s="11"/>
     </row>
     <row r="69" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3975,27 +4032,27 @@
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
-      <c r="H69" s="49"/>
-      <c r="I69" s="50"/>
-      <c r="J69" s="50"/>
-      <c r="K69" s="50"/>
-      <c r="L69" s="50"/>
-      <c r="M69" s="50"/>
-      <c r="N69" s="50"/>
-      <c r="O69" s="50"/>
-      <c r="P69" s="50"/>
-      <c r="Q69" s="50"/>
-      <c r="R69" s="50"/>
-      <c r="S69" s="50"/>
-      <c r="T69" s="50"/>
-      <c r="U69" s="50"/>
-      <c r="V69" s="50"/>
-      <c r="W69" s="50"/>
-      <c r="X69" s="50"/>
-      <c r="Y69" s="50"/>
-      <c r="Z69" s="50"/>
-      <c r="AA69" s="50"/>
-      <c r="AB69" s="51"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="66"/>
+      <c r="J69" s="66"/>
+      <c r="K69" s="66"/>
+      <c r="L69" s="66"/>
+      <c r="M69" s="66"/>
+      <c r="N69" s="66"/>
+      <c r="O69" s="66"/>
+      <c r="P69" s="66"/>
+      <c r="Q69" s="66"/>
+      <c r="R69" s="66"/>
+      <c r="S69" s="66"/>
+      <c r="T69" s="66"/>
+      <c r="U69" s="66"/>
+      <c r="V69" s="66"/>
+      <c r="W69" s="66"/>
+      <c r="X69" s="66"/>
+      <c r="Y69" s="66"/>
+      <c r="Z69" s="66"/>
+      <c r="AA69" s="66"/>
+      <c r="AB69" s="37"/>
       <c r="AC69" s="11"/>
     </row>
     <row r="70" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4005,27 +4062,27 @@
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="50"/>
-      <c r="J70" s="50"/>
-      <c r="K70" s="50"/>
-      <c r="L70" s="50"/>
-      <c r="M70" s="50"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="50"/>
-      <c r="P70" s="50"/>
-      <c r="Q70" s="50"/>
-      <c r="R70" s="50"/>
-      <c r="S70" s="50"/>
-      <c r="T70" s="50"/>
-      <c r="U70" s="50"/>
-      <c r="V70" s="50"/>
-      <c r="W70" s="50"/>
-      <c r="X70" s="50"/>
-      <c r="Y70" s="50"/>
-      <c r="Z70" s="50"/>
-      <c r="AA70" s="50"/>
-      <c r="AB70" s="51"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="66"/>
+      <c r="J70" s="66"/>
+      <c r="K70" s="66"/>
+      <c r="L70" s="66"/>
+      <c r="M70" s="66"/>
+      <c r="N70" s="66"/>
+      <c r="O70" s="66"/>
+      <c r="P70" s="66"/>
+      <c r="Q70" s="66"/>
+      <c r="R70" s="66"/>
+      <c r="S70" s="66"/>
+      <c r="T70" s="66"/>
+      <c r="U70" s="66"/>
+      <c r="V70" s="66"/>
+      <c r="W70" s="66"/>
+      <c r="X70" s="66"/>
+      <c r="Y70" s="66"/>
+      <c r="Z70" s="66"/>
+      <c r="AA70" s="66"/>
+      <c r="AB70" s="37"/>
       <c r="AC70" s="11"/>
     </row>
     <row r="71" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4035,27 +4092,27 @@
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
-      <c r="H71" s="52"/>
-      <c r="I71" s="53"/>
-      <c r="J71" s="53"/>
-      <c r="K71" s="53"/>
-      <c r="L71" s="53"/>
-      <c r="M71" s="53"/>
-      <c r="N71" s="53"/>
-      <c r="O71" s="53"/>
-      <c r="P71" s="53"/>
-      <c r="Q71" s="53"/>
-      <c r="R71" s="53"/>
-      <c r="S71" s="53"/>
-      <c r="T71" s="53"/>
-      <c r="U71" s="53"/>
-      <c r="V71" s="53"/>
-      <c r="W71" s="53"/>
-      <c r="X71" s="53"/>
-      <c r="Y71" s="53"/>
-      <c r="Z71" s="53"/>
-      <c r="AA71" s="53"/>
-      <c r="AB71" s="54"/>
+      <c r="H71" s="35"/>
+      <c r="I71" s="66"/>
+      <c r="J71" s="66"/>
+      <c r="K71" s="66"/>
+      <c r="L71" s="66"/>
+      <c r="M71" s="66"/>
+      <c r="N71" s="66"/>
+      <c r="O71" s="66"/>
+      <c r="P71" s="66"/>
+      <c r="Q71" s="66"/>
+      <c r="R71" s="66"/>
+      <c r="S71" s="66"/>
+      <c r="T71" s="66"/>
+      <c r="U71" s="66"/>
+      <c r="V71" s="66"/>
+      <c r="W71" s="66"/>
+      <c r="X71" s="66"/>
+      <c r="Y71" s="66"/>
+      <c r="Z71" s="66"/>
+      <c r="AA71" s="66"/>
+      <c r="AB71" s="37"/>
       <c r="AC71" s="11"/>
     </row>
     <row r="72" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4065,29 +4122,27 @@
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
-      <c r="H72" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="6"/>
-      <c r="O72" s="6"/>
-      <c r="P72" s="6"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
-      <c r="V72" s="6"/>
-      <c r="W72" s="6"/>
-      <c r="X72" s="6"/>
-      <c r="Y72" s="6"/>
-      <c r="Z72" s="6"/>
-      <c r="AA72" s="6"/>
-      <c r="AB72" s="6"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="66"/>
+      <c r="J72" s="66"/>
+      <c r="K72" s="66"/>
+      <c r="L72" s="66"/>
+      <c r="M72" s="66"/>
+      <c r="N72" s="66"/>
+      <c r="O72" s="66"/>
+      <c r="P72" s="66"/>
+      <c r="Q72" s="66"/>
+      <c r="R72" s="66"/>
+      <c r="S72" s="66"/>
+      <c r="T72" s="66"/>
+      <c r="U72" s="66"/>
+      <c r="V72" s="66"/>
+      <c r="W72" s="66"/>
+      <c r="X72" s="66"/>
+      <c r="Y72" s="66"/>
+      <c r="Z72" s="66"/>
+      <c r="AA72" s="66"/>
+      <c r="AB72" s="37"/>
       <c r="AC72" s="11"/>
     </row>
     <row r="73" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4097,27 +4152,27 @@
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
-      <c r="H73" s="46"/>
-      <c r="I73" s="47"/>
-      <c r="J73" s="47"/>
-      <c r="K73" s="47"/>
-      <c r="L73" s="47"/>
-      <c r="M73" s="47"/>
-      <c r="N73" s="47"/>
-      <c r="O73" s="47"/>
-      <c r="P73" s="47"/>
-      <c r="Q73" s="47"/>
-      <c r="R73" s="47"/>
-      <c r="S73" s="47"/>
-      <c r="T73" s="47"/>
-      <c r="U73" s="47"/>
-      <c r="V73" s="47"/>
-      <c r="W73" s="47"/>
-      <c r="X73" s="47"/>
-      <c r="Y73" s="47"/>
-      <c r="Z73" s="47"/>
-      <c r="AA73" s="47"/>
-      <c r="AB73" s="48"/>
+      <c r="H73" s="35"/>
+      <c r="I73" s="66"/>
+      <c r="J73" s="66"/>
+      <c r="K73" s="66"/>
+      <c r="L73" s="66"/>
+      <c r="M73" s="66"/>
+      <c r="N73" s="66"/>
+      <c r="O73" s="66"/>
+      <c r="P73" s="66"/>
+      <c r="Q73" s="66"/>
+      <c r="R73" s="66"/>
+      <c r="S73" s="66"/>
+      <c r="T73" s="66"/>
+      <c r="U73" s="66"/>
+      <c r="V73" s="66"/>
+      <c r="W73" s="66"/>
+      <c r="X73" s="66"/>
+      <c r="Y73" s="66"/>
+      <c r="Z73" s="66"/>
+      <c r="AA73" s="66"/>
+      <c r="AB73" s="37"/>
       <c r="AC73" s="11"/>
     </row>
     <row r="74" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4127,27 +4182,27 @@
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="50"/>
-      <c r="J74" s="50"/>
-      <c r="K74" s="50"/>
-      <c r="L74" s="50"/>
-      <c r="M74" s="50"/>
-      <c r="N74" s="50"/>
-      <c r="O74" s="50"/>
-      <c r="P74" s="50"/>
-      <c r="Q74" s="50"/>
-      <c r="R74" s="50"/>
-      <c r="S74" s="50"/>
-      <c r="T74" s="50"/>
-      <c r="U74" s="50"/>
-      <c r="V74" s="50"/>
-      <c r="W74" s="50"/>
-      <c r="X74" s="50"/>
-      <c r="Y74" s="50"/>
-      <c r="Z74" s="50"/>
-      <c r="AA74" s="50"/>
-      <c r="AB74" s="51"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="39"/>
+      <c r="J74" s="39"/>
+      <c r="K74" s="39"/>
+      <c r="L74" s="39"/>
+      <c r="M74" s="39"/>
+      <c r="N74" s="39"/>
+      <c r="O74" s="39"/>
+      <c r="P74" s="39"/>
+      <c r="Q74" s="39"/>
+      <c r="R74" s="39"/>
+      <c r="S74" s="39"/>
+      <c r="T74" s="39"/>
+      <c r="U74" s="39"/>
+      <c r="V74" s="39"/>
+      <c r="W74" s="39"/>
+      <c r="X74" s="39"/>
+      <c r="Y74" s="39"/>
+      <c r="Z74" s="39"/>
+      <c r="AA74" s="39"/>
+      <c r="AB74" s="40"/>
       <c r="AC74" s="11"/>
     </row>
     <row r="75" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4157,27 +4212,29 @@
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="50"/>
-      <c r="J75" s="50"/>
-      <c r="K75" s="50"/>
-      <c r="L75" s="50"/>
-      <c r="M75" s="50"/>
-      <c r="N75" s="50"/>
-      <c r="O75" s="50"/>
-      <c r="P75" s="50"/>
-      <c r="Q75" s="50"/>
-      <c r="R75" s="50"/>
-      <c r="S75" s="50"/>
-      <c r="T75" s="50"/>
-      <c r="U75" s="50"/>
-      <c r="V75" s="50"/>
-      <c r="W75" s="50"/>
-      <c r="X75" s="50"/>
-      <c r="Y75" s="50"/>
-      <c r="Z75" s="50"/>
-      <c r="AA75" s="50"/>
-      <c r="AB75" s="51"/>
+      <c r="H75" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
+      <c r="P75" s="6"/>
+      <c r="Q75" s="6"/>
+      <c r="R75" s="6"/>
+      <c r="S75" s="6"/>
+      <c r="T75" s="6"/>
+      <c r="U75" s="6"/>
+      <c r="V75" s="6"/>
+      <c r="W75" s="6"/>
+      <c r="X75" s="6"/>
+      <c r="Y75" s="6"/>
+      <c r="Z75" s="6"/>
+      <c r="AA75" s="6"/>
+      <c r="AB75" s="6"/>
       <c r="AC75" s="11"/>
     </row>
     <row r="76" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4187,27 +4244,29 @@
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="50"/>
-      <c r="J76" s="50"/>
-      <c r="K76" s="50"/>
-      <c r="L76" s="50"/>
-      <c r="M76" s="50"/>
-      <c r="N76" s="50"/>
-      <c r="O76" s="50"/>
-      <c r="P76" s="50"/>
-      <c r="Q76" s="50"/>
-      <c r="R76" s="50"/>
-      <c r="S76" s="50"/>
-      <c r="T76" s="50"/>
-      <c r="U76" s="50"/>
-      <c r="V76" s="50"/>
-      <c r="W76" s="50"/>
-      <c r="X76" s="50"/>
-      <c r="Y76" s="50"/>
-      <c r="Z76" s="50"/>
-      <c r="AA76" s="50"/>
-      <c r="AB76" s="51"/>
+      <c r="H76" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="I76" s="33"/>
+      <c r="J76" s="33"/>
+      <c r="K76" s="33"/>
+      <c r="L76" s="33"/>
+      <c r="M76" s="33"/>
+      <c r="N76" s="33"/>
+      <c r="O76" s="33"/>
+      <c r="P76" s="33"/>
+      <c r="Q76" s="33"/>
+      <c r="R76" s="33"/>
+      <c r="S76" s="33"/>
+      <c r="T76" s="33"/>
+      <c r="U76" s="33"/>
+      <c r="V76" s="33"/>
+      <c r="W76" s="33"/>
+      <c r="X76" s="33"/>
+      <c r="Y76" s="33"/>
+      <c r="Z76" s="33"/>
+      <c r="AA76" s="33"/>
+      <c r="AB76" s="34"/>
       <c r="AC76" s="11"/>
     </row>
     <row r="77" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4217,27 +4276,27 @@
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="50"/>
-      <c r="J77" s="50"/>
-      <c r="K77" s="50"/>
-      <c r="L77" s="50"/>
-      <c r="M77" s="50"/>
-      <c r="N77" s="50"/>
-      <c r="O77" s="50"/>
-      <c r="P77" s="50"/>
-      <c r="Q77" s="50"/>
-      <c r="R77" s="50"/>
-      <c r="S77" s="50"/>
-      <c r="T77" s="50"/>
-      <c r="U77" s="50"/>
-      <c r="V77" s="50"/>
-      <c r="W77" s="50"/>
-      <c r="X77" s="50"/>
-      <c r="Y77" s="50"/>
-      <c r="Z77" s="50"/>
-      <c r="AA77" s="50"/>
-      <c r="AB77" s="51"/>
+      <c r="H77" s="35"/>
+      <c r="I77" s="36"/>
+      <c r="J77" s="36"/>
+      <c r="K77" s="36"/>
+      <c r="L77" s="36"/>
+      <c r="M77" s="36"/>
+      <c r="N77" s="36"/>
+      <c r="O77" s="36"/>
+      <c r="P77" s="36"/>
+      <c r="Q77" s="36"/>
+      <c r="R77" s="36"/>
+      <c r="S77" s="36"/>
+      <c r="T77" s="36"/>
+      <c r="U77" s="36"/>
+      <c r="V77" s="36"/>
+      <c r="W77" s="36"/>
+      <c r="X77" s="36"/>
+      <c r="Y77" s="36"/>
+      <c r="Z77" s="36"/>
+      <c r="AA77" s="36"/>
+      <c r="AB77" s="37"/>
       <c r="AC77" s="11"/>
     </row>
     <row r="78" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4247,27 +4306,27 @@
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="50"/>
-      <c r="J78" s="50"/>
-      <c r="K78" s="50"/>
-      <c r="L78" s="50"/>
-      <c r="M78" s="50"/>
-      <c r="N78" s="50"/>
-      <c r="O78" s="50"/>
-      <c r="P78" s="50"/>
-      <c r="Q78" s="50"/>
-      <c r="R78" s="50"/>
-      <c r="S78" s="50"/>
-      <c r="T78" s="50"/>
-      <c r="U78" s="50"/>
-      <c r="V78" s="50"/>
-      <c r="W78" s="50"/>
-      <c r="X78" s="50"/>
-      <c r="Y78" s="50"/>
-      <c r="Z78" s="50"/>
-      <c r="AA78" s="50"/>
-      <c r="AB78" s="51"/>
+      <c r="H78" s="35"/>
+      <c r="I78" s="36"/>
+      <c r="J78" s="36"/>
+      <c r="K78" s="36"/>
+      <c r="L78" s="36"/>
+      <c r="M78" s="36"/>
+      <c r="N78" s="36"/>
+      <c r="O78" s="36"/>
+      <c r="P78" s="36"/>
+      <c r="Q78" s="36"/>
+      <c r="R78" s="36"/>
+      <c r="S78" s="36"/>
+      <c r="T78" s="36"/>
+      <c r="U78" s="36"/>
+      <c r="V78" s="36"/>
+      <c r="W78" s="36"/>
+      <c r="X78" s="36"/>
+      <c r="Y78" s="36"/>
+      <c r="Z78" s="36"/>
+      <c r="AA78" s="36"/>
+      <c r="AB78" s="37"/>
       <c r="AC78" s="11"/>
     </row>
     <row r="79" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4277,245 +4336,245 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="53"/>
-      <c r="K79" s="53"/>
-      <c r="L79" s="53"/>
-      <c r="M79" s="53"/>
-      <c r="N79" s="53"/>
-      <c r="O79" s="53"/>
-      <c r="P79" s="53"/>
-      <c r="Q79" s="53"/>
-      <c r="R79" s="53"/>
-      <c r="S79" s="53"/>
-      <c r="T79" s="53"/>
-      <c r="U79" s="53"/>
-      <c r="V79" s="53"/>
-      <c r="W79" s="53"/>
-      <c r="X79" s="53"/>
-      <c r="Y79" s="53"/>
-      <c r="Z79" s="53"/>
-      <c r="AA79" s="53"/>
-      <c r="AB79" s="54"/>
+      <c r="H79" s="35"/>
+      <c r="I79" s="36"/>
+      <c r="J79" s="36"/>
+      <c r="K79" s="36"/>
+      <c r="L79" s="36"/>
+      <c r="M79" s="36"/>
+      <c r="N79" s="36"/>
+      <c r="O79" s="36"/>
+      <c r="P79" s="36"/>
+      <c r="Q79" s="36"/>
+      <c r="R79" s="36"/>
+      <c r="S79" s="36"/>
+      <c r="T79" s="36"/>
+      <c r="U79" s="36"/>
+      <c r="V79" s="36"/>
+      <c r="W79" s="36"/>
+      <c r="X79" s="36"/>
+      <c r="Y79" s="36"/>
+      <c r="Z79" s="36"/>
+      <c r="AA79" s="36"/>
+      <c r="AB79" s="37"/>
       <c r="AC79" s="11"/>
     </row>
     <row r="80" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="45"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="4"/>
-      <c r="S80" s="4"/>
-      <c r="T80" s="4"/>
-      <c r="U80" s="4"/>
-      <c r="V80" s="4"/>
-      <c r="W80" s="4"/>
-      <c r="X80" s="4"/>
-      <c r="Y80" s="4"/>
-      <c r="Z80" s="4"/>
-      <c r="AA80" s="4"/>
-      <c r="AB80" s="4"/>
-      <c r="AC80" s="12"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="35"/>
+      <c r="I80" s="36"/>
+      <c r="J80" s="36"/>
+      <c r="K80" s="36"/>
+      <c r="L80" s="36"/>
+      <c r="M80" s="36"/>
+      <c r="N80" s="36"/>
+      <c r="O80" s="36"/>
+      <c r="P80" s="36"/>
+      <c r="Q80" s="36"/>
+      <c r="R80" s="36"/>
+      <c r="S80" s="36"/>
+      <c r="T80" s="36"/>
+      <c r="U80" s="36"/>
+      <c r="V80" s="36"/>
+      <c r="W80" s="36"/>
+      <c r="X80" s="36"/>
+      <c r="Y80" s="36"/>
+      <c r="Z80" s="36"/>
+      <c r="AA80" s="36"/>
+      <c r="AB80" s="37"/>
+      <c r="AC80" s="11"/>
+    </row>
+    <row r="81" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="44"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="35"/>
+      <c r="I81" s="36"/>
+      <c r="J81" s="36"/>
+      <c r="K81" s="36"/>
+      <c r="L81" s="36"/>
+      <c r="M81" s="36"/>
+      <c r="N81" s="36"/>
+      <c r="O81" s="36"/>
+      <c r="P81" s="36"/>
+      <c r="Q81" s="36"/>
+      <c r="R81" s="36"/>
+      <c r="S81" s="36"/>
+      <c r="T81" s="36"/>
+      <c r="U81" s="36"/>
+      <c r="V81" s="36"/>
+      <c r="W81" s="36"/>
+      <c r="X81" s="36"/>
+      <c r="Y81" s="36"/>
+      <c r="Z81" s="36"/>
+      <c r="AA81" s="36"/>
+      <c r="AB81" s="37"/>
+      <c r="AC81" s="11"/>
     </row>
     <row r="82" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="43" t="s">
+      <c r="B82" s="44"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="39"/>
+      <c r="J82" s="39"/>
+      <c r="K82" s="39"/>
+      <c r="L82" s="39"/>
+      <c r="M82" s="39"/>
+      <c r="N82" s="39"/>
+      <c r="O82" s="39"/>
+      <c r="P82" s="39"/>
+      <c r="Q82" s="39"/>
+      <c r="R82" s="39"/>
+      <c r="S82" s="39"/>
+      <c r="T82" s="39"/>
+      <c r="U82" s="39"/>
+      <c r="V82" s="39"/>
+      <c r="W82" s="39"/>
+      <c r="X82" s="39"/>
+      <c r="Y82" s="39"/>
+      <c r="Z82" s="39"/>
+      <c r="AA82" s="39"/>
+      <c r="AB82" s="40"/>
+      <c r="AC82" s="11"/>
+    </row>
+    <row r="83" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="45"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="4"/>
+      <c r="S83" s="4"/>
+      <c r="T83" s="4"/>
+      <c r="U83" s="4"/>
+      <c r="V83" s="4"/>
+      <c r="W83" s="4"/>
+      <c r="X83" s="4"/>
+      <c r="Y83" s="4"/>
+      <c r="Z83" s="4"/>
+      <c r="AA83" s="4"/>
+      <c r="AB83" s="4"/>
+      <c r="AC83" s="12"/>
+    </row>
+    <row r="85" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="C82" s="8"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9"/>
-      <c r="L82" s="9"/>
-      <c r="M82" s="9"/>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
-      <c r="P82" s="9"/>
-      <c r="Q82" s="9"/>
-      <c r="R82" s="9"/>
-      <c r="S82" s="9"/>
-      <c r="T82" s="9"/>
-      <c r="U82" s="9"/>
-      <c r="V82" s="9"/>
-      <c r="W82" s="9"/>
-      <c r="X82" s="9"/>
-      <c r="Y82" s="9"/>
-      <c r="Z82" s="9"/>
-      <c r="AA82" s="9"/>
-      <c r="AB82" s="9"/>
-      <c r="AC82" s="10"/>
-    </row>
-    <row r="83" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="44"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-      <c r="M83" s="6"/>
-      <c r="N83" s="6"/>
-      <c r="O83" s="6"/>
-      <c r="P83" s="6"/>
-      <c r="Q83" s="6"/>
-      <c r="R83" s="6"/>
-      <c r="S83" s="6"/>
-      <c r="T83" s="6"/>
-      <c r="U83" s="6"/>
-      <c r="V83" s="6"/>
-      <c r="W83" s="6"/>
-      <c r="X83" s="6"/>
-      <c r="Y83" s="6"/>
-      <c r="Z83" s="6"/>
-      <c r="AA83" s="6"/>
-      <c r="AB83" s="6"/>
-      <c r="AC83" s="11"/>
-    </row>
-    <row r="84" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="44"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="42"/>
-      <c r="F84" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G84" s="6"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="47"/>
-      <c r="J84" s="47"/>
-      <c r="K84" s="47"/>
-      <c r="L84" s="47"/>
-      <c r="M84" s="47"/>
-      <c r="N84" s="47"/>
-      <c r="O84" s="47"/>
-      <c r="P84" s="47"/>
-      <c r="Q84" s="47"/>
-      <c r="R84" s="47"/>
-      <c r="S84" s="47"/>
-      <c r="T84" s="47"/>
-      <c r="U84" s="47"/>
-      <c r="V84" s="47"/>
-      <c r="W84" s="47"/>
-      <c r="X84" s="47"/>
-      <c r="Y84" s="47"/>
-      <c r="Z84" s="47"/>
-      <c r="AA84" s="47"/>
-      <c r="AB84" s="48"/>
-      <c r="AC84" s="11"/>
-    </row>
-    <row r="85" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="44"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="49"/>
-      <c r="I85" s="50"/>
-      <c r="J85" s="50"/>
-      <c r="K85" s="50"/>
-      <c r="L85" s="50"/>
-      <c r="M85" s="50"/>
-      <c r="N85" s="50"/>
-      <c r="O85" s="50"/>
-      <c r="P85" s="50"/>
-      <c r="Q85" s="50"/>
-      <c r="R85" s="50"/>
-      <c r="S85" s="50"/>
-      <c r="T85" s="50"/>
-      <c r="U85" s="50"/>
-      <c r="V85" s="50"/>
-      <c r="W85" s="50"/>
-      <c r="X85" s="50"/>
-      <c r="Y85" s="50"/>
-      <c r="Z85" s="50"/>
-      <c r="AA85" s="50"/>
-      <c r="AB85" s="51"/>
-      <c r="AC85" s="11"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+      <c r="N85" s="9"/>
+      <c r="O85" s="9"/>
+      <c r="P85" s="9"/>
+      <c r="Q85" s="9"/>
+      <c r="R85" s="9"/>
+      <c r="S85" s="9"/>
+      <c r="T85" s="9"/>
+      <c r="U85" s="9"/>
+      <c r="V85" s="9"/>
+      <c r="W85" s="9"/>
+      <c r="X85" s="9"/>
+      <c r="Y85" s="9"/>
+      <c r="Z85" s="9"/>
+      <c r="AA85" s="9"/>
+      <c r="AB85" s="9"/>
+      <c r="AC85" s="10"/>
     </row>
     <row r="86" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="44"/>
       <c r="C86" s="5"/>
-      <c r="D86" s="6"/>
+      <c r="D86" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
-      <c r="H86" s="49"/>
-      <c r="I86" s="50"/>
-      <c r="J86" s="50"/>
-      <c r="K86" s="50"/>
-      <c r="L86" s="50"/>
-      <c r="M86" s="50"/>
-      <c r="N86" s="50"/>
-      <c r="O86" s="50"/>
-      <c r="P86" s="50"/>
-      <c r="Q86" s="50"/>
-      <c r="R86" s="50"/>
-      <c r="S86" s="50"/>
-      <c r="T86" s="50"/>
-      <c r="U86" s="50"/>
-      <c r="V86" s="50"/>
-      <c r="W86" s="50"/>
-      <c r="X86" s="50"/>
-      <c r="Y86" s="50"/>
-      <c r="Z86" s="50"/>
-      <c r="AA86" s="50"/>
-      <c r="AB86" s="51"/>
+      <c r="H86" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="6"/>
+      <c r="P86" s="6"/>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="6"/>
+      <c r="T86" s="6"/>
+      <c r="U86" s="6"/>
+      <c r="V86" s="6"/>
+      <c r="W86" s="6"/>
+      <c r="X86" s="6"/>
+      <c r="Y86" s="6"/>
+      <c r="Z86" s="6"/>
+      <c r="AA86" s="6"/>
+      <c r="AB86" s="6"/>
       <c r="AC86" s="11"/>
     </row>
     <row r="87" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="44"/>
       <c r="C87" s="5"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="G87" s="6"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="50"/>
-      <c r="J87" s="50"/>
-      <c r="K87" s="50"/>
-      <c r="L87" s="50"/>
-      <c r="M87" s="50"/>
-      <c r="N87" s="50"/>
-      <c r="O87" s="50"/>
-      <c r="P87" s="50"/>
-      <c r="Q87" s="50"/>
-      <c r="R87" s="50"/>
-      <c r="S87" s="50"/>
-      <c r="T87" s="50"/>
-      <c r="U87" s="50"/>
-      <c r="V87" s="50"/>
-      <c r="W87" s="50"/>
-      <c r="X87" s="50"/>
-      <c r="Y87" s="50"/>
-      <c r="Z87" s="50"/>
-      <c r="AA87" s="50"/>
-      <c r="AB87" s="51"/>
+      <c r="H87" s="46"/>
+      <c r="I87" s="47"/>
+      <c r="J87" s="47"/>
+      <c r="K87" s="47"/>
+      <c r="L87" s="47"/>
+      <c r="M87" s="47"/>
+      <c r="N87" s="47"/>
+      <c r="O87" s="47"/>
+      <c r="P87" s="47"/>
+      <c r="Q87" s="47"/>
+      <c r="R87" s="47"/>
+      <c r="S87" s="47"/>
+      <c r="T87" s="47"/>
+      <c r="U87" s="47"/>
+      <c r="V87" s="47"/>
+      <c r="W87" s="47"/>
+      <c r="X87" s="47"/>
+      <c r="Y87" s="47"/>
+      <c r="Z87" s="47"/>
+      <c r="AA87" s="47"/>
+      <c r="AB87" s="48"/>
       <c r="AC87" s="11"/>
     </row>
     <row r="88" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4585,27 +4644,27 @@
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
-      <c r="L90" s="53"/>
-      <c r="M90" s="53"/>
-      <c r="N90" s="53"/>
-      <c r="O90" s="53"/>
-      <c r="P90" s="53"/>
-      <c r="Q90" s="53"/>
-      <c r="R90" s="53"/>
-      <c r="S90" s="53"/>
-      <c r="T90" s="53"/>
-      <c r="U90" s="53"/>
-      <c r="V90" s="53"/>
-      <c r="W90" s="53"/>
-      <c r="X90" s="53"/>
-      <c r="Y90" s="53"/>
-      <c r="Z90" s="53"/>
-      <c r="AA90" s="53"/>
-      <c r="AB90" s="54"/>
+      <c r="H90" s="49"/>
+      <c r="I90" s="50"/>
+      <c r="J90" s="50"/>
+      <c r="K90" s="50"/>
+      <c r="L90" s="50"/>
+      <c r="M90" s="50"/>
+      <c r="N90" s="50"/>
+      <c r="O90" s="50"/>
+      <c r="P90" s="50"/>
+      <c r="Q90" s="50"/>
+      <c r="R90" s="50"/>
+      <c r="S90" s="50"/>
+      <c r="T90" s="50"/>
+      <c r="U90" s="50"/>
+      <c r="V90" s="50"/>
+      <c r="W90" s="50"/>
+      <c r="X90" s="50"/>
+      <c r="Y90" s="50"/>
+      <c r="Z90" s="50"/>
+      <c r="AA90" s="50"/>
+      <c r="AB90" s="51"/>
       <c r="AC90" s="11"/>
     </row>
     <row r="91" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4615,29 +4674,27 @@
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
-      <c r="H91" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
-      <c r="M91" s="6"/>
-      <c r="N91" s="6"/>
-      <c r="O91" s="6"/>
-      <c r="P91" s="6"/>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="6"/>
-      <c r="S91" s="6"/>
-      <c r="T91" s="6"/>
-      <c r="U91" s="6"/>
-      <c r="V91" s="6"/>
-      <c r="W91" s="6"/>
-      <c r="X91" s="6"/>
-      <c r="Y91" s="6"/>
-      <c r="Z91" s="6"/>
-      <c r="AA91" s="6"/>
-      <c r="AB91" s="6"/>
+      <c r="H91" s="49"/>
+      <c r="I91" s="50"/>
+      <c r="J91" s="50"/>
+      <c r="K91" s="50"/>
+      <c r="L91" s="50"/>
+      <c r="M91" s="50"/>
+      <c r="N91" s="50"/>
+      <c r="O91" s="50"/>
+      <c r="P91" s="50"/>
+      <c r="Q91" s="50"/>
+      <c r="R91" s="50"/>
+      <c r="S91" s="50"/>
+      <c r="T91" s="50"/>
+      <c r="U91" s="50"/>
+      <c r="V91" s="50"/>
+      <c r="W91" s="50"/>
+      <c r="X91" s="50"/>
+      <c r="Y91" s="50"/>
+      <c r="Z91" s="50"/>
+      <c r="AA91" s="50"/>
+      <c r="AB91" s="51"/>
       <c r="AC91" s="11"/>
     </row>
     <row r="92" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4647,27 +4704,27 @@
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
-      <c r="H92" s="46"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="47"/>
-      <c r="K92" s="47"/>
-      <c r="L92" s="47"/>
-      <c r="M92" s="47"/>
-      <c r="N92" s="47"/>
-      <c r="O92" s="47"/>
-      <c r="P92" s="47"/>
-      <c r="Q92" s="47"/>
-      <c r="R92" s="47"/>
-      <c r="S92" s="47"/>
-      <c r="T92" s="47"/>
-      <c r="U92" s="47"/>
-      <c r="V92" s="47"/>
-      <c r="W92" s="47"/>
-      <c r="X92" s="47"/>
-      <c r="Y92" s="47"/>
-      <c r="Z92" s="47"/>
-      <c r="AA92" s="47"/>
-      <c r="AB92" s="48"/>
+      <c r="H92" s="49"/>
+      <c r="I92" s="50"/>
+      <c r="J92" s="50"/>
+      <c r="K92" s="50"/>
+      <c r="L92" s="50"/>
+      <c r="M92" s="50"/>
+      <c r="N92" s="50"/>
+      <c r="O92" s="50"/>
+      <c r="P92" s="50"/>
+      <c r="Q92" s="50"/>
+      <c r="R92" s="50"/>
+      <c r="S92" s="50"/>
+      <c r="T92" s="50"/>
+      <c r="U92" s="50"/>
+      <c r="V92" s="50"/>
+      <c r="W92" s="50"/>
+      <c r="X92" s="50"/>
+      <c r="Y92" s="50"/>
+      <c r="Z92" s="50"/>
+      <c r="AA92" s="50"/>
+      <c r="AB92" s="51"/>
       <c r="AC92" s="11"/>
     </row>
     <row r="93" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4677,27 +4734,27 @@
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
-      <c r="H93" s="49"/>
-      <c r="I93" s="50"/>
-      <c r="J93" s="50"/>
-      <c r="K93" s="50"/>
-      <c r="L93" s="50"/>
-      <c r="M93" s="50"/>
-      <c r="N93" s="50"/>
-      <c r="O93" s="50"/>
-      <c r="P93" s="50"/>
-      <c r="Q93" s="50"/>
-      <c r="R93" s="50"/>
-      <c r="S93" s="50"/>
-      <c r="T93" s="50"/>
-      <c r="U93" s="50"/>
-      <c r="V93" s="50"/>
-      <c r="W93" s="50"/>
-      <c r="X93" s="50"/>
-      <c r="Y93" s="50"/>
-      <c r="Z93" s="50"/>
-      <c r="AA93" s="50"/>
-      <c r="AB93" s="51"/>
+      <c r="H93" s="52"/>
+      <c r="I93" s="53"/>
+      <c r="J93" s="53"/>
+      <c r="K93" s="53"/>
+      <c r="L93" s="53"/>
+      <c r="M93" s="53"/>
+      <c r="N93" s="53"/>
+      <c r="O93" s="53"/>
+      <c r="P93" s="53"/>
+      <c r="Q93" s="53"/>
+      <c r="R93" s="53"/>
+      <c r="S93" s="53"/>
+      <c r="T93" s="53"/>
+      <c r="U93" s="53"/>
+      <c r="V93" s="53"/>
+      <c r="W93" s="53"/>
+      <c r="X93" s="53"/>
+      <c r="Y93" s="53"/>
+      <c r="Z93" s="53"/>
+      <c r="AA93" s="53"/>
+      <c r="AB93" s="54"/>
       <c r="AC93" s="11"/>
     </row>
     <row r="94" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4707,27 +4764,29 @@
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
-      <c r="H94" s="49"/>
-      <c r="I94" s="50"/>
-      <c r="J94" s="50"/>
-      <c r="K94" s="50"/>
-      <c r="L94" s="50"/>
-      <c r="M94" s="50"/>
-      <c r="N94" s="50"/>
-      <c r="O94" s="50"/>
-      <c r="P94" s="50"/>
-      <c r="Q94" s="50"/>
-      <c r="R94" s="50"/>
-      <c r="S94" s="50"/>
-      <c r="T94" s="50"/>
-      <c r="U94" s="50"/>
-      <c r="V94" s="50"/>
-      <c r="W94" s="50"/>
-      <c r="X94" s="50"/>
-      <c r="Y94" s="50"/>
-      <c r="Z94" s="50"/>
-      <c r="AA94" s="50"/>
-      <c r="AB94" s="51"/>
+      <c r="H94" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6"/>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
+      <c r="V94" s="6"/>
+      <c r="W94" s="6"/>
+      <c r="X94" s="6"/>
+      <c r="Y94" s="6"/>
+      <c r="Z94" s="6"/>
+      <c r="AA94" s="6"/>
+      <c r="AB94" s="6"/>
       <c r="AC94" s="11"/>
     </row>
     <row r="95" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4737,27 +4796,27 @@
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
-      <c r="H95" s="49"/>
-      <c r="I95" s="50"/>
-      <c r="J95" s="50"/>
-      <c r="K95" s="50"/>
-      <c r="L95" s="50"/>
-      <c r="M95" s="50"/>
-      <c r="N95" s="50"/>
-      <c r="O95" s="50"/>
-      <c r="P95" s="50"/>
-      <c r="Q95" s="50"/>
-      <c r="R95" s="50"/>
-      <c r="S95" s="50"/>
-      <c r="T95" s="50"/>
-      <c r="U95" s="50"/>
-      <c r="V95" s="50"/>
-      <c r="W95" s="50"/>
-      <c r="X95" s="50"/>
-      <c r="Y95" s="50"/>
-      <c r="Z95" s="50"/>
-      <c r="AA95" s="50"/>
-      <c r="AB95" s="51"/>
+      <c r="H95" s="46"/>
+      <c r="I95" s="47"/>
+      <c r="J95" s="47"/>
+      <c r="K95" s="47"/>
+      <c r="L95" s="47"/>
+      <c r="M95" s="47"/>
+      <c r="N95" s="47"/>
+      <c r="O95" s="47"/>
+      <c r="P95" s="47"/>
+      <c r="Q95" s="47"/>
+      <c r="R95" s="47"/>
+      <c r="S95" s="47"/>
+      <c r="T95" s="47"/>
+      <c r="U95" s="47"/>
+      <c r="V95" s="47"/>
+      <c r="W95" s="47"/>
+      <c r="X95" s="47"/>
+      <c r="Y95" s="47"/>
+      <c r="Z95" s="47"/>
+      <c r="AA95" s="47"/>
+      <c r="AB95" s="48"/>
       <c r="AC95" s="11"/>
     </row>
     <row r="96" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4827,245 +4886,245 @@
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="53"/>
-      <c r="J98" s="53"/>
-      <c r="K98" s="53"/>
-      <c r="L98" s="53"/>
-      <c r="M98" s="53"/>
-      <c r="N98" s="53"/>
-      <c r="O98" s="53"/>
-      <c r="P98" s="53"/>
-      <c r="Q98" s="53"/>
-      <c r="R98" s="53"/>
-      <c r="S98" s="53"/>
-      <c r="T98" s="53"/>
-      <c r="U98" s="53"/>
-      <c r="V98" s="53"/>
-      <c r="W98" s="53"/>
-      <c r="X98" s="53"/>
-      <c r="Y98" s="53"/>
-      <c r="Z98" s="53"/>
-      <c r="AA98" s="53"/>
-      <c r="AB98" s="54"/>
+      <c r="H98" s="49"/>
+      <c r="I98" s="50"/>
+      <c r="J98" s="50"/>
+      <c r="K98" s="50"/>
+      <c r="L98" s="50"/>
+      <c r="M98" s="50"/>
+      <c r="N98" s="50"/>
+      <c r="O98" s="50"/>
+      <c r="P98" s="50"/>
+      <c r="Q98" s="50"/>
+      <c r="R98" s="50"/>
+      <c r="S98" s="50"/>
+      <c r="T98" s="50"/>
+      <c r="U98" s="50"/>
+      <c r="V98" s="50"/>
+      <c r="W98" s="50"/>
+      <c r="X98" s="50"/>
+      <c r="Y98" s="50"/>
+      <c r="Z98" s="50"/>
+      <c r="AA98" s="50"/>
+      <c r="AB98" s="51"/>
       <c r="AC98" s="11"/>
     </row>
     <row r="99" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="45"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
-      <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
-      <c r="V99" s="4"/>
-      <c r="W99" s="4"/>
-      <c r="X99" s="4"/>
-      <c r="Y99" s="4"/>
-      <c r="Z99" s="4"/>
-      <c r="AA99" s="4"/>
-      <c r="AB99" s="4"/>
-      <c r="AC99" s="12"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="49"/>
+      <c r="I99" s="50"/>
+      <c r="J99" s="50"/>
+      <c r="K99" s="50"/>
+      <c r="L99" s="50"/>
+      <c r="M99" s="50"/>
+      <c r="N99" s="50"/>
+      <c r="O99" s="50"/>
+      <c r="P99" s="50"/>
+      <c r="Q99" s="50"/>
+      <c r="R99" s="50"/>
+      <c r="S99" s="50"/>
+      <c r="T99" s="50"/>
+      <c r="U99" s="50"/>
+      <c r="V99" s="50"/>
+      <c r="W99" s="50"/>
+      <c r="X99" s="50"/>
+      <c r="Y99" s="50"/>
+      <c r="Z99" s="50"/>
+      <c r="AA99" s="50"/>
+      <c r="AB99" s="51"/>
+      <c r="AC99" s="11"/>
+    </row>
+    <row r="100" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="44"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="49"/>
+      <c r="I100" s="50"/>
+      <c r="J100" s="50"/>
+      <c r="K100" s="50"/>
+      <c r="L100" s="50"/>
+      <c r="M100" s="50"/>
+      <c r="N100" s="50"/>
+      <c r="O100" s="50"/>
+      <c r="P100" s="50"/>
+      <c r="Q100" s="50"/>
+      <c r="R100" s="50"/>
+      <c r="S100" s="50"/>
+      <c r="T100" s="50"/>
+      <c r="U100" s="50"/>
+      <c r="V100" s="50"/>
+      <c r="W100" s="50"/>
+      <c r="X100" s="50"/>
+      <c r="Y100" s="50"/>
+      <c r="Z100" s="50"/>
+      <c r="AA100" s="50"/>
+      <c r="AB100" s="51"/>
+      <c r="AC100" s="11"/>
     </row>
     <row r="101" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="43" t="s">
+      <c r="B101" s="44"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="52"/>
+      <c r="I101" s="53"/>
+      <c r="J101" s="53"/>
+      <c r="K101" s="53"/>
+      <c r="L101" s="53"/>
+      <c r="M101" s="53"/>
+      <c r="N101" s="53"/>
+      <c r="O101" s="53"/>
+      <c r="P101" s="53"/>
+      <c r="Q101" s="53"/>
+      <c r="R101" s="53"/>
+      <c r="S101" s="53"/>
+      <c r="T101" s="53"/>
+      <c r="U101" s="53"/>
+      <c r="V101" s="53"/>
+      <c r="W101" s="53"/>
+      <c r="X101" s="53"/>
+      <c r="Y101" s="53"/>
+      <c r="Z101" s="53"/>
+      <c r="AA101" s="53"/>
+      <c r="AB101" s="54"/>
+      <c r="AC101" s="11"/>
+    </row>
+    <row r="102" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="45"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="4"/>
+      <c r="T102" s="4"/>
+      <c r="U102" s="4"/>
+      <c r="V102" s="4"/>
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+      <c r="AA102" s="4"/>
+      <c r="AB102" s="4"/>
+      <c r="AC102" s="12"/>
+    </row>
+    <row r="104" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C101" s="8"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="9"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
-      <c r="I101" s="9"/>
-      <c r="J101" s="9"/>
-      <c r="K101" s="9"/>
-      <c r="L101" s="9"/>
-      <c r="M101" s="9"/>
-      <c r="N101" s="9"/>
-      <c r="O101" s="9"/>
-      <c r="P101" s="9"/>
-      <c r="Q101" s="9"/>
-      <c r="R101" s="9"/>
-      <c r="S101" s="9"/>
-      <c r="T101" s="9"/>
-      <c r="U101" s="9"/>
-      <c r="V101" s="9"/>
-      <c r="W101" s="9"/>
-      <c r="X101" s="9"/>
-      <c r="Y101" s="9"/>
-      <c r="Z101" s="9"/>
-      <c r="AA101" s="9"/>
-      <c r="AB101" s="9"/>
-      <c r="AC101" s="10"/>
-    </row>
-    <row r="102" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B102" s="44"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102" s="6"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="6"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="6"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="6"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="6"/>
-      <c r="AB102" s="6"/>
-      <c r="AC102" s="11"/>
-    </row>
-    <row r="103" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B103" s="44"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="41"/>
-      <c r="E103" s="42"/>
-      <c r="F103" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G103" s="6"/>
-      <c r="H103" s="46"/>
-      <c r="I103" s="47"/>
-      <c r="J103" s="47"/>
-      <c r="K103" s="47"/>
-      <c r="L103" s="47"/>
-      <c r="M103" s="47"/>
-      <c r="N103" s="47"/>
-      <c r="O103" s="47"/>
-      <c r="P103" s="47"/>
-      <c r="Q103" s="47"/>
-      <c r="R103" s="47"/>
-      <c r="S103" s="47"/>
-      <c r="T103" s="47"/>
-      <c r="U103" s="47"/>
-      <c r="V103" s="47"/>
-      <c r="W103" s="47"/>
-      <c r="X103" s="47"/>
-      <c r="Y103" s="47"/>
-      <c r="Z103" s="47"/>
-      <c r="AA103" s="47"/>
-      <c r="AB103" s="48"/>
-      <c r="AC103" s="11"/>
-    </row>
-    <row r="104" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="44"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="49"/>
-      <c r="I104" s="50"/>
-      <c r="J104" s="50"/>
-      <c r="K104" s="50"/>
-      <c r="L104" s="50"/>
-      <c r="M104" s="50"/>
-      <c r="N104" s="50"/>
-      <c r="O104" s="50"/>
-      <c r="P104" s="50"/>
-      <c r="Q104" s="50"/>
-      <c r="R104" s="50"/>
-      <c r="S104" s="50"/>
-      <c r="T104" s="50"/>
-      <c r="U104" s="50"/>
-      <c r="V104" s="50"/>
-      <c r="W104" s="50"/>
-      <c r="X104" s="50"/>
-      <c r="Y104" s="50"/>
-      <c r="Z104" s="50"/>
-      <c r="AA104" s="50"/>
-      <c r="AB104" s="51"/>
-      <c r="AC104" s="11"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="9"/>
+      <c r="F104" s="9"/>
+      <c r="G104" s="9"/>
+      <c r="H104" s="9"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="9"/>
+      <c r="K104" s="9"/>
+      <c r="L104" s="9"/>
+      <c r="M104" s="9"/>
+      <c r="N104" s="9"/>
+      <c r="O104" s="9"/>
+      <c r="P104" s="9"/>
+      <c r="Q104" s="9"/>
+      <c r="R104" s="9"/>
+      <c r="S104" s="9"/>
+      <c r="T104" s="9"/>
+      <c r="U104" s="9"/>
+      <c r="V104" s="9"/>
+      <c r="W104" s="9"/>
+      <c r="X104" s="9"/>
+      <c r="Y104" s="9"/>
+      <c r="Z104" s="9"/>
+      <c r="AA104" s="9"/>
+      <c r="AB104" s="9"/>
+      <c r="AC104" s="10"/>
     </row>
     <row r="105" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" s="44"/>
       <c r="C105" s="5"/>
-      <c r="D105" s="6"/>
+      <c r="D105" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
-      <c r="H105" s="49"/>
-      <c r="I105" s="50"/>
-      <c r="J105" s="50"/>
-      <c r="K105" s="50"/>
-      <c r="L105" s="50"/>
-      <c r="M105" s="50"/>
-      <c r="N105" s="50"/>
-      <c r="O105" s="50"/>
-      <c r="P105" s="50"/>
-      <c r="Q105" s="50"/>
-      <c r="R105" s="50"/>
-      <c r="S105" s="50"/>
-      <c r="T105" s="50"/>
-      <c r="U105" s="50"/>
-      <c r="V105" s="50"/>
-      <c r="W105" s="50"/>
-      <c r="X105" s="50"/>
-      <c r="Y105" s="50"/>
-      <c r="Z105" s="50"/>
-      <c r="AA105" s="50"/>
-      <c r="AB105" s="51"/>
+      <c r="H105" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="6"/>
+      <c r="N105" s="6"/>
+      <c r="O105" s="6"/>
+      <c r="P105" s="6"/>
+      <c r="Q105" s="6"/>
+      <c r="R105" s="6"/>
+      <c r="S105" s="6"/>
+      <c r="T105" s="6"/>
+      <c r="U105" s="6"/>
+      <c r="V105" s="6"/>
+      <c r="W105" s="6"/>
+      <c r="X105" s="6"/>
+      <c r="Y105" s="6"/>
+      <c r="Z105" s="6"/>
+      <c r="AA105" s="6"/>
+      <c r="AB105" s="6"/>
       <c r="AC105" s="11"/>
     </row>
     <row r="106" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="44"/>
       <c r="C106" s="5"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
+      <c r="D106" s="41"/>
+      <c r="E106" s="42"/>
+      <c r="F106" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="G106" s="6"/>
-      <c r="H106" s="49"/>
-      <c r="I106" s="50"/>
-      <c r="J106" s="50"/>
-      <c r="K106" s="50"/>
-      <c r="L106" s="50"/>
-      <c r="M106" s="50"/>
-      <c r="N106" s="50"/>
-      <c r="O106" s="50"/>
-      <c r="P106" s="50"/>
-      <c r="Q106" s="50"/>
-      <c r="R106" s="50"/>
-      <c r="S106" s="50"/>
-      <c r="T106" s="50"/>
-      <c r="U106" s="50"/>
-      <c r="V106" s="50"/>
-      <c r="W106" s="50"/>
-      <c r="X106" s="50"/>
-      <c r="Y106" s="50"/>
-      <c r="Z106" s="50"/>
-      <c r="AA106" s="50"/>
-      <c r="AB106" s="51"/>
+      <c r="H106" s="46"/>
+      <c r="I106" s="47"/>
+      <c r="J106" s="47"/>
+      <c r="K106" s="47"/>
+      <c r="L106" s="47"/>
+      <c r="M106" s="47"/>
+      <c r="N106" s="47"/>
+      <c r="O106" s="47"/>
+      <c r="P106" s="47"/>
+      <c r="Q106" s="47"/>
+      <c r="R106" s="47"/>
+      <c r="S106" s="47"/>
+      <c r="T106" s="47"/>
+      <c r="U106" s="47"/>
+      <c r="V106" s="47"/>
+      <c r="W106" s="47"/>
+      <c r="X106" s="47"/>
+      <c r="Y106" s="47"/>
+      <c r="Z106" s="47"/>
+      <c r="AA106" s="47"/>
+      <c r="AB106" s="48"/>
       <c r="AC106" s="11"/>
     </row>
     <row r="107" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5135,27 +5194,27 @@
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
-      <c r="H109" s="52"/>
-      <c r="I109" s="53"/>
-      <c r="J109" s="53"/>
-      <c r="K109" s="53"/>
-      <c r="L109" s="53"/>
-      <c r="M109" s="53"/>
-      <c r="N109" s="53"/>
-      <c r="O109" s="53"/>
-      <c r="P109" s="53"/>
-      <c r="Q109" s="53"/>
-      <c r="R109" s="53"/>
-      <c r="S109" s="53"/>
-      <c r="T109" s="53"/>
-      <c r="U109" s="53"/>
-      <c r="V109" s="53"/>
-      <c r="W109" s="53"/>
-      <c r="X109" s="53"/>
-      <c r="Y109" s="53"/>
-      <c r="Z109" s="53"/>
-      <c r="AA109" s="53"/>
-      <c r="AB109" s="54"/>
+      <c r="H109" s="49"/>
+      <c r="I109" s="50"/>
+      <c r="J109" s="50"/>
+      <c r="K109" s="50"/>
+      <c r="L109" s="50"/>
+      <c r="M109" s="50"/>
+      <c r="N109" s="50"/>
+      <c r="O109" s="50"/>
+      <c r="P109" s="50"/>
+      <c r="Q109" s="50"/>
+      <c r="R109" s="50"/>
+      <c r="S109" s="50"/>
+      <c r="T109" s="50"/>
+      <c r="U109" s="50"/>
+      <c r="V109" s="50"/>
+      <c r="W109" s="50"/>
+      <c r="X109" s="50"/>
+      <c r="Y109" s="50"/>
+      <c r="Z109" s="50"/>
+      <c r="AA109" s="50"/>
+      <c r="AB109" s="51"/>
       <c r="AC109" s="11"/>
     </row>
     <row r="110" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5165,29 +5224,27 @@
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
-      <c r="H110" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
-      <c r="M110" s="6"/>
-      <c r="N110" s="6"/>
-      <c r="O110" s="6"/>
-      <c r="P110" s="6"/>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-      <c r="U110" s="6"/>
-      <c r="V110" s="6"/>
-      <c r="W110" s="6"/>
-      <c r="X110" s="6"/>
-      <c r="Y110" s="6"/>
-      <c r="Z110" s="6"/>
-      <c r="AA110" s="6"/>
-      <c r="AB110" s="6"/>
+      <c r="H110" s="49"/>
+      <c r="I110" s="50"/>
+      <c r="J110" s="50"/>
+      <c r="K110" s="50"/>
+      <c r="L110" s="50"/>
+      <c r="M110" s="50"/>
+      <c r="N110" s="50"/>
+      <c r="O110" s="50"/>
+      <c r="P110" s="50"/>
+      <c r="Q110" s="50"/>
+      <c r="R110" s="50"/>
+      <c r="S110" s="50"/>
+      <c r="T110" s="50"/>
+      <c r="U110" s="50"/>
+      <c r="V110" s="50"/>
+      <c r="W110" s="50"/>
+      <c r="X110" s="50"/>
+      <c r="Y110" s="50"/>
+      <c r="Z110" s="50"/>
+      <c r="AA110" s="50"/>
+      <c r="AB110" s="51"/>
       <c r="AC110" s="11"/>
     </row>
     <row r="111" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5197,27 +5254,27 @@
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
-      <c r="H111" s="46"/>
-      <c r="I111" s="47"/>
-      <c r="J111" s="47"/>
-      <c r="K111" s="47"/>
-      <c r="L111" s="47"/>
-      <c r="M111" s="47"/>
-      <c r="N111" s="47"/>
-      <c r="O111" s="47"/>
-      <c r="P111" s="47"/>
-      <c r="Q111" s="47"/>
-      <c r="R111" s="47"/>
-      <c r="S111" s="47"/>
-      <c r="T111" s="47"/>
-      <c r="U111" s="47"/>
-      <c r="V111" s="47"/>
-      <c r="W111" s="47"/>
-      <c r="X111" s="47"/>
-      <c r="Y111" s="47"/>
-      <c r="Z111" s="47"/>
-      <c r="AA111" s="47"/>
-      <c r="AB111" s="48"/>
+      <c r="H111" s="49"/>
+      <c r="I111" s="50"/>
+      <c r="J111" s="50"/>
+      <c r="K111" s="50"/>
+      <c r="L111" s="50"/>
+      <c r="M111" s="50"/>
+      <c r="N111" s="50"/>
+      <c r="O111" s="50"/>
+      <c r="P111" s="50"/>
+      <c r="Q111" s="50"/>
+      <c r="R111" s="50"/>
+      <c r="S111" s="50"/>
+      <c r="T111" s="50"/>
+      <c r="U111" s="50"/>
+      <c r="V111" s="50"/>
+      <c r="W111" s="50"/>
+      <c r="X111" s="50"/>
+      <c r="Y111" s="50"/>
+      <c r="Z111" s="50"/>
+      <c r="AA111" s="50"/>
+      <c r="AB111" s="51"/>
       <c r="AC111" s="11"/>
     </row>
     <row r="112" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5227,27 +5284,27 @@
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
-      <c r="H112" s="49"/>
-      <c r="I112" s="50"/>
-      <c r="J112" s="50"/>
-      <c r="K112" s="50"/>
-      <c r="L112" s="50"/>
-      <c r="M112" s="50"/>
-      <c r="N112" s="50"/>
-      <c r="O112" s="50"/>
-      <c r="P112" s="50"/>
-      <c r="Q112" s="50"/>
-      <c r="R112" s="50"/>
-      <c r="S112" s="50"/>
-      <c r="T112" s="50"/>
-      <c r="U112" s="50"/>
-      <c r="V112" s="50"/>
-      <c r="W112" s="50"/>
-      <c r="X112" s="50"/>
-      <c r="Y112" s="50"/>
-      <c r="Z112" s="50"/>
-      <c r="AA112" s="50"/>
-      <c r="AB112" s="51"/>
+      <c r="H112" s="52"/>
+      <c r="I112" s="53"/>
+      <c r="J112" s="53"/>
+      <c r="K112" s="53"/>
+      <c r="L112" s="53"/>
+      <c r="M112" s="53"/>
+      <c r="N112" s="53"/>
+      <c r="O112" s="53"/>
+      <c r="P112" s="53"/>
+      <c r="Q112" s="53"/>
+      <c r="R112" s="53"/>
+      <c r="S112" s="53"/>
+      <c r="T112" s="53"/>
+      <c r="U112" s="53"/>
+      <c r="V112" s="53"/>
+      <c r="W112" s="53"/>
+      <c r="X112" s="53"/>
+      <c r="Y112" s="53"/>
+      <c r="Z112" s="53"/>
+      <c r="AA112" s="53"/>
+      <c r="AB112" s="54"/>
       <c r="AC112" s="11"/>
     </row>
     <row r="113" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5257,27 +5314,29 @@
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
-      <c r="H113" s="49"/>
-      <c r="I113" s="50"/>
-      <c r="J113" s="50"/>
-      <c r="K113" s="50"/>
-      <c r="L113" s="50"/>
-      <c r="M113" s="50"/>
-      <c r="N113" s="50"/>
-      <c r="O113" s="50"/>
-      <c r="P113" s="50"/>
-      <c r="Q113" s="50"/>
-      <c r="R113" s="50"/>
-      <c r="S113" s="50"/>
-      <c r="T113" s="50"/>
-      <c r="U113" s="50"/>
-      <c r="V113" s="50"/>
-      <c r="W113" s="50"/>
-      <c r="X113" s="50"/>
-      <c r="Y113" s="50"/>
-      <c r="Z113" s="50"/>
-      <c r="AA113" s="50"/>
-      <c r="AB113" s="51"/>
+      <c r="H113" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
+      <c r="N113" s="6"/>
+      <c r="O113" s="6"/>
+      <c r="P113" s="6"/>
+      <c r="Q113" s="6"/>
+      <c r="R113" s="6"/>
+      <c r="S113" s="6"/>
+      <c r="T113" s="6"/>
+      <c r="U113" s="6"/>
+      <c r="V113" s="6"/>
+      <c r="W113" s="6"/>
+      <c r="X113" s="6"/>
+      <c r="Y113" s="6"/>
+      <c r="Z113" s="6"/>
+      <c r="AA113" s="6"/>
+      <c r="AB113" s="6"/>
       <c r="AC113" s="11"/>
     </row>
     <row r="114" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5287,27 +5346,27 @@
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
-      <c r="H114" s="49"/>
-      <c r="I114" s="50"/>
-      <c r="J114" s="50"/>
-      <c r="K114" s="50"/>
-      <c r="L114" s="50"/>
-      <c r="M114" s="50"/>
-      <c r="N114" s="50"/>
-      <c r="O114" s="50"/>
-      <c r="P114" s="50"/>
-      <c r="Q114" s="50"/>
-      <c r="R114" s="50"/>
-      <c r="S114" s="50"/>
-      <c r="T114" s="50"/>
-      <c r="U114" s="50"/>
-      <c r="V114" s="50"/>
-      <c r="W114" s="50"/>
-      <c r="X114" s="50"/>
-      <c r="Y114" s="50"/>
-      <c r="Z114" s="50"/>
-      <c r="AA114" s="50"/>
-      <c r="AB114" s="51"/>
+      <c r="H114" s="46"/>
+      <c r="I114" s="47"/>
+      <c r="J114" s="47"/>
+      <c r="K114" s="47"/>
+      <c r="L114" s="47"/>
+      <c r="M114" s="47"/>
+      <c r="N114" s="47"/>
+      <c r="O114" s="47"/>
+      <c r="P114" s="47"/>
+      <c r="Q114" s="47"/>
+      <c r="R114" s="47"/>
+      <c r="S114" s="47"/>
+      <c r="T114" s="47"/>
+      <c r="U114" s="47"/>
+      <c r="V114" s="47"/>
+      <c r="W114" s="47"/>
+      <c r="X114" s="47"/>
+      <c r="Y114" s="47"/>
+      <c r="Z114" s="47"/>
+      <c r="AA114" s="47"/>
+      <c r="AB114" s="48"/>
       <c r="AC114" s="11"/>
     </row>
     <row r="115" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5377,245 +5436,245 @@
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
-      <c r="H117" s="52"/>
-      <c r="I117" s="53"/>
-      <c r="J117" s="53"/>
-      <c r="K117" s="53"/>
-      <c r="L117" s="53"/>
-      <c r="M117" s="53"/>
-      <c r="N117" s="53"/>
-      <c r="O117" s="53"/>
-      <c r="P117" s="53"/>
-      <c r="Q117" s="53"/>
-      <c r="R117" s="53"/>
-      <c r="S117" s="53"/>
-      <c r="T117" s="53"/>
-      <c r="U117" s="53"/>
-      <c r="V117" s="53"/>
-      <c r="W117" s="53"/>
-      <c r="X117" s="53"/>
-      <c r="Y117" s="53"/>
-      <c r="Z117" s="53"/>
-      <c r="AA117" s="53"/>
-      <c r="AB117" s="54"/>
+      <c r="H117" s="49"/>
+      <c r="I117" s="50"/>
+      <c r="J117" s="50"/>
+      <c r="K117" s="50"/>
+      <c r="L117" s="50"/>
+      <c r="M117" s="50"/>
+      <c r="N117" s="50"/>
+      <c r="O117" s="50"/>
+      <c r="P117" s="50"/>
+      <c r="Q117" s="50"/>
+      <c r="R117" s="50"/>
+      <c r="S117" s="50"/>
+      <c r="T117" s="50"/>
+      <c r="U117" s="50"/>
+      <c r="V117" s="50"/>
+      <c r="W117" s="50"/>
+      <c r="X117" s="50"/>
+      <c r="Y117" s="50"/>
+      <c r="Z117" s="50"/>
+      <c r="AA117" s="50"/>
+      <c r="AB117" s="51"/>
       <c r="AC117" s="11"/>
     </row>
     <row r="118" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="45"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
-      <c r="I118" s="4"/>
-      <c r="J118" s="4"/>
-      <c r="K118" s="4"/>
-      <c r="L118" s="4"/>
-      <c r="M118" s="4"/>
-      <c r="N118" s="4"/>
-      <c r="O118" s="4"/>
-      <c r="P118" s="4"/>
-      <c r="Q118" s="4"/>
-      <c r="R118" s="4"/>
-      <c r="S118" s="4"/>
-      <c r="T118" s="4"/>
-      <c r="U118" s="4"/>
-      <c r="V118" s="4"/>
-      <c r="W118" s="4"/>
-      <c r="X118" s="4"/>
-      <c r="Y118" s="4"/>
-      <c r="Z118" s="4"/>
-      <c r="AA118" s="4"/>
-      <c r="AB118" s="4"/>
-      <c r="AC118" s="12"/>
+      <c r="B118" s="44"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+      <c r="H118" s="49"/>
+      <c r="I118" s="50"/>
+      <c r="J118" s="50"/>
+      <c r="K118" s="50"/>
+      <c r="L118" s="50"/>
+      <c r="M118" s="50"/>
+      <c r="N118" s="50"/>
+      <c r="O118" s="50"/>
+      <c r="P118" s="50"/>
+      <c r="Q118" s="50"/>
+      <c r="R118" s="50"/>
+      <c r="S118" s="50"/>
+      <c r="T118" s="50"/>
+      <c r="U118" s="50"/>
+      <c r="V118" s="50"/>
+      <c r="W118" s="50"/>
+      <c r="X118" s="50"/>
+      <c r="Y118" s="50"/>
+      <c r="Z118" s="50"/>
+      <c r="AA118" s="50"/>
+      <c r="AB118" s="51"/>
+      <c r="AC118" s="11"/>
+    </row>
+    <row r="119" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="44"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="49"/>
+      <c r="I119" s="50"/>
+      <c r="J119" s="50"/>
+      <c r="K119" s="50"/>
+      <c r="L119" s="50"/>
+      <c r="M119" s="50"/>
+      <c r="N119" s="50"/>
+      <c r="O119" s="50"/>
+      <c r="P119" s="50"/>
+      <c r="Q119" s="50"/>
+      <c r="R119" s="50"/>
+      <c r="S119" s="50"/>
+      <c r="T119" s="50"/>
+      <c r="U119" s="50"/>
+      <c r="V119" s="50"/>
+      <c r="W119" s="50"/>
+      <c r="X119" s="50"/>
+      <c r="Y119" s="50"/>
+      <c r="Z119" s="50"/>
+      <c r="AA119" s="50"/>
+      <c r="AB119" s="51"/>
+      <c r="AC119" s="11"/>
     </row>
     <row r="120" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="43" t="s">
+      <c r="B120" s="44"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="52"/>
+      <c r="I120" s="53"/>
+      <c r="J120" s="53"/>
+      <c r="K120" s="53"/>
+      <c r="L120" s="53"/>
+      <c r="M120" s="53"/>
+      <c r="N120" s="53"/>
+      <c r="O120" s="53"/>
+      <c r="P120" s="53"/>
+      <c r="Q120" s="53"/>
+      <c r="R120" s="53"/>
+      <c r="S120" s="53"/>
+      <c r="T120" s="53"/>
+      <c r="U120" s="53"/>
+      <c r="V120" s="53"/>
+      <c r="W120" s="53"/>
+      <c r="X120" s="53"/>
+      <c r="Y120" s="53"/>
+      <c r="Z120" s="53"/>
+      <c r="AA120" s="53"/>
+      <c r="AB120" s="54"/>
+      <c r="AC120" s="11"/>
+    </row>
+    <row r="121" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="45"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="4"/>
+      <c r="R121" s="4"/>
+      <c r="S121" s="4"/>
+      <c r="T121" s="4"/>
+      <c r="U121" s="4"/>
+      <c r="V121" s="4"/>
+      <c r="W121" s="4"/>
+      <c r="X121" s="4"/>
+      <c r="Y121" s="4"/>
+      <c r="Z121" s="4"/>
+      <c r="AA121" s="4"/>
+      <c r="AB121" s="4"/>
+      <c r="AC121" s="12"/>
+    </row>
+    <row r="123" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="C120" s="8"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="9"/>
-      <c r="H120" s="9"/>
-      <c r="I120" s="9"/>
-      <c r="J120" s="9"/>
-      <c r="K120" s="9"/>
-      <c r="L120" s="9"/>
-      <c r="M120" s="9"/>
-      <c r="N120" s="9"/>
-      <c r="O120" s="9"/>
-      <c r="P120" s="9"/>
-      <c r="Q120" s="9"/>
-      <c r="R120" s="9"/>
-      <c r="S120" s="9"/>
-      <c r="T120" s="9"/>
-      <c r="U120" s="9"/>
-      <c r="V120" s="9"/>
-      <c r="W120" s="9"/>
-      <c r="X120" s="9"/>
-      <c r="Y120" s="9"/>
-      <c r="Z120" s="9"/>
-      <c r="AA120" s="9"/>
-      <c r="AB120" s="9"/>
-      <c r="AC120" s="10"/>
-    </row>
-    <row r="121" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="44"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="M121" s="6"/>
-      <c r="N121" s="6"/>
-      <c r="O121" s="6"/>
-      <c r="P121" s="6"/>
-      <c r="Q121" s="6"/>
-      <c r="R121" s="6"/>
-      <c r="S121" s="6"/>
-      <c r="T121" s="6"/>
-      <c r="U121" s="6"/>
-      <c r="V121" s="6"/>
-      <c r="W121" s="6"/>
-      <c r="X121" s="6"/>
-      <c r="Y121" s="6"/>
-      <c r="Z121" s="6"/>
-      <c r="AA121" s="6"/>
-      <c r="AB121" s="6"/>
-      <c r="AC121" s="11"/>
-    </row>
-    <row r="122" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="44"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="41"/>
-      <c r="E122" s="42"/>
-      <c r="F122" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G122" s="6"/>
-      <c r="H122" s="46"/>
-      <c r="I122" s="47"/>
-      <c r="J122" s="47"/>
-      <c r="K122" s="47"/>
-      <c r="L122" s="47"/>
-      <c r="M122" s="47"/>
-      <c r="N122" s="47"/>
-      <c r="O122" s="47"/>
-      <c r="P122" s="47"/>
-      <c r="Q122" s="47"/>
-      <c r="R122" s="47"/>
-      <c r="S122" s="47"/>
-      <c r="T122" s="47"/>
-      <c r="U122" s="47"/>
-      <c r="V122" s="47"/>
-      <c r="W122" s="47"/>
-      <c r="X122" s="47"/>
-      <c r="Y122" s="47"/>
-      <c r="Z122" s="47"/>
-      <c r="AA122" s="47"/>
-      <c r="AB122" s="48"/>
-      <c r="AC122" s="11"/>
-    </row>
-    <row r="123" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="44"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="49"/>
-      <c r="I123" s="50"/>
-      <c r="J123" s="50"/>
-      <c r="K123" s="50"/>
-      <c r="L123" s="50"/>
-      <c r="M123" s="50"/>
-      <c r="N123" s="50"/>
-      <c r="O123" s="50"/>
-      <c r="P123" s="50"/>
-      <c r="Q123" s="50"/>
-      <c r="R123" s="50"/>
-      <c r="S123" s="50"/>
-      <c r="T123" s="50"/>
-      <c r="U123" s="50"/>
-      <c r="V123" s="50"/>
-      <c r="W123" s="50"/>
-      <c r="X123" s="50"/>
-      <c r="Y123" s="50"/>
-      <c r="Z123" s="50"/>
-      <c r="AA123" s="50"/>
-      <c r="AB123" s="51"/>
-      <c r="AC123" s="11"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
+      <c r="M123" s="9"/>
+      <c r="N123" s="9"/>
+      <c r="O123" s="9"/>
+      <c r="P123" s="9"/>
+      <c r="Q123" s="9"/>
+      <c r="R123" s="9"/>
+      <c r="S123" s="9"/>
+      <c r="T123" s="9"/>
+      <c r="U123" s="9"/>
+      <c r="V123" s="9"/>
+      <c r="W123" s="9"/>
+      <c r="X123" s="9"/>
+      <c r="Y123" s="9"/>
+      <c r="Z123" s="9"/>
+      <c r="AA123" s="9"/>
+      <c r="AB123" s="9"/>
+      <c r="AC123" s="10"/>
     </row>
     <row r="124" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" s="44"/>
       <c r="C124" s="5"/>
-      <c r="D124" s="6"/>
+      <c r="D124" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
-      <c r="H124" s="49"/>
-      <c r="I124" s="50"/>
-      <c r="J124" s="50"/>
-      <c r="K124" s="50"/>
-      <c r="L124" s="50"/>
-      <c r="M124" s="50"/>
-      <c r="N124" s="50"/>
-      <c r="O124" s="50"/>
-      <c r="P124" s="50"/>
-      <c r="Q124" s="50"/>
-      <c r="R124" s="50"/>
-      <c r="S124" s="50"/>
-      <c r="T124" s="50"/>
-      <c r="U124" s="50"/>
-      <c r="V124" s="50"/>
-      <c r="W124" s="50"/>
-      <c r="X124" s="50"/>
-      <c r="Y124" s="50"/>
-      <c r="Z124" s="50"/>
-      <c r="AA124" s="50"/>
-      <c r="AB124" s="51"/>
+      <c r="H124" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I124" s="6"/>
+      <c r="J124" s="6"/>
+      <c r="K124" s="6"/>
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
+      <c r="N124" s="6"/>
+      <c r="O124" s="6"/>
+      <c r="P124" s="6"/>
+      <c r="Q124" s="6"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="6"/>
+      <c r="T124" s="6"/>
+      <c r="U124" s="6"/>
+      <c r="V124" s="6"/>
+      <c r="W124" s="6"/>
+      <c r="X124" s="6"/>
+      <c r="Y124" s="6"/>
+      <c r="Z124" s="6"/>
+      <c r="AA124" s="6"/>
+      <c r="AB124" s="6"/>
       <c r="AC124" s="11"/>
     </row>
     <row r="125" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" s="44"/>
       <c r="C125" s="5"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
+      <c r="D125" s="41"/>
+      <c r="E125" s="42"/>
+      <c r="F125" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="G125" s="6"/>
-      <c r="H125" s="49"/>
-      <c r="I125" s="50"/>
-      <c r="J125" s="50"/>
-      <c r="K125" s="50"/>
-      <c r="L125" s="50"/>
-      <c r="M125" s="50"/>
-      <c r="N125" s="50"/>
-      <c r="O125" s="50"/>
-      <c r="P125" s="50"/>
-      <c r="Q125" s="50"/>
-      <c r="R125" s="50"/>
-      <c r="S125" s="50"/>
-      <c r="T125" s="50"/>
-      <c r="U125" s="50"/>
-      <c r="V125" s="50"/>
-      <c r="W125" s="50"/>
-      <c r="X125" s="50"/>
-      <c r="Y125" s="50"/>
-      <c r="Z125" s="50"/>
-      <c r="AA125" s="50"/>
-      <c r="AB125" s="51"/>
+      <c r="H125" s="46"/>
+      <c r="I125" s="47"/>
+      <c r="J125" s="47"/>
+      <c r="K125" s="47"/>
+      <c r="L125" s="47"/>
+      <c r="M125" s="47"/>
+      <c r="N125" s="47"/>
+      <c r="O125" s="47"/>
+      <c r="P125" s="47"/>
+      <c r="Q125" s="47"/>
+      <c r="R125" s="47"/>
+      <c r="S125" s="47"/>
+      <c r="T125" s="47"/>
+      <c r="U125" s="47"/>
+      <c r="V125" s="47"/>
+      <c r="W125" s="47"/>
+      <c r="X125" s="47"/>
+      <c r="Y125" s="47"/>
+      <c r="Z125" s="47"/>
+      <c r="AA125" s="47"/>
+      <c r="AB125" s="48"/>
       <c r="AC125" s="11"/>
     </row>
     <row r="126" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5685,27 +5744,27 @@
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
-      <c r="H128" s="52"/>
-      <c r="I128" s="53"/>
-      <c r="J128" s="53"/>
-      <c r="K128" s="53"/>
-      <c r="L128" s="53"/>
-      <c r="M128" s="53"/>
-      <c r="N128" s="53"/>
-      <c r="O128" s="53"/>
-      <c r="P128" s="53"/>
-      <c r="Q128" s="53"/>
-      <c r="R128" s="53"/>
-      <c r="S128" s="53"/>
-      <c r="T128" s="53"/>
-      <c r="U128" s="53"/>
-      <c r="V128" s="53"/>
-      <c r="W128" s="53"/>
-      <c r="X128" s="53"/>
-      <c r="Y128" s="53"/>
-      <c r="Z128" s="53"/>
-      <c r="AA128" s="53"/>
-      <c r="AB128" s="54"/>
+      <c r="H128" s="49"/>
+      <c r="I128" s="50"/>
+      <c r="J128" s="50"/>
+      <c r="K128" s="50"/>
+      <c r="L128" s="50"/>
+      <c r="M128" s="50"/>
+      <c r="N128" s="50"/>
+      <c r="O128" s="50"/>
+      <c r="P128" s="50"/>
+      <c r="Q128" s="50"/>
+      <c r="R128" s="50"/>
+      <c r="S128" s="50"/>
+      <c r="T128" s="50"/>
+      <c r="U128" s="50"/>
+      <c r="V128" s="50"/>
+      <c r="W128" s="50"/>
+      <c r="X128" s="50"/>
+      <c r="Y128" s="50"/>
+      <c r="Z128" s="50"/>
+      <c r="AA128" s="50"/>
+      <c r="AB128" s="51"/>
       <c r="AC128" s="11"/>
     </row>
     <row r="129" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5715,29 +5774,27 @@
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
-      <c r="H129" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6"/>
-      <c r="M129" s="6"/>
-      <c r="N129" s="6"/>
-      <c r="O129" s="6"/>
-      <c r="P129" s="6"/>
-      <c r="Q129" s="6"/>
-      <c r="R129" s="6"/>
-      <c r="S129" s="6"/>
-      <c r="T129" s="6"/>
-      <c r="U129" s="6"/>
-      <c r="V129" s="6"/>
-      <c r="W129" s="6"/>
-      <c r="X129" s="6"/>
-      <c r="Y129" s="6"/>
-      <c r="Z129" s="6"/>
-      <c r="AA129" s="6"/>
-      <c r="AB129" s="6"/>
+      <c r="H129" s="49"/>
+      <c r="I129" s="50"/>
+      <c r="J129" s="50"/>
+      <c r="K129" s="50"/>
+      <c r="L129" s="50"/>
+      <c r="M129" s="50"/>
+      <c r="N129" s="50"/>
+      <c r="O129" s="50"/>
+      <c r="P129" s="50"/>
+      <c r="Q129" s="50"/>
+      <c r="R129" s="50"/>
+      <c r="S129" s="50"/>
+      <c r="T129" s="50"/>
+      <c r="U129" s="50"/>
+      <c r="V129" s="50"/>
+      <c r="W129" s="50"/>
+      <c r="X129" s="50"/>
+      <c r="Y129" s="50"/>
+      <c r="Z129" s="50"/>
+      <c r="AA129" s="50"/>
+      <c r="AB129" s="51"/>
       <c r="AC129" s="11"/>
     </row>
     <row r="130" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5747,27 +5804,27 @@
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
-      <c r="H130" s="46"/>
-      <c r="I130" s="47"/>
-      <c r="J130" s="47"/>
-      <c r="K130" s="47"/>
-      <c r="L130" s="47"/>
-      <c r="M130" s="47"/>
-      <c r="N130" s="47"/>
-      <c r="O130" s="47"/>
-      <c r="P130" s="47"/>
-      <c r="Q130" s="47"/>
-      <c r="R130" s="47"/>
-      <c r="S130" s="47"/>
-      <c r="T130" s="47"/>
-      <c r="U130" s="47"/>
-      <c r="V130" s="47"/>
-      <c r="W130" s="47"/>
-      <c r="X130" s="47"/>
-      <c r="Y130" s="47"/>
-      <c r="Z130" s="47"/>
-      <c r="AA130" s="47"/>
-      <c r="AB130" s="48"/>
+      <c r="H130" s="49"/>
+      <c r="I130" s="50"/>
+      <c r="J130" s="50"/>
+      <c r="K130" s="50"/>
+      <c r="L130" s="50"/>
+      <c r="M130" s="50"/>
+      <c r="N130" s="50"/>
+      <c r="O130" s="50"/>
+      <c r="P130" s="50"/>
+      <c r="Q130" s="50"/>
+      <c r="R130" s="50"/>
+      <c r="S130" s="50"/>
+      <c r="T130" s="50"/>
+      <c r="U130" s="50"/>
+      <c r="V130" s="50"/>
+      <c r="W130" s="50"/>
+      <c r="X130" s="50"/>
+      <c r="Y130" s="50"/>
+      <c r="Z130" s="50"/>
+      <c r="AA130" s="50"/>
+      <c r="AB130" s="51"/>
       <c r="AC130" s="11"/>
     </row>
     <row r="131" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5777,27 +5834,27 @@
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
-      <c r="H131" s="49"/>
-      <c r="I131" s="50"/>
-      <c r="J131" s="50"/>
-      <c r="K131" s="50"/>
-      <c r="L131" s="50"/>
-      <c r="M131" s="50"/>
-      <c r="N131" s="50"/>
-      <c r="O131" s="50"/>
-      <c r="P131" s="50"/>
-      <c r="Q131" s="50"/>
-      <c r="R131" s="50"/>
-      <c r="S131" s="50"/>
-      <c r="T131" s="50"/>
-      <c r="U131" s="50"/>
-      <c r="V131" s="50"/>
-      <c r="W131" s="50"/>
-      <c r="X131" s="50"/>
-      <c r="Y131" s="50"/>
-      <c r="Z131" s="50"/>
-      <c r="AA131" s="50"/>
-      <c r="AB131" s="51"/>
+      <c r="H131" s="52"/>
+      <c r="I131" s="53"/>
+      <c r="J131" s="53"/>
+      <c r="K131" s="53"/>
+      <c r="L131" s="53"/>
+      <c r="M131" s="53"/>
+      <c r="N131" s="53"/>
+      <c r="O131" s="53"/>
+      <c r="P131" s="53"/>
+      <c r="Q131" s="53"/>
+      <c r="R131" s="53"/>
+      <c r="S131" s="53"/>
+      <c r="T131" s="53"/>
+      <c r="U131" s="53"/>
+      <c r="V131" s="53"/>
+      <c r="W131" s="53"/>
+      <c r="X131" s="53"/>
+      <c r="Y131" s="53"/>
+      <c r="Z131" s="53"/>
+      <c r="AA131" s="53"/>
+      <c r="AB131" s="54"/>
       <c r="AC131" s="11"/>
     </row>
     <row r="132" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5807,27 +5864,29 @@
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
-      <c r="H132" s="49"/>
-      <c r="I132" s="50"/>
-      <c r="J132" s="50"/>
-      <c r="K132" s="50"/>
-      <c r="L132" s="50"/>
-      <c r="M132" s="50"/>
-      <c r="N132" s="50"/>
-      <c r="O132" s="50"/>
-      <c r="P132" s="50"/>
-      <c r="Q132" s="50"/>
-      <c r="R132" s="50"/>
-      <c r="S132" s="50"/>
-      <c r="T132" s="50"/>
-      <c r="U132" s="50"/>
-      <c r="V132" s="50"/>
-      <c r="W132" s="50"/>
-      <c r="X132" s="50"/>
-      <c r="Y132" s="50"/>
-      <c r="Z132" s="50"/>
-      <c r="AA132" s="50"/>
-      <c r="AB132" s="51"/>
+      <c r="H132" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I132" s="6"/>
+      <c r="J132" s="6"/>
+      <c r="K132" s="6"/>
+      <c r="L132" s="6"/>
+      <c r="M132" s="6"/>
+      <c r="N132" s="6"/>
+      <c r="O132" s="6"/>
+      <c r="P132" s="6"/>
+      <c r="Q132" s="6"/>
+      <c r="R132" s="6"/>
+      <c r="S132" s="6"/>
+      <c r="T132" s="6"/>
+      <c r="U132" s="6"/>
+      <c r="V132" s="6"/>
+      <c r="W132" s="6"/>
+      <c r="X132" s="6"/>
+      <c r="Y132" s="6"/>
+      <c r="Z132" s="6"/>
+      <c r="AA132" s="6"/>
+      <c r="AB132" s="6"/>
       <c r="AC132" s="11"/>
     </row>
     <row r="133" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5837,27 +5896,27 @@
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="49"/>
-      <c r="I133" s="50"/>
-      <c r="J133" s="50"/>
-      <c r="K133" s="50"/>
-      <c r="L133" s="50"/>
-      <c r="M133" s="50"/>
-      <c r="N133" s="50"/>
-      <c r="O133" s="50"/>
-      <c r="P133" s="50"/>
-      <c r="Q133" s="50"/>
-      <c r="R133" s="50"/>
-      <c r="S133" s="50"/>
-      <c r="T133" s="50"/>
-      <c r="U133" s="50"/>
-      <c r="V133" s="50"/>
-      <c r="W133" s="50"/>
-      <c r="X133" s="50"/>
-      <c r="Y133" s="50"/>
-      <c r="Z133" s="50"/>
-      <c r="AA133" s="50"/>
-      <c r="AB133" s="51"/>
+      <c r="H133" s="46"/>
+      <c r="I133" s="47"/>
+      <c r="J133" s="47"/>
+      <c r="K133" s="47"/>
+      <c r="L133" s="47"/>
+      <c r="M133" s="47"/>
+      <c r="N133" s="47"/>
+      <c r="O133" s="47"/>
+      <c r="P133" s="47"/>
+      <c r="Q133" s="47"/>
+      <c r="R133" s="47"/>
+      <c r="S133" s="47"/>
+      <c r="T133" s="47"/>
+      <c r="U133" s="47"/>
+      <c r="V133" s="47"/>
+      <c r="W133" s="47"/>
+      <c r="X133" s="47"/>
+      <c r="Y133" s="47"/>
+      <c r="Z133" s="47"/>
+      <c r="AA133" s="47"/>
+      <c r="AB133" s="48"/>
       <c r="AC133" s="11"/>
     </row>
     <row r="134" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5927,245 +5986,245 @@
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="52"/>
-      <c r="I136" s="53"/>
-      <c r="J136" s="53"/>
-      <c r="K136" s="53"/>
-      <c r="L136" s="53"/>
-      <c r="M136" s="53"/>
-      <c r="N136" s="53"/>
-      <c r="O136" s="53"/>
-      <c r="P136" s="53"/>
-      <c r="Q136" s="53"/>
-      <c r="R136" s="53"/>
-      <c r="S136" s="53"/>
-      <c r="T136" s="53"/>
-      <c r="U136" s="53"/>
-      <c r="V136" s="53"/>
-      <c r="W136" s="53"/>
-      <c r="X136" s="53"/>
-      <c r="Y136" s="53"/>
-      <c r="Z136" s="53"/>
-      <c r="AA136" s="53"/>
-      <c r="AB136" s="54"/>
+      <c r="H136" s="49"/>
+      <c r="I136" s="50"/>
+      <c r="J136" s="50"/>
+      <c r="K136" s="50"/>
+      <c r="L136" s="50"/>
+      <c r="M136" s="50"/>
+      <c r="N136" s="50"/>
+      <c r="O136" s="50"/>
+      <c r="P136" s="50"/>
+      <c r="Q136" s="50"/>
+      <c r="R136" s="50"/>
+      <c r="S136" s="50"/>
+      <c r="T136" s="50"/>
+      <c r="U136" s="50"/>
+      <c r="V136" s="50"/>
+      <c r="W136" s="50"/>
+      <c r="X136" s="50"/>
+      <c r="Y136" s="50"/>
+      <c r="Z136" s="50"/>
+      <c r="AA136" s="50"/>
+      <c r="AB136" s="51"/>
       <c r="AC136" s="11"/>
     </row>
     <row r="137" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B137" s="45"/>
-      <c r="C137" s="3"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="4"/>
-      <c r="L137" s="4"/>
-      <c r="M137" s="4"/>
-      <c r="N137" s="4"/>
-      <c r="O137" s="4"/>
-      <c r="P137" s="4"/>
-      <c r="Q137" s="4"/>
-      <c r="R137" s="4"/>
-      <c r="S137" s="4"/>
-      <c r="T137" s="4"/>
-      <c r="U137" s="4"/>
-      <c r="V137" s="4"/>
-      <c r="W137" s="4"/>
-      <c r="X137" s="4"/>
-      <c r="Y137" s="4"/>
-      <c r="Z137" s="4"/>
-      <c r="AA137" s="4"/>
-      <c r="AB137" s="4"/>
-      <c r="AC137" s="12"/>
+      <c r="B137" s="44"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="49"/>
+      <c r="I137" s="50"/>
+      <c r="J137" s="50"/>
+      <c r="K137" s="50"/>
+      <c r="L137" s="50"/>
+      <c r="M137" s="50"/>
+      <c r="N137" s="50"/>
+      <c r="O137" s="50"/>
+      <c r="P137" s="50"/>
+      <c r="Q137" s="50"/>
+      <c r="R137" s="50"/>
+      <c r="S137" s="50"/>
+      <c r="T137" s="50"/>
+      <c r="U137" s="50"/>
+      <c r="V137" s="50"/>
+      <c r="W137" s="50"/>
+      <c r="X137" s="50"/>
+      <c r="Y137" s="50"/>
+      <c r="Z137" s="50"/>
+      <c r="AA137" s="50"/>
+      <c r="AB137" s="51"/>
+      <c r="AC137" s="11"/>
+    </row>
+    <row r="138" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B138" s="44"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="6"/>
+      <c r="H138" s="49"/>
+      <c r="I138" s="50"/>
+      <c r="J138" s="50"/>
+      <c r="K138" s="50"/>
+      <c r="L138" s="50"/>
+      <c r="M138" s="50"/>
+      <c r="N138" s="50"/>
+      <c r="O138" s="50"/>
+      <c r="P138" s="50"/>
+      <c r="Q138" s="50"/>
+      <c r="R138" s="50"/>
+      <c r="S138" s="50"/>
+      <c r="T138" s="50"/>
+      <c r="U138" s="50"/>
+      <c r="V138" s="50"/>
+      <c r="W138" s="50"/>
+      <c r="X138" s="50"/>
+      <c r="Y138" s="50"/>
+      <c r="Z138" s="50"/>
+      <c r="AA138" s="50"/>
+      <c r="AB138" s="51"/>
+      <c r="AC138" s="11"/>
     </row>
     <row r="139" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B139" s="43" t="s">
+      <c r="B139" s="44"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="6"/>
+      <c r="H139" s="52"/>
+      <c r="I139" s="53"/>
+      <c r="J139" s="53"/>
+      <c r="K139" s="53"/>
+      <c r="L139" s="53"/>
+      <c r="M139" s="53"/>
+      <c r="N139" s="53"/>
+      <c r="O139" s="53"/>
+      <c r="P139" s="53"/>
+      <c r="Q139" s="53"/>
+      <c r="R139" s="53"/>
+      <c r="S139" s="53"/>
+      <c r="T139" s="53"/>
+      <c r="U139" s="53"/>
+      <c r="V139" s="53"/>
+      <c r="W139" s="53"/>
+      <c r="X139" s="53"/>
+      <c r="Y139" s="53"/>
+      <c r="Z139" s="53"/>
+      <c r="AA139" s="53"/>
+      <c r="AB139" s="54"/>
+      <c r="AC139" s="11"/>
+    </row>
+    <row r="140" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B140" s="45"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4"/>
+      <c r="G140" s="4"/>
+      <c r="H140" s="4"/>
+      <c r="I140" s="4"/>
+      <c r="J140" s="4"/>
+      <c r="K140" s="4"/>
+      <c r="L140" s="4"/>
+      <c r="M140" s="4"/>
+      <c r="N140" s="4"/>
+      <c r="O140" s="4"/>
+      <c r="P140" s="4"/>
+      <c r="Q140" s="4"/>
+      <c r="R140" s="4"/>
+      <c r="S140" s="4"/>
+      <c r="T140" s="4"/>
+      <c r="U140" s="4"/>
+      <c r="V140" s="4"/>
+      <c r="W140" s="4"/>
+      <c r="X140" s="4"/>
+      <c r="Y140" s="4"/>
+      <c r="Z140" s="4"/>
+      <c r="AA140" s="4"/>
+      <c r="AB140" s="4"/>
+      <c r="AC140" s="12"/>
+    </row>
+    <row r="142" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C139" s="8"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
-      <c r="I139" s="9"/>
-      <c r="J139" s="9"/>
-      <c r="K139" s="9"/>
-      <c r="L139" s="9"/>
-      <c r="M139" s="9"/>
-      <c r="N139" s="9"/>
-      <c r="O139" s="9"/>
-      <c r="P139" s="9"/>
-      <c r="Q139" s="9"/>
-      <c r="R139" s="9"/>
-      <c r="S139" s="9"/>
-      <c r="T139" s="9"/>
-      <c r="U139" s="9"/>
-      <c r="V139" s="9"/>
-      <c r="W139" s="9"/>
-      <c r="X139" s="9"/>
-      <c r="Y139" s="9"/>
-      <c r="Z139" s="9"/>
-      <c r="AA139" s="9"/>
-      <c r="AB139" s="9"/>
-      <c r="AC139" s="10"/>
-    </row>
-    <row r="140" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="44"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
-      <c r="M140" s="6"/>
-      <c r="N140" s="6"/>
-      <c r="O140" s="6"/>
-      <c r="P140" s="6"/>
-      <c r="Q140" s="6"/>
-      <c r="R140" s="6"/>
-      <c r="S140" s="6"/>
-      <c r="T140" s="6"/>
-      <c r="U140" s="6"/>
-      <c r="V140" s="6"/>
-      <c r="W140" s="6"/>
-      <c r="X140" s="6"/>
-      <c r="Y140" s="6"/>
-      <c r="Z140" s="6"/>
-      <c r="AA140" s="6"/>
-      <c r="AB140" s="6"/>
-      <c r="AC140" s="11"/>
-    </row>
-    <row r="141" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B141" s="44"/>
-      <c r="C141" s="5"/>
-      <c r="D141" s="41"/>
-      <c r="E141" s="42"/>
-      <c r="F141" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G141" s="6"/>
-      <c r="H141" s="46"/>
-      <c r="I141" s="47"/>
-      <c r="J141" s="47"/>
-      <c r="K141" s="47"/>
-      <c r="L141" s="47"/>
-      <c r="M141" s="47"/>
-      <c r="N141" s="47"/>
-      <c r="O141" s="47"/>
-      <c r="P141" s="47"/>
-      <c r="Q141" s="47"/>
-      <c r="R141" s="47"/>
-      <c r="S141" s="47"/>
-      <c r="T141" s="47"/>
-      <c r="U141" s="47"/>
-      <c r="V141" s="47"/>
-      <c r="W141" s="47"/>
-      <c r="X141" s="47"/>
-      <c r="Y141" s="47"/>
-      <c r="Z141" s="47"/>
-      <c r="AA141" s="47"/>
-      <c r="AB141" s="48"/>
-      <c r="AC141" s="11"/>
-    </row>
-    <row r="142" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="44"/>
-      <c r="C142" s="5"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="49"/>
-      <c r="I142" s="50"/>
-      <c r="J142" s="50"/>
-      <c r="K142" s="50"/>
-      <c r="L142" s="50"/>
-      <c r="M142" s="50"/>
-      <c r="N142" s="50"/>
-      <c r="O142" s="50"/>
-      <c r="P142" s="50"/>
-      <c r="Q142" s="50"/>
-      <c r="R142" s="50"/>
-      <c r="S142" s="50"/>
-      <c r="T142" s="50"/>
-      <c r="U142" s="50"/>
-      <c r="V142" s="50"/>
-      <c r="W142" s="50"/>
-      <c r="X142" s="50"/>
-      <c r="Y142" s="50"/>
-      <c r="Z142" s="50"/>
-      <c r="AA142" s="50"/>
-      <c r="AB142" s="51"/>
-      <c r="AC142" s="11"/>
+      <c r="C142" s="8"/>
+      <c r="D142" s="9"/>
+      <c r="E142" s="9"/>
+      <c r="F142" s="9"/>
+      <c r="G142" s="9"/>
+      <c r="H142" s="9"/>
+      <c r="I142" s="9"/>
+      <c r="J142" s="9"/>
+      <c r="K142" s="9"/>
+      <c r="L142" s="9"/>
+      <c r="M142" s="9"/>
+      <c r="N142" s="9"/>
+      <c r="O142" s="9"/>
+      <c r="P142" s="9"/>
+      <c r="Q142" s="9"/>
+      <c r="R142" s="9"/>
+      <c r="S142" s="9"/>
+      <c r="T142" s="9"/>
+      <c r="U142" s="9"/>
+      <c r="V142" s="9"/>
+      <c r="W142" s="9"/>
+      <c r="X142" s="9"/>
+      <c r="Y142" s="9"/>
+      <c r="Z142" s="9"/>
+      <c r="AA142" s="9"/>
+      <c r="AB142" s="9"/>
+      <c r="AC142" s="10"/>
     </row>
     <row r="143" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B143" s="44"/>
       <c r="C143" s="5"/>
-      <c r="D143" s="6"/>
+      <c r="D143" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
-      <c r="H143" s="49"/>
-      <c r="I143" s="50"/>
-      <c r="J143" s="50"/>
-      <c r="K143" s="50"/>
-      <c r="L143" s="50"/>
-      <c r="M143" s="50"/>
-      <c r="N143" s="50"/>
-      <c r="O143" s="50"/>
-      <c r="P143" s="50"/>
-      <c r="Q143" s="50"/>
-      <c r="R143" s="50"/>
-      <c r="S143" s="50"/>
-      <c r="T143" s="50"/>
-      <c r="U143" s="50"/>
-      <c r="V143" s="50"/>
-      <c r="W143" s="50"/>
-      <c r="X143" s="50"/>
-      <c r="Y143" s="50"/>
-      <c r="Z143" s="50"/>
-      <c r="AA143" s="50"/>
-      <c r="AB143" s="51"/>
+      <c r="H143" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I143" s="6"/>
+      <c r="J143" s="6"/>
+      <c r="K143" s="6"/>
+      <c r="L143" s="6"/>
+      <c r="M143" s="6"/>
+      <c r="N143" s="6"/>
+      <c r="O143" s="6"/>
+      <c r="P143" s="6"/>
+      <c r="Q143" s="6"/>
+      <c r="R143" s="6"/>
+      <c r="S143" s="6"/>
+      <c r="T143" s="6"/>
+      <c r="U143" s="6"/>
+      <c r="V143" s="6"/>
+      <c r="W143" s="6"/>
+      <c r="X143" s="6"/>
+      <c r="Y143" s="6"/>
+      <c r="Z143" s="6"/>
+      <c r="AA143" s="6"/>
+      <c r="AB143" s="6"/>
       <c r="AC143" s="11"/>
     </row>
     <row r="144" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B144" s="44"/>
       <c r="C144" s="5"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
+      <c r="D144" s="41"/>
+      <c r="E144" s="42"/>
+      <c r="F144" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="G144" s="6"/>
-      <c r="H144" s="49"/>
-      <c r="I144" s="50"/>
-      <c r="J144" s="50"/>
-      <c r="K144" s="50"/>
-      <c r="L144" s="50"/>
-      <c r="M144" s="50"/>
-      <c r="N144" s="50"/>
-      <c r="O144" s="50"/>
-      <c r="P144" s="50"/>
-      <c r="Q144" s="50"/>
-      <c r="R144" s="50"/>
-      <c r="S144" s="50"/>
-      <c r="T144" s="50"/>
-      <c r="U144" s="50"/>
-      <c r="V144" s="50"/>
-      <c r="W144" s="50"/>
-      <c r="X144" s="50"/>
-      <c r="Y144" s="50"/>
-      <c r="Z144" s="50"/>
-      <c r="AA144" s="50"/>
-      <c r="AB144" s="51"/>
+      <c r="H144" s="46"/>
+      <c r="I144" s="47"/>
+      <c r="J144" s="47"/>
+      <c r="K144" s="47"/>
+      <c r="L144" s="47"/>
+      <c r="M144" s="47"/>
+      <c r="N144" s="47"/>
+      <c r="O144" s="47"/>
+      <c r="P144" s="47"/>
+      <c r="Q144" s="47"/>
+      <c r="R144" s="47"/>
+      <c r="S144" s="47"/>
+      <c r="T144" s="47"/>
+      <c r="U144" s="47"/>
+      <c r="V144" s="47"/>
+      <c r="W144" s="47"/>
+      <c r="X144" s="47"/>
+      <c r="Y144" s="47"/>
+      <c r="Z144" s="47"/>
+      <c r="AA144" s="47"/>
+      <c r="AB144" s="48"/>
       <c r="AC144" s="11"/>
     </row>
     <row r="145" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6235,27 +6294,27 @@
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
-      <c r="H147" s="52"/>
-      <c r="I147" s="53"/>
-      <c r="J147" s="53"/>
-      <c r="K147" s="53"/>
-      <c r="L147" s="53"/>
-      <c r="M147" s="53"/>
-      <c r="N147" s="53"/>
-      <c r="O147" s="53"/>
-      <c r="P147" s="53"/>
-      <c r="Q147" s="53"/>
-      <c r="R147" s="53"/>
-      <c r="S147" s="53"/>
-      <c r="T147" s="53"/>
-      <c r="U147" s="53"/>
-      <c r="V147" s="53"/>
-      <c r="W147" s="53"/>
-      <c r="X147" s="53"/>
-      <c r="Y147" s="53"/>
-      <c r="Z147" s="53"/>
-      <c r="AA147" s="53"/>
-      <c r="AB147" s="54"/>
+      <c r="H147" s="49"/>
+      <c r="I147" s="50"/>
+      <c r="J147" s="50"/>
+      <c r="K147" s="50"/>
+      <c r="L147" s="50"/>
+      <c r="M147" s="50"/>
+      <c r="N147" s="50"/>
+      <c r="O147" s="50"/>
+      <c r="P147" s="50"/>
+      <c r="Q147" s="50"/>
+      <c r="R147" s="50"/>
+      <c r="S147" s="50"/>
+      <c r="T147" s="50"/>
+      <c r="U147" s="50"/>
+      <c r="V147" s="50"/>
+      <c r="W147" s="50"/>
+      <c r="X147" s="50"/>
+      <c r="Y147" s="50"/>
+      <c r="Z147" s="50"/>
+      <c r="AA147" s="50"/>
+      <c r="AB147" s="51"/>
       <c r="AC147" s="11"/>
     </row>
     <row r="148" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6265,29 +6324,27 @@
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
-      <c r="H148" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="6"/>
-      <c r="L148" s="6"/>
-      <c r="M148" s="6"/>
-      <c r="N148" s="6"/>
-      <c r="O148" s="6"/>
-      <c r="P148" s="6"/>
-      <c r="Q148" s="6"/>
-      <c r="R148" s="6"/>
-      <c r="S148" s="6"/>
-      <c r="T148" s="6"/>
-      <c r="U148" s="6"/>
-      <c r="V148" s="6"/>
-      <c r="W148" s="6"/>
-      <c r="X148" s="6"/>
-      <c r="Y148" s="6"/>
-      <c r="Z148" s="6"/>
-      <c r="AA148" s="6"/>
-      <c r="AB148" s="6"/>
+      <c r="H148" s="49"/>
+      <c r="I148" s="50"/>
+      <c r="J148" s="50"/>
+      <c r="K148" s="50"/>
+      <c r="L148" s="50"/>
+      <c r="M148" s="50"/>
+      <c r="N148" s="50"/>
+      <c r="O148" s="50"/>
+      <c r="P148" s="50"/>
+      <c r="Q148" s="50"/>
+      <c r="R148" s="50"/>
+      <c r="S148" s="50"/>
+      <c r="T148" s="50"/>
+      <c r="U148" s="50"/>
+      <c r="V148" s="50"/>
+      <c r="W148" s="50"/>
+      <c r="X148" s="50"/>
+      <c r="Y148" s="50"/>
+      <c r="Z148" s="50"/>
+      <c r="AA148" s="50"/>
+      <c r="AB148" s="51"/>
       <c r="AC148" s="11"/>
     </row>
     <row r="149" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6297,27 +6354,27 @@
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
-      <c r="H149" s="46"/>
-      <c r="I149" s="47"/>
-      <c r="J149" s="47"/>
-      <c r="K149" s="47"/>
-      <c r="L149" s="47"/>
-      <c r="M149" s="47"/>
-      <c r="N149" s="47"/>
-      <c r="O149" s="47"/>
-      <c r="P149" s="47"/>
-      <c r="Q149" s="47"/>
-      <c r="R149" s="47"/>
-      <c r="S149" s="47"/>
-      <c r="T149" s="47"/>
-      <c r="U149" s="47"/>
-      <c r="V149" s="47"/>
-      <c r="W149" s="47"/>
-      <c r="X149" s="47"/>
-      <c r="Y149" s="47"/>
-      <c r="Z149" s="47"/>
-      <c r="AA149" s="47"/>
-      <c r="AB149" s="48"/>
+      <c r="H149" s="49"/>
+      <c r="I149" s="50"/>
+      <c r="J149" s="50"/>
+      <c r="K149" s="50"/>
+      <c r="L149" s="50"/>
+      <c r="M149" s="50"/>
+      <c r="N149" s="50"/>
+      <c r="O149" s="50"/>
+      <c r="P149" s="50"/>
+      <c r="Q149" s="50"/>
+      <c r="R149" s="50"/>
+      <c r="S149" s="50"/>
+      <c r="T149" s="50"/>
+      <c r="U149" s="50"/>
+      <c r="V149" s="50"/>
+      <c r="W149" s="50"/>
+      <c r="X149" s="50"/>
+      <c r="Y149" s="50"/>
+      <c r="Z149" s="50"/>
+      <c r="AA149" s="50"/>
+      <c r="AB149" s="51"/>
       <c r="AC149" s="11"/>
     </row>
     <row r="150" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6327,27 +6384,27 @@
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
-      <c r="H150" s="49"/>
-      <c r="I150" s="50"/>
-      <c r="J150" s="50"/>
-      <c r="K150" s="50"/>
-      <c r="L150" s="50"/>
-      <c r="M150" s="50"/>
-      <c r="N150" s="50"/>
-      <c r="O150" s="50"/>
-      <c r="P150" s="50"/>
-      <c r="Q150" s="50"/>
-      <c r="R150" s="50"/>
-      <c r="S150" s="50"/>
-      <c r="T150" s="50"/>
-      <c r="U150" s="50"/>
-      <c r="V150" s="50"/>
-      <c r="W150" s="50"/>
-      <c r="X150" s="50"/>
-      <c r="Y150" s="50"/>
-      <c r="Z150" s="50"/>
-      <c r="AA150" s="50"/>
-      <c r="AB150" s="51"/>
+      <c r="H150" s="52"/>
+      <c r="I150" s="53"/>
+      <c r="J150" s="53"/>
+      <c r="K150" s="53"/>
+      <c r="L150" s="53"/>
+      <c r="M150" s="53"/>
+      <c r="N150" s="53"/>
+      <c r="O150" s="53"/>
+      <c r="P150" s="53"/>
+      <c r="Q150" s="53"/>
+      <c r="R150" s="53"/>
+      <c r="S150" s="53"/>
+      <c r="T150" s="53"/>
+      <c r="U150" s="53"/>
+      <c r="V150" s="53"/>
+      <c r="W150" s="53"/>
+      <c r="X150" s="53"/>
+      <c r="Y150" s="53"/>
+      <c r="Z150" s="53"/>
+      <c r="AA150" s="53"/>
+      <c r="AB150" s="54"/>
       <c r="AC150" s="11"/>
     </row>
     <row r="151" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6357,27 +6414,29 @@
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
-      <c r="H151" s="49"/>
-      <c r="I151" s="50"/>
-      <c r="J151" s="50"/>
-      <c r="K151" s="50"/>
-      <c r="L151" s="50"/>
-      <c r="M151" s="50"/>
-      <c r="N151" s="50"/>
-      <c r="O151" s="50"/>
-      <c r="P151" s="50"/>
-      <c r="Q151" s="50"/>
-      <c r="R151" s="50"/>
-      <c r="S151" s="50"/>
-      <c r="T151" s="50"/>
-      <c r="U151" s="50"/>
-      <c r="V151" s="50"/>
-      <c r="W151" s="50"/>
-      <c r="X151" s="50"/>
-      <c r="Y151" s="50"/>
-      <c r="Z151" s="50"/>
-      <c r="AA151" s="50"/>
-      <c r="AB151" s="51"/>
+      <c r="H151" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I151" s="6"/>
+      <c r="J151" s="6"/>
+      <c r="K151" s="6"/>
+      <c r="L151" s="6"/>
+      <c r="M151" s="6"/>
+      <c r="N151" s="6"/>
+      <c r="O151" s="6"/>
+      <c r="P151" s="6"/>
+      <c r="Q151" s="6"/>
+      <c r="R151" s="6"/>
+      <c r="S151" s="6"/>
+      <c r="T151" s="6"/>
+      <c r="U151" s="6"/>
+      <c r="V151" s="6"/>
+      <c r="W151" s="6"/>
+      <c r="X151" s="6"/>
+      <c r="Y151" s="6"/>
+      <c r="Z151" s="6"/>
+      <c r="AA151" s="6"/>
+      <c r="AB151" s="6"/>
       <c r="AC151" s="11"/>
     </row>
     <row r="152" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6387,27 +6446,27 @@
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
-      <c r="H152" s="49"/>
-      <c r="I152" s="50"/>
-      <c r="J152" s="50"/>
-      <c r="K152" s="50"/>
-      <c r="L152" s="50"/>
-      <c r="M152" s="50"/>
-      <c r="N152" s="50"/>
-      <c r="O152" s="50"/>
-      <c r="P152" s="50"/>
-      <c r="Q152" s="50"/>
-      <c r="R152" s="50"/>
-      <c r="S152" s="50"/>
-      <c r="T152" s="50"/>
-      <c r="U152" s="50"/>
-      <c r="V152" s="50"/>
-      <c r="W152" s="50"/>
-      <c r="X152" s="50"/>
-      <c r="Y152" s="50"/>
-      <c r="Z152" s="50"/>
-      <c r="AA152" s="50"/>
-      <c r="AB152" s="51"/>
+      <c r="H152" s="46"/>
+      <c r="I152" s="47"/>
+      <c r="J152" s="47"/>
+      <c r="K152" s="47"/>
+      <c r="L152" s="47"/>
+      <c r="M152" s="47"/>
+      <c r="N152" s="47"/>
+      <c r="O152" s="47"/>
+      <c r="P152" s="47"/>
+      <c r="Q152" s="47"/>
+      <c r="R152" s="47"/>
+      <c r="S152" s="47"/>
+      <c r="T152" s="47"/>
+      <c r="U152" s="47"/>
+      <c r="V152" s="47"/>
+      <c r="W152" s="47"/>
+      <c r="X152" s="47"/>
+      <c r="Y152" s="47"/>
+      <c r="Z152" s="47"/>
+      <c r="AA152" s="47"/>
+      <c r="AB152" s="48"/>
       <c r="AC152" s="11"/>
     </row>
     <row r="153" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6477,245 +6536,245 @@
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
-      <c r="H155" s="52"/>
-      <c r="I155" s="53"/>
-      <c r="J155" s="53"/>
-      <c r="K155" s="53"/>
-      <c r="L155" s="53"/>
-      <c r="M155" s="53"/>
-      <c r="N155" s="53"/>
-      <c r="O155" s="53"/>
-      <c r="P155" s="53"/>
-      <c r="Q155" s="53"/>
-      <c r="R155" s="53"/>
-      <c r="S155" s="53"/>
-      <c r="T155" s="53"/>
-      <c r="U155" s="53"/>
-      <c r="V155" s="53"/>
-      <c r="W155" s="53"/>
-      <c r="X155" s="53"/>
-      <c r="Y155" s="53"/>
-      <c r="Z155" s="53"/>
-      <c r="AA155" s="53"/>
-      <c r="AB155" s="54"/>
+      <c r="H155" s="49"/>
+      <c r="I155" s="50"/>
+      <c r="J155" s="50"/>
+      <c r="K155" s="50"/>
+      <c r="L155" s="50"/>
+      <c r="M155" s="50"/>
+      <c r="N155" s="50"/>
+      <c r="O155" s="50"/>
+      <c r="P155" s="50"/>
+      <c r="Q155" s="50"/>
+      <c r="R155" s="50"/>
+      <c r="S155" s="50"/>
+      <c r="T155" s="50"/>
+      <c r="U155" s="50"/>
+      <c r="V155" s="50"/>
+      <c r="W155" s="50"/>
+      <c r="X155" s="50"/>
+      <c r="Y155" s="50"/>
+      <c r="Z155" s="50"/>
+      <c r="AA155" s="50"/>
+      <c r="AB155" s="51"/>
       <c r="AC155" s="11"/>
     </row>
     <row r="156" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B156" s="45"/>
-      <c r="C156" s="3"/>
-      <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
-      <c r="F156" s="4"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
-      <c r="K156" s="4"/>
-      <c r="L156" s="4"/>
-      <c r="M156" s="4"/>
-      <c r="N156" s="4"/>
-      <c r="O156" s="4"/>
-      <c r="P156" s="4"/>
-      <c r="Q156" s="4"/>
-      <c r="R156" s="4"/>
-      <c r="S156" s="4"/>
-      <c r="T156" s="4"/>
-      <c r="U156" s="4"/>
-      <c r="V156" s="4"/>
-      <c r="W156" s="4"/>
-      <c r="X156" s="4"/>
-      <c r="Y156" s="4"/>
-      <c r="Z156" s="4"/>
-      <c r="AA156" s="4"/>
-      <c r="AB156" s="4"/>
-      <c r="AC156" s="12"/>
+      <c r="B156" s="44"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="6"/>
+      <c r="H156" s="49"/>
+      <c r="I156" s="50"/>
+      <c r="J156" s="50"/>
+      <c r="K156" s="50"/>
+      <c r="L156" s="50"/>
+      <c r="M156" s="50"/>
+      <c r="N156" s="50"/>
+      <c r="O156" s="50"/>
+      <c r="P156" s="50"/>
+      <c r="Q156" s="50"/>
+      <c r="R156" s="50"/>
+      <c r="S156" s="50"/>
+      <c r="T156" s="50"/>
+      <c r="U156" s="50"/>
+      <c r="V156" s="50"/>
+      <c r="W156" s="50"/>
+      <c r="X156" s="50"/>
+      <c r="Y156" s="50"/>
+      <c r="Z156" s="50"/>
+      <c r="AA156" s="50"/>
+      <c r="AB156" s="51"/>
+      <c r="AC156" s="11"/>
+    </row>
+    <row r="157" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B157" s="44"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="6"/>
+      <c r="E157" s="6"/>
+      <c r="F157" s="6"/>
+      <c r="G157" s="6"/>
+      <c r="H157" s="49"/>
+      <c r="I157" s="50"/>
+      <c r="J157" s="50"/>
+      <c r="K157" s="50"/>
+      <c r="L157" s="50"/>
+      <c r="M157" s="50"/>
+      <c r="N157" s="50"/>
+      <c r="O157" s="50"/>
+      <c r="P157" s="50"/>
+      <c r="Q157" s="50"/>
+      <c r="R157" s="50"/>
+      <c r="S157" s="50"/>
+      <c r="T157" s="50"/>
+      <c r="U157" s="50"/>
+      <c r="V157" s="50"/>
+      <c r="W157" s="50"/>
+      <c r="X157" s="50"/>
+      <c r="Y157" s="50"/>
+      <c r="Z157" s="50"/>
+      <c r="AA157" s="50"/>
+      <c r="AB157" s="51"/>
+      <c r="AC157" s="11"/>
     </row>
     <row r="158" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="43" t="s">
+      <c r="B158" s="44"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="6"/>
+      <c r="F158" s="6"/>
+      <c r="G158" s="6"/>
+      <c r="H158" s="52"/>
+      <c r="I158" s="53"/>
+      <c r="J158" s="53"/>
+      <c r="K158" s="53"/>
+      <c r="L158" s="53"/>
+      <c r="M158" s="53"/>
+      <c r="N158" s="53"/>
+      <c r="O158" s="53"/>
+      <c r="P158" s="53"/>
+      <c r="Q158" s="53"/>
+      <c r="R158" s="53"/>
+      <c r="S158" s="53"/>
+      <c r="T158" s="53"/>
+      <c r="U158" s="53"/>
+      <c r="V158" s="53"/>
+      <c r="W158" s="53"/>
+      <c r="X158" s="53"/>
+      <c r="Y158" s="53"/>
+      <c r="Z158" s="53"/>
+      <c r="AA158" s="53"/>
+      <c r="AB158" s="54"/>
+      <c r="AC158" s="11"/>
+    </row>
+    <row r="159" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B159" s="45"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4"/>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
+      <c r="I159" s="4"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
+      <c r="L159" s="4"/>
+      <c r="M159" s="4"/>
+      <c r="N159" s="4"/>
+      <c r="O159" s="4"/>
+      <c r="P159" s="4"/>
+      <c r="Q159" s="4"/>
+      <c r="R159" s="4"/>
+      <c r="S159" s="4"/>
+      <c r="T159" s="4"/>
+      <c r="U159" s="4"/>
+      <c r="V159" s="4"/>
+      <c r="W159" s="4"/>
+      <c r="X159" s="4"/>
+      <c r="Y159" s="4"/>
+      <c r="Z159" s="4"/>
+      <c r="AA159" s="4"/>
+      <c r="AB159" s="4"/>
+      <c r="AC159" s="12"/>
+    </row>
+    <row r="161" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B161" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="C158" s="8"/>
-      <c r="D158" s="9"/>
-      <c r="E158" s="9"/>
-      <c r="F158" s="9"/>
-      <c r="G158" s="9"/>
-      <c r="H158" s="9"/>
-      <c r="I158" s="9"/>
-      <c r="J158" s="9"/>
-      <c r="K158" s="9"/>
-      <c r="L158" s="9"/>
-      <c r="M158" s="9"/>
-      <c r="N158" s="9"/>
-      <c r="O158" s="9"/>
-      <c r="P158" s="9"/>
-      <c r="Q158" s="9"/>
-      <c r="R158" s="9"/>
-      <c r="S158" s="9"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="10"/>
-    </row>
-    <row r="159" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B159" s="44"/>
-      <c r="C159" s="5"/>
-      <c r="D159" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I159" s="6"/>
-      <c r="J159" s="6"/>
-      <c r="K159" s="6"/>
-      <c r="L159" s="6"/>
-      <c r="M159" s="6"/>
-      <c r="N159" s="6"/>
-      <c r="O159" s="6"/>
-      <c r="P159" s="6"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="6"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="6"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="6"/>
-      <c r="AB159" s="6"/>
-      <c r="AC159" s="11"/>
-    </row>
-    <row r="160" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B160" s="44"/>
-      <c r="C160" s="5"/>
-      <c r="D160" s="41"/>
-      <c r="E160" s="42"/>
-      <c r="F160" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G160" s="6"/>
-      <c r="H160" s="46"/>
-      <c r="I160" s="47"/>
-      <c r="J160" s="47"/>
-      <c r="K160" s="47"/>
-      <c r="L160" s="47"/>
-      <c r="M160" s="47"/>
-      <c r="N160" s="47"/>
-      <c r="O160" s="47"/>
-      <c r="P160" s="47"/>
-      <c r="Q160" s="47"/>
-      <c r="R160" s="47"/>
-      <c r="S160" s="47"/>
-      <c r="T160" s="47"/>
-      <c r="U160" s="47"/>
-      <c r="V160" s="47"/>
-      <c r="W160" s="47"/>
-      <c r="X160" s="47"/>
-      <c r="Y160" s="47"/>
-      <c r="Z160" s="47"/>
-      <c r="AA160" s="47"/>
-      <c r="AB160" s="48"/>
-      <c r="AC160" s="11"/>
-    </row>
-    <row r="161" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B161" s="44"/>
-      <c r="C161" s="5"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="49"/>
-      <c r="I161" s="50"/>
-      <c r="J161" s="50"/>
-      <c r="K161" s="50"/>
-      <c r="L161" s="50"/>
-      <c r="M161" s="50"/>
-      <c r="N161" s="50"/>
-      <c r="O161" s="50"/>
-      <c r="P161" s="50"/>
-      <c r="Q161" s="50"/>
-      <c r="R161" s="50"/>
-      <c r="S161" s="50"/>
-      <c r="T161" s="50"/>
-      <c r="U161" s="50"/>
-      <c r="V161" s="50"/>
-      <c r="W161" s="50"/>
-      <c r="X161" s="50"/>
-      <c r="Y161" s="50"/>
-      <c r="Z161" s="50"/>
-      <c r="AA161" s="50"/>
-      <c r="AB161" s="51"/>
-      <c r="AC161" s="11"/>
+      <c r="C161" s="8"/>
+      <c r="D161" s="9"/>
+      <c r="E161" s="9"/>
+      <c r="F161" s="9"/>
+      <c r="G161" s="9"/>
+      <c r="H161" s="9"/>
+      <c r="I161" s="9"/>
+      <c r="J161" s="9"/>
+      <c r="K161" s="9"/>
+      <c r="L161" s="9"/>
+      <c r="M161" s="9"/>
+      <c r="N161" s="9"/>
+      <c r="O161" s="9"/>
+      <c r="P161" s="9"/>
+      <c r="Q161" s="9"/>
+      <c r="R161" s="9"/>
+      <c r="S161" s="9"/>
+      <c r="T161" s="9"/>
+      <c r="U161" s="9"/>
+      <c r="V161" s="9"/>
+      <c r="W161" s="9"/>
+      <c r="X161" s="9"/>
+      <c r="Y161" s="9"/>
+      <c r="Z161" s="9"/>
+      <c r="AA161" s="9"/>
+      <c r="AB161" s="9"/>
+      <c r="AC161" s="10"/>
     </row>
     <row r="162" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B162" s="44"/>
       <c r="C162" s="5"/>
-      <c r="D162" s="6"/>
+      <c r="D162" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
-      <c r="H162" s="49"/>
-      <c r="I162" s="50"/>
-      <c r="J162" s="50"/>
-      <c r="K162" s="50"/>
-      <c r="L162" s="50"/>
-      <c r="M162" s="50"/>
-      <c r="N162" s="50"/>
-      <c r="O162" s="50"/>
-      <c r="P162" s="50"/>
-      <c r="Q162" s="50"/>
-      <c r="R162" s="50"/>
-      <c r="S162" s="50"/>
-      <c r="T162" s="50"/>
-      <c r="U162" s="50"/>
-      <c r="V162" s="50"/>
-      <c r="W162" s="50"/>
-      <c r="X162" s="50"/>
-      <c r="Y162" s="50"/>
-      <c r="Z162" s="50"/>
-      <c r="AA162" s="50"/>
-      <c r="AB162" s="51"/>
+      <c r="H162" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I162" s="6"/>
+      <c r="J162" s="6"/>
+      <c r="K162" s="6"/>
+      <c r="L162" s="6"/>
+      <c r="M162" s="6"/>
+      <c r="N162" s="6"/>
+      <c r="O162" s="6"/>
+      <c r="P162" s="6"/>
+      <c r="Q162" s="6"/>
+      <c r="R162" s="6"/>
+      <c r="S162" s="6"/>
+      <c r="T162" s="6"/>
+      <c r="U162" s="6"/>
+      <c r="V162" s="6"/>
+      <c r="W162" s="6"/>
+      <c r="X162" s="6"/>
+      <c r="Y162" s="6"/>
+      <c r="Z162" s="6"/>
+      <c r="AA162" s="6"/>
+      <c r="AB162" s="6"/>
       <c r="AC162" s="11"/>
     </row>
     <row r="163" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B163" s="44"/>
       <c r="C163" s="5"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
+      <c r="D163" s="41"/>
+      <c r="E163" s="42"/>
+      <c r="F163" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="G163" s="6"/>
-      <c r="H163" s="49"/>
-      <c r="I163" s="50"/>
-      <c r="J163" s="50"/>
-      <c r="K163" s="50"/>
-      <c r="L163" s="50"/>
-      <c r="M163" s="50"/>
-      <c r="N163" s="50"/>
-      <c r="O163" s="50"/>
-      <c r="P163" s="50"/>
-      <c r="Q163" s="50"/>
-      <c r="R163" s="50"/>
-      <c r="S163" s="50"/>
-      <c r="T163" s="50"/>
-      <c r="U163" s="50"/>
-      <c r="V163" s="50"/>
-      <c r="W163" s="50"/>
-      <c r="X163" s="50"/>
-      <c r="Y163" s="50"/>
-      <c r="Z163" s="50"/>
-      <c r="AA163" s="50"/>
-      <c r="AB163" s="51"/>
+      <c r="H163" s="46"/>
+      <c r="I163" s="47"/>
+      <c r="J163" s="47"/>
+      <c r="K163" s="47"/>
+      <c r="L163" s="47"/>
+      <c r="M163" s="47"/>
+      <c r="N163" s="47"/>
+      <c r="O163" s="47"/>
+      <c r="P163" s="47"/>
+      <c r="Q163" s="47"/>
+      <c r="R163" s="47"/>
+      <c r="S163" s="47"/>
+      <c r="T163" s="47"/>
+      <c r="U163" s="47"/>
+      <c r="V163" s="47"/>
+      <c r="W163" s="47"/>
+      <c r="X163" s="47"/>
+      <c r="Y163" s="47"/>
+      <c r="Z163" s="47"/>
+      <c r="AA163" s="47"/>
+      <c r="AB163" s="48"/>
       <c r="AC163" s="11"/>
     </row>
     <row r="164" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6785,27 +6844,27 @@
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
-      <c r="H166" s="52"/>
-      <c r="I166" s="53"/>
-      <c r="J166" s="53"/>
-      <c r="K166" s="53"/>
-      <c r="L166" s="53"/>
-      <c r="M166" s="53"/>
-      <c r="N166" s="53"/>
-      <c r="O166" s="53"/>
-      <c r="P166" s="53"/>
-      <c r="Q166" s="53"/>
-      <c r="R166" s="53"/>
-      <c r="S166" s="53"/>
-      <c r="T166" s="53"/>
-      <c r="U166" s="53"/>
-      <c r="V166" s="53"/>
-      <c r="W166" s="53"/>
-      <c r="X166" s="53"/>
-      <c r="Y166" s="53"/>
-      <c r="Z166" s="53"/>
-      <c r="AA166" s="53"/>
-      <c r="AB166" s="54"/>
+      <c r="H166" s="49"/>
+      <c r="I166" s="50"/>
+      <c r="J166" s="50"/>
+      <c r="K166" s="50"/>
+      <c r="L166" s="50"/>
+      <c r="M166" s="50"/>
+      <c r="N166" s="50"/>
+      <c r="O166" s="50"/>
+      <c r="P166" s="50"/>
+      <c r="Q166" s="50"/>
+      <c r="R166" s="50"/>
+      <c r="S166" s="50"/>
+      <c r="T166" s="50"/>
+      <c r="U166" s="50"/>
+      <c r="V166" s="50"/>
+      <c r="W166" s="50"/>
+      <c r="X166" s="50"/>
+      <c r="Y166" s="50"/>
+      <c r="Z166" s="50"/>
+      <c r="AA166" s="50"/>
+      <c r="AB166" s="51"/>
       <c r="AC166" s="11"/>
     </row>
     <row r="167" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6815,29 +6874,27 @@
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
-      <c r="H167" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
-      <c r="L167" s="6"/>
-      <c r="M167" s="6"/>
-      <c r="N167" s="6"/>
-      <c r="O167" s="6"/>
-      <c r="P167" s="6"/>
-      <c r="Q167" s="6"/>
-      <c r="R167" s="6"/>
-      <c r="S167" s="6"/>
-      <c r="T167" s="6"/>
-      <c r="U167" s="6"/>
-      <c r="V167" s="6"/>
-      <c r="W167" s="6"/>
-      <c r="X167" s="6"/>
-      <c r="Y167" s="6"/>
-      <c r="Z167" s="6"/>
-      <c r="AA167" s="6"/>
-      <c r="AB167" s="6"/>
+      <c r="H167" s="49"/>
+      <c r="I167" s="50"/>
+      <c r="J167" s="50"/>
+      <c r="K167" s="50"/>
+      <c r="L167" s="50"/>
+      <c r="M167" s="50"/>
+      <c r="N167" s="50"/>
+      <c r="O167" s="50"/>
+      <c r="P167" s="50"/>
+      <c r="Q167" s="50"/>
+      <c r="R167" s="50"/>
+      <c r="S167" s="50"/>
+      <c r="T167" s="50"/>
+      <c r="U167" s="50"/>
+      <c r="V167" s="50"/>
+      <c r="W167" s="50"/>
+      <c r="X167" s="50"/>
+      <c r="Y167" s="50"/>
+      <c r="Z167" s="50"/>
+      <c r="AA167" s="50"/>
+      <c r="AB167" s="51"/>
       <c r="AC167" s="11"/>
     </row>
     <row r="168" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6847,27 +6904,27 @@
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
-      <c r="H168" s="46"/>
-      <c r="I168" s="47"/>
-      <c r="J168" s="47"/>
-      <c r="K168" s="47"/>
-      <c r="L168" s="47"/>
-      <c r="M168" s="47"/>
-      <c r="N168" s="47"/>
-      <c r="O168" s="47"/>
-      <c r="P168" s="47"/>
-      <c r="Q168" s="47"/>
-      <c r="R168" s="47"/>
-      <c r="S168" s="47"/>
-      <c r="T168" s="47"/>
-      <c r="U168" s="47"/>
-      <c r="V168" s="47"/>
-      <c r="W168" s="47"/>
-      <c r="X168" s="47"/>
-      <c r="Y168" s="47"/>
-      <c r="Z168" s="47"/>
-      <c r="AA168" s="47"/>
-      <c r="AB168" s="48"/>
+      <c r="H168" s="49"/>
+      <c r="I168" s="50"/>
+      <c r="J168" s="50"/>
+      <c r="K168" s="50"/>
+      <c r="L168" s="50"/>
+      <c r="M168" s="50"/>
+      <c r="N168" s="50"/>
+      <c r="O168" s="50"/>
+      <c r="P168" s="50"/>
+      <c r="Q168" s="50"/>
+      <c r="R168" s="50"/>
+      <c r="S168" s="50"/>
+      <c r="T168" s="50"/>
+      <c r="U168" s="50"/>
+      <c r="V168" s="50"/>
+      <c r="W168" s="50"/>
+      <c r="X168" s="50"/>
+      <c r="Y168" s="50"/>
+      <c r="Z168" s="50"/>
+      <c r="AA168" s="50"/>
+      <c r="AB168" s="51"/>
       <c r="AC168" s="11"/>
     </row>
     <row r="169" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6877,27 +6934,27 @@
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
-      <c r="H169" s="49"/>
-      <c r="I169" s="50"/>
-      <c r="J169" s="50"/>
-      <c r="K169" s="50"/>
-      <c r="L169" s="50"/>
-      <c r="M169" s="50"/>
-      <c r="N169" s="50"/>
-      <c r="O169" s="50"/>
-      <c r="P169" s="50"/>
-      <c r="Q169" s="50"/>
-      <c r="R169" s="50"/>
-      <c r="S169" s="50"/>
-      <c r="T169" s="50"/>
-      <c r="U169" s="50"/>
-      <c r="V169" s="50"/>
-      <c r="W169" s="50"/>
-      <c r="X169" s="50"/>
-      <c r="Y169" s="50"/>
-      <c r="Z169" s="50"/>
-      <c r="AA169" s="50"/>
-      <c r="AB169" s="51"/>
+      <c r="H169" s="52"/>
+      <c r="I169" s="53"/>
+      <c r="J169" s="53"/>
+      <c r="K169" s="53"/>
+      <c r="L169" s="53"/>
+      <c r="M169" s="53"/>
+      <c r="N169" s="53"/>
+      <c r="O169" s="53"/>
+      <c r="P169" s="53"/>
+      <c r="Q169" s="53"/>
+      <c r="R169" s="53"/>
+      <c r="S169" s="53"/>
+      <c r="T169" s="53"/>
+      <c r="U169" s="53"/>
+      <c r="V169" s="53"/>
+      <c r="W169" s="53"/>
+      <c r="X169" s="53"/>
+      <c r="Y169" s="53"/>
+      <c r="Z169" s="53"/>
+      <c r="AA169" s="53"/>
+      <c r="AB169" s="54"/>
       <c r="AC169" s="11"/>
     </row>
     <row r="170" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6907,27 +6964,29 @@
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
-      <c r="H170" s="49"/>
-      <c r="I170" s="50"/>
-      <c r="J170" s="50"/>
-      <c r="K170" s="50"/>
-      <c r="L170" s="50"/>
-      <c r="M170" s="50"/>
-      <c r="N170" s="50"/>
-      <c r="O170" s="50"/>
-      <c r="P170" s="50"/>
-      <c r="Q170" s="50"/>
-      <c r="R170" s="50"/>
-      <c r="S170" s="50"/>
-      <c r="T170" s="50"/>
-      <c r="U170" s="50"/>
-      <c r="V170" s="50"/>
-      <c r="W170" s="50"/>
-      <c r="X170" s="50"/>
-      <c r="Y170" s="50"/>
-      <c r="Z170" s="50"/>
-      <c r="AA170" s="50"/>
-      <c r="AB170" s="51"/>
+      <c r="H170" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I170" s="6"/>
+      <c r="J170" s="6"/>
+      <c r="K170" s="6"/>
+      <c r="L170" s="6"/>
+      <c r="M170" s="6"/>
+      <c r="N170" s="6"/>
+      <c r="O170" s="6"/>
+      <c r="P170" s="6"/>
+      <c r="Q170" s="6"/>
+      <c r="R170" s="6"/>
+      <c r="S170" s="6"/>
+      <c r="T170" s="6"/>
+      <c r="U170" s="6"/>
+      <c r="V170" s="6"/>
+      <c r="W170" s="6"/>
+      <c r="X170" s="6"/>
+      <c r="Y170" s="6"/>
+      <c r="Z170" s="6"/>
+      <c r="AA170" s="6"/>
+      <c r="AB170" s="6"/>
       <c r="AC170" s="11"/>
     </row>
     <row r="171" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6937,27 +6996,27 @@
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
-      <c r="H171" s="49"/>
-      <c r="I171" s="50"/>
-      <c r="J171" s="50"/>
-      <c r="K171" s="50"/>
-      <c r="L171" s="50"/>
-      <c r="M171" s="50"/>
-      <c r="N171" s="50"/>
-      <c r="O171" s="50"/>
-      <c r="P171" s="50"/>
-      <c r="Q171" s="50"/>
-      <c r="R171" s="50"/>
-      <c r="S171" s="50"/>
-      <c r="T171" s="50"/>
-      <c r="U171" s="50"/>
-      <c r="V171" s="50"/>
-      <c r="W171" s="50"/>
-      <c r="X171" s="50"/>
-      <c r="Y171" s="50"/>
-      <c r="Z171" s="50"/>
-      <c r="AA171" s="50"/>
-      <c r="AB171" s="51"/>
+      <c r="H171" s="46"/>
+      <c r="I171" s="47"/>
+      <c r="J171" s="47"/>
+      <c r="K171" s="47"/>
+      <c r="L171" s="47"/>
+      <c r="M171" s="47"/>
+      <c r="N171" s="47"/>
+      <c r="O171" s="47"/>
+      <c r="P171" s="47"/>
+      <c r="Q171" s="47"/>
+      <c r="R171" s="47"/>
+      <c r="S171" s="47"/>
+      <c r="T171" s="47"/>
+      <c r="U171" s="47"/>
+      <c r="V171" s="47"/>
+      <c r="W171" s="47"/>
+      <c r="X171" s="47"/>
+      <c r="Y171" s="47"/>
+      <c r="Z171" s="47"/>
+      <c r="AA171" s="47"/>
+      <c r="AB171" s="48"/>
       <c r="AC171" s="11"/>
     </row>
     <row r="172" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7027,245 +7086,245 @@
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
-      <c r="H174" s="52"/>
-      <c r="I174" s="53"/>
-      <c r="J174" s="53"/>
-      <c r="K174" s="53"/>
-      <c r="L174" s="53"/>
-      <c r="M174" s="53"/>
-      <c r="N174" s="53"/>
-      <c r="O174" s="53"/>
-      <c r="P174" s="53"/>
-      <c r="Q174" s="53"/>
-      <c r="R174" s="53"/>
-      <c r="S174" s="53"/>
-      <c r="T174" s="53"/>
-      <c r="U174" s="53"/>
-      <c r="V174" s="53"/>
-      <c r="W174" s="53"/>
-      <c r="X174" s="53"/>
-      <c r="Y174" s="53"/>
-      <c r="Z174" s="53"/>
-      <c r="AA174" s="53"/>
-      <c r="AB174" s="54"/>
+      <c r="H174" s="49"/>
+      <c r="I174" s="50"/>
+      <c r="J174" s="50"/>
+      <c r="K174" s="50"/>
+      <c r="L174" s="50"/>
+      <c r="M174" s="50"/>
+      <c r="N174" s="50"/>
+      <c r="O174" s="50"/>
+      <c r="P174" s="50"/>
+      <c r="Q174" s="50"/>
+      <c r="R174" s="50"/>
+      <c r="S174" s="50"/>
+      <c r="T174" s="50"/>
+      <c r="U174" s="50"/>
+      <c r="V174" s="50"/>
+      <c r="W174" s="50"/>
+      <c r="X174" s="50"/>
+      <c r="Y174" s="50"/>
+      <c r="Z174" s="50"/>
+      <c r="AA174" s="50"/>
+      <c r="AB174" s="51"/>
       <c r="AC174" s="11"/>
     </row>
     <row r="175" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B175" s="45"/>
-      <c r="C175" s="3"/>
-      <c r="D175" s="4"/>
-      <c r="E175" s="4"/>
-      <c r="F175" s="4"/>
-      <c r="G175" s="4"/>
-      <c r="H175" s="4"/>
-      <c r="I175" s="4"/>
-      <c r="J175" s="4"/>
-      <c r="K175" s="4"/>
-      <c r="L175" s="4"/>
-      <c r="M175" s="4"/>
-      <c r="N175" s="4"/>
-      <c r="O175" s="4"/>
-      <c r="P175" s="4"/>
-      <c r="Q175" s="4"/>
-      <c r="R175" s="4"/>
-      <c r="S175" s="4"/>
-      <c r="T175" s="4"/>
-      <c r="U175" s="4"/>
-      <c r="V175" s="4"/>
-      <c r="W175" s="4"/>
-      <c r="X175" s="4"/>
-      <c r="Y175" s="4"/>
-      <c r="Z175" s="4"/>
-      <c r="AA175" s="4"/>
-      <c r="AB175" s="4"/>
-      <c r="AC175" s="12"/>
+      <c r="B175" s="44"/>
+      <c r="C175" s="5"/>
+      <c r="D175" s="6"/>
+      <c r="E175" s="6"/>
+      <c r="F175" s="6"/>
+      <c r="G175" s="6"/>
+      <c r="H175" s="49"/>
+      <c r="I175" s="50"/>
+      <c r="J175" s="50"/>
+      <c r="K175" s="50"/>
+      <c r="L175" s="50"/>
+      <c r="M175" s="50"/>
+      <c r="N175" s="50"/>
+      <c r="O175" s="50"/>
+      <c r="P175" s="50"/>
+      <c r="Q175" s="50"/>
+      <c r="R175" s="50"/>
+      <c r="S175" s="50"/>
+      <c r="T175" s="50"/>
+      <c r="U175" s="50"/>
+      <c r="V175" s="50"/>
+      <c r="W175" s="50"/>
+      <c r="X175" s="50"/>
+      <c r="Y175" s="50"/>
+      <c r="Z175" s="50"/>
+      <c r="AA175" s="50"/>
+      <c r="AB175" s="51"/>
+      <c r="AC175" s="11"/>
+    </row>
+    <row r="176" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B176" s="44"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
+      <c r="G176" s="6"/>
+      <c r="H176" s="49"/>
+      <c r="I176" s="50"/>
+      <c r="J176" s="50"/>
+      <c r="K176" s="50"/>
+      <c r="L176" s="50"/>
+      <c r="M176" s="50"/>
+      <c r="N176" s="50"/>
+      <c r="O176" s="50"/>
+      <c r="P176" s="50"/>
+      <c r="Q176" s="50"/>
+      <c r="R176" s="50"/>
+      <c r="S176" s="50"/>
+      <c r="T176" s="50"/>
+      <c r="U176" s="50"/>
+      <c r="V176" s="50"/>
+      <c r="W176" s="50"/>
+      <c r="X176" s="50"/>
+      <c r="Y176" s="50"/>
+      <c r="Z176" s="50"/>
+      <c r="AA176" s="50"/>
+      <c r="AB176" s="51"/>
+      <c r="AC176" s="11"/>
     </row>
     <row r="177" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B177" s="43" t="s">
+      <c r="B177" s="44"/>
+      <c r="C177" s="5"/>
+      <c r="D177" s="6"/>
+      <c r="E177" s="6"/>
+      <c r="F177" s="6"/>
+      <c r="G177" s="6"/>
+      <c r="H177" s="52"/>
+      <c r="I177" s="53"/>
+      <c r="J177" s="53"/>
+      <c r="K177" s="53"/>
+      <c r="L177" s="53"/>
+      <c r="M177" s="53"/>
+      <c r="N177" s="53"/>
+      <c r="O177" s="53"/>
+      <c r="P177" s="53"/>
+      <c r="Q177" s="53"/>
+      <c r="R177" s="53"/>
+      <c r="S177" s="53"/>
+      <c r="T177" s="53"/>
+      <c r="U177" s="53"/>
+      <c r="V177" s="53"/>
+      <c r="W177" s="53"/>
+      <c r="X177" s="53"/>
+      <c r="Y177" s="53"/>
+      <c r="Z177" s="53"/>
+      <c r="AA177" s="53"/>
+      <c r="AB177" s="54"/>
+      <c r="AC177" s="11"/>
+    </row>
+    <row r="178" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B178" s="45"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="4"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4"/>
+      <c r="G178" s="4"/>
+      <c r="H178" s="4"/>
+      <c r="I178" s="4"/>
+      <c r="J178" s="4"/>
+      <c r="K178" s="4"/>
+      <c r="L178" s="4"/>
+      <c r="M178" s="4"/>
+      <c r="N178" s="4"/>
+      <c r="O178" s="4"/>
+      <c r="P178" s="4"/>
+      <c r="Q178" s="4"/>
+      <c r="R178" s="4"/>
+      <c r="S178" s="4"/>
+      <c r="T178" s="4"/>
+      <c r="U178" s="4"/>
+      <c r="V178" s="4"/>
+      <c r="W178" s="4"/>
+      <c r="X178" s="4"/>
+      <c r="Y178" s="4"/>
+      <c r="Z178" s="4"/>
+      <c r="AA178" s="4"/>
+      <c r="AB178" s="4"/>
+      <c r="AC178" s="12"/>
+    </row>
+    <row r="180" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B180" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="C177" s="8"/>
-      <c r="D177" s="9"/>
-      <c r="E177" s="9"/>
-      <c r="F177" s="9"/>
-      <c r="G177" s="9"/>
-      <c r="H177" s="9"/>
-      <c r="I177" s="9"/>
-      <c r="J177" s="9"/>
-      <c r="K177" s="9"/>
-      <c r="L177" s="9"/>
-      <c r="M177" s="9"/>
-      <c r="N177" s="9"/>
-      <c r="O177" s="9"/>
-      <c r="P177" s="9"/>
-      <c r="Q177" s="9"/>
-      <c r="R177" s="9"/>
-      <c r="S177" s="9"/>
-      <c r="T177" s="9"/>
-      <c r="U177" s="9"/>
-      <c r="V177" s="9"/>
-      <c r="W177" s="9"/>
-      <c r="X177" s="9"/>
-      <c r="Y177" s="9"/>
-      <c r="Z177" s="9"/>
-      <c r="AA177" s="9"/>
-      <c r="AB177" s="9"/>
-      <c r="AC177" s="10"/>
-    </row>
-    <row r="178" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B178" s="44"/>
-      <c r="C178" s="5"/>
-      <c r="D178" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I178" s="6"/>
-      <c r="J178" s="6"/>
-      <c r="K178" s="6"/>
-      <c r="L178" s="6"/>
-      <c r="M178" s="6"/>
-      <c r="N178" s="6"/>
-      <c r="O178" s="6"/>
-      <c r="P178" s="6"/>
-      <c r="Q178" s="6"/>
-      <c r="R178" s="6"/>
-      <c r="S178" s="6"/>
-      <c r="T178" s="6"/>
-      <c r="U178" s="6"/>
-      <c r="V178" s="6"/>
-      <c r="W178" s="6"/>
-      <c r="X178" s="6"/>
-      <c r="Y178" s="6"/>
-      <c r="Z178" s="6"/>
-      <c r="AA178" s="6"/>
-      <c r="AB178" s="6"/>
-      <c r="AC178" s="11"/>
-    </row>
-    <row r="179" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B179" s="44"/>
-      <c r="C179" s="5"/>
-      <c r="D179" s="41"/>
-      <c r="E179" s="42"/>
-      <c r="F179" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G179" s="6"/>
-      <c r="H179" s="46"/>
-      <c r="I179" s="47"/>
-      <c r="J179" s="47"/>
-      <c r="K179" s="47"/>
-      <c r="L179" s="47"/>
-      <c r="M179" s="47"/>
-      <c r="N179" s="47"/>
-      <c r="O179" s="47"/>
-      <c r="P179" s="47"/>
-      <c r="Q179" s="47"/>
-      <c r="R179" s="47"/>
-      <c r="S179" s="47"/>
-      <c r="T179" s="47"/>
-      <c r="U179" s="47"/>
-      <c r="V179" s="47"/>
-      <c r="W179" s="47"/>
-      <c r="X179" s="47"/>
-      <c r="Y179" s="47"/>
-      <c r="Z179" s="47"/>
-      <c r="AA179" s="47"/>
-      <c r="AB179" s="48"/>
-      <c r="AC179" s="11"/>
-    </row>
-    <row r="180" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B180" s="44"/>
-      <c r="C180" s="5"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="49"/>
-      <c r="I180" s="50"/>
-      <c r="J180" s="50"/>
-      <c r="K180" s="50"/>
-      <c r="L180" s="50"/>
-      <c r="M180" s="50"/>
-      <c r="N180" s="50"/>
-      <c r="O180" s="50"/>
-      <c r="P180" s="50"/>
-      <c r="Q180" s="50"/>
-      <c r="R180" s="50"/>
-      <c r="S180" s="50"/>
-      <c r="T180" s="50"/>
-      <c r="U180" s="50"/>
-      <c r="V180" s="50"/>
-      <c r="W180" s="50"/>
-      <c r="X180" s="50"/>
-      <c r="Y180" s="50"/>
-      <c r="Z180" s="50"/>
-      <c r="AA180" s="50"/>
-      <c r="AB180" s="51"/>
-      <c r="AC180" s="11"/>
+      <c r="C180" s="8"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
+      <c r="F180" s="9"/>
+      <c r="G180" s="9"/>
+      <c r="H180" s="9"/>
+      <c r="I180" s="9"/>
+      <c r="J180" s="9"/>
+      <c r="K180" s="9"/>
+      <c r="L180" s="9"/>
+      <c r="M180" s="9"/>
+      <c r="N180" s="9"/>
+      <c r="O180" s="9"/>
+      <c r="P180" s="9"/>
+      <c r="Q180" s="9"/>
+      <c r="R180" s="9"/>
+      <c r="S180" s="9"/>
+      <c r="T180" s="9"/>
+      <c r="U180" s="9"/>
+      <c r="V180" s="9"/>
+      <c r="W180" s="9"/>
+      <c r="X180" s="9"/>
+      <c r="Y180" s="9"/>
+      <c r="Z180" s="9"/>
+      <c r="AA180" s="9"/>
+      <c r="AB180" s="9"/>
+      <c r="AC180" s="10"/>
     </row>
     <row r="181" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B181" s="44"/>
       <c r="C181" s="5"/>
-      <c r="D181" s="6"/>
+      <c r="D181" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
-      <c r="H181" s="49"/>
-      <c r="I181" s="50"/>
-      <c r="J181" s="50"/>
-      <c r="K181" s="50"/>
-      <c r="L181" s="50"/>
-      <c r="M181" s="50"/>
-      <c r="N181" s="50"/>
-      <c r="O181" s="50"/>
-      <c r="P181" s="50"/>
-      <c r="Q181" s="50"/>
-      <c r="R181" s="50"/>
-      <c r="S181" s="50"/>
-      <c r="T181" s="50"/>
-      <c r="U181" s="50"/>
-      <c r="V181" s="50"/>
-      <c r="W181" s="50"/>
-      <c r="X181" s="50"/>
-      <c r="Y181" s="50"/>
-      <c r="Z181" s="50"/>
-      <c r="AA181" s="50"/>
-      <c r="AB181" s="51"/>
+      <c r="H181" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I181" s="6"/>
+      <c r="J181" s="6"/>
+      <c r="K181" s="6"/>
+      <c r="L181" s="6"/>
+      <c r="M181" s="6"/>
+      <c r="N181" s="6"/>
+      <c r="O181" s="6"/>
+      <c r="P181" s="6"/>
+      <c r="Q181" s="6"/>
+      <c r="R181" s="6"/>
+      <c r="S181" s="6"/>
+      <c r="T181" s="6"/>
+      <c r="U181" s="6"/>
+      <c r="V181" s="6"/>
+      <c r="W181" s="6"/>
+      <c r="X181" s="6"/>
+      <c r="Y181" s="6"/>
+      <c r="Z181" s="6"/>
+      <c r="AA181" s="6"/>
+      <c r="AB181" s="6"/>
       <c r="AC181" s="11"/>
     </row>
     <row r="182" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B182" s="44"/>
       <c r="C182" s="5"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
+      <c r="D182" s="41"/>
+      <c r="E182" s="42"/>
+      <c r="F182" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="G182" s="6"/>
-      <c r="H182" s="49"/>
-      <c r="I182" s="50"/>
-      <c r="J182" s="50"/>
-      <c r="K182" s="50"/>
-      <c r="L182" s="50"/>
-      <c r="M182" s="50"/>
-      <c r="N182" s="50"/>
-      <c r="O182" s="50"/>
-      <c r="P182" s="50"/>
-      <c r="Q182" s="50"/>
-      <c r="R182" s="50"/>
-      <c r="S182" s="50"/>
-      <c r="T182" s="50"/>
-      <c r="U182" s="50"/>
-      <c r="V182" s="50"/>
-      <c r="W182" s="50"/>
-      <c r="X182" s="50"/>
-      <c r="Y182" s="50"/>
-      <c r="Z182" s="50"/>
-      <c r="AA182" s="50"/>
-      <c r="AB182" s="51"/>
+      <c r="H182" s="46"/>
+      <c r="I182" s="47"/>
+      <c r="J182" s="47"/>
+      <c r="K182" s="47"/>
+      <c r="L182" s="47"/>
+      <c r="M182" s="47"/>
+      <c r="N182" s="47"/>
+      <c r="O182" s="47"/>
+      <c r="P182" s="47"/>
+      <c r="Q182" s="47"/>
+      <c r="R182" s="47"/>
+      <c r="S182" s="47"/>
+      <c r="T182" s="47"/>
+      <c r="U182" s="47"/>
+      <c r="V182" s="47"/>
+      <c r="W182" s="47"/>
+      <c r="X182" s="47"/>
+      <c r="Y182" s="47"/>
+      <c r="Z182" s="47"/>
+      <c r="AA182" s="47"/>
+      <c r="AB182" s="48"/>
       <c r="AC182" s="11"/>
     </row>
     <row r="183" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7335,27 +7394,27 @@
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
-      <c r="H185" s="52"/>
-      <c r="I185" s="53"/>
-      <c r="J185" s="53"/>
-      <c r="K185" s="53"/>
-      <c r="L185" s="53"/>
-      <c r="M185" s="53"/>
-      <c r="N185" s="53"/>
-      <c r="O185" s="53"/>
-      <c r="P185" s="53"/>
-      <c r="Q185" s="53"/>
-      <c r="R185" s="53"/>
-      <c r="S185" s="53"/>
-      <c r="T185" s="53"/>
-      <c r="U185" s="53"/>
-      <c r="V185" s="53"/>
-      <c r="W185" s="53"/>
-      <c r="X185" s="53"/>
-      <c r="Y185" s="53"/>
-      <c r="Z185" s="53"/>
-      <c r="AA185" s="53"/>
-      <c r="AB185" s="54"/>
+      <c r="H185" s="49"/>
+      <c r="I185" s="50"/>
+      <c r="J185" s="50"/>
+      <c r="K185" s="50"/>
+      <c r="L185" s="50"/>
+      <c r="M185" s="50"/>
+      <c r="N185" s="50"/>
+      <c r="O185" s="50"/>
+      <c r="P185" s="50"/>
+      <c r="Q185" s="50"/>
+      <c r="R185" s="50"/>
+      <c r="S185" s="50"/>
+      <c r="T185" s="50"/>
+      <c r="U185" s="50"/>
+      <c r="V185" s="50"/>
+      <c r="W185" s="50"/>
+      <c r="X185" s="50"/>
+      <c r="Y185" s="50"/>
+      <c r="Z185" s="50"/>
+      <c r="AA185" s="50"/>
+      <c r="AB185" s="51"/>
       <c r="AC185" s="11"/>
     </row>
     <row r="186" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7365,29 +7424,27 @@
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
-      <c r="H186" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I186" s="6"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="6"/>
-      <c r="L186" s="6"/>
-      <c r="M186" s="6"/>
-      <c r="N186" s="6"/>
-      <c r="O186" s="6"/>
-      <c r="P186" s="6"/>
-      <c r="Q186" s="6"/>
-      <c r="R186" s="6"/>
-      <c r="S186" s="6"/>
-      <c r="T186" s="6"/>
-      <c r="U186" s="6"/>
-      <c r="V186" s="6"/>
-      <c r="W186" s="6"/>
-      <c r="X186" s="6"/>
-      <c r="Y186" s="6"/>
-      <c r="Z186" s="6"/>
-      <c r="AA186" s="6"/>
-      <c r="AB186" s="6"/>
+      <c r="H186" s="49"/>
+      <c r="I186" s="50"/>
+      <c r="J186" s="50"/>
+      <c r="K186" s="50"/>
+      <c r="L186" s="50"/>
+      <c r="M186" s="50"/>
+      <c r="N186" s="50"/>
+      <c r="O186" s="50"/>
+      <c r="P186" s="50"/>
+      <c r="Q186" s="50"/>
+      <c r="R186" s="50"/>
+      <c r="S186" s="50"/>
+      <c r="T186" s="50"/>
+      <c r="U186" s="50"/>
+      <c r="V186" s="50"/>
+      <c r="W186" s="50"/>
+      <c r="X186" s="50"/>
+      <c r="Y186" s="50"/>
+      <c r="Z186" s="50"/>
+      <c r="AA186" s="50"/>
+      <c r="AB186" s="51"/>
       <c r="AC186" s="11"/>
     </row>
     <row r="187" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7397,27 +7454,27 @@
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
-      <c r="H187" s="46"/>
-      <c r="I187" s="47"/>
-      <c r="J187" s="47"/>
-      <c r="K187" s="47"/>
-      <c r="L187" s="47"/>
-      <c r="M187" s="47"/>
-      <c r="N187" s="47"/>
-      <c r="O187" s="47"/>
-      <c r="P187" s="47"/>
-      <c r="Q187" s="47"/>
-      <c r="R187" s="47"/>
-      <c r="S187" s="47"/>
-      <c r="T187" s="47"/>
-      <c r="U187" s="47"/>
-      <c r="V187" s="47"/>
-      <c r="W187" s="47"/>
-      <c r="X187" s="47"/>
-      <c r="Y187" s="47"/>
-      <c r="Z187" s="47"/>
-      <c r="AA187" s="47"/>
-      <c r="AB187" s="48"/>
+      <c r="H187" s="49"/>
+      <c r="I187" s="50"/>
+      <c r="J187" s="50"/>
+      <c r="K187" s="50"/>
+      <c r="L187" s="50"/>
+      <c r="M187" s="50"/>
+      <c r="N187" s="50"/>
+      <c r="O187" s="50"/>
+      <c r="P187" s="50"/>
+      <c r="Q187" s="50"/>
+      <c r="R187" s="50"/>
+      <c r="S187" s="50"/>
+      <c r="T187" s="50"/>
+      <c r="U187" s="50"/>
+      <c r="V187" s="50"/>
+      <c r="W187" s="50"/>
+      <c r="X187" s="50"/>
+      <c r="Y187" s="50"/>
+      <c r="Z187" s="50"/>
+      <c r="AA187" s="50"/>
+      <c r="AB187" s="51"/>
       <c r="AC187" s="11"/>
     </row>
     <row r="188" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7427,27 +7484,27 @@
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
-      <c r="H188" s="49"/>
-      <c r="I188" s="50"/>
-      <c r="J188" s="50"/>
-      <c r="K188" s="50"/>
-      <c r="L188" s="50"/>
-      <c r="M188" s="50"/>
-      <c r="N188" s="50"/>
-      <c r="O188" s="50"/>
-      <c r="P188" s="50"/>
-      <c r="Q188" s="50"/>
-      <c r="R188" s="50"/>
-      <c r="S188" s="50"/>
-      <c r="T188" s="50"/>
-      <c r="U188" s="50"/>
-      <c r="V188" s="50"/>
-      <c r="W188" s="50"/>
-      <c r="X188" s="50"/>
-      <c r="Y188" s="50"/>
-      <c r="Z188" s="50"/>
-      <c r="AA188" s="50"/>
-      <c r="AB188" s="51"/>
+      <c r="H188" s="52"/>
+      <c r="I188" s="53"/>
+      <c r="J188" s="53"/>
+      <c r="K188" s="53"/>
+      <c r="L188" s="53"/>
+      <c r="M188" s="53"/>
+      <c r="N188" s="53"/>
+      <c r="O188" s="53"/>
+      <c r="P188" s="53"/>
+      <c r="Q188" s="53"/>
+      <c r="R188" s="53"/>
+      <c r="S188" s="53"/>
+      <c r="T188" s="53"/>
+      <c r="U188" s="53"/>
+      <c r="V188" s="53"/>
+      <c r="W188" s="53"/>
+      <c r="X188" s="53"/>
+      <c r="Y188" s="53"/>
+      <c r="Z188" s="53"/>
+      <c r="AA188" s="53"/>
+      <c r="AB188" s="54"/>
       <c r="AC188" s="11"/>
     </row>
     <row r="189" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7457,27 +7514,29 @@
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
-      <c r="H189" s="49"/>
-      <c r="I189" s="50"/>
-      <c r="J189" s="50"/>
-      <c r="K189" s="50"/>
-      <c r="L189" s="50"/>
-      <c r="M189" s="50"/>
-      <c r="N189" s="50"/>
-      <c r="O189" s="50"/>
-      <c r="P189" s="50"/>
-      <c r="Q189" s="50"/>
-      <c r="R189" s="50"/>
-      <c r="S189" s="50"/>
-      <c r="T189" s="50"/>
-      <c r="U189" s="50"/>
-      <c r="V189" s="50"/>
-      <c r="W189" s="50"/>
-      <c r="X189" s="50"/>
-      <c r="Y189" s="50"/>
-      <c r="Z189" s="50"/>
-      <c r="AA189" s="50"/>
-      <c r="AB189" s="51"/>
+      <c r="H189" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I189" s="6"/>
+      <c r="J189" s="6"/>
+      <c r="K189" s="6"/>
+      <c r="L189" s="6"/>
+      <c r="M189" s="6"/>
+      <c r="N189" s="6"/>
+      <c r="O189" s="6"/>
+      <c r="P189" s="6"/>
+      <c r="Q189" s="6"/>
+      <c r="R189" s="6"/>
+      <c r="S189" s="6"/>
+      <c r="T189" s="6"/>
+      <c r="U189" s="6"/>
+      <c r="V189" s="6"/>
+      <c r="W189" s="6"/>
+      <c r="X189" s="6"/>
+      <c r="Y189" s="6"/>
+      <c r="Z189" s="6"/>
+      <c r="AA189" s="6"/>
+      <c r="AB189" s="6"/>
       <c r="AC189" s="11"/>
     </row>
     <row r="190" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7487,27 +7546,27 @@
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
-      <c r="H190" s="49"/>
-      <c r="I190" s="50"/>
-      <c r="J190" s="50"/>
-      <c r="K190" s="50"/>
-      <c r="L190" s="50"/>
-      <c r="M190" s="50"/>
-      <c r="N190" s="50"/>
-      <c r="O190" s="50"/>
-      <c r="P190" s="50"/>
-      <c r="Q190" s="50"/>
-      <c r="R190" s="50"/>
-      <c r="S190" s="50"/>
-      <c r="T190" s="50"/>
-      <c r="U190" s="50"/>
-      <c r="V190" s="50"/>
-      <c r="W190" s="50"/>
-      <c r="X190" s="50"/>
-      <c r="Y190" s="50"/>
-      <c r="Z190" s="50"/>
-      <c r="AA190" s="50"/>
-      <c r="AB190" s="51"/>
+      <c r="H190" s="46"/>
+      <c r="I190" s="47"/>
+      <c r="J190" s="47"/>
+      <c r="K190" s="47"/>
+      <c r="L190" s="47"/>
+      <c r="M190" s="47"/>
+      <c r="N190" s="47"/>
+      <c r="O190" s="47"/>
+      <c r="P190" s="47"/>
+      <c r="Q190" s="47"/>
+      <c r="R190" s="47"/>
+      <c r="S190" s="47"/>
+      <c r="T190" s="47"/>
+      <c r="U190" s="47"/>
+      <c r="V190" s="47"/>
+      <c r="W190" s="47"/>
+      <c r="X190" s="47"/>
+      <c r="Y190" s="47"/>
+      <c r="Z190" s="47"/>
+      <c r="AA190" s="47"/>
+      <c r="AB190" s="48"/>
       <c r="AC190" s="11"/>
     </row>
     <row r="191" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7577,245 +7636,245 @@
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
-      <c r="H193" s="52"/>
-      <c r="I193" s="53"/>
-      <c r="J193" s="53"/>
-      <c r="K193" s="53"/>
-      <c r="L193" s="53"/>
-      <c r="M193" s="53"/>
-      <c r="N193" s="53"/>
-      <c r="O193" s="53"/>
-      <c r="P193" s="53"/>
-      <c r="Q193" s="53"/>
-      <c r="R193" s="53"/>
-      <c r="S193" s="53"/>
-      <c r="T193" s="53"/>
-      <c r="U193" s="53"/>
-      <c r="V193" s="53"/>
-      <c r="W193" s="53"/>
-      <c r="X193" s="53"/>
-      <c r="Y193" s="53"/>
-      <c r="Z193" s="53"/>
-      <c r="AA193" s="53"/>
-      <c r="AB193" s="54"/>
+      <c r="H193" s="49"/>
+      <c r="I193" s="50"/>
+      <c r="J193" s="50"/>
+      <c r="K193" s="50"/>
+      <c r="L193" s="50"/>
+      <c r="M193" s="50"/>
+      <c r="N193" s="50"/>
+      <c r="O193" s="50"/>
+      <c r="P193" s="50"/>
+      <c r="Q193" s="50"/>
+      <c r="R193" s="50"/>
+      <c r="S193" s="50"/>
+      <c r="T193" s="50"/>
+      <c r="U193" s="50"/>
+      <c r="V193" s="50"/>
+      <c r="W193" s="50"/>
+      <c r="X193" s="50"/>
+      <c r="Y193" s="50"/>
+      <c r="Z193" s="50"/>
+      <c r="AA193" s="50"/>
+      <c r="AB193" s="51"/>
       <c r="AC193" s="11"/>
     </row>
     <row r="194" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B194" s="45"/>
-      <c r="C194" s="3"/>
-      <c r="D194" s="4"/>
-      <c r="E194" s="4"/>
-      <c r="F194" s="4"/>
-      <c r="G194" s="4"/>
-      <c r="H194" s="4"/>
-      <c r="I194" s="4"/>
-      <c r="J194" s="4"/>
-      <c r="K194" s="4"/>
-      <c r="L194" s="4"/>
-      <c r="M194" s="4"/>
-      <c r="N194" s="4"/>
-      <c r="O194" s="4"/>
-      <c r="P194" s="4"/>
-      <c r="Q194" s="4"/>
-      <c r="R194" s="4"/>
-      <c r="S194" s="4"/>
-      <c r="T194" s="4"/>
-      <c r="U194" s="4"/>
-      <c r="V194" s="4"/>
-      <c r="W194" s="4"/>
-      <c r="X194" s="4"/>
-      <c r="Y194" s="4"/>
-      <c r="Z194" s="4"/>
-      <c r="AA194" s="4"/>
-      <c r="AB194" s="4"/>
-      <c r="AC194" s="12"/>
+      <c r="B194" s="44"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="6"/>
+      <c r="E194" s="6"/>
+      <c r="F194" s="6"/>
+      <c r="G194" s="6"/>
+      <c r="H194" s="49"/>
+      <c r="I194" s="50"/>
+      <c r="J194" s="50"/>
+      <c r="K194" s="50"/>
+      <c r="L194" s="50"/>
+      <c r="M194" s="50"/>
+      <c r="N194" s="50"/>
+      <c r="O194" s="50"/>
+      <c r="P194" s="50"/>
+      <c r="Q194" s="50"/>
+      <c r="R194" s="50"/>
+      <c r="S194" s="50"/>
+      <c r="T194" s="50"/>
+      <c r="U194" s="50"/>
+      <c r="V194" s="50"/>
+      <c r="W194" s="50"/>
+      <c r="X194" s="50"/>
+      <c r="Y194" s="50"/>
+      <c r="Z194" s="50"/>
+      <c r="AA194" s="50"/>
+      <c r="AB194" s="51"/>
+      <c r="AC194" s="11"/>
+    </row>
+    <row r="195" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B195" s="44"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="6"/>
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
+      <c r="G195" s="6"/>
+      <c r="H195" s="49"/>
+      <c r="I195" s="50"/>
+      <c r="J195" s="50"/>
+      <c r="K195" s="50"/>
+      <c r="L195" s="50"/>
+      <c r="M195" s="50"/>
+      <c r="N195" s="50"/>
+      <c r="O195" s="50"/>
+      <c r="P195" s="50"/>
+      <c r="Q195" s="50"/>
+      <c r="R195" s="50"/>
+      <c r="S195" s="50"/>
+      <c r="T195" s="50"/>
+      <c r="U195" s="50"/>
+      <c r="V195" s="50"/>
+      <c r="W195" s="50"/>
+      <c r="X195" s="50"/>
+      <c r="Y195" s="50"/>
+      <c r="Z195" s="50"/>
+      <c r="AA195" s="50"/>
+      <c r="AB195" s="51"/>
+      <c r="AC195" s="11"/>
     </row>
     <row r="196" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B196" s="43" t="s">
+      <c r="B196" s="44"/>
+      <c r="C196" s="5"/>
+      <c r="D196" s="6"/>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6"/>
+      <c r="G196" s="6"/>
+      <c r="H196" s="52"/>
+      <c r="I196" s="53"/>
+      <c r="J196" s="53"/>
+      <c r="K196" s="53"/>
+      <c r="L196" s="53"/>
+      <c r="M196" s="53"/>
+      <c r="N196" s="53"/>
+      <c r="O196" s="53"/>
+      <c r="P196" s="53"/>
+      <c r="Q196" s="53"/>
+      <c r="R196" s="53"/>
+      <c r="S196" s="53"/>
+      <c r="T196" s="53"/>
+      <c r="U196" s="53"/>
+      <c r="V196" s="53"/>
+      <c r="W196" s="53"/>
+      <c r="X196" s="53"/>
+      <c r="Y196" s="53"/>
+      <c r="Z196" s="53"/>
+      <c r="AA196" s="53"/>
+      <c r="AB196" s="54"/>
+      <c r="AC196" s="11"/>
+    </row>
+    <row r="197" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B197" s="45"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="H197" s="4"/>
+      <c r="I197" s="4"/>
+      <c r="J197" s="4"/>
+      <c r="K197" s="4"/>
+      <c r="L197" s="4"/>
+      <c r="M197" s="4"/>
+      <c r="N197" s="4"/>
+      <c r="O197" s="4"/>
+      <c r="P197" s="4"/>
+      <c r="Q197" s="4"/>
+      <c r="R197" s="4"/>
+      <c r="S197" s="4"/>
+      <c r="T197" s="4"/>
+      <c r="U197" s="4"/>
+      <c r="V197" s="4"/>
+      <c r="W197" s="4"/>
+      <c r="X197" s="4"/>
+      <c r="Y197" s="4"/>
+      <c r="Z197" s="4"/>
+      <c r="AA197" s="4"/>
+      <c r="AB197" s="4"/>
+      <c r="AC197" s="12"/>
+    </row>
+    <row r="199" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B199" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="C196" s="8"/>
-      <c r="D196" s="9"/>
-      <c r="E196" s="9"/>
-      <c r="F196" s="9"/>
-      <c r="G196" s="9"/>
-      <c r="H196" s="9"/>
-      <c r="I196" s="9"/>
-      <c r="J196" s="9"/>
-      <c r="K196" s="9"/>
-      <c r="L196" s="9"/>
-      <c r="M196" s="9"/>
-      <c r="N196" s="9"/>
-      <c r="O196" s="9"/>
-      <c r="P196" s="9"/>
-      <c r="Q196" s="9"/>
-      <c r="R196" s="9"/>
-      <c r="S196" s="9"/>
-      <c r="T196" s="9"/>
-      <c r="U196" s="9"/>
-      <c r="V196" s="9"/>
-      <c r="W196" s="9"/>
-      <c r="X196" s="9"/>
-      <c r="Y196" s="9"/>
-      <c r="Z196" s="9"/>
-      <c r="AA196" s="9"/>
-      <c r="AB196" s="9"/>
-      <c r="AC196" s="10"/>
-    </row>
-    <row r="197" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B197" s="44"/>
-      <c r="C197" s="5"/>
-      <c r="D197" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="6"/>
-      <c r="L197" s="6"/>
-      <c r="M197" s="6"/>
-      <c r="N197" s="6"/>
-      <c r="O197" s="6"/>
-      <c r="P197" s="6"/>
-      <c r="Q197" s="6"/>
-      <c r="R197" s="6"/>
-      <c r="S197" s="6"/>
-      <c r="T197" s="6"/>
-      <c r="U197" s="6"/>
-      <c r="V197" s="6"/>
-      <c r="W197" s="6"/>
-      <c r="X197" s="6"/>
-      <c r="Y197" s="6"/>
-      <c r="Z197" s="6"/>
-      <c r="AA197" s="6"/>
-      <c r="AB197" s="6"/>
-      <c r="AC197" s="11"/>
-    </row>
-    <row r="198" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B198" s="44"/>
-      <c r="C198" s="5"/>
-      <c r="D198" s="41"/>
-      <c r="E198" s="42"/>
-      <c r="F198" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G198" s="6"/>
-      <c r="H198" s="46"/>
-      <c r="I198" s="47"/>
-      <c r="J198" s="47"/>
-      <c r="K198" s="47"/>
-      <c r="L198" s="47"/>
-      <c r="M198" s="47"/>
-      <c r="N198" s="47"/>
-      <c r="O198" s="47"/>
-      <c r="P198" s="47"/>
-      <c r="Q198" s="47"/>
-      <c r="R198" s="47"/>
-      <c r="S198" s="47"/>
-      <c r="T198" s="47"/>
-      <c r="U198" s="47"/>
-      <c r="V198" s="47"/>
-      <c r="W198" s="47"/>
-      <c r="X198" s="47"/>
-      <c r="Y198" s="47"/>
-      <c r="Z198" s="47"/>
-      <c r="AA198" s="47"/>
-      <c r="AB198" s="48"/>
-      <c r="AC198" s="11"/>
-    </row>
-    <row r="199" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B199" s="44"/>
-      <c r="C199" s="5"/>
-      <c r="D199" s="6"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="49"/>
-      <c r="I199" s="50"/>
-      <c r="J199" s="50"/>
-      <c r="K199" s="50"/>
-      <c r="L199" s="50"/>
-      <c r="M199" s="50"/>
-      <c r="N199" s="50"/>
-      <c r="O199" s="50"/>
-      <c r="P199" s="50"/>
-      <c r="Q199" s="50"/>
-      <c r="R199" s="50"/>
-      <c r="S199" s="50"/>
-      <c r="T199" s="50"/>
-      <c r="U199" s="50"/>
-      <c r="V199" s="50"/>
-      <c r="W199" s="50"/>
-      <c r="X199" s="50"/>
-      <c r="Y199" s="50"/>
-      <c r="Z199" s="50"/>
-      <c r="AA199" s="50"/>
-      <c r="AB199" s="51"/>
-      <c r="AC199" s="11"/>
+      <c r="C199" s="8"/>
+      <c r="D199" s="9"/>
+      <c r="E199" s="9"/>
+      <c r="F199" s="9"/>
+      <c r="G199" s="9"/>
+      <c r="H199" s="9"/>
+      <c r="I199" s="9"/>
+      <c r="J199" s="9"/>
+      <c r="K199" s="9"/>
+      <c r="L199" s="9"/>
+      <c r="M199" s="9"/>
+      <c r="N199" s="9"/>
+      <c r="O199" s="9"/>
+      <c r="P199" s="9"/>
+      <c r="Q199" s="9"/>
+      <c r="R199" s="9"/>
+      <c r="S199" s="9"/>
+      <c r="T199" s="9"/>
+      <c r="U199" s="9"/>
+      <c r="V199" s="9"/>
+      <c r="W199" s="9"/>
+      <c r="X199" s="9"/>
+      <c r="Y199" s="9"/>
+      <c r="Z199" s="9"/>
+      <c r="AA199" s="9"/>
+      <c r="AB199" s="9"/>
+      <c r="AC199" s="10"/>
     </row>
     <row r="200" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B200" s="44"/>
       <c r="C200" s="5"/>
-      <c r="D200" s="6"/>
+      <c r="D200" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="E200" s="6"/>
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
-      <c r="H200" s="49"/>
-      <c r="I200" s="50"/>
-      <c r="J200" s="50"/>
-      <c r="K200" s="50"/>
-      <c r="L200" s="50"/>
-      <c r="M200" s="50"/>
-      <c r="N200" s="50"/>
-      <c r="O200" s="50"/>
-      <c r="P200" s="50"/>
-      <c r="Q200" s="50"/>
-      <c r="R200" s="50"/>
-      <c r="S200" s="50"/>
-      <c r="T200" s="50"/>
-      <c r="U200" s="50"/>
-      <c r="V200" s="50"/>
-      <c r="W200" s="50"/>
-      <c r="X200" s="50"/>
-      <c r="Y200" s="50"/>
-      <c r="Z200" s="50"/>
-      <c r="AA200" s="50"/>
-      <c r="AB200" s="51"/>
+      <c r="H200" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I200" s="6"/>
+      <c r="J200" s="6"/>
+      <c r="K200" s="6"/>
+      <c r="L200" s="6"/>
+      <c r="M200" s="6"/>
+      <c r="N200" s="6"/>
+      <c r="O200" s="6"/>
+      <c r="P200" s="6"/>
+      <c r="Q200" s="6"/>
+      <c r="R200" s="6"/>
+      <c r="S200" s="6"/>
+      <c r="T200" s="6"/>
+      <c r="U200" s="6"/>
+      <c r="V200" s="6"/>
+      <c r="W200" s="6"/>
+      <c r="X200" s="6"/>
+      <c r="Y200" s="6"/>
+      <c r="Z200" s="6"/>
+      <c r="AA200" s="6"/>
+      <c r="AB200" s="6"/>
       <c r="AC200" s="11"/>
     </row>
     <row r="201" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B201" s="44"/>
       <c r="C201" s="5"/>
-      <c r="D201" s="6"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
+      <c r="D201" s="41"/>
+      <c r="E201" s="42"/>
+      <c r="F201" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="G201" s="6"/>
-      <c r="H201" s="49"/>
-      <c r="I201" s="50"/>
-      <c r="J201" s="50"/>
-      <c r="K201" s="50"/>
-      <c r="L201" s="50"/>
-      <c r="M201" s="50"/>
-      <c r="N201" s="50"/>
-      <c r="O201" s="50"/>
-      <c r="P201" s="50"/>
-      <c r="Q201" s="50"/>
-      <c r="R201" s="50"/>
-      <c r="S201" s="50"/>
-      <c r="T201" s="50"/>
-      <c r="U201" s="50"/>
-      <c r="V201" s="50"/>
-      <c r="W201" s="50"/>
-      <c r="X201" s="50"/>
-      <c r="Y201" s="50"/>
-      <c r="Z201" s="50"/>
-      <c r="AA201" s="50"/>
-      <c r="AB201" s="51"/>
+      <c r="H201" s="46"/>
+      <c r="I201" s="47"/>
+      <c r="J201" s="47"/>
+      <c r="K201" s="47"/>
+      <c r="L201" s="47"/>
+      <c r="M201" s="47"/>
+      <c r="N201" s="47"/>
+      <c r="O201" s="47"/>
+      <c r="P201" s="47"/>
+      <c r="Q201" s="47"/>
+      <c r="R201" s="47"/>
+      <c r="S201" s="47"/>
+      <c r="T201" s="47"/>
+      <c r="U201" s="47"/>
+      <c r="V201" s="47"/>
+      <c r="W201" s="47"/>
+      <c r="X201" s="47"/>
+      <c r="Y201" s="47"/>
+      <c r="Z201" s="47"/>
+      <c r="AA201" s="47"/>
+      <c r="AB201" s="48"/>
       <c r="AC201" s="11"/>
     </row>
     <row r="202" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7885,27 +7944,27 @@
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
-      <c r="H204" s="52"/>
-      <c r="I204" s="53"/>
-      <c r="J204" s="53"/>
-      <c r="K204" s="53"/>
-      <c r="L204" s="53"/>
-      <c r="M204" s="53"/>
-      <c r="N204" s="53"/>
-      <c r="O204" s="53"/>
-      <c r="P204" s="53"/>
-      <c r="Q204" s="53"/>
-      <c r="R204" s="53"/>
-      <c r="S204" s="53"/>
-      <c r="T204" s="53"/>
-      <c r="U204" s="53"/>
-      <c r="V204" s="53"/>
-      <c r="W204" s="53"/>
-      <c r="X204" s="53"/>
-      <c r="Y204" s="53"/>
-      <c r="Z204" s="53"/>
-      <c r="AA204" s="53"/>
-      <c r="AB204" s="54"/>
+      <c r="H204" s="49"/>
+      <c r="I204" s="50"/>
+      <c r="J204" s="50"/>
+      <c r="K204" s="50"/>
+      <c r="L204" s="50"/>
+      <c r="M204" s="50"/>
+      <c r="N204" s="50"/>
+      <c r="O204" s="50"/>
+      <c r="P204" s="50"/>
+      <c r="Q204" s="50"/>
+      <c r="R204" s="50"/>
+      <c r="S204" s="50"/>
+      <c r="T204" s="50"/>
+      <c r="U204" s="50"/>
+      <c r="V204" s="50"/>
+      <c r="W204" s="50"/>
+      <c r="X204" s="50"/>
+      <c r="Y204" s="50"/>
+      <c r="Z204" s="50"/>
+      <c r="AA204" s="50"/>
+      <c r="AB204" s="51"/>
       <c r="AC204" s="11"/>
     </row>
     <row r="205" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7915,29 +7974,27 @@
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
       <c r="G205" s="6"/>
-      <c r="H205" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I205" s="6"/>
-      <c r="J205" s="6"/>
-      <c r="K205" s="6"/>
-      <c r="L205" s="6"/>
-      <c r="M205" s="6"/>
-      <c r="N205" s="6"/>
-      <c r="O205" s="6"/>
-      <c r="P205" s="6"/>
-      <c r="Q205" s="6"/>
-      <c r="R205" s="6"/>
-      <c r="S205" s="6"/>
-      <c r="T205" s="6"/>
-      <c r="U205" s="6"/>
-      <c r="V205" s="6"/>
-      <c r="W205" s="6"/>
-      <c r="X205" s="6"/>
-      <c r="Y205" s="6"/>
-      <c r="Z205" s="6"/>
-      <c r="AA205" s="6"/>
-      <c r="AB205" s="6"/>
+      <c r="H205" s="49"/>
+      <c r="I205" s="50"/>
+      <c r="J205" s="50"/>
+      <c r="K205" s="50"/>
+      <c r="L205" s="50"/>
+      <c r="M205" s="50"/>
+      <c r="N205" s="50"/>
+      <c r="O205" s="50"/>
+      <c r="P205" s="50"/>
+      <c r="Q205" s="50"/>
+      <c r="R205" s="50"/>
+      <c r="S205" s="50"/>
+      <c r="T205" s="50"/>
+      <c r="U205" s="50"/>
+      <c r="V205" s="50"/>
+      <c r="W205" s="50"/>
+      <c r="X205" s="50"/>
+      <c r="Y205" s="50"/>
+      <c r="Z205" s="50"/>
+      <c r="AA205" s="50"/>
+      <c r="AB205" s="51"/>
       <c r="AC205" s="11"/>
     </row>
     <row r="206" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7947,27 +8004,27 @@
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
-      <c r="H206" s="46"/>
-      <c r="I206" s="47"/>
-      <c r="J206" s="47"/>
-      <c r="K206" s="47"/>
-      <c r="L206" s="47"/>
-      <c r="M206" s="47"/>
-      <c r="N206" s="47"/>
-      <c r="O206" s="47"/>
-      <c r="P206" s="47"/>
-      <c r="Q206" s="47"/>
-      <c r="R206" s="47"/>
-      <c r="S206" s="47"/>
-      <c r="T206" s="47"/>
-      <c r="U206" s="47"/>
-      <c r="V206" s="47"/>
-      <c r="W206" s="47"/>
-      <c r="X206" s="47"/>
-      <c r="Y206" s="47"/>
-      <c r="Z206" s="47"/>
-      <c r="AA206" s="47"/>
-      <c r="AB206" s="48"/>
+      <c r="H206" s="49"/>
+      <c r="I206" s="50"/>
+      <c r="J206" s="50"/>
+      <c r="K206" s="50"/>
+      <c r="L206" s="50"/>
+      <c r="M206" s="50"/>
+      <c r="N206" s="50"/>
+      <c r="O206" s="50"/>
+      <c r="P206" s="50"/>
+      <c r="Q206" s="50"/>
+      <c r="R206" s="50"/>
+      <c r="S206" s="50"/>
+      <c r="T206" s="50"/>
+      <c r="U206" s="50"/>
+      <c r="V206" s="50"/>
+      <c r="W206" s="50"/>
+      <c r="X206" s="50"/>
+      <c r="Y206" s="50"/>
+      <c r="Z206" s="50"/>
+      <c r="AA206" s="50"/>
+      <c r="AB206" s="51"/>
       <c r="AC206" s="11"/>
     </row>
     <row r="207" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7977,27 +8034,27 @@
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
-      <c r="H207" s="49"/>
-      <c r="I207" s="50"/>
-      <c r="J207" s="50"/>
-      <c r="K207" s="50"/>
-      <c r="L207" s="50"/>
-      <c r="M207" s="50"/>
-      <c r="N207" s="50"/>
-      <c r="O207" s="50"/>
-      <c r="P207" s="50"/>
-      <c r="Q207" s="50"/>
-      <c r="R207" s="50"/>
-      <c r="S207" s="50"/>
-      <c r="T207" s="50"/>
-      <c r="U207" s="50"/>
-      <c r="V207" s="50"/>
-      <c r="W207" s="50"/>
-      <c r="X207" s="50"/>
-      <c r="Y207" s="50"/>
-      <c r="Z207" s="50"/>
-      <c r="AA207" s="50"/>
-      <c r="AB207" s="51"/>
+      <c r="H207" s="52"/>
+      <c r="I207" s="53"/>
+      <c r="J207" s="53"/>
+      <c r="K207" s="53"/>
+      <c r="L207" s="53"/>
+      <c r="M207" s="53"/>
+      <c r="N207" s="53"/>
+      <c r="O207" s="53"/>
+      <c r="P207" s="53"/>
+      <c r="Q207" s="53"/>
+      <c r="R207" s="53"/>
+      <c r="S207" s="53"/>
+      <c r="T207" s="53"/>
+      <c r="U207" s="53"/>
+      <c r="V207" s="53"/>
+      <c r="W207" s="53"/>
+      <c r="X207" s="53"/>
+      <c r="Y207" s="53"/>
+      <c r="Z207" s="53"/>
+      <c r="AA207" s="53"/>
+      <c r="AB207" s="54"/>
       <c r="AC207" s="11"/>
     </row>
     <row r="208" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8007,27 +8064,29 @@
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
       <c r="G208" s="6"/>
-      <c r="H208" s="49"/>
-      <c r="I208" s="50"/>
-      <c r="J208" s="50"/>
-      <c r="K208" s="50"/>
-      <c r="L208" s="50"/>
-      <c r="M208" s="50"/>
-      <c r="N208" s="50"/>
-      <c r="O208" s="50"/>
-      <c r="P208" s="50"/>
-      <c r="Q208" s="50"/>
-      <c r="R208" s="50"/>
-      <c r="S208" s="50"/>
-      <c r="T208" s="50"/>
-      <c r="U208" s="50"/>
-      <c r="V208" s="50"/>
-      <c r="W208" s="50"/>
-      <c r="X208" s="50"/>
-      <c r="Y208" s="50"/>
-      <c r="Z208" s="50"/>
-      <c r="AA208" s="50"/>
-      <c r="AB208" s="51"/>
+      <c r="H208" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I208" s="6"/>
+      <c r="J208" s="6"/>
+      <c r="K208" s="6"/>
+      <c r="L208" s="6"/>
+      <c r="M208" s="6"/>
+      <c r="N208" s="6"/>
+      <c r="O208" s="6"/>
+      <c r="P208" s="6"/>
+      <c r="Q208" s="6"/>
+      <c r="R208" s="6"/>
+      <c r="S208" s="6"/>
+      <c r="T208" s="6"/>
+      <c r="U208" s="6"/>
+      <c r="V208" s="6"/>
+      <c r="W208" s="6"/>
+      <c r="X208" s="6"/>
+      <c r="Y208" s="6"/>
+      <c r="Z208" s="6"/>
+      <c r="AA208" s="6"/>
+      <c r="AB208" s="6"/>
       <c r="AC208" s="11"/>
     </row>
     <row r="209" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8037,27 +8096,27 @@
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
-      <c r="H209" s="49"/>
-      <c r="I209" s="50"/>
-      <c r="J209" s="50"/>
-      <c r="K209" s="50"/>
-      <c r="L209" s="50"/>
-      <c r="M209" s="50"/>
-      <c r="N209" s="50"/>
-      <c r="O209" s="50"/>
-      <c r="P209" s="50"/>
-      <c r="Q209" s="50"/>
-      <c r="R209" s="50"/>
-      <c r="S209" s="50"/>
-      <c r="T209" s="50"/>
-      <c r="U209" s="50"/>
-      <c r="V209" s="50"/>
-      <c r="W209" s="50"/>
-      <c r="X209" s="50"/>
-      <c r="Y209" s="50"/>
-      <c r="Z209" s="50"/>
-      <c r="AA209" s="50"/>
-      <c r="AB209" s="51"/>
+      <c r="H209" s="46"/>
+      <c r="I209" s="47"/>
+      <c r="J209" s="47"/>
+      <c r="K209" s="47"/>
+      <c r="L209" s="47"/>
+      <c r="M209" s="47"/>
+      <c r="N209" s="47"/>
+      <c r="O209" s="47"/>
+      <c r="P209" s="47"/>
+      <c r="Q209" s="47"/>
+      <c r="R209" s="47"/>
+      <c r="S209" s="47"/>
+      <c r="T209" s="47"/>
+      <c r="U209" s="47"/>
+      <c r="V209" s="47"/>
+      <c r="W209" s="47"/>
+      <c r="X209" s="47"/>
+      <c r="Y209" s="47"/>
+      <c r="Z209" s="47"/>
+      <c r="AA209" s="47"/>
+      <c r="AB209" s="48"/>
       <c r="AC209" s="11"/>
     </row>
     <row r="210" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8127,58 +8186,148 @@
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
-      <c r="H212" s="52"/>
-      <c r="I212" s="53"/>
-      <c r="J212" s="53"/>
-      <c r="K212" s="53"/>
-      <c r="L212" s="53"/>
-      <c r="M212" s="53"/>
-      <c r="N212" s="53"/>
-      <c r="O212" s="53"/>
-      <c r="P212" s="53"/>
-      <c r="Q212" s="53"/>
-      <c r="R212" s="53"/>
-      <c r="S212" s="53"/>
-      <c r="T212" s="53"/>
-      <c r="U212" s="53"/>
-      <c r="V212" s="53"/>
-      <c r="W212" s="53"/>
-      <c r="X212" s="53"/>
-      <c r="Y212" s="53"/>
-      <c r="Z212" s="53"/>
-      <c r="AA212" s="53"/>
-      <c r="AB212" s="54"/>
+      <c r="H212" s="49"/>
+      <c r="I212" s="50"/>
+      <c r="J212" s="50"/>
+      <c r="K212" s="50"/>
+      <c r="L212" s="50"/>
+      <c r="M212" s="50"/>
+      <c r="N212" s="50"/>
+      <c r="O212" s="50"/>
+      <c r="P212" s="50"/>
+      <c r="Q212" s="50"/>
+      <c r="R212" s="50"/>
+      <c r="S212" s="50"/>
+      <c r="T212" s="50"/>
+      <c r="U212" s="50"/>
+      <c r="V212" s="50"/>
+      <c r="W212" s="50"/>
+      <c r="X212" s="50"/>
+      <c r="Y212" s="50"/>
+      <c r="Z212" s="50"/>
+      <c r="AA212" s="50"/>
+      <c r="AB212" s="51"/>
       <c r="AC212" s="11"/>
     </row>
     <row r="213" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B213" s="45"/>
-      <c r="C213" s="3"/>
-      <c r="D213" s="4"/>
-      <c r="E213" s="4"/>
-      <c r="F213" s="4"/>
-      <c r="G213" s="4"/>
-      <c r="H213" s="4"/>
-      <c r="I213" s="4"/>
-      <c r="J213" s="4"/>
-      <c r="K213" s="4"/>
-      <c r="L213" s="4"/>
-      <c r="M213" s="4"/>
-      <c r="N213" s="4"/>
-      <c r="O213" s="4"/>
-      <c r="P213" s="4"/>
-      <c r="Q213" s="4"/>
-      <c r="R213" s="4"/>
-      <c r="S213" s="4"/>
-      <c r="T213" s="4"/>
-      <c r="U213" s="4"/>
-      <c r="V213" s="4"/>
-      <c r="W213" s="4"/>
-      <c r="X213" s="4"/>
-      <c r="Y213" s="4"/>
-      <c r="Z213" s="4"/>
-      <c r="AA213" s="4"/>
-      <c r="AB213" s="4"/>
-      <c r="AC213" s="12"/>
+      <c r="B213" s="44"/>
+      <c r="C213" s="5"/>
+      <c r="D213" s="6"/>
+      <c r="E213" s="6"/>
+      <c r="F213" s="6"/>
+      <c r="G213" s="6"/>
+      <c r="H213" s="49"/>
+      <c r="I213" s="50"/>
+      <c r="J213" s="50"/>
+      <c r="K213" s="50"/>
+      <c r="L213" s="50"/>
+      <c r="M213" s="50"/>
+      <c r="N213" s="50"/>
+      <c r="O213" s="50"/>
+      <c r="P213" s="50"/>
+      <c r="Q213" s="50"/>
+      <c r="R213" s="50"/>
+      <c r="S213" s="50"/>
+      <c r="T213" s="50"/>
+      <c r="U213" s="50"/>
+      <c r="V213" s="50"/>
+      <c r="W213" s="50"/>
+      <c r="X213" s="50"/>
+      <c r="Y213" s="50"/>
+      <c r="Z213" s="50"/>
+      <c r="AA213" s="50"/>
+      <c r="AB213" s="51"/>
+      <c r="AC213" s="11"/>
+    </row>
+    <row r="214" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B214" s="44"/>
+      <c r="C214" s="5"/>
+      <c r="D214" s="6"/>
+      <c r="E214" s="6"/>
+      <c r="F214" s="6"/>
+      <c r="G214" s="6"/>
+      <c r="H214" s="49"/>
+      <c r="I214" s="50"/>
+      <c r="J214" s="50"/>
+      <c r="K214" s="50"/>
+      <c r="L214" s="50"/>
+      <c r="M214" s="50"/>
+      <c r="N214" s="50"/>
+      <c r="O214" s="50"/>
+      <c r="P214" s="50"/>
+      <c r="Q214" s="50"/>
+      <c r="R214" s="50"/>
+      <c r="S214" s="50"/>
+      <c r="T214" s="50"/>
+      <c r="U214" s="50"/>
+      <c r="V214" s="50"/>
+      <c r="W214" s="50"/>
+      <c r="X214" s="50"/>
+      <c r="Y214" s="50"/>
+      <c r="Z214" s="50"/>
+      <c r="AA214" s="50"/>
+      <c r="AB214" s="51"/>
+      <c r="AC214" s="11"/>
+    </row>
+    <row r="215" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B215" s="44"/>
+      <c r="C215" s="5"/>
+      <c r="D215" s="6"/>
+      <c r="E215" s="6"/>
+      <c r="F215" s="6"/>
+      <c r="G215" s="6"/>
+      <c r="H215" s="52"/>
+      <c r="I215" s="53"/>
+      <c r="J215" s="53"/>
+      <c r="K215" s="53"/>
+      <c r="L215" s="53"/>
+      <c r="M215" s="53"/>
+      <c r="N215" s="53"/>
+      <c r="O215" s="53"/>
+      <c r="P215" s="53"/>
+      <c r="Q215" s="53"/>
+      <c r="R215" s="53"/>
+      <c r="S215" s="53"/>
+      <c r="T215" s="53"/>
+      <c r="U215" s="53"/>
+      <c r="V215" s="53"/>
+      <c r="W215" s="53"/>
+      <c r="X215" s="53"/>
+      <c r="Y215" s="53"/>
+      <c r="Z215" s="53"/>
+      <c r="AA215" s="53"/>
+      <c r="AB215" s="54"/>
+      <c r="AC215" s="11"/>
+    </row>
+    <row r="216" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B216" s="45"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="4"/>
+      <c r="E216" s="4"/>
+      <c r="F216" s="4"/>
+      <c r="G216" s="4"/>
+      <c r="H216" s="4"/>
+      <c r="I216" s="4"/>
+      <c r="J216" s="4"/>
+      <c r="K216" s="4"/>
+      <c r="L216" s="4"/>
+      <c r="M216" s="4"/>
+      <c r="N216" s="4"/>
+      <c r="O216" s="4"/>
+      <c r="P216" s="4"/>
+      <c r="Q216" s="4"/>
+      <c r="R216" s="4"/>
+      <c r="S216" s="4"/>
+      <c r="T216" s="4"/>
+      <c r="U216" s="4"/>
+      <c r="V216" s="4"/>
+      <c r="W216" s="4"/>
+      <c r="X216" s="4"/>
+      <c r="Y216" s="4"/>
+      <c r="Z216" s="4"/>
+      <c r="AA216" s="4"/>
+      <c r="AB216" s="4"/>
+      <c r="AC216" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -8195,39 +8344,42 @@
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="H46:AB52"/>
     <mergeCell ref="H54:AB60"/>
-    <mergeCell ref="B63:B80"/>
+    <mergeCell ref="B63:B83"/>
     <mergeCell ref="D65:E65"/>
-    <mergeCell ref="H65:AB71"/>
-    <mergeCell ref="H73:AB79"/>
-    <mergeCell ref="B82:B99"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="H84:AB90"/>
-    <mergeCell ref="H92:AB98"/>
-    <mergeCell ref="B101:B118"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="H103:AB109"/>
-    <mergeCell ref="H111:AB117"/>
-    <mergeCell ref="B120:B137"/>
-    <mergeCell ref="D122:E122"/>
-    <mergeCell ref="H122:AB128"/>
-    <mergeCell ref="H130:AB136"/>
-    <mergeCell ref="B139:B156"/>
-    <mergeCell ref="D141:E141"/>
-    <mergeCell ref="H141:AB147"/>
-    <mergeCell ref="H149:AB155"/>
-    <mergeCell ref="B158:B175"/>
-    <mergeCell ref="D160:E160"/>
-    <mergeCell ref="H160:AB166"/>
-    <mergeCell ref="H168:AB174"/>
-    <mergeCell ref="B177:B194"/>
-    <mergeCell ref="D179:E179"/>
-    <mergeCell ref="H179:AB185"/>
-    <mergeCell ref="H187:AB193"/>
-    <mergeCell ref="B196:B213"/>
-    <mergeCell ref="D198:E198"/>
-    <mergeCell ref="H198:AB204"/>
-    <mergeCell ref="H206:AB212"/>
+    <mergeCell ref="H76:AB82"/>
+    <mergeCell ref="B85:B102"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="H87:AB93"/>
+    <mergeCell ref="H95:AB101"/>
+    <mergeCell ref="H65:AB74"/>
+    <mergeCell ref="B104:B121"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="H106:AB112"/>
+    <mergeCell ref="H114:AB120"/>
+    <mergeCell ref="B123:B140"/>
+    <mergeCell ref="D125:E125"/>
+    <mergeCell ref="H125:AB131"/>
+    <mergeCell ref="H133:AB139"/>
+    <mergeCell ref="B142:B159"/>
+    <mergeCell ref="D144:E144"/>
+    <mergeCell ref="H144:AB150"/>
+    <mergeCell ref="H152:AB158"/>
+    <mergeCell ref="B161:B178"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="H163:AB169"/>
+    <mergeCell ref="H171:AB177"/>
+    <mergeCell ref="B180:B197"/>
+    <mergeCell ref="D182:E182"/>
+    <mergeCell ref="H182:AB188"/>
+    <mergeCell ref="H190:AB196"/>
+    <mergeCell ref="B199:B216"/>
+    <mergeCell ref="D201:E201"/>
+    <mergeCell ref="H201:AB207"/>
+    <mergeCell ref="H209:AB215"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H65" r:id="rId1" display="https://learn.microsoft.com/en-us/dotnet/maui/platform-integration/device/geolocation" xr:uid="{6A2F2CBC-218B-43EA-806A-9BF39365BDB2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"ORF Universal SemiCond TX Regular"&amp;7&amp;KFFDA00 INTERN</oddFooter>

--- a/Projekttagebuch.xlsx
+++ b/Projekttagebuch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\projects\GW.Demo.Maui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CE483E-9C59-4B4D-9496-8649B2DDA058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4A69A8-43B1-4CCB-BFD7-CED0A21CD247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="68">
   <si>
     <t>Framework:</t>
   </si>
@@ -259,6 +259,36 @@
   </si>
   <si>
     <t>82</t>
+  </si>
+  <si>
+    <t>https://dummyjson.com/docs/posts
+https://learn.microsoft.com/en-us/dotnet/architecture/maui/mvvm
+https://learn.microsoft.com/de-de/dotnet/communitytoolkit/mvvm/
+https://learn.microsoft.com/de-de/dotnet/maui/fundamentals/data-binding
+https://medium.com/%40myofficework000/mvvm-architecture-using-repository-pattern-for-beginners-181a5df3fff8
+https://learn.microsoft.com/en-us/aspnet/web-api/overview/advanced/calling-a-web-api-from-a-net-client
+https://code-maze.com/different-ways-consume-restful-api-csharp/
+https://learn.microsoft.com/de-de/dotnet/standard/serialization/system-text-json/how-to</t>
+  </si>
+  <si>
+    <t>Einige architektonische Überlegungen angestellt. Data-Client-Store-Pattern angewandt. REST-Call, JSON-Serialisierung gut dokumentiert und nicht schwierig umzusetzen,</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/listview
+https://www.codemag.com/Article/2503021/Exploring-.NET-MAUI-Working-with-Lists-of-Data
+https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/collectionview
+https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/collectionview/populate-data
+https://xamarincodingtutorial.blogspot.com/2022/05/implementing-pull-to-refresh-with.html
+https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/refreshview</t>
+  </si>
+  <si>
+    <t>Im Großen und Ganzen wenig problematisch. Dokumentation ok. Wieder Binding-Fehler, wenn man das schon öfter gehabt hat, tut man sich leichter, CoPilot hilft zT. auch aus.</t>
   </si>
 </sst>
 </file>
@@ -503,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -590,6 +620,12 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -617,12 +653,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -649,9 +679,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2158,11 +2185,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>11</v>
       </c>
@@ -3943,25 +3970,25 @@
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="35"/>
-      <c r="I66" s="66"/>
-      <c r="J66" s="66"/>
-      <c r="K66" s="66"/>
-      <c r="L66" s="66"/>
-      <c r="M66" s="66"/>
-      <c r="N66" s="66"/>
-      <c r="O66" s="66"/>
-      <c r="P66" s="66"/>
-      <c r="Q66" s="66"/>
-      <c r="R66" s="66"/>
-      <c r="S66" s="66"/>
-      <c r="T66" s="66"/>
-      <c r="U66" s="66"/>
-      <c r="V66" s="66"/>
-      <c r="W66" s="66"/>
-      <c r="X66" s="66"/>
-      <c r="Y66" s="66"/>
-      <c r="Z66" s="66"/>
-      <c r="AA66" s="66"/>
+      <c r="I66" s="36"/>
+      <c r="J66" s="36"/>
+      <c r="K66" s="36"/>
+      <c r="L66" s="36"/>
+      <c r="M66" s="36"/>
+      <c r="N66" s="36"/>
+      <c r="O66" s="36"/>
+      <c r="P66" s="36"/>
+      <c r="Q66" s="36"/>
+      <c r="R66" s="36"/>
+      <c r="S66" s="36"/>
+      <c r="T66" s="36"/>
+      <c r="U66" s="36"/>
+      <c r="V66" s="36"/>
+      <c r="W66" s="36"/>
+      <c r="X66" s="36"/>
+      <c r="Y66" s="36"/>
+      <c r="Z66" s="36"/>
+      <c r="AA66" s="36"/>
       <c r="AB66" s="37"/>
       <c r="AC66" s="11"/>
     </row>
@@ -3973,25 +4000,25 @@
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="35"/>
-      <c r="I67" s="66"/>
-      <c r="J67" s="66"/>
-      <c r="K67" s="66"/>
-      <c r="L67" s="66"/>
-      <c r="M67" s="66"/>
-      <c r="N67" s="66"/>
-      <c r="O67" s="66"/>
-      <c r="P67" s="66"/>
-      <c r="Q67" s="66"/>
-      <c r="R67" s="66"/>
-      <c r="S67" s="66"/>
-      <c r="T67" s="66"/>
-      <c r="U67" s="66"/>
-      <c r="V67" s="66"/>
-      <c r="W67" s="66"/>
-      <c r="X67" s="66"/>
-      <c r="Y67" s="66"/>
-      <c r="Z67" s="66"/>
-      <c r="AA67" s="66"/>
+      <c r="I67" s="36"/>
+      <c r="J67" s="36"/>
+      <c r="K67" s="36"/>
+      <c r="L67" s="36"/>
+      <c r="M67" s="36"/>
+      <c r="N67" s="36"/>
+      <c r="O67" s="36"/>
+      <c r="P67" s="36"/>
+      <c r="Q67" s="36"/>
+      <c r="R67" s="36"/>
+      <c r="S67" s="36"/>
+      <c r="T67" s="36"/>
+      <c r="U67" s="36"/>
+      <c r="V67" s="36"/>
+      <c r="W67" s="36"/>
+      <c r="X67" s="36"/>
+      <c r="Y67" s="36"/>
+      <c r="Z67" s="36"/>
+      <c r="AA67" s="36"/>
       <c r="AB67" s="37"/>
       <c r="AC67" s="11"/>
     </row>
@@ -4003,25 +4030,25 @@
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="35"/>
-      <c r="I68" s="66"/>
-      <c r="J68" s="66"/>
-      <c r="K68" s="66"/>
-      <c r="L68" s="66"/>
-      <c r="M68" s="66"/>
-      <c r="N68" s="66"/>
-      <c r="O68" s="66"/>
-      <c r="P68" s="66"/>
-      <c r="Q68" s="66"/>
-      <c r="R68" s="66"/>
-      <c r="S68" s="66"/>
-      <c r="T68" s="66"/>
-      <c r="U68" s="66"/>
-      <c r="V68" s="66"/>
-      <c r="W68" s="66"/>
-      <c r="X68" s="66"/>
-      <c r="Y68" s="66"/>
-      <c r="Z68" s="66"/>
-      <c r="AA68" s="66"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="36"/>
+      <c r="K68" s="36"/>
+      <c r="L68" s="36"/>
+      <c r="M68" s="36"/>
+      <c r="N68" s="36"/>
+      <c r="O68" s="36"/>
+      <c r="P68" s="36"/>
+      <c r="Q68" s="36"/>
+      <c r="R68" s="36"/>
+      <c r="S68" s="36"/>
+      <c r="T68" s="36"/>
+      <c r="U68" s="36"/>
+      <c r="V68" s="36"/>
+      <c r="W68" s="36"/>
+      <c r="X68" s="36"/>
+      <c r="Y68" s="36"/>
+      <c r="Z68" s="36"/>
+      <c r="AA68" s="36"/>
       <c r="AB68" s="37"/>
       <c r="AC68" s="11"/>
     </row>
@@ -4033,25 +4060,25 @@
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="35"/>
-      <c r="I69" s="66"/>
-      <c r="J69" s="66"/>
-      <c r="K69" s="66"/>
-      <c r="L69" s="66"/>
-      <c r="M69" s="66"/>
-      <c r="N69" s="66"/>
-      <c r="O69" s="66"/>
-      <c r="P69" s="66"/>
-      <c r="Q69" s="66"/>
-      <c r="R69" s="66"/>
-      <c r="S69" s="66"/>
-      <c r="T69" s="66"/>
-      <c r="U69" s="66"/>
-      <c r="V69" s="66"/>
-      <c r="W69" s="66"/>
-      <c r="X69" s="66"/>
-      <c r="Y69" s="66"/>
-      <c r="Z69" s="66"/>
-      <c r="AA69" s="66"/>
+      <c r="I69" s="36"/>
+      <c r="J69" s="36"/>
+      <c r="K69" s="36"/>
+      <c r="L69" s="36"/>
+      <c r="M69" s="36"/>
+      <c r="N69" s="36"/>
+      <c r="O69" s="36"/>
+      <c r="P69" s="36"/>
+      <c r="Q69" s="36"/>
+      <c r="R69" s="36"/>
+      <c r="S69" s="36"/>
+      <c r="T69" s="36"/>
+      <c r="U69" s="36"/>
+      <c r="V69" s="36"/>
+      <c r="W69" s="36"/>
+      <c r="X69" s="36"/>
+      <c r="Y69" s="36"/>
+      <c r="Z69" s="36"/>
+      <c r="AA69" s="36"/>
       <c r="AB69" s="37"/>
       <c r="AC69" s="11"/>
     </row>
@@ -4063,25 +4090,25 @@
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="35"/>
-      <c r="I70" s="66"/>
-      <c r="J70" s="66"/>
-      <c r="K70" s="66"/>
-      <c r="L70" s="66"/>
-      <c r="M70" s="66"/>
-      <c r="N70" s="66"/>
-      <c r="O70" s="66"/>
-      <c r="P70" s="66"/>
-      <c r="Q70" s="66"/>
-      <c r="R70" s="66"/>
-      <c r="S70" s="66"/>
-      <c r="T70" s="66"/>
-      <c r="U70" s="66"/>
-      <c r="V70" s="66"/>
-      <c r="W70" s="66"/>
-      <c r="X70" s="66"/>
-      <c r="Y70" s="66"/>
-      <c r="Z70" s="66"/>
-      <c r="AA70" s="66"/>
+      <c r="I70" s="36"/>
+      <c r="J70" s="36"/>
+      <c r="K70" s="36"/>
+      <c r="L70" s="36"/>
+      <c r="M70" s="36"/>
+      <c r="N70" s="36"/>
+      <c r="O70" s="36"/>
+      <c r="P70" s="36"/>
+      <c r="Q70" s="36"/>
+      <c r="R70" s="36"/>
+      <c r="S70" s="36"/>
+      <c r="T70" s="36"/>
+      <c r="U70" s="36"/>
+      <c r="V70" s="36"/>
+      <c r="W70" s="36"/>
+      <c r="X70" s="36"/>
+      <c r="Y70" s="36"/>
+      <c r="Z70" s="36"/>
+      <c r="AA70" s="36"/>
       <c r="AB70" s="37"/>
       <c r="AC70" s="11"/>
     </row>
@@ -4093,25 +4120,25 @@
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="35"/>
-      <c r="I71" s="66"/>
-      <c r="J71" s="66"/>
-      <c r="K71" s="66"/>
-      <c r="L71" s="66"/>
-      <c r="M71" s="66"/>
-      <c r="N71" s="66"/>
-      <c r="O71" s="66"/>
-      <c r="P71" s="66"/>
-      <c r="Q71" s="66"/>
-      <c r="R71" s="66"/>
-      <c r="S71" s="66"/>
-      <c r="T71" s="66"/>
-      <c r="U71" s="66"/>
-      <c r="V71" s="66"/>
-      <c r="W71" s="66"/>
-      <c r="X71" s="66"/>
-      <c r="Y71" s="66"/>
-      <c r="Z71" s="66"/>
-      <c r="AA71" s="66"/>
+      <c r="I71" s="36"/>
+      <c r="J71" s="36"/>
+      <c r="K71" s="36"/>
+      <c r="L71" s="36"/>
+      <c r="M71" s="36"/>
+      <c r="N71" s="36"/>
+      <c r="O71" s="36"/>
+      <c r="P71" s="36"/>
+      <c r="Q71" s="36"/>
+      <c r="R71" s="36"/>
+      <c r="S71" s="36"/>
+      <c r="T71" s="36"/>
+      <c r="U71" s="36"/>
+      <c r="V71" s="36"/>
+      <c r="W71" s="36"/>
+      <c r="X71" s="36"/>
+      <c r="Y71" s="36"/>
+      <c r="Z71" s="36"/>
+      <c r="AA71" s="36"/>
       <c r="AB71" s="37"/>
       <c r="AC71" s="11"/>
     </row>
@@ -4123,25 +4150,25 @@
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="35"/>
-      <c r="I72" s="66"/>
-      <c r="J72" s="66"/>
-      <c r="K72" s="66"/>
-      <c r="L72" s="66"/>
-      <c r="M72" s="66"/>
-      <c r="N72" s="66"/>
-      <c r="O72" s="66"/>
-      <c r="P72" s="66"/>
-      <c r="Q72" s="66"/>
-      <c r="R72" s="66"/>
-      <c r="S72" s="66"/>
-      <c r="T72" s="66"/>
-      <c r="U72" s="66"/>
-      <c r="V72" s="66"/>
-      <c r="W72" s="66"/>
-      <c r="X72" s="66"/>
-      <c r="Y72" s="66"/>
-      <c r="Z72" s="66"/>
-      <c r="AA72" s="66"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="36"/>
+      <c r="K72" s="36"/>
+      <c r="L72" s="36"/>
+      <c r="M72" s="36"/>
+      <c r="N72" s="36"/>
+      <c r="O72" s="36"/>
+      <c r="P72" s="36"/>
+      <c r="Q72" s="36"/>
+      <c r="R72" s="36"/>
+      <c r="S72" s="36"/>
+      <c r="T72" s="36"/>
+      <c r="U72" s="36"/>
+      <c r="V72" s="36"/>
+      <c r="W72" s="36"/>
+      <c r="X72" s="36"/>
+      <c r="Y72" s="36"/>
+      <c r="Z72" s="36"/>
+      <c r="AA72" s="36"/>
       <c r="AB72" s="37"/>
       <c r="AC72" s="11"/>
     </row>
@@ -4153,25 +4180,25 @@
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="35"/>
-      <c r="I73" s="66"/>
-      <c r="J73" s="66"/>
-      <c r="K73" s="66"/>
-      <c r="L73" s="66"/>
-      <c r="M73" s="66"/>
-      <c r="N73" s="66"/>
-      <c r="O73" s="66"/>
-      <c r="P73" s="66"/>
-      <c r="Q73" s="66"/>
-      <c r="R73" s="66"/>
-      <c r="S73" s="66"/>
-      <c r="T73" s="66"/>
-      <c r="U73" s="66"/>
-      <c r="V73" s="66"/>
-      <c r="W73" s="66"/>
-      <c r="X73" s="66"/>
-      <c r="Y73" s="66"/>
-      <c r="Z73" s="66"/>
-      <c r="AA73" s="66"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="36"/>
+      <c r="K73" s="36"/>
+      <c r="L73" s="36"/>
+      <c r="M73" s="36"/>
+      <c r="N73" s="36"/>
+      <c r="O73" s="36"/>
+      <c r="P73" s="36"/>
+      <c r="Q73" s="36"/>
+      <c r="R73" s="36"/>
+      <c r="S73" s="36"/>
+      <c r="T73" s="36"/>
+      <c r="U73" s="36"/>
+      <c r="V73" s="36"/>
+      <c r="W73" s="36"/>
+      <c r="X73" s="36"/>
+      <c r="Y73" s="36"/>
+      <c r="Z73" s="36"/>
+      <c r="AA73" s="36"/>
       <c r="AB73" s="37"/>
       <c r="AC73" s="11"/>
     </row>
@@ -4548,33 +4575,37 @@
     <row r="87" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="44"/>
       <c r="C87" s="5"/>
-      <c r="D87" s="41"/>
+      <c r="D87" s="41" t="s">
+        <v>64</v>
+      </c>
       <c r="E87" s="42"/>
       <c r="F87" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G87" s="6"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="47"/>
-      <c r="J87" s="47"/>
-      <c r="K87" s="47"/>
-      <c r="L87" s="47"/>
-      <c r="M87" s="47"/>
-      <c r="N87" s="47"/>
-      <c r="O87" s="47"/>
-      <c r="P87" s="47"/>
-      <c r="Q87" s="47"/>
-      <c r="R87" s="47"/>
-      <c r="S87" s="47"/>
-      <c r="T87" s="47"/>
-      <c r="U87" s="47"/>
-      <c r="V87" s="47"/>
-      <c r="W87" s="47"/>
-      <c r="X87" s="47"/>
-      <c r="Y87" s="47"/>
-      <c r="Z87" s="47"/>
-      <c r="AA87" s="47"/>
-      <c r="AB87" s="48"/>
+      <c r="H87" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="I87" s="33"/>
+      <c r="J87" s="33"/>
+      <c r="K87" s="33"/>
+      <c r="L87" s="33"/>
+      <c r="M87" s="33"/>
+      <c r="N87" s="33"/>
+      <c r="O87" s="33"/>
+      <c r="P87" s="33"/>
+      <c r="Q87" s="33"/>
+      <c r="R87" s="33"/>
+      <c r="S87" s="33"/>
+      <c r="T87" s="33"/>
+      <c r="U87" s="33"/>
+      <c r="V87" s="33"/>
+      <c r="W87" s="33"/>
+      <c r="X87" s="33"/>
+      <c r="Y87" s="33"/>
+      <c r="Z87" s="33"/>
+      <c r="AA87" s="33"/>
+      <c r="AB87" s="34"/>
       <c r="AC87" s="11"/>
     </row>
     <row r="88" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4584,27 +4615,27 @@
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="50"/>
-      <c r="J88" s="50"/>
-      <c r="K88" s="50"/>
-      <c r="L88" s="50"/>
-      <c r="M88" s="50"/>
-      <c r="N88" s="50"/>
-      <c r="O88" s="50"/>
-      <c r="P88" s="50"/>
-      <c r="Q88" s="50"/>
-      <c r="R88" s="50"/>
-      <c r="S88" s="50"/>
-      <c r="T88" s="50"/>
-      <c r="U88" s="50"/>
-      <c r="V88" s="50"/>
-      <c r="W88" s="50"/>
-      <c r="X88" s="50"/>
-      <c r="Y88" s="50"/>
-      <c r="Z88" s="50"/>
-      <c r="AA88" s="50"/>
-      <c r="AB88" s="51"/>
+      <c r="H88" s="35"/>
+      <c r="I88" s="36"/>
+      <c r="J88" s="36"/>
+      <c r="K88" s="36"/>
+      <c r="L88" s="36"/>
+      <c r="M88" s="36"/>
+      <c r="N88" s="36"/>
+      <c r="O88" s="36"/>
+      <c r="P88" s="36"/>
+      <c r="Q88" s="36"/>
+      <c r="R88" s="36"/>
+      <c r="S88" s="36"/>
+      <c r="T88" s="36"/>
+      <c r="U88" s="36"/>
+      <c r="V88" s="36"/>
+      <c r="W88" s="36"/>
+      <c r="X88" s="36"/>
+      <c r="Y88" s="36"/>
+      <c r="Z88" s="36"/>
+      <c r="AA88" s="36"/>
+      <c r="AB88" s="37"/>
       <c r="AC88" s="11"/>
     </row>
     <row r="89" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4614,27 +4645,27 @@
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
-      <c r="H89" s="49"/>
-      <c r="I89" s="50"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="50"/>
-      <c r="L89" s="50"/>
-      <c r="M89" s="50"/>
-      <c r="N89" s="50"/>
-      <c r="O89" s="50"/>
-      <c r="P89" s="50"/>
-      <c r="Q89" s="50"/>
-      <c r="R89" s="50"/>
-      <c r="S89" s="50"/>
-      <c r="T89" s="50"/>
-      <c r="U89" s="50"/>
-      <c r="V89" s="50"/>
-      <c r="W89" s="50"/>
-      <c r="X89" s="50"/>
-      <c r="Y89" s="50"/>
-      <c r="Z89" s="50"/>
-      <c r="AA89" s="50"/>
-      <c r="AB89" s="51"/>
+      <c r="H89" s="35"/>
+      <c r="I89" s="36"/>
+      <c r="J89" s="36"/>
+      <c r="K89" s="36"/>
+      <c r="L89" s="36"/>
+      <c r="M89" s="36"/>
+      <c r="N89" s="36"/>
+      <c r="O89" s="36"/>
+      <c r="P89" s="36"/>
+      <c r="Q89" s="36"/>
+      <c r="R89" s="36"/>
+      <c r="S89" s="36"/>
+      <c r="T89" s="36"/>
+      <c r="U89" s="36"/>
+      <c r="V89" s="36"/>
+      <c r="W89" s="36"/>
+      <c r="X89" s="36"/>
+      <c r="Y89" s="36"/>
+      <c r="Z89" s="36"/>
+      <c r="AA89" s="36"/>
+      <c r="AB89" s="37"/>
       <c r="AC89" s="11"/>
     </row>
     <row r="90" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4644,27 +4675,27 @@
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
-      <c r="H90" s="49"/>
-      <c r="I90" s="50"/>
-      <c r="J90" s="50"/>
-      <c r="K90" s="50"/>
-      <c r="L90" s="50"/>
-      <c r="M90" s="50"/>
-      <c r="N90" s="50"/>
-      <c r="O90" s="50"/>
-      <c r="P90" s="50"/>
-      <c r="Q90" s="50"/>
-      <c r="R90" s="50"/>
-      <c r="S90" s="50"/>
-      <c r="T90" s="50"/>
-      <c r="U90" s="50"/>
-      <c r="V90" s="50"/>
-      <c r="W90" s="50"/>
-      <c r="X90" s="50"/>
-      <c r="Y90" s="50"/>
-      <c r="Z90" s="50"/>
-      <c r="AA90" s="50"/>
-      <c r="AB90" s="51"/>
+      <c r="H90" s="35"/>
+      <c r="I90" s="36"/>
+      <c r="J90" s="36"/>
+      <c r="K90" s="36"/>
+      <c r="L90" s="36"/>
+      <c r="M90" s="36"/>
+      <c r="N90" s="36"/>
+      <c r="O90" s="36"/>
+      <c r="P90" s="36"/>
+      <c r="Q90" s="36"/>
+      <c r="R90" s="36"/>
+      <c r="S90" s="36"/>
+      <c r="T90" s="36"/>
+      <c r="U90" s="36"/>
+      <c r="V90" s="36"/>
+      <c r="W90" s="36"/>
+      <c r="X90" s="36"/>
+      <c r="Y90" s="36"/>
+      <c r="Z90" s="36"/>
+      <c r="AA90" s="36"/>
+      <c r="AB90" s="37"/>
       <c r="AC90" s="11"/>
     </row>
     <row r="91" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4674,27 +4705,27 @@
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
-      <c r="H91" s="49"/>
-      <c r="I91" s="50"/>
-      <c r="J91" s="50"/>
-      <c r="K91" s="50"/>
-      <c r="L91" s="50"/>
-      <c r="M91" s="50"/>
-      <c r="N91" s="50"/>
-      <c r="O91" s="50"/>
-      <c r="P91" s="50"/>
-      <c r="Q91" s="50"/>
-      <c r="R91" s="50"/>
-      <c r="S91" s="50"/>
-      <c r="T91" s="50"/>
-      <c r="U91" s="50"/>
-      <c r="V91" s="50"/>
-      <c r="W91" s="50"/>
-      <c r="X91" s="50"/>
-      <c r="Y91" s="50"/>
-      <c r="Z91" s="50"/>
-      <c r="AA91" s="50"/>
-      <c r="AB91" s="51"/>
+      <c r="H91" s="35"/>
+      <c r="I91" s="36"/>
+      <c r="J91" s="36"/>
+      <c r="K91" s="36"/>
+      <c r="L91" s="36"/>
+      <c r="M91" s="36"/>
+      <c r="N91" s="36"/>
+      <c r="O91" s="36"/>
+      <c r="P91" s="36"/>
+      <c r="Q91" s="36"/>
+      <c r="R91" s="36"/>
+      <c r="S91" s="36"/>
+      <c r="T91" s="36"/>
+      <c r="U91" s="36"/>
+      <c r="V91" s="36"/>
+      <c r="W91" s="36"/>
+      <c r="X91" s="36"/>
+      <c r="Y91" s="36"/>
+      <c r="Z91" s="36"/>
+      <c r="AA91" s="36"/>
+      <c r="AB91" s="37"/>
       <c r="AC91" s="11"/>
     </row>
     <row r="92" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4704,27 +4735,27 @@
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
-      <c r="H92" s="49"/>
-      <c r="I92" s="50"/>
-      <c r="J92" s="50"/>
-      <c r="K92" s="50"/>
-      <c r="L92" s="50"/>
-      <c r="M92" s="50"/>
-      <c r="N92" s="50"/>
-      <c r="O92" s="50"/>
-      <c r="P92" s="50"/>
-      <c r="Q92" s="50"/>
-      <c r="R92" s="50"/>
-      <c r="S92" s="50"/>
-      <c r="T92" s="50"/>
-      <c r="U92" s="50"/>
-      <c r="V92" s="50"/>
-      <c r="W92" s="50"/>
-      <c r="X92" s="50"/>
-      <c r="Y92" s="50"/>
-      <c r="Z92" s="50"/>
-      <c r="AA92" s="50"/>
-      <c r="AB92" s="51"/>
+      <c r="H92" s="35"/>
+      <c r="I92" s="36"/>
+      <c r="J92" s="36"/>
+      <c r="K92" s="36"/>
+      <c r="L92" s="36"/>
+      <c r="M92" s="36"/>
+      <c r="N92" s="36"/>
+      <c r="O92" s="36"/>
+      <c r="P92" s="36"/>
+      <c r="Q92" s="36"/>
+      <c r="R92" s="36"/>
+      <c r="S92" s="36"/>
+      <c r="T92" s="36"/>
+      <c r="U92" s="36"/>
+      <c r="V92" s="36"/>
+      <c r="W92" s="36"/>
+      <c r="X92" s="36"/>
+      <c r="Y92" s="36"/>
+      <c r="Z92" s="36"/>
+      <c r="AA92" s="36"/>
+      <c r="AB92" s="37"/>
       <c r="AC92" s="11"/>
     </row>
     <row r="93" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4734,27 +4765,27 @@
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="53"/>
-      <c r="J93" s="53"/>
-      <c r="K93" s="53"/>
-      <c r="L93" s="53"/>
-      <c r="M93" s="53"/>
-      <c r="N93" s="53"/>
-      <c r="O93" s="53"/>
-      <c r="P93" s="53"/>
-      <c r="Q93" s="53"/>
-      <c r="R93" s="53"/>
-      <c r="S93" s="53"/>
-      <c r="T93" s="53"/>
-      <c r="U93" s="53"/>
-      <c r="V93" s="53"/>
-      <c r="W93" s="53"/>
-      <c r="X93" s="53"/>
-      <c r="Y93" s="53"/>
-      <c r="Z93" s="53"/>
-      <c r="AA93" s="53"/>
-      <c r="AB93" s="54"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="39"/>
+      <c r="J93" s="39"/>
+      <c r="K93" s="39"/>
+      <c r="L93" s="39"/>
+      <c r="M93" s="39"/>
+      <c r="N93" s="39"/>
+      <c r="O93" s="39"/>
+      <c r="P93" s="39"/>
+      <c r="Q93" s="39"/>
+      <c r="R93" s="39"/>
+      <c r="S93" s="39"/>
+      <c r="T93" s="39"/>
+      <c r="U93" s="39"/>
+      <c r="V93" s="39"/>
+      <c r="W93" s="39"/>
+      <c r="X93" s="39"/>
+      <c r="Y93" s="39"/>
+      <c r="Z93" s="39"/>
+      <c r="AA93" s="39"/>
+      <c r="AB93" s="40"/>
       <c r="AC93" s="11"/>
     </row>
     <row r="94" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4796,27 +4827,29 @@
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
-      <c r="H95" s="46"/>
-      <c r="I95" s="47"/>
-      <c r="J95" s="47"/>
-      <c r="K95" s="47"/>
-      <c r="L95" s="47"/>
-      <c r="M95" s="47"/>
-      <c r="N95" s="47"/>
-      <c r="O95" s="47"/>
-      <c r="P95" s="47"/>
-      <c r="Q95" s="47"/>
-      <c r="R95" s="47"/>
-      <c r="S95" s="47"/>
-      <c r="T95" s="47"/>
-      <c r="U95" s="47"/>
-      <c r="V95" s="47"/>
-      <c r="W95" s="47"/>
-      <c r="X95" s="47"/>
-      <c r="Y95" s="47"/>
-      <c r="Z95" s="47"/>
-      <c r="AA95" s="47"/>
-      <c r="AB95" s="48"/>
+      <c r="H95" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="I95" s="33"/>
+      <c r="J95" s="33"/>
+      <c r="K95" s="33"/>
+      <c r="L95" s="33"/>
+      <c r="M95" s="33"/>
+      <c r="N95" s="33"/>
+      <c r="O95" s="33"/>
+      <c r="P95" s="33"/>
+      <c r="Q95" s="33"/>
+      <c r="R95" s="33"/>
+      <c r="S95" s="33"/>
+      <c r="T95" s="33"/>
+      <c r="U95" s="33"/>
+      <c r="V95" s="33"/>
+      <c r="W95" s="33"/>
+      <c r="X95" s="33"/>
+      <c r="Y95" s="33"/>
+      <c r="Z95" s="33"/>
+      <c r="AA95" s="33"/>
+      <c r="AB95" s="34"/>
       <c r="AC95" s="11"/>
     </row>
     <row r="96" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4826,27 +4859,27 @@
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
-      <c r="H96" s="49"/>
-      <c r="I96" s="50"/>
-      <c r="J96" s="50"/>
-      <c r="K96" s="50"/>
-      <c r="L96" s="50"/>
-      <c r="M96" s="50"/>
-      <c r="N96" s="50"/>
-      <c r="O96" s="50"/>
-      <c r="P96" s="50"/>
-      <c r="Q96" s="50"/>
-      <c r="R96" s="50"/>
-      <c r="S96" s="50"/>
-      <c r="T96" s="50"/>
-      <c r="U96" s="50"/>
-      <c r="V96" s="50"/>
-      <c r="W96" s="50"/>
-      <c r="X96" s="50"/>
-      <c r="Y96" s="50"/>
-      <c r="Z96" s="50"/>
-      <c r="AA96" s="50"/>
-      <c r="AB96" s="51"/>
+      <c r="H96" s="35"/>
+      <c r="I96" s="36"/>
+      <c r="J96" s="36"/>
+      <c r="K96" s="36"/>
+      <c r="L96" s="36"/>
+      <c r="M96" s="36"/>
+      <c r="N96" s="36"/>
+      <c r="O96" s="36"/>
+      <c r="P96" s="36"/>
+      <c r="Q96" s="36"/>
+      <c r="R96" s="36"/>
+      <c r="S96" s="36"/>
+      <c r="T96" s="36"/>
+      <c r="U96" s="36"/>
+      <c r="V96" s="36"/>
+      <c r="W96" s="36"/>
+      <c r="X96" s="36"/>
+      <c r="Y96" s="36"/>
+      <c r="Z96" s="36"/>
+      <c r="AA96" s="36"/>
+      <c r="AB96" s="37"/>
       <c r="AC96" s="11"/>
     </row>
     <row r="97" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4856,27 +4889,27 @@
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
-      <c r="H97" s="49"/>
-      <c r="I97" s="50"/>
-      <c r="J97" s="50"/>
-      <c r="K97" s="50"/>
-      <c r="L97" s="50"/>
-      <c r="M97" s="50"/>
-      <c r="N97" s="50"/>
-      <c r="O97" s="50"/>
-      <c r="P97" s="50"/>
-      <c r="Q97" s="50"/>
-      <c r="R97" s="50"/>
-      <c r="S97" s="50"/>
-      <c r="T97" s="50"/>
-      <c r="U97" s="50"/>
-      <c r="V97" s="50"/>
-      <c r="W97" s="50"/>
-      <c r="X97" s="50"/>
-      <c r="Y97" s="50"/>
-      <c r="Z97" s="50"/>
-      <c r="AA97" s="50"/>
-      <c r="AB97" s="51"/>
+      <c r="H97" s="35"/>
+      <c r="I97" s="36"/>
+      <c r="J97" s="36"/>
+      <c r="K97" s="36"/>
+      <c r="L97" s="36"/>
+      <c r="M97" s="36"/>
+      <c r="N97" s="36"/>
+      <c r="O97" s="36"/>
+      <c r="P97" s="36"/>
+      <c r="Q97" s="36"/>
+      <c r="R97" s="36"/>
+      <c r="S97" s="36"/>
+      <c r="T97" s="36"/>
+      <c r="U97" s="36"/>
+      <c r="V97" s="36"/>
+      <c r="W97" s="36"/>
+      <c r="X97" s="36"/>
+      <c r="Y97" s="36"/>
+      <c r="Z97" s="36"/>
+      <c r="AA97" s="36"/>
+      <c r="AB97" s="37"/>
       <c r="AC97" s="11"/>
     </row>
     <row r="98" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4886,27 +4919,27 @@
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
-      <c r="H98" s="49"/>
-      <c r="I98" s="50"/>
-      <c r="J98" s="50"/>
-      <c r="K98" s="50"/>
-      <c r="L98" s="50"/>
-      <c r="M98" s="50"/>
-      <c r="N98" s="50"/>
-      <c r="O98" s="50"/>
-      <c r="P98" s="50"/>
-      <c r="Q98" s="50"/>
-      <c r="R98" s="50"/>
-      <c r="S98" s="50"/>
-      <c r="T98" s="50"/>
-      <c r="U98" s="50"/>
-      <c r="V98" s="50"/>
-      <c r="W98" s="50"/>
-      <c r="X98" s="50"/>
-      <c r="Y98" s="50"/>
-      <c r="Z98" s="50"/>
-      <c r="AA98" s="50"/>
-      <c r="AB98" s="51"/>
+      <c r="H98" s="35"/>
+      <c r="I98" s="36"/>
+      <c r="J98" s="36"/>
+      <c r="K98" s="36"/>
+      <c r="L98" s="36"/>
+      <c r="M98" s="36"/>
+      <c r="N98" s="36"/>
+      <c r="O98" s="36"/>
+      <c r="P98" s="36"/>
+      <c r="Q98" s="36"/>
+      <c r="R98" s="36"/>
+      <c r="S98" s="36"/>
+      <c r="T98" s="36"/>
+      <c r="U98" s="36"/>
+      <c r="V98" s="36"/>
+      <c r="W98" s="36"/>
+      <c r="X98" s="36"/>
+      <c r="Y98" s="36"/>
+      <c r="Z98" s="36"/>
+      <c r="AA98" s="36"/>
+      <c r="AB98" s="37"/>
       <c r="AC98" s="11"/>
     </row>
     <row r="99" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4916,27 +4949,27 @@
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
-      <c r="H99" s="49"/>
-      <c r="I99" s="50"/>
-      <c r="J99" s="50"/>
-      <c r="K99" s="50"/>
-      <c r="L99" s="50"/>
-      <c r="M99" s="50"/>
-      <c r="N99" s="50"/>
-      <c r="O99" s="50"/>
-      <c r="P99" s="50"/>
-      <c r="Q99" s="50"/>
-      <c r="R99" s="50"/>
-      <c r="S99" s="50"/>
-      <c r="T99" s="50"/>
-      <c r="U99" s="50"/>
-      <c r="V99" s="50"/>
-      <c r="W99" s="50"/>
-      <c r="X99" s="50"/>
-      <c r="Y99" s="50"/>
-      <c r="Z99" s="50"/>
-      <c r="AA99" s="50"/>
-      <c r="AB99" s="51"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="36"/>
+      <c r="J99" s="36"/>
+      <c r="K99" s="36"/>
+      <c r="L99" s="36"/>
+      <c r="M99" s="36"/>
+      <c r="N99" s="36"/>
+      <c r="O99" s="36"/>
+      <c r="P99" s="36"/>
+      <c r="Q99" s="36"/>
+      <c r="R99" s="36"/>
+      <c r="S99" s="36"/>
+      <c r="T99" s="36"/>
+      <c r="U99" s="36"/>
+      <c r="V99" s="36"/>
+      <c r="W99" s="36"/>
+      <c r="X99" s="36"/>
+      <c r="Y99" s="36"/>
+      <c r="Z99" s="36"/>
+      <c r="AA99" s="36"/>
+      <c r="AB99" s="37"/>
       <c r="AC99" s="11"/>
     </row>
     <row r="100" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4946,27 +4979,27 @@
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
-      <c r="H100" s="49"/>
-      <c r="I100" s="50"/>
-      <c r="J100" s="50"/>
-      <c r="K100" s="50"/>
-      <c r="L100" s="50"/>
-      <c r="M100" s="50"/>
-      <c r="N100" s="50"/>
-      <c r="O100" s="50"/>
-      <c r="P100" s="50"/>
-      <c r="Q100" s="50"/>
-      <c r="R100" s="50"/>
-      <c r="S100" s="50"/>
-      <c r="T100" s="50"/>
-      <c r="U100" s="50"/>
-      <c r="V100" s="50"/>
-      <c r="W100" s="50"/>
-      <c r="X100" s="50"/>
-      <c r="Y100" s="50"/>
-      <c r="Z100" s="50"/>
-      <c r="AA100" s="50"/>
-      <c r="AB100" s="51"/>
+      <c r="H100" s="35"/>
+      <c r="I100" s="36"/>
+      <c r="J100" s="36"/>
+      <c r="K100" s="36"/>
+      <c r="L100" s="36"/>
+      <c r="M100" s="36"/>
+      <c r="N100" s="36"/>
+      <c r="O100" s="36"/>
+      <c r="P100" s="36"/>
+      <c r="Q100" s="36"/>
+      <c r="R100" s="36"/>
+      <c r="S100" s="36"/>
+      <c r="T100" s="36"/>
+      <c r="U100" s="36"/>
+      <c r="V100" s="36"/>
+      <c r="W100" s="36"/>
+      <c r="X100" s="36"/>
+      <c r="Y100" s="36"/>
+      <c r="Z100" s="36"/>
+      <c r="AA100" s="36"/>
+      <c r="AB100" s="37"/>
       <c r="AC100" s="11"/>
     </row>
     <row r="101" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4976,27 +5009,27 @@
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
-      <c r="H101" s="52"/>
-      <c r="I101" s="53"/>
-      <c r="J101" s="53"/>
-      <c r="K101" s="53"/>
-      <c r="L101" s="53"/>
-      <c r="M101" s="53"/>
-      <c r="N101" s="53"/>
-      <c r="O101" s="53"/>
-      <c r="P101" s="53"/>
-      <c r="Q101" s="53"/>
-      <c r="R101" s="53"/>
-      <c r="S101" s="53"/>
-      <c r="T101" s="53"/>
-      <c r="U101" s="53"/>
-      <c r="V101" s="53"/>
-      <c r="W101" s="53"/>
-      <c r="X101" s="53"/>
-      <c r="Y101" s="53"/>
-      <c r="Z101" s="53"/>
-      <c r="AA101" s="53"/>
-      <c r="AB101" s="54"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="39"/>
+      <c r="J101" s="39"/>
+      <c r="K101" s="39"/>
+      <c r="L101" s="39"/>
+      <c r="M101" s="39"/>
+      <c r="N101" s="39"/>
+      <c r="O101" s="39"/>
+      <c r="P101" s="39"/>
+      <c r="Q101" s="39"/>
+      <c r="R101" s="39"/>
+      <c r="S101" s="39"/>
+      <c r="T101" s="39"/>
+      <c r="U101" s="39"/>
+      <c r="V101" s="39"/>
+      <c r="W101" s="39"/>
+      <c r="X101" s="39"/>
+      <c r="Y101" s="39"/>
+      <c r="Z101" s="39"/>
+      <c r="AA101" s="39"/>
+      <c r="AB101" s="40"/>
       <c r="AC101" s="11"/>
     </row>
     <row r="102" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5098,33 +5131,37 @@
     <row r="106" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="44"/>
       <c r="C106" s="5"/>
-      <c r="D106" s="41"/>
+      <c r="D106" s="41" t="s">
+        <v>65</v>
+      </c>
       <c r="E106" s="42"/>
       <c r="F106" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G106" s="6"/>
-      <c r="H106" s="46"/>
-      <c r="I106" s="47"/>
-      <c r="J106" s="47"/>
-      <c r="K106" s="47"/>
-      <c r="L106" s="47"/>
-      <c r="M106" s="47"/>
-      <c r="N106" s="47"/>
-      <c r="O106" s="47"/>
-      <c r="P106" s="47"/>
-      <c r="Q106" s="47"/>
-      <c r="R106" s="47"/>
-      <c r="S106" s="47"/>
-      <c r="T106" s="47"/>
-      <c r="U106" s="47"/>
-      <c r="V106" s="47"/>
-      <c r="W106" s="47"/>
-      <c r="X106" s="47"/>
-      <c r="Y106" s="47"/>
-      <c r="Z106" s="47"/>
-      <c r="AA106" s="47"/>
-      <c r="AB106" s="48"/>
+      <c r="H106" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="I106" s="33"/>
+      <c r="J106" s="33"/>
+      <c r="K106" s="33"/>
+      <c r="L106" s="33"/>
+      <c r="M106" s="33"/>
+      <c r="N106" s="33"/>
+      <c r="O106" s="33"/>
+      <c r="P106" s="33"/>
+      <c r="Q106" s="33"/>
+      <c r="R106" s="33"/>
+      <c r="S106" s="33"/>
+      <c r="T106" s="33"/>
+      <c r="U106" s="33"/>
+      <c r="V106" s="33"/>
+      <c r="W106" s="33"/>
+      <c r="X106" s="33"/>
+      <c r="Y106" s="33"/>
+      <c r="Z106" s="33"/>
+      <c r="AA106" s="33"/>
+      <c r="AB106" s="34"/>
       <c r="AC106" s="11"/>
     </row>
     <row r="107" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5134,27 +5171,27 @@
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
-      <c r="H107" s="49"/>
-      <c r="I107" s="50"/>
-      <c r="J107" s="50"/>
-      <c r="K107" s="50"/>
-      <c r="L107" s="50"/>
-      <c r="M107" s="50"/>
-      <c r="N107" s="50"/>
-      <c r="O107" s="50"/>
-      <c r="P107" s="50"/>
-      <c r="Q107" s="50"/>
-      <c r="R107" s="50"/>
-      <c r="S107" s="50"/>
-      <c r="T107" s="50"/>
-      <c r="U107" s="50"/>
-      <c r="V107" s="50"/>
-      <c r="W107" s="50"/>
-      <c r="X107" s="50"/>
-      <c r="Y107" s="50"/>
-      <c r="Z107" s="50"/>
-      <c r="AA107" s="50"/>
-      <c r="AB107" s="51"/>
+      <c r="H107" s="35"/>
+      <c r="I107" s="36"/>
+      <c r="J107" s="36"/>
+      <c r="K107" s="36"/>
+      <c r="L107" s="36"/>
+      <c r="M107" s="36"/>
+      <c r="N107" s="36"/>
+      <c r="O107" s="36"/>
+      <c r="P107" s="36"/>
+      <c r="Q107" s="36"/>
+      <c r="R107" s="36"/>
+      <c r="S107" s="36"/>
+      <c r="T107" s="36"/>
+      <c r="U107" s="36"/>
+      <c r="V107" s="36"/>
+      <c r="W107" s="36"/>
+      <c r="X107" s="36"/>
+      <c r="Y107" s="36"/>
+      <c r="Z107" s="36"/>
+      <c r="AA107" s="36"/>
+      <c r="AB107" s="37"/>
       <c r="AC107" s="11"/>
     </row>
     <row r="108" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5164,27 +5201,27 @@
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
-      <c r="H108" s="49"/>
-      <c r="I108" s="50"/>
-      <c r="J108" s="50"/>
-      <c r="K108" s="50"/>
-      <c r="L108" s="50"/>
-      <c r="M108" s="50"/>
-      <c r="N108" s="50"/>
-      <c r="O108" s="50"/>
-      <c r="P108" s="50"/>
-      <c r="Q108" s="50"/>
-      <c r="R108" s="50"/>
-      <c r="S108" s="50"/>
-      <c r="T108" s="50"/>
-      <c r="U108" s="50"/>
-      <c r="V108" s="50"/>
-      <c r="W108" s="50"/>
-      <c r="X108" s="50"/>
-      <c r="Y108" s="50"/>
-      <c r="Z108" s="50"/>
-      <c r="AA108" s="50"/>
-      <c r="AB108" s="51"/>
+      <c r="H108" s="35"/>
+      <c r="I108" s="36"/>
+      <c r="J108" s="36"/>
+      <c r="K108" s="36"/>
+      <c r="L108" s="36"/>
+      <c r="M108" s="36"/>
+      <c r="N108" s="36"/>
+      <c r="O108" s="36"/>
+      <c r="P108" s="36"/>
+      <c r="Q108" s="36"/>
+      <c r="R108" s="36"/>
+      <c r="S108" s="36"/>
+      <c r="T108" s="36"/>
+      <c r="U108" s="36"/>
+      <c r="V108" s="36"/>
+      <c r="W108" s="36"/>
+      <c r="X108" s="36"/>
+      <c r="Y108" s="36"/>
+      <c r="Z108" s="36"/>
+      <c r="AA108" s="36"/>
+      <c r="AB108" s="37"/>
       <c r="AC108" s="11"/>
     </row>
     <row r="109" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5194,27 +5231,27 @@
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
-      <c r="H109" s="49"/>
-      <c r="I109" s="50"/>
-      <c r="J109" s="50"/>
-      <c r="K109" s="50"/>
-      <c r="L109" s="50"/>
-      <c r="M109" s="50"/>
-      <c r="N109" s="50"/>
-      <c r="O109" s="50"/>
-      <c r="P109" s="50"/>
-      <c r="Q109" s="50"/>
-      <c r="R109" s="50"/>
-      <c r="S109" s="50"/>
-      <c r="T109" s="50"/>
-      <c r="U109" s="50"/>
-      <c r="V109" s="50"/>
-      <c r="W109" s="50"/>
-      <c r="X109" s="50"/>
-      <c r="Y109" s="50"/>
-      <c r="Z109" s="50"/>
-      <c r="AA109" s="50"/>
-      <c r="AB109" s="51"/>
+      <c r="H109" s="35"/>
+      <c r="I109" s="36"/>
+      <c r="J109" s="36"/>
+      <c r="K109" s="36"/>
+      <c r="L109" s="36"/>
+      <c r="M109" s="36"/>
+      <c r="N109" s="36"/>
+      <c r="O109" s="36"/>
+      <c r="P109" s="36"/>
+      <c r="Q109" s="36"/>
+      <c r="R109" s="36"/>
+      <c r="S109" s="36"/>
+      <c r="T109" s="36"/>
+      <c r="U109" s="36"/>
+      <c r="V109" s="36"/>
+      <c r="W109" s="36"/>
+      <c r="X109" s="36"/>
+      <c r="Y109" s="36"/>
+      <c r="Z109" s="36"/>
+      <c r="AA109" s="36"/>
+      <c r="AB109" s="37"/>
       <c r="AC109" s="11"/>
     </row>
     <row r="110" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5224,27 +5261,27 @@
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
-      <c r="H110" s="49"/>
-      <c r="I110" s="50"/>
-      <c r="J110" s="50"/>
-      <c r="K110" s="50"/>
-      <c r="L110" s="50"/>
-      <c r="M110" s="50"/>
-      <c r="N110" s="50"/>
-      <c r="O110" s="50"/>
-      <c r="P110" s="50"/>
-      <c r="Q110" s="50"/>
-      <c r="R110" s="50"/>
-      <c r="S110" s="50"/>
-      <c r="T110" s="50"/>
-      <c r="U110" s="50"/>
-      <c r="V110" s="50"/>
-      <c r="W110" s="50"/>
-      <c r="X110" s="50"/>
-      <c r="Y110" s="50"/>
-      <c r="Z110" s="50"/>
-      <c r="AA110" s="50"/>
-      <c r="AB110" s="51"/>
+      <c r="H110" s="35"/>
+      <c r="I110" s="36"/>
+      <c r="J110" s="36"/>
+      <c r="K110" s="36"/>
+      <c r="L110" s="36"/>
+      <c r="M110" s="36"/>
+      <c r="N110" s="36"/>
+      <c r="O110" s="36"/>
+      <c r="P110" s="36"/>
+      <c r="Q110" s="36"/>
+      <c r="R110" s="36"/>
+      <c r="S110" s="36"/>
+      <c r="T110" s="36"/>
+      <c r="U110" s="36"/>
+      <c r="V110" s="36"/>
+      <c r="W110" s="36"/>
+      <c r="X110" s="36"/>
+      <c r="Y110" s="36"/>
+      <c r="Z110" s="36"/>
+      <c r="AA110" s="36"/>
+      <c r="AB110" s="37"/>
       <c r="AC110" s="11"/>
     </row>
     <row r="111" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5254,27 +5291,27 @@
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
-      <c r="H111" s="49"/>
-      <c r="I111" s="50"/>
-      <c r="J111" s="50"/>
-      <c r="K111" s="50"/>
-      <c r="L111" s="50"/>
-      <c r="M111" s="50"/>
-      <c r="N111" s="50"/>
-      <c r="O111" s="50"/>
-      <c r="P111" s="50"/>
-      <c r="Q111" s="50"/>
-      <c r="R111" s="50"/>
-      <c r="S111" s="50"/>
-      <c r="T111" s="50"/>
-      <c r="U111" s="50"/>
-      <c r="V111" s="50"/>
-      <c r="W111" s="50"/>
-      <c r="X111" s="50"/>
-      <c r="Y111" s="50"/>
-      <c r="Z111" s="50"/>
-      <c r="AA111" s="50"/>
-      <c r="AB111" s="51"/>
+      <c r="H111" s="35"/>
+      <c r="I111" s="36"/>
+      <c r="J111" s="36"/>
+      <c r="K111" s="36"/>
+      <c r="L111" s="36"/>
+      <c r="M111" s="36"/>
+      <c r="N111" s="36"/>
+      <c r="O111" s="36"/>
+      <c r="P111" s="36"/>
+      <c r="Q111" s="36"/>
+      <c r="R111" s="36"/>
+      <c r="S111" s="36"/>
+      <c r="T111" s="36"/>
+      <c r="U111" s="36"/>
+      <c r="V111" s="36"/>
+      <c r="W111" s="36"/>
+      <c r="X111" s="36"/>
+      <c r="Y111" s="36"/>
+      <c r="Z111" s="36"/>
+      <c r="AA111" s="36"/>
+      <c r="AB111" s="37"/>
       <c r="AC111" s="11"/>
     </row>
     <row r="112" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5284,27 +5321,27 @@
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
-      <c r="H112" s="52"/>
-      <c r="I112" s="53"/>
-      <c r="J112" s="53"/>
-      <c r="K112" s="53"/>
-      <c r="L112" s="53"/>
-      <c r="M112" s="53"/>
-      <c r="N112" s="53"/>
-      <c r="O112" s="53"/>
-      <c r="P112" s="53"/>
-      <c r="Q112" s="53"/>
-      <c r="R112" s="53"/>
-      <c r="S112" s="53"/>
-      <c r="T112" s="53"/>
-      <c r="U112" s="53"/>
-      <c r="V112" s="53"/>
-      <c r="W112" s="53"/>
-      <c r="X112" s="53"/>
-      <c r="Y112" s="53"/>
-      <c r="Z112" s="53"/>
-      <c r="AA112" s="53"/>
-      <c r="AB112" s="54"/>
+      <c r="H112" s="38"/>
+      <c r="I112" s="39"/>
+      <c r="J112" s="39"/>
+      <c r="K112" s="39"/>
+      <c r="L112" s="39"/>
+      <c r="M112" s="39"/>
+      <c r="N112" s="39"/>
+      <c r="O112" s="39"/>
+      <c r="P112" s="39"/>
+      <c r="Q112" s="39"/>
+      <c r="R112" s="39"/>
+      <c r="S112" s="39"/>
+      <c r="T112" s="39"/>
+      <c r="U112" s="39"/>
+      <c r="V112" s="39"/>
+      <c r="W112" s="39"/>
+      <c r="X112" s="39"/>
+      <c r="Y112" s="39"/>
+      <c r="Z112" s="39"/>
+      <c r="AA112" s="39"/>
+      <c r="AB112" s="40"/>
       <c r="AC112" s="11"/>
     </row>
     <row r="113" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5346,27 +5383,29 @@
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
-      <c r="H114" s="46"/>
-      <c r="I114" s="47"/>
-      <c r="J114" s="47"/>
-      <c r="K114" s="47"/>
-      <c r="L114" s="47"/>
-      <c r="M114" s="47"/>
-      <c r="N114" s="47"/>
-      <c r="O114" s="47"/>
-      <c r="P114" s="47"/>
-      <c r="Q114" s="47"/>
-      <c r="R114" s="47"/>
-      <c r="S114" s="47"/>
-      <c r="T114" s="47"/>
-      <c r="U114" s="47"/>
-      <c r="V114" s="47"/>
-      <c r="W114" s="47"/>
-      <c r="X114" s="47"/>
-      <c r="Y114" s="47"/>
-      <c r="Z114" s="47"/>
-      <c r="AA114" s="47"/>
-      <c r="AB114" s="48"/>
+      <c r="H114" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I114" s="33"/>
+      <c r="J114" s="33"/>
+      <c r="K114" s="33"/>
+      <c r="L114" s="33"/>
+      <c r="M114" s="33"/>
+      <c r="N114" s="33"/>
+      <c r="O114" s="33"/>
+      <c r="P114" s="33"/>
+      <c r="Q114" s="33"/>
+      <c r="R114" s="33"/>
+      <c r="S114" s="33"/>
+      <c r="T114" s="33"/>
+      <c r="U114" s="33"/>
+      <c r="V114" s="33"/>
+      <c r="W114" s="33"/>
+      <c r="X114" s="33"/>
+      <c r="Y114" s="33"/>
+      <c r="Z114" s="33"/>
+      <c r="AA114" s="33"/>
+      <c r="AB114" s="34"/>
       <c r="AC114" s="11"/>
     </row>
     <row r="115" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5376,27 +5415,27 @@
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
-      <c r="H115" s="49"/>
-      <c r="I115" s="50"/>
-      <c r="J115" s="50"/>
-      <c r="K115" s="50"/>
-      <c r="L115" s="50"/>
-      <c r="M115" s="50"/>
-      <c r="N115" s="50"/>
-      <c r="O115" s="50"/>
-      <c r="P115" s="50"/>
-      <c r="Q115" s="50"/>
-      <c r="R115" s="50"/>
-      <c r="S115" s="50"/>
-      <c r="T115" s="50"/>
-      <c r="U115" s="50"/>
-      <c r="V115" s="50"/>
-      <c r="W115" s="50"/>
-      <c r="X115" s="50"/>
-      <c r="Y115" s="50"/>
-      <c r="Z115" s="50"/>
-      <c r="AA115" s="50"/>
-      <c r="AB115" s="51"/>
+      <c r="H115" s="35"/>
+      <c r="I115" s="36"/>
+      <c r="J115" s="36"/>
+      <c r="K115" s="36"/>
+      <c r="L115" s="36"/>
+      <c r="M115" s="36"/>
+      <c r="N115" s="36"/>
+      <c r="O115" s="36"/>
+      <c r="P115" s="36"/>
+      <c r="Q115" s="36"/>
+      <c r="R115" s="36"/>
+      <c r="S115" s="36"/>
+      <c r="T115" s="36"/>
+      <c r="U115" s="36"/>
+      <c r="V115" s="36"/>
+      <c r="W115" s="36"/>
+      <c r="X115" s="36"/>
+      <c r="Y115" s="36"/>
+      <c r="Z115" s="36"/>
+      <c r="AA115" s="36"/>
+      <c r="AB115" s="37"/>
       <c r="AC115" s="11"/>
     </row>
     <row r="116" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5406,27 +5445,27 @@
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
-      <c r="H116" s="49"/>
-      <c r="I116" s="50"/>
-      <c r="J116" s="50"/>
-      <c r="K116" s="50"/>
-      <c r="L116" s="50"/>
-      <c r="M116" s="50"/>
-      <c r="N116" s="50"/>
-      <c r="O116" s="50"/>
-      <c r="P116" s="50"/>
-      <c r="Q116" s="50"/>
-      <c r="R116" s="50"/>
-      <c r="S116" s="50"/>
-      <c r="T116" s="50"/>
-      <c r="U116" s="50"/>
-      <c r="V116" s="50"/>
-      <c r="W116" s="50"/>
-      <c r="X116" s="50"/>
-      <c r="Y116" s="50"/>
-      <c r="Z116" s="50"/>
-      <c r="AA116" s="50"/>
-      <c r="AB116" s="51"/>
+      <c r="H116" s="35"/>
+      <c r="I116" s="36"/>
+      <c r="J116" s="36"/>
+      <c r="K116" s="36"/>
+      <c r="L116" s="36"/>
+      <c r="M116" s="36"/>
+      <c r="N116" s="36"/>
+      <c r="O116" s="36"/>
+      <c r="P116" s="36"/>
+      <c r="Q116" s="36"/>
+      <c r="R116" s="36"/>
+      <c r="S116" s="36"/>
+      <c r="T116" s="36"/>
+      <c r="U116" s="36"/>
+      <c r="V116" s="36"/>
+      <c r="W116" s="36"/>
+      <c r="X116" s="36"/>
+      <c r="Y116" s="36"/>
+      <c r="Z116" s="36"/>
+      <c r="AA116" s="36"/>
+      <c r="AB116" s="37"/>
       <c r="AC116" s="11"/>
     </row>
     <row r="117" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5436,27 +5475,27 @@
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
-      <c r="H117" s="49"/>
-      <c r="I117" s="50"/>
-      <c r="J117" s="50"/>
-      <c r="K117" s="50"/>
-      <c r="L117" s="50"/>
-      <c r="M117" s="50"/>
-      <c r="N117" s="50"/>
-      <c r="O117" s="50"/>
-      <c r="P117" s="50"/>
-      <c r="Q117" s="50"/>
-      <c r="R117" s="50"/>
-      <c r="S117" s="50"/>
-      <c r="T117" s="50"/>
-      <c r="U117" s="50"/>
-      <c r="V117" s="50"/>
-      <c r="W117" s="50"/>
-      <c r="X117" s="50"/>
-      <c r="Y117" s="50"/>
-      <c r="Z117" s="50"/>
-      <c r="AA117" s="50"/>
-      <c r="AB117" s="51"/>
+      <c r="H117" s="35"/>
+      <c r="I117" s="36"/>
+      <c r="J117" s="36"/>
+      <c r="K117" s="36"/>
+      <c r="L117" s="36"/>
+      <c r="M117" s="36"/>
+      <c r="N117" s="36"/>
+      <c r="O117" s="36"/>
+      <c r="P117" s="36"/>
+      <c r="Q117" s="36"/>
+      <c r="R117" s="36"/>
+      <c r="S117" s="36"/>
+      <c r="T117" s="36"/>
+      <c r="U117" s="36"/>
+      <c r="V117" s="36"/>
+      <c r="W117" s="36"/>
+      <c r="X117" s="36"/>
+      <c r="Y117" s="36"/>
+      <c r="Z117" s="36"/>
+      <c r="AA117" s="36"/>
+      <c r="AB117" s="37"/>
       <c r="AC117" s="11"/>
     </row>
     <row r="118" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5466,27 +5505,27 @@
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
-      <c r="H118" s="49"/>
-      <c r="I118" s="50"/>
-      <c r="J118" s="50"/>
-      <c r="K118" s="50"/>
-      <c r="L118" s="50"/>
-      <c r="M118" s="50"/>
-      <c r="N118" s="50"/>
-      <c r="O118" s="50"/>
-      <c r="P118" s="50"/>
-      <c r="Q118" s="50"/>
-      <c r="R118" s="50"/>
-      <c r="S118" s="50"/>
-      <c r="T118" s="50"/>
-      <c r="U118" s="50"/>
-      <c r="V118" s="50"/>
-      <c r="W118" s="50"/>
-      <c r="X118" s="50"/>
-      <c r="Y118" s="50"/>
-      <c r="Z118" s="50"/>
-      <c r="AA118" s="50"/>
-      <c r="AB118" s="51"/>
+      <c r="H118" s="35"/>
+      <c r="I118" s="36"/>
+      <c r="J118" s="36"/>
+      <c r="K118" s="36"/>
+      <c r="L118" s="36"/>
+      <c r="M118" s="36"/>
+      <c r="N118" s="36"/>
+      <c r="O118" s="36"/>
+      <c r="P118" s="36"/>
+      <c r="Q118" s="36"/>
+      <c r="R118" s="36"/>
+      <c r="S118" s="36"/>
+      <c r="T118" s="36"/>
+      <c r="U118" s="36"/>
+      <c r="V118" s="36"/>
+      <c r="W118" s="36"/>
+      <c r="X118" s="36"/>
+      <c r="Y118" s="36"/>
+      <c r="Z118" s="36"/>
+      <c r="AA118" s="36"/>
+      <c r="AB118" s="37"/>
       <c r="AC118" s="11"/>
     </row>
     <row r="119" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5496,27 +5535,27 @@
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
-      <c r="H119" s="49"/>
-      <c r="I119" s="50"/>
-      <c r="J119" s="50"/>
-      <c r="K119" s="50"/>
-      <c r="L119" s="50"/>
-      <c r="M119" s="50"/>
-      <c r="N119" s="50"/>
-      <c r="O119" s="50"/>
-      <c r="P119" s="50"/>
-      <c r="Q119" s="50"/>
-      <c r="R119" s="50"/>
-      <c r="S119" s="50"/>
-      <c r="T119" s="50"/>
-      <c r="U119" s="50"/>
-      <c r="V119" s="50"/>
-      <c r="W119" s="50"/>
-      <c r="X119" s="50"/>
-      <c r="Y119" s="50"/>
-      <c r="Z119" s="50"/>
-      <c r="AA119" s="50"/>
-      <c r="AB119" s="51"/>
+      <c r="H119" s="35"/>
+      <c r="I119" s="36"/>
+      <c r="J119" s="36"/>
+      <c r="K119" s="36"/>
+      <c r="L119" s="36"/>
+      <c r="M119" s="36"/>
+      <c r="N119" s="36"/>
+      <c r="O119" s="36"/>
+      <c r="P119" s="36"/>
+      <c r="Q119" s="36"/>
+      <c r="R119" s="36"/>
+      <c r="S119" s="36"/>
+      <c r="T119" s="36"/>
+      <c r="U119" s="36"/>
+      <c r="V119" s="36"/>
+      <c r="W119" s="36"/>
+      <c r="X119" s="36"/>
+      <c r="Y119" s="36"/>
+      <c r="Z119" s="36"/>
+      <c r="AA119" s="36"/>
+      <c r="AB119" s="37"/>
       <c r="AC119" s="11"/>
     </row>
     <row r="120" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5526,27 +5565,27 @@
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
-      <c r="H120" s="52"/>
-      <c r="I120" s="53"/>
-      <c r="J120" s="53"/>
-      <c r="K120" s="53"/>
-      <c r="L120" s="53"/>
-      <c r="M120" s="53"/>
-      <c r="N120" s="53"/>
-      <c r="O120" s="53"/>
-      <c r="P120" s="53"/>
-      <c r="Q120" s="53"/>
-      <c r="R120" s="53"/>
-      <c r="S120" s="53"/>
-      <c r="T120" s="53"/>
-      <c r="U120" s="53"/>
-      <c r="V120" s="53"/>
-      <c r="W120" s="53"/>
-      <c r="X120" s="53"/>
-      <c r="Y120" s="53"/>
-      <c r="Z120" s="53"/>
-      <c r="AA120" s="53"/>
-      <c r="AB120" s="54"/>
+      <c r="H120" s="38"/>
+      <c r="I120" s="39"/>
+      <c r="J120" s="39"/>
+      <c r="K120" s="39"/>
+      <c r="L120" s="39"/>
+      <c r="M120" s="39"/>
+      <c r="N120" s="39"/>
+      <c r="O120" s="39"/>
+      <c r="P120" s="39"/>
+      <c r="Q120" s="39"/>
+      <c r="R120" s="39"/>
+      <c r="S120" s="39"/>
+      <c r="T120" s="39"/>
+      <c r="U120" s="39"/>
+      <c r="V120" s="39"/>
+      <c r="W120" s="39"/>
+      <c r="X120" s="39"/>
+      <c r="Y120" s="39"/>
+      <c r="Z120" s="39"/>
+      <c r="AA120" s="39"/>
+      <c r="AB120" s="40"/>
       <c r="AC120" s="11"/>
     </row>
     <row r="121" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5654,27 +5693,27 @@
         <v>2</v>
       </c>
       <c r="G125" s="6"/>
-      <c r="H125" s="46"/>
-      <c r="I125" s="47"/>
-      <c r="J125" s="47"/>
-      <c r="K125" s="47"/>
-      <c r="L125" s="47"/>
-      <c r="M125" s="47"/>
-      <c r="N125" s="47"/>
-      <c r="O125" s="47"/>
-      <c r="P125" s="47"/>
-      <c r="Q125" s="47"/>
-      <c r="R125" s="47"/>
-      <c r="S125" s="47"/>
-      <c r="T125" s="47"/>
-      <c r="U125" s="47"/>
-      <c r="V125" s="47"/>
-      <c r="W125" s="47"/>
-      <c r="X125" s="47"/>
-      <c r="Y125" s="47"/>
-      <c r="Z125" s="47"/>
-      <c r="AA125" s="47"/>
-      <c r="AB125" s="48"/>
+      <c r="H125" s="48"/>
+      <c r="I125" s="49"/>
+      <c r="J125" s="49"/>
+      <c r="K125" s="49"/>
+      <c r="L125" s="49"/>
+      <c r="M125" s="49"/>
+      <c r="N125" s="49"/>
+      <c r="O125" s="49"/>
+      <c r="P125" s="49"/>
+      <c r="Q125" s="49"/>
+      <c r="R125" s="49"/>
+      <c r="S125" s="49"/>
+      <c r="T125" s="49"/>
+      <c r="U125" s="49"/>
+      <c r="V125" s="49"/>
+      <c r="W125" s="49"/>
+      <c r="X125" s="49"/>
+      <c r="Y125" s="49"/>
+      <c r="Z125" s="49"/>
+      <c r="AA125" s="49"/>
+      <c r="AB125" s="50"/>
       <c r="AC125" s="11"/>
     </row>
     <row r="126" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5684,27 +5723,27 @@
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
-      <c r="H126" s="49"/>
-      <c r="I126" s="50"/>
-      <c r="J126" s="50"/>
-      <c r="K126" s="50"/>
-      <c r="L126" s="50"/>
-      <c r="M126" s="50"/>
-      <c r="N126" s="50"/>
-      <c r="O126" s="50"/>
-      <c r="P126" s="50"/>
-      <c r="Q126" s="50"/>
-      <c r="R126" s="50"/>
-      <c r="S126" s="50"/>
-      <c r="T126" s="50"/>
-      <c r="U126" s="50"/>
-      <c r="V126" s="50"/>
-      <c r="W126" s="50"/>
-      <c r="X126" s="50"/>
-      <c r="Y126" s="50"/>
-      <c r="Z126" s="50"/>
-      <c r="AA126" s="50"/>
-      <c r="AB126" s="51"/>
+      <c r="H126" s="51"/>
+      <c r="I126" s="52"/>
+      <c r="J126" s="52"/>
+      <c r="K126" s="52"/>
+      <c r="L126" s="52"/>
+      <c r="M126" s="52"/>
+      <c r="N126" s="52"/>
+      <c r="O126" s="52"/>
+      <c r="P126" s="52"/>
+      <c r="Q126" s="52"/>
+      <c r="R126" s="52"/>
+      <c r="S126" s="52"/>
+      <c r="T126" s="52"/>
+      <c r="U126" s="52"/>
+      <c r="V126" s="52"/>
+      <c r="W126" s="52"/>
+      <c r="X126" s="52"/>
+      <c r="Y126" s="52"/>
+      <c r="Z126" s="52"/>
+      <c r="AA126" s="52"/>
+      <c r="AB126" s="53"/>
       <c r="AC126" s="11"/>
     </row>
     <row r="127" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5714,27 +5753,27 @@
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
-      <c r="H127" s="49"/>
-      <c r="I127" s="50"/>
-      <c r="J127" s="50"/>
-      <c r="K127" s="50"/>
-      <c r="L127" s="50"/>
-      <c r="M127" s="50"/>
-      <c r="N127" s="50"/>
-      <c r="O127" s="50"/>
-      <c r="P127" s="50"/>
-      <c r="Q127" s="50"/>
-      <c r="R127" s="50"/>
-      <c r="S127" s="50"/>
-      <c r="T127" s="50"/>
-      <c r="U127" s="50"/>
-      <c r="V127" s="50"/>
-      <c r="W127" s="50"/>
-      <c r="X127" s="50"/>
-      <c r="Y127" s="50"/>
-      <c r="Z127" s="50"/>
-      <c r="AA127" s="50"/>
-      <c r="AB127" s="51"/>
+      <c r="H127" s="51"/>
+      <c r="I127" s="52"/>
+      <c r="J127" s="52"/>
+      <c r="K127" s="52"/>
+      <c r="L127" s="52"/>
+      <c r="M127" s="52"/>
+      <c r="N127" s="52"/>
+      <c r="O127" s="52"/>
+      <c r="P127" s="52"/>
+      <c r="Q127" s="52"/>
+      <c r="R127" s="52"/>
+      <c r="S127" s="52"/>
+      <c r="T127" s="52"/>
+      <c r="U127" s="52"/>
+      <c r="V127" s="52"/>
+      <c r="W127" s="52"/>
+      <c r="X127" s="52"/>
+      <c r="Y127" s="52"/>
+      <c r="Z127" s="52"/>
+      <c r="AA127" s="52"/>
+      <c r="AB127" s="53"/>
       <c r="AC127" s="11"/>
     </row>
     <row r="128" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5744,27 +5783,27 @@
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
-      <c r="H128" s="49"/>
-      <c r="I128" s="50"/>
-      <c r="J128" s="50"/>
-      <c r="K128" s="50"/>
-      <c r="L128" s="50"/>
-      <c r="M128" s="50"/>
-      <c r="N128" s="50"/>
-      <c r="O128" s="50"/>
-      <c r="P128" s="50"/>
-      <c r="Q128" s="50"/>
-      <c r="R128" s="50"/>
-      <c r="S128" s="50"/>
-      <c r="T128" s="50"/>
-      <c r="U128" s="50"/>
-      <c r="V128" s="50"/>
-      <c r="W128" s="50"/>
-      <c r="X128" s="50"/>
-      <c r="Y128" s="50"/>
-      <c r="Z128" s="50"/>
-      <c r="AA128" s="50"/>
-      <c r="AB128" s="51"/>
+      <c r="H128" s="51"/>
+      <c r="I128" s="52"/>
+      <c r="J128" s="52"/>
+      <c r="K128" s="52"/>
+      <c r="L128" s="52"/>
+      <c r="M128" s="52"/>
+      <c r="N128" s="52"/>
+      <c r="O128" s="52"/>
+      <c r="P128" s="52"/>
+      <c r="Q128" s="52"/>
+      <c r="R128" s="52"/>
+      <c r="S128" s="52"/>
+      <c r="T128" s="52"/>
+      <c r="U128" s="52"/>
+      <c r="V128" s="52"/>
+      <c r="W128" s="52"/>
+      <c r="X128" s="52"/>
+      <c r="Y128" s="52"/>
+      <c r="Z128" s="52"/>
+      <c r="AA128" s="52"/>
+      <c r="AB128" s="53"/>
       <c r="AC128" s="11"/>
     </row>
     <row r="129" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5774,27 +5813,27 @@
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
-      <c r="H129" s="49"/>
-      <c r="I129" s="50"/>
-      <c r="J129" s="50"/>
-      <c r="K129" s="50"/>
-      <c r="L129" s="50"/>
-      <c r="M129" s="50"/>
-      <c r="N129" s="50"/>
-      <c r="O129" s="50"/>
-      <c r="P129" s="50"/>
-      <c r="Q129" s="50"/>
-      <c r="R129" s="50"/>
-      <c r="S129" s="50"/>
-      <c r="T129" s="50"/>
-      <c r="U129" s="50"/>
-      <c r="V129" s="50"/>
-      <c r="W129" s="50"/>
-      <c r="X129" s="50"/>
-      <c r="Y129" s="50"/>
-      <c r="Z129" s="50"/>
-      <c r="AA129" s="50"/>
-      <c r="AB129" s="51"/>
+      <c r="H129" s="51"/>
+      <c r="I129" s="52"/>
+      <c r="J129" s="52"/>
+      <c r="K129" s="52"/>
+      <c r="L129" s="52"/>
+      <c r="M129" s="52"/>
+      <c r="N129" s="52"/>
+      <c r="O129" s="52"/>
+      <c r="P129" s="52"/>
+      <c r="Q129" s="52"/>
+      <c r="R129" s="52"/>
+      <c r="S129" s="52"/>
+      <c r="T129" s="52"/>
+      <c r="U129" s="52"/>
+      <c r="V129" s="52"/>
+      <c r="W129" s="52"/>
+      <c r="X129" s="52"/>
+      <c r="Y129" s="52"/>
+      <c r="Z129" s="52"/>
+      <c r="AA129" s="52"/>
+      <c r="AB129" s="53"/>
       <c r="AC129" s="11"/>
     </row>
     <row r="130" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5804,27 +5843,27 @@
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
-      <c r="H130" s="49"/>
-      <c r="I130" s="50"/>
-      <c r="J130" s="50"/>
-      <c r="K130" s="50"/>
-      <c r="L130" s="50"/>
-      <c r="M130" s="50"/>
-      <c r="N130" s="50"/>
-      <c r="O130" s="50"/>
-      <c r="P130" s="50"/>
-      <c r="Q130" s="50"/>
-      <c r="R130" s="50"/>
-      <c r="S130" s="50"/>
-      <c r="T130" s="50"/>
-      <c r="U130" s="50"/>
-      <c r="V130" s="50"/>
-      <c r="W130" s="50"/>
-      <c r="X130" s="50"/>
-      <c r="Y130" s="50"/>
-      <c r="Z130" s="50"/>
-      <c r="AA130" s="50"/>
-      <c r="AB130" s="51"/>
+      <c r="H130" s="51"/>
+      <c r="I130" s="52"/>
+      <c r="J130" s="52"/>
+      <c r="K130" s="52"/>
+      <c r="L130" s="52"/>
+      <c r="M130" s="52"/>
+      <c r="N130" s="52"/>
+      <c r="O130" s="52"/>
+      <c r="P130" s="52"/>
+      <c r="Q130" s="52"/>
+      <c r="R130" s="52"/>
+      <c r="S130" s="52"/>
+      <c r="T130" s="52"/>
+      <c r="U130" s="52"/>
+      <c r="V130" s="52"/>
+      <c r="W130" s="52"/>
+      <c r="X130" s="52"/>
+      <c r="Y130" s="52"/>
+      <c r="Z130" s="52"/>
+      <c r="AA130" s="52"/>
+      <c r="AB130" s="53"/>
       <c r="AC130" s="11"/>
     </row>
     <row r="131" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5834,27 +5873,27 @@
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
-      <c r="H131" s="52"/>
-      <c r="I131" s="53"/>
-      <c r="J131" s="53"/>
-      <c r="K131" s="53"/>
-      <c r="L131" s="53"/>
-      <c r="M131" s="53"/>
-      <c r="N131" s="53"/>
-      <c r="O131" s="53"/>
-      <c r="P131" s="53"/>
-      <c r="Q131" s="53"/>
-      <c r="R131" s="53"/>
-      <c r="S131" s="53"/>
-      <c r="T131" s="53"/>
-      <c r="U131" s="53"/>
-      <c r="V131" s="53"/>
-      <c r="W131" s="53"/>
-      <c r="X131" s="53"/>
-      <c r="Y131" s="53"/>
-      <c r="Z131" s="53"/>
-      <c r="AA131" s="53"/>
-      <c r="AB131" s="54"/>
+      <c r="H131" s="54"/>
+      <c r="I131" s="55"/>
+      <c r="J131" s="55"/>
+      <c r="K131" s="55"/>
+      <c r="L131" s="55"/>
+      <c r="M131" s="55"/>
+      <c r="N131" s="55"/>
+      <c r="O131" s="55"/>
+      <c r="P131" s="55"/>
+      <c r="Q131" s="55"/>
+      <c r="R131" s="55"/>
+      <c r="S131" s="55"/>
+      <c r="T131" s="55"/>
+      <c r="U131" s="55"/>
+      <c r="V131" s="55"/>
+      <c r="W131" s="55"/>
+      <c r="X131" s="55"/>
+      <c r="Y131" s="55"/>
+      <c r="Z131" s="55"/>
+      <c r="AA131" s="55"/>
+      <c r="AB131" s="56"/>
       <c r="AC131" s="11"/>
     </row>
     <row r="132" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5896,27 +5935,27 @@
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="46"/>
-      <c r="I133" s="47"/>
-      <c r="J133" s="47"/>
-      <c r="K133" s="47"/>
-      <c r="L133" s="47"/>
-      <c r="M133" s="47"/>
-      <c r="N133" s="47"/>
-      <c r="O133" s="47"/>
-      <c r="P133" s="47"/>
-      <c r="Q133" s="47"/>
-      <c r="R133" s="47"/>
-      <c r="S133" s="47"/>
-      <c r="T133" s="47"/>
-      <c r="U133" s="47"/>
-      <c r="V133" s="47"/>
-      <c r="W133" s="47"/>
-      <c r="X133" s="47"/>
-      <c r="Y133" s="47"/>
-      <c r="Z133" s="47"/>
-      <c r="AA133" s="47"/>
-      <c r="AB133" s="48"/>
+      <c r="H133" s="48"/>
+      <c r="I133" s="49"/>
+      <c r="J133" s="49"/>
+      <c r="K133" s="49"/>
+      <c r="L133" s="49"/>
+      <c r="M133" s="49"/>
+      <c r="N133" s="49"/>
+      <c r="O133" s="49"/>
+      <c r="P133" s="49"/>
+      <c r="Q133" s="49"/>
+      <c r="R133" s="49"/>
+      <c r="S133" s="49"/>
+      <c r="T133" s="49"/>
+      <c r="U133" s="49"/>
+      <c r="V133" s="49"/>
+      <c r="W133" s="49"/>
+      <c r="X133" s="49"/>
+      <c r="Y133" s="49"/>
+      <c r="Z133" s="49"/>
+      <c r="AA133" s="49"/>
+      <c r="AB133" s="50"/>
       <c r="AC133" s="11"/>
     </row>
     <row r="134" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5926,27 +5965,27 @@
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="49"/>
-      <c r="I134" s="50"/>
-      <c r="J134" s="50"/>
-      <c r="K134" s="50"/>
-      <c r="L134" s="50"/>
-      <c r="M134" s="50"/>
-      <c r="N134" s="50"/>
-      <c r="O134" s="50"/>
-      <c r="P134" s="50"/>
-      <c r="Q134" s="50"/>
-      <c r="R134" s="50"/>
-      <c r="S134" s="50"/>
-      <c r="T134" s="50"/>
-      <c r="U134" s="50"/>
-      <c r="V134" s="50"/>
-      <c r="W134" s="50"/>
-      <c r="X134" s="50"/>
-      <c r="Y134" s="50"/>
-      <c r="Z134" s="50"/>
-      <c r="AA134" s="50"/>
-      <c r="AB134" s="51"/>
+      <c r="H134" s="51"/>
+      <c r="I134" s="52"/>
+      <c r="J134" s="52"/>
+      <c r="K134" s="52"/>
+      <c r="L134" s="52"/>
+      <c r="M134" s="52"/>
+      <c r="N134" s="52"/>
+      <c r="O134" s="52"/>
+      <c r="P134" s="52"/>
+      <c r="Q134" s="52"/>
+      <c r="R134" s="52"/>
+      <c r="S134" s="52"/>
+      <c r="T134" s="52"/>
+      <c r="U134" s="52"/>
+      <c r="V134" s="52"/>
+      <c r="W134" s="52"/>
+      <c r="X134" s="52"/>
+      <c r="Y134" s="52"/>
+      <c r="Z134" s="52"/>
+      <c r="AA134" s="52"/>
+      <c r="AB134" s="53"/>
       <c r="AC134" s="11"/>
     </row>
     <row r="135" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5956,27 +5995,27 @@
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="49"/>
-      <c r="I135" s="50"/>
-      <c r="J135" s="50"/>
-      <c r="K135" s="50"/>
-      <c r="L135" s="50"/>
-      <c r="M135" s="50"/>
-      <c r="N135" s="50"/>
-      <c r="O135" s="50"/>
-      <c r="P135" s="50"/>
-      <c r="Q135" s="50"/>
-      <c r="R135" s="50"/>
-      <c r="S135" s="50"/>
-      <c r="T135" s="50"/>
-      <c r="U135" s="50"/>
-      <c r="V135" s="50"/>
-      <c r="W135" s="50"/>
-      <c r="X135" s="50"/>
-      <c r="Y135" s="50"/>
-      <c r="Z135" s="50"/>
-      <c r="AA135" s="50"/>
-      <c r="AB135" s="51"/>
+      <c r="H135" s="51"/>
+      <c r="I135" s="52"/>
+      <c r="J135" s="52"/>
+      <c r="K135" s="52"/>
+      <c r="L135" s="52"/>
+      <c r="M135" s="52"/>
+      <c r="N135" s="52"/>
+      <c r="O135" s="52"/>
+      <c r="P135" s="52"/>
+      <c r="Q135" s="52"/>
+      <c r="R135" s="52"/>
+      <c r="S135" s="52"/>
+      <c r="T135" s="52"/>
+      <c r="U135" s="52"/>
+      <c r="V135" s="52"/>
+      <c r="W135" s="52"/>
+      <c r="X135" s="52"/>
+      <c r="Y135" s="52"/>
+      <c r="Z135" s="52"/>
+      <c r="AA135" s="52"/>
+      <c r="AB135" s="53"/>
       <c r="AC135" s="11"/>
     </row>
     <row r="136" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5986,27 +6025,27 @@
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="49"/>
-      <c r="I136" s="50"/>
-      <c r="J136" s="50"/>
-      <c r="K136" s="50"/>
-      <c r="L136" s="50"/>
-      <c r="M136" s="50"/>
-      <c r="N136" s="50"/>
-      <c r="O136" s="50"/>
-      <c r="P136" s="50"/>
-      <c r="Q136" s="50"/>
-      <c r="R136" s="50"/>
-      <c r="S136" s="50"/>
-      <c r="T136" s="50"/>
-      <c r="U136" s="50"/>
-      <c r="V136" s="50"/>
-      <c r="W136" s="50"/>
-      <c r="X136" s="50"/>
-      <c r="Y136" s="50"/>
-      <c r="Z136" s="50"/>
-      <c r="AA136" s="50"/>
-      <c r="AB136" s="51"/>
+      <c r="H136" s="51"/>
+      <c r="I136" s="52"/>
+      <c r="J136" s="52"/>
+      <c r="K136" s="52"/>
+      <c r="L136" s="52"/>
+      <c r="M136" s="52"/>
+      <c r="N136" s="52"/>
+      <c r="O136" s="52"/>
+      <c r="P136" s="52"/>
+      <c r="Q136" s="52"/>
+      <c r="R136" s="52"/>
+      <c r="S136" s="52"/>
+      <c r="T136" s="52"/>
+      <c r="U136" s="52"/>
+      <c r="V136" s="52"/>
+      <c r="W136" s="52"/>
+      <c r="X136" s="52"/>
+      <c r="Y136" s="52"/>
+      <c r="Z136" s="52"/>
+      <c r="AA136" s="52"/>
+      <c r="AB136" s="53"/>
       <c r="AC136" s="11"/>
     </row>
     <row r="137" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6016,27 +6055,27 @@
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
-      <c r="H137" s="49"/>
-      <c r="I137" s="50"/>
-      <c r="J137" s="50"/>
-      <c r="K137" s="50"/>
-      <c r="L137" s="50"/>
-      <c r="M137" s="50"/>
-      <c r="N137" s="50"/>
-      <c r="O137" s="50"/>
-      <c r="P137" s="50"/>
-      <c r="Q137" s="50"/>
-      <c r="R137" s="50"/>
-      <c r="S137" s="50"/>
-      <c r="T137" s="50"/>
-      <c r="U137" s="50"/>
-      <c r="V137" s="50"/>
-      <c r="W137" s="50"/>
-      <c r="X137" s="50"/>
-      <c r="Y137" s="50"/>
-      <c r="Z137" s="50"/>
-      <c r="AA137" s="50"/>
-      <c r="AB137" s="51"/>
+      <c r="H137" s="51"/>
+      <c r="I137" s="52"/>
+      <c r="J137" s="52"/>
+      <c r="K137" s="52"/>
+      <c r="L137" s="52"/>
+      <c r="M137" s="52"/>
+      <c r="N137" s="52"/>
+      <c r="O137" s="52"/>
+      <c r="P137" s="52"/>
+      <c r="Q137" s="52"/>
+      <c r="R137" s="52"/>
+      <c r="S137" s="52"/>
+      <c r="T137" s="52"/>
+      <c r="U137" s="52"/>
+      <c r="V137" s="52"/>
+      <c r="W137" s="52"/>
+      <c r="X137" s="52"/>
+      <c r="Y137" s="52"/>
+      <c r="Z137" s="52"/>
+      <c r="AA137" s="52"/>
+      <c r="AB137" s="53"/>
       <c r="AC137" s="11"/>
     </row>
     <row r="138" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6046,27 +6085,27 @@
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
       <c r="G138" s="6"/>
-      <c r="H138" s="49"/>
-      <c r="I138" s="50"/>
-      <c r="J138" s="50"/>
-      <c r="K138" s="50"/>
-      <c r="L138" s="50"/>
-      <c r="M138" s="50"/>
-      <c r="N138" s="50"/>
-      <c r="O138" s="50"/>
-      <c r="P138" s="50"/>
-      <c r="Q138" s="50"/>
-      <c r="R138" s="50"/>
-      <c r="S138" s="50"/>
-      <c r="T138" s="50"/>
-      <c r="U138" s="50"/>
-      <c r="V138" s="50"/>
-      <c r="W138" s="50"/>
-      <c r="X138" s="50"/>
-      <c r="Y138" s="50"/>
-      <c r="Z138" s="50"/>
-      <c r="AA138" s="50"/>
-      <c r="AB138" s="51"/>
+      <c r="H138" s="51"/>
+      <c r="I138" s="52"/>
+      <c r="J138" s="52"/>
+      <c r="K138" s="52"/>
+      <c r="L138" s="52"/>
+      <c r="M138" s="52"/>
+      <c r="N138" s="52"/>
+      <c r="O138" s="52"/>
+      <c r="P138" s="52"/>
+      <c r="Q138" s="52"/>
+      <c r="R138" s="52"/>
+      <c r="S138" s="52"/>
+      <c r="T138" s="52"/>
+      <c r="U138" s="52"/>
+      <c r="V138" s="52"/>
+      <c r="W138" s="52"/>
+      <c r="X138" s="52"/>
+      <c r="Y138" s="52"/>
+      <c r="Z138" s="52"/>
+      <c r="AA138" s="52"/>
+      <c r="AB138" s="53"/>
       <c r="AC138" s="11"/>
     </row>
     <row r="139" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6076,27 +6115,27 @@
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
-      <c r="H139" s="52"/>
-      <c r="I139" s="53"/>
-      <c r="J139" s="53"/>
-      <c r="K139" s="53"/>
-      <c r="L139" s="53"/>
-      <c r="M139" s="53"/>
-      <c r="N139" s="53"/>
-      <c r="O139" s="53"/>
-      <c r="P139" s="53"/>
-      <c r="Q139" s="53"/>
-      <c r="R139" s="53"/>
-      <c r="S139" s="53"/>
-      <c r="T139" s="53"/>
-      <c r="U139" s="53"/>
-      <c r="V139" s="53"/>
-      <c r="W139" s="53"/>
-      <c r="X139" s="53"/>
-      <c r="Y139" s="53"/>
-      <c r="Z139" s="53"/>
-      <c r="AA139" s="53"/>
-      <c r="AB139" s="54"/>
+      <c r="H139" s="54"/>
+      <c r="I139" s="55"/>
+      <c r="J139" s="55"/>
+      <c r="K139" s="55"/>
+      <c r="L139" s="55"/>
+      <c r="M139" s="55"/>
+      <c r="N139" s="55"/>
+      <c r="O139" s="55"/>
+      <c r="P139" s="55"/>
+      <c r="Q139" s="55"/>
+      <c r="R139" s="55"/>
+      <c r="S139" s="55"/>
+      <c r="T139" s="55"/>
+      <c r="U139" s="55"/>
+      <c r="V139" s="55"/>
+      <c r="W139" s="55"/>
+      <c r="X139" s="55"/>
+      <c r="Y139" s="55"/>
+      <c r="Z139" s="55"/>
+      <c r="AA139" s="55"/>
+      <c r="AB139" s="56"/>
       <c r="AC139" s="11"/>
     </row>
     <row r="140" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6204,27 +6243,27 @@
         <v>2</v>
       </c>
       <c r="G144" s="6"/>
-      <c r="H144" s="46"/>
-      <c r="I144" s="47"/>
-      <c r="J144" s="47"/>
-      <c r="K144" s="47"/>
-      <c r="L144" s="47"/>
-      <c r="M144" s="47"/>
-      <c r="N144" s="47"/>
-      <c r="O144" s="47"/>
-      <c r="P144" s="47"/>
-      <c r="Q144" s="47"/>
-      <c r="R144" s="47"/>
-      <c r="S144" s="47"/>
-      <c r="T144" s="47"/>
-      <c r="U144" s="47"/>
-      <c r="V144" s="47"/>
-      <c r="W144" s="47"/>
-      <c r="X144" s="47"/>
-      <c r="Y144" s="47"/>
-      <c r="Z144" s="47"/>
-      <c r="AA144" s="47"/>
-      <c r="AB144" s="48"/>
+      <c r="H144" s="48"/>
+      <c r="I144" s="49"/>
+      <c r="J144" s="49"/>
+      <c r="K144" s="49"/>
+      <c r="L144" s="49"/>
+      <c r="M144" s="49"/>
+      <c r="N144" s="49"/>
+      <c r="O144" s="49"/>
+      <c r="P144" s="49"/>
+      <c r="Q144" s="49"/>
+      <c r="R144" s="49"/>
+      <c r="S144" s="49"/>
+      <c r="T144" s="49"/>
+      <c r="U144" s="49"/>
+      <c r="V144" s="49"/>
+      <c r="W144" s="49"/>
+      <c r="X144" s="49"/>
+      <c r="Y144" s="49"/>
+      <c r="Z144" s="49"/>
+      <c r="AA144" s="49"/>
+      <c r="AB144" s="50"/>
       <c r="AC144" s="11"/>
     </row>
     <row r="145" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6234,27 +6273,27 @@
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
-      <c r="H145" s="49"/>
-      <c r="I145" s="50"/>
-      <c r="J145" s="50"/>
-      <c r="K145" s="50"/>
-      <c r="L145" s="50"/>
-      <c r="M145" s="50"/>
-      <c r="N145" s="50"/>
-      <c r="O145" s="50"/>
-      <c r="P145" s="50"/>
-      <c r="Q145" s="50"/>
-      <c r="R145" s="50"/>
-      <c r="S145" s="50"/>
-      <c r="T145" s="50"/>
-      <c r="U145" s="50"/>
-      <c r="V145" s="50"/>
-      <c r="W145" s="50"/>
-      <c r="X145" s="50"/>
-      <c r="Y145" s="50"/>
-      <c r="Z145" s="50"/>
-      <c r="AA145" s="50"/>
-      <c r="AB145" s="51"/>
+      <c r="H145" s="51"/>
+      <c r="I145" s="52"/>
+      <c r="J145" s="52"/>
+      <c r="K145" s="52"/>
+      <c r="L145" s="52"/>
+      <c r="M145" s="52"/>
+      <c r="N145" s="52"/>
+      <c r="O145" s="52"/>
+      <c r="P145" s="52"/>
+      <c r="Q145" s="52"/>
+      <c r="R145" s="52"/>
+      <c r="S145" s="52"/>
+      <c r="T145" s="52"/>
+      <c r="U145" s="52"/>
+      <c r="V145" s="52"/>
+      <c r="W145" s="52"/>
+      <c r="X145" s="52"/>
+      <c r="Y145" s="52"/>
+      <c r="Z145" s="52"/>
+      <c r="AA145" s="52"/>
+      <c r="AB145" s="53"/>
       <c r="AC145" s="11"/>
     </row>
     <row r="146" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6264,27 +6303,27 @@
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
-      <c r="H146" s="49"/>
-      <c r="I146" s="50"/>
-      <c r="J146" s="50"/>
-      <c r="K146" s="50"/>
-      <c r="L146" s="50"/>
-      <c r="M146" s="50"/>
-      <c r="N146" s="50"/>
-      <c r="O146" s="50"/>
-      <c r="P146" s="50"/>
-      <c r="Q146" s="50"/>
-      <c r="R146" s="50"/>
-      <c r="S146" s="50"/>
-      <c r="T146" s="50"/>
-      <c r="U146" s="50"/>
-      <c r="V146" s="50"/>
-      <c r="W146" s="50"/>
-      <c r="X146" s="50"/>
-      <c r="Y146" s="50"/>
-      <c r="Z146" s="50"/>
-      <c r="AA146" s="50"/>
-      <c r="AB146" s="51"/>
+      <c r="H146" s="51"/>
+      <c r="I146" s="52"/>
+      <c r="J146" s="52"/>
+      <c r="K146" s="52"/>
+      <c r="L146" s="52"/>
+      <c r="M146" s="52"/>
+      <c r="N146" s="52"/>
+      <c r="O146" s="52"/>
+      <c r="P146" s="52"/>
+      <c r="Q146" s="52"/>
+      <c r="R146" s="52"/>
+      <c r="S146" s="52"/>
+      <c r="T146" s="52"/>
+      <c r="U146" s="52"/>
+      <c r="V146" s="52"/>
+      <c r="W146" s="52"/>
+      <c r="X146" s="52"/>
+      <c r="Y146" s="52"/>
+      <c r="Z146" s="52"/>
+      <c r="AA146" s="52"/>
+      <c r="AB146" s="53"/>
       <c r="AC146" s="11"/>
     </row>
     <row r="147" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6294,27 +6333,27 @@
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
-      <c r="H147" s="49"/>
-      <c r="I147" s="50"/>
-      <c r="J147" s="50"/>
-      <c r="K147" s="50"/>
-      <c r="L147" s="50"/>
-      <c r="M147" s="50"/>
-      <c r="N147" s="50"/>
-      <c r="O147" s="50"/>
-      <c r="P147" s="50"/>
-      <c r="Q147" s="50"/>
-      <c r="R147" s="50"/>
-      <c r="S147" s="50"/>
-      <c r="T147" s="50"/>
-      <c r="U147" s="50"/>
-      <c r="V147" s="50"/>
-      <c r="W147" s="50"/>
-      <c r="X147" s="50"/>
-      <c r="Y147" s="50"/>
-      <c r="Z147" s="50"/>
-      <c r="AA147" s="50"/>
-      <c r="AB147" s="51"/>
+      <c r="H147" s="51"/>
+      <c r="I147" s="52"/>
+      <c r="J147" s="52"/>
+      <c r="K147" s="52"/>
+      <c r="L147" s="52"/>
+      <c r="M147" s="52"/>
+      <c r="N147" s="52"/>
+      <c r="O147" s="52"/>
+      <c r="P147" s="52"/>
+      <c r="Q147" s="52"/>
+      <c r="R147" s="52"/>
+      <c r="S147" s="52"/>
+      <c r="T147" s="52"/>
+      <c r="U147" s="52"/>
+      <c r="V147" s="52"/>
+      <c r="W147" s="52"/>
+      <c r="X147" s="52"/>
+      <c r="Y147" s="52"/>
+      <c r="Z147" s="52"/>
+      <c r="AA147" s="52"/>
+      <c r="AB147" s="53"/>
       <c r="AC147" s="11"/>
     </row>
     <row r="148" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6324,27 +6363,27 @@
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
-      <c r="H148" s="49"/>
-      <c r="I148" s="50"/>
-      <c r="J148" s="50"/>
-      <c r="K148" s="50"/>
-      <c r="L148" s="50"/>
-      <c r="M148" s="50"/>
-      <c r="N148" s="50"/>
-      <c r="O148" s="50"/>
-      <c r="P148" s="50"/>
-      <c r="Q148" s="50"/>
-      <c r="R148" s="50"/>
-      <c r="S148" s="50"/>
-      <c r="T148" s="50"/>
-      <c r="U148" s="50"/>
-      <c r="V148" s="50"/>
-      <c r="W148" s="50"/>
-      <c r="X148" s="50"/>
-      <c r="Y148" s="50"/>
-      <c r="Z148" s="50"/>
-      <c r="AA148" s="50"/>
-      <c r="AB148" s="51"/>
+      <c r="H148" s="51"/>
+      <c r="I148" s="52"/>
+      <c r="J148" s="52"/>
+      <c r="K148" s="52"/>
+      <c r="L148" s="52"/>
+      <c r="M148" s="52"/>
+      <c r="N148" s="52"/>
+      <c r="O148" s="52"/>
+      <c r="P148" s="52"/>
+      <c r="Q148" s="52"/>
+      <c r="R148" s="52"/>
+      <c r="S148" s="52"/>
+      <c r="T148" s="52"/>
+      <c r="U148" s="52"/>
+      <c r="V148" s="52"/>
+      <c r="W148" s="52"/>
+      <c r="X148" s="52"/>
+      <c r="Y148" s="52"/>
+      <c r="Z148" s="52"/>
+      <c r="AA148" s="52"/>
+      <c r="AB148" s="53"/>
       <c r="AC148" s="11"/>
     </row>
     <row r="149" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6354,27 +6393,27 @@
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
-      <c r="H149" s="49"/>
-      <c r="I149" s="50"/>
-      <c r="J149" s="50"/>
-      <c r="K149" s="50"/>
-      <c r="L149" s="50"/>
-      <c r="M149" s="50"/>
-      <c r="N149" s="50"/>
-      <c r="O149" s="50"/>
-      <c r="P149" s="50"/>
-      <c r="Q149" s="50"/>
-      <c r="R149" s="50"/>
-      <c r="S149" s="50"/>
-      <c r="T149" s="50"/>
-      <c r="U149" s="50"/>
-      <c r="V149" s="50"/>
-      <c r="W149" s="50"/>
-      <c r="X149" s="50"/>
-      <c r="Y149" s="50"/>
-      <c r="Z149" s="50"/>
-      <c r="AA149" s="50"/>
-      <c r="AB149" s="51"/>
+      <c r="H149" s="51"/>
+      <c r="I149" s="52"/>
+      <c r="J149" s="52"/>
+      <c r="K149" s="52"/>
+      <c r="L149" s="52"/>
+      <c r="M149" s="52"/>
+      <c r="N149" s="52"/>
+      <c r="O149" s="52"/>
+      <c r="P149" s="52"/>
+      <c r="Q149" s="52"/>
+      <c r="R149" s="52"/>
+      <c r="S149" s="52"/>
+      <c r="T149" s="52"/>
+      <c r="U149" s="52"/>
+      <c r="V149" s="52"/>
+      <c r="W149" s="52"/>
+      <c r="X149" s="52"/>
+      <c r="Y149" s="52"/>
+      <c r="Z149" s="52"/>
+      <c r="AA149" s="52"/>
+      <c r="AB149" s="53"/>
       <c r="AC149" s="11"/>
     </row>
     <row r="150" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6384,27 +6423,27 @@
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
-      <c r="H150" s="52"/>
-      <c r="I150" s="53"/>
-      <c r="J150" s="53"/>
-      <c r="K150" s="53"/>
-      <c r="L150" s="53"/>
-      <c r="M150" s="53"/>
-      <c r="N150" s="53"/>
-      <c r="O150" s="53"/>
-      <c r="P150" s="53"/>
-      <c r="Q150" s="53"/>
-      <c r="R150" s="53"/>
-      <c r="S150" s="53"/>
-      <c r="T150" s="53"/>
-      <c r="U150" s="53"/>
-      <c r="V150" s="53"/>
-      <c r="W150" s="53"/>
-      <c r="X150" s="53"/>
-      <c r="Y150" s="53"/>
-      <c r="Z150" s="53"/>
-      <c r="AA150" s="53"/>
-      <c r="AB150" s="54"/>
+      <c r="H150" s="54"/>
+      <c r="I150" s="55"/>
+      <c r="J150" s="55"/>
+      <c r="K150" s="55"/>
+      <c r="L150" s="55"/>
+      <c r="M150" s="55"/>
+      <c r="N150" s="55"/>
+      <c r="O150" s="55"/>
+      <c r="P150" s="55"/>
+      <c r="Q150" s="55"/>
+      <c r="R150" s="55"/>
+      <c r="S150" s="55"/>
+      <c r="T150" s="55"/>
+      <c r="U150" s="55"/>
+      <c r="V150" s="55"/>
+      <c r="W150" s="55"/>
+      <c r="X150" s="55"/>
+      <c r="Y150" s="55"/>
+      <c r="Z150" s="55"/>
+      <c r="AA150" s="55"/>
+      <c r="AB150" s="56"/>
       <c r="AC150" s="11"/>
     </row>
     <row r="151" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6446,27 +6485,27 @@
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
-      <c r="H152" s="46"/>
-      <c r="I152" s="47"/>
-      <c r="J152" s="47"/>
-      <c r="K152" s="47"/>
-      <c r="L152" s="47"/>
-      <c r="M152" s="47"/>
-      <c r="N152" s="47"/>
-      <c r="O152" s="47"/>
-      <c r="P152" s="47"/>
-      <c r="Q152" s="47"/>
-      <c r="R152" s="47"/>
-      <c r="S152" s="47"/>
-      <c r="T152" s="47"/>
-      <c r="U152" s="47"/>
-      <c r="V152" s="47"/>
-      <c r="W152" s="47"/>
-      <c r="X152" s="47"/>
-      <c r="Y152" s="47"/>
-      <c r="Z152" s="47"/>
-      <c r="AA152" s="47"/>
-      <c r="AB152" s="48"/>
+      <c r="H152" s="48"/>
+      <c r="I152" s="49"/>
+      <c r="J152" s="49"/>
+      <c r="K152" s="49"/>
+      <c r="L152" s="49"/>
+      <c r="M152" s="49"/>
+      <c r="N152" s="49"/>
+      <c r="O152" s="49"/>
+      <c r="P152" s="49"/>
+      <c r="Q152" s="49"/>
+      <c r="R152" s="49"/>
+      <c r="S152" s="49"/>
+      <c r="T152" s="49"/>
+      <c r="U152" s="49"/>
+      <c r="V152" s="49"/>
+      <c r="W152" s="49"/>
+      <c r="X152" s="49"/>
+      <c r="Y152" s="49"/>
+      <c r="Z152" s="49"/>
+      <c r="AA152" s="49"/>
+      <c r="AB152" s="50"/>
       <c r="AC152" s="11"/>
     </row>
     <row r="153" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6476,27 +6515,27 @@
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
-      <c r="H153" s="49"/>
-      <c r="I153" s="50"/>
-      <c r="J153" s="50"/>
-      <c r="K153" s="50"/>
-      <c r="L153" s="50"/>
-      <c r="M153" s="50"/>
-      <c r="N153" s="50"/>
-      <c r="O153" s="50"/>
-      <c r="P153" s="50"/>
-      <c r="Q153" s="50"/>
-      <c r="R153" s="50"/>
-      <c r="S153" s="50"/>
-      <c r="T153" s="50"/>
-      <c r="U153" s="50"/>
-      <c r="V153" s="50"/>
-      <c r="W153" s="50"/>
-      <c r="X153" s="50"/>
-      <c r="Y153" s="50"/>
-      <c r="Z153" s="50"/>
-      <c r="AA153" s="50"/>
-      <c r="AB153" s="51"/>
+      <c r="H153" s="51"/>
+      <c r="I153" s="52"/>
+      <c r="J153" s="52"/>
+      <c r="K153" s="52"/>
+      <c r="L153" s="52"/>
+      <c r="M153" s="52"/>
+      <c r="N153" s="52"/>
+      <c r="O153" s="52"/>
+      <c r="P153" s="52"/>
+      <c r="Q153" s="52"/>
+      <c r="R153" s="52"/>
+      <c r="S153" s="52"/>
+      <c r="T153" s="52"/>
+      <c r="U153" s="52"/>
+      <c r="V153" s="52"/>
+      <c r="W153" s="52"/>
+      <c r="X153" s="52"/>
+      <c r="Y153" s="52"/>
+      <c r="Z153" s="52"/>
+      <c r="AA153" s="52"/>
+      <c r="AB153" s="53"/>
       <c r="AC153" s="11"/>
     </row>
     <row r="154" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6506,27 +6545,27 @@
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
-      <c r="H154" s="49"/>
-      <c r="I154" s="50"/>
-      <c r="J154" s="50"/>
-      <c r="K154" s="50"/>
-      <c r="L154" s="50"/>
-      <c r="M154" s="50"/>
-      <c r="N154" s="50"/>
-      <c r="O154" s="50"/>
-      <c r="P154" s="50"/>
-      <c r="Q154" s="50"/>
-      <c r="R154" s="50"/>
-      <c r="S154" s="50"/>
-      <c r="T154" s="50"/>
-      <c r="U154" s="50"/>
-      <c r="V154" s="50"/>
-      <c r="W154" s="50"/>
-      <c r="X154" s="50"/>
-      <c r="Y154" s="50"/>
-      <c r="Z154" s="50"/>
-      <c r="AA154" s="50"/>
-      <c r="AB154" s="51"/>
+      <c r="H154" s="51"/>
+      <c r="I154" s="52"/>
+      <c r="J154" s="52"/>
+      <c r="K154" s="52"/>
+      <c r="L154" s="52"/>
+      <c r="M154" s="52"/>
+      <c r="N154" s="52"/>
+      <c r="O154" s="52"/>
+      <c r="P154" s="52"/>
+      <c r="Q154" s="52"/>
+      <c r="R154" s="52"/>
+      <c r="S154" s="52"/>
+      <c r="T154" s="52"/>
+      <c r="U154" s="52"/>
+      <c r="V154" s="52"/>
+      <c r="W154" s="52"/>
+      <c r="X154" s="52"/>
+      <c r="Y154" s="52"/>
+      <c r="Z154" s="52"/>
+      <c r="AA154" s="52"/>
+      <c r="AB154" s="53"/>
       <c r="AC154" s="11"/>
     </row>
     <row r="155" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6536,27 +6575,27 @@
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
-      <c r="H155" s="49"/>
-      <c r="I155" s="50"/>
-      <c r="J155" s="50"/>
-      <c r="K155" s="50"/>
-      <c r="L155" s="50"/>
-      <c r="M155" s="50"/>
-      <c r="N155" s="50"/>
-      <c r="O155" s="50"/>
-      <c r="P155" s="50"/>
-      <c r="Q155" s="50"/>
-      <c r="R155" s="50"/>
-      <c r="S155" s="50"/>
-      <c r="T155" s="50"/>
-      <c r="U155" s="50"/>
-      <c r="V155" s="50"/>
-      <c r="W155" s="50"/>
-      <c r="X155" s="50"/>
-      <c r="Y155" s="50"/>
-      <c r="Z155" s="50"/>
-      <c r="AA155" s="50"/>
-      <c r="AB155" s="51"/>
+      <c r="H155" s="51"/>
+      <c r="I155" s="52"/>
+      <c r="J155" s="52"/>
+      <c r="K155" s="52"/>
+      <c r="L155" s="52"/>
+      <c r="M155" s="52"/>
+      <c r="N155" s="52"/>
+      <c r="O155" s="52"/>
+      <c r="P155" s="52"/>
+      <c r="Q155" s="52"/>
+      <c r="R155" s="52"/>
+      <c r="S155" s="52"/>
+      <c r="T155" s="52"/>
+      <c r="U155" s="52"/>
+      <c r="V155" s="52"/>
+      <c r="W155" s="52"/>
+      <c r="X155" s="52"/>
+      <c r="Y155" s="52"/>
+      <c r="Z155" s="52"/>
+      <c r="AA155" s="52"/>
+      <c r="AB155" s="53"/>
       <c r="AC155" s="11"/>
     </row>
     <row r="156" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6566,27 +6605,27 @@
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
-      <c r="H156" s="49"/>
-      <c r="I156" s="50"/>
-      <c r="J156" s="50"/>
-      <c r="K156" s="50"/>
-      <c r="L156" s="50"/>
-      <c r="M156" s="50"/>
-      <c r="N156" s="50"/>
-      <c r="O156" s="50"/>
-      <c r="P156" s="50"/>
-      <c r="Q156" s="50"/>
-      <c r="R156" s="50"/>
-      <c r="S156" s="50"/>
-      <c r="T156" s="50"/>
-      <c r="U156" s="50"/>
-      <c r="V156" s="50"/>
-      <c r="W156" s="50"/>
-      <c r="X156" s="50"/>
-      <c r="Y156" s="50"/>
-      <c r="Z156" s="50"/>
-      <c r="AA156" s="50"/>
-      <c r="AB156" s="51"/>
+      <c r="H156" s="51"/>
+      <c r="I156" s="52"/>
+      <c r="J156" s="52"/>
+      <c r="K156" s="52"/>
+      <c r="L156" s="52"/>
+      <c r="M156" s="52"/>
+      <c r="N156" s="52"/>
+      <c r="O156" s="52"/>
+      <c r="P156" s="52"/>
+      <c r="Q156" s="52"/>
+      <c r="R156" s="52"/>
+      <c r="S156" s="52"/>
+      <c r="T156" s="52"/>
+      <c r="U156" s="52"/>
+      <c r="V156" s="52"/>
+      <c r="W156" s="52"/>
+      <c r="X156" s="52"/>
+      <c r="Y156" s="52"/>
+      <c r="Z156" s="52"/>
+      <c r="AA156" s="52"/>
+      <c r="AB156" s="53"/>
       <c r="AC156" s="11"/>
     </row>
     <row r="157" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6596,27 +6635,27 @@
       <c r="E157" s="6"/>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
-      <c r="H157" s="49"/>
-      <c r="I157" s="50"/>
-      <c r="J157" s="50"/>
-      <c r="K157" s="50"/>
-      <c r="L157" s="50"/>
-      <c r="M157" s="50"/>
-      <c r="N157" s="50"/>
-      <c r="O157" s="50"/>
-      <c r="P157" s="50"/>
-      <c r="Q157" s="50"/>
-      <c r="R157" s="50"/>
-      <c r="S157" s="50"/>
-      <c r="T157" s="50"/>
-      <c r="U157" s="50"/>
-      <c r="V157" s="50"/>
-      <c r="W157" s="50"/>
-      <c r="X157" s="50"/>
-      <c r="Y157" s="50"/>
-      <c r="Z157" s="50"/>
-      <c r="AA157" s="50"/>
-      <c r="AB157" s="51"/>
+      <c r="H157" s="51"/>
+      <c r="I157" s="52"/>
+      <c r="J157" s="52"/>
+      <c r="K157" s="52"/>
+      <c r="L157" s="52"/>
+      <c r="M157" s="52"/>
+      <c r="N157" s="52"/>
+      <c r="O157" s="52"/>
+      <c r="P157" s="52"/>
+      <c r="Q157" s="52"/>
+      <c r="R157" s="52"/>
+      <c r="S157" s="52"/>
+      <c r="T157" s="52"/>
+      <c r="U157" s="52"/>
+      <c r="V157" s="52"/>
+      <c r="W157" s="52"/>
+      <c r="X157" s="52"/>
+      <c r="Y157" s="52"/>
+      <c r="Z157" s="52"/>
+      <c r="AA157" s="52"/>
+      <c r="AB157" s="53"/>
       <c r="AC157" s="11"/>
     </row>
     <row r="158" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6626,27 +6665,27 @@
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
-      <c r="H158" s="52"/>
-      <c r="I158" s="53"/>
-      <c r="J158" s="53"/>
-      <c r="K158" s="53"/>
-      <c r="L158" s="53"/>
-      <c r="M158" s="53"/>
-      <c r="N158" s="53"/>
-      <c r="O158" s="53"/>
-      <c r="P158" s="53"/>
-      <c r="Q158" s="53"/>
-      <c r="R158" s="53"/>
-      <c r="S158" s="53"/>
-      <c r="T158" s="53"/>
-      <c r="U158" s="53"/>
-      <c r="V158" s="53"/>
-      <c r="W158" s="53"/>
-      <c r="X158" s="53"/>
-      <c r="Y158" s="53"/>
-      <c r="Z158" s="53"/>
-      <c r="AA158" s="53"/>
-      <c r="AB158" s="54"/>
+      <c r="H158" s="54"/>
+      <c r="I158" s="55"/>
+      <c r="J158" s="55"/>
+      <c r="K158" s="55"/>
+      <c r="L158" s="55"/>
+      <c r="M158" s="55"/>
+      <c r="N158" s="55"/>
+      <c r="O158" s="55"/>
+      <c r="P158" s="55"/>
+      <c r="Q158" s="55"/>
+      <c r="R158" s="55"/>
+      <c r="S158" s="55"/>
+      <c r="T158" s="55"/>
+      <c r="U158" s="55"/>
+      <c r="V158" s="55"/>
+      <c r="W158" s="55"/>
+      <c r="X158" s="55"/>
+      <c r="Y158" s="55"/>
+      <c r="Z158" s="55"/>
+      <c r="AA158" s="55"/>
+      <c r="AB158" s="56"/>
       <c r="AC158" s="11"/>
     </row>
     <row r="159" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6754,27 +6793,27 @@
         <v>2</v>
       </c>
       <c r="G163" s="6"/>
-      <c r="H163" s="46"/>
-      <c r="I163" s="47"/>
-      <c r="J163" s="47"/>
-      <c r="K163" s="47"/>
-      <c r="L163" s="47"/>
-      <c r="M163" s="47"/>
-      <c r="N163" s="47"/>
-      <c r="O163" s="47"/>
-      <c r="P163" s="47"/>
-      <c r="Q163" s="47"/>
-      <c r="R163" s="47"/>
-      <c r="S163" s="47"/>
-      <c r="T163" s="47"/>
-      <c r="U163" s="47"/>
-      <c r="V163" s="47"/>
-      <c r="W163" s="47"/>
-      <c r="X163" s="47"/>
-      <c r="Y163" s="47"/>
-      <c r="Z163" s="47"/>
-      <c r="AA163" s="47"/>
-      <c r="AB163" s="48"/>
+      <c r="H163" s="48"/>
+      <c r="I163" s="49"/>
+      <c r="J163" s="49"/>
+      <c r="K163" s="49"/>
+      <c r="L163" s="49"/>
+      <c r="M163" s="49"/>
+      <c r="N163" s="49"/>
+      <c r="O163" s="49"/>
+      <c r="P163" s="49"/>
+      <c r="Q163" s="49"/>
+      <c r="R163" s="49"/>
+      <c r="S163" s="49"/>
+      <c r="T163" s="49"/>
+      <c r="U163" s="49"/>
+      <c r="V163" s="49"/>
+      <c r="W163" s="49"/>
+      <c r="X163" s="49"/>
+      <c r="Y163" s="49"/>
+      <c r="Z163" s="49"/>
+      <c r="AA163" s="49"/>
+      <c r="AB163" s="50"/>
       <c r="AC163" s="11"/>
     </row>
     <row r="164" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6784,27 +6823,27 @@
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
-      <c r="H164" s="49"/>
-      <c r="I164" s="50"/>
-      <c r="J164" s="50"/>
-      <c r="K164" s="50"/>
-      <c r="L164" s="50"/>
-      <c r="M164" s="50"/>
-      <c r="N164" s="50"/>
-      <c r="O164" s="50"/>
-      <c r="P164" s="50"/>
-      <c r="Q164" s="50"/>
-      <c r="R164" s="50"/>
-      <c r="S164" s="50"/>
-      <c r="T164" s="50"/>
-      <c r="U164" s="50"/>
-      <c r="V164" s="50"/>
-      <c r="W164" s="50"/>
-      <c r="X164" s="50"/>
-      <c r="Y164" s="50"/>
-      <c r="Z164" s="50"/>
-      <c r="AA164" s="50"/>
-      <c r="AB164" s="51"/>
+      <c r="H164" s="51"/>
+      <c r="I164" s="52"/>
+      <c r="J164" s="52"/>
+      <c r="K164" s="52"/>
+      <c r="L164" s="52"/>
+      <c r="M164" s="52"/>
+      <c r="N164" s="52"/>
+      <c r="O164" s="52"/>
+      <c r="P164" s="52"/>
+      <c r="Q164" s="52"/>
+      <c r="R164" s="52"/>
+      <c r="S164" s="52"/>
+      <c r="T164" s="52"/>
+      <c r="U164" s="52"/>
+      <c r="V164" s="52"/>
+      <c r="W164" s="52"/>
+      <c r="X164" s="52"/>
+      <c r="Y164" s="52"/>
+      <c r="Z164" s="52"/>
+      <c r="AA164" s="52"/>
+      <c r="AB164" s="53"/>
       <c r="AC164" s="11"/>
     </row>
     <row r="165" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6814,27 +6853,27 @@
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
-      <c r="H165" s="49"/>
-      <c r="I165" s="50"/>
-      <c r="J165" s="50"/>
-      <c r="K165" s="50"/>
-      <c r="L165" s="50"/>
-      <c r="M165" s="50"/>
-      <c r="N165" s="50"/>
-      <c r="O165" s="50"/>
-      <c r="P165" s="50"/>
-      <c r="Q165" s="50"/>
-      <c r="R165" s="50"/>
-      <c r="S165" s="50"/>
-      <c r="T165" s="50"/>
-      <c r="U165" s="50"/>
-      <c r="V165" s="50"/>
-      <c r="W165" s="50"/>
-      <c r="X165" s="50"/>
-      <c r="Y165" s="50"/>
-      <c r="Z165" s="50"/>
-      <c r="AA165" s="50"/>
-      <c r="AB165" s="51"/>
+      <c r="H165" s="51"/>
+      <c r="I165" s="52"/>
+      <c r="J165" s="52"/>
+      <c r="K165" s="52"/>
+      <c r="L165" s="52"/>
+      <c r="M165" s="52"/>
+      <c r="N165" s="52"/>
+      <c r="O165" s="52"/>
+      <c r="P165" s="52"/>
+      <c r="Q165" s="52"/>
+      <c r="R165" s="52"/>
+      <c r="S165" s="52"/>
+      <c r="T165" s="52"/>
+      <c r="U165" s="52"/>
+      <c r="V165" s="52"/>
+      <c r="W165" s="52"/>
+      <c r="X165" s="52"/>
+      <c r="Y165" s="52"/>
+      <c r="Z165" s="52"/>
+      <c r="AA165" s="52"/>
+      <c r="AB165" s="53"/>
       <c r="AC165" s="11"/>
     </row>
     <row r="166" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6844,27 +6883,27 @@
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
-      <c r="H166" s="49"/>
-      <c r="I166" s="50"/>
-      <c r="J166" s="50"/>
-      <c r="K166" s="50"/>
-      <c r="L166" s="50"/>
-      <c r="M166" s="50"/>
-      <c r="N166" s="50"/>
-      <c r="O166" s="50"/>
-      <c r="P166" s="50"/>
-      <c r="Q166" s="50"/>
-      <c r="R166" s="50"/>
-      <c r="S166" s="50"/>
-      <c r="T166" s="50"/>
-      <c r="U166" s="50"/>
-      <c r="V166" s="50"/>
-      <c r="W166" s="50"/>
-      <c r="X166" s="50"/>
-      <c r="Y166" s="50"/>
-      <c r="Z166" s="50"/>
-      <c r="AA166" s="50"/>
-      <c r="AB166" s="51"/>
+      <c r="H166" s="51"/>
+      <c r="I166" s="52"/>
+      <c r="J166" s="52"/>
+      <c r="K166" s="52"/>
+      <c r="L166" s="52"/>
+      <c r="M166" s="52"/>
+      <c r="N166" s="52"/>
+      <c r="O166" s="52"/>
+      <c r="P166" s="52"/>
+      <c r="Q166" s="52"/>
+      <c r="R166" s="52"/>
+      <c r="S166" s="52"/>
+      <c r="T166" s="52"/>
+      <c r="U166" s="52"/>
+      <c r="V166" s="52"/>
+      <c r="W166" s="52"/>
+      <c r="X166" s="52"/>
+      <c r="Y166" s="52"/>
+      <c r="Z166" s="52"/>
+      <c r="AA166" s="52"/>
+      <c r="AB166" s="53"/>
       <c r="AC166" s="11"/>
     </row>
     <row r="167" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6874,27 +6913,27 @@
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
-      <c r="H167" s="49"/>
-      <c r="I167" s="50"/>
-      <c r="J167" s="50"/>
-      <c r="K167" s="50"/>
-      <c r="L167" s="50"/>
-      <c r="M167" s="50"/>
-      <c r="N167" s="50"/>
-      <c r="O167" s="50"/>
-      <c r="P167" s="50"/>
-      <c r="Q167" s="50"/>
-      <c r="R167" s="50"/>
-      <c r="S167" s="50"/>
-      <c r="T167" s="50"/>
-      <c r="U167" s="50"/>
-      <c r="V167" s="50"/>
-      <c r="W167" s="50"/>
-      <c r="X167" s="50"/>
-      <c r="Y167" s="50"/>
-      <c r="Z167" s="50"/>
-      <c r="AA167" s="50"/>
-      <c r="AB167" s="51"/>
+      <c r="H167" s="51"/>
+      <c r="I167" s="52"/>
+      <c r="J167" s="52"/>
+      <c r="K167" s="52"/>
+      <c r="L167" s="52"/>
+      <c r="M167" s="52"/>
+      <c r="N167" s="52"/>
+      <c r="O167" s="52"/>
+      <c r="P167" s="52"/>
+      <c r="Q167" s="52"/>
+      <c r="R167" s="52"/>
+      <c r="S167" s="52"/>
+      <c r="T167" s="52"/>
+      <c r="U167" s="52"/>
+      <c r="V167" s="52"/>
+      <c r="W167" s="52"/>
+      <c r="X167" s="52"/>
+      <c r="Y167" s="52"/>
+      <c r="Z167" s="52"/>
+      <c r="AA167" s="52"/>
+      <c r="AB167" s="53"/>
       <c r="AC167" s="11"/>
     </row>
     <row r="168" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6904,27 +6943,27 @@
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
-      <c r="H168" s="49"/>
-      <c r="I168" s="50"/>
-      <c r="J168" s="50"/>
-      <c r="K168" s="50"/>
-      <c r="L168" s="50"/>
-      <c r="M168" s="50"/>
-      <c r="N168" s="50"/>
-      <c r="O168" s="50"/>
-      <c r="P168" s="50"/>
-      <c r="Q168" s="50"/>
-      <c r="R168" s="50"/>
-      <c r="S168" s="50"/>
-      <c r="T168" s="50"/>
-      <c r="U168" s="50"/>
-      <c r="V168" s="50"/>
-      <c r="W168" s="50"/>
-      <c r="X168" s="50"/>
-      <c r="Y168" s="50"/>
-      <c r="Z168" s="50"/>
-      <c r="AA168" s="50"/>
-      <c r="AB168" s="51"/>
+      <c r="H168" s="51"/>
+      <c r="I168" s="52"/>
+      <c r="J168" s="52"/>
+      <c r="K168" s="52"/>
+      <c r="L168" s="52"/>
+      <c r="M168" s="52"/>
+      <c r="N168" s="52"/>
+      <c r="O168" s="52"/>
+      <c r="P168" s="52"/>
+      <c r="Q168" s="52"/>
+      <c r="R168" s="52"/>
+      <c r="S168" s="52"/>
+      <c r="T168" s="52"/>
+      <c r="U168" s="52"/>
+      <c r="V168" s="52"/>
+      <c r="W168" s="52"/>
+      <c r="X168" s="52"/>
+      <c r="Y168" s="52"/>
+      <c r="Z168" s="52"/>
+      <c r="AA168" s="52"/>
+      <c r="AB168" s="53"/>
       <c r="AC168" s="11"/>
     </row>
     <row r="169" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6934,27 +6973,27 @@
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
-      <c r="H169" s="52"/>
-      <c r="I169" s="53"/>
-      <c r="J169" s="53"/>
-      <c r="K169" s="53"/>
-      <c r="L169" s="53"/>
-      <c r="M169" s="53"/>
-      <c r="N169" s="53"/>
-      <c r="O169" s="53"/>
-      <c r="P169" s="53"/>
-      <c r="Q169" s="53"/>
-      <c r="R169" s="53"/>
-      <c r="S169" s="53"/>
-      <c r="T169" s="53"/>
-      <c r="U169" s="53"/>
-      <c r="V169" s="53"/>
-      <c r="W169" s="53"/>
-      <c r="X169" s="53"/>
-      <c r="Y169" s="53"/>
-      <c r="Z169" s="53"/>
-      <c r="AA169" s="53"/>
-      <c r="AB169" s="54"/>
+      <c r="H169" s="54"/>
+      <c r="I169" s="55"/>
+      <c r="J169" s="55"/>
+      <c r="K169" s="55"/>
+      <c r="L169" s="55"/>
+      <c r="M169" s="55"/>
+      <c r="N169" s="55"/>
+      <c r="O169" s="55"/>
+      <c r="P169" s="55"/>
+      <c r="Q169" s="55"/>
+      <c r="R169" s="55"/>
+      <c r="S169" s="55"/>
+      <c r="T169" s="55"/>
+      <c r="U169" s="55"/>
+      <c r="V169" s="55"/>
+      <c r="W169" s="55"/>
+      <c r="X169" s="55"/>
+      <c r="Y169" s="55"/>
+      <c r="Z169" s="55"/>
+      <c r="AA169" s="55"/>
+      <c r="AB169" s="56"/>
       <c r="AC169" s="11"/>
     </row>
     <row r="170" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6996,27 +7035,27 @@
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
-      <c r="H171" s="46"/>
-      <c r="I171" s="47"/>
-      <c r="J171" s="47"/>
-      <c r="K171" s="47"/>
-      <c r="L171" s="47"/>
-      <c r="M171" s="47"/>
-      <c r="N171" s="47"/>
-      <c r="O171" s="47"/>
-      <c r="P171" s="47"/>
-      <c r="Q171" s="47"/>
-      <c r="R171" s="47"/>
-      <c r="S171" s="47"/>
-      <c r="T171" s="47"/>
-      <c r="U171" s="47"/>
-      <c r="V171" s="47"/>
-      <c r="W171" s="47"/>
-      <c r="X171" s="47"/>
-      <c r="Y171" s="47"/>
-      <c r="Z171" s="47"/>
-      <c r="AA171" s="47"/>
-      <c r="AB171" s="48"/>
+      <c r="H171" s="48"/>
+      <c r="I171" s="49"/>
+      <c r="J171" s="49"/>
+      <c r="K171" s="49"/>
+      <c r="L171" s="49"/>
+      <c r="M171" s="49"/>
+      <c r="N171" s="49"/>
+      <c r="O171" s="49"/>
+      <c r="P171" s="49"/>
+      <c r="Q171" s="49"/>
+      <c r="R171" s="49"/>
+      <c r="S171" s="49"/>
+      <c r="T171" s="49"/>
+      <c r="U171" s="49"/>
+      <c r="V171" s="49"/>
+      <c r="W171" s="49"/>
+      <c r="X171" s="49"/>
+      <c r="Y171" s="49"/>
+      <c r="Z171" s="49"/>
+      <c r="AA171" s="49"/>
+      <c r="AB171" s="50"/>
       <c r="AC171" s="11"/>
     </row>
     <row r="172" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7026,27 +7065,27 @@
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
-      <c r="H172" s="49"/>
-      <c r="I172" s="50"/>
-      <c r="J172" s="50"/>
-      <c r="K172" s="50"/>
-      <c r="L172" s="50"/>
-      <c r="M172" s="50"/>
-      <c r="N172" s="50"/>
-      <c r="O172" s="50"/>
-      <c r="P172" s="50"/>
-      <c r="Q172" s="50"/>
-      <c r="R172" s="50"/>
-      <c r="S172" s="50"/>
-      <c r="T172" s="50"/>
-      <c r="U172" s="50"/>
-      <c r="V172" s="50"/>
-      <c r="W172" s="50"/>
-      <c r="X172" s="50"/>
-      <c r="Y172" s="50"/>
-      <c r="Z172" s="50"/>
-      <c r="AA172" s="50"/>
-      <c r="AB172" s="51"/>
+      <c r="H172" s="51"/>
+      <c r="I172" s="52"/>
+      <c r="J172" s="52"/>
+      <c r="K172" s="52"/>
+      <c r="L172" s="52"/>
+      <c r="M172" s="52"/>
+      <c r="N172" s="52"/>
+      <c r="O172" s="52"/>
+      <c r="P172" s="52"/>
+      <c r="Q172" s="52"/>
+      <c r="R172" s="52"/>
+      <c r="S172" s="52"/>
+      <c r="T172" s="52"/>
+      <c r="U172" s="52"/>
+      <c r="V172" s="52"/>
+      <c r="W172" s="52"/>
+      <c r="X172" s="52"/>
+      <c r="Y172" s="52"/>
+      <c r="Z172" s="52"/>
+      <c r="AA172" s="52"/>
+      <c r="AB172" s="53"/>
       <c r="AC172" s="11"/>
     </row>
     <row r="173" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7056,27 +7095,27 @@
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
-      <c r="H173" s="49"/>
-      <c r="I173" s="50"/>
-      <c r="J173" s="50"/>
-      <c r="K173" s="50"/>
-      <c r="L173" s="50"/>
-      <c r="M173" s="50"/>
-      <c r="N173" s="50"/>
-      <c r="O173" s="50"/>
-      <c r="P173" s="50"/>
-      <c r="Q173" s="50"/>
-      <c r="R173" s="50"/>
-      <c r="S173" s="50"/>
-      <c r="T173" s="50"/>
-      <c r="U173" s="50"/>
-      <c r="V173" s="50"/>
-      <c r="W173" s="50"/>
-      <c r="X173" s="50"/>
-      <c r="Y173" s="50"/>
-      <c r="Z173" s="50"/>
-      <c r="AA173" s="50"/>
-      <c r="AB173" s="51"/>
+      <c r="H173" s="51"/>
+      <c r="I173" s="52"/>
+      <c r="J173" s="52"/>
+      <c r="K173" s="52"/>
+      <c r="L173" s="52"/>
+      <c r="M173" s="52"/>
+      <c r="N173" s="52"/>
+      <c r="O173" s="52"/>
+      <c r="P173" s="52"/>
+      <c r="Q173" s="52"/>
+      <c r="R173" s="52"/>
+      <c r="S173" s="52"/>
+      <c r="T173" s="52"/>
+      <c r="U173" s="52"/>
+      <c r="V173" s="52"/>
+      <c r="W173" s="52"/>
+      <c r="X173" s="52"/>
+      <c r="Y173" s="52"/>
+      <c r="Z173" s="52"/>
+      <c r="AA173" s="52"/>
+      <c r="AB173" s="53"/>
       <c r="AC173" s="11"/>
     </row>
     <row r="174" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7086,27 +7125,27 @@
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
-      <c r="H174" s="49"/>
-      <c r="I174" s="50"/>
-      <c r="J174" s="50"/>
-      <c r="K174" s="50"/>
-      <c r="L174" s="50"/>
-      <c r="M174" s="50"/>
-      <c r="N174" s="50"/>
-      <c r="O174" s="50"/>
-      <c r="P174" s="50"/>
-      <c r="Q174" s="50"/>
-      <c r="R174" s="50"/>
-      <c r="S174" s="50"/>
-      <c r="T174" s="50"/>
-      <c r="U174" s="50"/>
-      <c r="V174" s="50"/>
-      <c r="W174" s="50"/>
-      <c r="X174" s="50"/>
-      <c r="Y174" s="50"/>
-      <c r="Z174" s="50"/>
-      <c r="AA174" s="50"/>
-      <c r="AB174" s="51"/>
+      <c r="H174" s="51"/>
+      <c r="I174" s="52"/>
+      <c r="J174" s="52"/>
+      <c r="K174" s="52"/>
+      <c r="L174" s="52"/>
+      <c r="M174" s="52"/>
+      <c r="N174" s="52"/>
+      <c r="O174" s="52"/>
+      <c r="P174" s="52"/>
+      <c r="Q174" s="52"/>
+      <c r="R174" s="52"/>
+      <c r="S174" s="52"/>
+      <c r="T174" s="52"/>
+      <c r="U174" s="52"/>
+      <c r="V174" s="52"/>
+      <c r="W174" s="52"/>
+      <c r="X174" s="52"/>
+      <c r="Y174" s="52"/>
+      <c r="Z174" s="52"/>
+      <c r="AA174" s="52"/>
+      <c r="AB174" s="53"/>
       <c r="AC174" s="11"/>
     </row>
     <row r="175" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7116,27 +7155,27 @@
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
-      <c r="H175" s="49"/>
-      <c r="I175" s="50"/>
-      <c r="J175" s="50"/>
-      <c r="K175" s="50"/>
-      <c r="L175" s="50"/>
-      <c r="M175" s="50"/>
-      <c r="N175" s="50"/>
-      <c r="O175" s="50"/>
-      <c r="P175" s="50"/>
-      <c r="Q175" s="50"/>
-      <c r="R175" s="50"/>
-      <c r="S175" s="50"/>
-      <c r="T175" s="50"/>
-      <c r="U175" s="50"/>
-      <c r="V175" s="50"/>
-      <c r="W175" s="50"/>
-      <c r="X175" s="50"/>
-      <c r="Y175" s="50"/>
-      <c r="Z175" s="50"/>
-      <c r="AA175" s="50"/>
-      <c r="AB175" s="51"/>
+      <c r="H175" s="51"/>
+      <c r="I175" s="52"/>
+      <c r="J175" s="52"/>
+      <c r="K175" s="52"/>
+      <c r="L175" s="52"/>
+      <c r="M175" s="52"/>
+      <c r="N175" s="52"/>
+      <c r="O175" s="52"/>
+      <c r="P175" s="52"/>
+      <c r="Q175" s="52"/>
+      <c r="R175" s="52"/>
+      <c r="S175" s="52"/>
+      <c r="T175" s="52"/>
+      <c r="U175" s="52"/>
+      <c r="V175" s="52"/>
+      <c r="W175" s="52"/>
+      <c r="X175" s="52"/>
+      <c r="Y175" s="52"/>
+      <c r="Z175" s="52"/>
+      <c r="AA175" s="52"/>
+      <c r="AB175" s="53"/>
       <c r="AC175" s="11"/>
     </row>
     <row r="176" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7146,27 +7185,27 @@
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
-      <c r="H176" s="49"/>
-      <c r="I176" s="50"/>
-      <c r="J176" s="50"/>
-      <c r="K176" s="50"/>
-      <c r="L176" s="50"/>
-      <c r="M176" s="50"/>
-      <c r="N176" s="50"/>
-      <c r="O176" s="50"/>
-      <c r="P176" s="50"/>
-      <c r="Q176" s="50"/>
-      <c r="R176" s="50"/>
-      <c r="S176" s="50"/>
-      <c r="T176" s="50"/>
-      <c r="U176" s="50"/>
-      <c r="V176" s="50"/>
-      <c r="W176" s="50"/>
-      <c r="X176" s="50"/>
-      <c r="Y176" s="50"/>
-      <c r="Z176" s="50"/>
-      <c r="AA176" s="50"/>
-      <c r="AB176" s="51"/>
+      <c r="H176" s="51"/>
+      <c r="I176" s="52"/>
+      <c r="J176" s="52"/>
+      <c r="K176" s="52"/>
+      <c r="L176" s="52"/>
+      <c r="M176" s="52"/>
+      <c r="N176" s="52"/>
+      <c r="O176" s="52"/>
+      <c r="P176" s="52"/>
+      <c r="Q176" s="52"/>
+      <c r="R176" s="52"/>
+      <c r="S176" s="52"/>
+      <c r="T176" s="52"/>
+      <c r="U176" s="52"/>
+      <c r="V176" s="52"/>
+      <c r="W176" s="52"/>
+      <c r="X176" s="52"/>
+      <c r="Y176" s="52"/>
+      <c r="Z176" s="52"/>
+      <c r="AA176" s="52"/>
+      <c r="AB176" s="53"/>
       <c r="AC176" s="11"/>
     </row>
     <row r="177" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7176,27 +7215,27 @@
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
-      <c r="H177" s="52"/>
-      <c r="I177" s="53"/>
-      <c r="J177" s="53"/>
-      <c r="K177" s="53"/>
-      <c r="L177" s="53"/>
-      <c r="M177" s="53"/>
-      <c r="N177" s="53"/>
-      <c r="O177" s="53"/>
-      <c r="P177" s="53"/>
-      <c r="Q177" s="53"/>
-      <c r="R177" s="53"/>
-      <c r="S177" s="53"/>
-      <c r="T177" s="53"/>
-      <c r="U177" s="53"/>
-      <c r="V177" s="53"/>
-      <c r="W177" s="53"/>
-      <c r="X177" s="53"/>
-      <c r="Y177" s="53"/>
-      <c r="Z177" s="53"/>
-      <c r="AA177" s="53"/>
-      <c r="AB177" s="54"/>
+      <c r="H177" s="54"/>
+      <c r="I177" s="55"/>
+      <c r="J177" s="55"/>
+      <c r="K177" s="55"/>
+      <c r="L177" s="55"/>
+      <c r="M177" s="55"/>
+      <c r="N177" s="55"/>
+      <c r="O177" s="55"/>
+      <c r="P177" s="55"/>
+      <c r="Q177" s="55"/>
+      <c r="R177" s="55"/>
+      <c r="S177" s="55"/>
+      <c r="T177" s="55"/>
+      <c r="U177" s="55"/>
+      <c r="V177" s="55"/>
+      <c r="W177" s="55"/>
+      <c r="X177" s="55"/>
+      <c r="Y177" s="55"/>
+      <c r="Z177" s="55"/>
+      <c r="AA177" s="55"/>
+      <c r="AB177" s="56"/>
       <c r="AC177" s="11"/>
     </row>
     <row r="178" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7304,27 +7343,27 @@
         <v>2</v>
       </c>
       <c r="G182" s="6"/>
-      <c r="H182" s="46"/>
-      <c r="I182" s="47"/>
-      <c r="J182" s="47"/>
-      <c r="K182" s="47"/>
-      <c r="L182" s="47"/>
-      <c r="M182" s="47"/>
-      <c r="N182" s="47"/>
-      <c r="O182" s="47"/>
-      <c r="P182" s="47"/>
-      <c r="Q182" s="47"/>
-      <c r="R182" s="47"/>
-      <c r="S182" s="47"/>
-      <c r="T182" s="47"/>
-      <c r="U182" s="47"/>
-      <c r="V182" s="47"/>
-      <c r="W182" s="47"/>
-      <c r="X182" s="47"/>
-      <c r="Y182" s="47"/>
-      <c r="Z182" s="47"/>
-      <c r="AA182" s="47"/>
-      <c r="AB182" s="48"/>
+      <c r="H182" s="48"/>
+      <c r="I182" s="49"/>
+      <c r="J182" s="49"/>
+      <c r="K182" s="49"/>
+      <c r="L182" s="49"/>
+      <c r="M182" s="49"/>
+      <c r="N182" s="49"/>
+      <c r="O182" s="49"/>
+      <c r="P182" s="49"/>
+      <c r="Q182" s="49"/>
+      <c r="R182" s="49"/>
+      <c r="S182" s="49"/>
+      <c r="T182" s="49"/>
+      <c r="U182" s="49"/>
+      <c r="V182" s="49"/>
+      <c r="W182" s="49"/>
+      <c r="X182" s="49"/>
+      <c r="Y182" s="49"/>
+      <c r="Z182" s="49"/>
+      <c r="AA182" s="49"/>
+      <c r="AB182" s="50"/>
       <c r="AC182" s="11"/>
     </row>
     <row r="183" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7334,27 +7373,27 @@
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
-      <c r="H183" s="49"/>
-      <c r="I183" s="50"/>
-      <c r="J183" s="50"/>
-      <c r="K183" s="50"/>
-      <c r="L183" s="50"/>
-      <c r="M183" s="50"/>
-      <c r="N183" s="50"/>
-      <c r="O183" s="50"/>
-      <c r="P183" s="50"/>
-      <c r="Q183" s="50"/>
-      <c r="R183" s="50"/>
-      <c r="S183" s="50"/>
-      <c r="T183" s="50"/>
-      <c r="U183" s="50"/>
-      <c r="V183" s="50"/>
-      <c r="W183" s="50"/>
-      <c r="X183" s="50"/>
-      <c r="Y183" s="50"/>
-      <c r="Z183" s="50"/>
-      <c r="AA183" s="50"/>
-      <c r="AB183" s="51"/>
+      <c r="H183" s="51"/>
+      <c r="I183" s="52"/>
+      <c r="J183" s="52"/>
+      <c r="K183" s="52"/>
+      <c r="L183" s="52"/>
+      <c r="M183" s="52"/>
+      <c r="N183" s="52"/>
+      <c r="O183" s="52"/>
+      <c r="P183" s="52"/>
+      <c r="Q183" s="52"/>
+      <c r="R183" s="52"/>
+      <c r="S183" s="52"/>
+      <c r="T183" s="52"/>
+      <c r="U183" s="52"/>
+      <c r="V183" s="52"/>
+      <c r="W183" s="52"/>
+      <c r="X183" s="52"/>
+      <c r="Y183" s="52"/>
+      <c r="Z183" s="52"/>
+      <c r="AA183" s="52"/>
+      <c r="AB183" s="53"/>
       <c r="AC183" s="11"/>
     </row>
     <row r="184" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7364,27 +7403,27 @@
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
-      <c r="H184" s="49"/>
-      <c r="I184" s="50"/>
-      <c r="J184" s="50"/>
-      <c r="K184" s="50"/>
-      <c r="L184" s="50"/>
-      <c r="M184" s="50"/>
-      <c r="N184" s="50"/>
-      <c r="O184" s="50"/>
-      <c r="P184" s="50"/>
-      <c r="Q184" s="50"/>
-      <c r="R184" s="50"/>
-      <c r="S184" s="50"/>
-      <c r="T184" s="50"/>
-      <c r="U184" s="50"/>
-      <c r="V184" s="50"/>
-      <c r="W184" s="50"/>
-      <c r="X184" s="50"/>
-      <c r="Y184" s="50"/>
-      <c r="Z184" s="50"/>
-      <c r="AA184" s="50"/>
-      <c r="AB184" s="51"/>
+      <c r="H184" s="51"/>
+      <c r="I184" s="52"/>
+      <c r="J184" s="52"/>
+      <c r="K184" s="52"/>
+      <c r="L184" s="52"/>
+      <c r="M184" s="52"/>
+      <c r="N184" s="52"/>
+      <c r="O184" s="52"/>
+      <c r="P184" s="52"/>
+      <c r="Q184" s="52"/>
+      <c r="R184" s="52"/>
+      <c r="S184" s="52"/>
+      <c r="T184" s="52"/>
+      <c r="U184" s="52"/>
+      <c r="V184" s="52"/>
+      <c r="W184" s="52"/>
+      <c r="X184" s="52"/>
+      <c r="Y184" s="52"/>
+      <c r="Z184" s="52"/>
+      <c r="AA184" s="52"/>
+      <c r="AB184" s="53"/>
       <c r="AC184" s="11"/>
     </row>
     <row r="185" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7394,27 +7433,27 @@
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
-      <c r="H185" s="49"/>
-      <c r="I185" s="50"/>
-      <c r="J185" s="50"/>
-      <c r="K185" s="50"/>
-      <c r="L185" s="50"/>
-      <c r="M185" s="50"/>
-      <c r="N185" s="50"/>
-      <c r="O185" s="50"/>
-      <c r="P185" s="50"/>
-      <c r="Q185" s="50"/>
-      <c r="R185" s="50"/>
-      <c r="S185" s="50"/>
-      <c r="T185" s="50"/>
-      <c r="U185" s="50"/>
-      <c r="V185" s="50"/>
-      <c r="W185" s="50"/>
-      <c r="X185" s="50"/>
-      <c r="Y185" s="50"/>
-      <c r="Z185" s="50"/>
-      <c r="AA185" s="50"/>
-      <c r="AB185" s="51"/>
+      <c r="H185" s="51"/>
+      <c r="I185" s="52"/>
+      <c r="J185" s="52"/>
+      <c r="K185" s="52"/>
+      <c r="L185" s="52"/>
+      <c r="M185" s="52"/>
+      <c r="N185" s="52"/>
+      <c r="O185" s="52"/>
+      <c r="P185" s="52"/>
+      <c r="Q185" s="52"/>
+      <c r="R185" s="52"/>
+      <c r="S185" s="52"/>
+      <c r="T185" s="52"/>
+      <c r="U185" s="52"/>
+      <c r="V185" s="52"/>
+      <c r="W185" s="52"/>
+      <c r="X185" s="52"/>
+      <c r="Y185" s="52"/>
+      <c r="Z185" s="52"/>
+      <c r="AA185" s="52"/>
+      <c r="AB185" s="53"/>
       <c r="AC185" s="11"/>
     </row>
     <row r="186" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7424,27 +7463,27 @@
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
-      <c r="H186" s="49"/>
-      <c r="I186" s="50"/>
-      <c r="J186" s="50"/>
-      <c r="K186" s="50"/>
-      <c r="L186" s="50"/>
-      <c r="M186" s="50"/>
-      <c r="N186" s="50"/>
-      <c r="O186" s="50"/>
-      <c r="P186" s="50"/>
-      <c r="Q186" s="50"/>
-      <c r="R186" s="50"/>
-      <c r="S186" s="50"/>
-      <c r="T186" s="50"/>
-      <c r="U186" s="50"/>
-      <c r="V186" s="50"/>
-      <c r="W186" s="50"/>
-      <c r="X186" s="50"/>
-      <c r="Y186" s="50"/>
-      <c r="Z186" s="50"/>
-      <c r="AA186" s="50"/>
-      <c r="AB186" s="51"/>
+      <c r="H186" s="51"/>
+      <c r="I186" s="52"/>
+      <c r="J186" s="52"/>
+      <c r="K186" s="52"/>
+      <c r="L186" s="52"/>
+      <c r="M186" s="52"/>
+      <c r="N186" s="52"/>
+      <c r="O186" s="52"/>
+      <c r="P186" s="52"/>
+      <c r="Q186" s="52"/>
+      <c r="R186" s="52"/>
+      <c r="S186" s="52"/>
+      <c r="T186" s="52"/>
+      <c r="U186" s="52"/>
+      <c r="V186" s="52"/>
+      <c r="W186" s="52"/>
+      <c r="X186" s="52"/>
+      <c r="Y186" s="52"/>
+      <c r="Z186" s="52"/>
+      <c r="AA186" s="52"/>
+      <c r="AB186" s="53"/>
       <c r="AC186" s="11"/>
     </row>
     <row r="187" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7454,27 +7493,27 @@
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
-      <c r="H187" s="49"/>
-      <c r="I187" s="50"/>
-      <c r="J187" s="50"/>
-      <c r="K187" s="50"/>
-      <c r="L187" s="50"/>
-      <c r="M187" s="50"/>
-      <c r="N187" s="50"/>
-      <c r="O187" s="50"/>
-      <c r="P187" s="50"/>
-      <c r="Q187" s="50"/>
-      <c r="R187" s="50"/>
-      <c r="S187" s="50"/>
-      <c r="T187" s="50"/>
-      <c r="U187" s="50"/>
-      <c r="V187" s="50"/>
-      <c r="W187" s="50"/>
-      <c r="X187" s="50"/>
-      <c r="Y187" s="50"/>
-      <c r="Z187" s="50"/>
-      <c r="AA187" s="50"/>
-      <c r="AB187" s="51"/>
+      <c r="H187" s="51"/>
+      <c r="I187" s="52"/>
+      <c r="J187" s="52"/>
+      <c r="K187" s="52"/>
+      <c r="L187" s="52"/>
+      <c r="M187" s="52"/>
+      <c r="N187" s="52"/>
+      <c r="O187" s="52"/>
+      <c r="P187" s="52"/>
+      <c r="Q187" s="52"/>
+      <c r="R187" s="52"/>
+      <c r="S187" s="52"/>
+      <c r="T187" s="52"/>
+      <c r="U187" s="52"/>
+      <c r="V187" s="52"/>
+      <c r="W187" s="52"/>
+      <c r="X187" s="52"/>
+      <c r="Y187" s="52"/>
+      <c r="Z187" s="52"/>
+      <c r="AA187" s="52"/>
+      <c r="AB187" s="53"/>
       <c r="AC187" s="11"/>
     </row>
     <row r="188" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7484,27 +7523,27 @@
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
-      <c r="H188" s="52"/>
-      <c r="I188" s="53"/>
-      <c r="J188" s="53"/>
-      <c r="K188" s="53"/>
-      <c r="L188" s="53"/>
-      <c r="M188" s="53"/>
-      <c r="N188" s="53"/>
-      <c r="O188" s="53"/>
-      <c r="P188" s="53"/>
-      <c r="Q188" s="53"/>
-      <c r="R188" s="53"/>
-      <c r="S188" s="53"/>
-      <c r="T188" s="53"/>
-      <c r="U188" s="53"/>
-      <c r="V188" s="53"/>
-      <c r="W188" s="53"/>
-      <c r="X188" s="53"/>
-      <c r="Y188" s="53"/>
-      <c r="Z188" s="53"/>
-      <c r="AA188" s="53"/>
-      <c r="AB188" s="54"/>
+      <c r="H188" s="54"/>
+      <c r="I188" s="55"/>
+      <c r="J188" s="55"/>
+      <c r="K188" s="55"/>
+      <c r="L188" s="55"/>
+      <c r="M188" s="55"/>
+      <c r="N188" s="55"/>
+      <c r="O188" s="55"/>
+      <c r="P188" s="55"/>
+      <c r="Q188" s="55"/>
+      <c r="R188" s="55"/>
+      <c r="S188" s="55"/>
+      <c r="T188" s="55"/>
+      <c r="U188" s="55"/>
+      <c r="V188" s="55"/>
+      <c r="W188" s="55"/>
+      <c r="X188" s="55"/>
+      <c r="Y188" s="55"/>
+      <c r="Z188" s="55"/>
+      <c r="AA188" s="55"/>
+      <c r="AB188" s="56"/>
       <c r="AC188" s="11"/>
     </row>
     <row r="189" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7546,27 +7585,27 @@
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
-      <c r="H190" s="46"/>
-      <c r="I190" s="47"/>
-      <c r="J190" s="47"/>
-      <c r="K190" s="47"/>
-      <c r="L190" s="47"/>
-      <c r="M190" s="47"/>
-      <c r="N190" s="47"/>
-      <c r="O190" s="47"/>
-      <c r="P190" s="47"/>
-      <c r="Q190" s="47"/>
-      <c r="R190" s="47"/>
-      <c r="S190" s="47"/>
-      <c r="T190" s="47"/>
-      <c r="U190" s="47"/>
-      <c r="V190" s="47"/>
-      <c r="W190" s="47"/>
-      <c r="X190" s="47"/>
-      <c r="Y190" s="47"/>
-      <c r="Z190" s="47"/>
-      <c r="AA190" s="47"/>
-      <c r="AB190" s="48"/>
+      <c r="H190" s="48"/>
+      <c r="I190" s="49"/>
+      <c r="J190" s="49"/>
+      <c r="K190" s="49"/>
+      <c r="L190" s="49"/>
+      <c r="M190" s="49"/>
+      <c r="N190" s="49"/>
+      <c r="O190" s="49"/>
+      <c r="P190" s="49"/>
+      <c r="Q190" s="49"/>
+      <c r="R190" s="49"/>
+      <c r="S190" s="49"/>
+      <c r="T190" s="49"/>
+      <c r="U190" s="49"/>
+      <c r="V190" s="49"/>
+      <c r="W190" s="49"/>
+      <c r="X190" s="49"/>
+      <c r="Y190" s="49"/>
+      <c r="Z190" s="49"/>
+      <c r="AA190" s="49"/>
+      <c r="AB190" s="50"/>
       <c r="AC190" s="11"/>
     </row>
     <row r="191" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7576,27 +7615,27 @@
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
-      <c r="H191" s="49"/>
-      <c r="I191" s="50"/>
-      <c r="J191" s="50"/>
-      <c r="K191" s="50"/>
-      <c r="L191" s="50"/>
-      <c r="M191" s="50"/>
-      <c r="N191" s="50"/>
-      <c r="O191" s="50"/>
-      <c r="P191" s="50"/>
-      <c r="Q191" s="50"/>
-      <c r="R191" s="50"/>
-      <c r="S191" s="50"/>
-      <c r="T191" s="50"/>
-      <c r="U191" s="50"/>
-      <c r="V191" s="50"/>
-      <c r="W191" s="50"/>
-      <c r="X191" s="50"/>
-      <c r="Y191" s="50"/>
-      <c r="Z191" s="50"/>
-      <c r="AA191" s="50"/>
-      <c r="AB191" s="51"/>
+      <c r="H191" s="51"/>
+      <c r="I191" s="52"/>
+      <c r="J191" s="52"/>
+      <c r="K191" s="52"/>
+      <c r="L191" s="52"/>
+      <c r="M191" s="52"/>
+      <c r="N191" s="52"/>
+      <c r="O191" s="52"/>
+      <c r="P191" s="52"/>
+      <c r="Q191" s="52"/>
+      <c r="R191" s="52"/>
+      <c r="S191" s="52"/>
+      <c r="T191" s="52"/>
+      <c r="U191" s="52"/>
+      <c r="V191" s="52"/>
+      <c r="W191" s="52"/>
+      <c r="X191" s="52"/>
+      <c r="Y191" s="52"/>
+      <c r="Z191" s="52"/>
+      <c r="AA191" s="52"/>
+      <c r="AB191" s="53"/>
       <c r="AC191" s="11"/>
     </row>
     <row r="192" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7606,27 +7645,27 @@
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
-      <c r="H192" s="49"/>
-      <c r="I192" s="50"/>
-      <c r="J192" s="50"/>
-      <c r="K192" s="50"/>
-      <c r="L192" s="50"/>
-      <c r="M192" s="50"/>
-      <c r="N192" s="50"/>
-      <c r="O192" s="50"/>
-      <c r="P192" s="50"/>
-      <c r="Q192" s="50"/>
-      <c r="R192" s="50"/>
-      <c r="S192" s="50"/>
-      <c r="T192" s="50"/>
-      <c r="U192" s="50"/>
-      <c r="V192" s="50"/>
-      <c r="W192" s="50"/>
-      <c r="X192" s="50"/>
-      <c r="Y192" s="50"/>
-      <c r="Z192" s="50"/>
-      <c r="AA192" s="50"/>
-      <c r="AB192" s="51"/>
+      <c r="H192" s="51"/>
+      <c r="I192" s="52"/>
+      <c r="J192" s="52"/>
+      <c r="K192" s="52"/>
+      <c r="L192" s="52"/>
+      <c r="M192" s="52"/>
+      <c r="N192" s="52"/>
+      <c r="O192" s="52"/>
+      <c r="P192" s="52"/>
+      <c r="Q192" s="52"/>
+      <c r="R192" s="52"/>
+      <c r="S192" s="52"/>
+      <c r="T192" s="52"/>
+      <c r="U192" s="52"/>
+      <c r="V192" s="52"/>
+      <c r="W192" s="52"/>
+      <c r="X192" s="52"/>
+      <c r="Y192" s="52"/>
+      <c r="Z192" s="52"/>
+      <c r="AA192" s="52"/>
+      <c r="AB192" s="53"/>
       <c r="AC192" s="11"/>
     </row>
     <row r="193" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7636,27 +7675,27 @@
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
-      <c r="H193" s="49"/>
-      <c r="I193" s="50"/>
-      <c r="J193" s="50"/>
-      <c r="K193" s="50"/>
-      <c r="L193" s="50"/>
-      <c r="M193" s="50"/>
-      <c r="N193" s="50"/>
-      <c r="O193" s="50"/>
-      <c r="P193" s="50"/>
-      <c r="Q193" s="50"/>
-      <c r="R193" s="50"/>
-      <c r="S193" s="50"/>
-      <c r="T193" s="50"/>
-      <c r="U193" s="50"/>
-      <c r="V193" s="50"/>
-      <c r="W193" s="50"/>
-      <c r="X193" s="50"/>
-      <c r="Y193" s="50"/>
-      <c r="Z193" s="50"/>
-      <c r="AA193" s="50"/>
-      <c r="AB193" s="51"/>
+      <c r="H193" s="51"/>
+      <c r="I193" s="52"/>
+      <c r="J193" s="52"/>
+      <c r="K193" s="52"/>
+      <c r="L193" s="52"/>
+      <c r="M193" s="52"/>
+      <c r="N193" s="52"/>
+      <c r="O193" s="52"/>
+      <c r="P193" s="52"/>
+      <c r="Q193" s="52"/>
+      <c r="R193" s="52"/>
+      <c r="S193" s="52"/>
+      <c r="T193" s="52"/>
+      <c r="U193" s="52"/>
+      <c r="V193" s="52"/>
+      <c r="W193" s="52"/>
+      <c r="X193" s="52"/>
+      <c r="Y193" s="52"/>
+      <c r="Z193" s="52"/>
+      <c r="AA193" s="52"/>
+      <c r="AB193" s="53"/>
       <c r="AC193" s="11"/>
     </row>
     <row r="194" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7666,27 +7705,27 @@
       <c r="E194" s="6"/>
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
-      <c r="H194" s="49"/>
-      <c r="I194" s="50"/>
-      <c r="J194" s="50"/>
-      <c r="K194" s="50"/>
-      <c r="L194" s="50"/>
-      <c r="M194" s="50"/>
-      <c r="N194" s="50"/>
-      <c r="O194" s="50"/>
-      <c r="P194" s="50"/>
-      <c r="Q194" s="50"/>
-      <c r="R194" s="50"/>
-      <c r="S194" s="50"/>
-      <c r="T194" s="50"/>
-      <c r="U194" s="50"/>
-      <c r="V194" s="50"/>
-      <c r="W194" s="50"/>
-      <c r="X194" s="50"/>
-      <c r="Y194" s="50"/>
-      <c r="Z194" s="50"/>
-      <c r="AA194" s="50"/>
-      <c r="AB194" s="51"/>
+      <c r="H194" s="51"/>
+      <c r="I194" s="52"/>
+      <c r="J194" s="52"/>
+      <c r="K194" s="52"/>
+      <c r="L194" s="52"/>
+      <c r="M194" s="52"/>
+      <c r="N194" s="52"/>
+      <c r="O194" s="52"/>
+      <c r="P194" s="52"/>
+      <c r="Q194" s="52"/>
+      <c r="R194" s="52"/>
+      <c r="S194" s="52"/>
+      <c r="T194" s="52"/>
+      <c r="U194" s="52"/>
+      <c r="V194" s="52"/>
+      <c r="W194" s="52"/>
+      <c r="X194" s="52"/>
+      <c r="Y194" s="52"/>
+      <c r="Z194" s="52"/>
+      <c r="AA194" s="52"/>
+      <c r="AB194" s="53"/>
       <c r="AC194" s="11"/>
     </row>
     <row r="195" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7696,27 +7735,27 @@
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
-      <c r="H195" s="49"/>
-      <c r="I195" s="50"/>
-      <c r="J195" s="50"/>
-      <c r="K195" s="50"/>
-      <c r="L195" s="50"/>
-      <c r="M195" s="50"/>
-      <c r="N195" s="50"/>
-      <c r="O195" s="50"/>
-      <c r="P195" s="50"/>
-      <c r="Q195" s="50"/>
-      <c r="R195" s="50"/>
-      <c r="S195" s="50"/>
-      <c r="T195" s="50"/>
-      <c r="U195" s="50"/>
-      <c r="V195" s="50"/>
-      <c r="W195" s="50"/>
-      <c r="X195" s="50"/>
-      <c r="Y195" s="50"/>
-      <c r="Z195" s="50"/>
-      <c r="AA195" s="50"/>
-      <c r="AB195" s="51"/>
+      <c r="H195" s="51"/>
+      <c r="I195" s="52"/>
+      <c r="J195" s="52"/>
+      <c r="K195" s="52"/>
+      <c r="L195" s="52"/>
+      <c r="M195" s="52"/>
+      <c r="N195" s="52"/>
+      <c r="O195" s="52"/>
+      <c r="P195" s="52"/>
+      <c r="Q195" s="52"/>
+      <c r="R195" s="52"/>
+      <c r="S195" s="52"/>
+      <c r="T195" s="52"/>
+      <c r="U195" s="52"/>
+      <c r="V195" s="52"/>
+      <c r="W195" s="52"/>
+      <c r="X195" s="52"/>
+      <c r="Y195" s="52"/>
+      <c r="Z195" s="52"/>
+      <c r="AA195" s="52"/>
+      <c r="AB195" s="53"/>
       <c r="AC195" s="11"/>
     </row>
     <row r="196" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7726,27 +7765,27 @@
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
-      <c r="H196" s="52"/>
-      <c r="I196" s="53"/>
-      <c r="J196" s="53"/>
-      <c r="K196" s="53"/>
-      <c r="L196" s="53"/>
-      <c r="M196" s="53"/>
-      <c r="N196" s="53"/>
-      <c r="O196" s="53"/>
-      <c r="P196" s="53"/>
-      <c r="Q196" s="53"/>
-      <c r="R196" s="53"/>
-      <c r="S196" s="53"/>
-      <c r="T196" s="53"/>
-      <c r="U196" s="53"/>
-      <c r="V196" s="53"/>
-      <c r="W196" s="53"/>
-      <c r="X196" s="53"/>
-      <c r="Y196" s="53"/>
-      <c r="Z196" s="53"/>
-      <c r="AA196" s="53"/>
-      <c r="AB196" s="54"/>
+      <c r="H196" s="54"/>
+      <c r="I196" s="55"/>
+      <c r="J196" s="55"/>
+      <c r="K196" s="55"/>
+      <c r="L196" s="55"/>
+      <c r="M196" s="55"/>
+      <c r="N196" s="55"/>
+      <c r="O196" s="55"/>
+      <c r="P196" s="55"/>
+      <c r="Q196" s="55"/>
+      <c r="R196" s="55"/>
+      <c r="S196" s="55"/>
+      <c r="T196" s="55"/>
+      <c r="U196" s="55"/>
+      <c r="V196" s="55"/>
+      <c r="W196" s="55"/>
+      <c r="X196" s="55"/>
+      <c r="Y196" s="55"/>
+      <c r="Z196" s="55"/>
+      <c r="AA196" s="55"/>
+      <c r="AB196" s="56"/>
       <c r="AC196" s="11"/>
     </row>
     <row r="197" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7854,27 +7893,27 @@
         <v>2</v>
       </c>
       <c r="G201" s="6"/>
-      <c r="H201" s="46"/>
-      <c r="I201" s="47"/>
-      <c r="J201" s="47"/>
-      <c r="K201" s="47"/>
-      <c r="L201" s="47"/>
-      <c r="M201" s="47"/>
-      <c r="N201" s="47"/>
-      <c r="O201" s="47"/>
-      <c r="P201" s="47"/>
-      <c r="Q201" s="47"/>
-      <c r="R201" s="47"/>
-      <c r="S201" s="47"/>
-      <c r="T201" s="47"/>
-      <c r="U201" s="47"/>
-      <c r="V201" s="47"/>
-      <c r="W201" s="47"/>
-      <c r="X201" s="47"/>
-      <c r="Y201" s="47"/>
-      <c r="Z201" s="47"/>
-      <c r="AA201" s="47"/>
-      <c r="AB201" s="48"/>
+      <c r="H201" s="48"/>
+      <c r="I201" s="49"/>
+      <c r="J201" s="49"/>
+      <c r="K201" s="49"/>
+      <c r="L201" s="49"/>
+      <c r="M201" s="49"/>
+      <c r="N201" s="49"/>
+      <c r="O201" s="49"/>
+      <c r="P201" s="49"/>
+      <c r="Q201" s="49"/>
+      <c r="R201" s="49"/>
+      <c r="S201" s="49"/>
+      <c r="T201" s="49"/>
+      <c r="U201" s="49"/>
+      <c r="V201" s="49"/>
+      <c r="W201" s="49"/>
+      <c r="X201" s="49"/>
+      <c r="Y201" s="49"/>
+      <c r="Z201" s="49"/>
+      <c r="AA201" s="49"/>
+      <c r="AB201" s="50"/>
       <c r="AC201" s="11"/>
     </row>
     <row r="202" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7884,27 +7923,27 @@
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
-      <c r="H202" s="49"/>
-      <c r="I202" s="50"/>
-      <c r="J202" s="50"/>
-      <c r="K202" s="50"/>
-      <c r="L202" s="50"/>
-      <c r="M202" s="50"/>
-      <c r="N202" s="50"/>
-      <c r="O202" s="50"/>
-      <c r="P202" s="50"/>
-      <c r="Q202" s="50"/>
-      <c r="R202" s="50"/>
-      <c r="S202" s="50"/>
-      <c r="T202" s="50"/>
-      <c r="U202" s="50"/>
-      <c r="V202" s="50"/>
-      <c r="W202" s="50"/>
-      <c r="X202" s="50"/>
-      <c r="Y202" s="50"/>
-      <c r="Z202" s="50"/>
-      <c r="AA202" s="50"/>
-      <c r="AB202" s="51"/>
+      <c r="H202" s="51"/>
+      <c r="I202" s="52"/>
+      <c r="J202" s="52"/>
+      <c r="K202" s="52"/>
+      <c r="L202" s="52"/>
+      <c r="M202" s="52"/>
+      <c r="N202" s="52"/>
+      <c r="O202" s="52"/>
+      <c r="P202" s="52"/>
+      <c r="Q202" s="52"/>
+      <c r="R202" s="52"/>
+      <c r="S202" s="52"/>
+      <c r="T202" s="52"/>
+      <c r="U202" s="52"/>
+      <c r="V202" s="52"/>
+      <c r="W202" s="52"/>
+      <c r="X202" s="52"/>
+      <c r="Y202" s="52"/>
+      <c r="Z202" s="52"/>
+      <c r="AA202" s="52"/>
+      <c r="AB202" s="53"/>
       <c r="AC202" s="11"/>
     </row>
     <row r="203" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7914,27 +7953,27 @@
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
-      <c r="H203" s="49"/>
-      <c r="I203" s="50"/>
-      <c r="J203" s="50"/>
-      <c r="K203" s="50"/>
-      <c r="L203" s="50"/>
-      <c r="M203" s="50"/>
-      <c r="N203" s="50"/>
-      <c r="O203" s="50"/>
-      <c r="P203" s="50"/>
-      <c r="Q203" s="50"/>
-      <c r="R203" s="50"/>
-      <c r="S203" s="50"/>
-      <c r="T203" s="50"/>
-      <c r="U203" s="50"/>
-      <c r="V203" s="50"/>
-      <c r="W203" s="50"/>
-      <c r="X203" s="50"/>
-      <c r="Y203" s="50"/>
-      <c r="Z203" s="50"/>
-      <c r="AA203" s="50"/>
-      <c r="AB203" s="51"/>
+      <c r="H203" s="51"/>
+      <c r="I203" s="52"/>
+      <c r="J203" s="52"/>
+      <c r="K203" s="52"/>
+      <c r="L203" s="52"/>
+      <c r="M203" s="52"/>
+      <c r="N203" s="52"/>
+      <c r="O203" s="52"/>
+      <c r="P203" s="52"/>
+      <c r="Q203" s="52"/>
+      <c r="R203" s="52"/>
+      <c r="S203" s="52"/>
+      <c r="T203" s="52"/>
+      <c r="U203" s="52"/>
+      <c r="V203" s="52"/>
+      <c r="W203" s="52"/>
+      <c r="X203" s="52"/>
+      <c r="Y203" s="52"/>
+      <c r="Z203" s="52"/>
+      <c r="AA203" s="52"/>
+      <c r="AB203" s="53"/>
       <c r="AC203" s="11"/>
     </row>
     <row r="204" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7944,27 +7983,27 @@
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
-      <c r="H204" s="49"/>
-      <c r="I204" s="50"/>
-      <c r="J204" s="50"/>
-      <c r="K204" s="50"/>
-      <c r="L204" s="50"/>
-      <c r="M204" s="50"/>
-      <c r="N204" s="50"/>
-      <c r="O204" s="50"/>
-      <c r="P204" s="50"/>
-      <c r="Q204" s="50"/>
-      <c r="R204" s="50"/>
-      <c r="S204" s="50"/>
-      <c r="T204" s="50"/>
-      <c r="U204" s="50"/>
-      <c r="V204" s="50"/>
-      <c r="W204" s="50"/>
-      <c r="X204" s="50"/>
-      <c r="Y204" s="50"/>
-      <c r="Z204" s="50"/>
-      <c r="AA204" s="50"/>
-      <c r="AB204" s="51"/>
+      <c r="H204" s="51"/>
+      <c r="I204" s="52"/>
+      <c r="J204" s="52"/>
+      <c r="K204" s="52"/>
+      <c r="L204" s="52"/>
+      <c r="M204" s="52"/>
+      <c r="N204" s="52"/>
+      <c r="O204" s="52"/>
+      <c r="P204" s="52"/>
+      <c r="Q204" s="52"/>
+      <c r="R204" s="52"/>
+      <c r="S204" s="52"/>
+      <c r="T204" s="52"/>
+      <c r="U204" s="52"/>
+      <c r="V204" s="52"/>
+      <c r="W204" s="52"/>
+      <c r="X204" s="52"/>
+      <c r="Y204" s="52"/>
+      <c r="Z204" s="52"/>
+      <c r="AA204" s="52"/>
+      <c r="AB204" s="53"/>
       <c r="AC204" s="11"/>
     </row>
     <row r="205" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7974,27 +8013,27 @@
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
       <c r="G205" s="6"/>
-      <c r="H205" s="49"/>
-      <c r="I205" s="50"/>
-      <c r="J205" s="50"/>
-      <c r="K205" s="50"/>
-      <c r="L205" s="50"/>
-      <c r="M205" s="50"/>
-      <c r="N205" s="50"/>
-      <c r="O205" s="50"/>
-      <c r="P205" s="50"/>
-      <c r="Q205" s="50"/>
-      <c r="R205" s="50"/>
-      <c r="S205" s="50"/>
-      <c r="T205" s="50"/>
-      <c r="U205" s="50"/>
-      <c r="V205" s="50"/>
-      <c r="W205" s="50"/>
-      <c r="X205" s="50"/>
-      <c r="Y205" s="50"/>
-      <c r="Z205" s="50"/>
-      <c r="AA205" s="50"/>
-      <c r="AB205" s="51"/>
+      <c r="H205" s="51"/>
+      <c r="I205" s="52"/>
+      <c r="J205" s="52"/>
+      <c r="K205" s="52"/>
+      <c r="L205" s="52"/>
+      <c r="M205" s="52"/>
+      <c r="N205" s="52"/>
+      <c r="O205" s="52"/>
+      <c r="P205" s="52"/>
+      <c r="Q205" s="52"/>
+      <c r="R205" s="52"/>
+      <c r="S205" s="52"/>
+      <c r="T205" s="52"/>
+      <c r="U205" s="52"/>
+      <c r="V205" s="52"/>
+      <c r="W205" s="52"/>
+      <c r="X205" s="52"/>
+      <c r="Y205" s="52"/>
+      <c r="Z205" s="52"/>
+      <c r="AA205" s="52"/>
+      <c r="AB205" s="53"/>
       <c r="AC205" s="11"/>
     </row>
     <row r="206" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8004,27 +8043,27 @@
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
-      <c r="H206" s="49"/>
-      <c r="I206" s="50"/>
-      <c r="J206" s="50"/>
-      <c r="K206" s="50"/>
-      <c r="L206" s="50"/>
-      <c r="M206" s="50"/>
-      <c r="N206" s="50"/>
-      <c r="O206" s="50"/>
-      <c r="P206" s="50"/>
-      <c r="Q206" s="50"/>
-      <c r="R206" s="50"/>
-      <c r="S206" s="50"/>
-      <c r="T206" s="50"/>
-      <c r="U206" s="50"/>
-      <c r="V206" s="50"/>
-      <c r="W206" s="50"/>
-      <c r="X206" s="50"/>
-      <c r="Y206" s="50"/>
-      <c r="Z206" s="50"/>
-      <c r="AA206" s="50"/>
-      <c r="AB206" s="51"/>
+      <c r="H206" s="51"/>
+      <c r="I206" s="52"/>
+      <c r="J206" s="52"/>
+      <c r="K206" s="52"/>
+      <c r="L206" s="52"/>
+      <c r="M206" s="52"/>
+      <c r="N206" s="52"/>
+      <c r="O206" s="52"/>
+      <c r="P206" s="52"/>
+      <c r="Q206" s="52"/>
+      <c r="R206" s="52"/>
+      <c r="S206" s="52"/>
+      <c r="T206" s="52"/>
+      <c r="U206" s="52"/>
+      <c r="V206" s="52"/>
+      <c r="W206" s="52"/>
+      <c r="X206" s="52"/>
+      <c r="Y206" s="52"/>
+      <c r="Z206" s="52"/>
+      <c r="AA206" s="52"/>
+      <c r="AB206" s="53"/>
       <c r="AC206" s="11"/>
     </row>
     <row r="207" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8034,27 +8073,27 @@
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
-      <c r="H207" s="52"/>
-      <c r="I207" s="53"/>
-      <c r="J207" s="53"/>
-      <c r="K207" s="53"/>
-      <c r="L207" s="53"/>
-      <c r="M207" s="53"/>
-      <c r="N207" s="53"/>
-      <c r="O207" s="53"/>
-      <c r="P207" s="53"/>
-      <c r="Q207" s="53"/>
-      <c r="R207" s="53"/>
-      <c r="S207" s="53"/>
-      <c r="T207" s="53"/>
-      <c r="U207" s="53"/>
-      <c r="V207" s="53"/>
-      <c r="W207" s="53"/>
-      <c r="X207" s="53"/>
-      <c r="Y207" s="53"/>
-      <c r="Z207" s="53"/>
-      <c r="AA207" s="53"/>
-      <c r="AB207" s="54"/>
+      <c r="H207" s="54"/>
+      <c r="I207" s="55"/>
+      <c r="J207" s="55"/>
+      <c r="K207" s="55"/>
+      <c r="L207" s="55"/>
+      <c r="M207" s="55"/>
+      <c r="N207" s="55"/>
+      <c r="O207" s="55"/>
+      <c r="P207" s="55"/>
+      <c r="Q207" s="55"/>
+      <c r="R207" s="55"/>
+      <c r="S207" s="55"/>
+      <c r="T207" s="55"/>
+      <c r="U207" s="55"/>
+      <c r="V207" s="55"/>
+      <c r="W207" s="55"/>
+      <c r="X207" s="55"/>
+      <c r="Y207" s="55"/>
+      <c r="Z207" s="55"/>
+      <c r="AA207" s="55"/>
+      <c r="AB207" s="56"/>
       <c r="AC207" s="11"/>
     </row>
     <row r="208" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8096,27 +8135,27 @@
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
-      <c r="H209" s="46"/>
-      <c r="I209" s="47"/>
-      <c r="J209" s="47"/>
-      <c r="K209" s="47"/>
-      <c r="L209" s="47"/>
-      <c r="M209" s="47"/>
-      <c r="N209" s="47"/>
-      <c r="O209" s="47"/>
-      <c r="P209" s="47"/>
-      <c r="Q209" s="47"/>
-      <c r="R209" s="47"/>
-      <c r="S209" s="47"/>
-      <c r="T209" s="47"/>
-      <c r="U209" s="47"/>
-      <c r="V209" s="47"/>
-      <c r="W209" s="47"/>
-      <c r="X209" s="47"/>
-      <c r="Y209" s="47"/>
-      <c r="Z209" s="47"/>
-      <c r="AA209" s="47"/>
-      <c r="AB209" s="48"/>
+      <c r="H209" s="48"/>
+      <c r="I209" s="49"/>
+      <c r="J209" s="49"/>
+      <c r="K209" s="49"/>
+      <c r="L209" s="49"/>
+      <c r="M209" s="49"/>
+      <c r="N209" s="49"/>
+      <c r="O209" s="49"/>
+      <c r="P209" s="49"/>
+      <c r="Q209" s="49"/>
+      <c r="R209" s="49"/>
+      <c r="S209" s="49"/>
+      <c r="T209" s="49"/>
+      <c r="U209" s="49"/>
+      <c r="V209" s="49"/>
+      <c r="W209" s="49"/>
+      <c r="X209" s="49"/>
+      <c r="Y209" s="49"/>
+      <c r="Z209" s="49"/>
+      <c r="AA209" s="49"/>
+      <c r="AB209" s="50"/>
       <c r="AC209" s="11"/>
     </row>
     <row r="210" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8126,27 +8165,27 @@
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
-      <c r="H210" s="49"/>
-      <c r="I210" s="50"/>
-      <c r="J210" s="50"/>
-      <c r="K210" s="50"/>
-      <c r="L210" s="50"/>
-      <c r="M210" s="50"/>
-      <c r="N210" s="50"/>
-      <c r="O210" s="50"/>
-      <c r="P210" s="50"/>
-      <c r="Q210" s="50"/>
-      <c r="R210" s="50"/>
-      <c r="S210" s="50"/>
-      <c r="T210" s="50"/>
-      <c r="U210" s="50"/>
-      <c r="V210" s="50"/>
-      <c r="W210" s="50"/>
-      <c r="X210" s="50"/>
-      <c r="Y210" s="50"/>
-      <c r="Z210" s="50"/>
-      <c r="AA210" s="50"/>
-      <c r="AB210" s="51"/>
+      <c r="H210" s="51"/>
+      <c r="I210" s="52"/>
+      <c r="J210" s="52"/>
+      <c r="K210" s="52"/>
+      <c r="L210" s="52"/>
+      <c r="M210" s="52"/>
+      <c r="N210" s="52"/>
+      <c r="O210" s="52"/>
+      <c r="P210" s="52"/>
+      <c r="Q210" s="52"/>
+      <c r="R210" s="52"/>
+      <c r="S210" s="52"/>
+      <c r="T210" s="52"/>
+      <c r="U210" s="52"/>
+      <c r="V210" s="52"/>
+      <c r="W210" s="52"/>
+      <c r="X210" s="52"/>
+      <c r="Y210" s="52"/>
+      <c r="Z210" s="52"/>
+      <c r="AA210" s="52"/>
+      <c r="AB210" s="53"/>
       <c r="AC210" s="11"/>
     </row>
     <row r="211" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8156,27 +8195,27 @@
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
       <c r="G211" s="6"/>
-      <c r="H211" s="49"/>
-      <c r="I211" s="50"/>
-      <c r="J211" s="50"/>
-      <c r="K211" s="50"/>
-      <c r="L211" s="50"/>
-      <c r="M211" s="50"/>
-      <c r="N211" s="50"/>
-      <c r="O211" s="50"/>
-      <c r="P211" s="50"/>
-      <c r="Q211" s="50"/>
-      <c r="R211" s="50"/>
-      <c r="S211" s="50"/>
-      <c r="T211" s="50"/>
-      <c r="U211" s="50"/>
-      <c r="V211" s="50"/>
-      <c r="W211" s="50"/>
-      <c r="X211" s="50"/>
-      <c r="Y211" s="50"/>
-      <c r="Z211" s="50"/>
-      <c r="AA211" s="50"/>
-      <c r="AB211" s="51"/>
+      <c r="H211" s="51"/>
+      <c r="I211" s="52"/>
+      <c r="J211" s="52"/>
+      <c r="K211" s="52"/>
+      <c r="L211" s="52"/>
+      <c r="M211" s="52"/>
+      <c r="N211" s="52"/>
+      <c r="O211" s="52"/>
+      <c r="P211" s="52"/>
+      <c r="Q211" s="52"/>
+      <c r="R211" s="52"/>
+      <c r="S211" s="52"/>
+      <c r="T211" s="52"/>
+      <c r="U211" s="52"/>
+      <c r="V211" s="52"/>
+      <c r="W211" s="52"/>
+      <c r="X211" s="52"/>
+      <c r="Y211" s="52"/>
+      <c r="Z211" s="52"/>
+      <c r="AA211" s="52"/>
+      <c r="AB211" s="53"/>
       <c r="AC211" s="11"/>
     </row>
     <row r="212" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8186,27 +8225,27 @@
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
-      <c r="H212" s="49"/>
-      <c r="I212" s="50"/>
-      <c r="J212" s="50"/>
-      <c r="K212" s="50"/>
-      <c r="L212" s="50"/>
-      <c r="M212" s="50"/>
-      <c r="N212" s="50"/>
-      <c r="O212" s="50"/>
-      <c r="P212" s="50"/>
-      <c r="Q212" s="50"/>
-      <c r="R212" s="50"/>
-      <c r="S212" s="50"/>
-      <c r="T212" s="50"/>
-      <c r="U212" s="50"/>
-      <c r="V212" s="50"/>
-      <c r="W212" s="50"/>
-      <c r="X212" s="50"/>
-      <c r="Y212" s="50"/>
-      <c r="Z212" s="50"/>
-      <c r="AA212" s="50"/>
-      <c r="AB212" s="51"/>
+      <c r="H212" s="51"/>
+      <c r="I212" s="52"/>
+      <c r="J212" s="52"/>
+      <c r="K212" s="52"/>
+      <c r="L212" s="52"/>
+      <c r="M212" s="52"/>
+      <c r="N212" s="52"/>
+      <c r="O212" s="52"/>
+      <c r="P212" s="52"/>
+      <c r="Q212" s="52"/>
+      <c r="R212" s="52"/>
+      <c r="S212" s="52"/>
+      <c r="T212" s="52"/>
+      <c r="U212" s="52"/>
+      <c r="V212" s="52"/>
+      <c r="W212" s="52"/>
+      <c r="X212" s="52"/>
+      <c r="Y212" s="52"/>
+      <c r="Z212" s="52"/>
+      <c r="AA212" s="52"/>
+      <c r="AB212" s="53"/>
       <c r="AC212" s="11"/>
     </row>
     <row r="213" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8216,27 +8255,27 @@
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
       <c r="G213" s="6"/>
-      <c r="H213" s="49"/>
-      <c r="I213" s="50"/>
-      <c r="J213" s="50"/>
-      <c r="K213" s="50"/>
-      <c r="L213" s="50"/>
-      <c r="M213" s="50"/>
-      <c r="N213" s="50"/>
-      <c r="O213" s="50"/>
-      <c r="P213" s="50"/>
-      <c r="Q213" s="50"/>
-      <c r="R213" s="50"/>
-      <c r="S213" s="50"/>
-      <c r="T213" s="50"/>
-      <c r="U213" s="50"/>
-      <c r="V213" s="50"/>
-      <c r="W213" s="50"/>
-      <c r="X213" s="50"/>
-      <c r="Y213" s="50"/>
-      <c r="Z213" s="50"/>
-      <c r="AA213" s="50"/>
-      <c r="AB213" s="51"/>
+      <c r="H213" s="51"/>
+      <c r="I213" s="52"/>
+      <c r="J213" s="52"/>
+      <c r="K213" s="52"/>
+      <c r="L213" s="52"/>
+      <c r="M213" s="52"/>
+      <c r="N213" s="52"/>
+      <c r="O213" s="52"/>
+      <c r="P213" s="52"/>
+      <c r="Q213" s="52"/>
+      <c r="R213" s="52"/>
+      <c r="S213" s="52"/>
+      <c r="T213" s="52"/>
+      <c r="U213" s="52"/>
+      <c r="V213" s="52"/>
+      <c r="W213" s="52"/>
+      <c r="X213" s="52"/>
+      <c r="Y213" s="52"/>
+      <c r="Z213" s="52"/>
+      <c r="AA213" s="52"/>
+      <c r="AB213" s="53"/>
       <c r="AC213" s="11"/>
     </row>
     <row r="214" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8246,27 +8285,27 @@
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
       <c r="G214" s="6"/>
-      <c r="H214" s="49"/>
-      <c r="I214" s="50"/>
-      <c r="J214" s="50"/>
-      <c r="K214" s="50"/>
-      <c r="L214" s="50"/>
-      <c r="M214" s="50"/>
-      <c r="N214" s="50"/>
-      <c r="O214" s="50"/>
-      <c r="P214" s="50"/>
-      <c r="Q214" s="50"/>
-      <c r="R214" s="50"/>
-      <c r="S214" s="50"/>
-      <c r="T214" s="50"/>
-      <c r="U214" s="50"/>
-      <c r="V214" s="50"/>
-      <c r="W214" s="50"/>
-      <c r="X214" s="50"/>
-      <c r="Y214" s="50"/>
-      <c r="Z214" s="50"/>
-      <c r="AA214" s="50"/>
-      <c r="AB214" s="51"/>
+      <c r="H214" s="51"/>
+      <c r="I214" s="52"/>
+      <c r="J214" s="52"/>
+      <c r="K214" s="52"/>
+      <c r="L214" s="52"/>
+      <c r="M214" s="52"/>
+      <c r="N214" s="52"/>
+      <c r="O214" s="52"/>
+      <c r="P214" s="52"/>
+      <c r="Q214" s="52"/>
+      <c r="R214" s="52"/>
+      <c r="S214" s="52"/>
+      <c r="T214" s="52"/>
+      <c r="U214" s="52"/>
+      <c r="V214" s="52"/>
+      <c r="W214" s="52"/>
+      <c r="X214" s="52"/>
+      <c r="Y214" s="52"/>
+      <c r="Z214" s="52"/>
+      <c r="AA214" s="52"/>
+      <c r="AB214" s="53"/>
       <c r="AC214" s="11"/>
     </row>
     <row r="215" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8276,27 +8315,27 @@
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
       <c r="G215" s="6"/>
-      <c r="H215" s="52"/>
-      <c r="I215" s="53"/>
-      <c r="J215" s="53"/>
-      <c r="K215" s="53"/>
-      <c r="L215" s="53"/>
-      <c r="M215" s="53"/>
-      <c r="N215" s="53"/>
-      <c r="O215" s="53"/>
-      <c r="P215" s="53"/>
-      <c r="Q215" s="53"/>
-      <c r="R215" s="53"/>
-      <c r="S215" s="53"/>
-      <c r="T215" s="53"/>
-      <c r="U215" s="53"/>
-      <c r="V215" s="53"/>
-      <c r="W215" s="53"/>
-      <c r="X215" s="53"/>
-      <c r="Y215" s="53"/>
-      <c r="Z215" s="53"/>
-      <c r="AA215" s="53"/>
-      <c r="AB215" s="54"/>
+      <c r="H215" s="54"/>
+      <c r="I215" s="55"/>
+      <c r="J215" s="55"/>
+      <c r="K215" s="55"/>
+      <c r="L215" s="55"/>
+      <c r="M215" s="55"/>
+      <c r="N215" s="55"/>
+      <c r="O215" s="55"/>
+      <c r="P215" s="55"/>
+      <c r="Q215" s="55"/>
+      <c r="R215" s="55"/>
+      <c r="S215" s="55"/>
+      <c r="T215" s="55"/>
+      <c r="U215" s="55"/>
+      <c r="V215" s="55"/>
+      <c r="W215" s="55"/>
+      <c r="X215" s="55"/>
+      <c r="Y215" s="55"/>
+      <c r="Z215" s="55"/>
+      <c r="AA215" s="55"/>
+      <c r="AB215" s="56"/>
       <c r="AC215" s="11"/>
     </row>
     <row r="216" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8331,11 +8370,38 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B180:B197"/>
+    <mergeCell ref="D182:E182"/>
+    <mergeCell ref="H182:AB188"/>
+    <mergeCell ref="H190:AB196"/>
+    <mergeCell ref="B199:B216"/>
+    <mergeCell ref="D201:E201"/>
+    <mergeCell ref="H201:AB207"/>
+    <mergeCell ref="H209:AB215"/>
+    <mergeCell ref="B142:B159"/>
+    <mergeCell ref="D144:E144"/>
+    <mergeCell ref="H144:AB150"/>
+    <mergeCell ref="H152:AB158"/>
+    <mergeCell ref="B161:B178"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="H163:AB169"/>
+    <mergeCell ref="H171:AB177"/>
+    <mergeCell ref="B104:B121"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="H106:AB112"/>
+    <mergeCell ref="H114:AB120"/>
+    <mergeCell ref="B123:B140"/>
+    <mergeCell ref="D125:E125"/>
+    <mergeCell ref="H125:AB131"/>
+    <mergeCell ref="H133:AB139"/>
+    <mergeCell ref="B63:B83"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="H76:AB82"/>
+    <mergeCell ref="B85:B102"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="H87:AB93"/>
+    <mergeCell ref="H95:AB101"/>
+    <mergeCell ref="H65:AB74"/>
     <mergeCell ref="B25:B42"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="H27:AB33"/>
@@ -8344,41 +8410,16 @@
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="H46:AB52"/>
     <mergeCell ref="H54:AB60"/>
-    <mergeCell ref="B63:B83"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="H76:AB82"/>
-    <mergeCell ref="B85:B102"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="H87:AB93"/>
-    <mergeCell ref="H95:AB101"/>
-    <mergeCell ref="H65:AB74"/>
-    <mergeCell ref="B104:B121"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="H106:AB112"/>
-    <mergeCell ref="H114:AB120"/>
-    <mergeCell ref="B123:B140"/>
-    <mergeCell ref="D125:E125"/>
-    <mergeCell ref="H125:AB131"/>
-    <mergeCell ref="H133:AB139"/>
-    <mergeCell ref="B142:B159"/>
-    <mergeCell ref="D144:E144"/>
-    <mergeCell ref="H144:AB150"/>
-    <mergeCell ref="H152:AB158"/>
-    <mergeCell ref="B161:B178"/>
-    <mergeCell ref="D163:E163"/>
-    <mergeCell ref="H163:AB169"/>
-    <mergeCell ref="H171:AB177"/>
-    <mergeCell ref="B180:B197"/>
-    <mergeCell ref="D182:E182"/>
-    <mergeCell ref="H182:AB188"/>
-    <mergeCell ref="H190:AB196"/>
-    <mergeCell ref="B199:B216"/>
-    <mergeCell ref="D201:E201"/>
-    <mergeCell ref="H201:AB207"/>
-    <mergeCell ref="H209:AB215"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H65" r:id="rId1" display="https://learn.microsoft.com/en-us/dotnet/maui/platform-integration/device/geolocation" xr:uid="{6A2F2CBC-218B-43EA-806A-9BF39365BDB2}"/>
+    <hyperlink ref="H87" r:id="rId2" display="https://dummyjson.com/docs/posts_x000a_" xr:uid="{AFA4F006-3754-4C92-A758-50B6915FC379}"/>
+    <hyperlink ref="H106" r:id="rId3" display="https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/refreshview_x000a_" xr:uid="{80E066CC-CE62-4304-89CB-2C900A3EBBE5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -8405,11 +8446,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>21</v>
       </c>
@@ -9251,27 +9292,27 @@
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" s="19"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="47"/>
-      <c r="U34" s="47"/>
-      <c r="V34" s="47"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="47"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="47"/>
-      <c r="AA34" s="47"/>
-      <c r="AB34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="49"/>
+      <c r="L34" s="49"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="49"/>
+      <c r="P34" s="49"/>
+      <c r="Q34" s="49"/>
+      <c r="R34" s="49"/>
+      <c r="S34" s="49"/>
+      <c r="T34" s="49"/>
+      <c r="U34" s="49"/>
+      <c r="V34" s="49"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="49"/>
+      <c r="Y34" s="49"/>
+      <c r="Z34" s="49"/>
+      <c r="AA34" s="49"/>
+      <c r="AB34" s="50"/>
       <c r="AC34" s="16"/>
     </row>
     <row r="35" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9281,27 +9322,27 @@
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50"/>
-      <c r="S35" s="50"/>
-      <c r="T35" s="50"/>
-      <c r="U35" s="50"/>
-      <c r="V35" s="50"/>
-      <c r="W35" s="50"/>
-      <c r="X35" s="50"/>
-      <c r="Y35" s="50"/>
-      <c r="Z35" s="50"/>
-      <c r="AA35" s="50"/>
-      <c r="AB35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="52"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="52"/>
+      <c r="X35" s="52"/>
+      <c r="Y35" s="52"/>
+      <c r="Z35" s="52"/>
+      <c r="AA35" s="52"/>
+      <c r="AB35" s="53"/>
       <c r="AC35" s="16"/>
     </row>
     <row r="36" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9311,27 +9352,27 @@
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="50"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
-      <c r="Y36" s="50"/>
-      <c r="Z36" s="50"/>
-      <c r="AA36" s="50"/>
-      <c r="AB36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="52"/>
+      <c r="Q36" s="52"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="52"/>
+      <c r="T36" s="52"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="52"/>
+      <c r="W36" s="52"/>
+      <c r="X36" s="52"/>
+      <c r="Y36" s="52"/>
+      <c r="Z36" s="52"/>
+      <c r="AA36" s="52"/>
+      <c r="AB36" s="53"/>
       <c r="AC36" s="16"/>
     </row>
     <row r="37" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9341,27 +9382,27 @@
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="50"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+      <c r="O37" s="52"/>
+      <c r="P37" s="52"/>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="52"/>
+      <c r="T37" s="52"/>
+      <c r="U37" s="52"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="52"/>
+      <c r="X37" s="52"/>
+      <c r="Y37" s="52"/>
+      <c r="Z37" s="52"/>
+      <c r="AA37" s="52"/>
+      <c r="AB37" s="53"/>
       <c r="AC37" s="16"/>
     </row>
     <row r="38" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9371,27 +9412,27 @@
       <c r="E38" s="19"/>
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50"/>
-      <c r="S38" s="50"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="50"/>
-      <c r="Y38" s="50"/>
-      <c r="Z38" s="50"/>
-      <c r="AA38" s="50"/>
-      <c r="AB38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="52"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="52"/>
+      <c r="X38" s="52"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="52"/>
+      <c r="AA38" s="52"/>
+      <c r="AB38" s="53"/>
       <c r="AC38" s="16"/>
     </row>
     <row r="39" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9401,27 +9442,27 @@
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50"/>
-      <c r="Y39" s="50"/>
-      <c r="Z39" s="50"/>
-      <c r="AA39" s="50"/>
-      <c r="AB39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="52"/>
+      <c r="P39" s="52"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="52"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="52"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="52"/>
+      <c r="X39" s="52"/>
+      <c r="Y39" s="52"/>
+      <c r="Z39" s="52"/>
+      <c r="AA39" s="52"/>
+      <c r="AB39" s="53"/>
       <c r="AC39" s="16"/>
     </row>
     <row r="40" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9431,27 +9472,27 @@
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="53"/>
-      <c r="N40" s="53"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="53"/>
-      <c r="Q40" s="53"/>
-      <c r="R40" s="53"/>
-      <c r="S40" s="53"/>
-      <c r="T40" s="53"/>
-      <c r="U40" s="53"/>
-      <c r="V40" s="53"/>
-      <c r="W40" s="53"/>
-      <c r="X40" s="53"/>
-      <c r="Y40" s="53"/>
-      <c r="Z40" s="53"/>
-      <c r="AA40" s="53"/>
-      <c r="AB40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="55"/>
+      <c r="R40" s="55"/>
+      <c r="S40" s="55"/>
+      <c r="T40" s="55"/>
+      <c r="U40" s="55"/>
+      <c r="V40" s="55"/>
+      <c r="W40" s="55"/>
+      <c r="X40" s="55"/>
+      <c r="Y40" s="55"/>
+      <c r="Z40" s="55"/>
+      <c r="AA40" s="55"/>
+      <c r="AB40" s="56"/>
       <c r="AC40" s="16"/>
     </row>
     <row r="41" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9493,27 +9534,27 @@
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
       <c r="G42" s="19"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="47"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47"/>
-      <c r="S42" s="47"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="47"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="47"/>
-      <c r="X42" s="47"/>
-      <c r="Y42" s="47"/>
-      <c r="Z42" s="47"/>
-      <c r="AA42" s="47"/>
-      <c r="AB42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="49"/>
+      <c r="O42" s="49"/>
+      <c r="P42" s="49"/>
+      <c r="Q42" s="49"/>
+      <c r="R42" s="49"/>
+      <c r="S42" s="49"/>
+      <c r="T42" s="49"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="49"/>
+      <c r="W42" s="49"/>
+      <c r="X42" s="49"/>
+      <c r="Y42" s="49"/>
+      <c r="Z42" s="49"/>
+      <c r="AA42" s="49"/>
+      <c r="AB42" s="50"/>
       <c r="AC42" s="16"/>
     </row>
     <row r="43" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9523,27 +9564,27 @@
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="50"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="50"/>
-      <c r="AA43" s="50"/>
-      <c r="AB43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="52"/>
+      <c r="L43" s="52"/>
+      <c r="M43" s="52"/>
+      <c r="N43" s="52"/>
+      <c r="O43" s="52"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="52"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="52"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="52"/>
+      <c r="W43" s="52"/>
+      <c r="X43" s="52"/>
+      <c r="Y43" s="52"/>
+      <c r="Z43" s="52"/>
+      <c r="AA43" s="52"/>
+      <c r="AB43" s="53"/>
       <c r="AC43" s="16"/>
     </row>
     <row r="44" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9553,27 +9594,27 @@
       <c r="E44" s="19"/>
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="50"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50"/>
-      <c r="S44" s="50"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
-      <c r="V44" s="50"/>
-      <c r="W44" s="50"/>
-      <c r="X44" s="50"/>
-      <c r="Y44" s="50"/>
-      <c r="Z44" s="50"/>
-      <c r="AA44" s="50"/>
-      <c r="AB44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="52"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="52"/>
+      <c r="O44" s="52"/>
+      <c r="P44" s="52"/>
+      <c r="Q44" s="52"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="52"/>
+      <c r="T44" s="52"/>
+      <c r="U44" s="52"/>
+      <c r="V44" s="52"/>
+      <c r="W44" s="52"/>
+      <c r="X44" s="52"/>
+      <c r="Y44" s="52"/>
+      <c r="Z44" s="52"/>
+      <c r="AA44" s="52"/>
+      <c r="AB44" s="53"/>
       <c r="AC44" s="16"/>
     </row>
     <row r="45" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9583,27 +9624,27 @@
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="50"/>
-      <c r="O45" s="50"/>
-      <c r="P45" s="50"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50"/>
-      <c r="S45" s="50"/>
-      <c r="T45" s="50"/>
-      <c r="U45" s="50"/>
-      <c r="V45" s="50"/>
-      <c r="W45" s="50"/>
-      <c r="X45" s="50"/>
-      <c r="Y45" s="50"/>
-      <c r="Z45" s="50"/>
-      <c r="AA45" s="50"/>
-      <c r="AB45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="52"/>
+      <c r="O45" s="52"/>
+      <c r="P45" s="52"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="52"/>
+      <c r="V45" s="52"/>
+      <c r="W45" s="52"/>
+      <c r="X45" s="52"/>
+      <c r="Y45" s="52"/>
+      <c r="Z45" s="52"/>
+      <c r="AA45" s="52"/>
+      <c r="AB45" s="53"/>
       <c r="AC45" s="16"/>
     </row>
     <row r="46" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9613,27 +9654,27 @@
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="50"/>
-      <c r="J46" s="50"/>
-      <c r="K46" s="50"/>
-      <c r="L46" s="50"/>
-      <c r="M46" s="50"/>
-      <c r="N46" s="50"/>
-      <c r="O46" s="50"/>
-      <c r="P46" s="50"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50"/>
-      <c r="S46" s="50"/>
-      <c r="T46" s="50"/>
-      <c r="U46" s="50"/>
-      <c r="V46" s="50"/>
-      <c r="W46" s="50"/>
-      <c r="X46" s="50"/>
-      <c r="Y46" s="50"/>
-      <c r="Z46" s="50"/>
-      <c r="AA46" s="50"/>
-      <c r="AB46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="52"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="52"/>
+      <c r="O46" s="52"/>
+      <c r="P46" s="52"/>
+      <c r="Q46" s="52"/>
+      <c r="R46" s="52"/>
+      <c r="S46" s="52"/>
+      <c r="T46" s="52"/>
+      <c r="U46" s="52"/>
+      <c r="V46" s="52"/>
+      <c r="W46" s="52"/>
+      <c r="X46" s="52"/>
+      <c r="Y46" s="52"/>
+      <c r="Z46" s="52"/>
+      <c r="AA46" s="52"/>
+      <c r="AB46" s="53"/>
       <c r="AC46" s="16"/>
     </row>
     <row r="47" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9643,27 +9684,27 @@
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
       <c r="G47" s="19"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="50"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="50"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50"/>
-      <c r="S47" s="50"/>
-      <c r="T47" s="50"/>
-      <c r="U47" s="50"/>
-      <c r="V47" s="50"/>
-      <c r="W47" s="50"/>
-      <c r="X47" s="50"/>
-      <c r="Y47" s="50"/>
-      <c r="Z47" s="50"/>
-      <c r="AA47" s="50"/>
-      <c r="AB47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="52"/>
+      <c r="M47" s="52"/>
+      <c r="N47" s="52"/>
+      <c r="O47" s="52"/>
+      <c r="P47" s="52"/>
+      <c r="Q47" s="52"/>
+      <c r="R47" s="52"/>
+      <c r="S47" s="52"/>
+      <c r="T47" s="52"/>
+      <c r="U47" s="52"/>
+      <c r="V47" s="52"/>
+      <c r="W47" s="52"/>
+      <c r="X47" s="52"/>
+      <c r="Y47" s="52"/>
+      <c r="Z47" s="52"/>
+      <c r="AA47" s="52"/>
+      <c r="AB47" s="53"/>
       <c r="AC47" s="16"/>
     </row>
     <row r="48" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9673,27 +9714,27 @@
       <c r="E48" s="19"/>
       <c r="F48" s="19"/>
       <c r="G48" s="19"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="53"/>
-      <c r="T48" s="53"/>
-      <c r="U48" s="53"/>
-      <c r="V48" s="53"/>
-      <c r="W48" s="53"/>
-      <c r="X48" s="53"/>
-      <c r="Y48" s="53"/>
-      <c r="Z48" s="53"/>
-      <c r="AA48" s="53"/>
-      <c r="AB48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="55"/>
+      <c r="K48" s="55"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
+      <c r="O48" s="55"/>
+      <c r="P48" s="55"/>
+      <c r="Q48" s="55"/>
+      <c r="R48" s="55"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="55"/>
+      <c r="U48" s="55"/>
+      <c r="V48" s="55"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="55"/>
+      <c r="Y48" s="55"/>
+      <c r="Z48" s="55"/>
+      <c r="AA48" s="55"/>
+      <c r="AB48" s="56"/>
       <c r="AC48" s="16"/>
     </row>
     <row r="49" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9766,11 +9807,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
@@ -10575,11 +10616,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>33</v>
       </c>
@@ -11717,11 +11758,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>34</v>
       </c>
@@ -14468,11 +14509,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B66:B83"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="H68:AB74"/>
+    <mergeCell ref="H76:AB82"/>
+    <mergeCell ref="B86:B103"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="H88:AB94"/>
+    <mergeCell ref="H96:AB102"/>
     <mergeCell ref="B26:B43"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="H28:AB34"/>
@@ -14481,14 +14525,11 @@
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="H48:AB54"/>
     <mergeCell ref="H56:AB62"/>
-    <mergeCell ref="B66:B83"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="H68:AB74"/>
-    <mergeCell ref="H76:AB82"/>
-    <mergeCell ref="B86:B103"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="H88:AB94"/>
-    <mergeCell ref="H96:AB102"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -14515,11 +14556,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>41</v>
       </c>

--- a/Projekttagebuch.xlsx
+++ b/Projekttagebuch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\projects\GW.Demo.Maui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4A69A8-43B1-4CCB-BFD7-CED0A21CD247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0FEF5D-B9F5-4CEF-979F-DC51AEA9698A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
   </bookViews>
@@ -235,9 +235,6 @@
 https://medium.com/@cristian_lopes/net-maui-flyout-navigation-tab-navigation-ca62913c98fa</t>
   </si>
   <si>
-    <t>166</t>
-  </si>
-  <si>
     <t>Menü-Commands feuern nicht, mühsam, Video und AI haben geholfen.
 Um das mit Commands zu machen, musste ich dann noch weiter rumzangeln. Richtiges VM haben wir so einmal nicht.</t>
   </si>
@@ -277,9 +274,6 @@
     <t>48</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/listview
 https://www.codemag.com/Article/2503021/Exploring-.NET-MAUI-Working-with-Lists-of-Data
 https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/collectionview
@@ -289,6 +283,12 @@
   </si>
   <si>
     <t>Im Großen und Ganzen wenig problematisch. Dokumentation ok. Wieder Binding-Fehler, wenn man das schon öfter gehabt hat, tut man sich leichter, CoPilot hilft zT. auch aus.</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>162</t>
   </si>
 </sst>
 </file>
@@ -3374,7 +3374,7 @@
       <c r="B46" s="44"/>
       <c r="C46" s="5"/>
       <c r="D46" s="41" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E46" s="42"/>
       <c r="F46" s="6" t="s">
@@ -3626,7 +3626,7 @@
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I54" s="33"/>
       <c r="J54" s="33"/>
@@ -3930,7 +3930,7 @@
       <c r="B65" s="44"/>
       <c r="C65" s="5"/>
       <c r="D65" s="41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E65" s="42"/>
       <c r="F65" s="6" t="s">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I65" s="33"/>
       <c r="J65" s="33"/>
@@ -4272,7 +4272,7 @@
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I76" s="33"/>
       <c r="J76" s="33"/>
@@ -4576,7 +4576,7 @@
       <c r="B87" s="44"/>
       <c r="C87" s="5"/>
       <c r="D87" s="41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E87" s="42"/>
       <c r="F87" s="6" t="s">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I87" s="33"/>
       <c r="J87" s="33"/>
@@ -4828,7 +4828,7 @@
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I95" s="33"/>
       <c r="J95" s="33"/>
@@ -5132,7 +5132,7 @@
       <c r="B106" s="44"/>
       <c r="C106" s="5"/>
       <c r="D106" s="41" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E106" s="42"/>
       <c r="F106" s="6" t="s">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="G106" s="6"/>
       <c r="H106" s="32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I106" s="33"/>
       <c r="J106" s="33"/>
@@ -5384,7 +5384,7 @@
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I114" s="33"/>
       <c r="J114" s="33"/>

--- a/Projekttagebuch.xlsx
+++ b/Projekttagebuch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\projects\GW.Demo.Maui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0FEF5D-B9F5-4CEF-979F-DC51AEA9698A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBF2A8D-30D6-4535-A3DB-09311CFBC2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="71">
   <si>
     <t>Framework:</t>
   </si>
@@ -289,6 +289,17 @@
   </si>
   <si>
     <t>162</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/de-de/dotnet/communitytoolkit/maui/views/mediaelement
+https://www.c-sharpcorner.com/article/net-maui-video-player-using-community-toolkit/
+https://www.infoq.com/news/2023/02/dot-net-maui-mediaelement/</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>MediaElement ist eher komfortabel.</t>
   </si>
 </sst>
 </file>
@@ -620,12 +631,6 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -652,6 +657,12 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2185,11 +2196,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>11</v>
       </c>
@@ -5687,33 +5698,37 @@
     <row r="125" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" s="44"/>
       <c r="C125" s="5"/>
-      <c r="D125" s="41"/>
+      <c r="D125" s="41" t="s">
+        <v>69</v>
+      </c>
       <c r="E125" s="42"/>
       <c r="F125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G125" s="6"/>
-      <c r="H125" s="48"/>
-      <c r="I125" s="49"/>
-      <c r="J125" s="49"/>
-      <c r="K125" s="49"/>
-      <c r="L125" s="49"/>
-      <c r="M125" s="49"/>
-      <c r="N125" s="49"/>
-      <c r="O125" s="49"/>
-      <c r="P125" s="49"/>
-      <c r="Q125" s="49"/>
-      <c r="R125" s="49"/>
-      <c r="S125" s="49"/>
-      <c r="T125" s="49"/>
-      <c r="U125" s="49"/>
-      <c r="V125" s="49"/>
-      <c r="W125" s="49"/>
-      <c r="X125" s="49"/>
-      <c r="Y125" s="49"/>
-      <c r="Z125" s="49"/>
-      <c r="AA125" s="49"/>
-      <c r="AB125" s="50"/>
+      <c r="H125" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="I125" s="33"/>
+      <c r="J125" s="33"/>
+      <c r="K125" s="33"/>
+      <c r="L125" s="33"/>
+      <c r="M125" s="33"/>
+      <c r="N125" s="33"/>
+      <c r="O125" s="33"/>
+      <c r="P125" s="33"/>
+      <c r="Q125" s="33"/>
+      <c r="R125" s="33"/>
+      <c r="S125" s="33"/>
+      <c r="T125" s="33"/>
+      <c r="U125" s="33"/>
+      <c r="V125" s="33"/>
+      <c r="W125" s="33"/>
+      <c r="X125" s="33"/>
+      <c r="Y125" s="33"/>
+      <c r="Z125" s="33"/>
+      <c r="AA125" s="33"/>
+      <c r="AB125" s="34"/>
       <c r="AC125" s="11"/>
     </row>
     <row r="126" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5723,27 +5738,27 @@
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
-      <c r="H126" s="51"/>
-      <c r="I126" s="52"/>
-      <c r="J126" s="52"/>
-      <c r="K126" s="52"/>
-      <c r="L126" s="52"/>
-      <c r="M126" s="52"/>
-      <c r="N126" s="52"/>
-      <c r="O126" s="52"/>
-      <c r="P126" s="52"/>
-      <c r="Q126" s="52"/>
-      <c r="R126" s="52"/>
-      <c r="S126" s="52"/>
-      <c r="T126" s="52"/>
-      <c r="U126" s="52"/>
-      <c r="V126" s="52"/>
-      <c r="W126" s="52"/>
-      <c r="X126" s="52"/>
-      <c r="Y126" s="52"/>
-      <c r="Z126" s="52"/>
-      <c r="AA126" s="52"/>
-      <c r="AB126" s="53"/>
+      <c r="H126" s="35"/>
+      <c r="I126" s="36"/>
+      <c r="J126" s="36"/>
+      <c r="K126" s="36"/>
+      <c r="L126" s="36"/>
+      <c r="M126" s="36"/>
+      <c r="N126" s="36"/>
+      <c r="O126" s="36"/>
+      <c r="P126" s="36"/>
+      <c r="Q126" s="36"/>
+      <c r="R126" s="36"/>
+      <c r="S126" s="36"/>
+      <c r="T126" s="36"/>
+      <c r="U126" s="36"/>
+      <c r="V126" s="36"/>
+      <c r="W126" s="36"/>
+      <c r="X126" s="36"/>
+      <c r="Y126" s="36"/>
+      <c r="Z126" s="36"/>
+      <c r="AA126" s="36"/>
+      <c r="AB126" s="37"/>
       <c r="AC126" s="11"/>
     </row>
     <row r="127" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5753,27 +5768,27 @@
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
-      <c r="H127" s="51"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="52"/>
-      <c r="K127" s="52"/>
-      <c r="L127" s="52"/>
-      <c r="M127" s="52"/>
-      <c r="N127" s="52"/>
-      <c r="O127" s="52"/>
-      <c r="P127" s="52"/>
-      <c r="Q127" s="52"/>
-      <c r="R127" s="52"/>
-      <c r="S127" s="52"/>
-      <c r="T127" s="52"/>
-      <c r="U127" s="52"/>
-      <c r="V127" s="52"/>
-      <c r="W127" s="52"/>
-      <c r="X127" s="52"/>
-      <c r="Y127" s="52"/>
-      <c r="Z127" s="52"/>
-      <c r="AA127" s="52"/>
-      <c r="AB127" s="53"/>
+      <c r="H127" s="35"/>
+      <c r="I127" s="36"/>
+      <c r="J127" s="36"/>
+      <c r="K127" s="36"/>
+      <c r="L127" s="36"/>
+      <c r="M127" s="36"/>
+      <c r="N127" s="36"/>
+      <c r="O127" s="36"/>
+      <c r="P127" s="36"/>
+      <c r="Q127" s="36"/>
+      <c r="R127" s="36"/>
+      <c r="S127" s="36"/>
+      <c r="T127" s="36"/>
+      <c r="U127" s="36"/>
+      <c r="V127" s="36"/>
+      <c r="W127" s="36"/>
+      <c r="X127" s="36"/>
+      <c r="Y127" s="36"/>
+      <c r="Z127" s="36"/>
+      <c r="AA127" s="36"/>
+      <c r="AB127" s="37"/>
       <c r="AC127" s="11"/>
     </row>
     <row r="128" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5783,27 +5798,27 @@
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
-      <c r="H128" s="51"/>
-      <c r="I128" s="52"/>
-      <c r="J128" s="52"/>
-      <c r="K128" s="52"/>
-      <c r="L128" s="52"/>
-      <c r="M128" s="52"/>
-      <c r="N128" s="52"/>
-      <c r="O128" s="52"/>
-      <c r="P128" s="52"/>
-      <c r="Q128" s="52"/>
-      <c r="R128" s="52"/>
-      <c r="S128" s="52"/>
-      <c r="T128" s="52"/>
-      <c r="U128" s="52"/>
-      <c r="V128" s="52"/>
-      <c r="W128" s="52"/>
-      <c r="X128" s="52"/>
-      <c r="Y128" s="52"/>
-      <c r="Z128" s="52"/>
-      <c r="AA128" s="52"/>
-      <c r="AB128" s="53"/>
+      <c r="H128" s="35"/>
+      <c r="I128" s="36"/>
+      <c r="J128" s="36"/>
+      <c r="K128" s="36"/>
+      <c r="L128" s="36"/>
+      <c r="M128" s="36"/>
+      <c r="N128" s="36"/>
+      <c r="O128" s="36"/>
+      <c r="P128" s="36"/>
+      <c r="Q128" s="36"/>
+      <c r="R128" s="36"/>
+      <c r="S128" s="36"/>
+      <c r="T128" s="36"/>
+      <c r="U128" s="36"/>
+      <c r="V128" s="36"/>
+      <c r="W128" s="36"/>
+      <c r="X128" s="36"/>
+      <c r="Y128" s="36"/>
+      <c r="Z128" s="36"/>
+      <c r="AA128" s="36"/>
+      <c r="AB128" s="37"/>
       <c r="AC128" s="11"/>
     </row>
     <row r="129" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5813,27 +5828,27 @@
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
-      <c r="H129" s="51"/>
-      <c r="I129" s="52"/>
-      <c r="J129" s="52"/>
-      <c r="K129" s="52"/>
-      <c r="L129" s="52"/>
-      <c r="M129" s="52"/>
-      <c r="N129" s="52"/>
-      <c r="O129" s="52"/>
-      <c r="P129" s="52"/>
-      <c r="Q129" s="52"/>
-      <c r="R129" s="52"/>
-      <c r="S129" s="52"/>
-      <c r="T129" s="52"/>
-      <c r="U129" s="52"/>
-      <c r="V129" s="52"/>
-      <c r="W129" s="52"/>
-      <c r="X129" s="52"/>
-      <c r="Y129" s="52"/>
-      <c r="Z129" s="52"/>
-      <c r="AA129" s="52"/>
-      <c r="AB129" s="53"/>
+      <c r="H129" s="35"/>
+      <c r="I129" s="36"/>
+      <c r="J129" s="36"/>
+      <c r="K129" s="36"/>
+      <c r="L129" s="36"/>
+      <c r="M129" s="36"/>
+      <c r="N129" s="36"/>
+      <c r="O129" s="36"/>
+      <c r="P129" s="36"/>
+      <c r="Q129" s="36"/>
+      <c r="R129" s="36"/>
+      <c r="S129" s="36"/>
+      <c r="T129" s="36"/>
+      <c r="U129" s="36"/>
+      <c r="V129" s="36"/>
+      <c r="W129" s="36"/>
+      <c r="X129" s="36"/>
+      <c r="Y129" s="36"/>
+      <c r="Z129" s="36"/>
+      <c r="AA129" s="36"/>
+      <c r="AB129" s="37"/>
       <c r="AC129" s="11"/>
     </row>
     <row r="130" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5843,27 +5858,27 @@
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
-      <c r="H130" s="51"/>
-      <c r="I130" s="52"/>
-      <c r="J130" s="52"/>
-      <c r="K130" s="52"/>
-      <c r="L130" s="52"/>
-      <c r="M130" s="52"/>
-      <c r="N130" s="52"/>
-      <c r="O130" s="52"/>
-      <c r="P130" s="52"/>
-      <c r="Q130" s="52"/>
-      <c r="R130" s="52"/>
-      <c r="S130" s="52"/>
-      <c r="T130" s="52"/>
-      <c r="U130" s="52"/>
-      <c r="V130" s="52"/>
-      <c r="W130" s="52"/>
-      <c r="X130" s="52"/>
-      <c r="Y130" s="52"/>
-      <c r="Z130" s="52"/>
-      <c r="AA130" s="52"/>
-      <c r="AB130" s="53"/>
+      <c r="H130" s="35"/>
+      <c r="I130" s="36"/>
+      <c r="J130" s="36"/>
+      <c r="K130" s="36"/>
+      <c r="L130" s="36"/>
+      <c r="M130" s="36"/>
+      <c r="N130" s="36"/>
+      <c r="O130" s="36"/>
+      <c r="P130" s="36"/>
+      <c r="Q130" s="36"/>
+      <c r="R130" s="36"/>
+      <c r="S130" s="36"/>
+      <c r="T130" s="36"/>
+      <c r="U130" s="36"/>
+      <c r="V130" s="36"/>
+      <c r="W130" s="36"/>
+      <c r="X130" s="36"/>
+      <c r="Y130" s="36"/>
+      <c r="Z130" s="36"/>
+      <c r="AA130" s="36"/>
+      <c r="AB130" s="37"/>
       <c r="AC130" s="11"/>
     </row>
     <row r="131" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5873,27 +5888,27 @@
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
-      <c r="H131" s="54"/>
-      <c r="I131" s="55"/>
-      <c r="J131" s="55"/>
-      <c r="K131" s="55"/>
-      <c r="L131" s="55"/>
-      <c r="M131" s="55"/>
-      <c r="N131" s="55"/>
-      <c r="O131" s="55"/>
-      <c r="P131" s="55"/>
-      <c r="Q131" s="55"/>
-      <c r="R131" s="55"/>
-      <c r="S131" s="55"/>
-      <c r="T131" s="55"/>
-      <c r="U131" s="55"/>
-      <c r="V131" s="55"/>
-      <c r="W131" s="55"/>
-      <c r="X131" s="55"/>
-      <c r="Y131" s="55"/>
-      <c r="Z131" s="55"/>
-      <c r="AA131" s="55"/>
-      <c r="AB131" s="56"/>
+      <c r="H131" s="38"/>
+      <c r="I131" s="39"/>
+      <c r="J131" s="39"/>
+      <c r="K131" s="39"/>
+      <c r="L131" s="39"/>
+      <c r="M131" s="39"/>
+      <c r="N131" s="39"/>
+      <c r="O131" s="39"/>
+      <c r="P131" s="39"/>
+      <c r="Q131" s="39"/>
+      <c r="R131" s="39"/>
+      <c r="S131" s="39"/>
+      <c r="T131" s="39"/>
+      <c r="U131" s="39"/>
+      <c r="V131" s="39"/>
+      <c r="W131" s="39"/>
+      <c r="X131" s="39"/>
+      <c r="Y131" s="39"/>
+      <c r="Z131" s="39"/>
+      <c r="AA131" s="39"/>
+      <c r="AB131" s="40"/>
       <c r="AC131" s="11"/>
     </row>
     <row r="132" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5935,27 +5950,29 @@
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="48"/>
-      <c r="I133" s="49"/>
-      <c r="J133" s="49"/>
-      <c r="K133" s="49"/>
-      <c r="L133" s="49"/>
-      <c r="M133" s="49"/>
-      <c r="N133" s="49"/>
-      <c r="O133" s="49"/>
-      <c r="P133" s="49"/>
-      <c r="Q133" s="49"/>
-      <c r="R133" s="49"/>
-      <c r="S133" s="49"/>
-      <c r="T133" s="49"/>
-      <c r="U133" s="49"/>
-      <c r="V133" s="49"/>
-      <c r="W133" s="49"/>
-      <c r="X133" s="49"/>
-      <c r="Y133" s="49"/>
-      <c r="Z133" s="49"/>
-      <c r="AA133" s="49"/>
-      <c r="AB133" s="50"/>
+      <c r="H133" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="I133" s="33"/>
+      <c r="J133" s="33"/>
+      <c r="K133" s="33"/>
+      <c r="L133" s="33"/>
+      <c r="M133" s="33"/>
+      <c r="N133" s="33"/>
+      <c r="O133" s="33"/>
+      <c r="P133" s="33"/>
+      <c r="Q133" s="33"/>
+      <c r="R133" s="33"/>
+      <c r="S133" s="33"/>
+      <c r="T133" s="33"/>
+      <c r="U133" s="33"/>
+      <c r="V133" s="33"/>
+      <c r="W133" s="33"/>
+      <c r="X133" s="33"/>
+      <c r="Y133" s="33"/>
+      <c r="Z133" s="33"/>
+      <c r="AA133" s="33"/>
+      <c r="AB133" s="34"/>
       <c r="AC133" s="11"/>
     </row>
     <row r="134" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5965,27 +5982,27 @@
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="51"/>
-      <c r="I134" s="52"/>
-      <c r="J134" s="52"/>
-      <c r="K134" s="52"/>
-      <c r="L134" s="52"/>
-      <c r="M134" s="52"/>
-      <c r="N134" s="52"/>
-      <c r="O134" s="52"/>
-      <c r="P134" s="52"/>
-      <c r="Q134" s="52"/>
-      <c r="R134" s="52"/>
-      <c r="S134" s="52"/>
-      <c r="T134" s="52"/>
-      <c r="U134" s="52"/>
-      <c r="V134" s="52"/>
-      <c r="W134" s="52"/>
-      <c r="X134" s="52"/>
-      <c r="Y134" s="52"/>
-      <c r="Z134" s="52"/>
-      <c r="AA134" s="52"/>
-      <c r="AB134" s="53"/>
+      <c r="H134" s="35"/>
+      <c r="I134" s="36"/>
+      <c r="J134" s="36"/>
+      <c r="K134" s="36"/>
+      <c r="L134" s="36"/>
+      <c r="M134" s="36"/>
+      <c r="N134" s="36"/>
+      <c r="O134" s="36"/>
+      <c r="P134" s="36"/>
+      <c r="Q134" s="36"/>
+      <c r="R134" s="36"/>
+      <c r="S134" s="36"/>
+      <c r="T134" s="36"/>
+      <c r="U134" s="36"/>
+      <c r="V134" s="36"/>
+      <c r="W134" s="36"/>
+      <c r="X134" s="36"/>
+      <c r="Y134" s="36"/>
+      <c r="Z134" s="36"/>
+      <c r="AA134" s="36"/>
+      <c r="AB134" s="37"/>
       <c r="AC134" s="11"/>
     </row>
     <row r="135" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5995,27 +6012,27 @@
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="51"/>
-      <c r="I135" s="52"/>
-      <c r="J135" s="52"/>
-      <c r="K135" s="52"/>
-      <c r="L135" s="52"/>
-      <c r="M135" s="52"/>
-      <c r="N135" s="52"/>
-      <c r="O135" s="52"/>
-      <c r="P135" s="52"/>
-      <c r="Q135" s="52"/>
-      <c r="R135" s="52"/>
-      <c r="S135" s="52"/>
-      <c r="T135" s="52"/>
-      <c r="U135" s="52"/>
-      <c r="V135" s="52"/>
-      <c r="W135" s="52"/>
-      <c r="X135" s="52"/>
-      <c r="Y135" s="52"/>
-      <c r="Z135" s="52"/>
-      <c r="AA135" s="52"/>
-      <c r="AB135" s="53"/>
+      <c r="H135" s="35"/>
+      <c r="I135" s="36"/>
+      <c r="J135" s="36"/>
+      <c r="K135" s="36"/>
+      <c r="L135" s="36"/>
+      <c r="M135" s="36"/>
+      <c r="N135" s="36"/>
+      <c r="O135" s="36"/>
+      <c r="P135" s="36"/>
+      <c r="Q135" s="36"/>
+      <c r="R135" s="36"/>
+      <c r="S135" s="36"/>
+      <c r="T135" s="36"/>
+      <c r="U135" s="36"/>
+      <c r="V135" s="36"/>
+      <c r="W135" s="36"/>
+      <c r="X135" s="36"/>
+      <c r="Y135" s="36"/>
+      <c r="Z135" s="36"/>
+      <c r="AA135" s="36"/>
+      <c r="AB135" s="37"/>
       <c r="AC135" s="11"/>
     </row>
     <row r="136" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6025,27 +6042,27 @@
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="51"/>
-      <c r="I136" s="52"/>
-      <c r="J136" s="52"/>
-      <c r="K136" s="52"/>
-      <c r="L136" s="52"/>
-      <c r="M136" s="52"/>
-      <c r="N136" s="52"/>
-      <c r="O136" s="52"/>
-      <c r="P136" s="52"/>
-      <c r="Q136" s="52"/>
-      <c r="R136" s="52"/>
-      <c r="S136" s="52"/>
-      <c r="T136" s="52"/>
-      <c r="U136" s="52"/>
-      <c r="V136" s="52"/>
-      <c r="W136" s="52"/>
-      <c r="X136" s="52"/>
-      <c r="Y136" s="52"/>
-      <c r="Z136" s="52"/>
-      <c r="AA136" s="52"/>
-      <c r="AB136" s="53"/>
+      <c r="H136" s="35"/>
+      <c r="I136" s="36"/>
+      <c r="J136" s="36"/>
+      <c r="K136" s="36"/>
+      <c r="L136" s="36"/>
+      <c r="M136" s="36"/>
+      <c r="N136" s="36"/>
+      <c r="O136" s="36"/>
+      <c r="P136" s="36"/>
+      <c r="Q136" s="36"/>
+      <c r="R136" s="36"/>
+      <c r="S136" s="36"/>
+      <c r="T136" s="36"/>
+      <c r="U136" s="36"/>
+      <c r="V136" s="36"/>
+      <c r="W136" s="36"/>
+      <c r="X136" s="36"/>
+      <c r="Y136" s="36"/>
+      <c r="Z136" s="36"/>
+      <c r="AA136" s="36"/>
+      <c r="AB136" s="37"/>
       <c r="AC136" s="11"/>
     </row>
     <row r="137" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6055,27 +6072,27 @@
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
-      <c r="H137" s="51"/>
-      <c r="I137" s="52"/>
-      <c r="J137" s="52"/>
-      <c r="K137" s="52"/>
-      <c r="L137" s="52"/>
-      <c r="M137" s="52"/>
-      <c r="N137" s="52"/>
-      <c r="O137" s="52"/>
-      <c r="P137" s="52"/>
-      <c r="Q137" s="52"/>
-      <c r="R137" s="52"/>
-      <c r="S137" s="52"/>
-      <c r="T137" s="52"/>
-      <c r="U137" s="52"/>
-      <c r="V137" s="52"/>
-      <c r="W137" s="52"/>
-      <c r="X137" s="52"/>
-      <c r="Y137" s="52"/>
-      <c r="Z137" s="52"/>
-      <c r="AA137" s="52"/>
-      <c r="AB137" s="53"/>
+      <c r="H137" s="35"/>
+      <c r="I137" s="36"/>
+      <c r="J137" s="36"/>
+      <c r="K137" s="36"/>
+      <c r="L137" s="36"/>
+      <c r="M137" s="36"/>
+      <c r="N137" s="36"/>
+      <c r="O137" s="36"/>
+      <c r="P137" s="36"/>
+      <c r="Q137" s="36"/>
+      <c r="R137" s="36"/>
+      <c r="S137" s="36"/>
+      <c r="T137" s="36"/>
+      <c r="U137" s="36"/>
+      <c r="V137" s="36"/>
+      <c r="W137" s="36"/>
+      <c r="X137" s="36"/>
+      <c r="Y137" s="36"/>
+      <c r="Z137" s="36"/>
+      <c r="AA137" s="36"/>
+      <c r="AB137" s="37"/>
       <c r="AC137" s="11"/>
     </row>
     <row r="138" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6085,27 +6102,27 @@
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
       <c r="G138" s="6"/>
-      <c r="H138" s="51"/>
-      <c r="I138" s="52"/>
-      <c r="J138" s="52"/>
-      <c r="K138" s="52"/>
-      <c r="L138" s="52"/>
-      <c r="M138" s="52"/>
-      <c r="N138" s="52"/>
-      <c r="O138" s="52"/>
-      <c r="P138" s="52"/>
-      <c r="Q138" s="52"/>
-      <c r="R138" s="52"/>
-      <c r="S138" s="52"/>
-      <c r="T138" s="52"/>
-      <c r="U138" s="52"/>
-      <c r="V138" s="52"/>
-      <c r="W138" s="52"/>
-      <c r="X138" s="52"/>
-      <c r="Y138" s="52"/>
-      <c r="Z138" s="52"/>
-      <c r="AA138" s="52"/>
-      <c r="AB138" s="53"/>
+      <c r="H138" s="35"/>
+      <c r="I138" s="36"/>
+      <c r="J138" s="36"/>
+      <c r="K138" s="36"/>
+      <c r="L138" s="36"/>
+      <c r="M138" s="36"/>
+      <c r="N138" s="36"/>
+      <c r="O138" s="36"/>
+      <c r="P138" s="36"/>
+      <c r="Q138" s="36"/>
+      <c r="R138" s="36"/>
+      <c r="S138" s="36"/>
+      <c r="T138" s="36"/>
+      <c r="U138" s="36"/>
+      <c r="V138" s="36"/>
+      <c r="W138" s="36"/>
+      <c r="X138" s="36"/>
+      <c r="Y138" s="36"/>
+      <c r="Z138" s="36"/>
+      <c r="AA138" s="36"/>
+      <c r="AB138" s="37"/>
       <c r="AC138" s="11"/>
     </row>
     <row r="139" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6115,27 +6132,27 @@
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
-      <c r="H139" s="54"/>
-      <c r="I139" s="55"/>
-      <c r="J139" s="55"/>
-      <c r="K139" s="55"/>
-      <c r="L139" s="55"/>
-      <c r="M139" s="55"/>
-      <c r="N139" s="55"/>
-      <c r="O139" s="55"/>
-      <c r="P139" s="55"/>
-      <c r="Q139" s="55"/>
-      <c r="R139" s="55"/>
-      <c r="S139" s="55"/>
-      <c r="T139" s="55"/>
-      <c r="U139" s="55"/>
-      <c r="V139" s="55"/>
-      <c r="W139" s="55"/>
-      <c r="X139" s="55"/>
-      <c r="Y139" s="55"/>
-      <c r="Z139" s="55"/>
-      <c r="AA139" s="55"/>
-      <c r="AB139" s="56"/>
+      <c r="H139" s="38"/>
+      <c r="I139" s="39"/>
+      <c r="J139" s="39"/>
+      <c r="K139" s="39"/>
+      <c r="L139" s="39"/>
+      <c r="M139" s="39"/>
+      <c r="N139" s="39"/>
+      <c r="O139" s="39"/>
+      <c r="P139" s="39"/>
+      <c r="Q139" s="39"/>
+      <c r="R139" s="39"/>
+      <c r="S139" s="39"/>
+      <c r="T139" s="39"/>
+      <c r="U139" s="39"/>
+      <c r="V139" s="39"/>
+      <c r="W139" s="39"/>
+      <c r="X139" s="39"/>
+      <c r="Y139" s="39"/>
+      <c r="Z139" s="39"/>
+      <c r="AA139" s="39"/>
+      <c r="AB139" s="40"/>
       <c r="AC139" s="11"/>
     </row>
     <row r="140" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6243,27 +6260,27 @@
         <v>2</v>
       </c>
       <c r="G144" s="6"/>
-      <c r="H144" s="48"/>
-      <c r="I144" s="49"/>
-      <c r="J144" s="49"/>
-      <c r="K144" s="49"/>
-      <c r="L144" s="49"/>
-      <c r="M144" s="49"/>
-      <c r="N144" s="49"/>
-      <c r="O144" s="49"/>
-      <c r="P144" s="49"/>
-      <c r="Q144" s="49"/>
-      <c r="R144" s="49"/>
-      <c r="S144" s="49"/>
-      <c r="T144" s="49"/>
-      <c r="U144" s="49"/>
-      <c r="V144" s="49"/>
-      <c r="W144" s="49"/>
-      <c r="X144" s="49"/>
-      <c r="Y144" s="49"/>
-      <c r="Z144" s="49"/>
-      <c r="AA144" s="49"/>
-      <c r="AB144" s="50"/>
+      <c r="H144" s="46"/>
+      <c r="I144" s="47"/>
+      <c r="J144" s="47"/>
+      <c r="K144" s="47"/>
+      <c r="L144" s="47"/>
+      <c r="M144" s="47"/>
+      <c r="N144" s="47"/>
+      <c r="O144" s="47"/>
+      <c r="P144" s="47"/>
+      <c r="Q144" s="47"/>
+      <c r="R144" s="47"/>
+      <c r="S144" s="47"/>
+      <c r="T144" s="47"/>
+      <c r="U144" s="47"/>
+      <c r="V144" s="47"/>
+      <c r="W144" s="47"/>
+      <c r="X144" s="47"/>
+      <c r="Y144" s="47"/>
+      <c r="Z144" s="47"/>
+      <c r="AA144" s="47"/>
+      <c r="AB144" s="48"/>
       <c r="AC144" s="11"/>
     </row>
     <row r="145" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6273,27 +6290,27 @@
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
-      <c r="H145" s="51"/>
-      <c r="I145" s="52"/>
-      <c r="J145" s="52"/>
-      <c r="K145" s="52"/>
-      <c r="L145" s="52"/>
-      <c r="M145" s="52"/>
-      <c r="N145" s="52"/>
-      <c r="O145" s="52"/>
-      <c r="P145" s="52"/>
-      <c r="Q145" s="52"/>
-      <c r="R145" s="52"/>
-      <c r="S145" s="52"/>
-      <c r="T145" s="52"/>
-      <c r="U145" s="52"/>
-      <c r="V145" s="52"/>
-      <c r="W145" s="52"/>
-      <c r="X145" s="52"/>
-      <c r="Y145" s="52"/>
-      <c r="Z145" s="52"/>
-      <c r="AA145" s="52"/>
-      <c r="AB145" s="53"/>
+      <c r="H145" s="49"/>
+      <c r="I145" s="50"/>
+      <c r="J145" s="50"/>
+      <c r="K145" s="50"/>
+      <c r="L145" s="50"/>
+      <c r="M145" s="50"/>
+      <c r="N145" s="50"/>
+      <c r="O145" s="50"/>
+      <c r="P145" s="50"/>
+      <c r="Q145" s="50"/>
+      <c r="R145" s="50"/>
+      <c r="S145" s="50"/>
+      <c r="T145" s="50"/>
+      <c r="U145" s="50"/>
+      <c r="V145" s="50"/>
+      <c r="W145" s="50"/>
+      <c r="X145" s="50"/>
+      <c r="Y145" s="50"/>
+      <c r="Z145" s="50"/>
+      <c r="AA145" s="50"/>
+      <c r="AB145" s="51"/>
       <c r="AC145" s="11"/>
     </row>
     <row r="146" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6303,27 +6320,27 @@
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
-      <c r="H146" s="51"/>
-      <c r="I146" s="52"/>
-      <c r="J146" s="52"/>
-      <c r="K146" s="52"/>
-      <c r="L146" s="52"/>
-      <c r="M146" s="52"/>
-      <c r="N146" s="52"/>
-      <c r="O146" s="52"/>
-      <c r="P146" s="52"/>
-      <c r="Q146" s="52"/>
-      <c r="R146" s="52"/>
-      <c r="S146" s="52"/>
-      <c r="T146" s="52"/>
-      <c r="U146" s="52"/>
-      <c r="V146" s="52"/>
-      <c r="W146" s="52"/>
-      <c r="X146" s="52"/>
-      <c r="Y146" s="52"/>
-      <c r="Z146" s="52"/>
-      <c r="AA146" s="52"/>
-      <c r="AB146" s="53"/>
+      <c r="H146" s="49"/>
+      <c r="I146" s="50"/>
+      <c r="J146" s="50"/>
+      <c r="K146" s="50"/>
+      <c r="L146" s="50"/>
+      <c r="M146" s="50"/>
+      <c r="N146" s="50"/>
+      <c r="O146" s="50"/>
+      <c r="P146" s="50"/>
+      <c r="Q146" s="50"/>
+      <c r="R146" s="50"/>
+      <c r="S146" s="50"/>
+      <c r="T146" s="50"/>
+      <c r="U146" s="50"/>
+      <c r="V146" s="50"/>
+      <c r="W146" s="50"/>
+      <c r="X146" s="50"/>
+      <c r="Y146" s="50"/>
+      <c r="Z146" s="50"/>
+      <c r="AA146" s="50"/>
+      <c r="AB146" s="51"/>
       <c r="AC146" s="11"/>
     </row>
     <row r="147" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6333,27 +6350,27 @@
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
-      <c r="H147" s="51"/>
-      <c r="I147" s="52"/>
-      <c r="J147" s="52"/>
-      <c r="K147" s="52"/>
-      <c r="L147" s="52"/>
-      <c r="M147" s="52"/>
-      <c r="N147" s="52"/>
-      <c r="O147" s="52"/>
-      <c r="P147" s="52"/>
-      <c r="Q147" s="52"/>
-      <c r="R147" s="52"/>
-      <c r="S147" s="52"/>
-      <c r="T147" s="52"/>
-      <c r="U147" s="52"/>
-      <c r="V147" s="52"/>
-      <c r="W147" s="52"/>
-      <c r="X147" s="52"/>
-      <c r="Y147" s="52"/>
-      <c r="Z147" s="52"/>
-      <c r="AA147" s="52"/>
-      <c r="AB147" s="53"/>
+      <c r="H147" s="49"/>
+      <c r="I147" s="50"/>
+      <c r="J147" s="50"/>
+      <c r="K147" s="50"/>
+      <c r="L147" s="50"/>
+      <c r="M147" s="50"/>
+      <c r="N147" s="50"/>
+      <c r="O147" s="50"/>
+      <c r="P147" s="50"/>
+      <c r="Q147" s="50"/>
+      <c r="R147" s="50"/>
+      <c r="S147" s="50"/>
+      <c r="T147" s="50"/>
+      <c r="U147" s="50"/>
+      <c r="V147" s="50"/>
+      <c r="W147" s="50"/>
+      <c r="X147" s="50"/>
+      <c r="Y147" s="50"/>
+      <c r="Z147" s="50"/>
+      <c r="AA147" s="50"/>
+      <c r="AB147" s="51"/>
       <c r="AC147" s="11"/>
     </row>
     <row r="148" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6363,27 +6380,27 @@
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
-      <c r="H148" s="51"/>
-      <c r="I148" s="52"/>
-      <c r="J148" s="52"/>
-      <c r="K148" s="52"/>
-      <c r="L148" s="52"/>
-      <c r="M148" s="52"/>
-      <c r="N148" s="52"/>
-      <c r="O148" s="52"/>
-      <c r="P148" s="52"/>
-      <c r="Q148" s="52"/>
-      <c r="R148" s="52"/>
-      <c r="S148" s="52"/>
-      <c r="T148" s="52"/>
-      <c r="U148" s="52"/>
-      <c r="V148" s="52"/>
-      <c r="W148" s="52"/>
-      <c r="X148" s="52"/>
-      <c r="Y148" s="52"/>
-      <c r="Z148" s="52"/>
-      <c r="AA148" s="52"/>
-      <c r="AB148" s="53"/>
+      <c r="H148" s="49"/>
+      <c r="I148" s="50"/>
+      <c r="J148" s="50"/>
+      <c r="K148" s="50"/>
+      <c r="L148" s="50"/>
+      <c r="M148" s="50"/>
+      <c r="N148" s="50"/>
+      <c r="O148" s="50"/>
+      <c r="P148" s="50"/>
+      <c r="Q148" s="50"/>
+      <c r="R148" s="50"/>
+      <c r="S148" s="50"/>
+      <c r="T148" s="50"/>
+      <c r="U148" s="50"/>
+      <c r="V148" s="50"/>
+      <c r="W148" s="50"/>
+      <c r="X148" s="50"/>
+      <c r="Y148" s="50"/>
+      <c r="Z148" s="50"/>
+      <c r="AA148" s="50"/>
+      <c r="AB148" s="51"/>
       <c r="AC148" s="11"/>
     </row>
     <row r="149" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6393,27 +6410,27 @@
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
-      <c r="H149" s="51"/>
-      <c r="I149" s="52"/>
-      <c r="J149" s="52"/>
-      <c r="K149" s="52"/>
-      <c r="L149" s="52"/>
-      <c r="M149" s="52"/>
-      <c r="N149" s="52"/>
-      <c r="O149" s="52"/>
-      <c r="P149" s="52"/>
-      <c r="Q149" s="52"/>
-      <c r="R149" s="52"/>
-      <c r="S149" s="52"/>
-      <c r="T149" s="52"/>
-      <c r="U149" s="52"/>
-      <c r="V149" s="52"/>
-      <c r="W149" s="52"/>
-      <c r="X149" s="52"/>
-      <c r="Y149" s="52"/>
-      <c r="Z149" s="52"/>
-      <c r="AA149" s="52"/>
-      <c r="AB149" s="53"/>
+      <c r="H149" s="49"/>
+      <c r="I149" s="50"/>
+      <c r="J149" s="50"/>
+      <c r="K149" s="50"/>
+      <c r="L149" s="50"/>
+      <c r="M149" s="50"/>
+      <c r="N149" s="50"/>
+      <c r="O149" s="50"/>
+      <c r="P149" s="50"/>
+      <c r="Q149" s="50"/>
+      <c r="R149" s="50"/>
+      <c r="S149" s="50"/>
+      <c r="T149" s="50"/>
+      <c r="U149" s="50"/>
+      <c r="V149" s="50"/>
+      <c r="W149" s="50"/>
+      <c r="X149" s="50"/>
+      <c r="Y149" s="50"/>
+      <c r="Z149" s="50"/>
+      <c r="AA149" s="50"/>
+      <c r="AB149" s="51"/>
       <c r="AC149" s="11"/>
     </row>
     <row r="150" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6423,27 +6440,27 @@
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
-      <c r="H150" s="54"/>
-      <c r="I150" s="55"/>
-      <c r="J150" s="55"/>
-      <c r="K150" s="55"/>
-      <c r="L150" s="55"/>
-      <c r="M150" s="55"/>
-      <c r="N150" s="55"/>
-      <c r="O150" s="55"/>
-      <c r="P150" s="55"/>
-      <c r="Q150" s="55"/>
-      <c r="R150" s="55"/>
-      <c r="S150" s="55"/>
-      <c r="T150" s="55"/>
-      <c r="U150" s="55"/>
-      <c r="V150" s="55"/>
-      <c r="W150" s="55"/>
-      <c r="X150" s="55"/>
-      <c r="Y150" s="55"/>
-      <c r="Z150" s="55"/>
-      <c r="AA150" s="55"/>
-      <c r="AB150" s="56"/>
+      <c r="H150" s="52"/>
+      <c r="I150" s="53"/>
+      <c r="J150" s="53"/>
+      <c r="K150" s="53"/>
+      <c r="L150" s="53"/>
+      <c r="M150" s="53"/>
+      <c r="N150" s="53"/>
+      <c r="O150" s="53"/>
+      <c r="P150" s="53"/>
+      <c r="Q150" s="53"/>
+      <c r="R150" s="53"/>
+      <c r="S150" s="53"/>
+      <c r="T150" s="53"/>
+      <c r="U150" s="53"/>
+      <c r="V150" s="53"/>
+      <c r="W150" s="53"/>
+      <c r="X150" s="53"/>
+      <c r="Y150" s="53"/>
+      <c r="Z150" s="53"/>
+      <c r="AA150" s="53"/>
+      <c r="AB150" s="54"/>
       <c r="AC150" s="11"/>
     </row>
     <row r="151" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6485,27 +6502,27 @@
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
-      <c r="H152" s="48"/>
-      <c r="I152" s="49"/>
-      <c r="J152" s="49"/>
-      <c r="K152" s="49"/>
-      <c r="L152" s="49"/>
-      <c r="M152" s="49"/>
-      <c r="N152" s="49"/>
-      <c r="O152" s="49"/>
-      <c r="P152" s="49"/>
-      <c r="Q152" s="49"/>
-      <c r="R152" s="49"/>
-      <c r="S152" s="49"/>
-      <c r="T152" s="49"/>
-      <c r="U152" s="49"/>
-      <c r="V152" s="49"/>
-      <c r="W152" s="49"/>
-      <c r="X152" s="49"/>
-      <c r="Y152" s="49"/>
-      <c r="Z152" s="49"/>
-      <c r="AA152" s="49"/>
-      <c r="AB152" s="50"/>
+      <c r="H152" s="46"/>
+      <c r="I152" s="47"/>
+      <c r="J152" s="47"/>
+      <c r="K152" s="47"/>
+      <c r="L152" s="47"/>
+      <c r="M152" s="47"/>
+      <c r="N152" s="47"/>
+      <c r="O152" s="47"/>
+      <c r="P152" s="47"/>
+      <c r="Q152" s="47"/>
+      <c r="R152" s="47"/>
+      <c r="S152" s="47"/>
+      <c r="T152" s="47"/>
+      <c r="U152" s="47"/>
+      <c r="V152" s="47"/>
+      <c r="W152" s="47"/>
+      <c r="X152" s="47"/>
+      <c r="Y152" s="47"/>
+      <c r="Z152" s="47"/>
+      <c r="AA152" s="47"/>
+      <c r="AB152" s="48"/>
       <c r="AC152" s="11"/>
     </row>
     <row r="153" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6515,27 +6532,27 @@
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
-      <c r="H153" s="51"/>
-      <c r="I153" s="52"/>
-      <c r="J153" s="52"/>
-      <c r="K153" s="52"/>
-      <c r="L153" s="52"/>
-      <c r="M153" s="52"/>
-      <c r="N153" s="52"/>
-      <c r="O153" s="52"/>
-      <c r="P153" s="52"/>
-      <c r="Q153" s="52"/>
-      <c r="R153" s="52"/>
-      <c r="S153" s="52"/>
-      <c r="T153" s="52"/>
-      <c r="U153" s="52"/>
-      <c r="V153" s="52"/>
-      <c r="W153" s="52"/>
-      <c r="X153" s="52"/>
-      <c r="Y153" s="52"/>
-      <c r="Z153" s="52"/>
-      <c r="AA153" s="52"/>
-      <c r="AB153" s="53"/>
+      <c r="H153" s="49"/>
+      <c r="I153" s="50"/>
+      <c r="J153" s="50"/>
+      <c r="K153" s="50"/>
+      <c r="L153" s="50"/>
+      <c r="M153" s="50"/>
+      <c r="N153" s="50"/>
+      <c r="O153" s="50"/>
+      <c r="P153" s="50"/>
+      <c r="Q153" s="50"/>
+      <c r="R153" s="50"/>
+      <c r="S153" s="50"/>
+      <c r="T153" s="50"/>
+      <c r="U153" s="50"/>
+      <c r="V153" s="50"/>
+      <c r="W153" s="50"/>
+      <c r="X153" s="50"/>
+      <c r="Y153" s="50"/>
+      <c r="Z153" s="50"/>
+      <c r="AA153" s="50"/>
+      <c r="AB153" s="51"/>
       <c r="AC153" s="11"/>
     </row>
     <row r="154" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6545,27 +6562,27 @@
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
-      <c r="H154" s="51"/>
-      <c r="I154" s="52"/>
-      <c r="J154" s="52"/>
-      <c r="K154" s="52"/>
-      <c r="L154" s="52"/>
-      <c r="M154" s="52"/>
-      <c r="N154" s="52"/>
-      <c r="O154" s="52"/>
-      <c r="P154" s="52"/>
-      <c r="Q154" s="52"/>
-      <c r="R154" s="52"/>
-      <c r="S154" s="52"/>
-      <c r="T154" s="52"/>
-      <c r="U154" s="52"/>
-      <c r="V154" s="52"/>
-      <c r="W154" s="52"/>
-      <c r="X154" s="52"/>
-      <c r="Y154" s="52"/>
-      <c r="Z154" s="52"/>
-      <c r="AA154" s="52"/>
-      <c r="AB154" s="53"/>
+      <c r="H154" s="49"/>
+      <c r="I154" s="50"/>
+      <c r="J154" s="50"/>
+      <c r="K154" s="50"/>
+      <c r="L154" s="50"/>
+      <c r="M154" s="50"/>
+      <c r="N154" s="50"/>
+      <c r="O154" s="50"/>
+      <c r="P154" s="50"/>
+      <c r="Q154" s="50"/>
+      <c r="R154" s="50"/>
+      <c r="S154" s="50"/>
+      <c r="T154" s="50"/>
+      <c r="U154" s="50"/>
+      <c r="V154" s="50"/>
+      <c r="W154" s="50"/>
+      <c r="X154" s="50"/>
+      <c r="Y154" s="50"/>
+      <c r="Z154" s="50"/>
+      <c r="AA154" s="50"/>
+      <c r="AB154" s="51"/>
       <c r="AC154" s="11"/>
     </row>
     <row r="155" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6575,27 +6592,27 @@
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
-      <c r="H155" s="51"/>
-      <c r="I155" s="52"/>
-      <c r="J155" s="52"/>
-      <c r="K155" s="52"/>
-      <c r="L155" s="52"/>
-      <c r="M155" s="52"/>
-      <c r="N155" s="52"/>
-      <c r="O155" s="52"/>
-      <c r="P155" s="52"/>
-      <c r="Q155" s="52"/>
-      <c r="R155" s="52"/>
-      <c r="S155" s="52"/>
-      <c r="T155" s="52"/>
-      <c r="U155" s="52"/>
-      <c r="V155" s="52"/>
-      <c r="W155" s="52"/>
-      <c r="X155" s="52"/>
-      <c r="Y155" s="52"/>
-      <c r="Z155" s="52"/>
-      <c r="AA155" s="52"/>
-      <c r="AB155" s="53"/>
+      <c r="H155" s="49"/>
+      <c r="I155" s="50"/>
+      <c r="J155" s="50"/>
+      <c r="K155" s="50"/>
+      <c r="L155" s="50"/>
+      <c r="M155" s="50"/>
+      <c r="N155" s="50"/>
+      <c r="O155" s="50"/>
+      <c r="P155" s="50"/>
+      <c r="Q155" s="50"/>
+      <c r="R155" s="50"/>
+      <c r="S155" s="50"/>
+      <c r="T155" s="50"/>
+      <c r="U155" s="50"/>
+      <c r="V155" s="50"/>
+      <c r="W155" s="50"/>
+      <c r="X155" s="50"/>
+      <c r="Y155" s="50"/>
+      <c r="Z155" s="50"/>
+      <c r="AA155" s="50"/>
+      <c r="AB155" s="51"/>
       <c r="AC155" s="11"/>
     </row>
     <row r="156" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6605,27 +6622,27 @@
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
-      <c r="H156" s="51"/>
-      <c r="I156" s="52"/>
-      <c r="J156" s="52"/>
-      <c r="K156" s="52"/>
-      <c r="L156" s="52"/>
-      <c r="M156" s="52"/>
-      <c r="N156" s="52"/>
-      <c r="O156" s="52"/>
-      <c r="P156" s="52"/>
-      <c r="Q156" s="52"/>
-      <c r="R156" s="52"/>
-      <c r="S156" s="52"/>
-      <c r="T156" s="52"/>
-      <c r="U156" s="52"/>
-      <c r="V156" s="52"/>
-      <c r="W156" s="52"/>
-      <c r="X156" s="52"/>
-      <c r="Y156" s="52"/>
-      <c r="Z156" s="52"/>
-      <c r="AA156" s="52"/>
-      <c r="AB156" s="53"/>
+      <c r="H156" s="49"/>
+      <c r="I156" s="50"/>
+      <c r="J156" s="50"/>
+      <c r="K156" s="50"/>
+      <c r="L156" s="50"/>
+      <c r="M156" s="50"/>
+      <c r="N156" s="50"/>
+      <c r="O156" s="50"/>
+      <c r="P156" s="50"/>
+      <c r="Q156" s="50"/>
+      <c r="R156" s="50"/>
+      <c r="S156" s="50"/>
+      <c r="T156" s="50"/>
+      <c r="U156" s="50"/>
+      <c r="V156" s="50"/>
+      <c r="W156" s="50"/>
+      <c r="X156" s="50"/>
+      <c r="Y156" s="50"/>
+      <c r="Z156" s="50"/>
+      <c r="AA156" s="50"/>
+      <c r="AB156" s="51"/>
       <c r="AC156" s="11"/>
     </row>
     <row r="157" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6635,27 +6652,27 @@
       <c r="E157" s="6"/>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
-      <c r="H157" s="51"/>
-      <c r="I157" s="52"/>
-      <c r="J157" s="52"/>
-      <c r="K157" s="52"/>
-      <c r="L157" s="52"/>
-      <c r="M157" s="52"/>
-      <c r="N157" s="52"/>
-      <c r="O157" s="52"/>
-      <c r="P157" s="52"/>
-      <c r="Q157" s="52"/>
-      <c r="R157" s="52"/>
-      <c r="S157" s="52"/>
-      <c r="T157" s="52"/>
-      <c r="U157" s="52"/>
-      <c r="V157" s="52"/>
-      <c r="W157" s="52"/>
-      <c r="X157" s="52"/>
-      <c r="Y157" s="52"/>
-      <c r="Z157" s="52"/>
-      <c r="AA157" s="52"/>
-      <c r="AB157" s="53"/>
+      <c r="H157" s="49"/>
+      <c r="I157" s="50"/>
+      <c r="J157" s="50"/>
+      <c r="K157" s="50"/>
+      <c r="L157" s="50"/>
+      <c r="M157" s="50"/>
+      <c r="N157" s="50"/>
+      <c r="O157" s="50"/>
+      <c r="P157" s="50"/>
+      <c r="Q157" s="50"/>
+      <c r="R157" s="50"/>
+      <c r="S157" s="50"/>
+      <c r="T157" s="50"/>
+      <c r="U157" s="50"/>
+      <c r="V157" s="50"/>
+      <c r="W157" s="50"/>
+      <c r="X157" s="50"/>
+      <c r="Y157" s="50"/>
+      <c r="Z157" s="50"/>
+      <c r="AA157" s="50"/>
+      <c r="AB157" s="51"/>
       <c r="AC157" s="11"/>
     </row>
     <row r="158" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6665,27 +6682,27 @@
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
-      <c r="H158" s="54"/>
-      <c r="I158" s="55"/>
-      <c r="J158" s="55"/>
-      <c r="K158" s="55"/>
-      <c r="L158" s="55"/>
-      <c r="M158" s="55"/>
-      <c r="N158" s="55"/>
-      <c r="O158" s="55"/>
-      <c r="P158" s="55"/>
-      <c r="Q158" s="55"/>
-      <c r="R158" s="55"/>
-      <c r="S158" s="55"/>
-      <c r="T158" s="55"/>
-      <c r="U158" s="55"/>
-      <c r="V158" s="55"/>
-      <c r="W158" s="55"/>
-      <c r="X158" s="55"/>
-      <c r="Y158" s="55"/>
-      <c r="Z158" s="55"/>
-      <c r="AA158" s="55"/>
-      <c r="AB158" s="56"/>
+      <c r="H158" s="52"/>
+      <c r="I158" s="53"/>
+      <c r="J158" s="53"/>
+      <c r="K158" s="53"/>
+      <c r="L158" s="53"/>
+      <c r="M158" s="53"/>
+      <c r="N158" s="53"/>
+      <c r="O158" s="53"/>
+      <c r="P158" s="53"/>
+      <c r="Q158" s="53"/>
+      <c r="R158" s="53"/>
+      <c r="S158" s="53"/>
+      <c r="T158" s="53"/>
+      <c r="U158" s="53"/>
+      <c r="V158" s="53"/>
+      <c r="W158" s="53"/>
+      <c r="X158" s="53"/>
+      <c r="Y158" s="53"/>
+      <c r="Z158" s="53"/>
+      <c r="AA158" s="53"/>
+      <c r="AB158" s="54"/>
       <c r="AC158" s="11"/>
     </row>
     <row r="159" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6793,27 +6810,27 @@
         <v>2</v>
       </c>
       <c r="G163" s="6"/>
-      <c r="H163" s="48"/>
-      <c r="I163" s="49"/>
-      <c r="J163" s="49"/>
-      <c r="K163" s="49"/>
-      <c r="L163" s="49"/>
-      <c r="M163" s="49"/>
-      <c r="N163" s="49"/>
-      <c r="O163" s="49"/>
-      <c r="P163" s="49"/>
-      <c r="Q163" s="49"/>
-      <c r="R163" s="49"/>
-      <c r="S163" s="49"/>
-      <c r="T163" s="49"/>
-      <c r="U163" s="49"/>
-      <c r="V163" s="49"/>
-      <c r="W163" s="49"/>
-      <c r="X163" s="49"/>
-      <c r="Y163" s="49"/>
-      <c r="Z163" s="49"/>
-      <c r="AA163" s="49"/>
-      <c r="AB163" s="50"/>
+      <c r="H163" s="46"/>
+      <c r="I163" s="47"/>
+      <c r="J163" s="47"/>
+      <c r="K163" s="47"/>
+      <c r="L163" s="47"/>
+      <c r="M163" s="47"/>
+      <c r="N163" s="47"/>
+      <c r="O163" s="47"/>
+      <c r="P163" s="47"/>
+      <c r="Q163" s="47"/>
+      <c r="R163" s="47"/>
+      <c r="S163" s="47"/>
+      <c r="T163" s="47"/>
+      <c r="U163" s="47"/>
+      <c r="V163" s="47"/>
+      <c r="W163" s="47"/>
+      <c r="X163" s="47"/>
+      <c r="Y163" s="47"/>
+      <c r="Z163" s="47"/>
+      <c r="AA163" s="47"/>
+      <c r="AB163" s="48"/>
       <c r="AC163" s="11"/>
     </row>
     <row r="164" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6823,27 +6840,27 @@
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
-      <c r="H164" s="51"/>
-      <c r="I164" s="52"/>
-      <c r="J164" s="52"/>
-      <c r="K164" s="52"/>
-      <c r="L164" s="52"/>
-      <c r="M164" s="52"/>
-      <c r="N164" s="52"/>
-      <c r="O164" s="52"/>
-      <c r="P164" s="52"/>
-      <c r="Q164" s="52"/>
-      <c r="R164" s="52"/>
-      <c r="S164" s="52"/>
-      <c r="T164" s="52"/>
-      <c r="U164" s="52"/>
-      <c r="V164" s="52"/>
-      <c r="W164" s="52"/>
-      <c r="X164" s="52"/>
-      <c r="Y164" s="52"/>
-      <c r="Z164" s="52"/>
-      <c r="AA164" s="52"/>
-      <c r="AB164" s="53"/>
+      <c r="H164" s="49"/>
+      <c r="I164" s="50"/>
+      <c r="J164" s="50"/>
+      <c r="K164" s="50"/>
+      <c r="L164" s="50"/>
+      <c r="M164" s="50"/>
+      <c r="N164" s="50"/>
+      <c r="O164" s="50"/>
+      <c r="P164" s="50"/>
+      <c r="Q164" s="50"/>
+      <c r="R164" s="50"/>
+      <c r="S164" s="50"/>
+      <c r="T164" s="50"/>
+      <c r="U164" s="50"/>
+      <c r="V164" s="50"/>
+      <c r="W164" s="50"/>
+      <c r="X164" s="50"/>
+      <c r="Y164" s="50"/>
+      <c r="Z164" s="50"/>
+      <c r="AA164" s="50"/>
+      <c r="AB164" s="51"/>
       <c r="AC164" s="11"/>
     </row>
     <row r="165" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6853,27 +6870,27 @@
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
-      <c r="H165" s="51"/>
-      <c r="I165" s="52"/>
-      <c r="J165" s="52"/>
-      <c r="K165" s="52"/>
-      <c r="L165" s="52"/>
-      <c r="M165" s="52"/>
-      <c r="N165" s="52"/>
-      <c r="O165" s="52"/>
-      <c r="P165" s="52"/>
-      <c r="Q165" s="52"/>
-      <c r="R165" s="52"/>
-      <c r="S165" s="52"/>
-      <c r="T165" s="52"/>
-      <c r="U165" s="52"/>
-      <c r="V165" s="52"/>
-      <c r="W165" s="52"/>
-      <c r="X165" s="52"/>
-      <c r="Y165" s="52"/>
-      <c r="Z165" s="52"/>
-      <c r="AA165" s="52"/>
-      <c r="AB165" s="53"/>
+      <c r="H165" s="49"/>
+      <c r="I165" s="50"/>
+      <c r="J165" s="50"/>
+      <c r="K165" s="50"/>
+      <c r="L165" s="50"/>
+      <c r="M165" s="50"/>
+      <c r="N165" s="50"/>
+      <c r="O165" s="50"/>
+      <c r="P165" s="50"/>
+      <c r="Q165" s="50"/>
+      <c r="R165" s="50"/>
+      <c r="S165" s="50"/>
+      <c r="T165" s="50"/>
+      <c r="U165" s="50"/>
+      <c r="V165" s="50"/>
+      <c r="W165" s="50"/>
+      <c r="X165" s="50"/>
+      <c r="Y165" s="50"/>
+      <c r="Z165" s="50"/>
+      <c r="AA165" s="50"/>
+      <c r="AB165" s="51"/>
       <c r="AC165" s="11"/>
     </row>
     <row r="166" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6883,27 +6900,27 @@
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
-      <c r="H166" s="51"/>
-      <c r="I166" s="52"/>
-      <c r="J166" s="52"/>
-      <c r="K166" s="52"/>
-      <c r="L166" s="52"/>
-      <c r="M166" s="52"/>
-      <c r="N166" s="52"/>
-      <c r="O166" s="52"/>
-      <c r="P166" s="52"/>
-      <c r="Q166" s="52"/>
-      <c r="R166" s="52"/>
-      <c r="S166" s="52"/>
-      <c r="T166" s="52"/>
-      <c r="U166" s="52"/>
-      <c r="V166" s="52"/>
-      <c r="W166" s="52"/>
-      <c r="X166" s="52"/>
-      <c r="Y166" s="52"/>
-      <c r="Z166" s="52"/>
-      <c r="AA166" s="52"/>
-      <c r="AB166" s="53"/>
+      <c r="H166" s="49"/>
+      <c r="I166" s="50"/>
+      <c r="J166" s="50"/>
+      <c r="K166" s="50"/>
+      <c r="L166" s="50"/>
+      <c r="M166" s="50"/>
+      <c r="N166" s="50"/>
+      <c r="O166" s="50"/>
+      <c r="P166" s="50"/>
+      <c r="Q166" s="50"/>
+      <c r="R166" s="50"/>
+      <c r="S166" s="50"/>
+      <c r="T166" s="50"/>
+      <c r="U166" s="50"/>
+      <c r="V166" s="50"/>
+      <c r="W166" s="50"/>
+      <c r="X166" s="50"/>
+      <c r="Y166" s="50"/>
+      <c r="Z166" s="50"/>
+      <c r="AA166" s="50"/>
+      <c r="AB166" s="51"/>
       <c r="AC166" s="11"/>
     </row>
     <row r="167" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6913,27 +6930,27 @@
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
-      <c r="H167" s="51"/>
-      <c r="I167" s="52"/>
-      <c r="J167" s="52"/>
-      <c r="K167" s="52"/>
-      <c r="L167" s="52"/>
-      <c r="M167" s="52"/>
-      <c r="N167" s="52"/>
-      <c r="O167" s="52"/>
-      <c r="P167" s="52"/>
-      <c r="Q167" s="52"/>
-      <c r="R167" s="52"/>
-      <c r="S167" s="52"/>
-      <c r="T167" s="52"/>
-      <c r="U167" s="52"/>
-      <c r="V167" s="52"/>
-      <c r="W167" s="52"/>
-      <c r="X167" s="52"/>
-      <c r="Y167" s="52"/>
-      <c r="Z167" s="52"/>
-      <c r="AA167" s="52"/>
-      <c r="AB167" s="53"/>
+      <c r="H167" s="49"/>
+      <c r="I167" s="50"/>
+      <c r="J167" s="50"/>
+      <c r="K167" s="50"/>
+      <c r="L167" s="50"/>
+      <c r="M167" s="50"/>
+      <c r="N167" s="50"/>
+      <c r="O167" s="50"/>
+      <c r="P167" s="50"/>
+      <c r="Q167" s="50"/>
+      <c r="R167" s="50"/>
+      <c r="S167" s="50"/>
+      <c r="T167" s="50"/>
+      <c r="U167" s="50"/>
+      <c r="V167" s="50"/>
+      <c r="W167" s="50"/>
+      <c r="X167" s="50"/>
+      <c r="Y167" s="50"/>
+      <c r="Z167" s="50"/>
+      <c r="AA167" s="50"/>
+      <c r="AB167" s="51"/>
       <c r="AC167" s="11"/>
     </row>
     <row r="168" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6943,27 +6960,27 @@
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
-      <c r="H168" s="51"/>
-      <c r="I168" s="52"/>
-      <c r="J168" s="52"/>
-      <c r="K168" s="52"/>
-      <c r="L168" s="52"/>
-      <c r="M168" s="52"/>
-      <c r="N168" s="52"/>
-      <c r="O168" s="52"/>
-      <c r="P168" s="52"/>
-      <c r="Q168" s="52"/>
-      <c r="R168" s="52"/>
-      <c r="S168" s="52"/>
-      <c r="T168" s="52"/>
-      <c r="U168" s="52"/>
-      <c r="V168" s="52"/>
-      <c r="W168" s="52"/>
-      <c r="X168" s="52"/>
-      <c r="Y168" s="52"/>
-      <c r="Z168" s="52"/>
-      <c r="AA168" s="52"/>
-      <c r="AB168" s="53"/>
+      <c r="H168" s="49"/>
+      <c r="I168" s="50"/>
+      <c r="J168" s="50"/>
+      <c r="K168" s="50"/>
+      <c r="L168" s="50"/>
+      <c r="M168" s="50"/>
+      <c r="N168" s="50"/>
+      <c r="O168" s="50"/>
+      <c r="P168" s="50"/>
+      <c r="Q168" s="50"/>
+      <c r="R168" s="50"/>
+      <c r="S168" s="50"/>
+      <c r="T168" s="50"/>
+      <c r="U168" s="50"/>
+      <c r="V168" s="50"/>
+      <c r="W168" s="50"/>
+      <c r="X168" s="50"/>
+      <c r="Y168" s="50"/>
+      <c r="Z168" s="50"/>
+      <c r="AA168" s="50"/>
+      <c r="AB168" s="51"/>
       <c r="AC168" s="11"/>
     </row>
     <row r="169" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6973,27 +6990,27 @@
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
-      <c r="H169" s="54"/>
-      <c r="I169" s="55"/>
-      <c r="J169" s="55"/>
-      <c r="K169" s="55"/>
-      <c r="L169" s="55"/>
-      <c r="M169" s="55"/>
-      <c r="N169" s="55"/>
-      <c r="O169" s="55"/>
-      <c r="P169" s="55"/>
-      <c r="Q169" s="55"/>
-      <c r="R169" s="55"/>
-      <c r="S169" s="55"/>
-      <c r="T169" s="55"/>
-      <c r="U169" s="55"/>
-      <c r="V169" s="55"/>
-      <c r="W169" s="55"/>
-      <c r="X169" s="55"/>
-      <c r="Y169" s="55"/>
-      <c r="Z169" s="55"/>
-      <c r="AA169" s="55"/>
-      <c r="AB169" s="56"/>
+      <c r="H169" s="52"/>
+      <c r="I169" s="53"/>
+      <c r="J169" s="53"/>
+      <c r="K169" s="53"/>
+      <c r="L169" s="53"/>
+      <c r="M169" s="53"/>
+      <c r="N169" s="53"/>
+      <c r="O169" s="53"/>
+      <c r="P169" s="53"/>
+      <c r="Q169" s="53"/>
+      <c r="R169" s="53"/>
+      <c r="S169" s="53"/>
+      <c r="T169" s="53"/>
+      <c r="U169" s="53"/>
+      <c r="V169" s="53"/>
+      <c r="W169" s="53"/>
+      <c r="X169" s="53"/>
+      <c r="Y169" s="53"/>
+      <c r="Z169" s="53"/>
+      <c r="AA169" s="53"/>
+      <c r="AB169" s="54"/>
       <c r="AC169" s="11"/>
     </row>
     <row r="170" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7035,27 +7052,27 @@
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
-      <c r="H171" s="48"/>
-      <c r="I171" s="49"/>
-      <c r="J171" s="49"/>
-      <c r="K171" s="49"/>
-      <c r="L171" s="49"/>
-      <c r="M171" s="49"/>
-      <c r="N171" s="49"/>
-      <c r="O171" s="49"/>
-      <c r="P171" s="49"/>
-      <c r="Q171" s="49"/>
-      <c r="R171" s="49"/>
-      <c r="S171" s="49"/>
-      <c r="T171" s="49"/>
-      <c r="U171" s="49"/>
-      <c r="V171" s="49"/>
-      <c r="W171" s="49"/>
-      <c r="X171" s="49"/>
-      <c r="Y171" s="49"/>
-      <c r="Z171" s="49"/>
-      <c r="AA171" s="49"/>
-      <c r="AB171" s="50"/>
+      <c r="H171" s="46"/>
+      <c r="I171" s="47"/>
+      <c r="J171" s="47"/>
+      <c r="K171" s="47"/>
+      <c r="L171" s="47"/>
+      <c r="M171" s="47"/>
+      <c r="N171" s="47"/>
+      <c r="O171" s="47"/>
+      <c r="P171" s="47"/>
+      <c r="Q171" s="47"/>
+      <c r="R171" s="47"/>
+      <c r="S171" s="47"/>
+      <c r="T171" s="47"/>
+      <c r="U171" s="47"/>
+      <c r="V171" s="47"/>
+      <c r="W171" s="47"/>
+      <c r="X171" s="47"/>
+      <c r="Y171" s="47"/>
+      <c r="Z171" s="47"/>
+      <c r="AA171" s="47"/>
+      <c r="AB171" s="48"/>
       <c r="AC171" s="11"/>
     </row>
     <row r="172" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7065,27 +7082,27 @@
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
-      <c r="H172" s="51"/>
-      <c r="I172" s="52"/>
-      <c r="J172" s="52"/>
-      <c r="K172" s="52"/>
-      <c r="L172" s="52"/>
-      <c r="M172" s="52"/>
-      <c r="N172" s="52"/>
-      <c r="O172" s="52"/>
-      <c r="P172" s="52"/>
-      <c r="Q172" s="52"/>
-      <c r="R172" s="52"/>
-      <c r="S172" s="52"/>
-      <c r="T172" s="52"/>
-      <c r="U172" s="52"/>
-      <c r="V172" s="52"/>
-      <c r="W172" s="52"/>
-      <c r="X172" s="52"/>
-      <c r="Y172" s="52"/>
-      <c r="Z172" s="52"/>
-      <c r="AA172" s="52"/>
-      <c r="AB172" s="53"/>
+      <c r="H172" s="49"/>
+      <c r="I172" s="50"/>
+      <c r="J172" s="50"/>
+      <c r="K172" s="50"/>
+      <c r="L172" s="50"/>
+      <c r="M172" s="50"/>
+      <c r="N172" s="50"/>
+      <c r="O172" s="50"/>
+      <c r="P172" s="50"/>
+      <c r="Q172" s="50"/>
+      <c r="R172" s="50"/>
+      <c r="S172" s="50"/>
+      <c r="T172" s="50"/>
+      <c r="U172" s="50"/>
+      <c r="V172" s="50"/>
+      <c r="W172" s="50"/>
+      <c r="X172" s="50"/>
+      <c r="Y172" s="50"/>
+      <c r="Z172" s="50"/>
+      <c r="AA172" s="50"/>
+      <c r="AB172" s="51"/>
       <c r="AC172" s="11"/>
     </row>
     <row r="173" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7095,27 +7112,27 @@
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
-      <c r="H173" s="51"/>
-      <c r="I173" s="52"/>
-      <c r="J173" s="52"/>
-      <c r="K173" s="52"/>
-      <c r="L173" s="52"/>
-      <c r="M173" s="52"/>
-      <c r="N173" s="52"/>
-      <c r="O173" s="52"/>
-      <c r="P173" s="52"/>
-      <c r="Q173" s="52"/>
-      <c r="R173" s="52"/>
-      <c r="S173" s="52"/>
-      <c r="T173" s="52"/>
-      <c r="U173" s="52"/>
-      <c r="V173" s="52"/>
-      <c r="W173" s="52"/>
-      <c r="X173" s="52"/>
-      <c r="Y173" s="52"/>
-      <c r="Z173" s="52"/>
-      <c r="AA173" s="52"/>
-      <c r="AB173" s="53"/>
+      <c r="H173" s="49"/>
+      <c r="I173" s="50"/>
+      <c r="J173" s="50"/>
+      <c r="K173" s="50"/>
+      <c r="L173" s="50"/>
+      <c r="M173" s="50"/>
+      <c r="N173" s="50"/>
+      <c r="O173" s="50"/>
+      <c r="P173" s="50"/>
+      <c r="Q173" s="50"/>
+      <c r="R173" s="50"/>
+      <c r="S173" s="50"/>
+      <c r="T173" s="50"/>
+      <c r="U173" s="50"/>
+      <c r="V173" s="50"/>
+      <c r="W173" s="50"/>
+      <c r="X173" s="50"/>
+      <c r="Y173" s="50"/>
+      <c r="Z173" s="50"/>
+      <c r="AA173" s="50"/>
+      <c r="AB173" s="51"/>
       <c r="AC173" s="11"/>
     </row>
     <row r="174" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7125,27 +7142,27 @@
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
-      <c r="H174" s="51"/>
-      <c r="I174" s="52"/>
-      <c r="J174" s="52"/>
-      <c r="K174" s="52"/>
-      <c r="L174" s="52"/>
-      <c r="M174" s="52"/>
-      <c r="N174" s="52"/>
-      <c r="O174" s="52"/>
-      <c r="P174" s="52"/>
-      <c r="Q174" s="52"/>
-      <c r="R174" s="52"/>
-      <c r="S174" s="52"/>
-      <c r="T174" s="52"/>
-      <c r="U174" s="52"/>
-      <c r="V174" s="52"/>
-      <c r="W174" s="52"/>
-      <c r="X174" s="52"/>
-      <c r="Y174" s="52"/>
-      <c r="Z174" s="52"/>
-      <c r="AA174" s="52"/>
-      <c r="AB174" s="53"/>
+      <c r="H174" s="49"/>
+      <c r="I174" s="50"/>
+      <c r="J174" s="50"/>
+      <c r="K174" s="50"/>
+      <c r="L174" s="50"/>
+      <c r="M174" s="50"/>
+      <c r="N174" s="50"/>
+      <c r="O174" s="50"/>
+      <c r="P174" s="50"/>
+      <c r="Q174" s="50"/>
+      <c r="R174" s="50"/>
+      <c r="S174" s="50"/>
+      <c r="T174" s="50"/>
+      <c r="U174" s="50"/>
+      <c r="V174" s="50"/>
+      <c r="W174" s="50"/>
+      <c r="X174" s="50"/>
+      <c r="Y174" s="50"/>
+      <c r="Z174" s="50"/>
+      <c r="AA174" s="50"/>
+      <c r="AB174" s="51"/>
       <c r="AC174" s="11"/>
     </row>
     <row r="175" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7155,27 +7172,27 @@
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
-      <c r="H175" s="51"/>
-      <c r="I175" s="52"/>
-      <c r="J175" s="52"/>
-      <c r="K175" s="52"/>
-      <c r="L175" s="52"/>
-      <c r="M175" s="52"/>
-      <c r="N175" s="52"/>
-      <c r="O175" s="52"/>
-      <c r="P175" s="52"/>
-      <c r="Q175" s="52"/>
-      <c r="R175" s="52"/>
-      <c r="S175" s="52"/>
-      <c r="T175" s="52"/>
-      <c r="U175" s="52"/>
-      <c r="V175" s="52"/>
-      <c r="W175" s="52"/>
-      <c r="X175" s="52"/>
-      <c r="Y175" s="52"/>
-      <c r="Z175" s="52"/>
-      <c r="AA175" s="52"/>
-      <c r="AB175" s="53"/>
+      <c r="H175" s="49"/>
+      <c r="I175" s="50"/>
+      <c r="J175" s="50"/>
+      <c r="K175" s="50"/>
+      <c r="L175" s="50"/>
+      <c r="M175" s="50"/>
+      <c r="N175" s="50"/>
+      <c r="O175" s="50"/>
+      <c r="P175" s="50"/>
+      <c r="Q175" s="50"/>
+      <c r="R175" s="50"/>
+      <c r="S175" s="50"/>
+      <c r="T175" s="50"/>
+      <c r="U175" s="50"/>
+      <c r="V175" s="50"/>
+      <c r="W175" s="50"/>
+      <c r="X175" s="50"/>
+      <c r="Y175" s="50"/>
+      <c r="Z175" s="50"/>
+      <c r="AA175" s="50"/>
+      <c r="AB175" s="51"/>
       <c r="AC175" s="11"/>
     </row>
     <row r="176" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7185,27 +7202,27 @@
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
-      <c r="H176" s="51"/>
-      <c r="I176" s="52"/>
-      <c r="J176" s="52"/>
-      <c r="K176" s="52"/>
-      <c r="L176" s="52"/>
-      <c r="M176" s="52"/>
-      <c r="N176" s="52"/>
-      <c r="O176" s="52"/>
-      <c r="P176" s="52"/>
-      <c r="Q176" s="52"/>
-      <c r="R176" s="52"/>
-      <c r="S176" s="52"/>
-      <c r="T176" s="52"/>
-      <c r="U176" s="52"/>
-      <c r="V176" s="52"/>
-      <c r="W176" s="52"/>
-      <c r="X176" s="52"/>
-      <c r="Y176" s="52"/>
-      <c r="Z176" s="52"/>
-      <c r="AA176" s="52"/>
-      <c r="AB176" s="53"/>
+      <c r="H176" s="49"/>
+      <c r="I176" s="50"/>
+      <c r="J176" s="50"/>
+      <c r="K176" s="50"/>
+      <c r="L176" s="50"/>
+      <c r="M176" s="50"/>
+      <c r="N176" s="50"/>
+      <c r="O176" s="50"/>
+      <c r="P176" s="50"/>
+      <c r="Q176" s="50"/>
+      <c r="R176" s="50"/>
+      <c r="S176" s="50"/>
+      <c r="T176" s="50"/>
+      <c r="U176" s="50"/>
+      <c r="V176" s="50"/>
+      <c r="W176" s="50"/>
+      <c r="X176" s="50"/>
+      <c r="Y176" s="50"/>
+      <c r="Z176" s="50"/>
+      <c r="AA176" s="50"/>
+      <c r="AB176" s="51"/>
       <c r="AC176" s="11"/>
     </row>
     <row r="177" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7215,27 +7232,27 @@
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
-      <c r="H177" s="54"/>
-      <c r="I177" s="55"/>
-      <c r="J177" s="55"/>
-      <c r="K177" s="55"/>
-      <c r="L177" s="55"/>
-      <c r="M177" s="55"/>
-      <c r="N177" s="55"/>
-      <c r="O177" s="55"/>
-      <c r="P177" s="55"/>
-      <c r="Q177" s="55"/>
-      <c r="R177" s="55"/>
-      <c r="S177" s="55"/>
-      <c r="T177" s="55"/>
-      <c r="U177" s="55"/>
-      <c r="V177" s="55"/>
-      <c r="W177" s="55"/>
-      <c r="X177" s="55"/>
-      <c r="Y177" s="55"/>
-      <c r="Z177" s="55"/>
-      <c r="AA177" s="55"/>
-      <c r="AB177" s="56"/>
+      <c r="H177" s="52"/>
+      <c r="I177" s="53"/>
+      <c r="J177" s="53"/>
+      <c r="K177" s="53"/>
+      <c r="L177" s="53"/>
+      <c r="M177" s="53"/>
+      <c r="N177" s="53"/>
+      <c r="O177" s="53"/>
+      <c r="P177" s="53"/>
+      <c r="Q177" s="53"/>
+      <c r="R177" s="53"/>
+      <c r="S177" s="53"/>
+      <c r="T177" s="53"/>
+      <c r="U177" s="53"/>
+      <c r="V177" s="53"/>
+      <c r="W177" s="53"/>
+      <c r="X177" s="53"/>
+      <c r="Y177" s="53"/>
+      <c r="Z177" s="53"/>
+      <c r="AA177" s="53"/>
+      <c r="AB177" s="54"/>
       <c r="AC177" s="11"/>
     </row>
     <row r="178" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7343,27 +7360,27 @@
         <v>2</v>
       </c>
       <c r="G182" s="6"/>
-      <c r="H182" s="48"/>
-      <c r="I182" s="49"/>
-      <c r="J182" s="49"/>
-      <c r="K182" s="49"/>
-      <c r="L182" s="49"/>
-      <c r="M182" s="49"/>
-      <c r="N182" s="49"/>
-      <c r="O182" s="49"/>
-      <c r="P182" s="49"/>
-      <c r="Q182" s="49"/>
-      <c r="R182" s="49"/>
-      <c r="S182" s="49"/>
-      <c r="T182" s="49"/>
-      <c r="U182" s="49"/>
-      <c r="V182" s="49"/>
-      <c r="W182" s="49"/>
-      <c r="X182" s="49"/>
-      <c r="Y182" s="49"/>
-      <c r="Z182" s="49"/>
-      <c r="AA182" s="49"/>
-      <c r="AB182" s="50"/>
+      <c r="H182" s="46"/>
+      <c r="I182" s="47"/>
+      <c r="J182" s="47"/>
+      <c r="K182" s="47"/>
+      <c r="L182" s="47"/>
+      <c r="M182" s="47"/>
+      <c r="N182" s="47"/>
+      <c r="O182" s="47"/>
+      <c r="P182" s="47"/>
+      <c r="Q182" s="47"/>
+      <c r="R182" s="47"/>
+      <c r="S182" s="47"/>
+      <c r="T182" s="47"/>
+      <c r="U182" s="47"/>
+      <c r="V182" s="47"/>
+      <c r="W182" s="47"/>
+      <c r="X182" s="47"/>
+      <c r="Y182" s="47"/>
+      <c r="Z182" s="47"/>
+      <c r="AA182" s="47"/>
+      <c r="AB182" s="48"/>
       <c r="AC182" s="11"/>
     </row>
     <row r="183" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7373,27 +7390,27 @@
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
-      <c r="H183" s="51"/>
-      <c r="I183" s="52"/>
-      <c r="J183" s="52"/>
-      <c r="K183" s="52"/>
-      <c r="L183" s="52"/>
-      <c r="M183" s="52"/>
-      <c r="N183" s="52"/>
-      <c r="O183" s="52"/>
-      <c r="P183" s="52"/>
-      <c r="Q183" s="52"/>
-      <c r="R183" s="52"/>
-      <c r="S183" s="52"/>
-      <c r="T183" s="52"/>
-      <c r="U183" s="52"/>
-      <c r="V183" s="52"/>
-      <c r="W183" s="52"/>
-      <c r="X183" s="52"/>
-      <c r="Y183" s="52"/>
-      <c r="Z183" s="52"/>
-      <c r="AA183" s="52"/>
-      <c r="AB183" s="53"/>
+      <c r="H183" s="49"/>
+      <c r="I183" s="50"/>
+      <c r="J183" s="50"/>
+      <c r="K183" s="50"/>
+      <c r="L183" s="50"/>
+      <c r="M183" s="50"/>
+      <c r="N183" s="50"/>
+      <c r="O183" s="50"/>
+      <c r="P183" s="50"/>
+      <c r="Q183" s="50"/>
+      <c r="R183" s="50"/>
+      <c r="S183" s="50"/>
+      <c r="T183" s="50"/>
+      <c r="U183" s="50"/>
+      <c r="V183" s="50"/>
+      <c r="W183" s="50"/>
+      <c r="X183" s="50"/>
+      <c r="Y183" s="50"/>
+      <c r="Z183" s="50"/>
+      <c r="AA183" s="50"/>
+      <c r="AB183" s="51"/>
       <c r="AC183" s="11"/>
     </row>
     <row r="184" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7403,27 +7420,27 @@
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
-      <c r="H184" s="51"/>
-      <c r="I184" s="52"/>
-      <c r="J184" s="52"/>
-      <c r="K184" s="52"/>
-      <c r="L184" s="52"/>
-      <c r="M184" s="52"/>
-      <c r="N184" s="52"/>
-      <c r="O184" s="52"/>
-      <c r="P184" s="52"/>
-      <c r="Q184" s="52"/>
-      <c r="R184" s="52"/>
-      <c r="S184" s="52"/>
-      <c r="T184" s="52"/>
-      <c r="U184" s="52"/>
-      <c r="V184" s="52"/>
-      <c r="W184" s="52"/>
-      <c r="X184" s="52"/>
-      <c r="Y184" s="52"/>
-      <c r="Z184" s="52"/>
-      <c r="AA184" s="52"/>
-      <c r="AB184" s="53"/>
+      <c r="H184" s="49"/>
+      <c r="I184" s="50"/>
+      <c r="J184" s="50"/>
+      <c r="K184" s="50"/>
+      <c r="L184" s="50"/>
+      <c r="M184" s="50"/>
+      <c r="N184" s="50"/>
+      <c r="O184" s="50"/>
+      <c r="P184" s="50"/>
+      <c r="Q184" s="50"/>
+      <c r="R184" s="50"/>
+      <c r="S184" s="50"/>
+      <c r="T184" s="50"/>
+      <c r="U184" s="50"/>
+      <c r="V184" s="50"/>
+      <c r="W184" s="50"/>
+      <c r="X184" s="50"/>
+      <c r="Y184" s="50"/>
+      <c r="Z184" s="50"/>
+      <c r="AA184" s="50"/>
+      <c r="AB184" s="51"/>
       <c r="AC184" s="11"/>
     </row>
     <row r="185" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7433,27 +7450,27 @@
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
-      <c r="H185" s="51"/>
-      <c r="I185" s="52"/>
-      <c r="J185" s="52"/>
-      <c r="K185" s="52"/>
-      <c r="L185" s="52"/>
-      <c r="M185" s="52"/>
-      <c r="N185" s="52"/>
-      <c r="O185" s="52"/>
-      <c r="P185" s="52"/>
-      <c r="Q185" s="52"/>
-      <c r="R185" s="52"/>
-      <c r="S185" s="52"/>
-      <c r="T185" s="52"/>
-      <c r="U185" s="52"/>
-      <c r="V185" s="52"/>
-      <c r="W185" s="52"/>
-      <c r="X185" s="52"/>
-      <c r="Y185" s="52"/>
-      <c r="Z185" s="52"/>
-      <c r="AA185" s="52"/>
-      <c r="AB185" s="53"/>
+      <c r="H185" s="49"/>
+      <c r="I185" s="50"/>
+      <c r="J185" s="50"/>
+      <c r="K185" s="50"/>
+      <c r="L185" s="50"/>
+      <c r="M185" s="50"/>
+      <c r="N185" s="50"/>
+      <c r="O185" s="50"/>
+      <c r="P185" s="50"/>
+      <c r="Q185" s="50"/>
+      <c r="R185" s="50"/>
+      <c r="S185" s="50"/>
+      <c r="T185" s="50"/>
+      <c r="U185" s="50"/>
+      <c r="V185" s="50"/>
+      <c r="W185" s="50"/>
+      <c r="X185" s="50"/>
+      <c r="Y185" s="50"/>
+      <c r="Z185" s="50"/>
+      <c r="AA185" s="50"/>
+      <c r="AB185" s="51"/>
       <c r="AC185" s="11"/>
     </row>
     <row r="186" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7463,27 +7480,27 @@
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
-      <c r="H186" s="51"/>
-      <c r="I186" s="52"/>
-      <c r="J186" s="52"/>
-      <c r="K186" s="52"/>
-      <c r="L186" s="52"/>
-      <c r="M186" s="52"/>
-      <c r="N186" s="52"/>
-      <c r="O186" s="52"/>
-      <c r="P186" s="52"/>
-      <c r="Q186" s="52"/>
-      <c r="R186" s="52"/>
-      <c r="S186" s="52"/>
-      <c r="T186" s="52"/>
-      <c r="U186" s="52"/>
-      <c r="V186" s="52"/>
-      <c r="W186" s="52"/>
-      <c r="X186" s="52"/>
-      <c r="Y186" s="52"/>
-      <c r="Z186" s="52"/>
-      <c r="AA186" s="52"/>
-      <c r="AB186" s="53"/>
+      <c r="H186" s="49"/>
+      <c r="I186" s="50"/>
+      <c r="J186" s="50"/>
+      <c r="K186" s="50"/>
+      <c r="L186" s="50"/>
+      <c r="M186" s="50"/>
+      <c r="N186" s="50"/>
+      <c r="O186" s="50"/>
+      <c r="P186" s="50"/>
+      <c r="Q186" s="50"/>
+      <c r="R186" s="50"/>
+      <c r="S186" s="50"/>
+      <c r="T186" s="50"/>
+      <c r="U186" s="50"/>
+      <c r="V186" s="50"/>
+      <c r="W186" s="50"/>
+      <c r="X186" s="50"/>
+      <c r="Y186" s="50"/>
+      <c r="Z186" s="50"/>
+      <c r="AA186" s="50"/>
+      <c r="AB186" s="51"/>
       <c r="AC186" s="11"/>
     </row>
     <row r="187" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7493,27 +7510,27 @@
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
-      <c r="H187" s="51"/>
-      <c r="I187" s="52"/>
-      <c r="J187" s="52"/>
-      <c r="K187" s="52"/>
-      <c r="L187" s="52"/>
-      <c r="M187" s="52"/>
-      <c r="N187" s="52"/>
-      <c r="O187" s="52"/>
-      <c r="P187" s="52"/>
-      <c r="Q187" s="52"/>
-      <c r="R187" s="52"/>
-      <c r="S187" s="52"/>
-      <c r="T187" s="52"/>
-      <c r="U187" s="52"/>
-      <c r="V187" s="52"/>
-      <c r="W187" s="52"/>
-      <c r="X187" s="52"/>
-      <c r="Y187" s="52"/>
-      <c r="Z187" s="52"/>
-      <c r="AA187" s="52"/>
-      <c r="AB187" s="53"/>
+      <c r="H187" s="49"/>
+      <c r="I187" s="50"/>
+      <c r="J187" s="50"/>
+      <c r="K187" s="50"/>
+      <c r="L187" s="50"/>
+      <c r="M187" s="50"/>
+      <c r="N187" s="50"/>
+      <c r="O187" s="50"/>
+      <c r="P187" s="50"/>
+      <c r="Q187" s="50"/>
+      <c r="R187" s="50"/>
+      <c r="S187" s="50"/>
+      <c r="T187" s="50"/>
+      <c r="U187" s="50"/>
+      <c r="V187" s="50"/>
+      <c r="W187" s="50"/>
+      <c r="X187" s="50"/>
+      <c r="Y187" s="50"/>
+      <c r="Z187" s="50"/>
+      <c r="AA187" s="50"/>
+      <c r="AB187" s="51"/>
       <c r="AC187" s="11"/>
     </row>
     <row r="188" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7523,27 +7540,27 @@
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
-      <c r="H188" s="54"/>
-      <c r="I188" s="55"/>
-      <c r="J188" s="55"/>
-      <c r="K188" s="55"/>
-      <c r="L188" s="55"/>
-      <c r="M188" s="55"/>
-      <c r="N188" s="55"/>
-      <c r="O188" s="55"/>
-      <c r="P188" s="55"/>
-      <c r="Q188" s="55"/>
-      <c r="R188" s="55"/>
-      <c r="S188" s="55"/>
-      <c r="T188" s="55"/>
-      <c r="U188" s="55"/>
-      <c r="V188" s="55"/>
-      <c r="W188" s="55"/>
-      <c r="X188" s="55"/>
-      <c r="Y188" s="55"/>
-      <c r="Z188" s="55"/>
-      <c r="AA188" s="55"/>
-      <c r="AB188" s="56"/>
+      <c r="H188" s="52"/>
+      <c r="I188" s="53"/>
+      <c r="J188" s="53"/>
+      <c r="K188" s="53"/>
+      <c r="L188" s="53"/>
+      <c r="M188" s="53"/>
+      <c r="N188" s="53"/>
+      <c r="O188" s="53"/>
+      <c r="P188" s="53"/>
+      <c r="Q188" s="53"/>
+      <c r="R188" s="53"/>
+      <c r="S188" s="53"/>
+      <c r="T188" s="53"/>
+      <c r="U188" s="53"/>
+      <c r="V188" s="53"/>
+      <c r="W188" s="53"/>
+      <c r="X188" s="53"/>
+      <c r="Y188" s="53"/>
+      <c r="Z188" s="53"/>
+      <c r="AA188" s="53"/>
+      <c r="AB188" s="54"/>
       <c r="AC188" s="11"/>
     </row>
     <row r="189" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7585,27 +7602,27 @@
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
-      <c r="H190" s="48"/>
-      <c r="I190" s="49"/>
-      <c r="J190" s="49"/>
-      <c r="K190" s="49"/>
-      <c r="L190" s="49"/>
-      <c r="M190" s="49"/>
-      <c r="N190" s="49"/>
-      <c r="O190" s="49"/>
-      <c r="P190" s="49"/>
-      <c r="Q190" s="49"/>
-      <c r="R190" s="49"/>
-      <c r="S190" s="49"/>
-      <c r="T190" s="49"/>
-      <c r="U190" s="49"/>
-      <c r="V190" s="49"/>
-      <c r="W190" s="49"/>
-      <c r="X190" s="49"/>
-      <c r="Y190" s="49"/>
-      <c r="Z190" s="49"/>
-      <c r="AA190" s="49"/>
-      <c r="AB190" s="50"/>
+      <c r="H190" s="46"/>
+      <c r="I190" s="47"/>
+      <c r="J190" s="47"/>
+      <c r="K190" s="47"/>
+      <c r="L190" s="47"/>
+      <c r="M190" s="47"/>
+      <c r="N190" s="47"/>
+      <c r="O190" s="47"/>
+      <c r="P190" s="47"/>
+      <c r="Q190" s="47"/>
+      <c r="R190" s="47"/>
+      <c r="S190" s="47"/>
+      <c r="T190" s="47"/>
+      <c r="U190" s="47"/>
+      <c r="V190" s="47"/>
+      <c r="W190" s="47"/>
+      <c r="X190" s="47"/>
+      <c r="Y190" s="47"/>
+      <c r="Z190" s="47"/>
+      <c r="AA190" s="47"/>
+      <c r="AB190" s="48"/>
       <c r="AC190" s="11"/>
     </row>
     <row r="191" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7615,27 +7632,27 @@
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
-      <c r="H191" s="51"/>
-      <c r="I191" s="52"/>
-      <c r="J191" s="52"/>
-      <c r="K191" s="52"/>
-      <c r="L191" s="52"/>
-      <c r="M191" s="52"/>
-      <c r="N191" s="52"/>
-      <c r="O191" s="52"/>
-      <c r="P191" s="52"/>
-      <c r="Q191" s="52"/>
-      <c r="R191" s="52"/>
-      <c r="S191" s="52"/>
-      <c r="T191" s="52"/>
-      <c r="U191" s="52"/>
-      <c r="V191" s="52"/>
-      <c r="W191" s="52"/>
-      <c r="X191" s="52"/>
-      <c r="Y191" s="52"/>
-      <c r="Z191" s="52"/>
-      <c r="AA191" s="52"/>
-      <c r="AB191" s="53"/>
+      <c r="H191" s="49"/>
+      <c r="I191" s="50"/>
+      <c r="J191" s="50"/>
+      <c r="K191" s="50"/>
+      <c r="L191" s="50"/>
+      <c r="M191" s="50"/>
+      <c r="N191" s="50"/>
+      <c r="O191" s="50"/>
+      <c r="P191" s="50"/>
+      <c r="Q191" s="50"/>
+      <c r="R191" s="50"/>
+      <c r="S191" s="50"/>
+      <c r="T191" s="50"/>
+      <c r="U191" s="50"/>
+      <c r="V191" s="50"/>
+      <c r="W191" s="50"/>
+      <c r="X191" s="50"/>
+      <c r="Y191" s="50"/>
+      <c r="Z191" s="50"/>
+      <c r="AA191" s="50"/>
+      <c r="AB191" s="51"/>
       <c r="AC191" s="11"/>
     </row>
     <row r="192" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7645,27 +7662,27 @@
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
-      <c r="H192" s="51"/>
-      <c r="I192" s="52"/>
-      <c r="J192" s="52"/>
-      <c r="K192" s="52"/>
-      <c r="L192" s="52"/>
-      <c r="M192" s="52"/>
-      <c r="N192" s="52"/>
-      <c r="O192" s="52"/>
-      <c r="P192" s="52"/>
-      <c r="Q192" s="52"/>
-      <c r="R192" s="52"/>
-      <c r="S192" s="52"/>
-      <c r="T192" s="52"/>
-      <c r="U192" s="52"/>
-      <c r="V192" s="52"/>
-      <c r="W192" s="52"/>
-      <c r="X192" s="52"/>
-      <c r="Y192" s="52"/>
-      <c r="Z192" s="52"/>
-      <c r="AA192" s="52"/>
-      <c r="AB192" s="53"/>
+      <c r="H192" s="49"/>
+      <c r="I192" s="50"/>
+      <c r="J192" s="50"/>
+      <c r="K192" s="50"/>
+      <c r="L192" s="50"/>
+      <c r="M192" s="50"/>
+      <c r="N192" s="50"/>
+      <c r="O192" s="50"/>
+      <c r="P192" s="50"/>
+      <c r="Q192" s="50"/>
+      <c r="R192" s="50"/>
+      <c r="S192" s="50"/>
+      <c r="T192" s="50"/>
+      <c r="U192" s="50"/>
+      <c r="V192" s="50"/>
+      <c r="W192" s="50"/>
+      <c r="X192" s="50"/>
+      <c r="Y192" s="50"/>
+      <c r="Z192" s="50"/>
+      <c r="AA192" s="50"/>
+      <c r="AB192" s="51"/>
       <c r="AC192" s="11"/>
     </row>
     <row r="193" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7675,27 +7692,27 @@
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
-      <c r="H193" s="51"/>
-      <c r="I193" s="52"/>
-      <c r="J193" s="52"/>
-      <c r="K193" s="52"/>
-      <c r="L193" s="52"/>
-      <c r="M193" s="52"/>
-      <c r="N193" s="52"/>
-      <c r="O193" s="52"/>
-      <c r="P193" s="52"/>
-      <c r="Q193" s="52"/>
-      <c r="R193" s="52"/>
-      <c r="S193" s="52"/>
-      <c r="T193" s="52"/>
-      <c r="U193" s="52"/>
-      <c r="V193" s="52"/>
-      <c r="W193" s="52"/>
-      <c r="X193" s="52"/>
-      <c r="Y193" s="52"/>
-      <c r="Z193" s="52"/>
-      <c r="AA193" s="52"/>
-      <c r="AB193" s="53"/>
+      <c r="H193" s="49"/>
+      <c r="I193" s="50"/>
+      <c r="J193" s="50"/>
+      <c r="K193" s="50"/>
+      <c r="L193" s="50"/>
+      <c r="M193" s="50"/>
+      <c r="N193" s="50"/>
+      <c r="O193" s="50"/>
+      <c r="P193" s="50"/>
+      <c r="Q193" s="50"/>
+      <c r="R193" s="50"/>
+      <c r="S193" s="50"/>
+      <c r="T193" s="50"/>
+      <c r="U193" s="50"/>
+      <c r="V193" s="50"/>
+      <c r="W193" s="50"/>
+      <c r="X193" s="50"/>
+      <c r="Y193" s="50"/>
+      <c r="Z193" s="50"/>
+      <c r="AA193" s="50"/>
+      <c r="AB193" s="51"/>
       <c r="AC193" s="11"/>
     </row>
     <row r="194" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7705,27 +7722,27 @@
       <c r="E194" s="6"/>
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
-      <c r="H194" s="51"/>
-      <c r="I194" s="52"/>
-      <c r="J194" s="52"/>
-      <c r="K194" s="52"/>
-      <c r="L194" s="52"/>
-      <c r="M194" s="52"/>
-      <c r="N194" s="52"/>
-      <c r="O194" s="52"/>
-      <c r="P194" s="52"/>
-      <c r="Q194" s="52"/>
-      <c r="R194" s="52"/>
-      <c r="S194" s="52"/>
-      <c r="T194" s="52"/>
-      <c r="U194" s="52"/>
-      <c r="V194" s="52"/>
-      <c r="W194" s="52"/>
-      <c r="X194" s="52"/>
-      <c r="Y194" s="52"/>
-      <c r="Z194" s="52"/>
-      <c r="AA194" s="52"/>
-      <c r="AB194" s="53"/>
+      <c r="H194" s="49"/>
+      <c r="I194" s="50"/>
+      <c r="J194" s="50"/>
+      <c r="K194" s="50"/>
+      <c r="L194" s="50"/>
+      <c r="M194" s="50"/>
+      <c r="N194" s="50"/>
+      <c r="O194" s="50"/>
+      <c r="P194" s="50"/>
+      <c r="Q194" s="50"/>
+      <c r="R194" s="50"/>
+      <c r="S194" s="50"/>
+      <c r="T194" s="50"/>
+      <c r="U194" s="50"/>
+      <c r="V194" s="50"/>
+      <c r="W194" s="50"/>
+      <c r="X194" s="50"/>
+      <c r="Y194" s="50"/>
+      <c r="Z194" s="50"/>
+      <c r="AA194" s="50"/>
+      <c r="AB194" s="51"/>
       <c r="AC194" s="11"/>
     </row>
     <row r="195" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7735,27 +7752,27 @@
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
-      <c r="H195" s="51"/>
-      <c r="I195" s="52"/>
-      <c r="J195" s="52"/>
-      <c r="K195" s="52"/>
-      <c r="L195" s="52"/>
-      <c r="M195" s="52"/>
-      <c r="N195" s="52"/>
-      <c r="O195" s="52"/>
-      <c r="P195" s="52"/>
-      <c r="Q195" s="52"/>
-      <c r="R195" s="52"/>
-      <c r="S195" s="52"/>
-      <c r="T195" s="52"/>
-      <c r="U195" s="52"/>
-      <c r="V195" s="52"/>
-      <c r="W195" s="52"/>
-      <c r="X195" s="52"/>
-      <c r="Y195" s="52"/>
-      <c r="Z195" s="52"/>
-      <c r="AA195" s="52"/>
-      <c r="AB195" s="53"/>
+      <c r="H195" s="49"/>
+      <c r="I195" s="50"/>
+      <c r="J195" s="50"/>
+      <c r="K195" s="50"/>
+      <c r="L195" s="50"/>
+      <c r="M195" s="50"/>
+      <c r="N195" s="50"/>
+      <c r="O195" s="50"/>
+      <c r="P195" s="50"/>
+      <c r="Q195" s="50"/>
+      <c r="R195" s="50"/>
+      <c r="S195" s="50"/>
+      <c r="T195" s="50"/>
+      <c r="U195" s="50"/>
+      <c r="V195" s="50"/>
+      <c r="W195" s="50"/>
+      <c r="X195" s="50"/>
+      <c r="Y195" s="50"/>
+      <c r="Z195" s="50"/>
+      <c r="AA195" s="50"/>
+      <c r="AB195" s="51"/>
       <c r="AC195" s="11"/>
     </row>
     <row r="196" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7765,27 +7782,27 @@
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
-      <c r="H196" s="54"/>
-      <c r="I196" s="55"/>
-      <c r="J196" s="55"/>
-      <c r="K196" s="55"/>
-      <c r="L196" s="55"/>
-      <c r="M196" s="55"/>
-      <c r="N196" s="55"/>
-      <c r="O196" s="55"/>
-      <c r="P196" s="55"/>
-      <c r="Q196" s="55"/>
-      <c r="R196" s="55"/>
-      <c r="S196" s="55"/>
-      <c r="T196" s="55"/>
-      <c r="U196" s="55"/>
-      <c r="V196" s="55"/>
-      <c r="W196" s="55"/>
-      <c r="X196" s="55"/>
-      <c r="Y196" s="55"/>
-      <c r="Z196" s="55"/>
-      <c r="AA196" s="55"/>
-      <c r="AB196" s="56"/>
+      <c r="H196" s="52"/>
+      <c r="I196" s="53"/>
+      <c r="J196" s="53"/>
+      <c r="K196" s="53"/>
+      <c r="L196" s="53"/>
+      <c r="M196" s="53"/>
+      <c r="N196" s="53"/>
+      <c r="O196" s="53"/>
+      <c r="P196" s="53"/>
+      <c r="Q196" s="53"/>
+      <c r="R196" s="53"/>
+      <c r="S196" s="53"/>
+      <c r="T196" s="53"/>
+      <c r="U196" s="53"/>
+      <c r="V196" s="53"/>
+      <c r="W196" s="53"/>
+      <c r="X196" s="53"/>
+      <c r="Y196" s="53"/>
+      <c r="Z196" s="53"/>
+      <c r="AA196" s="53"/>
+      <c r="AB196" s="54"/>
       <c r="AC196" s="11"/>
     </row>
     <row r="197" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7893,27 +7910,27 @@
         <v>2</v>
       </c>
       <c r="G201" s="6"/>
-      <c r="H201" s="48"/>
-      <c r="I201" s="49"/>
-      <c r="J201" s="49"/>
-      <c r="K201" s="49"/>
-      <c r="L201" s="49"/>
-      <c r="M201" s="49"/>
-      <c r="N201" s="49"/>
-      <c r="O201" s="49"/>
-      <c r="P201" s="49"/>
-      <c r="Q201" s="49"/>
-      <c r="R201" s="49"/>
-      <c r="S201" s="49"/>
-      <c r="T201" s="49"/>
-      <c r="U201" s="49"/>
-      <c r="V201" s="49"/>
-      <c r="W201" s="49"/>
-      <c r="X201" s="49"/>
-      <c r="Y201" s="49"/>
-      <c r="Z201" s="49"/>
-      <c r="AA201" s="49"/>
-      <c r="AB201" s="50"/>
+      <c r="H201" s="46"/>
+      <c r="I201" s="47"/>
+      <c r="J201" s="47"/>
+      <c r="K201" s="47"/>
+      <c r="L201" s="47"/>
+      <c r="M201" s="47"/>
+      <c r="N201" s="47"/>
+      <c r="O201" s="47"/>
+      <c r="P201" s="47"/>
+      <c r="Q201" s="47"/>
+      <c r="R201" s="47"/>
+      <c r="S201" s="47"/>
+      <c r="T201" s="47"/>
+      <c r="U201" s="47"/>
+      <c r="V201" s="47"/>
+      <c r="W201" s="47"/>
+      <c r="X201" s="47"/>
+      <c r="Y201" s="47"/>
+      <c r="Z201" s="47"/>
+      <c r="AA201" s="47"/>
+      <c r="AB201" s="48"/>
       <c r="AC201" s="11"/>
     </row>
     <row r="202" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7923,27 +7940,27 @@
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
-      <c r="H202" s="51"/>
-      <c r="I202" s="52"/>
-      <c r="J202" s="52"/>
-      <c r="K202" s="52"/>
-      <c r="L202" s="52"/>
-      <c r="M202" s="52"/>
-      <c r="N202" s="52"/>
-      <c r="O202" s="52"/>
-      <c r="P202" s="52"/>
-      <c r="Q202" s="52"/>
-      <c r="R202" s="52"/>
-      <c r="S202" s="52"/>
-      <c r="T202" s="52"/>
-      <c r="U202" s="52"/>
-      <c r="V202" s="52"/>
-      <c r="W202" s="52"/>
-      <c r="X202" s="52"/>
-      <c r="Y202" s="52"/>
-      <c r="Z202" s="52"/>
-      <c r="AA202" s="52"/>
-      <c r="AB202" s="53"/>
+      <c r="H202" s="49"/>
+      <c r="I202" s="50"/>
+      <c r="J202" s="50"/>
+      <c r="K202" s="50"/>
+      <c r="L202" s="50"/>
+      <c r="M202" s="50"/>
+      <c r="N202" s="50"/>
+      <c r="O202" s="50"/>
+      <c r="P202" s="50"/>
+      <c r="Q202" s="50"/>
+      <c r="R202" s="50"/>
+      <c r="S202" s="50"/>
+      <c r="T202" s="50"/>
+      <c r="U202" s="50"/>
+      <c r="V202" s="50"/>
+      <c r="W202" s="50"/>
+      <c r="X202" s="50"/>
+      <c r="Y202" s="50"/>
+      <c r="Z202" s="50"/>
+      <c r="AA202" s="50"/>
+      <c r="AB202" s="51"/>
       <c r="AC202" s="11"/>
     </row>
     <row r="203" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7953,27 +7970,27 @@
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
-      <c r="H203" s="51"/>
-      <c r="I203" s="52"/>
-      <c r="J203" s="52"/>
-      <c r="K203" s="52"/>
-      <c r="L203" s="52"/>
-      <c r="M203" s="52"/>
-      <c r="N203" s="52"/>
-      <c r="O203" s="52"/>
-      <c r="P203" s="52"/>
-      <c r="Q203" s="52"/>
-      <c r="R203" s="52"/>
-      <c r="S203" s="52"/>
-      <c r="T203" s="52"/>
-      <c r="U203" s="52"/>
-      <c r="V203" s="52"/>
-      <c r="W203" s="52"/>
-      <c r="X203" s="52"/>
-      <c r="Y203" s="52"/>
-      <c r="Z203" s="52"/>
-      <c r="AA203" s="52"/>
-      <c r="AB203" s="53"/>
+      <c r="H203" s="49"/>
+      <c r="I203" s="50"/>
+      <c r="J203" s="50"/>
+      <c r="K203" s="50"/>
+      <c r="L203" s="50"/>
+      <c r="M203" s="50"/>
+      <c r="N203" s="50"/>
+      <c r="O203" s="50"/>
+      <c r="P203" s="50"/>
+      <c r="Q203" s="50"/>
+      <c r="R203" s="50"/>
+      <c r="S203" s="50"/>
+      <c r="T203" s="50"/>
+      <c r="U203" s="50"/>
+      <c r="V203" s="50"/>
+      <c r="W203" s="50"/>
+      <c r="X203" s="50"/>
+      <c r="Y203" s="50"/>
+      <c r="Z203" s="50"/>
+      <c r="AA203" s="50"/>
+      <c r="AB203" s="51"/>
       <c r="AC203" s="11"/>
     </row>
     <row r="204" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7983,27 +8000,27 @@
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
-      <c r="H204" s="51"/>
-      <c r="I204" s="52"/>
-      <c r="J204" s="52"/>
-      <c r="K204" s="52"/>
-      <c r="L204" s="52"/>
-      <c r="M204" s="52"/>
-      <c r="N204" s="52"/>
-      <c r="O204" s="52"/>
-      <c r="P204" s="52"/>
-      <c r="Q204" s="52"/>
-      <c r="R204" s="52"/>
-      <c r="S204" s="52"/>
-      <c r="T204" s="52"/>
-      <c r="U204" s="52"/>
-      <c r="V204" s="52"/>
-      <c r="W204" s="52"/>
-      <c r="X204" s="52"/>
-      <c r="Y204" s="52"/>
-      <c r="Z204" s="52"/>
-      <c r="AA204" s="52"/>
-      <c r="AB204" s="53"/>
+      <c r="H204" s="49"/>
+      <c r="I204" s="50"/>
+      <c r="J204" s="50"/>
+      <c r="K204" s="50"/>
+      <c r="L204" s="50"/>
+      <c r="M204" s="50"/>
+      <c r="N204" s="50"/>
+      <c r="O204" s="50"/>
+      <c r="P204" s="50"/>
+      <c r="Q204" s="50"/>
+      <c r="R204" s="50"/>
+      <c r="S204" s="50"/>
+      <c r="T204" s="50"/>
+      <c r="U204" s="50"/>
+      <c r="V204" s="50"/>
+      <c r="W204" s="50"/>
+      <c r="X204" s="50"/>
+      <c r="Y204" s="50"/>
+      <c r="Z204" s="50"/>
+      <c r="AA204" s="50"/>
+      <c r="AB204" s="51"/>
       <c r="AC204" s="11"/>
     </row>
     <row r="205" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8013,27 +8030,27 @@
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
       <c r="G205" s="6"/>
-      <c r="H205" s="51"/>
-      <c r="I205" s="52"/>
-      <c r="J205" s="52"/>
-      <c r="K205" s="52"/>
-      <c r="L205" s="52"/>
-      <c r="M205" s="52"/>
-      <c r="N205" s="52"/>
-      <c r="O205" s="52"/>
-      <c r="P205" s="52"/>
-      <c r="Q205" s="52"/>
-      <c r="R205" s="52"/>
-      <c r="S205" s="52"/>
-      <c r="T205" s="52"/>
-      <c r="U205" s="52"/>
-      <c r="V205" s="52"/>
-      <c r="W205" s="52"/>
-      <c r="X205" s="52"/>
-      <c r="Y205" s="52"/>
-      <c r="Z205" s="52"/>
-      <c r="AA205" s="52"/>
-      <c r="AB205" s="53"/>
+      <c r="H205" s="49"/>
+      <c r="I205" s="50"/>
+      <c r="J205" s="50"/>
+      <c r="K205" s="50"/>
+      <c r="L205" s="50"/>
+      <c r="M205" s="50"/>
+      <c r="N205" s="50"/>
+      <c r="O205" s="50"/>
+      <c r="P205" s="50"/>
+      <c r="Q205" s="50"/>
+      <c r="R205" s="50"/>
+      <c r="S205" s="50"/>
+      <c r="T205" s="50"/>
+      <c r="U205" s="50"/>
+      <c r="V205" s="50"/>
+      <c r="W205" s="50"/>
+      <c r="X205" s="50"/>
+      <c r="Y205" s="50"/>
+      <c r="Z205" s="50"/>
+      <c r="AA205" s="50"/>
+      <c r="AB205" s="51"/>
       <c r="AC205" s="11"/>
     </row>
     <row r="206" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8043,27 +8060,27 @@
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
-      <c r="H206" s="51"/>
-      <c r="I206" s="52"/>
-      <c r="J206" s="52"/>
-      <c r="K206" s="52"/>
-      <c r="L206" s="52"/>
-      <c r="M206" s="52"/>
-      <c r="N206" s="52"/>
-      <c r="O206" s="52"/>
-      <c r="P206" s="52"/>
-      <c r="Q206" s="52"/>
-      <c r="R206" s="52"/>
-      <c r="S206" s="52"/>
-      <c r="T206" s="52"/>
-      <c r="U206" s="52"/>
-      <c r="V206" s="52"/>
-      <c r="W206" s="52"/>
-      <c r="X206" s="52"/>
-      <c r="Y206" s="52"/>
-      <c r="Z206" s="52"/>
-      <c r="AA206" s="52"/>
-      <c r="AB206" s="53"/>
+      <c r="H206" s="49"/>
+      <c r="I206" s="50"/>
+      <c r="J206" s="50"/>
+      <c r="K206" s="50"/>
+      <c r="L206" s="50"/>
+      <c r="M206" s="50"/>
+      <c r="N206" s="50"/>
+      <c r="O206" s="50"/>
+      <c r="P206" s="50"/>
+      <c r="Q206" s="50"/>
+      <c r="R206" s="50"/>
+      <c r="S206" s="50"/>
+      <c r="T206" s="50"/>
+      <c r="U206" s="50"/>
+      <c r="V206" s="50"/>
+      <c r="W206" s="50"/>
+      <c r="X206" s="50"/>
+      <c r="Y206" s="50"/>
+      <c r="Z206" s="50"/>
+      <c r="AA206" s="50"/>
+      <c r="AB206" s="51"/>
       <c r="AC206" s="11"/>
     </row>
     <row r="207" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8073,27 +8090,27 @@
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
-      <c r="H207" s="54"/>
-      <c r="I207" s="55"/>
-      <c r="J207" s="55"/>
-      <c r="K207" s="55"/>
-      <c r="L207" s="55"/>
-      <c r="M207" s="55"/>
-      <c r="N207" s="55"/>
-      <c r="O207" s="55"/>
-      <c r="P207" s="55"/>
-      <c r="Q207" s="55"/>
-      <c r="R207" s="55"/>
-      <c r="S207" s="55"/>
-      <c r="T207" s="55"/>
-      <c r="U207" s="55"/>
-      <c r="V207" s="55"/>
-      <c r="W207" s="55"/>
-      <c r="X207" s="55"/>
-      <c r="Y207" s="55"/>
-      <c r="Z207" s="55"/>
-      <c r="AA207" s="55"/>
-      <c r="AB207" s="56"/>
+      <c r="H207" s="52"/>
+      <c r="I207" s="53"/>
+      <c r="J207" s="53"/>
+      <c r="K207" s="53"/>
+      <c r="L207" s="53"/>
+      <c r="M207" s="53"/>
+      <c r="N207" s="53"/>
+      <c r="O207" s="53"/>
+      <c r="P207" s="53"/>
+      <c r="Q207" s="53"/>
+      <c r="R207" s="53"/>
+      <c r="S207" s="53"/>
+      <c r="T207" s="53"/>
+      <c r="U207" s="53"/>
+      <c r="V207" s="53"/>
+      <c r="W207" s="53"/>
+      <c r="X207" s="53"/>
+      <c r="Y207" s="53"/>
+      <c r="Z207" s="53"/>
+      <c r="AA207" s="53"/>
+      <c r="AB207" s="54"/>
       <c r="AC207" s="11"/>
     </row>
     <row r="208" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8135,27 +8152,27 @@
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
-      <c r="H209" s="48"/>
-      <c r="I209" s="49"/>
-      <c r="J209" s="49"/>
-      <c r="K209" s="49"/>
-      <c r="L209" s="49"/>
-      <c r="M209" s="49"/>
-      <c r="N209" s="49"/>
-      <c r="O209" s="49"/>
-      <c r="P209" s="49"/>
-      <c r="Q209" s="49"/>
-      <c r="R209" s="49"/>
-      <c r="S209" s="49"/>
-      <c r="T209" s="49"/>
-      <c r="U209" s="49"/>
-      <c r="V209" s="49"/>
-      <c r="W209" s="49"/>
-      <c r="X209" s="49"/>
-      <c r="Y209" s="49"/>
-      <c r="Z209" s="49"/>
-      <c r="AA209" s="49"/>
-      <c r="AB209" s="50"/>
+      <c r="H209" s="46"/>
+      <c r="I209" s="47"/>
+      <c r="J209" s="47"/>
+      <c r="K209" s="47"/>
+      <c r="L209" s="47"/>
+      <c r="M209" s="47"/>
+      <c r="N209" s="47"/>
+      <c r="O209" s="47"/>
+      <c r="P209" s="47"/>
+      <c r="Q209" s="47"/>
+      <c r="R209" s="47"/>
+      <c r="S209" s="47"/>
+      <c r="T209" s="47"/>
+      <c r="U209" s="47"/>
+      <c r="V209" s="47"/>
+      <c r="W209" s="47"/>
+      <c r="X209" s="47"/>
+      <c r="Y209" s="47"/>
+      <c r="Z209" s="47"/>
+      <c r="AA209" s="47"/>
+      <c r="AB209" s="48"/>
       <c r="AC209" s="11"/>
     </row>
     <row r="210" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8165,27 +8182,27 @@
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
-      <c r="H210" s="51"/>
-      <c r="I210" s="52"/>
-      <c r="J210" s="52"/>
-      <c r="K210" s="52"/>
-      <c r="L210" s="52"/>
-      <c r="M210" s="52"/>
-      <c r="N210" s="52"/>
-      <c r="O210" s="52"/>
-      <c r="P210" s="52"/>
-      <c r="Q210" s="52"/>
-      <c r="R210" s="52"/>
-      <c r="S210" s="52"/>
-      <c r="T210" s="52"/>
-      <c r="U210" s="52"/>
-      <c r="V210" s="52"/>
-      <c r="W210" s="52"/>
-      <c r="X210" s="52"/>
-      <c r="Y210" s="52"/>
-      <c r="Z210" s="52"/>
-      <c r="AA210" s="52"/>
-      <c r="AB210" s="53"/>
+      <c r="H210" s="49"/>
+      <c r="I210" s="50"/>
+      <c r="J210" s="50"/>
+      <c r="K210" s="50"/>
+      <c r="L210" s="50"/>
+      <c r="M210" s="50"/>
+      <c r="N210" s="50"/>
+      <c r="O210" s="50"/>
+      <c r="P210" s="50"/>
+      <c r="Q210" s="50"/>
+      <c r="R210" s="50"/>
+      <c r="S210" s="50"/>
+      <c r="T210" s="50"/>
+      <c r="U210" s="50"/>
+      <c r="V210" s="50"/>
+      <c r="W210" s="50"/>
+      <c r="X210" s="50"/>
+      <c r="Y210" s="50"/>
+      <c r="Z210" s="50"/>
+      <c r="AA210" s="50"/>
+      <c r="AB210" s="51"/>
       <c r="AC210" s="11"/>
     </row>
     <row r="211" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8195,27 +8212,27 @@
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
       <c r="G211" s="6"/>
-      <c r="H211" s="51"/>
-      <c r="I211" s="52"/>
-      <c r="J211" s="52"/>
-      <c r="K211" s="52"/>
-      <c r="L211" s="52"/>
-      <c r="M211" s="52"/>
-      <c r="N211" s="52"/>
-      <c r="O211" s="52"/>
-      <c r="P211" s="52"/>
-      <c r="Q211" s="52"/>
-      <c r="R211" s="52"/>
-      <c r="S211" s="52"/>
-      <c r="T211" s="52"/>
-      <c r="U211" s="52"/>
-      <c r="V211" s="52"/>
-      <c r="W211" s="52"/>
-      <c r="X211" s="52"/>
-      <c r="Y211" s="52"/>
-      <c r="Z211" s="52"/>
-      <c r="AA211" s="52"/>
-      <c r="AB211" s="53"/>
+      <c r="H211" s="49"/>
+      <c r="I211" s="50"/>
+      <c r="J211" s="50"/>
+      <c r="K211" s="50"/>
+      <c r="L211" s="50"/>
+      <c r="M211" s="50"/>
+      <c r="N211" s="50"/>
+      <c r="O211" s="50"/>
+      <c r="P211" s="50"/>
+      <c r="Q211" s="50"/>
+      <c r="R211" s="50"/>
+      <c r="S211" s="50"/>
+      <c r="T211" s="50"/>
+      <c r="U211" s="50"/>
+      <c r="V211" s="50"/>
+      <c r="W211" s="50"/>
+      <c r="X211" s="50"/>
+      <c r="Y211" s="50"/>
+      <c r="Z211" s="50"/>
+      <c r="AA211" s="50"/>
+      <c r="AB211" s="51"/>
       <c r="AC211" s="11"/>
     </row>
     <row r="212" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8225,27 +8242,27 @@
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
-      <c r="H212" s="51"/>
-      <c r="I212" s="52"/>
-      <c r="J212" s="52"/>
-      <c r="K212" s="52"/>
-      <c r="L212" s="52"/>
-      <c r="M212" s="52"/>
-      <c r="N212" s="52"/>
-      <c r="O212" s="52"/>
-      <c r="P212" s="52"/>
-      <c r="Q212" s="52"/>
-      <c r="R212" s="52"/>
-      <c r="S212" s="52"/>
-      <c r="T212" s="52"/>
-      <c r="U212" s="52"/>
-      <c r="V212" s="52"/>
-      <c r="W212" s="52"/>
-      <c r="X212" s="52"/>
-      <c r="Y212" s="52"/>
-      <c r="Z212" s="52"/>
-      <c r="AA212" s="52"/>
-      <c r="AB212" s="53"/>
+      <c r="H212" s="49"/>
+      <c r="I212" s="50"/>
+      <c r="J212" s="50"/>
+      <c r="K212" s="50"/>
+      <c r="L212" s="50"/>
+      <c r="M212" s="50"/>
+      <c r="N212" s="50"/>
+      <c r="O212" s="50"/>
+      <c r="P212" s="50"/>
+      <c r="Q212" s="50"/>
+      <c r="R212" s="50"/>
+      <c r="S212" s="50"/>
+      <c r="T212" s="50"/>
+      <c r="U212" s="50"/>
+      <c r="V212" s="50"/>
+      <c r="W212" s="50"/>
+      <c r="X212" s="50"/>
+      <c r="Y212" s="50"/>
+      <c r="Z212" s="50"/>
+      <c r="AA212" s="50"/>
+      <c r="AB212" s="51"/>
       <c r="AC212" s="11"/>
     </row>
     <row r="213" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8255,27 +8272,27 @@
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
       <c r="G213" s="6"/>
-      <c r="H213" s="51"/>
-      <c r="I213" s="52"/>
-      <c r="J213" s="52"/>
-      <c r="K213" s="52"/>
-      <c r="L213" s="52"/>
-      <c r="M213" s="52"/>
-      <c r="N213" s="52"/>
-      <c r="O213" s="52"/>
-      <c r="P213" s="52"/>
-      <c r="Q213" s="52"/>
-      <c r="R213" s="52"/>
-      <c r="S213" s="52"/>
-      <c r="T213" s="52"/>
-      <c r="U213" s="52"/>
-      <c r="V213" s="52"/>
-      <c r="W213" s="52"/>
-      <c r="X213" s="52"/>
-      <c r="Y213" s="52"/>
-      <c r="Z213" s="52"/>
-      <c r="AA213" s="52"/>
-      <c r="AB213" s="53"/>
+      <c r="H213" s="49"/>
+      <c r="I213" s="50"/>
+      <c r="J213" s="50"/>
+      <c r="K213" s="50"/>
+      <c r="L213" s="50"/>
+      <c r="M213" s="50"/>
+      <c r="N213" s="50"/>
+      <c r="O213" s="50"/>
+      <c r="P213" s="50"/>
+      <c r="Q213" s="50"/>
+      <c r="R213" s="50"/>
+      <c r="S213" s="50"/>
+      <c r="T213" s="50"/>
+      <c r="U213" s="50"/>
+      <c r="V213" s="50"/>
+      <c r="W213" s="50"/>
+      <c r="X213" s="50"/>
+      <c r="Y213" s="50"/>
+      <c r="Z213" s="50"/>
+      <c r="AA213" s="50"/>
+      <c r="AB213" s="51"/>
       <c r="AC213" s="11"/>
     </row>
     <row r="214" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8285,27 +8302,27 @@
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
       <c r="G214" s="6"/>
-      <c r="H214" s="51"/>
-      <c r="I214" s="52"/>
-      <c r="J214" s="52"/>
-      <c r="K214" s="52"/>
-      <c r="L214" s="52"/>
-      <c r="M214" s="52"/>
-      <c r="N214" s="52"/>
-      <c r="O214" s="52"/>
-      <c r="P214" s="52"/>
-      <c r="Q214" s="52"/>
-      <c r="R214" s="52"/>
-      <c r="S214" s="52"/>
-      <c r="T214" s="52"/>
-      <c r="U214" s="52"/>
-      <c r="V214" s="52"/>
-      <c r="W214" s="52"/>
-      <c r="X214" s="52"/>
-      <c r="Y214" s="52"/>
-      <c r="Z214" s="52"/>
-      <c r="AA214" s="52"/>
-      <c r="AB214" s="53"/>
+      <c r="H214" s="49"/>
+      <c r="I214" s="50"/>
+      <c r="J214" s="50"/>
+      <c r="K214" s="50"/>
+      <c r="L214" s="50"/>
+      <c r="M214" s="50"/>
+      <c r="N214" s="50"/>
+      <c r="O214" s="50"/>
+      <c r="P214" s="50"/>
+      <c r="Q214" s="50"/>
+      <c r="R214" s="50"/>
+      <c r="S214" s="50"/>
+      <c r="T214" s="50"/>
+      <c r="U214" s="50"/>
+      <c r="V214" s="50"/>
+      <c r="W214" s="50"/>
+      <c r="X214" s="50"/>
+      <c r="Y214" s="50"/>
+      <c r="Z214" s="50"/>
+      <c r="AA214" s="50"/>
+      <c r="AB214" s="51"/>
       <c r="AC214" s="11"/>
     </row>
     <row r="215" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8315,27 +8332,27 @@
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
       <c r="G215" s="6"/>
-      <c r="H215" s="54"/>
-      <c r="I215" s="55"/>
-      <c r="J215" s="55"/>
-      <c r="K215" s="55"/>
-      <c r="L215" s="55"/>
-      <c r="M215" s="55"/>
-      <c r="N215" s="55"/>
-      <c r="O215" s="55"/>
-      <c r="P215" s="55"/>
-      <c r="Q215" s="55"/>
-      <c r="R215" s="55"/>
-      <c r="S215" s="55"/>
-      <c r="T215" s="55"/>
-      <c r="U215" s="55"/>
-      <c r="V215" s="55"/>
-      <c r="W215" s="55"/>
-      <c r="X215" s="55"/>
-      <c r="Y215" s="55"/>
-      <c r="Z215" s="55"/>
-      <c r="AA215" s="55"/>
-      <c r="AB215" s="56"/>
+      <c r="H215" s="52"/>
+      <c r="I215" s="53"/>
+      <c r="J215" s="53"/>
+      <c r="K215" s="53"/>
+      <c r="L215" s="53"/>
+      <c r="M215" s="53"/>
+      <c r="N215" s="53"/>
+      <c r="O215" s="53"/>
+      <c r="P215" s="53"/>
+      <c r="Q215" s="53"/>
+      <c r="R215" s="53"/>
+      <c r="S215" s="53"/>
+      <c r="T215" s="53"/>
+      <c r="U215" s="53"/>
+      <c r="V215" s="53"/>
+      <c r="W215" s="53"/>
+      <c r="X215" s="53"/>
+      <c r="Y215" s="53"/>
+      <c r="Z215" s="53"/>
+      <c r="AA215" s="53"/>
+      <c r="AB215" s="54"/>
       <c r="AC215" s="11"/>
     </row>
     <row r="216" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8370,6 +8387,43 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B25:B42"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="H27:AB33"/>
+    <mergeCell ref="H35:AB41"/>
+    <mergeCell ref="B44:B61"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:AB52"/>
+    <mergeCell ref="H54:AB60"/>
+    <mergeCell ref="B63:B83"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="H76:AB82"/>
+    <mergeCell ref="B85:B102"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="H87:AB93"/>
+    <mergeCell ref="H95:AB101"/>
+    <mergeCell ref="H65:AB74"/>
+    <mergeCell ref="B104:B121"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="H106:AB112"/>
+    <mergeCell ref="H114:AB120"/>
+    <mergeCell ref="B123:B140"/>
+    <mergeCell ref="D125:E125"/>
+    <mergeCell ref="H125:AB131"/>
+    <mergeCell ref="H133:AB139"/>
+    <mergeCell ref="B142:B159"/>
+    <mergeCell ref="D144:E144"/>
+    <mergeCell ref="H144:AB150"/>
+    <mergeCell ref="H152:AB158"/>
+    <mergeCell ref="B161:B178"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="H163:AB169"/>
+    <mergeCell ref="H171:AB177"/>
     <mergeCell ref="B180:B197"/>
     <mergeCell ref="D182:E182"/>
     <mergeCell ref="H182:AB188"/>
@@ -8378,48 +8432,12 @@
     <mergeCell ref="D201:E201"/>
     <mergeCell ref="H201:AB207"/>
     <mergeCell ref="H209:AB215"/>
-    <mergeCell ref="B142:B159"/>
-    <mergeCell ref="D144:E144"/>
-    <mergeCell ref="H144:AB150"/>
-    <mergeCell ref="H152:AB158"/>
-    <mergeCell ref="B161:B178"/>
-    <mergeCell ref="D163:E163"/>
-    <mergeCell ref="H163:AB169"/>
-    <mergeCell ref="H171:AB177"/>
-    <mergeCell ref="B104:B121"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="H106:AB112"/>
-    <mergeCell ref="H114:AB120"/>
-    <mergeCell ref="B123:B140"/>
-    <mergeCell ref="D125:E125"/>
-    <mergeCell ref="H125:AB131"/>
-    <mergeCell ref="H133:AB139"/>
-    <mergeCell ref="B63:B83"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="H76:AB82"/>
-    <mergeCell ref="B85:B102"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="H87:AB93"/>
-    <mergeCell ref="H95:AB101"/>
-    <mergeCell ref="H65:AB74"/>
-    <mergeCell ref="B25:B42"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="H27:AB33"/>
-    <mergeCell ref="H35:AB41"/>
-    <mergeCell ref="B44:B61"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:AB52"/>
-    <mergeCell ref="H54:AB60"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H65" r:id="rId1" display="https://learn.microsoft.com/en-us/dotnet/maui/platform-integration/device/geolocation" xr:uid="{6A2F2CBC-218B-43EA-806A-9BF39365BDB2}"/>
     <hyperlink ref="H87" r:id="rId2" display="https://dummyjson.com/docs/posts_x000a_" xr:uid="{AFA4F006-3754-4C92-A758-50B6915FC379}"/>
     <hyperlink ref="H106" r:id="rId3" display="https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/refreshview_x000a_" xr:uid="{80E066CC-CE62-4304-89CB-2C900A3EBBE5}"/>
+    <hyperlink ref="H125" r:id="rId4" display="https://learn.microsoft.com/de-de/dotnet/communitytoolkit/maui/views/mediaelement" xr:uid="{A9CAE96C-CEA9-42B5-BE11-A814029EF10A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -8446,11 +8464,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>21</v>
       </c>
@@ -9292,27 +9310,27 @@
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" s="19"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="49"/>
-      <c r="O34" s="49"/>
-      <c r="P34" s="49"/>
-      <c r="Q34" s="49"/>
-      <c r="R34" s="49"/>
-      <c r="S34" s="49"/>
-      <c r="T34" s="49"/>
-      <c r="U34" s="49"/>
-      <c r="V34" s="49"/>
-      <c r="W34" s="49"/>
-      <c r="X34" s="49"/>
-      <c r="Y34" s="49"/>
-      <c r="Z34" s="49"/>
-      <c r="AA34" s="49"/>
-      <c r="AB34" s="50"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
+      <c r="N34" s="47"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="47"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47"/>
+      <c r="S34" s="47"/>
+      <c r="T34" s="47"/>
+      <c r="U34" s="47"/>
+      <c r="V34" s="47"/>
+      <c r="W34" s="47"/>
+      <c r="X34" s="47"/>
+      <c r="Y34" s="47"/>
+      <c r="Z34" s="47"/>
+      <c r="AA34" s="47"/>
+      <c r="AB34" s="48"/>
       <c r="AC34" s="16"/>
     </row>
     <row r="35" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9322,27 +9340,27 @@
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
-      <c r="T35" s="52"/>
-      <c r="U35" s="52"/>
-      <c r="V35" s="52"/>
-      <c r="W35" s="52"/>
-      <c r="X35" s="52"/>
-      <c r="Y35" s="52"/>
-      <c r="Z35" s="52"/>
-      <c r="AA35" s="52"/>
-      <c r="AB35" s="53"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
+      <c r="P35" s="50"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="50"/>
+      <c r="S35" s="50"/>
+      <c r="T35" s="50"/>
+      <c r="U35" s="50"/>
+      <c r="V35" s="50"/>
+      <c r="W35" s="50"/>
+      <c r="X35" s="50"/>
+      <c r="Y35" s="50"/>
+      <c r="Z35" s="50"/>
+      <c r="AA35" s="50"/>
+      <c r="AB35" s="51"/>
       <c r="AC35" s="16"/>
     </row>
     <row r="36" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9352,27 +9370,27 @@
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="52"/>
-      <c r="Q36" s="52"/>
-      <c r="R36" s="52"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="52"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="52"/>
-      <c r="W36" s="52"/>
-      <c r="X36" s="52"/>
-      <c r="Y36" s="52"/>
-      <c r="Z36" s="52"/>
-      <c r="AA36" s="52"/>
-      <c r="AB36" s="53"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="50"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="50"/>
+      <c r="P36" s="50"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="50"/>
+      <c r="S36" s="50"/>
+      <c r="T36" s="50"/>
+      <c r="U36" s="50"/>
+      <c r="V36" s="50"/>
+      <c r="W36" s="50"/>
+      <c r="X36" s="50"/>
+      <c r="Y36" s="50"/>
+      <c r="Z36" s="50"/>
+      <c r="AA36" s="50"/>
+      <c r="AB36" s="51"/>
       <c r="AC36" s="16"/>
     </row>
     <row r="37" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9382,27 +9400,27 @@
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="52"/>
-      <c r="O37" s="52"/>
-      <c r="P37" s="52"/>
-      <c r="Q37" s="52"/>
-      <c r="R37" s="52"/>
-      <c r="S37" s="52"/>
-      <c r="T37" s="52"/>
-      <c r="U37" s="52"/>
-      <c r="V37" s="52"/>
-      <c r="W37" s="52"/>
-      <c r="X37" s="52"/>
-      <c r="Y37" s="52"/>
-      <c r="Z37" s="52"/>
-      <c r="AA37" s="52"/>
-      <c r="AB37" s="53"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="50"/>
+      <c r="M37" s="50"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="50"/>
+      <c r="P37" s="50"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="50"/>
+      <c r="S37" s="50"/>
+      <c r="T37" s="50"/>
+      <c r="U37" s="50"/>
+      <c r="V37" s="50"/>
+      <c r="W37" s="50"/>
+      <c r="X37" s="50"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="51"/>
       <c r="AC37" s="16"/>
     </row>
     <row r="38" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9412,27 +9430,27 @@
       <c r="E38" s="19"/>
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="52"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="52"/>
-      <c r="Q38" s="52"/>
-      <c r="R38" s="52"/>
-      <c r="S38" s="52"/>
-      <c r="T38" s="52"/>
-      <c r="U38" s="52"/>
-      <c r="V38" s="52"/>
-      <c r="W38" s="52"/>
-      <c r="X38" s="52"/>
-      <c r="Y38" s="52"/>
-      <c r="Z38" s="52"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="53"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="50"/>
+      <c r="L38" s="50"/>
+      <c r="M38" s="50"/>
+      <c r="N38" s="50"/>
+      <c r="O38" s="50"/>
+      <c r="P38" s="50"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="50"/>
+      <c r="S38" s="50"/>
+      <c r="T38" s="50"/>
+      <c r="U38" s="50"/>
+      <c r="V38" s="50"/>
+      <c r="W38" s="50"/>
+      <c r="X38" s="50"/>
+      <c r="Y38" s="50"/>
+      <c r="Z38" s="50"/>
+      <c r="AA38" s="50"/>
+      <c r="AB38" s="51"/>
       <c r="AC38" s="16"/>
     </row>
     <row r="39" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9442,27 +9460,27 @@
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="52"/>
-      <c r="K39" s="52"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="52"/>
-      <c r="N39" s="52"/>
-      <c r="O39" s="52"/>
-      <c r="P39" s="52"/>
-      <c r="Q39" s="52"/>
-      <c r="R39" s="52"/>
-      <c r="S39" s="52"/>
-      <c r="T39" s="52"/>
-      <c r="U39" s="52"/>
-      <c r="V39" s="52"/>
-      <c r="W39" s="52"/>
-      <c r="X39" s="52"/>
-      <c r="Y39" s="52"/>
-      <c r="Z39" s="52"/>
-      <c r="AA39" s="52"/>
-      <c r="AB39" s="53"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="50"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="50"/>
+      <c r="P39" s="50"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50"/>
+      <c r="S39" s="50"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="50"/>
+      <c r="V39" s="50"/>
+      <c r="W39" s="50"/>
+      <c r="X39" s="50"/>
+      <c r="Y39" s="50"/>
+      <c r="Z39" s="50"/>
+      <c r="AA39" s="50"/>
+      <c r="AB39" s="51"/>
       <c r="AC39" s="16"/>
     </row>
     <row r="40" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9472,27 +9490,27 @@
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="55"/>
-      <c r="R40" s="55"/>
-      <c r="S40" s="55"/>
-      <c r="T40" s="55"/>
-      <c r="U40" s="55"/>
-      <c r="V40" s="55"/>
-      <c r="W40" s="55"/>
-      <c r="X40" s="55"/>
-      <c r="Y40" s="55"/>
-      <c r="Z40" s="55"/>
-      <c r="AA40" s="55"/>
-      <c r="AB40" s="56"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="53"/>
+      <c r="N40" s="53"/>
+      <c r="O40" s="53"/>
+      <c r="P40" s="53"/>
+      <c r="Q40" s="53"/>
+      <c r="R40" s="53"/>
+      <c r="S40" s="53"/>
+      <c r="T40" s="53"/>
+      <c r="U40" s="53"/>
+      <c r="V40" s="53"/>
+      <c r="W40" s="53"/>
+      <c r="X40" s="53"/>
+      <c r="Y40" s="53"/>
+      <c r="Z40" s="53"/>
+      <c r="AA40" s="53"/>
+      <c r="AB40" s="54"/>
       <c r="AC40" s="16"/>
     </row>
     <row r="41" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9534,27 +9552,27 @@
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
       <c r="G42" s="19"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-      <c r="K42" s="49"/>
-      <c r="L42" s="49"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="49"/>
-      <c r="O42" s="49"/>
-      <c r="P42" s="49"/>
-      <c r="Q42" s="49"/>
-      <c r="R42" s="49"/>
-      <c r="S42" s="49"/>
-      <c r="T42" s="49"/>
-      <c r="U42" s="49"/>
-      <c r="V42" s="49"/>
-      <c r="W42" s="49"/>
-      <c r="X42" s="49"/>
-      <c r="Y42" s="49"/>
-      <c r="Z42" s="49"/>
-      <c r="AA42" s="49"/>
-      <c r="AB42" s="50"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
+      <c r="M42" s="47"/>
+      <c r="N42" s="47"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="47"/>
+      <c r="Q42" s="47"/>
+      <c r="R42" s="47"/>
+      <c r="S42" s="47"/>
+      <c r="T42" s="47"/>
+      <c r="U42" s="47"/>
+      <c r="V42" s="47"/>
+      <c r="W42" s="47"/>
+      <c r="X42" s="47"/>
+      <c r="Y42" s="47"/>
+      <c r="Z42" s="47"/>
+      <c r="AA42" s="47"/>
+      <c r="AB42" s="48"/>
       <c r="AC42" s="16"/>
     </row>
     <row r="43" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9564,27 +9582,27 @@
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="52"/>
-      <c r="L43" s="52"/>
-      <c r="M43" s="52"/>
-      <c r="N43" s="52"/>
-      <c r="O43" s="52"/>
-      <c r="P43" s="52"/>
-      <c r="Q43" s="52"/>
-      <c r="R43" s="52"/>
-      <c r="S43" s="52"/>
-      <c r="T43" s="52"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="52"/>
-      <c r="W43" s="52"/>
-      <c r="X43" s="52"/>
-      <c r="Y43" s="52"/>
-      <c r="Z43" s="52"/>
-      <c r="AA43" s="52"/>
-      <c r="AB43" s="53"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="50"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="50"/>
+      <c r="V43" s="50"/>
+      <c r="W43" s="50"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="50"/>
+      <c r="AA43" s="50"/>
+      <c r="AB43" s="51"/>
       <c r="AC43" s="16"/>
     </row>
     <row r="44" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9594,27 +9612,27 @@
       <c r="E44" s="19"/>
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="52"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="52"/>
-      <c r="O44" s="52"/>
-      <c r="P44" s="52"/>
-      <c r="Q44" s="52"/>
-      <c r="R44" s="52"/>
-      <c r="S44" s="52"/>
-      <c r="T44" s="52"/>
-      <c r="U44" s="52"/>
-      <c r="V44" s="52"/>
-      <c r="W44" s="52"/>
-      <c r="X44" s="52"/>
-      <c r="Y44" s="52"/>
-      <c r="Z44" s="52"/>
-      <c r="AA44" s="52"/>
-      <c r="AB44" s="53"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="50"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="50"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="50"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50"/>
+      <c r="S44" s="50"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="50"/>
+      <c r="W44" s="50"/>
+      <c r="X44" s="50"/>
+      <c r="Y44" s="50"/>
+      <c r="Z44" s="50"/>
+      <c r="AA44" s="50"/>
+      <c r="AB44" s="51"/>
       <c r="AC44" s="16"/>
     </row>
     <row r="45" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9624,27 +9642,27 @@
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="52"/>
-      <c r="O45" s="52"/>
-      <c r="P45" s="52"/>
-      <c r="Q45" s="52"/>
-      <c r="R45" s="52"/>
-      <c r="S45" s="52"/>
-      <c r="T45" s="52"/>
-      <c r="U45" s="52"/>
-      <c r="V45" s="52"/>
-      <c r="W45" s="52"/>
-      <c r="X45" s="52"/>
-      <c r="Y45" s="52"/>
-      <c r="Z45" s="52"/>
-      <c r="AA45" s="52"/>
-      <c r="AB45" s="53"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="L45" s="50"/>
+      <c r="M45" s="50"/>
+      <c r="N45" s="50"/>
+      <c r="O45" s="50"/>
+      <c r="P45" s="50"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50"/>
+      <c r="S45" s="50"/>
+      <c r="T45" s="50"/>
+      <c r="U45" s="50"/>
+      <c r="V45" s="50"/>
+      <c r="W45" s="50"/>
+      <c r="X45" s="50"/>
+      <c r="Y45" s="50"/>
+      <c r="Z45" s="50"/>
+      <c r="AA45" s="50"/>
+      <c r="AB45" s="51"/>
       <c r="AC45" s="16"/>
     </row>
     <row r="46" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9654,27 +9672,27 @@
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="52"/>
-      <c r="M46" s="52"/>
-      <c r="N46" s="52"/>
-      <c r="O46" s="52"/>
-      <c r="P46" s="52"/>
-      <c r="Q46" s="52"/>
-      <c r="R46" s="52"/>
-      <c r="S46" s="52"/>
-      <c r="T46" s="52"/>
-      <c r="U46" s="52"/>
-      <c r="V46" s="52"/>
-      <c r="W46" s="52"/>
-      <c r="X46" s="52"/>
-      <c r="Y46" s="52"/>
-      <c r="Z46" s="52"/>
-      <c r="AA46" s="52"/>
-      <c r="AB46" s="53"/>
+      <c r="H46" s="49"/>
+      <c r="I46" s="50"/>
+      <c r="J46" s="50"/>
+      <c r="K46" s="50"/>
+      <c r="L46" s="50"/>
+      <c r="M46" s="50"/>
+      <c r="N46" s="50"/>
+      <c r="O46" s="50"/>
+      <c r="P46" s="50"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50"/>
+      <c r="S46" s="50"/>
+      <c r="T46" s="50"/>
+      <c r="U46" s="50"/>
+      <c r="V46" s="50"/>
+      <c r="W46" s="50"/>
+      <c r="X46" s="50"/>
+      <c r="Y46" s="50"/>
+      <c r="Z46" s="50"/>
+      <c r="AA46" s="50"/>
+      <c r="AB46" s="51"/>
       <c r="AC46" s="16"/>
     </row>
     <row r="47" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9684,27 +9702,27 @@
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
       <c r="G47" s="19"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="52"/>
-      <c r="M47" s="52"/>
-      <c r="N47" s="52"/>
-      <c r="O47" s="52"/>
-      <c r="P47" s="52"/>
-      <c r="Q47" s="52"/>
-      <c r="R47" s="52"/>
-      <c r="S47" s="52"/>
-      <c r="T47" s="52"/>
-      <c r="U47" s="52"/>
-      <c r="V47" s="52"/>
-      <c r="W47" s="52"/>
-      <c r="X47" s="52"/>
-      <c r="Y47" s="52"/>
-      <c r="Z47" s="52"/>
-      <c r="AA47" s="52"/>
-      <c r="AB47" s="53"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="50"/>
+      <c r="J47" s="50"/>
+      <c r="K47" s="50"/>
+      <c r="L47" s="50"/>
+      <c r="M47" s="50"/>
+      <c r="N47" s="50"/>
+      <c r="O47" s="50"/>
+      <c r="P47" s="50"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50"/>
+      <c r="S47" s="50"/>
+      <c r="T47" s="50"/>
+      <c r="U47" s="50"/>
+      <c r="V47" s="50"/>
+      <c r="W47" s="50"/>
+      <c r="X47" s="50"/>
+      <c r="Y47" s="50"/>
+      <c r="Z47" s="50"/>
+      <c r="AA47" s="50"/>
+      <c r="AB47" s="51"/>
       <c r="AC47" s="16"/>
     </row>
     <row r="48" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9714,27 +9732,27 @@
       <c r="E48" s="19"/>
       <c r="F48" s="19"/>
       <c r="G48" s="19"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="55"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="55"/>
-      <c r="L48" s="55"/>
-      <c r="M48" s="55"/>
-      <c r="N48" s="55"/>
-      <c r="O48" s="55"/>
-      <c r="P48" s="55"/>
-      <c r="Q48" s="55"/>
-      <c r="R48" s="55"/>
-      <c r="S48" s="55"/>
-      <c r="T48" s="55"/>
-      <c r="U48" s="55"/>
-      <c r="V48" s="55"/>
-      <c r="W48" s="55"/>
-      <c r="X48" s="55"/>
-      <c r="Y48" s="55"/>
-      <c r="Z48" s="55"/>
-      <c r="AA48" s="55"/>
-      <c r="AB48" s="56"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="53"/>
+      <c r="S48" s="53"/>
+      <c r="T48" s="53"/>
+      <c r="U48" s="53"/>
+      <c r="V48" s="53"/>
+      <c r="W48" s="53"/>
+      <c r="X48" s="53"/>
+      <c r="Y48" s="53"/>
+      <c r="Z48" s="53"/>
+      <c r="AA48" s="53"/>
+      <c r="AB48" s="54"/>
       <c r="AC48" s="16"/>
     </row>
     <row r="49" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9807,11 +9825,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
@@ -10616,11 +10634,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>33</v>
       </c>
@@ -11758,11 +11776,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>34</v>
       </c>
@@ -14509,6 +14527,19 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B26:B43"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="H28:AB34"/>
+    <mergeCell ref="H36:AB42"/>
+    <mergeCell ref="B46:B63"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="H48:AB54"/>
+    <mergeCell ref="H56:AB62"/>
     <mergeCell ref="B66:B83"/>
     <mergeCell ref="D68:F68"/>
     <mergeCell ref="H68:AB74"/>
@@ -14517,19 +14548,6 @@
     <mergeCell ref="D88:F88"/>
     <mergeCell ref="H88:AB94"/>
     <mergeCell ref="H96:AB102"/>
-    <mergeCell ref="B26:B43"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="H28:AB34"/>
-    <mergeCell ref="H36:AB42"/>
-    <mergeCell ref="B46:B63"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="H48:AB54"/>
-    <mergeCell ref="H56:AB62"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -14556,11 +14574,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>41</v>
       </c>

--- a/Projekttagebuch.xlsx
+++ b/Projekttagebuch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\projects\GW.Demo.Maui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBF2A8D-30D6-4535-A3DB-09311CFBC2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B32E5BF-8CBF-4B81-BAA6-CAE5C42A590F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
   <si>
     <t>Framework:</t>
   </si>
@@ -300,6 +300,32 @@
   </si>
   <si>
     <t>MediaElement ist eher komfortabel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/image
+https://stackoverflow.com/questions/78133978/loading-images-from-a-folder-in-net-maui
+https://dev.to/serhii_korol_ab7776c50dba/working-with-files-in-net-maui-537n
+https://learn.microsoft.com/en-us/answers/questions/1024872/how-to-save-image-in-while-image-is-taken-from-cam
+https://learn.microsoft.com/en-us/dotnet/maui/platform-integration/storage/file-system-helpers
+</t>
+  </si>
+  <si>
+    <t>VM bereits vorbereitet für Erweiterung. Anzeige umgesetzt.</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://learn.microsoft.com/en-us/answers/questions/1024872/how-to-save-image-in-while-image-is-taken-from-cam
+https://learn.microsoft.com/en-us/dotnet/maui/platform-integration/device-media/picker
+https://learn.microsoft.com/en-us/dotnet/communitytoolkit/maui/views/camera-view
+</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>Konfiguration war tricky.</t>
   </si>
 </sst>
 </file>
@@ -631,6 +657,12 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -657,12 +689,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2196,11 +2222,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>11</v>
       </c>
@@ -6254,33 +6280,37 @@
     <row r="144" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B144" s="44"/>
       <c r="C144" s="5"/>
-      <c r="D144" s="41"/>
+      <c r="D144" s="41" t="s">
+        <v>73</v>
+      </c>
       <c r="E144" s="42"/>
       <c r="F144" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G144" s="6"/>
-      <c r="H144" s="46"/>
-      <c r="I144" s="47"/>
-      <c r="J144" s="47"/>
-      <c r="K144" s="47"/>
-      <c r="L144" s="47"/>
-      <c r="M144" s="47"/>
-      <c r="N144" s="47"/>
-      <c r="O144" s="47"/>
-      <c r="P144" s="47"/>
-      <c r="Q144" s="47"/>
-      <c r="R144" s="47"/>
-      <c r="S144" s="47"/>
-      <c r="T144" s="47"/>
-      <c r="U144" s="47"/>
-      <c r="V144" s="47"/>
-      <c r="W144" s="47"/>
-      <c r="X144" s="47"/>
-      <c r="Y144" s="47"/>
-      <c r="Z144" s="47"/>
-      <c r="AA144" s="47"/>
-      <c r="AB144" s="48"/>
+      <c r="H144" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="I144" s="33"/>
+      <c r="J144" s="33"/>
+      <c r="K144" s="33"/>
+      <c r="L144" s="33"/>
+      <c r="M144" s="33"/>
+      <c r="N144" s="33"/>
+      <c r="O144" s="33"/>
+      <c r="P144" s="33"/>
+      <c r="Q144" s="33"/>
+      <c r="R144" s="33"/>
+      <c r="S144" s="33"/>
+      <c r="T144" s="33"/>
+      <c r="U144" s="33"/>
+      <c r="V144" s="33"/>
+      <c r="W144" s="33"/>
+      <c r="X144" s="33"/>
+      <c r="Y144" s="33"/>
+      <c r="Z144" s="33"/>
+      <c r="AA144" s="33"/>
+      <c r="AB144" s="34"/>
       <c r="AC144" s="11"/>
     </row>
     <row r="145" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6290,27 +6320,27 @@
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
-      <c r="H145" s="49"/>
-      <c r="I145" s="50"/>
-      <c r="J145" s="50"/>
-      <c r="K145" s="50"/>
-      <c r="L145" s="50"/>
-      <c r="M145" s="50"/>
-      <c r="N145" s="50"/>
-      <c r="O145" s="50"/>
-      <c r="P145" s="50"/>
-      <c r="Q145" s="50"/>
-      <c r="R145" s="50"/>
-      <c r="S145" s="50"/>
-      <c r="T145" s="50"/>
-      <c r="U145" s="50"/>
-      <c r="V145" s="50"/>
-      <c r="W145" s="50"/>
-      <c r="X145" s="50"/>
-      <c r="Y145" s="50"/>
-      <c r="Z145" s="50"/>
-      <c r="AA145" s="50"/>
-      <c r="AB145" s="51"/>
+      <c r="H145" s="35"/>
+      <c r="I145" s="36"/>
+      <c r="J145" s="36"/>
+      <c r="K145" s="36"/>
+      <c r="L145" s="36"/>
+      <c r="M145" s="36"/>
+      <c r="N145" s="36"/>
+      <c r="O145" s="36"/>
+      <c r="P145" s="36"/>
+      <c r="Q145" s="36"/>
+      <c r="R145" s="36"/>
+      <c r="S145" s="36"/>
+      <c r="T145" s="36"/>
+      <c r="U145" s="36"/>
+      <c r="V145" s="36"/>
+      <c r="W145" s="36"/>
+      <c r="X145" s="36"/>
+      <c r="Y145" s="36"/>
+      <c r="Z145" s="36"/>
+      <c r="AA145" s="36"/>
+      <c r="AB145" s="37"/>
       <c r="AC145" s="11"/>
     </row>
     <row r="146" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6320,27 +6350,27 @@
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
-      <c r="H146" s="49"/>
-      <c r="I146" s="50"/>
-      <c r="J146" s="50"/>
-      <c r="K146" s="50"/>
-      <c r="L146" s="50"/>
-      <c r="M146" s="50"/>
-      <c r="N146" s="50"/>
-      <c r="O146" s="50"/>
-      <c r="P146" s="50"/>
-      <c r="Q146" s="50"/>
-      <c r="R146" s="50"/>
-      <c r="S146" s="50"/>
-      <c r="T146" s="50"/>
-      <c r="U146" s="50"/>
-      <c r="V146" s="50"/>
-      <c r="W146" s="50"/>
-      <c r="X146" s="50"/>
-      <c r="Y146" s="50"/>
-      <c r="Z146" s="50"/>
-      <c r="AA146" s="50"/>
-      <c r="AB146" s="51"/>
+      <c r="H146" s="35"/>
+      <c r="I146" s="36"/>
+      <c r="J146" s="36"/>
+      <c r="K146" s="36"/>
+      <c r="L146" s="36"/>
+      <c r="M146" s="36"/>
+      <c r="N146" s="36"/>
+      <c r="O146" s="36"/>
+      <c r="P146" s="36"/>
+      <c r="Q146" s="36"/>
+      <c r="R146" s="36"/>
+      <c r="S146" s="36"/>
+      <c r="T146" s="36"/>
+      <c r="U146" s="36"/>
+      <c r="V146" s="36"/>
+      <c r="W146" s="36"/>
+      <c r="X146" s="36"/>
+      <c r="Y146" s="36"/>
+      <c r="Z146" s="36"/>
+      <c r="AA146" s="36"/>
+      <c r="AB146" s="37"/>
       <c r="AC146" s="11"/>
     </row>
     <row r="147" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6350,27 +6380,27 @@
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
-      <c r="H147" s="49"/>
-      <c r="I147" s="50"/>
-      <c r="J147" s="50"/>
-      <c r="K147" s="50"/>
-      <c r="L147" s="50"/>
-      <c r="M147" s="50"/>
-      <c r="N147" s="50"/>
-      <c r="O147" s="50"/>
-      <c r="P147" s="50"/>
-      <c r="Q147" s="50"/>
-      <c r="R147" s="50"/>
-      <c r="S147" s="50"/>
-      <c r="T147" s="50"/>
-      <c r="U147" s="50"/>
-      <c r="V147" s="50"/>
-      <c r="W147" s="50"/>
-      <c r="X147" s="50"/>
-      <c r="Y147" s="50"/>
-      <c r="Z147" s="50"/>
-      <c r="AA147" s="50"/>
-      <c r="AB147" s="51"/>
+      <c r="H147" s="35"/>
+      <c r="I147" s="36"/>
+      <c r="J147" s="36"/>
+      <c r="K147" s="36"/>
+      <c r="L147" s="36"/>
+      <c r="M147" s="36"/>
+      <c r="N147" s="36"/>
+      <c r="O147" s="36"/>
+      <c r="P147" s="36"/>
+      <c r="Q147" s="36"/>
+      <c r="R147" s="36"/>
+      <c r="S147" s="36"/>
+      <c r="T147" s="36"/>
+      <c r="U147" s="36"/>
+      <c r="V147" s="36"/>
+      <c r="W147" s="36"/>
+      <c r="X147" s="36"/>
+      <c r="Y147" s="36"/>
+      <c r="Z147" s="36"/>
+      <c r="AA147" s="36"/>
+      <c r="AB147" s="37"/>
       <c r="AC147" s="11"/>
     </row>
     <row r="148" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6380,27 +6410,27 @@
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
-      <c r="H148" s="49"/>
-      <c r="I148" s="50"/>
-      <c r="J148" s="50"/>
-      <c r="K148" s="50"/>
-      <c r="L148" s="50"/>
-      <c r="M148" s="50"/>
-      <c r="N148" s="50"/>
-      <c r="O148" s="50"/>
-      <c r="P148" s="50"/>
-      <c r="Q148" s="50"/>
-      <c r="R148" s="50"/>
-      <c r="S148" s="50"/>
-      <c r="T148" s="50"/>
-      <c r="U148" s="50"/>
-      <c r="V148" s="50"/>
-      <c r="W148" s="50"/>
-      <c r="X148" s="50"/>
-      <c r="Y148" s="50"/>
-      <c r="Z148" s="50"/>
-      <c r="AA148" s="50"/>
-      <c r="AB148" s="51"/>
+      <c r="H148" s="35"/>
+      <c r="I148" s="36"/>
+      <c r="J148" s="36"/>
+      <c r="K148" s="36"/>
+      <c r="L148" s="36"/>
+      <c r="M148" s="36"/>
+      <c r="N148" s="36"/>
+      <c r="O148" s="36"/>
+      <c r="P148" s="36"/>
+      <c r="Q148" s="36"/>
+      <c r="R148" s="36"/>
+      <c r="S148" s="36"/>
+      <c r="T148" s="36"/>
+      <c r="U148" s="36"/>
+      <c r="V148" s="36"/>
+      <c r="W148" s="36"/>
+      <c r="X148" s="36"/>
+      <c r="Y148" s="36"/>
+      <c r="Z148" s="36"/>
+      <c r="AA148" s="36"/>
+      <c r="AB148" s="37"/>
       <c r="AC148" s="11"/>
     </row>
     <row r="149" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6410,27 +6440,27 @@
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
-      <c r="H149" s="49"/>
-      <c r="I149" s="50"/>
-      <c r="J149" s="50"/>
-      <c r="K149" s="50"/>
-      <c r="L149" s="50"/>
-      <c r="M149" s="50"/>
-      <c r="N149" s="50"/>
-      <c r="O149" s="50"/>
-      <c r="P149" s="50"/>
-      <c r="Q149" s="50"/>
-      <c r="R149" s="50"/>
-      <c r="S149" s="50"/>
-      <c r="T149" s="50"/>
-      <c r="U149" s="50"/>
-      <c r="V149" s="50"/>
-      <c r="W149" s="50"/>
-      <c r="X149" s="50"/>
-      <c r="Y149" s="50"/>
-      <c r="Z149" s="50"/>
-      <c r="AA149" s="50"/>
-      <c r="AB149" s="51"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="36"/>
+      <c r="J149" s="36"/>
+      <c r="K149" s="36"/>
+      <c r="L149" s="36"/>
+      <c r="M149" s="36"/>
+      <c r="N149" s="36"/>
+      <c r="O149" s="36"/>
+      <c r="P149" s="36"/>
+      <c r="Q149" s="36"/>
+      <c r="R149" s="36"/>
+      <c r="S149" s="36"/>
+      <c r="T149" s="36"/>
+      <c r="U149" s="36"/>
+      <c r="V149" s="36"/>
+      <c r="W149" s="36"/>
+      <c r="X149" s="36"/>
+      <c r="Y149" s="36"/>
+      <c r="Z149" s="36"/>
+      <c r="AA149" s="36"/>
+      <c r="AB149" s="37"/>
       <c r="AC149" s="11"/>
     </row>
     <row r="150" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6440,27 +6470,27 @@
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
-      <c r="H150" s="52"/>
-      <c r="I150" s="53"/>
-      <c r="J150" s="53"/>
-      <c r="K150" s="53"/>
-      <c r="L150" s="53"/>
-      <c r="M150" s="53"/>
-      <c r="N150" s="53"/>
-      <c r="O150" s="53"/>
-      <c r="P150" s="53"/>
-      <c r="Q150" s="53"/>
-      <c r="R150" s="53"/>
-      <c r="S150" s="53"/>
-      <c r="T150" s="53"/>
-      <c r="U150" s="53"/>
-      <c r="V150" s="53"/>
-      <c r="W150" s="53"/>
-      <c r="X150" s="53"/>
-      <c r="Y150" s="53"/>
-      <c r="Z150" s="53"/>
-      <c r="AA150" s="53"/>
-      <c r="AB150" s="54"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="39"/>
+      <c r="J150" s="39"/>
+      <c r="K150" s="39"/>
+      <c r="L150" s="39"/>
+      <c r="M150" s="39"/>
+      <c r="N150" s="39"/>
+      <c r="O150" s="39"/>
+      <c r="P150" s="39"/>
+      <c r="Q150" s="39"/>
+      <c r="R150" s="39"/>
+      <c r="S150" s="39"/>
+      <c r="T150" s="39"/>
+      <c r="U150" s="39"/>
+      <c r="V150" s="39"/>
+      <c r="W150" s="39"/>
+      <c r="X150" s="39"/>
+      <c r="Y150" s="39"/>
+      <c r="Z150" s="39"/>
+      <c r="AA150" s="39"/>
+      <c r="AB150" s="40"/>
       <c r="AC150" s="11"/>
     </row>
     <row r="151" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6502,27 +6532,29 @@
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
-      <c r="H152" s="46"/>
-      <c r="I152" s="47"/>
-      <c r="J152" s="47"/>
-      <c r="K152" s="47"/>
-      <c r="L152" s="47"/>
-      <c r="M152" s="47"/>
-      <c r="N152" s="47"/>
-      <c r="O152" s="47"/>
-      <c r="P152" s="47"/>
-      <c r="Q152" s="47"/>
-      <c r="R152" s="47"/>
-      <c r="S152" s="47"/>
-      <c r="T152" s="47"/>
-      <c r="U152" s="47"/>
-      <c r="V152" s="47"/>
-      <c r="W152" s="47"/>
-      <c r="X152" s="47"/>
-      <c r="Y152" s="47"/>
-      <c r="Z152" s="47"/>
-      <c r="AA152" s="47"/>
-      <c r="AB152" s="48"/>
+      <c r="H152" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="I152" s="33"/>
+      <c r="J152" s="33"/>
+      <c r="K152" s="33"/>
+      <c r="L152" s="33"/>
+      <c r="M152" s="33"/>
+      <c r="N152" s="33"/>
+      <c r="O152" s="33"/>
+      <c r="P152" s="33"/>
+      <c r="Q152" s="33"/>
+      <c r="R152" s="33"/>
+      <c r="S152" s="33"/>
+      <c r="T152" s="33"/>
+      <c r="U152" s="33"/>
+      <c r="V152" s="33"/>
+      <c r="W152" s="33"/>
+      <c r="X152" s="33"/>
+      <c r="Y152" s="33"/>
+      <c r="Z152" s="33"/>
+      <c r="AA152" s="33"/>
+      <c r="AB152" s="34"/>
       <c r="AC152" s="11"/>
     </row>
     <row r="153" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6532,27 +6564,27 @@
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
-      <c r="H153" s="49"/>
-      <c r="I153" s="50"/>
-      <c r="J153" s="50"/>
-      <c r="K153" s="50"/>
-      <c r="L153" s="50"/>
-      <c r="M153" s="50"/>
-      <c r="N153" s="50"/>
-      <c r="O153" s="50"/>
-      <c r="P153" s="50"/>
-      <c r="Q153" s="50"/>
-      <c r="R153" s="50"/>
-      <c r="S153" s="50"/>
-      <c r="T153" s="50"/>
-      <c r="U153" s="50"/>
-      <c r="V153" s="50"/>
-      <c r="W153" s="50"/>
-      <c r="X153" s="50"/>
-      <c r="Y153" s="50"/>
-      <c r="Z153" s="50"/>
-      <c r="AA153" s="50"/>
-      <c r="AB153" s="51"/>
+      <c r="H153" s="35"/>
+      <c r="I153" s="36"/>
+      <c r="J153" s="36"/>
+      <c r="K153" s="36"/>
+      <c r="L153" s="36"/>
+      <c r="M153" s="36"/>
+      <c r="N153" s="36"/>
+      <c r="O153" s="36"/>
+      <c r="P153" s="36"/>
+      <c r="Q153" s="36"/>
+      <c r="R153" s="36"/>
+      <c r="S153" s="36"/>
+      <c r="T153" s="36"/>
+      <c r="U153" s="36"/>
+      <c r="V153" s="36"/>
+      <c r="W153" s="36"/>
+      <c r="X153" s="36"/>
+      <c r="Y153" s="36"/>
+      <c r="Z153" s="36"/>
+      <c r="AA153" s="36"/>
+      <c r="AB153" s="37"/>
       <c r="AC153" s="11"/>
     </row>
     <row r="154" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6562,27 +6594,27 @@
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
-      <c r="H154" s="49"/>
-      <c r="I154" s="50"/>
-      <c r="J154" s="50"/>
-      <c r="K154" s="50"/>
-      <c r="L154" s="50"/>
-      <c r="M154" s="50"/>
-      <c r="N154" s="50"/>
-      <c r="O154" s="50"/>
-      <c r="P154" s="50"/>
-      <c r="Q154" s="50"/>
-      <c r="R154" s="50"/>
-      <c r="S154" s="50"/>
-      <c r="T154" s="50"/>
-      <c r="U154" s="50"/>
-      <c r="V154" s="50"/>
-      <c r="W154" s="50"/>
-      <c r="X154" s="50"/>
-      <c r="Y154" s="50"/>
-      <c r="Z154" s="50"/>
-      <c r="AA154" s="50"/>
-      <c r="AB154" s="51"/>
+      <c r="H154" s="35"/>
+      <c r="I154" s="36"/>
+      <c r="J154" s="36"/>
+      <c r="K154" s="36"/>
+      <c r="L154" s="36"/>
+      <c r="M154" s="36"/>
+      <c r="N154" s="36"/>
+      <c r="O154" s="36"/>
+      <c r="P154" s="36"/>
+      <c r="Q154" s="36"/>
+      <c r="R154" s="36"/>
+      <c r="S154" s="36"/>
+      <c r="T154" s="36"/>
+      <c r="U154" s="36"/>
+      <c r="V154" s="36"/>
+      <c r="W154" s="36"/>
+      <c r="X154" s="36"/>
+      <c r="Y154" s="36"/>
+      <c r="Z154" s="36"/>
+      <c r="AA154" s="36"/>
+      <c r="AB154" s="37"/>
       <c r="AC154" s="11"/>
     </row>
     <row r="155" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6592,27 +6624,27 @@
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
-      <c r="H155" s="49"/>
-      <c r="I155" s="50"/>
-      <c r="J155" s="50"/>
-      <c r="K155" s="50"/>
-      <c r="L155" s="50"/>
-      <c r="M155" s="50"/>
-      <c r="N155" s="50"/>
-      <c r="O155" s="50"/>
-      <c r="P155" s="50"/>
-      <c r="Q155" s="50"/>
-      <c r="R155" s="50"/>
-      <c r="S155" s="50"/>
-      <c r="T155" s="50"/>
-      <c r="U155" s="50"/>
-      <c r="V155" s="50"/>
-      <c r="W155" s="50"/>
-      <c r="X155" s="50"/>
-      <c r="Y155" s="50"/>
-      <c r="Z155" s="50"/>
-      <c r="AA155" s="50"/>
-      <c r="AB155" s="51"/>
+      <c r="H155" s="35"/>
+      <c r="I155" s="36"/>
+      <c r="J155" s="36"/>
+      <c r="K155" s="36"/>
+      <c r="L155" s="36"/>
+      <c r="M155" s="36"/>
+      <c r="N155" s="36"/>
+      <c r="O155" s="36"/>
+      <c r="P155" s="36"/>
+      <c r="Q155" s="36"/>
+      <c r="R155" s="36"/>
+      <c r="S155" s="36"/>
+      <c r="T155" s="36"/>
+      <c r="U155" s="36"/>
+      <c r="V155" s="36"/>
+      <c r="W155" s="36"/>
+      <c r="X155" s="36"/>
+      <c r="Y155" s="36"/>
+      <c r="Z155" s="36"/>
+      <c r="AA155" s="36"/>
+      <c r="AB155" s="37"/>
       <c r="AC155" s="11"/>
     </row>
     <row r="156" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6622,27 +6654,27 @@
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
-      <c r="H156" s="49"/>
-      <c r="I156" s="50"/>
-      <c r="J156" s="50"/>
-      <c r="K156" s="50"/>
-      <c r="L156" s="50"/>
-      <c r="M156" s="50"/>
-      <c r="N156" s="50"/>
-      <c r="O156" s="50"/>
-      <c r="P156" s="50"/>
-      <c r="Q156" s="50"/>
-      <c r="R156" s="50"/>
-      <c r="S156" s="50"/>
-      <c r="T156" s="50"/>
-      <c r="U156" s="50"/>
-      <c r="V156" s="50"/>
-      <c r="W156" s="50"/>
-      <c r="X156" s="50"/>
-      <c r="Y156" s="50"/>
-      <c r="Z156" s="50"/>
-      <c r="AA156" s="50"/>
-      <c r="AB156" s="51"/>
+      <c r="H156" s="35"/>
+      <c r="I156" s="36"/>
+      <c r="J156" s="36"/>
+      <c r="K156" s="36"/>
+      <c r="L156" s="36"/>
+      <c r="M156" s="36"/>
+      <c r="N156" s="36"/>
+      <c r="O156" s="36"/>
+      <c r="P156" s="36"/>
+      <c r="Q156" s="36"/>
+      <c r="R156" s="36"/>
+      <c r="S156" s="36"/>
+      <c r="T156" s="36"/>
+      <c r="U156" s="36"/>
+      <c r="V156" s="36"/>
+      <c r="W156" s="36"/>
+      <c r="X156" s="36"/>
+      <c r="Y156" s="36"/>
+      <c r="Z156" s="36"/>
+      <c r="AA156" s="36"/>
+      <c r="AB156" s="37"/>
       <c r="AC156" s="11"/>
     </row>
     <row r="157" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6652,27 +6684,27 @@
       <c r="E157" s="6"/>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
-      <c r="H157" s="49"/>
-      <c r="I157" s="50"/>
-      <c r="J157" s="50"/>
-      <c r="K157" s="50"/>
-      <c r="L157" s="50"/>
-      <c r="M157" s="50"/>
-      <c r="N157" s="50"/>
-      <c r="O157" s="50"/>
-      <c r="P157" s="50"/>
-      <c r="Q157" s="50"/>
-      <c r="R157" s="50"/>
-      <c r="S157" s="50"/>
-      <c r="T157" s="50"/>
-      <c r="U157" s="50"/>
-      <c r="V157" s="50"/>
-      <c r="W157" s="50"/>
-      <c r="X157" s="50"/>
-      <c r="Y157" s="50"/>
-      <c r="Z157" s="50"/>
-      <c r="AA157" s="50"/>
-      <c r="AB157" s="51"/>
+      <c r="H157" s="35"/>
+      <c r="I157" s="36"/>
+      <c r="J157" s="36"/>
+      <c r="K157" s="36"/>
+      <c r="L157" s="36"/>
+      <c r="M157" s="36"/>
+      <c r="N157" s="36"/>
+      <c r="O157" s="36"/>
+      <c r="P157" s="36"/>
+      <c r="Q157" s="36"/>
+      <c r="R157" s="36"/>
+      <c r="S157" s="36"/>
+      <c r="T157" s="36"/>
+      <c r="U157" s="36"/>
+      <c r="V157" s="36"/>
+      <c r="W157" s="36"/>
+      <c r="X157" s="36"/>
+      <c r="Y157" s="36"/>
+      <c r="Z157" s="36"/>
+      <c r="AA157" s="36"/>
+      <c r="AB157" s="37"/>
       <c r="AC157" s="11"/>
     </row>
     <row r="158" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6682,27 +6714,27 @@
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
-      <c r="H158" s="52"/>
-      <c r="I158" s="53"/>
-      <c r="J158" s="53"/>
-      <c r="K158" s="53"/>
-      <c r="L158" s="53"/>
-      <c r="M158" s="53"/>
-      <c r="N158" s="53"/>
-      <c r="O158" s="53"/>
-      <c r="P158" s="53"/>
-      <c r="Q158" s="53"/>
-      <c r="R158" s="53"/>
-      <c r="S158" s="53"/>
-      <c r="T158" s="53"/>
-      <c r="U158" s="53"/>
-      <c r="V158" s="53"/>
-      <c r="W158" s="53"/>
-      <c r="X158" s="53"/>
-      <c r="Y158" s="53"/>
-      <c r="Z158" s="53"/>
-      <c r="AA158" s="53"/>
-      <c r="AB158" s="54"/>
+      <c r="H158" s="38"/>
+      <c r="I158" s="39"/>
+      <c r="J158" s="39"/>
+      <c r="K158" s="39"/>
+      <c r="L158" s="39"/>
+      <c r="M158" s="39"/>
+      <c r="N158" s="39"/>
+      <c r="O158" s="39"/>
+      <c r="P158" s="39"/>
+      <c r="Q158" s="39"/>
+      <c r="R158" s="39"/>
+      <c r="S158" s="39"/>
+      <c r="T158" s="39"/>
+      <c r="U158" s="39"/>
+      <c r="V158" s="39"/>
+      <c r="W158" s="39"/>
+      <c r="X158" s="39"/>
+      <c r="Y158" s="39"/>
+      <c r="Z158" s="39"/>
+      <c r="AA158" s="39"/>
+      <c r="AB158" s="40"/>
       <c r="AC158" s="11"/>
     </row>
     <row r="159" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6804,33 +6836,37 @@
     <row r="163" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B163" s="44"/>
       <c r="C163" s="5"/>
-      <c r="D163" s="41"/>
+      <c r="D163" s="41" t="s">
+        <v>75</v>
+      </c>
       <c r="E163" s="42"/>
       <c r="F163" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G163" s="6"/>
-      <c r="H163" s="46"/>
-      <c r="I163" s="47"/>
-      <c r="J163" s="47"/>
-      <c r="K163" s="47"/>
-      <c r="L163" s="47"/>
-      <c r="M163" s="47"/>
-      <c r="N163" s="47"/>
-      <c r="O163" s="47"/>
-      <c r="P163" s="47"/>
-      <c r="Q163" s="47"/>
-      <c r="R163" s="47"/>
-      <c r="S163" s="47"/>
-      <c r="T163" s="47"/>
-      <c r="U163" s="47"/>
-      <c r="V163" s="47"/>
-      <c r="W163" s="47"/>
-      <c r="X163" s="47"/>
-      <c r="Y163" s="47"/>
-      <c r="Z163" s="47"/>
-      <c r="AA163" s="47"/>
-      <c r="AB163" s="48"/>
+      <c r="H163" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="I163" s="33"/>
+      <c r="J163" s="33"/>
+      <c r="K163" s="33"/>
+      <c r="L163" s="33"/>
+      <c r="M163" s="33"/>
+      <c r="N163" s="33"/>
+      <c r="O163" s="33"/>
+      <c r="P163" s="33"/>
+      <c r="Q163" s="33"/>
+      <c r="R163" s="33"/>
+      <c r="S163" s="33"/>
+      <c r="T163" s="33"/>
+      <c r="U163" s="33"/>
+      <c r="V163" s="33"/>
+      <c r="W163" s="33"/>
+      <c r="X163" s="33"/>
+      <c r="Y163" s="33"/>
+      <c r="Z163" s="33"/>
+      <c r="AA163" s="33"/>
+      <c r="AB163" s="34"/>
       <c r="AC163" s="11"/>
     </row>
     <row r="164" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6840,27 +6876,27 @@
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
-      <c r="H164" s="49"/>
-      <c r="I164" s="50"/>
-      <c r="J164" s="50"/>
-      <c r="K164" s="50"/>
-      <c r="L164" s="50"/>
-      <c r="M164" s="50"/>
-      <c r="N164" s="50"/>
-      <c r="O164" s="50"/>
-      <c r="P164" s="50"/>
-      <c r="Q164" s="50"/>
-      <c r="R164" s="50"/>
-      <c r="S164" s="50"/>
-      <c r="T164" s="50"/>
-      <c r="U164" s="50"/>
-      <c r="V164" s="50"/>
-      <c r="W164" s="50"/>
-      <c r="X164" s="50"/>
-      <c r="Y164" s="50"/>
-      <c r="Z164" s="50"/>
-      <c r="AA164" s="50"/>
-      <c r="AB164" s="51"/>
+      <c r="H164" s="35"/>
+      <c r="I164" s="36"/>
+      <c r="J164" s="36"/>
+      <c r="K164" s="36"/>
+      <c r="L164" s="36"/>
+      <c r="M164" s="36"/>
+      <c r="N164" s="36"/>
+      <c r="O164" s="36"/>
+      <c r="P164" s="36"/>
+      <c r="Q164" s="36"/>
+      <c r="R164" s="36"/>
+      <c r="S164" s="36"/>
+      <c r="T164" s="36"/>
+      <c r="U164" s="36"/>
+      <c r="V164" s="36"/>
+      <c r="W164" s="36"/>
+      <c r="X164" s="36"/>
+      <c r="Y164" s="36"/>
+      <c r="Z164" s="36"/>
+      <c r="AA164" s="36"/>
+      <c r="AB164" s="37"/>
       <c r="AC164" s="11"/>
     </row>
     <row r="165" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6870,27 +6906,27 @@
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
-      <c r="H165" s="49"/>
-      <c r="I165" s="50"/>
-      <c r="J165" s="50"/>
-      <c r="K165" s="50"/>
-      <c r="L165" s="50"/>
-      <c r="M165" s="50"/>
-      <c r="N165" s="50"/>
-      <c r="O165" s="50"/>
-      <c r="P165" s="50"/>
-      <c r="Q165" s="50"/>
-      <c r="R165" s="50"/>
-      <c r="S165" s="50"/>
-      <c r="T165" s="50"/>
-      <c r="U165" s="50"/>
-      <c r="V165" s="50"/>
-      <c r="W165" s="50"/>
-      <c r="X165" s="50"/>
-      <c r="Y165" s="50"/>
-      <c r="Z165" s="50"/>
-      <c r="AA165" s="50"/>
-      <c r="AB165" s="51"/>
+      <c r="H165" s="35"/>
+      <c r="I165" s="36"/>
+      <c r="J165" s="36"/>
+      <c r="K165" s="36"/>
+      <c r="L165" s="36"/>
+      <c r="M165" s="36"/>
+      <c r="N165" s="36"/>
+      <c r="O165" s="36"/>
+      <c r="P165" s="36"/>
+      <c r="Q165" s="36"/>
+      <c r="R165" s="36"/>
+      <c r="S165" s="36"/>
+      <c r="T165" s="36"/>
+      <c r="U165" s="36"/>
+      <c r="V165" s="36"/>
+      <c r="W165" s="36"/>
+      <c r="X165" s="36"/>
+      <c r="Y165" s="36"/>
+      <c r="Z165" s="36"/>
+      <c r="AA165" s="36"/>
+      <c r="AB165" s="37"/>
       <c r="AC165" s="11"/>
     </row>
     <row r="166" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6900,27 +6936,27 @@
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
-      <c r="H166" s="49"/>
-      <c r="I166" s="50"/>
-      <c r="J166" s="50"/>
-      <c r="K166" s="50"/>
-      <c r="L166" s="50"/>
-      <c r="M166" s="50"/>
-      <c r="N166" s="50"/>
-      <c r="O166" s="50"/>
-      <c r="P166" s="50"/>
-      <c r="Q166" s="50"/>
-      <c r="R166" s="50"/>
-      <c r="S166" s="50"/>
-      <c r="T166" s="50"/>
-      <c r="U166" s="50"/>
-      <c r="V166" s="50"/>
-      <c r="W166" s="50"/>
-      <c r="X166" s="50"/>
-      <c r="Y166" s="50"/>
-      <c r="Z166" s="50"/>
-      <c r="AA166" s="50"/>
-      <c r="AB166" s="51"/>
+      <c r="H166" s="35"/>
+      <c r="I166" s="36"/>
+      <c r="J166" s="36"/>
+      <c r="K166" s="36"/>
+      <c r="L166" s="36"/>
+      <c r="M166" s="36"/>
+      <c r="N166" s="36"/>
+      <c r="O166" s="36"/>
+      <c r="P166" s="36"/>
+      <c r="Q166" s="36"/>
+      <c r="R166" s="36"/>
+      <c r="S166" s="36"/>
+      <c r="T166" s="36"/>
+      <c r="U166" s="36"/>
+      <c r="V166" s="36"/>
+      <c r="W166" s="36"/>
+      <c r="X166" s="36"/>
+      <c r="Y166" s="36"/>
+      <c r="Z166" s="36"/>
+      <c r="AA166" s="36"/>
+      <c r="AB166" s="37"/>
       <c r="AC166" s="11"/>
     </row>
     <row r="167" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6930,27 +6966,27 @@
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
-      <c r="H167" s="49"/>
-      <c r="I167" s="50"/>
-      <c r="J167" s="50"/>
-      <c r="K167" s="50"/>
-      <c r="L167" s="50"/>
-      <c r="M167" s="50"/>
-      <c r="N167" s="50"/>
-      <c r="O167" s="50"/>
-      <c r="P167" s="50"/>
-      <c r="Q167" s="50"/>
-      <c r="R167" s="50"/>
-      <c r="S167" s="50"/>
-      <c r="T167" s="50"/>
-      <c r="U167" s="50"/>
-      <c r="V167" s="50"/>
-      <c r="W167" s="50"/>
-      <c r="X167" s="50"/>
-      <c r="Y167" s="50"/>
-      <c r="Z167" s="50"/>
-      <c r="AA167" s="50"/>
-      <c r="AB167" s="51"/>
+      <c r="H167" s="35"/>
+      <c r="I167" s="36"/>
+      <c r="J167" s="36"/>
+      <c r="K167" s="36"/>
+      <c r="L167" s="36"/>
+      <c r="M167" s="36"/>
+      <c r="N167" s="36"/>
+      <c r="O167" s="36"/>
+      <c r="P167" s="36"/>
+      <c r="Q167" s="36"/>
+      <c r="R167" s="36"/>
+      <c r="S167" s="36"/>
+      <c r="T167" s="36"/>
+      <c r="U167" s="36"/>
+      <c r="V167" s="36"/>
+      <c r="W167" s="36"/>
+      <c r="X167" s="36"/>
+      <c r="Y167" s="36"/>
+      <c r="Z167" s="36"/>
+      <c r="AA167" s="36"/>
+      <c r="AB167" s="37"/>
       <c r="AC167" s="11"/>
     </row>
     <row r="168" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6960,27 +6996,27 @@
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
-      <c r="H168" s="49"/>
-      <c r="I168" s="50"/>
-      <c r="J168" s="50"/>
-      <c r="K168" s="50"/>
-      <c r="L168" s="50"/>
-      <c r="M168" s="50"/>
-      <c r="N168" s="50"/>
-      <c r="O168" s="50"/>
-      <c r="P168" s="50"/>
-      <c r="Q168" s="50"/>
-      <c r="R168" s="50"/>
-      <c r="S168" s="50"/>
-      <c r="T168" s="50"/>
-      <c r="U168" s="50"/>
-      <c r="V168" s="50"/>
-      <c r="W168" s="50"/>
-      <c r="X168" s="50"/>
-      <c r="Y168" s="50"/>
-      <c r="Z168" s="50"/>
-      <c r="AA168" s="50"/>
-      <c r="AB168" s="51"/>
+      <c r="H168" s="35"/>
+      <c r="I168" s="36"/>
+      <c r="J168" s="36"/>
+      <c r="K168" s="36"/>
+      <c r="L168" s="36"/>
+      <c r="M168" s="36"/>
+      <c r="N168" s="36"/>
+      <c r="O168" s="36"/>
+      <c r="P168" s="36"/>
+      <c r="Q168" s="36"/>
+      <c r="R168" s="36"/>
+      <c r="S168" s="36"/>
+      <c r="T168" s="36"/>
+      <c r="U168" s="36"/>
+      <c r="V168" s="36"/>
+      <c r="W168" s="36"/>
+      <c r="X168" s="36"/>
+      <c r="Y168" s="36"/>
+      <c r="Z168" s="36"/>
+      <c r="AA168" s="36"/>
+      <c r="AB168" s="37"/>
       <c r="AC168" s="11"/>
     </row>
     <row r="169" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6990,27 +7026,27 @@
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
-      <c r="H169" s="52"/>
-      <c r="I169" s="53"/>
-      <c r="J169" s="53"/>
-      <c r="K169" s="53"/>
-      <c r="L169" s="53"/>
-      <c r="M169" s="53"/>
-      <c r="N169" s="53"/>
-      <c r="O169" s="53"/>
-      <c r="P169" s="53"/>
-      <c r="Q169" s="53"/>
-      <c r="R169" s="53"/>
-      <c r="S169" s="53"/>
-      <c r="T169" s="53"/>
-      <c r="U169" s="53"/>
-      <c r="V169" s="53"/>
-      <c r="W169" s="53"/>
-      <c r="X169" s="53"/>
-      <c r="Y169" s="53"/>
-      <c r="Z169" s="53"/>
-      <c r="AA169" s="53"/>
-      <c r="AB169" s="54"/>
+      <c r="H169" s="38"/>
+      <c r="I169" s="39"/>
+      <c r="J169" s="39"/>
+      <c r="K169" s="39"/>
+      <c r="L169" s="39"/>
+      <c r="M169" s="39"/>
+      <c r="N169" s="39"/>
+      <c r="O169" s="39"/>
+      <c r="P169" s="39"/>
+      <c r="Q169" s="39"/>
+      <c r="R169" s="39"/>
+      <c r="S169" s="39"/>
+      <c r="T169" s="39"/>
+      <c r="U169" s="39"/>
+      <c r="V169" s="39"/>
+      <c r="W169" s="39"/>
+      <c r="X169" s="39"/>
+      <c r="Y169" s="39"/>
+      <c r="Z169" s="39"/>
+      <c r="AA169" s="39"/>
+      <c r="AB169" s="40"/>
       <c r="AC169" s="11"/>
     </row>
     <row r="170" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7052,27 +7088,29 @@
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
-      <c r="H171" s="46"/>
-      <c r="I171" s="47"/>
-      <c r="J171" s="47"/>
-      <c r="K171" s="47"/>
-      <c r="L171" s="47"/>
-      <c r="M171" s="47"/>
-      <c r="N171" s="47"/>
-      <c r="O171" s="47"/>
-      <c r="P171" s="47"/>
-      <c r="Q171" s="47"/>
-      <c r="R171" s="47"/>
-      <c r="S171" s="47"/>
-      <c r="T171" s="47"/>
-      <c r="U171" s="47"/>
-      <c r="V171" s="47"/>
-      <c r="W171" s="47"/>
-      <c r="X171" s="47"/>
-      <c r="Y171" s="47"/>
-      <c r="Z171" s="47"/>
-      <c r="AA171" s="47"/>
-      <c r="AB171" s="48"/>
+      <c r="H171" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="I171" s="33"/>
+      <c r="J171" s="33"/>
+      <c r="K171" s="33"/>
+      <c r="L171" s="33"/>
+      <c r="M171" s="33"/>
+      <c r="N171" s="33"/>
+      <c r="O171" s="33"/>
+      <c r="P171" s="33"/>
+      <c r="Q171" s="33"/>
+      <c r="R171" s="33"/>
+      <c r="S171" s="33"/>
+      <c r="T171" s="33"/>
+      <c r="U171" s="33"/>
+      <c r="V171" s="33"/>
+      <c r="W171" s="33"/>
+      <c r="X171" s="33"/>
+      <c r="Y171" s="33"/>
+      <c r="Z171" s="33"/>
+      <c r="AA171" s="33"/>
+      <c r="AB171" s="34"/>
       <c r="AC171" s="11"/>
     </row>
     <row r="172" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7082,27 +7120,27 @@
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
-      <c r="H172" s="49"/>
-      <c r="I172" s="50"/>
-      <c r="J172" s="50"/>
-      <c r="K172" s="50"/>
-      <c r="L172" s="50"/>
-      <c r="M172" s="50"/>
-      <c r="N172" s="50"/>
-      <c r="O172" s="50"/>
-      <c r="P172" s="50"/>
-      <c r="Q172" s="50"/>
-      <c r="R172" s="50"/>
-      <c r="S172" s="50"/>
-      <c r="T172" s="50"/>
-      <c r="U172" s="50"/>
-      <c r="V172" s="50"/>
-      <c r="W172" s="50"/>
-      <c r="X172" s="50"/>
-      <c r="Y172" s="50"/>
-      <c r="Z172" s="50"/>
-      <c r="AA172" s="50"/>
-      <c r="AB172" s="51"/>
+      <c r="H172" s="35"/>
+      <c r="I172" s="36"/>
+      <c r="J172" s="36"/>
+      <c r="K172" s="36"/>
+      <c r="L172" s="36"/>
+      <c r="M172" s="36"/>
+      <c r="N172" s="36"/>
+      <c r="O172" s="36"/>
+      <c r="P172" s="36"/>
+      <c r="Q172" s="36"/>
+      <c r="R172" s="36"/>
+      <c r="S172" s="36"/>
+      <c r="T172" s="36"/>
+      <c r="U172" s="36"/>
+      <c r="V172" s="36"/>
+      <c r="W172" s="36"/>
+      <c r="X172" s="36"/>
+      <c r="Y172" s="36"/>
+      <c r="Z172" s="36"/>
+      <c r="AA172" s="36"/>
+      <c r="AB172" s="37"/>
       <c r="AC172" s="11"/>
     </row>
     <row r="173" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7112,27 +7150,27 @@
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
-      <c r="H173" s="49"/>
-      <c r="I173" s="50"/>
-      <c r="J173" s="50"/>
-      <c r="K173" s="50"/>
-      <c r="L173" s="50"/>
-      <c r="M173" s="50"/>
-      <c r="N173" s="50"/>
-      <c r="O173" s="50"/>
-      <c r="P173" s="50"/>
-      <c r="Q173" s="50"/>
-      <c r="R173" s="50"/>
-      <c r="S173" s="50"/>
-      <c r="T173" s="50"/>
-      <c r="U173" s="50"/>
-      <c r="V173" s="50"/>
-      <c r="W173" s="50"/>
-      <c r="X173" s="50"/>
-      <c r="Y173" s="50"/>
-      <c r="Z173" s="50"/>
-      <c r="AA173" s="50"/>
-      <c r="AB173" s="51"/>
+      <c r="H173" s="35"/>
+      <c r="I173" s="36"/>
+      <c r="J173" s="36"/>
+      <c r="K173" s="36"/>
+      <c r="L173" s="36"/>
+      <c r="M173" s="36"/>
+      <c r="N173" s="36"/>
+      <c r="O173" s="36"/>
+      <c r="P173" s="36"/>
+      <c r="Q173" s="36"/>
+      <c r="R173" s="36"/>
+      <c r="S173" s="36"/>
+      <c r="T173" s="36"/>
+      <c r="U173" s="36"/>
+      <c r="V173" s="36"/>
+      <c r="W173" s="36"/>
+      <c r="X173" s="36"/>
+      <c r="Y173" s="36"/>
+      <c r="Z173" s="36"/>
+      <c r="AA173" s="36"/>
+      <c r="AB173" s="37"/>
       <c r="AC173" s="11"/>
     </row>
     <row r="174" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7142,27 +7180,27 @@
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
-      <c r="H174" s="49"/>
-      <c r="I174" s="50"/>
-      <c r="J174" s="50"/>
-      <c r="K174" s="50"/>
-      <c r="L174" s="50"/>
-      <c r="M174" s="50"/>
-      <c r="N174" s="50"/>
-      <c r="O174" s="50"/>
-      <c r="P174" s="50"/>
-      <c r="Q174" s="50"/>
-      <c r="R174" s="50"/>
-      <c r="S174" s="50"/>
-      <c r="T174" s="50"/>
-      <c r="U174" s="50"/>
-      <c r="V174" s="50"/>
-      <c r="W174" s="50"/>
-      <c r="X174" s="50"/>
-      <c r="Y174" s="50"/>
-      <c r="Z174" s="50"/>
-      <c r="AA174" s="50"/>
-      <c r="AB174" s="51"/>
+      <c r="H174" s="35"/>
+      <c r="I174" s="36"/>
+      <c r="J174" s="36"/>
+      <c r="K174" s="36"/>
+      <c r="L174" s="36"/>
+      <c r="M174" s="36"/>
+      <c r="N174" s="36"/>
+      <c r="O174" s="36"/>
+      <c r="P174" s="36"/>
+      <c r="Q174" s="36"/>
+      <c r="R174" s="36"/>
+      <c r="S174" s="36"/>
+      <c r="T174" s="36"/>
+      <c r="U174" s="36"/>
+      <c r="V174" s="36"/>
+      <c r="W174" s="36"/>
+      <c r="X174" s="36"/>
+      <c r="Y174" s="36"/>
+      <c r="Z174" s="36"/>
+      <c r="AA174" s="36"/>
+      <c r="AB174" s="37"/>
       <c r="AC174" s="11"/>
     </row>
     <row r="175" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7172,27 +7210,27 @@
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
-      <c r="H175" s="49"/>
-      <c r="I175" s="50"/>
-      <c r="J175" s="50"/>
-      <c r="K175" s="50"/>
-      <c r="L175" s="50"/>
-      <c r="M175" s="50"/>
-      <c r="N175" s="50"/>
-      <c r="O175" s="50"/>
-      <c r="P175" s="50"/>
-      <c r="Q175" s="50"/>
-      <c r="R175" s="50"/>
-      <c r="S175" s="50"/>
-      <c r="T175" s="50"/>
-      <c r="U175" s="50"/>
-      <c r="V175" s="50"/>
-      <c r="W175" s="50"/>
-      <c r="X175" s="50"/>
-      <c r="Y175" s="50"/>
-      <c r="Z175" s="50"/>
-      <c r="AA175" s="50"/>
-      <c r="AB175" s="51"/>
+      <c r="H175" s="35"/>
+      <c r="I175" s="36"/>
+      <c r="J175" s="36"/>
+      <c r="K175" s="36"/>
+      <c r="L175" s="36"/>
+      <c r="M175" s="36"/>
+      <c r="N175" s="36"/>
+      <c r="O175" s="36"/>
+      <c r="P175" s="36"/>
+      <c r="Q175" s="36"/>
+      <c r="R175" s="36"/>
+      <c r="S175" s="36"/>
+      <c r="T175" s="36"/>
+      <c r="U175" s="36"/>
+      <c r="V175" s="36"/>
+      <c r="W175" s="36"/>
+      <c r="X175" s="36"/>
+      <c r="Y175" s="36"/>
+      <c r="Z175" s="36"/>
+      <c r="AA175" s="36"/>
+      <c r="AB175" s="37"/>
       <c r="AC175" s="11"/>
     </row>
     <row r="176" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7202,27 +7240,27 @@
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
-      <c r="H176" s="49"/>
-      <c r="I176" s="50"/>
-      <c r="J176" s="50"/>
-      <c r="K176" s="50"/>
-      <c r="L176" s="50"/>
-      <c r="M176" s="50"/>
-      <c r="N176" s="50"/>
-      <c r="O176" s="50"/>
-      <c r="P176" s="50"/>
-      <c r="Q176" s="50"/>
-      <c r="R176" s="50"/>
-      <c r="S176" s="50"/>
-      <c r="T176" s="50"/>
-      <c r="U176" s="50"/>
-      <c r="V176" s="50"/>
-      <c r="W176" s="50"/>
-      <c r="X176" s="50"/>
-      <c r="Y176" s="50"/>
-      <c r="Z176" s="50"/>
-      <c r="AA176" s="50"/>
-      <c r="AB176" s="51"/>
+      <c r="H176" s="35"/>
+      <c r="I176" s="36"/>
+      <c r="J176" s="36"/>
+      <c r="K176" s="36"/>
+      <c r="L176" s="36"/>
+      <c r="M176" s="36"/>
+      <c r="N176" s="36"/>
+      <c r="O176" s="36"/>
+      <c r="P176" s="36"/>
+      <c r="Q176" s="36"/>
+      <c r="R176" s="36"/>
+      <c r="S176" s="36"/>
+      <c r="T176" s="36"/>
+      <c r="U176" s="36"/>
+      <c r="V176" s="36"/>
+      <c r="W176" s="36"/>
+      <c r="X176" s="36"/>
+      <c r="Y176" s="36"/>
+      <c r="Z176" s="36"/>
+      <c r="AA176" s="36"/>
+      <c r="AB176" s="37"/>
       <c r="AC176" s="11"/>
     </row>
     <row r="177" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7232,27 +7270,27 @@
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
-      <c r="H177" s="52"/>
-      <c r="I177" s="53"/>
-      <c r="J177" s="53"/>
-      <c r="K177" s="53"/>
-      <c r="L177" s="53"/>
-      <c r="M177" s="53"/>
-      <c r="N177" s="53"/>
-      <c r="O177" s="53"/>
-      <c r="P177" s="53"/>
-      <c r="Q177" s="53"/>
-      <c r="R177" s="53"/>
-      <c r="S177" s="53"/>
-      <c r="T177" s="53"/>
-      <c r="U177" s="53"/>
-      <c r="V177" s="53"/>
-      <c r="W177" s="53"/>
-      <c r="X177" s="53"/>
-      <c r="Y177" s="53"/>
-      <c r="Z177" s="53"/>
-      <c r="AA177" s="53"/>
-      <c r="AB177" s="54"/>
+      <c r="H177" s="38"/>
+      <c r="I177" s="39"/>
+      <c r="J177" s="39"/>
+      <c r="K177" s="39"/>
+      <c r="L177" s="39"/>
+      <c r="M177" s="39"/>
+      <c r="N177" s="39"/>
+      <c r="O177" s="39"/>
+      <c r="P177" s="39"/>
+      <c r="Q177" s="39"/>
+      <c r="R177" s="39"/>
+      <c r="S177" s="39"/>
+      <c r="T177" s="39"/>
+      <c r="U177" s="39"/>
+      <c r="V177" s="39"/>
+      <c r="W177" s="39"/>
+      <c r="X177" s="39"/>
+      <c r="Y177" s="39"/>
+      <c r="Z177" s="39"/>
+      <c r="AA177" s="39"/>
+      <c r="AB177" s="40"/>
       <c r="AC177" s="11"/>
     </row>
     <row r="178" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7360,27 +7398,27 @@
         <v>2</v>
       </c>
       <c r="G182" s="6"/>
-      <c r="H182" s="46"/>
-      <c r="I182" s="47"/>
-      <c r="J182" s="47"/>
-      <c r="K182" s="47"/>
-      <c r="L182" s="47"/>
-      <c r="M182" s="47"/>
-      <c r="N182" s="47"/>
-      <c r="O182" s="47"/>
-      <c r="P182" s="47"/>
-      <c r="Q182" s="47"/>
-      <c r="R182" s="47"/>
-      <c r="S182" s="47"/>
-      <c r="T182" s="47"/>
-      <c r="U182" s="47"/>
-      <c r="V182" s="47"/>
-      <c r="W182" s="47"/>
-      <c r="X182" s="47"/>
-      <c r="Y182" s="47"/>
-      <c r="Z182" s="47"/>
-      <c r="AA182" s="47"/>
-      <c r="AB182" s="48"/>
+      <c r="H182" s="48"/>
+      <c r="I182" s="49"/>
+      <c r="J182" s="49"/>
+      <c r="K182" s="49"/>
+      <c r="L182" s="49"/>
+      <c r="M182" s="49"/>
+      <c r="N182" s="49"/>
+      <c r="O182" s="49"/>
+      <c r="P182" s="49"/>
+      <c r="Q182" s="49"/>
+      <c r="R182" s="49"/>
+      <c r="S182" s="49"/>
+      <c r="T182" s="49"/>
+      <c r="U182" s="49"/>
+      <c r="V182" s="49"/>
+      <c r="W182" s="49"/>
+      <c r="X182" s="49"/>
+      <c r="Y182" s="49"/>
+      <c r="Z182" s="49"/>
+      <c r="AA182" s="49"/>
+      <c r="AB182" s="50"/>
       <c r="AC182" s="11"/>
     </row>
     <row r="183" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7390,27 +7428,27 @@
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
-      <c r="H183" s="49"/>
-      <c r="I183" s="50"/>
-      <c r="J183" s="50"/>
-      <c r="K183" s="50"/>
-      <c r="L183" s="50"/>
-      <c r="M183" s="50"/>
-      <c r="N183" s="50"/>
-      <c r="O183" s="50"/>
-      <c r="P183" s="50"/>
-      <c r="Q183" s="50"/>
-      <c r="R183" s="50"/>
-      <c r="S183" s="50"/>
-      <c r="T183" s="50"/>
-      <c r="U183" s="50"/>
-      <c r="V183" s="50"/>
-      <c r="W183" s="50"/>
-      <c r="X183" s="50"/>
-      <c r="Y183" s="50"/>
-      <c r="Z183" s="50"/>
-      <c r="AA183" s="50"/>
-      <c r="AB183" s="51"/>
+      <c r="H183" s="51"/>
+      <c r="I183" s="52"/>
+      <c r="J183" s="52"/>
+      <c r="K183" s="52"/>
+      <c r="L183" s="52"/>
+      <c r="M183" s="52"/>
+      <c r="N183" s="52"/>
+      <c r="O183" s="52"/>
+      <c r="P183" s="52"/>
+      <c r="Q183" s="52"/>
+      <c r="R183" s="52"/>
+      <c r="S183" s="52"/>
+      <c r="T183" s="52"/>
+      <c r="U183" s="52"/>
+      <c r="V183" s="52"/>
+      <c r="W183" s="52"/>
+      <c r="X183" s="52"/>
+      <c r="Y183" s="52"/>
+      <c r="Z183" s="52"/>
+      <c r="AA183" s="52"/>
+      <c r="AB183" s="53"/>
       <c r="AC183" s="11"/>
     </row>
     <row r="184" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7420,27 +7458,27 @@
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
-      <c r="H184" s="49"/>
-      <c r="I184" s="50"/>
-      <c r="J184" s="50"/>
-      <c r="K184" s="50"/>
-      <c r="L184" s="50"/>
-      <c r="M184" s="50"/>
-      <c r="N184" s="50"/>
-      <c r="O184" s="50"/>
-      <c r="P184" s="50"/>
-      <c r="Q184" s="50"/>
-      <c r="R184" s="50"/>
-      <c r="S184" s="50"/>
-      <c r="T184" s="50"/>
-      <c r="U184" s="50"/>
-      <c r="V184" s="50"/>
-      <c r="W184" s="50"/>
-      <c r="X184" s="50"/>
-      <c r="Y184" s="50"/>
-      <c r="Z184" s="50"/>
-      <c r="AA184" s="50"/>
-      <c r="AB184" s="51"/>
+      <c r="H184" s="51"/>
+      <c r="I184" s="52"/>
+      <c r="J184" s="52"/>
+      <c r="K184" s="52"/>
+      <c r="L184" s="52"/>
+      <c r="M184" s="52"/>
+      <c r="N184" s="52"/>
+      <c r="O184" s="52"/>
+      <c r="P184" s="52"/>
+      <c r="Q184" s="52"/>
+      <c r="R184" s="52"/>
+      <c r="S184" s="52"/>
+      <c r="T184" s="52"/>
+      <c r="U184" s="52"/>
+      <c r="V184" s="52"/>
+      <c r="W184" s="52"/>
+      <c r="X184" s="52"/>
+      <c r="Y184" s="52"/>
+      <c r="Z184" s="52"/>
+      <c r="AA184" s="52"/>
+      <c r="AB184" s="53"/>
       <c r="AC184" s="11"/>
     </row>
     <row r="185" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7450,27 +7488,27 @@
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
-      <c r="H185" s="49"/>
-      <c r="I185" s="50"/>
-      <c r="J185" s="50"/>
-      <c r="K185" s="50"/>
-      <c r="L185" s="50"/>
-      <c r="M185" s="50"/>
-      <c r="N185" s="50"/>
-      <c r="O185" s="50"/>
-      <c r="P185" s="50"/>
-      <c r="Q185" s="50"/>
-      <c r="R185" s="50"/>
-      <c r="S185" s="50"/>
-      <c r="T185" s="50"/>
-      <c r="U185" s="50"/>
-      <c r="V185" s="50"/>
-      <c r="W185" s="50"/>
-      <c r="X185" s="50"/>
-      <c r="Y185" s="50"/>
-      <c r="Z185" s="50"/>
-      <c r="AA185" s="50"/>
-      <c r="AB185" s="51"/>
+      <c r="H185" s="51"/>
+      <c r="I185" s="52"/>
+      <c r="J185" s="52"/>
+      <c r="K185" s="52"/>
+      <c r="L185" s="52"/>
+      <c r="M185" s="52"/>
+      <c r="N185" s="52"/>
+      <c r="O185" s="52"/>
+      <c r="P185" s="52"/>
+      <c r="Q185" s="52"/>
+      <c r="R185" s="52"/>
+      <c r="S185" s="52"/>
+      <c r="T185" s="52"/>
+      <c r="U185" s="52"/>
+      <c r="V185" s="52"/>
+      <c r="W185" s="52"/>
+      <c r="X185" s="52"/>
+      <c r="Y185" s="52"/>
+      <c r="Z185" s="52"/>
+      <c r="AA185" s="52"/>
+      <c r="AB185" s="53"/>
       <c r="AC185" s="11"/>
     </row>
     <row r="186" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7480,27 +7518,27 @@
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
-      <c r="H186" s="49"/>
-      <c r="I186" s="50"/>
-      <c r="J186" s="50"/>
-      <c r="K186" s="50"/>
-      <c r="L186" s="50"/>
-      <c r="M186" s="50"/>
-      <c r="N186" s="50"/>
-      <c r="O186" s="50"/>
-      <c r="P186" s="50"/>
-      <c r="Q186" s="50"/>
-      <c r="R186" s="50"/>
-      <c r="S186" s="50"/>
-      <c r="T186" s="50"/>
-      <c r="U186" s="50"/>
-      <c r="V186" s="50"/>
-      <c r="W186" s="50"/>
-      <c r="X186" s="50"/>
-      <c r="Y186" s="50"/>
-      <c r="Z186" s="50"/>
-      <c r="AA186" s="50"/>
-      <c r="AB186" s="51"/>
+      <c r="H186" s="51"/>
+      <c r="I186" s="52"/>
+      <c r="J186" s="52"/>
+      <c r="K186" s="52"/>
+      <c r="L186" s="52"/>
+      <c r="M186" s="52"/>
+      <c r="N186" s="52"/>
+      <c r="O186" s="52"/>
+      <c r="P186" s="52"/>
+      <c r="Q186" s="52"/>
+      <c r="R186" s="52"/>
+      <c r="S186" s="52"/>
+      <c r="T186" s="52"/>
+      <c r="U186" s="52"/>
+      <c r="V186" s="52"/>
+      <c r="W186" s="52"/>
+      <c r="X186" s="52"/>
+      <c r="Y186" s="52"/>
+      <c r="Z186" s="52"/>
+      <c r="AA186" s="52"/>
+      <c r="AB186" s="53"/>
       <c r="AC186" s="11"/>
     </row>
     <row r="187" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7510,27 +7548,27 @@
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
-      <c r="H187" s="49"/>
-      <c r="I187" s="50"/>
-      <c r="J187" s="50"/>
-      <c r="K187" s="50"/>
-      <c r="L187" s="50"/>
-      <c r="M187" s="50"/>
-      <c r="N187" s="50"/>
-      <c r="O187" s="50"/>
-      <c r="P187" s="50"/>
-      <c r="Q187" s="50"/>
-      <c r="R187" s="50"/>
-      <c r="S187" s="50"/>
-      <c r="T187" s="50"/>
-      <c r="U187" s="50"/>
-      <c r="V187" s="50"/>
-      <c r="W187" s="50"/>
-      <c r="X187" s="50"/>
-      <c r="Y187" s="50"/>
-      <c r="Z187" s="50"/>
-      <c r="AA187" s="50"/>
-      <c r="AB187" s="51"/>
+      <c r="H187" s="51"/>
+      <c r="I187" s="52"/>
+      <c r="J187" s="52"/>
+      <c r="K187" s="52"/>
+      <c r="L187" s="52"/>
+      <c r="M187" s="52"/>
+      <c r="N187" s="52"/>
+      <c r="O187" s="52"/>
+      <c r="P187" s="52"/>
+      <c r="Q187" s="52"/>
+      <c r="R187" s="52"/>
+      <c r="S187" s="52"/>
+      <c r="T187" s="52"/>
+      <c r="U187" s="52"/>
+      <c r="V187" s="52"/>
+      <c r="W187" s="52"/>
+      <c r="X187" s="52"/>
+      <c r="Y187" s="52"/>
+      <c r="Z187" s="52"/>
+      <c r="AA187" s="52"/>
+      <c r="AB187" s="53"/>
       <c r="AC187" s="11"/>
     </row>
     <row r="188" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7540,27 +7578,27 @@
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
-      <c r="H188" s="52"/>
-      <c r="I188" s="53"/>
-      <c r="J188" s="53"/>
-      <c r="K188" s="53"/>
-      <c r="L188" s="53"/>
-      <c r="M188" s="53"/>
-      <c r="N188" s="53"/>
-      <c r="O188" s="53"/>
-      <c r="P188" s="53"/>
-      <c r="Q188" s="53"/>
-      <c r="R188" s="53"/>
-      <c r="S188" s="53"/>
-      <c r="T188" s="53"/>
-      <c r="U188" s="53"/>
-      <c r="V188" s="53"/>
-      <c r="W188" s="53"/>
-      <c r="X188" s="53"/>
-      <c r="Y188" s="53"/>
-      <c r="Z188" s="53"/>
-      <c r="AA188" s="53"/>
-      <c r="AB188" s="54"/>
+      <c r="H188" s="54"/>
+      <c r="I188" s="55"/>
+      <c r="J188" s="55"/>
+      <c r="K188" s="55"/>
+      <c r="L188" s="55"/>
+      <c r="M188" s="55"/>
+      <c r="N188" s="55"/>
+      <c r="O188" s="55"/>
+      <c r="P188" s="55"/>
+      <c r="Q188" s="55"/>
+      <c r="R188" s="55"/>
+      <c r="S188" s="55"/>
+      <c r="T188" s="55"/>
+      <c r="U188" s="55"/>
+      <c r="V188" s="55"/>
+      <c r="W188" s="55"/>
+      <c r="X188" s="55"/>
+      <c r="Y188" s="55"/>
+      <c r="Z188" s="55"/>
+      <c r="AA188" s="55"/>
+      <c r="AB188" s="56"/>
       <c r="AC188" s="11"/>
     </row>
     <row r="189" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7602,27 +7640,27 @@
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
-      <c r="H190" s="46"/>
-      <c r="I190" s="47"/>
-      <c r="J190" s="47"/>
-      <c r="K190" s="47"/>
-      <c r="L190" s="47"/>
-      <c r="M190" s="47"/>
-      <c r="N190" s="47"/>
-      <c r="O190" s="47"/>
-      <c r="P190" s="47"/>
-      <c r="Q190" s="47"/>
-      <c r="R190" s="47"/>
-      <c r="S190" s="47"/>
-      <c r="T190" s="47"/>
-      <c r="U190" s="47"/>
-      <c r="V190" s="47"/>
-      <c r="W190" s="47"/>
-      <c r="X190" s="47"/>
-      <c r="Y190" s="47"/>
-      <c r="Z190" s="47"/>
-      <c r="AA190" s="47"/>
-      <c r="AB190" s="48"/>
+      <c r="H190" s="48"/>
+      <c r="I190" s="49"/>
+      <c r="J190" s="49"/>
+      <c r="K190" s="49"/>
+      <c r="L190" s="49"/>
+      <c r="M190" s="49"/>
+      <c r="N190" s="49"/>
+      <c r="O190" s="49"/>
+      <c r="P190" s="49"/>
+      <c r="Q190" s="49"/>
+      <c r="R190" s="49"/>
+      <c r="S190" s="49"/>
+      <c r="T190" s="49"/>
+      <c r="U190" s="49"/>
+      <c r="V190" s="49"/>
+      <c r="W190" s="49"/>
+      <c r="X190" s="49"/>
+      <c r="Y190" s="49"/>
+      <c r="Z190" s="49"/>
+      <c r="AA190" s="49"/>
+      <c r="AB190" s="50"/>
       <c r="AC190" s="11"/>
     </row>
     <row r="191" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7632,27 +7670,27 @@
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
-      <c r="H191" s="49"/>
-      <c r="I191" s="50"/>
-      <c r="J191" s="50"/>
-      <c r="K191" s="50"/>
-      <c r="L191" s="50"/>
-      <c r="M191" s="50"/>
-      <c r="N191" s="50"/>
-      <c r="O191" s="50"/>
-      <c r="P191" s="50"/>
-      <c r="Q191" s="50"/>
-      <c r="R191" s="50"/>
-      <c r="S191" s="50"/>
-      <c r="T191" s="50"/>
-      <c r="U191" s="50"/>
-      <c r="V191" s="50"/>
-      <c r="W191" s="50"/>
-      <c r="X191" s="50"/>
-      <c r="Y191" s="50"/>
-      <c r="Z191" s="50"/>
-      <c r="AA191" s="50"/>
-      <c r="AB191" s="51"/>
+      <c r="H191" s="51"/>
+      <c r="I191" s="52"/>
+      <c r="J191" s="52"/>
+      <c r="K191" s="52"/>
+      <c r="L191" s="52"/>
+      <c r="M191" s="52"/>
+      <c r="N191" s="52"/>
+      <c r="O191" s="52"/>
+      <c r="P191" s="52"/>
+      <c r="Q191" s="52"/>
+      <c r="R191" s="52"/>
+      <c r="S191" s="52"/>
+      <c r="T191" s="52"/>
+      <c r="U191" s="52"/>
+      <c r="V191" s="52"/>
+      <c r="W191" s="52"/>
+      <c r="X191" s="52"/>
+      <c r="Y191" s="52"/>
+      <c r="Z191" s="52"/>
+      <c r="AA191" s="52"/>
+      <c r="AB191" s="53"/>
       <c r="AC191" s="11"/>
     </row>
     <row r="192" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7662,27 +7700,27 @@
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
-      <c r="H192" s="49"/>
-      <c r="I192" s="50"/>
-      <c r="J192" s="50"/>
-      <c r="K192" s="50"/>
-      <c r="L192" s="50"/>
-      <c r="M192" s="50"/>
-      <c r="N192" s="50"/>
-      <c r="O192" s="50"/>
-      <c r="P192" s="50"/>
-      <c r="Q192" s="50"/>
-      <c r="R192" s="50"/>
-      <c r="S192" s="50"/>
-      <c r="T192" s="50"/>
-      <c r="U192" s="50"/>
-      <c r="V192" s="50"/>
-      <c r="W192" s="50"/>
-      <c r="X192" s="50"/>
-      <c r="Y192" s="50"/>
-      <c r="Z192" s="50"/>
-      <c r="AA192" s="50"/>
-      <c r="AB192" s="51"/>
+      <c r="H192" s="51"/>
+      <c r="I192" s="52"/>
+      <c r="J192" s="52"/>
+      <c r="K192" s="52"/>
+      <c r="L192" s="52"/>
+      <c r="M192" s="52"/>
+      <c r="N192" s="52"/>
+      <c r="O192" s="52"/>
+      <c r="P192" s="52"/>
+      <c r="Q192" s="52"/>
+      <c r="R192" s="52"/>
+      <c r="S192" s="52"/>
+      <c r="T192" s="52"/>
+      <c r="U192" s="52"/>
+      <c r="V192" s="52"/>
+      <c r="W192" s="52"/>
+      <c r="X192" s="52"/>
+      <c r="Y192" s="52"/>
+      <c r="Z192" s="52"/>
+      <c r="AA192" s="52"/>
+      <c r="AB192" s="53"/>
       <c r="AC192" s="11"/>
     </row>
     <row r="193" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7692,27 +7730,27 @@
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
-      <c r="H193" s="49"/>
-      <c r="I193" s="50"/>
-      <c r="J193" s="50"/>
-      <c r="K193" s="50"/>
-      <c r="L193" s="50"/>
-      <c r="M193" s="50"/>
-      <c r="N193" s="50"/>
-      <c r="O193" s="50"/>
-      <c r="P193" s="50"/>
-      <c r="Q193" s="50"/>
-      <c r="R193" s="50"/>
-      <c r="S193" s="50"/>
-      <c r="T193" s="50"/>
-      <c r="U193" s="50"/>
-      <c r="V193" s="50"/>
-      <c r="W193" s="50"/>
-      <c r="X193" s="50"/>
-      <c r="Y193" s="50"/>
-      <c r="Z193" s="50"/>
-      <c r="AA193" s="50"/>
-      <c r="AB193" s="51"/>
+      <c r="H193" s="51"/>
+      <c r="I193" s="52"/>
+      <c r="J193" s="52"/>
+      <c r="K193" s="52"/>
+      <c r="L193" s="52"/>
+      <c r="M193" s="52"/>
+      <c r="N193" s="52"/>
+      <c r="O193" s="52"/>
+      <c r="P193" s="52"/>
+      <c r="Q193" s="52"/>
+      <c r="R193" s="52"/>
+      <c r="S193" s="52"/>
+      <c r="T193" s="52"/>
+      <c r="U193" s="52"/>
+      <c r="V193" s="52"/>
+      <c r="W193" s="52"/>
+      <c r="X193" s="52"/>
+      <c r="Y193" s="52"/>
+      <c r="Z193" s="52"/>
+      <c r="AA193" s="52"/>
+      <c r="AB193" s="53"/>
       <c r="AC193" s="11"/>
     </row>
     <row r="194" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7722,27 +7760,27 @@
       <c r="E194" s="6"/>
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
-      <c r="H194" s="49"/>
-      <c r="I194" s="50"/>
-      <c r="J194" s="50"/>
-      <c r="K194" s="50"/>
-      <c r="L194" s="50"/>
-      <c r="M194" s="50"/>
-      <c r="N194" s="50"/>
-      <c r="O194" s="50"/>
-      <c r="P194" s="50"/>
-      <c r="Q194" s="50"/>
-      <c r="R194" s="50"/>
-      <c r="S194" s="50"/>
-      <c r="T194" s="50"/>
-      <c r="U194" s="50"/>
-      <c r="V194" s="50"/>
-      <c r="W194" s="50"/>
-      <c r="X194" s="50"/>
-      <c r="Y194" s="50"/>
-      <c r="Z194" s="50"/>
-      <c r="AA194" s="50"/>
-      <c r="AB194" s="51"/>
+      <c r="H194" s="51"/>
+      <c r="I194" s="52"/>
+      <c r="J194" s="52"/>
+      <c r="K194" s="52"/>
+      <c r="L194" s="52"/>
+      <c r="M194" s="52"/>
+      <c r="N194" s="52"/>
+      <c r="O194" s="52"/>
+      <c r="P194" s="52"/>
+      <c r="Q194" s="52"/>
+      <c r="R194" s="52"/>
+      <c r="S194" s="52"/>
+      <c r="T194" s="52"/>
+      <c r="U194" s="52"/>
+      <c r="V194" s="52"/>
+      <c r="W194" s="52"/>
+      <c r="X194" s="52"/>
+      <c r="Y194" s="52"/>
+      <c r="Z194" s="52"/>
+      <c r="AA194" s="52"/>
+      <c r="AB194" s="53"/>
       <c r="AC194" s="11"/>
     </row>
     <row r="195" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7752,27 +7790,27 @@
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
-      <c r="H195" s="49"/>
-      <c r="I195" s="50"/>
-      <c r="J195" s="50"/>
-      <c r="K195" s="50"/>
-      <c r="L195" s="50"/>
-      <c r="M195" s="50"/>
-      <c r="N195" s="50"/>
-      <c r="O195" s="50"/>
-      <c r="P195" s="50"/>
-      <c r="Q195" s="50"/>
-      <c r="R195" s="50"/>
-      <c r="S195" s="50"/>
-      <c r="T195" s="50"/>
-      <c r="U195" s="50"/>
-      <c r="V195" s="50"/>
-      <c r="W195" s="50"/>
-      <c r="X195" s="50"/>
-      <c r="Y195" s="50"/>
-      <c r="Z195" s="50"/>
-      <c r="AA195" s="50"/>
-      <c r="AB195" s="51"/>
+      <c r="H195" s="51"/>
+      <c r="I195" s="52"/>
+      <c r="J195" s="52"/>
+      <c r="K195" s="52"/>
+      <c r="L195" s="52"/>
+      <c r="M195" s="52"/>
+      <c r="N195" s="52"/>
+      <c r="O195" s="52"/>
+      <c r="P195" s="52"/>
+      <c r="Q195" s="52"/>
+      <c r="R195" s="52"/>
+      <c r="S195" s="52"/>
+      <c r="T195" s="52"/>
+      <c r="U195" s="52"/>
+      <c r="V195" s="52"/>
+      <c r="W195" s="52"/>
+      <c r="X195" s="52"/>
+      <c r="Y195" s="52"/>
+      <c r="Z195" s="52"/>
+      <c r="AA195" s="52"/>
+      <c r="AB195" s="53"/>
       <c r="AC195" s="11"/>
     </row>
     <row r="196" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7782,27 +7820,27 @@
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
-      <c r="H196" s="52"/>
-      <c r="I196" s="53"/>
-      <c r="J196" s="53"/>
-      <c r="K196" s="53"/>
-      <c r="L196" s="53"/>
-      <c r="M196" s="53"/>
-      <c r="N196" s="53"/>
-      <c r="O196" s="53"/>
-      <c r="P196" s="53"/>
-      <c r="Q196" s="53"/>
-      <c r="R196" s="53"/>
-      <c r="S196" s="53"/>
-      <c r="T196" s="53"/>
-      <c r="U196" s="53"/>
-      <c r="V196" s="53"/>
-      <c r="W196" s="53"/>
-      <c r="X196" s="53"/>
-      <c r="Y196" s="53"/>
-      <c r="Z196" s="53"/>
-      <c r="AA196" s="53"/>
-      <c r="AB196" s="54"/>
+      <c r="H196" s="54"/>
+      <c r="I196" s="55"/>
+      <c r="J196" s="55"/>
+      <c r="K196" s="55"/>
+      <c r="L196" s="55"/>
+      <c r="M196" s="55"/>
+      <c r="N196" s="55"/>
+      <c r="O196" s="55"/>
+      <c r="P196" s="55"/>
+      <c r="Q196" s="55"/>
+      <c r="R196" s="55"/>
+      <c r="S196" s="55"/>
+      <c r="T196" s="55"/>
+      <c r="U196" s="55"/>
+      <c r="V196" s="55"/>
+      <c r="W196" s="55"/>
+      <c r="X196" s="55"/>
+      <c r="Y196" s="55"/>
+      <c r="Z196" s="55"/>
+      <c r="AA196" s="55"/>
+      <c r="AB196" s="56"/>
       <c r="AC196" s="11"/>
     </row>
     <row r="197" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7910,27 +7948,27 @@
         <v>2</v>
       </c>
       <c r="G201" s="6"/>
-      <c r="H201" s="46"/>
-      <c r="I201" s="47"/>
-      <c r="J201" s="47"/>
-      <c r="K201" s="47"/>
-      <c r="L201" s="47"/>
-      <c r="M201" s="47"/>
-      <c r="N201" s="47"/>
-      <c r="O201" s="47"/>
-      <c r="P201" s="47"/>
-      <c r="Q201" s="47"/>
-      <c r="R201" s="47"/>
-      <c r="S201" s="47"/>
-      <c r="T201" s="47"/>
-      <c r="U201" s="47"/>
-      <c r="V201" s="47"/>
-      <c r="W201" s="47"/>
-      <c r="X201" s="47"/>
-      <c r="Y201" s="47"/>
-      <c r="Z201" s="47"/>
-      <c r="AA201" s="47"/>
-      <c r="AB201" s="48"/>
+      <c r="H201" s="48"/>
+      <c r="I201" s="49"/>
+      <c r="J201" s="49"/>
+      <c r="K201" s="49"/>
+      <c r="L201" s="49"/>
+      <c r="M201" s="49"/>
+      <c r="N201" s="49"/>
+      <c r="O201" s="49"/>
+      <c r="P201" s="49"/>
+      <c r="Q201" s="49"/>
+      <c r="R201" s="49"/>
+      <c r="S201" s="49"/>
+      <c r="T201" s="49"/>
+      <c r="U201" s="49"/>
+      <c r="V201" s="49"/>
+      <c r="W201" s="49"/>
+      <c r="X201" s="49"/>
+      <c r="Y201" s="49"/>
+      <c r="Z201" s="49"/>
+      <c r="AA201" s="49"/>
+      <c r="AB201" s="50"/>
       <c r="AC201" s="11"/>
     </row>
     <row r="202" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7940,27 +7978,27 @@
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
-      <c r="H202" s="49"/>
-      <c r="I202" s="50"/>
-      <c r="J202" s="50"/>
-      <c r="K202" s="50"/>
-      <c r="L202" s="50"/>
-      <c r="M202" s="50"/>
-      <c r="N202" s="50"/>
-      <c r="O202" s="50"/>
-      <c r="P202" s="50"/>
-      <c r="Q202" s="50"/>
-      <c r="R202" s="50"/>
-      <c r="S202" s="50"/>
-      <c r="T202" s="50"/>
-      <c r="U202" s="50"/>
-      <c r="V202" s="50"/>
-      <c r="W202" s="50"/>
-      <c r="X202" s="50"/>
-      <c r="Y202" s="50"/>
-      <c r="Z202" s="50"/>
-      <c r="AA202" s="50"/>
-      <c r="AB202" s="51"/>
+      <c r="H202" s="51"/>
+      <c r="I202" s="52"/>
+      <c r="J202" s="52"/>
+      <c r="K202" s="52"/>
+      <c r="L202" s="52"/>
+      <c r="M202" s="52"/>
+      <c r="N202" s="52"/>
+      <c r="O202" s="52"/>
+      <c r="P202" s="52"/>
+      <c r="Q202" s="52"/>
+      <c r="R202" s="52"/>
+      <c r="S202" s="52"/>
+      <c r="T202" s="52"/>
+      <c r="U202" s="52"/>
+      <c r="V202" s="52"/>
+      <c r="W202" s="52"/>
+      <c r="X202" s="52"/>
+      <c r="Y202" s="52"/>
+      <c r="Z202" s="52"/>
+      <c r="AA202" s="52"/>
+      <c r="AB202" s="53"/>
       <c r="AC202" s="11"/>
     </row>
     <row r="203" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7970,27 +8008,27 @@
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
-      <c r="H203" s="49"/>
-      <c r="I203" s="50"/>
-      <c r="J203" s="50"/>
-      <c r="K203" s="50"/>
-      <c r="L203" s="50"/>
-      <c r="M203" s="50"/>
-      <c r="N203" s="50"/>
-      <c r="O203" s="50"/>
-      <c r="P203" s="50"/>
-      <c r="Q203" s="50"/>
-      <c r="R203" s="50"/>
-      <c r="S203" s="50"/>
-      <c r="T203" s="50"/>
-      <c r="U203" s="50"/>
-      <c r="V203" s="50"/>
-      <c r="W203" s="50"/>
-      <c r="X203" s="50"/>
-      <c r="Y203" s="50"/>
-      <c r="Z203" s="50"/>
-      <c r="AA203" s="50"/>
-      <c r="AB203" s="51"/>
+      <c r="H203" s="51"/>
+      <c r="I203" s="52"/>
+      <c r="J203" s="52"/>
+      <c r="K203" s="52"/>
+      <c r="L203" s="52"/>
+      <c r="M203" s="52"/>
+      <c r="N203" s="52"/>
+      <c r="O203" s="52"/>
+      <c r="P203" s="52"/>
+      <c r="Q203" s="52"/>
+      <c r="R203" s="52"/>
+      <c r="S203" s="52"/>
+      <c r="T203" s="52"/>
+      <c r="U203" s="52"/>
+      <c r="V203" s="52"/>
+      <c r="W203" s="52"/>
+      <c r="X203" s="52"/>
+      <c r="Y203" s="52"/>
+      <c r="Z203" s="52"/>
+      <c r="AA203" s="52"/>
+      <c r="AB203" s="53"/>
       <c r="AC203" s="11"/>
     </row>
     <row r="204" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8000,27 +8038,27 @@
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
-      <c r="H204" s="49"/>
-      <c r="I204" s="50"/>
-      <c r="J204" s="50"/>
-      <c r="K204" s="50"/>
-      <c r="L204" s="50"/>
-      <c r="M204" s="50"/>
-      <c r="N204" s="50"/>
-      <c r="O204" s="50"/>
-      <c r="P204" s="50"/>
-      <c r="Q204" s="50"/>
-      <c r="R204" s="50"/>
-      <c r="S204" s="50"/>
-      <c r="T204" s="50"/>
-      <c r="U204" s="50"/>
-      <c r="V204" s="50"/>
-      <c r="W204" s="50"/>
-      <c r="X204" s="50"/>
-      <c r="Y204" s="50"/>
-      <c r="Z204" s="50"/>
-      <c r="AA204" s="50"/>
-      <c r="AB204" s="51"/>
+      <c r="H204" s="51"/>
+      <c r="I204" s="52"/>
+      <c r="J204" s="52"/>
+      <c r="K204" s="52"/>
+      <c r="L204" s="52"/>
+      <c r="M204" s="52"/>
+      <c r="N204" s="52"/>
+      <c r="O204" s="52"/>
+      <c r="P204" s="52"/>
+      <c r="Q204" s="52"/>
+      <c r="R204" s="52"/>
+      <c r="S204" s="52"/>
+      <c r="T204" s="52"/>
+      <c r="U204" s="52"/>
+      <c r="V204" s="52"/>
+      <c r="W204" s="52"/>
+      <c r="X204" s="52"/>
+      <c r="Y204" s="52"/>
+      <c r="Z204" s="52"/>
+      <c r="AA204" s="52"/>
+      <c r="AB204" s="53"/>
       <c r="AC204" s="11"/>
     </row>
     <row r="205" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8030,27 +8068,27 @@
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
       <c r="G205" s="6"/>
-      <c r="H205" s="49"/>
-      <c r="I205" s="50"/>
-      <c r="J205" s="50"/>
-      <c r="K205" s="50"/>
-      <c r="L205" s="50"/>
-      <c r="M205" s="50"/>
-      <c r="N205" s="50"/>
-      <c r="O205" s="50"/>
-      <c r="P205" s="50"/>
-      <c r="Q205" s="50"/>
-      <c r="R205" s="50"/>
-      <c r="S205" s="50"/>
-      <c r="T205" s="50"/>
-      <c r="U205" s="50"/>
-      <c r="V205" s="50"/>
-      <c r="W205" s="50"/>
-      <c r="X205" s="50"/>
-      <c r="Y205" s="50"/>
-      <c r="Z205" s="50"/>
-      <c r="AA205" s="50"/>
-      <c r="AB205" s="51"/>
+      <c r="H205" s="51"/>
+      <c r="I205" s="52"/>
+      <c r="J205" s="52"/>
+      <c r="K205" s="52"/>
+      <c r="L205" s="52"/>
+      <c r="M205" s="52"/>
+      <c r="N205" s="52"/>
+      <c r="O205" s="52"/>
+      <c r="P205" s="52"/>
+      <c r="Q205" s="52"/>
+      <c r="R205" s="52"/>
+      <c r="S205" s="52"/>
+      <c r="T205" s="52"/>
+      <c r="U205" s="52"/>
+      <c r="V205" s="52"/>
+      <c r="W205" s="52"/>
+      <c r="X205" s="52"/>
+      <c r="Y205" s="52"/>
+      <c r="Z205" s="52"/>
+      <c r="AA205" s="52"/>
+      <c r="AB205" s="53"/>
       <c r="AC205" s="11"/>
     </row>
     <row r="206" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8060,27 +8098,27 @@
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
-      <c r="H206" s="49"/>
-      <c r="I206" s="50"/>
-      <c r="J206" s="50"/>
-      <c r="K206" s="50"/>
-      <c r="L206" s="50"/>
-      <c r="M206" s="50"/>
-      <c r="N206" s="50"/>
-      <c r="O206" s="50"/>
-      <c r="P206" s="50"/>
-      <c r="Q206" s="50"/>
-      <c r="R206" s="50"/>
-      <c r="S206" s="50"/>
-      <c r="T206" s="50"/>
-      <c r="U206" s="50"/>
-      <c r="V206" s="50"/>
-      <c r="W206" s="50"/>
-      <c r="X206" s="50"/>
-      <c r="Y206" s="50"/>
-      <c r="Z206" s="50"/>
-      <c r="AA206" s="50"/>
-      <c r="AB206" s="51"/>
+      <c r="H206" s="51"/>
+      <c r="I206" s="52"/>
+      <c r="J206" s="52"/>
+      <c r="K206" s="52"/>
+      <c r="L206" s="52"/>
+      <c r="M206" s="52"/>
+      <c r="N206" s="52"/>
+      <c r="O206" s="52"/>
+      <c r="P206" s="52"/>
+      <c r="Q206" s="52"/>
+      <c r="R206" s="52"/>
+      <c r="S206" s="52"/>
+      <c r="T206" s="52"/>
+      <c r="U206" s="52"/>
+      <c r="V206" s="52"/>
+      <c r="W206" s="52"/>
+      <c r="X206" s="52"/>
+      <c r="Y206" s="52"/>
+      <c r="Z206" s="52"/>
+      <c r="AA206" s="52"/>
+      <c r="AB206" s="53"/>
       <c r="AC206" s="11"/>
     </row>
     <row r="207" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8090,27 +8128,27 @@
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
-      <c r="H207" s="52"/>
-      <c r="I207" s="53"/>
-      <c r="J207" s="53"/>
-      <c r="K207" s="53"/>
-      <c r="L207" s="53"/>
-      <c r="M207" s="53"/>
-      <c r="N207" s="53"/>
-      <c r="O207" s="53"/>
-      <c r="P207" s="53"/>
-      <c r="Q207" s="53"/>
-      <c r="R207" s="53"/>
-      <c r="S207" s="53"/>
-      <c r="T207" s="53"/>
-      <c r="U207" s="53"/>
-      <c r="V207" s="53"/>
-      <c r="W207" s="53"/>
-      <c r="X207" s="53"/>
-      <c r="Y207" s="53"/>
-      <c r="Z207" s="53"/>
-      <c r="AA207" s="53"/>
-      <c r="AB207" s="54"/>
+      <c r="H207" s="54"/>
+      <c r="I207" s="55"/>
+      <c r="J207" s="55"/>
+      <c r="K207" s="55"/>
+      <c r="L207" s="55"/>
+      <c r="M207" s="55"/>
+      <c r="N207" s="55"/>
+      <c r="O207" s="55"/>
+      <c r="P207" s="55"/>
+      <c r="Q207" s="55"/>
+      <c r="R207" s="55"/>
+      <c r="S207" s="55"/>
+      <c r="T207" s="55"/>
+      <c r="U207" s="55"/>
+      <c r="V207" s="55"/>
+      <c r="W207" s="55"/>
+      <c r="X207" s="55"/>
+      <c r="Y207" s="55"/>
+      <c r="Z207" s="55"/>
+      <c r="AA207" s="55"/>
+      <c r="AB207" s="56"/>
       <c r="AC207" s="11"/>
     </row>
     <row r="208" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8152,27 +8190,27 @@
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
-      <c r="H209" s="46"/>
-      <c r="I209" s="47"/>
-      <c r="J209" s="47"/>
-      <c r="K209" s="47"/>
-      <c r="L209" s="47"/>
-      <c r="M209" s="47"/>
-      <c r="N209" s="47"/>
-      <c r="O209" s="47"/>
-      <c r="P209" s="47"/>
-      <c r="Q209" s="47"/>
-      <c r="R209" s="47"/>
-      <c r="S209" s="47"/>
-      <c r="T209" s="47"/>
-      <c r="U209" s="47"/>
-      <c r="V209" s="47"/>
-      <c r="W209" s="47"/>
-      <c r="X209" s="47"/>
-      <c r="Y209" s="47"/>
-      <c r="Z209" s="47"/>
-      <c r="AA209" s="47"/>
-      <c r="AB209" s="48"/>
+      <c r="H209" s="48"/>
+      <c r="I209" s="49"/>
+      <c r="J209" s="49"/>
+      <c r="K209" s="49"/>
+      <c r="L209" s="49"/>
+      <c r="M209" s="49"/>
+      <c r="N209" s="49"/>
+      <c r="O209" s="49"/>
+      <c r="P209" s="49"/>
+      <c r="Q209" s="49"/>
+      <c r="R209" s="49"/>
+      <c r="S209" s="49"/>
+      <c r="T209" s="49"/>
+      <c r="U209" s="49"/>
+      <c r="V209" s="49"/>
+      <c r="W209" s="49"/>
+      <c r="X209" s="49"/>
+      <c r="Y209" s="49"/>
+      <c r="Z209" s="49"/>
+      <c r="AA209" s="49"/>
+      <c r="AB209" s="50"/>
       <c r="AC209" s="11"/>
     </row>
     <row r="210" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8182,27 +8220,27 @@
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
-      <c r="H210" s="49"/>
-      <c r="I210" s="50"/>
-      <c r="J210" s="50"/>
-      <c r="K210" s="50"/>
-      <c r="L210" s="50"/>
-      <c r="M210" s="50"/>
-      <c r="N210" s="50"/>
-      <c r="O210" s="50"/>
-      <c r="P210" s="50"/>
-      <c r="Q210" s="50"/>
-      <c r="R210" s="50"/>
-      <c r="S210" s="50"/>
-      <c r="T210" s="50"/>
-      <c r="U210" s="50"/>
-      <c r="V210" s="50"/>
-      <c r="W210" s="50"/>
-      <c r="X210" s="50"/>
-      <c r="Y210" s="50"/>
-      <c r="Z210" s="50"/>
-      <c r="AA210" s="50"/>
-      <c r="AB210" s="51"/>
+      <c r="H210" s="51"/>
+      <c r="I210" s="52"/>
+      <c r="J210" s="52"/>
+      <c r="K210" s="52"/>
+      <c r="L210" s="52"/>
+      <c r="M210" s="52"/>
+      <c r="N210" s="52"/>
+      <c r="O210" s="52"/>
+      <c r="P210" s="52"/>
+      <c r="Q210" s="52"/>
+      <c r="R210" s="52"/>
+      <c r="S210" s="52"/>
+      <c r="T210" s="52"/>
+      <c r="U210" s="52"/>
+      <c r="V210" s="52"/>
+      <c r="W210" s="52"/>
+      <c r="X210" s="52"/>
+      <c r="Y210" s="52"/>
+      <c r="Z210" s="52"/>
+      <c r="AA210" s="52"/>
+      <c r="AB210" s="53"/>
       <c r="AC210" s="11"/>
     </row>
     <row r="211" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8212,27 +8250,27 @@
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
       <c r="G211" s="6"/>
-      <c r="H211" s="49"/>
-      <c r="I211" s="50"/>
-      <c r="J211" s="50"/>
-      <c r="K211" s="50"/>
-      <c r="L211" s="50"/>
-      <c r="M211" s="50"/>
-      <c r="N211" s="50"/>
-      <c r="O211" s="50"/>
-      <c r="P211" s="50"/>
-      <c r="Q211" s="50"/>
-      <c r="R211" s="50"/>
-      <c r="S211" s="50"/>
-      <c r="T211" s="50"/>
-      <c r="U211" s="50"/>
-      <c r="V211" s="50"/>
-      <c r="W211" s="50"/>
-      <c r="X211" s="50"/>
-      <c r="Y211" s="50"/>
-      <c r="Z211" s="50"/>
-      <c r="AA211" s="50"/>
-      <c r="AB211" s="51"/>
+      <c r="H211" s="51"/>
+      <c r="I211" s="52"/>
+      <c r="J211" s="52"/>
+      <c r="K211" s="52"/>
+      <c r="L211" s="52"/>
+      <c r="M211" s="52"/>
+      <c r="N211" s="52"/>
+      <c r="O211" s="52"/>
+      <c r="P211" s="52"/>
+      <c r="Q211" s="52"/>
+      <c r="R211" s="52"/>
+      <c r="S211" s="52"/>
+      <c r="T211" s="52"/>
+      <c r="U211" s="52"/>
+      <c r="V211" s="52"/>
+      <c r="W211" s="52"/>
+      <c r="X211" s="52"/>
+      <c r="Y211" s="52"/>
+      <c r="Z211" s="52"/>
+      <c r="AA211" s="52"/>
+      <c r="AB211" s="53"/>
       <c r="AC211" s="11"/>
     </row>
     <row r="212" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8242,27 +8280,27 @@
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
-      <c r="H212" s="49"/>
-      <c r="I212" s="50"/>
-      <c r="J212" s="50"/>
-      <c r="K212" s="50"/>
-      <c r="L212" s="50"/>
-      <c r="M212" s="50"/>
-      <c r="N212" s="50"/>
-      <c r="O212" s="50"/>
-      <c r="P212" s="50"/>
-      <c r="Q212" s="50"/>
-      <c r="R212" s="50"/>
-      <c r="S212" s="50"/>
-      <c r="T212" s="50"/>
-      <c r="U212" s="50"/>
-      <c r="V212" s="50"/>
-      <c r="W212" s="50"/>
-      <c r="X212" s="50"/>
-      <c r="Y212" s="50"/>
-      <c r="Z212" s="50"/>
-      <c r="AA212" s="50"/>
-      <c r="AB212" s="51"/>
+      <c r="H212" s="51"/>
+      <c r="I212" s="52"/>
+      <c r="J212" s="52"/>
+      <c r="K212" s="52"/>
+      <c r="L212" s="52"/>
+      <c r="M212" s="52"/>
+      <c r="N212" s="52"/>
+      <c r="O212" s="52"/>
+      <c r="P212" s="52"/>
+      <c r="Q212" s="52"/>
+      <c r="R212" s="52"/>
+      <c r="S212" s="52"/>
+      <c r="T212" s="52"/>
+      <c r="U212" s="52"/>
+      <c r="V212" s="52"/>
+      <c r="W212" s="52"/>
+      <c r="X212" s="52"/>
+      <c r="Y212" s="52"/>
+      <c r="Z212" s="52"/>
+      <c r="AA212" s="52"/>
+      <c r="AB212" s="53"/>
       <c r="AC212" s="11"/>
     </row>
     <row r="213" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8272,27 +8310,27 @@
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
       <c r="G213" s="6"/>
-      <c r="H213" s="49"/>
-      <c r="I213" s="50"/>
-      <c r="J213" s="50"/>
-      <c r="K213" s="50"/>
-      <c r="L213" s="50"/>
-      <c r="M213" s="50"/>
-      <c r="N213" s="50"/>
-      <c r="O213" s="50"/>
-      <c r="P213" s="50"/>
-      <c r="Q213" s="50"/>
-      <c r="R213" s="50"/>
-      <c r="S213" s="50"/>
-      <c r="T213" s="50"/>
-      <c r="U213" s="50"/>
-      <c r="V213" s="50"/>
-      <c r="W213" s="50"/>
-      <c r="X213" s="50"/>
-      <c r="Y213" s="50"/>
-      <c r="Z213" s="50"/>
-      <c r="AA213" s="50"/>
-      <c r="AB213" s="51"/>
+      <c r="H213" s="51"/>
+      <c r="I213" s="52"/>
+      <c r="J213" s="52"/>
+      <c r="K213" s="52"/>
+      <c r="L213" s="52"/>
+      <c r="M213" s="52"/>
+      <c r="N213" s="52"/>
+      <c r="O213" s="52"/>
+      <c r="P213" s="52"/>
+      <c r="Q213" s="52"/>
+      <c r="R213" s="52"/>
+      <c r="S213" s="52"/>
+      <c r="T213" s="52"/>
+      <c r="U213" s="52"/>
+      <c r="V213" s="52"/>
+      <c r="W213" s="52"/>
+      <c r="X213" s="52"/>
+      <c r="Y213" s="52"/>
+      <c r="Z213" s="52"/>
+      <c r="AA213" s="52"/>
+      <c r="AB213" s="53"/>
       <c r="AC213" s="11"/>
     </row>
     <row r="214" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8302,27 +8340,27 @@
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
       <c r="G214" s="6"/>
-      <c r="H214" s="49"/>
-      <c r="I214" s="50"/>
-      <c r="J214" s="50"/>
-      <c r="K214" s="50"/>
-      <c r="L214" s="50"/>
-      <c r="M214" s="50"/>
-      <c r="N214" s="50"/>
-      <c r="O214" s="50"/>
-      <c r="P214" s="50"/>
-      <c r="Q214" s="50"/>
-      <c r="R214" s="50"/>
-      <c r="S214" s="50"/>
-      <c r="T214" s="50"/>
-      <c r="U214" s="50"/>
-      <c r="V214" s="50"/>
-      <c r="W214" s="50"/>
-      <c r="X214" s="50"/>
-      <c r="Y214" s="50"/>
-      <c r="Z214" s="50"/>
-      <c r="AA214" s="50"/>
-      <c r="AB214" s="51"/>
+      <c r="H214" s="51"/>
+      <c r="I214" s="52"/>
+      <c r="J214" s="52"/>
+      <c r="K214" s="52"/>
+      <c r="L214" s="52"/>
+      <c r="M214" s="52"/>
+      <c r="N214" s="52"/>
+      <c r="O214" s="52"/>
+      <c r="P214" s="52"/>
+      <c r="Q214" s="52"/>
+      <c r="R214" s="52"/>
+      <c r="S214" s="52"/>
+      <c r="T214" s="52"/>
+      <c r="U214" s="52"/>
+      <c r="V214" s="52"/>
+      <c r="W214" s="52"/>
+      <c r="X214" s="52"/>
+      <c r="Y214" s="52"/>
+      <c r="Z214" s="52"/>
+      <c r="AA214" s="52"/>
+      <c r="AB214" s="53"/>
       <c r="AC214" s="11"/>
     </row>
     <row r="215" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8332,27 +8370,27 @@
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
       <c r="G215" s="6"/>
-      <c r="H215" s="52"/>
-      <c r="I215" s="53"/>
-      <c r="J215" s="53"/>
-      <c r="K215" s="53"/>
-      <c r="L215" s="53"/>
-      <c r="M215" s="53"/>
-      <c r="N215" s="53"/>
-      <c r="O215" s="53"/>
-      <c r="P215" s="53"/>
-      <c r="Q215" s="53"/>
-      <c r="R215" s="53"/>
-      <c r="S215" s="53"/>
-      <c r="T215" s="53"/>
-      <c r="U215" s="53"/>
-      <c r="V215" s="53"/>
-      <c r="W215" s="53"/>
-      <c r="X215" s="53"/>
-      <c r="Y215" s="53"/>
-      <c r="Z215" s="53"/>
-      <c r="AA215" s="53"/>
-      <c r="AB215" s="54"/>
+      <c r="H215" s="54"/>
+      <c r="I215" s="55"/>
+      <c r="J215" s="55"/>
+      <c r="K215" s="55"/>
+      <c r="L215" s="55"/>
+      <c r="M215" s="55"/>
+      <c r="N215" s="55"/>
+      <c r="O215" s="55"/>
+      <c r="P215" s="55"/>
+      <c r="Q215" s="55"/>
+      <c r="R215" s="55"/>
+      <c r="S215" s="55"/>
+      <c r="T215" s="55"/>
+      <c r="U215" s="55"/>
+      <c r="V215" s="55"/>
+      <c r="W215" s="55"/>
+      <c r="X215" s="55"/>
+      <c r="Y215" s="55"/>
+      <c r="Z215" s="55"/>
+      <c r="AA215" s="55"/>
+      <c r="AB215" s="56"/>
       <c r="AC215" s="11"/>
     </row>
     <row r="216" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8387,11 +8425,38 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B180:B197"/>
+    <mergeCell ref="D182:E182"/>
+    <mergeCell ref="H182:AB188"/>
+    <mergeCell ref="H190:AB196"/>
+    <mergeCell ref="B199:B216"/>
+    <mergeCell ref="D201:E201"/>
+    <mergeCell ref="H201:AB207"/>
+    <mergeCell ref="H209:AB215"/>
+    <mergeCell ref="B142:B159"/>
+    <mergeCell ref="D144:E144"/>
+    <mergeCell ref="H144:AB150"/>
+    <mergeCell ref="H152:AB158"/>
+    <mergeCell ref="B161:B178"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="H163:AB169"/>
+    <mergeCell ref="H171:AB177"/>
+    <mergeCell ref="B104:B121"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="H106:AB112"/>
+    <mergeCell ref="H114:AB120"/>
+    <mergeCell ref="B123:B140"/>
+    <mergeCell ref="D125:E125"/>
+    <mergeCell ref="H125:AB131"/>
+    <mergeCell ref="H133:AB139"/>
+    <mergeCell ref="B63:B83"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="H76:AB82"/>
+    <mergeCell ref="B85:B102"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="H87:AB93"/>
+    <mergeCell ref="H95:AB101"/>
+    <mergeCell ref="H65:AB74"/>
     <mergeCell ref="B25:B42"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="H27:AB33"/>
@@ -8400,44 +8465,19 @@
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="H46:AB52"/>
     <mergeCell ref="H54:AB60"/>
-    <mergeCell ref="B63:B83"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="H76:AB82"/>
-    <mergeCell ref="B85:B102"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="H87:AB93"/>
-    <mergeCell ref="H95:AB101"/>
-    <mergeCell ref="H65:AB74"/>
-    <mergeCell ref="B104:B121"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="H106:AB112"/>
-    <mergeCell ref="H114:AB120"/>
-    <mergeCell ref="B123:B140"/>
-    <mergeCell ref="D125:E125"/>
-    <mergeCell ref="H125:AB131"/>
-    <mergeCell ref="H133:AB139"/>
-    <mergeCell ref="B142:B159"/>
-    <mergeCell ref="D144:E144"/>
-    <mergeCell ref="H144:AB150"/>
-    <mergeCell ref="H152:AB158"/>
-    <mergeCell ref="B161:B178"/>
-    <mergeCell ref="D163:E163"/>
-    <mergeCell ref="H163:AB169"/>
-    <mergeCell ref="H171:AB177"/>
-    <mergeCell ref="B180:B197"/>
-    <mergeCell ref="D182:E182"/>
-    <mergeCell ref="H182:AB188"/>
-    <mergeCell ref="H190:AB196"/>
-    <mergeCell ref="B199:B216"/>
-    <mergeCell ref="D201:E201"/>
-    <mergeCell ref="H201:AB207"/>
-    <mergeCell ref="H209:AB215"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H65" r:id="rId1" display="https://learn.microsoft.com/en-us/dotnet/maui/platform-integration/device/geolocation" xr:uid="{6A2F2CBC-218B-43EA-806A-9BF39365BDB2}"/>
     <hyperlink ref="H87" r:id="rId2" display="https://dummyjson.com/docs/posts_x000a_" xr:uid="{AFA4F006-3754-4C92-A758-50B6915FC379}"/>
     <hyperlink ref="H106" r:id="rId3" display="https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/refreshview_x000a_" xr:uid="{80E066CC-CE62-4304-89CB-2C900A3EBBE5}"/>
     <hyperlink ref="H125" r:id="rId4" display="https://learn.microsoft.com/de-de/dotnet/communitytoolkit/maui/views/mediaelement" xr:uid="{A9CAE96C-CEA9-42B5-BE11-A814029EF10A}"/>
+    <hyperlink ref="H144" r:id="rId5" display="https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/image_x000a_" xr:uid="{78B087E0-3533-42B3-9793-DB52FF358744}"/>
+    <hyperlink ref="H163" r:id="rId6" display="https://learn.microsoft.com/en-us/answers/questions/1024872/how-to-save-image-in-while-image-is-taken-from-cam_x000a_" xr:uid="{81FCBD1E-C0B4-4911-AA37-73831C593508}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -8464,11 +8504,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>21</v>
       </c>
@@ -9310,27 +9350,27 @@
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" s="19"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="47"/>
-      <c r="U34" s="47"/>
-      <c r="V34" s="47"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="47"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="47"/>
-      <c r="AA34" s="47"/>
-      <c r="AB34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="49"/>
+      <c r="L34" s="49"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="49"/>
+      <c r="P34" s="49"/>
+      <c r="Q34" s="49"/>
+      <c r="R34" s="49"/>
+      <c r="S34" s="49"/>
+      <c r="T34" s="49"/>
+      <c r="U34" s="49"/>
+      <c r="V34" s="49"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="49"/>
+      <c r="Y34" s="49"/>
+      <c r="Z34" s="49"/>
+      <c r="AA34" s="49"/>
+      <c r="AB34" s="50"/>
       <c r="AC34" s="16"/>
     </row>
     <row r="35" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9340,27 +9380,27 @@
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50"/>
-      <c r="S35" s="50"/>
-      <c r="T35" s="50"/>
-      <c r="U35" s="50"/>
-      <c r="V35" s="50"/>
-      <c r="W35" s="50"/>
-      <c r="X35" s="50"/>
-      <c r="Y35" s="50"/>
-      <c r="Z35" s="50"/>
-      <c r="AA35" s="50"/>
-      <c r="AB35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="52"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="52"/>
+      <c r="X35" s="52"/>
+      <c r="Y35" s="52"/>
+      <c r="Z35" s="52"/>
+      <c r="AA35" s="52"/>
+      <c r="AB35" s="53"/>
       <c r="AC35" s="16"/>
     </row>
     <row r="36" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9370,27 +9410,27 @@
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="50"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
-      <c r="Y36" s="50"/>
-      <c r="Z36" s="50"/>
-      <c r="AA36" s="50"/>
-      <c r="AB36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="52"/>
+      <c r="Q36" s="52"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="52"/>
+      <c r="T36" s="52"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="52"/>
+      <c r="W36" s="52"/>
+      <c r="X36" s="52"/>
+      <c r="Y36" s="52"/>
+      <c r="Z36" s="52"/>
+      <c r="AA36" s="52"/>
+      <c r="AB36" s="53"/>
       <c r="AC36" s="16"/>
     </row>
     <row r="37" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9400,27 +9440,27 @@
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="50"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+      <c r="O37" s="52"/>
+      <c r="P37" s="52"/>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="52"/>
+      <c r="T37" s="52"/>
+      <c r="U37" s="52"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="52"/>
+      <c r="X37" s="52"/>
+      <c r="Y37" s="52"/>
+      <c r="Z37" s="52"/>
+      <c r="AA37" s="52"/>
+      <c r="AB37" s="53"/>
       <c r="AC37" s="16"/>
     </row>
     <row r="38" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9430,27 +9470,27 @@
       <c r="E38" s="19"/>
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50"/>
-      <c r="S38" s="50"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="50"/>
-      <c r="Y38" s="50"/>
-      <c r="Z38" s="50"/>
-      <c r="AA38" s="50"/>
-      <c r="AB38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="52"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="52"/>
+      <c r="X38" s="52"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="52"/>
+      <c r="AA38" s="52"/>
+      <c r="AB38" s="53"/>
       <c r="AC38" s="16"/>
     </row>
     <row r="39" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9460,27 +9500,27 @@
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50"/>
-      <c r="Y39" s="50"/>
-      <c r="Z39" s="50"/>
-      <c r="AA39" s="50"/>
-      <c r="AB39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="52"/>
+      <c r="P39" s="52"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="52"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="52"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="52"/>
+      <c r="X39" s="52"/>
+      <c r="Y39" s="52"/>
+      <c r="Z39" s="52"/>
+      <c r="AA39" s="52"/>
+      <c r="AB39" s="53"/>
       <c r="AC39" s="16"/>
     </row>
     <row r="40" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9490,27 +9530,27 @@
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="53"/>
-      <c r="N40" s="53"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="53"/>
-      <c r="Q40" s="53"/>
-      <c r="R40" s="53"/>
-      <c r="S40" s="53"/>
-      <c r="T40" s="53"/>
-      <c r="U40" s="53"/>
-      <c r="V40" s="53"/>
-      <c r="W40" s="53"/>
-      <c r="X40" s="53"/>
-      <c r="Y40" s="53"/>
-      <c r="Z40" s="53"/>
-      <c r="AA40" s="53"/>
-      <c r="AB40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="55"/>
+      <c r="R40" s="55"/>
+      <c r="S40" s="55"/>
+      <c r="T40" s="55"/>
+      <c r="U40" s="55"/>
+      <c r="V40" s="55"/>
+      <c r="W40" s="55"/>
+      <c r="X40" s="55"/>
+      <c r="Y40" s="55"/>
+      <c r="Z40" s="55"/>
+      <c r="AA40" s="55"/>
+      <c r="AB40" s="56"/>
       <c r="AC40" s="16"/>
     </row>
     <row r="41" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9552,27 +9592,27 @@
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
       <c r="G42" s="19"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="47"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47"/>
-      <c r="S42" s="47"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="47"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="47"/>
-      <c r="X42" s="47"/>
-      <c r="Y42" s="47"/>
-      <c r="Z42" s="47"/>
-      <c r="AA42" s="47"/>
-      <c r="AB42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="49"/>
+      <c r="O42" s="49"/>
+      <c r="P42" s="49"/>
+      <c r="Q42" s="49"/>
+      <c r="R42" s="49"/>
+      <c r="S42" s="49"/>
+      <c r="T42" s="49"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="49"/>
+      <c r="W42" s="49"/>
+      <c r="X42" s="49"/>
+      <c r="Y42" s="49"/>
+      <c r="Z42" s="49"/>
+      <c r="AA42" s="49"/>
+      <c r="AB42" s="50"/>
       <c r="AC42" s="16"/>
     </row>
     <row r="43" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9582,27 +9622,27 @@
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="50"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="50"/>
-      <c r="AA43" s="50"/>
-      <c r="AB43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="52"/>
+      <c r="L43" s="52"/>
+      <c r="M43" s="52"/>
+      <c r="N43" s="52"/>
+      <c r="O43" s="52"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="52"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="52"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="52"/>
+      <c r="W43" s="52"/>
+      <c r="X43" s="52"/>
+      <c r="Y43" s="52"/>
+      <c r="Z43" s="52"/>
+      <c r="AA43" s="52"/>
+      <c r="AB43" s="53"/>
       <c r="AC43" s="16"/>
     </row>
     <row r="44" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9612,27 +9652,27 @@
       <c r="E44" s="19"/>
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="50"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50"/>
-      <c r="S44" s="50"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
-      <c r="V44" s="50"/>
-      <c r="W44" s="50"/>
-      <c r="X44" s="50"/>
-      <c r="Y44" s="50"/>
-      <c r="Z44" s="50"/>
-      <c r="AA44" s="50"/>
-      <c r="AB44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="52"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="52"/>
+      <c r="O44" s="52"/>
+      <c r="P44" s="52"/>
+      <c r="Q44" s="52"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="52"/>
+      <c r="T44" s="52"/>
+      <c r="U44" s="52"/>
+      <c r="V44" s="52"/>
+      <c r="W44" s="52"/>
+      <c r="X44" s="52"/>
+      <c r="Y44" s="52"/>
+      <c r="Z44" s="52"/>
+      <c r="AA44" s="52"/>
+      <c r="AB44" s="53"/>
       <c r="AC44" s="16"/>
     </row>
     <row r="45" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9642,27 +9682,27 @@
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="50"/>
-      <c r="O45" s="50"/>
-      <c r="P45" s="50"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50"/>
-      <c r="S45" s="50"/>
-      <c r="T45" s="50"/>
-      <c r="U45" s="50"/>
-      <c r="V45" s="50"/>
-      <c r="W45" s="50"/>
-      <c r="X45" s="50"/>
-      <c r="Y45" s="50"/>
-      <c r="Z45" s="50"/>
-      <c r="AA45" s="50"/>
-      <c r="AB45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="52"/>
+      <c r="O45" s="52"/>
+      <c r="P45" s="52"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="52"/>
+      <c r="V45" s="52"/>
+      <c r="W45" s="52"/>
+      <c r="X45" s="52"/>
+      <c r="Y45" s="52"/>
+      <c r="Z45" s="52"/>
+      <c r="AA45" s="52"/>
+      <c r="AB45" s="53"/>
       <c r="AC45" s="16"/>
     </row>
     <row r="46" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9672,27 +9712,27 @@
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="50"/>
-      <c r="J46" s="50"/>
-      <c r="K46" s="50"/>
-      <c r="L46" s="50"/>
-      <c r="M46" s="50"/>
-      <c r="N46" s="50"/>
-      <c r="O46" s="50"/>
-      <c r="P46" s="50"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50"/>
-      <c r="S46" s="50"/>
-      <c r="T46" s="50"/>
-      <c r="U46" s="50"/>
-      <c r="V46" s="50"/>
-      <c r="W46" s="50"/>
-      <c r="X46" s="50"/>
-      <c r="Y46" s="50"/>
-      <c r="Z46" s="50"/>
-      <c r="AA46" s="50"/>
-      <c r="AB46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="52"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="52"/>
+      <c r="O46" s="52"/>
+      <c r="P46" s="52"/>
+      <c r="Q46" s="52"/>
+      <c r="R46" s="52"/>
+      <c r="S46" s="52"/>
+      <c r="T46" s="52"/>
+      <c r="U46" s="52"/>
+      <c r="V46" s="52"/>
+      <c r="W46" s="52"/>
+      <c r="X46" s="52"/>
+      <c r="Y46" s="52"/>
+      <c r="Z46" s="52"/>
+      <c r="AA46" s="52"/>
+      <c r="AB46" s="53"/>
       <c r="AC46" s="16"/>
     </row>
     <row r="47" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9702,27 +9742,27 @@
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
       <c r="G47" s="19"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="50"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="50"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50"/>
-      <c r="S47" s="50"/>
-      <c r="T47" s="50"/>
-      <c r="U47" s="50"/>
-      <c r="V47" s="50"/>
-      <c r="W47" s="50"/>
-      <c r="X47" s="50"/>
-      <c r="Y47" s="50"/>
-      <c r="Z47" s="50"/>
-      <c r="AA47" s="50"/>
-      <c r="AB47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="52"/>
+      <c r="M47" s="52"/>
+      <c r="N47" s="52"/>
+      <c r="O47" s="52"/>
+      <c r="P47" s="52"/>
+      <c r="Q47" s="52"/>
+      <c r="R47" s="52"/>
+      <c r="S47" s="52"/>
+      <c r="T47" s="52"/>
+      <c r="U47" s="52"/>
+      <c r="V47" s="52"/>
+      <c r="W47" s="52"/>
+      <c r="X47" s="52"/>
+      <c r="Y47" s="52"/>
+      <c r="Z47" s="52"/>
+      <c r="AA47" s="52"/>
+      <c r="AB47" s="53"/>
       <c r="AC47" s="16"/>
     </row>
     <row r="48" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9732,27 +9772,27 @@
       <c r="E48" s="19"/>
       <c r="F48" s="19"/>
       <c r="G48" s="19"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="53"/>
-      <c r="T48" s="53"/>
-      <c r="U48" s="53"/>
-      <c r="V48" s="53"/>
-      <c r="W48" s="53"/>
-      <c r="X48" s="53"/>
-      <c r="Y48" s="53"/>
-      <c r="Z48" s="53"/>
-      <c r="AA48" s="53"/>
-      <c r="AB48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="55"/>
+      <c r="K48" s="55"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
+      <c r="O48" s="55"/>
+      <c r="P48" s="55"/>
+      <c r="Q48" s="55"/>
+      <c r="R48" s="55"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="55"/>
+      <c r="U48" s="55"/>
+      <c r="V48" s="55"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="55"/>
+      <c r="Y48" s="55"/>
+      <c r="Z48" s="55"/>
+      <c r="AA48" s="55"/>
+      <c r="AB48" s="56"/>
       <c r="AC48" s="16"/>
     </row>
     <row r="49" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9825,11 +9865,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
@@ -10634,11 +10674,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>33</v>
       </c>
@@ -11776,11 +11816,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>34</v>
       </c>
@@ -14527,11 +14567,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B66:B83"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="H68:AB74"/>
+    <mergeCell ref="H76:AB82"/>
+    <mergeCell ref="B86:B103"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="H88:AB94"/>
+    <mergeCell ref="H96:AB102"/>
     <mergeCell ref="B26:B43"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="H28:AB34"/>
@@ -14540,14 +14583,11 @@
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="H48:AB54"/>
     <mergeCell ref="H56:AB62"/>
-    <mergeCell ref="B66:B83"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="H68:AB74"/>
-    <mergeCell ref="H76:AB82"/>
-    <mergeCell ref="B86:B103"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="H88:AB94"/>
-    <mergeCell ref="H96:AB102"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -14574,11 +14614,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>41</v>
       </c>

--- a/Projekttagebuch.xlsx
+++ b/Projekttagebuch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\projects\GW.Demo.Maui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0491AB7-D99A-405E-A582-7143CEB6DE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDA11E4-8C80-4135-B3C9-77B358251254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
   </bookViews>
   <sheets>
     <sheet name="4.2.1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="53">
   <si>
     <t>Framework:</t>
   </si>
@@ -198,6 +198,22 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/shows/building-apps-with-xaml-and-dotnet-maui/navigate-between-screens-building-apps-with-xaml-and-dotnet-maui
+https://learn.microsoft.com/en-us/dotnet/maui/user-interface/controls/carouselview/?view=net-maui-9.0&amp;viewFallbackFrom=net-maui-8.0
+https://learn.microsoft.com/de-de/dotnet/maui/user-interface/controls/swipeview?view=net-maui-9.0
+ChatGPT, Copilot: "Ich möchte 5 Screens definieren, zwischen denen durch Swipen gewechselt werden kann."
+https://learn.microsoft.com/en-us/dotnet/maui/android/deployment/</t>
+  </si>
+  <si>
+    <t>Viel Herumgezicke mit NS. Besonders Compilieren dauert teilweise echt lang. Paketieren ist auch nicht auf Anhieb intuitiv.</t>
+  </si>
+  <si>
+    <t>.NET MAUI</t>
+  </si>
+  <si>
+    <t>114</t>
   </si>
 </sst>
 </file>
@@ -529,6 +545,12 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -555,12 +577,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -935,7 +951,9 @@
       </c>
     </row>
     <row r="3" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="26"/>
+      <c r="B3" s="26" t="s">
+        <v>51</v>
+      </c>
       <c r="C3" s="27"/>
       <c r="D3" s="27"/>
       <c r="E3" s="27"/>
@@ -2086,15 +2104,15 @@
       </c>
     </row>
     <row r="3" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="26">
+      <c r="B3" s="26" t="str">
         <f xml:space="preserve"> '4.2.1'!B3</f>
-        <v>0</v>
+        <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>11</v>
       </c>
@@ -2168,33 +2186,37 @@
     <row r="8" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="44"/>
       <c r="C8" s="5"/>
-      <c r="D8" s="41"/>
+      <c r="D8" s="41" t="s">
+        <v>52</v>
+      </c>
       <c r="E8" s="42"/>
       <c r="F8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
-      <c r="U8" s="47"/>
-      <c r="V8" s="47"/>
-      <c r="W8" s="47"/>
-      <c r="X8" s="47"/>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
-      <c r="AA8" s="47"/>
-      <c r="AB8" s="48"/>
+      <c r="H8" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="34"/>
       <c r="AC8" s="11"/>
     </row>
     <row r="9" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2204,27 +2226,27 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
-      <c r="V9" s="50"/>
-      <c r="W9" s="50"/>
-      <c r="X9" s="50"/>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="50"/>
-      <c r="AA9" s="50"/>
-      <c r="AB9" s="51"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="36"/>
+      <c r="AB9" s="37"/>
       <c r="AC9" s="11"/>
     </row>
     <row r="10" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2234,27 +2256,27 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
-      <c r="U10" s="50"/>
-      <c r="V10" s="50"/>
-      <c r="W10" s="50"/>
-      <c r="X10" s="50"/>
-      <c r="Y10" s="50"/>
-      <c r="Z10" s="50"/>
-      <c r="AA10" s="50"/>
-      <c r="AB10" s="51"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="36"/>
+      <c r="AB10" s="37"/>
       <c r="AC10" s="11"/>
     </row>
     <row r="11" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2264,27 +2286,27 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
-      <c r="P11" s="50"/>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="50"/>
-      <c r="S11" s="50"/>
-      <c r="T11" s="50"/>
-      <c r="U11" s="50"/>
-      <c r="V11" s="50"/>
-      <c r="W11" s="50"/>
-      <c r="X11" s="50"/>
-      <c r="Y11" s="50"/>
-      <c r="Z11" s="50"/>
-      <c r="AA11" s="50"/>
-      <c r="AB11" s="51"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="36"/>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="36"/>
+      <c r="AB11" s="37"/>
       <c r="AC11" s="11"/>
     </row>
     <row r="12" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2294,27 +2316,27 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="50"/>
-      <c r="AA12" s="50"/>
-      <c r="AB12" s="51"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
+      <c r="AB12" s="37"/>
       <c r="AC12" s="11"/>
     </row>
     <row r="13" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2324,27 +2346,27 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="50"/>
-      <c r="AA13" s="50"/>
-      <c r="AB13" s="51"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="37"/>
       <c r="AC13" s="11"/>
     </row>
     <row r="14" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2354,27 +2376,27 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="53"/>
-      <c r="W14" s="53"/>
-      <c r="X14" s="53"/>
-      <c r="Y14" s="53"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="53"/>
-      <c r="AB14" s="54"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="39"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="39"/>
+      <c r="AA14" s="39"/>
+      <c r="AB14" s="40"/>
       <c r="AC14" s="11"/>
     </row>
     <row r="15" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2416,27 +2438,29 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="47"/>
-      <c r="V16" s="47"/>
-      <c r="W16" s="47"/>
-      <c r="X16" s="47"/>
-      <c r="Y16" s="47"/>
-      <c r="Z16" s="47"/>
-      <c r="AA16" s="47"/>
-      <c r="AB16" s="48"/>
+      <c r="H16" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="33"/>
+      <c r="AB16" s="34"/>
       <c r="AC16" s="11"/>
     </row>
     <row r="17" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2446,27 +2470,27 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
-      <c r="P17" s="50"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50"/>
-      <c r="S17" s="50"/>
-      <c r="T17" s="50"/>
-      <c r="U17" s="50"/>
-      <c r="V17" s="50"/>
-      <c r="W17" s="50"/>
-      <c r="X17" s="50"/>
-      <c r="Y17" s="50"/>
-      <c r="Z17" s="50"/>
-      <c r="AA17" s="50"/>
-      <c r="AB17" s="51"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="36"/>
+      <c r="V17" s="36"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="36"/>
+      <c r="Y17" s="36"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="36"/>
+      <c r="AB17" s="37"/>
       <c r="AC17" s="11"/>
     </row>
     <row r="18" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2476,27 +2500,27 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="50"/>
-      <c r="T18" s="50"/>
-      <c r="U18" s="50"/>
-      <c r="V18" s="50"/>
-      <c r="W18" s="50"/>
-      <c r="X18" s="50"/>
-      <c r="Y18" s="50"/>
-      <c r="Z18" s="50"/>
-      <c r="AA18" s="50"/>
-      <c r="AB18" s="51"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="36"/>
+      <c r="Y18" s="36"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="36"/>
+      <c r="AB18" s="37"/>
       <c r="AC18" s="11"/>
     </row>
     <row r="19" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2506,27 +2530,27 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="50"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="50"/>
-      <c r="Y19" s="50"/>
-      <c r="Z19" s="50"/>
-      <c r="AA19" s="50"/>
-      <c r="AB19" s="51"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="36"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="36"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="36"/>
+      <c r="AB19" s="37"/>
       <c r="AC19" s="11"/>
     </row>
     <row r="20" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2536,27 +2560,27 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="50"/>
-      <c r="T20" s="50"/>
-      <c r="U20" s="50"/>
-      <c r="V20" s="50"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="50"/>
-      <c r="Y20" s="50"/>
-      <c r="Z20" s="50"/>
-      <c r="AA20" s="50"/>
-      <c r="AB20" s="51"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="36"/>
+      <c r="Y20" s="36"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="36"/>
+      <c r="AB20" s="37"/>
       <c r="AC20" s="11"/>
     </row>
     <row r="21" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2566,27 +2590,27 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="50"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="50"/>
-      <c r="Y21" s="50"/>
-      <c r="Z21" s="50"/>
-      <c r="AA21" s="50"/>
-      <c r="AB21" s="51"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="36"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="36"/>
+      <c r="Y21" s="36"/>
+      <c r="Z21" s="36"/>
+      <c r="AA21" s="36"/>
+      <c r="AB21" s="37"/>
       <c r="AC21" s="11"/>
     </row>
     <row r="22" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2596,27 +2620,27 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="53"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="53"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="53"/>
-      <c r="V22" s="53"/>
-      <c r="W22" s="53"/>
-      <c r="X22" s="53"/>
-      <c r="Y22" s="53"/>
-      <c r="Z22" s="53"/>
-      <c r="AA22" s="53"/>
-      <c r="AB22" s="54"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39"/>
+      <c r="S22" s="39"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="39"/>
+      <c r="V22" s="39"/>
+      <c r="W22" s="39"/>
+      <c r="X22" s="39"/>
+      <c r="Y22" s="39"/>
+      <c r="Z22" s="39"/>
+      <c r="AA22" s="39"/>
+      <c r="AB22" s="40"/>
       <c r="AC22" s="11"/>
     </row>
     <row r="23" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2724,27 +2748,27 @@
         <v>2</v>
       </c>
       <c r="G27" s="6"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="49"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="49"/>
+      <c r="AB27" s="50"/>
       <c r="AC27" s="11"/>
     </row>
     <row r="28" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2754,27 +2778,27 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="50"/>
-      <c r="AA28" s="50"/>
-      <c r="AB28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="52"/>
+      <c r="O28" s="52"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="52"/>
+      <c r="R28" s="52"/>
+      <c r="S28" s="52"/>
+      <c r="T28" s="52"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="52"/>
+      <c r="W28" s="52"/>
+      <c r="X28" s="52"/>
+      <c r="Y28" s="52"/>
+      <c r="Z28" s="52"/>
+      <c r="AA28" s="52"/>
+      <c r="AB28" s="53"/>
       <c r="AC28" s="11"/>
     </row>
     <row r="29" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2784,27 +2808,27 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="50"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="50"/>
-      <c r="AA29" s="50"/>
-      <c r="AB29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="52"/>
+      <c r="O29" s="52"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="52"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="52"/>
+      <c r="T29" s="52"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="52"/>
+      <c r="W29" s="52"/>
+      <c r="X29" s="52"/>
+      <c r="Y29" s="52"/>
+      <c r="Z29" s="52"/>
+      <c r="AA29" s="52"/>
+      <c r="AB29" s="53"/>
       <c r="AC29" s="11"/>
     </row>
     <row r="30" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2814,27 +2838,27 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="50"/>
-      <c r="W30" s="50"/>
-      <c r="X30" s="50"/>
-      <c r="Y30" s="50"/>
-      <c r="Z30" s="50"/>
-      <c r="AA30" s="50"/>
-      <c r="AB30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="52"/>
+      <c r="O30" s="52"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="52"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="52"/>
+      <c r="T30" s="52"/>
+      <c r="U30" s="52"/>
+      <c r="V30" s="52"/>
+      <c r="W30" s="52"/>
+      <c r="X30" s="52"/>
+      <c r="Y30" s="52"/>
+      <c r="Z30" s="52"/>
+      <c r="AA30" s="52"/>
+      <c r="AB30" s="53"/>
       <c r="AC30" s="11"/>
     </row>
     <row r="31" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2844,27 +2868,27 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="50"/>
-      <c r="V31" s="50"/>
-      <c r="W31" s="50"/>
-      <c r="X31" s="50"/>
-      <c r="Y31" s="50"/>
-      <c r="Z31" s="50"/>
-      <c r="AA31" s="50"/>
-      <c r="AB31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="52"/>
+      <c r="R31" s="52"/>
+      <c r="S31" s="52"/>
+      <c r="T31" s="52"/>
+      <c r="U31" s="52"/>
+      <c r="V31" s="52"/>
+      <c r="W31" s="52"/>
+      <c r="X31" s="52"/>
+      <c r="Y31" s="52"/>
+      <c r="Z31" s="52"/>
+      <c r="AA31" s="52"/>
+      <c r="AB31" s="53"/>
       <c r="AC31" s="11"/>
     </row>
     <row r="32" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2874,27 +2898,27 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50"/>
-      <c r="S32" s="50"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="50"/>
-      <c r="V32" s="50"/>
-      <c r="W32" s="50"/>
-      <c r="X32" s="50"/>
-      <c r="Y32" s="50"/>
-      <c r="Z32" s="50"/>
-      <c r="AA32" s="50"/>
-      <c r="AB32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="52"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="52"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="52"/>
+      <c r="W32" s="52"/>
+      <c r="X32" s="52"/>
+      <c r="Y32" s="52"/>
+      <c r="Z32" s="52"/>
+      <c r="AA32" s="52"/>
+      <c r="AB32" s="53"/>
       <c r="AC32" s="11"/>
     </row>
     <row r="33" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2904,27 +2928,27 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="53"/>
-      <c r="W33" s="53"/>
-      <c r="X33" s="53"/>
-      <c r="Y33" s="53"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="53"/>
-      <c r="AB33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="55"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="55"/>
+      <c r="U33" s="55"/>
+      <c r="V33" s="55"/>
+      <c r="W33" s="55"/>
+      <c r="X33" s="55"/>
+      <c r="Y33" s="55"/>
+      <c r="Z33" s="55"/>
+      <c r="AA33" s="55"/>
+      <c r="AB33" s="56"/>
       <c r="AC33" s="11"/>
     </row>
     <row r="34" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2966,27 +2990,27 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="47"/>
-      <c r="V35" s="47"/>
-      <c r="W35" s="47"/>
-      <c r="X35" s="47"/>
-      <c r="Y35" s="47"/>
-      <c r="Z35" s="47"/>
-      <c r="AA35" s="47"/>
-      <c r="AB35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="49"/>
+      <c r="R35" s="49"/>
+      <c r="S35" s="49"/>
+      <c r="T35" s="49"/>
+      <c r="U35" s="49"/>
+      <c r="V35" s="49"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="49"/>
+      <c r="Y35" s="49"/>
+      <c r="Z35" s="49"/>
+      <c r="AA35" s="49"/>
+      <c r="AB35" s="50"/>
       <c r="AC35" s="11"/>
     </row>
     <row r="36" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2996,27 +3020,27 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="50"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
-      <c r="Y36" s="50"/>
-      <c r="Z36" s="50"/>
-      <c r="AA36" s="50"/>
-      <c r="AB36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="52"/>
+      <c r="Q36" s="52"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="52"/>
+      <c r="T36" s="52"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="52"/>
+      <c r="W36" s="52"/>
+      <c r="X36" s="52"/>
+      <c r="Y36" s="52"/>
+      <c r="Z36" s="52"/>
+      <c r="AA36" s="52"/>
+      <c r="AB36" s="53"/>
       <c r="AC36" s="11"/>
     </row>
     <row r="37" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3026,27 +3050,27 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="50"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+      <c r="O37" s="52"/>
+      <c r="P37" s="52"/>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="52"/>
+      <c r="T37" s="52"/>
+      <c r="U37" s="52"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="52"/>
+      <c r="X37" s="52"/>
+      <c r="Y37" s="52"/>
+      <c r="Z37" s="52"/>
+      <c r="AA37" s="52"/>
+      <c r="AB37" s="53"/>
       <c r="AC37" s="11"/>
     </row>
     <row r="38" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3056,27 +3080,27 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50"/>
-      <c r="S38" s="50"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="50"/>
-      <c r="Y38" s="50"/>
-      <c r="Z38" s="50"/>
-      <c r="AA38" s="50"/>
-      <c r="AB38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="52"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="52"/>
+      <c r="X38" s="52"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="52"/>
+      <c r="AA38" s="52"/>
+      <c r="AB38" s="53"/>
       <c r="AC38" s="11"/>
     </row>
     <row r="39" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3086,27 +3110,27 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50"/>
-      <c r="Y39" s="50"/>
-      <c r="Z39" s="50"/>
-      <c r="AA39" s="50"/>
-      <c r="AB39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="52"/>
+      <c r="P39" s="52"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="52"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="52"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="52"/>
+      <c r="X39" s="52"/>
+      <c r="Y39" s="52"/>
+      <c r="Z39" s="52"/>
+      <c r="AA39" s="52"/>
+      <c r="AB39" s="53"/>
       <c r="AC39" s="11"/>
     </row>
     <row r="40" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3116,27 +3140,27 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="50"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="50"/>
-      <c r="O40" s="50"/>
-      <c r="P40" s="50"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="50"/>
-      <c r="S40" s="50"/>
-      <c r="T40" s="50"/>
-      <c r="U40" s="50"/>
-      <c r="V40" s="50"/>
-      <c r="W40" s="50"/>
-      <c r="X40" s="50"/>
-      <c r="Y40" s="50"/>
-      <c r="Z40" s="50"/>
-      <c r="AA40" s="50"/>
-      <c r="AB40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="52"/>
+      <c r="N40" s="52"/>
+      <c r="O40" s="52"/>
+      <c r="P40" s="52"/>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="52"/>
+      <c r="T40" s="52"/>
+      <c r="U40" s="52"/>
+      <c r="V40" s="52"/>
+      <c r="W40" s="52"/>
+      <c r="X40" s="52"/>
+      <c r="Y40" s="52"/>
+      <c r="Z40" s="52"/>
+      <c r="AA40" s="52"/>
+      <c r="AB40" s="53"/>
       <c r="AC40" s="11"/>
     </row>
     <row r="41" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3146,27 +3170,27 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="53"/>
-      <c r="N41" s="53"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="53"/>
-      <c r="Q41" s="53"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="53"/>
-      <c r="T41" s="53"/>
-      <c r="U41" s="53"/>
-      <c r="V41" s="53"/>
-      <c r="W41" s="53"/>
-      <c r="X41" s="53"/>
-      <c r="Y41" s="53"/>
-      <c r="Z41" s="53"/>
-      <c r="AA41" s="53"/>
-      <c r="AB41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="55"/>
+      <c r="T41" s="55"/>
+      <c r="U41" s="55"/>
+      <c r="V41" s="55"/>
+      <c r="W41" s="55"/>
+      <c r="X41" s="55"/>
+      <c r="Y41" s="55"/>
+      <c r="Z41" s="55"/>
+      <c r="AA41" s="55"/>
+      <c r="AB41" s="56"/>
       <c r="AC41" s="11"/>
     </row>
     <row r="42" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3274,27 +3298,27 @@
         <v>2</v>
       </c>
       <c r="G46" s="6"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
-      <c r="L46" s="47"/>
-      <c r="M46" s="47"/>
-      <c r="N46" s="47"/>
-      <c r="O46" s="47"/>
-      <c r="P46" s="47"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="47"/>
-      <c r="V46" s="47"/>
-      <c r="W46" s="47"/>
-      <c r="X46" s="47"/>
-      <c r="Y46" s="47"/>
-      <c r="Z46" s="47"/>
-      <c r="AA46" s="47"/>
-      <c r="AB46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="49"/>
+      <c r="K46" s="49"/>
+      <c r="L46" s="49"/>
+      <c r="M46" s="49"/>
+      <c r="N46" s="49"/>
+      <c r="O46" s="49"/>
+      <c r="P46" s="49"/>
+      <c r="Q46" s="49"/>
+      <c r="R46" s="49"/>
+      <c r="S46" s="49"/>
+      <c r="T46" s="49"/>
+      <c r="U46" s="49"/>
+      <c r="V46" s="49"/>
+      <c r="W46" s="49"/>
+      <c r="X46" s="49"/>
+      <c r="Y46" s="49"/>
+      <c r="Z46" s="49"/>
+      <c r="AA46" s="49"/>
+      <c r="AB46" s="50"/>
       <c r="AC46" s="11"/>
     </row>
     <row r="47" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3304,27 +3328,27 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="50"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="50"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50"/>
-      <c r="S47" s="50"/>
-      <c r="T47" s="50"/>
-      <c r="U47" s="50"/>
-      <c r="V47" s="50"/>
-      <c r="W47" s="50"/>
-      <c r="X47" s="50"/>
-      <c r="Y47" s="50"/>
-      <c r="Z47" s="50"/>
-      <c r="AA47" s="50"/>
-      <c r="AB47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="52"/>
+      <c r="M47" s="52"/>
+      <c r="N47" s="52"/>
+      <c r="O47" s="52"/>
+      <c r="P47" s="52"/>
+      <c r="Q47" s="52"/>
+      <c r="R47" s="52"/>
+      <c r="S47" s="52"/>
+      <c r="T47" s="52"/>
+      <c r="U47" s="52"/>
+      <c r="V47" s="52"/>
+      <c r="W47" s="52"/>
+      <c r="X47" s="52"/>
+      <c r="Y47" s="52"/>
+      <c r="Z47" s="52"/>
+      <c r="AA47" s="52"/>
+      <c r="AB47" s="53"/>
       <c r="AC47" s="11"/>
     </row>
     <row r="48" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3334,27 +3358,27 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="50"/>
-      <c r="J48" s="50"/>
-      <c r="K48" s="50"/>
-      <c r="L48" s="50"/>
-      <c r="M48" s="50"/>
-      <c r="N48" s="50"/>
-      <c r="O48" s="50"/>
-      <c r="P48" s="50"/>
-      <c r="Q48" s="50"/>
-      <c r="R48" s="50"/>
-      <c r="S48" s="50"/>
-      <c r="T48" s="50"/>
-      <c r="U48" s="50"/>
-      <c r="V48" s="50"/>
-      <c r="W48" s="50"/>
-      <c r="X48" s="50"/>
-      <c r="Y48" s="50"/>
-      <c r="Z48" s="50"/>
-      <c r="AA48" s="50"/>
-      <c r="AB48" s="51"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
+      <c r="K48" s="52"/>
+      <c r="L48" s="52"/>
+      <c r="M48" s="52"/>
+      <c r="N48" s="52"/>
+      <c r="O48" s="52"/>
+      <c r="P48" s="52"/>
+      <c r="Q48" s="52"/>
+      <c r="R48" s="52"/>
+      <c r="S48" s="52"/>
+      <c r="T48" s="52"/>
+      <c r="U48" s="52"/>
+      <c r="V48" s="52"/>
+      <c r="W48" s="52"/>
+      <c r="X48" s="52"/>
+      <c r="Y48" s="52"/>
+      <c r="Z48" s="52"/>
+      <c r="AA48" s="52"/>
+      <c r="AB48" s="53"/>
       <c r="AC48" s="11"/>
     </row>
     <row r="49" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3364,27 +3388,27 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="50"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="50"/>
-      <c r="P49" s="50"/>
-      <c r="Q49" s="50"/>
-      <c r="R49" s="50"/>
-      <c r="S49" s="50"/>
-      <c r="T49" s="50"/>
-      <c r="U49" s="50"/>
-      <c r="V49" s="50"/>
-      <c r="W49" s="50"/>
-      <c r="X49" s="50"/>
-      <c r="Y49" s="50"/>
-      <c r="Z49" s="50"/>
-      <c r="AA49" s="50"/>
-      <c r="AB49" s="51"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="52"/>
+      <c r="L49" s="52"/>
+      <c r="M49" s="52"/>
+      <c r="N49" s="52"/>
+      <c r="O49" s="52"/>
+      <c r="P49" s="52"/>
+      <c r="Q49" s="52"/>
+      <c r="R49" s="52"/>
+      <c r="S49" s="52"/>
+      <c r="T49" s="52"/>
+      <c r="U49" s="52"/>
+      <c r="V49" s="52"/>
+      <c r="W49" s="52"/>
+      <c r="X49" s="52"/>
+      <c r="Y49" s="52"/>
+      <c r="Z49" s="52"/>
+      <c r="AA49" s="52"/>
+      <c r="AB49" s="53"/>
       <c r="AC49" s="11"/>
     </row>
     <row r="50" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3394,27 +3418,27 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="50"/>
-      <c r="K50" s="50"/>
-      <c r="L50" s="50"/>
-      <c r="M50" s="50"/>
-      <c r="N50" s="50"/>
-      <c r="O50" s="50"/>
-      <c r="P50" s="50"/>
-      <c r="Q50" s="50"/>
-      <c r="R50" s="50"/>
-      <c r="S50" s="50"/>
-      <c r="T50" s="50"/>
-      <c r="U50" s="50"/>
-      <c r="V50" s="50"/>
-      <c r="W50" s="50"/>
-      <c r="X50" s="50"/>
-      <c r="Y50" s="50"/>
-      <c r="Z50" s="50"/>
-      <c r="AA50" s="50"/>
-      <c r="AB50" s="51"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
+      <c r="K50" s="52"/>
+      <c r="L50" s="52"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="52"/>
+      <c r="O50" s="52"/>
+      <c r="P50" s="52"/>
+      <c r="Q50" s="52"/>
+      <c r="R50" s="52"/>
+      <c r="S50" s="52"/>
+      <c r="T50" s="52"/>
+      <c r="U50" s="52"/>
+      <c r="V50" s="52"/>
+      <c r="W50" s="52"/>
+      <c r="X50" s="52"/>
+      <c r="Y50" s="52"/>
+      <c r="Z50" s="52"/>
+      <c r="AA50" s="52"/>
+      <c r="AB50" s="53"/>
       <c r="AC50" s="11"/>
     </row>
     <row r="51" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3424,27 +3448,27 @@
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="50"/>
-      <c r="J51" s="50"/>
-      <c r="K51" s="50"/>
-      <c r="L51" s="50"/>
-      <c r="M51" s="50"/>
-      <c r="N51" s="50"/>
-      <c r="O51" s="50"/>
-      <c r="P51" s="50"/>
-      <c r="Q51" s="50"/>
-      <c r="R51" s="50"/>
-      <c r="S51" s="50"/>
-      <c r="T51" s="50"/>
-      <c r="U51" s="50"/>
-      <c r="V51" s="50"/>
-      <c r="W51" s="50"/>
-      <c r="X51" s="50"/>
-      <c r="Y51" s="50"/>
-      <c r="Z51" s="50"/>
-      <c r="AA51" s="50"/>
-      <c r="AB51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="52"/>
+      <c r="O51" s="52"/>
+      <c r="P51" s="52"/>
+      <c r="Q51" s="52"/>
+      <c r="R51" s="52"/>
+      <c r="S51" s="52"/>
+      <c r="T51" s="52"/>
+      <c r="U51" s="52"/>
+      <c r="V51" s="52"/>
+      <c r="W51" s="52"/>
+      <c r="X51" s="52"/>
+      <c r="Y51" s="52"/>
+      <c r="Z51" s="52"/>
+      <c r="AA51" s="52"/>
+      <c r="AB51" s="53"/>
       <c r="AC51" s="11"/>
     </row>
     <row r="52" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3454,27 +3478,27 @@
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="53"/>
-      <c r="J52" s="53"/>
-      <c r="K52" s="53"/>
-      <c r="L52" s="53"/>
-      <c r="M52" s="53"/>
-      <c r="N52" s="53"/>
-      <c r="O52" s="53"/>
-      <c r="P52" s="53"/>
-      <c r="Q52" s="53"/>
-      <c r="R52" s="53"/>
-      <c r="S52" s="53"/>
-      <c r="T52" s="53"/>
-      <c r="U52" s="53"/>
-      <c r="V52" s="53"/>
-      <c r="W52" s="53"/>
-      <c r="X52" s="53"/>
-      <c r="Y52" s="53"/>
-      <c r="Z52" s="53"/>
-      <c r="AA52" s="53"/>
-      <c r="AB52" s="54"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="55"/>
+      <c r="N52" s="55"/>
+      <c r="O52" s="55"/>
+      <c r="P52" s="55"/>
+      <c r="Q52" s="55"/>
+      <c r="R52" s="55"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="55"/>
+      <c r="U52" s="55"/>
+      <c r="V52" s="55"/>
+      <c r="W52" s="55"/>
+      <c r="X52" s="55"/>
+      <c r="Y52" s="55"/>
+      <c r="Z52" s="55"/>
+      <c r="AA52" s="55"/>
+      <c r="AB52" s="56"/>
       <c r="AC52" s="11"/>
     </row>
     <row r="53" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3516,27 +3540,27 @@
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="47"/>
-      <c r="J54" s="47"/>
-      <c r="K54" s="47"/>
-      <c r="L54" s="47"/>
-      <c r="M54" s="47"/>
-      <c r="N54" s="47"/>
-      <c r="O54" s="47"/>
-      <c r="P54" s="47"/>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47"/>
-      <c r="S54" s="47"/>
-      <c r="T54" s="47"/>
-      <c r="U54" s="47"/>
-      <c r="V54" s="47"/>
-      <c r="W54" s="47"/>
-      <c r="X54" s="47"/>
-      <c r="Y54" s="47"/>
-      <c r="Z54" s="47"/>
-      <c r="AA54" s="47"/>
-      <c r="AB54" s="48"/>
+      <c r="H54" s="48"/>
+      <c r="I54" s="49"/>
+      <c r="J54" s="49"/>
+      <c r="K54" s="49"/>
+      <c r="L54" s="49"/>
+      <c r="M54" s="49"/>
+      <c r="N54" s="49"/>
+      <c r="O54" s="49"/>
+      <c r="P54" s="49"/>
+      <c r="Q54" s="49"/>
+      <c r="R54" s="49"/>
+      <c r="S54" s="49"/>
+      <c r="T54" s="49"/>
+      <c r="U54" s="49"/>
+      <c r="V54" s="49"/>
+      <c r="W54" s="49"/>
+      <c r="X54" s="49"/>
+      <c r="Y54" s="49"/>
+      <c r="Z54" s="49"/>
+      <c r="AA54" s="49"/>
+      <c r="AB54" s="50"/>
       <c r="AC54" s="11"/>
     </row>
     <row r="55" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3546,27 +3570,27 @@
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="50"/>
-      <c r="J55" s="50"/>
-      <c r="K55" s="50"/>
-      <c r="L55" s="50"/>
-      <c r="M55" s="50"/>
-      <c r="N55" s="50"/>
-      <c r="O55" s="50"/>
-      <c r="P55" s="50"/>
-      <c r="Q55" s="50"/>
-      <c r="R55" s="50"/>
-      <c r="S55" s="50"/>
-      <c r="T55" s="50"/>
-      <c r="U55" s="50"/>
-      <c r="V55" s="50"/>
-      <c r="W55" s="50"/>
-      <c r="X55" s="50"/>
-      <c r="Y55" s="50"/>
-      <c r="Z55" s="50"/>
-      <c r="AA55" s="50"/>
-      <c r="AB55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="52"/>
+      <c r="J55" s="52"/>
+      <c r="K55" s="52"/>
+      <c r="L55" s="52"/>
+      <c r="M55" s="52"/>
+      <c r="N55" s="52"/>
+      <c r="O55" s="52"/>
+      <c r="P55" s="52"/>
+      <c r="Q55" s="52"/>
+      <c r="R55" s="52"/>
+      <c r="S55" s="52"/>
+      <c r="T55" s="52"/>
+      <c r="U55" s="52"/>
+      <c r="V55" s="52"/>
+      <c r="W55" s="52"/>
+      <c r="X55" s="52"/>
+      <c r="Y55" s="52"/>
+      <c r="Z55" s="52"/>
+      <c r="AA55" s="52"/>
+      <c r="AB55" s="53"/>
       <c r="AC55" s="11"/>
     </row>
     <row r="56" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3576,27 +3600,27 @@
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="50"/>
-      <c r="L56" s="50"/>
-      <c r="M56" s="50"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="50"/>
-      <c r="P56" s="50"/>
-      <c r="Q56" s="50"/>
-      <c r="R56" s="50"/>
-      <c r="S56" s="50"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="50"/>
-      <c r="V56" s="50"/>
-      <c r="W56" s="50"/>
-      <c r="X56" s="50"/>
-      <c r="Y56" s="50"/>
-      <c r="Z56" s="50"/>
-      <c r="AA56" s="50"/>
-      <c r="AB56" s="51"/>
+      <c r="H56" s="51"/>
+      <c r="I56" s="52"/>
+      <c r="J56" s="52"/>
+      <c r="K56" s="52"/>
+      <c r="L56" s="52"/>
+      <c r="M56" s="52"/>
+      <c r="N56" s="52"/>
+      <c r="O56" s="52"/>
+      <c r="P56" s="52"/>
+      <c r="Q56" s="52"/>
+      <c r="R56" s="52"/>
+      <c r="S56" s="52"/>
+      <c r="T56" s="52"/>
+      <c r="U56" s="52"/>
+      <c r="V56" s="52"/>
+      <c r="W56" s="52"/>
+      <c r="X56" s="52"/>
+      <c r="Y56" s="52"/>
+      <c r="Z56" s="52"/>
+      <c r="AA56" s="52"/>
+      <c r="AB56" s="53"/>
       <c r="AC56" s="11"/>
     </row>
     <row r="57" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3606,27 +3630,27 @@
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="50"/>
-      <c r="J57" s="50"/>
-      <c r="K57" s="50"/>
-      <c r="L57" s="50"/>
-      <c r="M57" s="50"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="50"/>
-      <c r="P57" s="50"/>
-      <c r="Q57" s="50"/>
-      <c r="R57" s="50"/>
-      <c r="S57" s="50"/>
-      <c r="T57" s="50"/>
-      <c r="U57" s="50"/>
-      <c r="V57" s="50"/>
-      <c r="W57" s="50"/>
-      <c r="X57" s="50"/>
-      <c r="Y57" s="50"/>
-      <c r="Z57" s="50"/>
-      <c r="AA57" s="50"/>
-      <c r="AB57" s="51"/>
+      <c r="H57" s="51"/>
+      <c r="I57" s="52"/>
+      <c r="J57" s="52"/>
+      <c r="K57" s="52"/>
+      <c r="L57" s="52"/>
+      <c r="M57" s="52"/>
+      <c r="N57" s="52"/>
+      <c r="O57" s="52"/>
+      <c r="P57" s="52"/>
+      <c r="Q57" s="52"/>
+      <c r="R57" s="52"/>
+      <c r="S57" s="52"/>
+      <c r="T57" s="52"/>
+      <c r="U57" s="52"/>
+      <c r="V57" s="52"/>
+      <c r="W57" s="52"/>
+      <c r="X57" s="52"/>
+      <c r="Y57" s="52"/>
+      <c r="Z57" s="52"/>
+      <c r="AA57" s="52"/>
+      <c r="AB57" s="53"/>
       <c r="AC57" s="11"/>
     </row>
     <row r="58" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3636,27 +3660,27 @@
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
-      <c r="K58" s="50"/>
-      <c r="L58" s="50"/>
-      <c r="M58" s="50"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="50"/>
-      <c r="P58" s="50"/>
-      <c r="Q58" s="50"/>
-      <c r="R58" s="50"/>
-      <c r="S58" s="50"/>
-      <c r="T58" s="50"/>
-      <c r="U58" s="50"/>
-      <c r="V58" s="50"/>
-      <c r="W58" s="50"/>
-      <c r="X58" s="50"/>
-      <c r="Y58" s="50"/>
-      <c r="Z58" s="50"/>
-      <c r="AA58" s="50"/>
-      <c r="AB58" s="51"/>
+      <c r="H58" s="51"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="52"/>
+      <c r="M58" s="52"/>
+      <c r="N58" s="52"/>
+      <c r="O58" s="52"/>
+      <c r="P58" s="52"/>
+      <c r="Q58" s="52"/>
+      <c r="R58" s="52"/>
+      <c r="S58" s="52"/>
+      <c r="T58" s="52"/>
+      <c r="U58" s="52"/>
+      <c r="V58" s="52"/>
+      <c r="W58" s="52"/>
+      <c r="X58" s="52"/>
+      <c r="Y58" s="52"/>
+      <c r="Z58" s="52"/>
+      <c r="AA58" s="52"/>
+      <c r="AB58" s="53"/>
       <c r="AC58" s="11"/>
     </row>
     <row r="59" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3666,27 +3690,27 @@
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="50"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="50"/>
-      <c r="M59" s="50"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="50"/>
-      <c r="Q59" s="50"/>
-      <c r="R59" s="50"/>
-      <c r="S59" s="50"/>
-      <c r="T59" s="50"/>
-      <c r="U59" s="50"/>
-      <c r="V59" s="50"/>
-      <c r="W59" s="50"/>
-      <c r="X59" s="50"/>
-      <c r="Y59" s="50"/>
-      <c r="Z59" s="50"/>
-      <c r="AA59" s="50"/>
-      <c r="AB59" s="51"/>
+      <c r="H59" s="51"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52"/>
+      <c r="P59" s="52"/>
+      <c r="Q59" s="52"/>
+      <c r="R59" s="52"/>
+      <c r="S59" s="52"/>
+      <c r="T59" s="52"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="52"/>
+      <c r="W59" s="52"/>
+      <c r="X59" s="52"/>
+      <c r="Y59" s="52"/>
+      <c r="Z59" s="52"/>
+      <c r="AA59" s="52"/>
+      <c r="AB59" s="53"/>
       <c r="AC59" s="11"/>
     </row>
     <row r="60" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3696,27 +3720,27 @@
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="53"/>
-      <c r="J60" s="53"/>
-      <c r="K60" s="53"/>
-      <c r="L60" s="53"/>
-      <c r="M60" s="53"/>
-      <c r="N60" s="53"/>
-      <c r="O60" s="53"/>
-      <c r="P60" s="53"/>
-      <c r="Q60" s="53"/>
-      <c r="R60" s="53"/>
-      <c r="S60" s="53"/>
-      <c r="T60" s="53"/>
-      <c r="U60" s="53"/>
-      <c r="V60" s="53"/>
-      <c r="W60" s="53"/>
-      <c r="X60" s="53"/>
-      <c r="Y60" s="53"/>
-      <c r="Z60" s="53"/>
-      <c r="AA60" s="53"/>
-      <c r="AB60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="55"/>
+      <c r="J60" s="55"/>
+      <c r="K60" s="55"/>
+      <c r="L60" s="55"/>
+      <c r="M60" s="55"/>
+      <c r="N60" s="55"/>
+      <c r="O60" s="55"/>
+      <c r="P60" s="55"/>
+      <c r="Q60" s="55"/>
+      <c r="R60" s="55"/>
+      <c r="S60" s="55"/>
+      <c r="T60" s="55"/>
+      <c r="U60" s="55"/>
+      <c r="V60" s="55"/>
+      <c r="W60" s="55"/>
+      <c r="X60" s="55"/>
+      <c r="Y60" s="55"/>
+      <c r="Z60" s="55"/>
+      <c r="AA60" s="55"/>
+      <c r="AB60" s="56"/>
       <c r="AC60" s="11"/>
     </row>
     <row r="61" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3824,27 +3848,27 @@
         <v>2</v>
       </c>
       <c r="G65" s="6"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="47"/>
-      <c r="J65" s="47"/>
-      <c r="K65" s="47"/>
-      <c r="L65" s="47"/>
-      <c r="M65" s="47"/>
-      <c r="N65" s="47"/>
-      <c r="O65" s="47"/>
-      <c r="P65" s="47"/>
-      <c r="Q65" s="47"/>
-      <c r="R65" s="47"/>
-      <c r="S65" s="47"/>
-      <c r="T65" s="47"/>
-      <c r="U65" s="47"/>
-      <c r="V65" s="47"/>
-      <c r="W65" s="47"/>
-      <c r="X65" s="47"/>
-      <c r="Y65" s="47"/>
-      <c r="Z65" s="47"/>
-      <c r="AA65" s="47"/>
-      <c r="AB65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="49"/>
+      <c r="J65" s="49"/>
+      <c r="K65" s="49"/>
+      <c r="L65" s="49"/>
+      <c r="M65" s="49"/>
+      <c r="N65" s="49"/>
+      <c r="O65" s="49"/>
+      <c r="P65" s="49"/>
+      <c r="Q65" s="49"/>
+      <c r="R65" s="49"/>
+      <c r="S65" s="49"/>
+      <c r="T65" s="49"/>
+      <c r="U65" s="49"/>
+      <c r="V65" s="49"/>
+      <c r="W65" s="49"/>
+      <c r="X65" s="49"/>
+      <c r="Y65" s="49"/>
+      <c r="Z65" s="49"/>
+      <c r="AA65" s="49"/>
+      <c r="AB65" s="50"/>
       <c r="AC65" s="11"/>
     </row>
     <row r="66" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3854,27 +3878,27 @@
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
-      <c r="H66" s="49"/>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="50"/>
-      <c r="M66" s="50"/>
-      <c r="N66" s="50"/>
-      <c r="O66" s="50"/>
-      <c r="P66" s="50"/>
-      <c r="Q66" s="50"/>
-      <c r="R66" s="50"/>
-      <c r="S66" s="50"/>
-      <c r="T66" s="50"/>
-      <c r="U66" s="50"/>
-      <c r="V66" s="50"/>
-      <c r="W66" s="50"/>
-      <c r="X66" s="50"/>
-      <c r="Y66" s="50"/>
-      <c r="Z66" s="50"/>
-      <c r="AA66" s="50"/>
-      <c r="AB66" s="51"/>
+      <c r="H66" s="51"/>
+      <c r="I66" s="52"/>
+      <c r="J66" s="52"/>
+      <c r="K66" s="52"/>
+      <c r="L66" s="52"/>
+      <c r="M66" s="52"/>
+      <c r="N66" s="52"/>
+      <c r="O66" s="52"/>
+      <c r="P66" s="52"/>
+      <c r="Q66" s="52"/>
+      <c r="R66" s="52"/>
+      <c r="S66" s="52"/>
+      <c r="T66" s="52"/>
+      <c r="U66" s="52"/>
+      <c r="V66" s="52"/>
+      <c r="W66" s="52"/>
+      <c r="X66" s="52"/>
+      <c r="Y66" s="52"/>
+      <c r="Z66" s="52"/>
+      <c r="AA66" s="52"/>
+      <c r="AB66" s="53"/>
       <c r="AC66" s="11"/>
     </row>
     <row r="67" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3884,27 +3908,27 @@
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
-      <c r="H67" s="49"/>
-      <c r="I67" s="50"/>
-      <c r="J67" s="50"/>
-      <c r="K67" s="50"/>
-      <c r="L67" s="50"/>
-      <c r="M67" s="50"/>
-      <c r="N67" s="50"/>
-      <c r="O67" s="50"/>
-      <c r="P67" s="50"/>
-      <c r="Q67" s="50"/>
-      <c r="R67" s="50"/>
-      <c r="S67" s="50"/>
-      <c r="T67" s="50"/>
-      <c r="U67" s="50"/>
-      <c r="V67" s="50"/>
-      <c r="W67" s="50"/>
-      <c r="X67" s="50"/>
-      <c r="Y67" s="50"/>
-      <c r="Z67" s="50"/>
-      <c r="AA67" s="50"/>
-      <c r="AB67" s="51"/>
+      <c r="H67" s="51"/>
+      <c r="I67" s="52"/>
+      <c r="J67" s="52"/>
+      <c r="K67" s="52"/>
+      <c r="L67" s="52"/>
+      <c r="M67" s="52"/>
+      <c r="N67" s="52"/>
+      <c r="O67" s="52"/>
+      <c r="P67" s="52"/>
+      <c r="Q67" s="52"/>
+      <c r="R67" s="52"/>
+      <c r="S67" s="52"/>
+      <c r="T67" s="52"/>
+      <c r="U67" s="52"/>
+      <c r="V67" s="52"/>
+      <c r="W67" s="52"/>
+      <c r="X67" s="52"/>
+      <c r="Y67" s="52"/>
+      <c r="Z67" s="52"/>
+      <c r="AA67" s="52"/>
+      <c r="AB67" s="53"/>
       <c r="AC67" s="11"/>
     </row>
     <row r="68" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3914,27 +3938,27 @@
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="50"/>
-      <c r="J68" s="50"/>
-      <c r="K68" s="50"/>
-      <c r="L68" s="50"/>
-      <c r="M68" s="50"/>
-      <c r="N68" s="50"/>
-      <c r="O68" s="50"/>
-      <c r="P68" s="50"/>
-      <c r="Q68" s="50"/>
-      <c r="R68" s="50"/>
-      <c r="S68" s="50"/>
-      <c r="T68" s="50"/>
-      <c r="U68" s="50"/>
-      <c r="V68" s="50"/>
-      <c r="W68" s="50"/>
-      <c r="X68" s="50"/>
-      <c r="Y68" s="50"/>
-      <c r="Z68" s="50"/>
-      <c r="AA68" s="50"/>
-      <c r="AB68" s="51"/>
+      <c r="H68" s="51"/>
+      <c r="I68" s="52"/>
+      <c r="J68" s="52"/>
+      <c r="K68" s="52"/>
+      <c r="L68" s="52"/>
+      <c r="M68" s="52"/>
+      <c r="N68" s="52"/>
+      <c r="O68" s="52"/>
+      <c r="P68" s="52"/>
+      <c r="Q68" s="52"/>
+      <c r="R68" s="52"/>
+      <c r="S68" s="52"/>
+      <c r="T68" s="52"/>
+      <c r="U68" s="52"/>
+      <c r="V68" s="52"/>
+      <c r="W68" s="52"/>
+      <c r="X68" s="52"/>
+      <c r="Y68" s="52"/>
+      <c r="Z68" s="52"/>
+      <c r="AA68" s="52"/>
+      <c r="AB68" s="53"/>
       <c r="AC68" s="11"/>
     </row>
     <row r="69" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3944,27 +3968,27 @@
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
-      <c r="H69" s="49"/>
-      <c r="I69" s="50"/>
-      <c r="J69" s="50"/>
-      <c r="K69" s="50"/>
-      <c r="L69" s="50"/>
-      <c r="M69" s="50"/>
-      <c r="N69" s="50"/>
-      <c r="O69" s="50"/>
-      <c r="P69" s="50"/>
-      <c r="Q69" s="50"/>
-      <c r="R69" s="50"/>
-      <c r="S69" s="50"/>
-      <c r="T69" s="50"/>
-      <c r="U69" s="50"/>
-      <c r="V69" s="50"/>
-      <c r="W69" s="50"/>
-      <c r="X69" s="50"/>
-      <c r="Y69" s="50"/>
-      <c r="Z69" s="50"/>
-      <c r="AA69" s="50"/>
-      <c r="AB69" s="51"/>
+      <c r="H69" s="51"/>
+      <c r="I69" s="52"/>
+      <c r="J69" s="52"/>
+      <c r="K69" s="52"/>
+      <c r="L69" s="52"/>
+      <c r="M69" s="52"/>
+      <c r="N69" s="52"/>
+      <c r="O69" s="52"/>
+      <c r="P69" s="52"/>
+      <c r="Q69" s="52"/>
+      <c r="R69" s="52"/>
+      <c r="S69" s="52"/>
+      <c r="T69" s="52"/>
+      <c r="U69" s="52"/>
+      <c r="V69" s="52"/>
+      <c r="W69" s="52"/>
+      <c r="X69" s="52"/>
+      <c r="Y69" s="52"/>
+      <c r="Z69" s="52"/>
+      <c r="AA69" s="52"/>
+      <c r="AB69" s="53"/>
       <c r="AC69" s="11"/>
     </row>
     <row r="70" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3974,27 +3998,27 @@
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="50"/>
-      <c r="J70" s="50"/>
-      <c r="K70" s="50"/>
-      <c r="L70" s="50"/>
-      <c r="M70" s="50"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="50"/>
-      <c r="P70" s="50"/>
-      <c r="Q70" s="50"/>
-      <c r="R70" s="50"/>
-      <c r="S70" s="50"/>
-      <c r="T70" s="50"/>
-      <c r="U70" s="50"/>
-      <c r="V70" s="50"/>
-      <c r="W70" s="50"/>
-      <c r="X70" s="50"/>
-      <c r="Y70" s="50"/>
-      <c r="Z70" s="50"/>
-      <c r="AA70" s="50"/>
-      <c r="AB70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="52"/>
+      <c r="J70" s="52"/>
+      <c r="K70" s="52"/>
+      <c r="L70" s="52"/>
+      <c r="M70" s="52"/>
+      <c r="N70" s="52"/>
+      <c r="O70" s="52"/>
+      <c r="P70" s="52"/>
+      <c r="Q70" s="52"/>
+      <c r="R70" s="52"/>
+      <c r="S70" s="52"/>
+      <c r="T70" s="52"/>
+      <c r="U70" s="52"/>
+      <c r="V70" s="52"/>
+      <c r="W70" s="52"/>
+      <c r="X70" s="52"/>
+      <c r="Y70" s="52"/>
+      <c r="Z70" s="52"/>
+      <c r="AA70" s="52"/>
+      <c r="AB70" s="53"/>
       <c r="AC70" s="11"/>
     </row>
     <row r="71" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4004,27 +4028,27 @@
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
-      <c r="H71" s="52"/>
-      <c r="I71" s="53"/>
-      <c r="J71" s="53"/>
-      <c r="K71" s="53"/>
-      <c r="L71" s="53"/>
-      <c r="M71" s="53"/>
-      <c r="N71" s="53"/>
-      <c r="O71" s="53"/>
-      <c r="P71" s="53"/>
-      <c r="Q71" s="53"/>
-      <c r="R71" s="53"/>
-      <c r="S71" s="53"/>
-      <c r="T71" s="53"/>
-      <c r="U71" s="53"/>
-      <c r="V71" s="53"/>
-      <c r="W71" s="53"/>
-      <c r="X71" s="53"/>
-      <c r="Y71" s="53"/>
-      <c r="Z71" s="53"/>
-      <c r="AA71" s="53"/>
-      <c r="AB71" s="54"/>
+      <c r="H71" s="54"/>
+      <c r="I71" s="55"/>
+      <c r="J71" s="55"/>
+      <c r="K71" s="55"/>
+      <c r="L71" s="55"/>
+      <c r="M71" s="55"/>
+      <c r="N71" s="55"/>
+      <c r="O71" s="55"/>
+      <c r="P71" s="55"/>
+      <c r="Q71" s="55"/>
+      <c r="R71" s="55"/>
+      <c r="S71" s="55"/>
+      <c r="T71" s="55"/>
+      <c r="U71" s="55"/>
+      <c r="V71" s="55"/>
+      <c r="W71" s="55"/>
+      <c r="X71" s="55"/>
+      <c r="Y71" s="55"/>
+      <c r="Z71" s="55"/>
+      <c r="AA71" s="55"/>
+      <c r="AB71" s="56"/>
       <c r="AC71" s="11"/>
     </row>
     <row r="72" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4066,27 +4090,27 @@
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
-      <c r="H73" s="46"/>
-      <c r="I73" s="47"/>
-      <c r="J73" s="47"/>
-      <c r="K73" s="47"/>
-      <c r="L73" s="47"/>
-      <c r="M73" s="47"/>
-      <c r="N73" s="47"/>
-      <c r="O73" s="47"/>
-      <c r="P73" s="47"/>
-      <c r="Q73" s="47"/>
-      <c r="R73" s="47"/>
-      <c r="S73" s="47"/>
-      <c r="T73" s="47"/>
-      <c r="U73" s="47"/>
-      <c r="V73" s="47"/>
-      <c r="W73" s="47"/>
-      <c r="X73" s="47"/>
-      <c r="Y73" s="47"/>
-      <c r="Z73" s="47"/>
-      <c r="AA73" s="47"/>
-      <c r="AB73" s="48"/>
+      <c r="H73" s="48"/>
+      <c r="I73" s="49"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="49"/>
+      <c r="N73" s="49"/>
+      <c r="O73" s="49"/>
+      <c r="P73" s="49"/>
+      <c r="Q73" s="49"/>
+      <c r="R73" s="49"/>
+      <c r="S73" s="49"/>
+      <c r="T73" s="49"/>
+      <c r="U73" s="49"/>
+      <c r="V73" s="49"/>
+      <c r="W73" s="49"/>
+      <c r="X73" s="49"/>
+      <c r="Y73" s="49"/>
+      <c r="Z73" s="49"/>
+      <c r="AA73" s="49"/>
+      <c r="AB73" s="50"/>
       <c r="AC73" s="11"/>
     </row>
     <row r="74" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4096,27 +4120,27 @@
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="50"/>
-      <c r="J74" s="50"/>
-      <c r="K74" s="50"/>
-      <c r="L74" s="50"/>
-      <c r="M74" s="50"/>
-      <c r="N74" s="50"/>
-      <c r="O74" s="50"/>
-      <c r="P74" s="50"/>
-      <c r="Q74" s="50"/>
-      <c r="R74" s="50"/>
-      <c r="S74" s="50"/>
-      <c r="T74" s="50"/>
-      <c r="U74" s="50"/>
-      <c r="V74" s="50"/>
-      <c r="W74" s="50"/>
-      <c r="X74" s="50"/>
-      <c r="Y74" s="50"/>
-      <c r="Z74" s="50"/>
-      <c r="AA74" s="50"/>
-      <c r="AB74" s="51"/>
+      <c r="H74" s="51"/>
+      <c r="I74" s="52"/>
+      <c r="J74" s="52"/>
+      <c r="K74" s="52"/>
+      <c r="L74" s="52"/>
+      <c r="M74" s="52"/>
+      <c r="N74" s="52"/>
+      <c r="O74" s="52"/>
+      <c r="P74" s="52"/>
+      <c r="Q74" s="52"/>
+      <c r="R74" s="52"/>
+      <c r="S74" s="52"/>
+      <c r="T74" s="52"/>
+      <c r="U74" s="52"/>
+      <c r="V74" s="52"/>
+      <c r="W74" s="52"/>
+      <c r="X74" s="52"/>
+      <c r="Y74" s="52"/>
+      <c r="Z74" s="52"/>
+      <c r="AA74" s="52"/>
+      <c r="AB74" s="53"/>
       <c r="AC74" s="11"/>
     </row>
     <row r="75" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4126,27 +4150,27 @@
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="50"/>
-      <c r="J75" s="50"/>
-      <c r="K75" s="50"/>
-      <c r="L75" s="50"/>
-      <c r="M75" s="50"/>
-      <c r="N75" s="50"/>
-      <c r="O75" s="50"/>
-      <c r="P75" s="50"/>
-      <c r="Q75" s="50"/>
-      <c r="R75" s="50"/>
-      <c r="S75" s="50"/>
-      <c r="T75" s="50"/>
-      <c r="U75" s="50"/>
-      <c r="V75" s="50"/>
-      <c r="W75" s="50"/>
-      <c r="X75" s="50"/>
-      <c r="Y75" s="50"/>
-      <c r="Z75" s="50"/>
-      <c r="AA75" s="50"/>
-      <c r="AB75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="52"/>
+      <c r="J75" s="52"/>
+      <c r="K75" s="52"/>
+      <c r="L75" s="52"/>
+      <c r="M75" s="52"/>
+      <c r="N75" s="52"/>
+      <c r="O75" s="52"/>
+      <c r="P75" s="52"/>
+      <c r="Q75" s="52"/>
+      <c r="R75" s="52"/>
+      <c r="S75" s="52"/>
+      <c r="T75" s="52"/>
+      <c r="U75" s="52"/>
+      <c r="V75" s="52"/>
+      <c r="W75" s="52"/>
+      <c r="X75" s="52"/>
+      <c r="Y75" s="52"/>
+      <c r="Z75" s="52"/>
+      <c r="AA75" s="52"/>
+      <c r="AB75" s="53"/>
       <c r="AC75" s="11"/>
     </row>
     <row r="76" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4156,27 +4180,27 @@
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="50"/>
-      <c r="J76" s="50"/>
-      <c r="K76" s="50"/>
-      <c r="L76" s="50"/>
-      <c r="M76" s="50"/>
-      <c r="N76" s="50"/>
-      <c r="O76" s="50"/>
-      <c r="P76" s="50"/>
-      <c r="Q76" s="50"/>
-      <c r="R76" s="50"/>
-      <c r="S76" s="50"/>
-      <c r="T76" s="50"/>
-      <c r="U76" s="50"/>
-      <c r="V76" s="50"/>
-      <c r="W76" s="50"/>
-      <c r="X76" s="50"/>
-      <c r="Y76" s="50"/>
-      <c r="Z76" s="50"/>
-      <c r="AA76" s="50"/>
-      <c r="AB76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="52"/>
+      <c r="J76" s="52"/>
+      <c r="K76" s="52"/>
+      <c r="L76" s="52"/>
+      <c r="M76" s="52"/>
+      <c r="N76" s="52"/>
+      <c r="O76" s="52"/>
+      <c r="P76" s="52"/>
+      <c r="Q76" s="52"/>
+      <c r="R76" s="52"/>
+      <c r="S76" s="52"/>
+      <c r="T76" s="52"/>
+      <c r="U76" s="52"/>
+      <c r="V76" s="52"/>
+      <c r="W76" s="52"/>
+      <c r="X76" s="52"/>
+      <c r="Y76" s="52"/>
+      <c r="Z76" s="52"/>
+      <c r="AA76" s="52"/>
+      <c r="AB76" s="53"/>
       <c r="AC76" s="11"/>
     </row>
     <row r="77" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4186,27 +4210,27 @@
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="50"/>
-      <c r="J77" s="50"/>
-      <c r="K77" s="50"/>
-      <c r="L77" s="50"/>
-      <c r="M77" s="50"/>
-      <c r="N77" s="50"/>
-      <c r="O77" s="50"/>
-      <c r="P77" s="50"/>
-      <c r="Q77" s="50"/>
-      <c r="R77" s="50"/>
-      <c r="S77" s="50"/>
-      <c r="T77" s="50"/>
-      <c r="U77" s="50"/>
-      <c r="V77" s="50"/>
-      <c r="W77" s="50"/>
-      <c r="X77" s="50"/>
-      <c r="Y77" s="50"/>
-      <c r="Z77" s="50"/>
-      <c r="AA77" s="50"/>
-      <c r="AB77" s="51"/>
+      <c r="H77" s="51"/>
+      <c r="I77" s="52"/>
+      <c r="J77" s="52"/>
+      <c r="K77" s="52"/>
+      <c r="L77" s="52"/>
+      <c r="M77" s="52"/>
+      <c r="N77" s="52"/>
+      <c r="O77" s="52"/>
+      <c r="P77" s="52"/>
+      <c r="Q77" s="52"/>
+      <c r="R77" s="52"/>
+      <c r="S77" s="52"/>
+      <c r="T77" s="52"/>
+      <c r="U77" s="52"/>
+      <c r="V77" s="52"/>
+      <c r="W77" s="52"/>
+      <c r="X77" s="52"/>
+      <c r="Y77" s="52"/>
+      <c r="Z77" s="52"/>
+      <c r="AA77" s="52"/>
+      <c r="AB77" s="53"/>
       <c r="AC77" s="11"/>
     </row>
     <row r="78" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4216,27 +4240,27 @@
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="50"/>
-      <c r="J78" s="50"/>
-      <c r="K78" s="50"/>
-      <c r="L78" s="50"/>
-      <c r="M78" s="50"/>
-      <c r="N78" s="50"/>
-      <c r="O78" s="50"/>
-      <c r="P78" s="50"/>
-      <c r="Q78" s="50"/>
-      <c r="R78" s="50"/>
-      <c r="S78" s="50"/>
-      <c r="T78" s="50"/>
-      <c r="U78" s="50"/>
-      <c r="V78" s="50"/>
-      <c r="W78" s="50"/>
-      <c r="X78" s="50"/>
-      <c r="Y78" s="50"/>
-      <c r="Z78" s="50"/>
-      <c r="AA78" s="50"/>
-      <c r="AB78" s="51"/>
+      <c r="H78" s="51"/>
+      <c r="I78" s="52"/>
+      <c r="J78" s="52"/>
+      <c r="K78" s="52"/>
+      <c r="L78" s="52"/>
+      <c r="M78" s="52"/>
+      <c r="N78" s="52"/>
+      <c r="O78" s="52"/>
+      <c r="P78" s="52"/>
+      <c r="Q78" s="52"/>
+      <c r="R78" s="52"/>
+      <c r="S78" s="52"/>
+      <c r="T78" s="52"/>
+      <c r="U78" s="52"/>
+      <c r="V78" s="52"/>
+      <c r="W78" s="52"/>
+      <c r="X78" s="52"/>
+      <c r="Y78" s="52"/>
+      <c r="Z78" s="52"/>
+      <c r="AA78" s="52"/>
+      <c r="AB78" s="53"/>
       <c r="AC78" s="11"/>
     </row>
     <row r="79" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4246,27 +4270,27 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="53"/>
-      <c r="K79" s="53"/>
-      <c r="L79" s="53"/>
-      <c r="M79" s="53"/>
-      <c r="N79" s="53"/>
-      <c r="O79" s="53"/>
-      <c r="P79" s="53"/>
-      <c r="Q79" s="53"/>
-      <c r="R79" s="53"/>
-      <c r="S79" s="53"/>
-      <c r="T79" s="53"/>
-      <c r="U79" s="53"/>
-      <c r="V79" s="53"/>
-      <c r="W79" s="53"/>
-      <c r="X79" s="53"/>
-      <c r="Y79" s="53"/>
-      <c r="Z79" s="53"/>
-      <c r="AA79" s="53"/>
-      <c r="AB79" s="54"/>
+      <c r="H79" s="54"/>
+      <c r="I79" s="55"/>
+      <c r="J79" s="55"/>
+      <c r="K79" s="55"/>
+      <c r="L79" s="55"/>
+      <c r="M79" s="55"/>
+      <c r="N79" s="55"/>
+      <c r="O79" s="55"/>
+      <c r="P79" s="55"/>
+      <c r="Q79" s="55"/>
+      <c r="R79" s="55"/>
+      <c r="S79" s="55"/>
+      <c r="T79" s="55"/>
+      <c r="U79" s="55"/>
+      <c r="V79" s="55"/>
+      <c r="W79" s="55"/>
+      <c r="X79" s="55"/>
+      <c r="Y79" s="55"/>
+      <c r="Z79" s="55"/>
+      <c r="AA79" s="55"/>
+      <c r="AB79" s="56"/>
       <c r="AC79" s="11"/>
     </row>
     <row r="80" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4374,27 +4398,27 @@
         <v>2</v>
       </c>
       <c r="G84" s="6"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="47"/>
-      <c r="J84" s="47"/>
-      <c r="K84" s="47"/>
-      <c r="L84" s="47"/>
-      <c r="M84" s="47"/>
-      <c r="N84" s="47"/>
-      <c r="O84" s="47"/>
-      <c r="P84" s="47"/>
-      <c r="Q84" s="47"/>
-      <c r="R84" s="47"/>
-      <c r="S84" s="47"/>
-      <c r="T84" s="47"/>
-      <c r="U84" s="47"/>
-      <c r="V84" s="47"/>
-      <c r="W84" s="47"/>
-      <c r="X84" s="47"/>
-      <c r="Y84" s="47"/>
-      <c r="Z84" s="47"/>
-      <c r="AA84" s="47"/>
-      <c r="AB84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="49"/>
+      <c r="J84" s="49"/>
+      <c r="K84" s="49"/>
+      <c r="L84" s="49"/>
+      <c r="M84" s="49"/>
+      <c r="N84" s="49"/>
+      <c r="O84" s="49"/>
+      <c r="P84" s="49"/>
+      <c r="Q84" s="49"/>
+      <c r="R84" s="49"/>
+      <c r="S84" s="49"/>
+      <c r="T84" s="49"/>
+      <c r="U84" s="49"/>
+      <c r="V84" s="49"/>
+      <c r="W84" s="49"/>
+      <c r="X84" s="49"/>
+      <c r="Y84" s="49"/>
+      <c r="Z84" s="49"/>
+      <c r="AA84" s="49"/>
+      <c r="AB84" s="50"/>
       <c r="AC84" s="11"/>
     </row>
     <row r="85" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4404,27 +4428,27 @@
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
-      <c r="H85" s="49"/>
-      <c r="I85" s="50"/>
-      <c r="J85" s="50"/>
-      <c r="K85" s="50"/>
-      <c r="L85" s="50"/>
-      <c r="M85" s="50"/>
-      <c r="N85" s="50"/>
-      <c r="O85" s="50"/>
-      <c r="P85" s="50"/>
-      <c r="Q85" s="50"/>
-      <c r="R85" s="50"/>
-      <c r="S85" s="50"/>
-      <c r="T85" s="50"/>
-      <c r="U85" s="50"/>
-      <c r="V85" s="50"/>
-      <c r="W85" s="50"/>
-      <c r="X85" s="50"/>
-      <c r="Y85" s="50"/>
-      <c r="Z85" s="50"/>
-      <c r="AA85" s="50"/>
-      <c r="AB85" s="51"/>
+      <c r="H85" s="51"/>
+      <c r="I85" s="52"/>
+      <c r="J85" s="52"/>
+      <c r="K85" s="52"/>
+      <c r="L85" s="52"/>
+      <c r="M85" s="52"/>
+      <c r="N85" s="52"/>
+      <c r="O85" s="52"/>
+      <c r="P85" s="52"/>
+      <c r="Q85" s="52"/>
+      <c r="R85" s="52"/>
+      <c r="S85" s="52"/>
+      <c r="T85" s="52"/>
+      <c r="U85" s="52"/>
+      <c r="V85" s="52"/>
+      <c r="W85" s="52"/>
+      <c r="X85" s="52"/>
+      <c r="Y85" s="52"/>
+      <c r="Z85" s="52"/>
+      <c r="AA85" s="52"/>
+      <c r="AB85" s="53"/>
       <c r="AC85" s="11"/>
     </row>
     <row r="86" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4434,27 +4458,27 @@
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
-      <c r="H86" s="49"/>
-      <c r="I86" s="50"/>
-      <c r="J86" s="50"/>
-      <c r="K86" s="50"/>
-      <c r="L86" s="50"/>
-      <c r="M86" s="50"/>
-      <c r="N86" s="50"/>
-      <c r="O86" s="50"/>
-      <c r="P86" s="50"/>
-      <c r="Q86" s="50"/>
-      <c r="R86" s="50"/>
-      <c r="S86" s="50"/>
-      <c r="T86" s="50"/>
-      <c r="U86" s="50"/>
-      <c r="V86" s="50"/>
-      <c r="W86" s="50"/>
-      <c r="X86" s="50"/>
-      <c r="Y86" s="50"/>
-      <c r="Z86" s="50"/>
-      <c r="AA86" s="50"/>
-      <c r="AB86" s="51"/>
+      <c r="H86" s="51"/>
+      <c r="I86" s="52"/>
+      <c r="J86" s="52"/>
+      <c r="K86" s="52"/>
+      <c r="L86" s="52"/>
+      <c r="M86" s="52"/>
+      <c r="N86" s="52"/>
+      <c r="O86" s="52"/>
+      <c r="P86" s="52"/>
+      <c r="Q86" s="52"/>
+      <c r="R86" s="52"/>
+      <c r="S86" s="52"/>
+      <c r="T86" s="52"/>
+      <c r="U86" s="52"/>
+      <c r="V86" s="52"/>
+      <c r="W86" s="52"/>
+      <c r="X86" s="52"/>
+      <c r="Y86" s="52"/>
+      <c r="Z86" s="52"/>
+      <c r="AA86" s="52"/>
+      <c r="AB86" s="53"/>
       <c r="AC86" s="11"/>
     </row>
     <row r="87" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4464,27 +4488,27 @@
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="50"/>
-      <c r="J87" s="50"/>
-      <c r="K87" s="50"/>
-      <c r="L87" s="50"/>
-      <c r="M87" s="50"/>
-      <c r="N87" s="50"/>
-      <c r="O87" s="50"/>
-      <c r="P87" s="50"/>
-      <c r="Q87" s="50"/>
-      <c r="R87" s="50"/>
-      <c r="S87" s="50"/>
-      <c r="T87" s="50"/>
-      <c r="U87" s="50"/>
-      <c r="V87" s="50"/>
-      <c r="W87" s="50"/>
-      <c r="X87" s="50"/>
-      <c r="Y87" s="50"/>
-      <c r="Z87" s="50"/>
-      <c r="AA87" s="50"/>
-      <c r="AB87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="52"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="52"/>
+      <c r="P87" s="52"/>
+      <c r="Q87" s="52"/>
+      <c r="R87" s="52"/>
+      <c r="S87" s="52"/>
+      <c r="T87" s="52"/>
+      <c r="U87" s="52"/>
+      <c r="V87" s="52"/>
+      <c r="W87" s="52"/>
+      <c r="X87" s="52"/>
+      <c r="Y87" s="52"/>
+      <c r="Z87" s="52"/>
+      <c r="AA87" s="52"/>
+      <c r="AB87" s="53"/>
       <c r="AC87" s="11"/>
     </row>
     <row r="88" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4494,27 +4518,27 @@
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="50"/>
-      <c r="J88" s="50"/>
-      <c r="K88" s="50"/>
-      <c r="L88" s="50"/>
-      <c r="M88" s="50"/>
-      <c r="N88" s="50"/>
-      <c r="O88" s="50"/>
-      <c r="P88" s="50"/>
-      <c r="Q88" s="50"/>
-      <c r="R88" s="50"/>
-      <c r="S88" s="50"/>
-      <c r="T88" s="50"/>
-      <c r="U88" s="50"/>
-      <c r="V88" s="50"/>
-      <c r="W88" s="50"/>
-      <c r="X88" s="50"/>
-      <c r="Y88" s="50"/>
-      <c r="Z88" s="50"/>
-      <c r="AA88" s="50"/>
-      <c r="AB88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="52"/>
+      <c r="J88" s="52"/>
+      <c r="K88" s="52"/>
+      <c r="L88" s="52"/>
+      <c r="M88" s="52"/>
+      <c r="N88" s="52"/>
+      <c r="O88" s="52"/>
+      <c r="P88" s="52"/>
+      <c r="Q88" s="52"/>
+      <c r="R88" s="52"/>
+      <c r="S88" s="52"/>
+      <c r="T88" s="52"/>
+      <c r="U88" s="52"/>
+      <c r="V88" s="52"/>
+      <c r="W88" s="52"/>
+      <c r="X88" s="52"/>
+      <c r="Y88" s="52"/>
+      <c r="Z88" s="52"/>
+      <c r="AA88" s="52"/>
+      <c r="AB88" s="53"/>
       <c r="AC88" s="11"/>
     </row>
     <row r="89" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4524,27 +4548,27 @@
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
-      <c r="H89" s="49"/>
-      <c r="I89" s="50"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="50"/>
-      <c r="L89" s="50"/>
-      <c r="M89" s="50"/>
-      <c r="N89" s="50"/>
-      <c r="O89" s="50"/>
-      <c r="P89" s="50"/>
-      <c r="Q89" s="50"/>
-      <c r="R89" s="50"/>
-      <c r="S89" s="50"/>
-      <c r="T89" s="50"/>
-      <c r="U89" s="50"/>
-      <c r="V89" s="50"/>
-      <c r="W89" s="50"/>
-      <c r="X89" s="50"/>
-      <c r="Y89" s="50"/>
-      <c r="Z89" s="50"/>
-      <c r="AA89" s="50"/>
-      <c r="AB89" s="51"/>
+      <c r="H89" s="51"/>
+      <c r="I89" s="52"/>
+      <c r="J89" s="52"/>
+      <c r="K89" s="52"/>
+      <c r="L89" s="52"/>
+      <c r="M89" s="52"/>
+      <c r="N89" s="52"/>
+      <c r="O89" s="52"/>
+      <c r="P89" s="52"/>
+      <c r="Q89" s="52"/>
+      <c r="R89" s="52"/>
+      <c r="S89" s="52"/>
+      <c r="T89" s="52"/>
+      <c r="U89" s="52"/>
+      <c r="V89" s="52"/>
+      <c r="W89" s="52"/>
+      <c r="X89" s="52"/>
+      <c r="Y89" s="52"/>
+      <c r="Z89" s="52"/>
+      <c r="AA89" s="52"/>
+      <c r="AB89" s="53"/>
       <c r="AC89" s="11"/>
     </row>
     <row r="90" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4554,27 +4578,27 @@
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
-      <c r="L90" s="53"/>
-      <c r="M90" s="53"/>
-      <c r="N90" s="53"/>
-      <c r="O90" s="53"/>
-      <c r="P90" s="53"/>
-      <c r="Q90" s="53"/>
-      <c r="R90" s="53"/>
-      <c r="S90" s="53"/>
-      <c r="T90" s="53"/>
-      <c r="U90" s="53"/>
-      <c r="V90" s="53"/>
-      <c r="W90" s="53"/>
-      <c r="X90" s="53"/>
-      <c r="Y90" s="53"/>
-      <c r="Z90" s="53"/>
-      <c r="AA90" s="53"/>
-      <c r="AB90" s="54"/>
+      <c r="H90" s="54"/>
+      <c r="I90" s="55"/>
+      <c r="J90" s="55"/>
+      <c r="K90" s="55"/>
+      <c r="L90" s="55"/>
+      <c r="M90" s="55"/>
+      <c r="N90" s="55"/>
+      <c r="O90" s="55"/>
+      <c r="P90" s="55"/>
+      <c r="Q90" s="55"/>
+      <c r="R90" s="55"/>
+      <c r="S90" s="55"/>
+      <c r="T90" s="55"/>
+      <c r="U90" s="55"/>
+      <c r="V90" s="55"/>
+      <c r="W90" s="55"/>
+      <c r="X90" s="55"/>
+      <c r="Y90" s="55"/>
+      <c r="Z90" s="55"/>
+      <c r="AA90" s="55"/>
+      <c r="AB90" s="56"/>
       <c r="AC90" s="11"/>
     </row>
     <row r="91" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4616,27 +4640,27 @@
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
-      <c r="H92" s="46"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="47"/>
-      <c r="K92" s="47"/>
-      <c r="L92" s="47"/>
-      <c r="M92" s="47"/>
-      <c r="N92" s="47"/>
-      <c r="O92" s="47"/>
-      <c r="P92" s="47"/>
-      <c r="Q92" s="47"/>
-      <c r="R92" s="47"/>
-      <c r="S92" s="47"/>
-      <c r="T92" s="47"/>
-      <c r="U92" s="47"/>
-      <c r="V92" s="47"/>
-      <c r="W92" s="47"/>
-      <c r="X92" s="47"/>
-      <c r="Y92" s="47"/>
-      <c r="Z92" s="47"/>
-      <c r="AA92" s="47"/>
-      <c r="AB92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="49"/>
+      <c r="J92" s="49"/>
+      <c r="K92" s="49"/>
+      <c r="L92" s="49"/>
+      <c r="M92" s="49"/>
+      <c r="N92" s="49"/>
+      <c r="O92" s="49"/>
+      <c r="P92" s="49"/>
+      <c r="Q92" s="49"/>
+      <c r="R92" s="49"/>
+      <c r="S92" s="49"/>
+      <c r="T92" s="49"/>
+      <c r="U92" s="49"/>
+      <c r="V92" s="49"/>
+      <c r="W92" s="49"/>
+      <c r="X92" s="49"/>
+      <c r="Y92" s="49"/>
+      <c r="Z92" s="49"/>
+      <c r="AA92" s="49"/>
+      <c r="AB92" s="50"/>
       <c r="AC92" s="11"/>
     </row>
     <row r="93" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4646,27 +4670,27 @@
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
-      <c r="H93" s="49"/>
-      <c r="I93" s="50"/>
-      <c r="J93" s="50"/>
-      <c r="K93" s="50"/>
-      <c r="L93" s="50"/>
-      <c r="M93" s="50"/>
-      <c r="N93" s="50"/>
-      <c r="O93" s="50"/>
-      <c r="P93" s="50"/>
-      <c r="Q93" s="50"/>
-      <c r="R93" s="50"/>
-      <c r="S93" s="50"/>
-      <c r="T93" s="50"/>
-      <c r="U93" s="50"/>
-      <c r="V93" s="50"/>
-      <c r="W93" s="50"/>
-      <c r="X93" s="50"/>
-      <c r="Y93" s="50"/>
-      <c r="Z93" s="50"/>
-      <c r="AA93" s="50"/>
-      <c r="AB93" s="51"/>
+      <c r="H93" s="51"/>
+      <c r="I93" s="52"/>
+      <c r="J93" s="52"/>
+      <c r="K93" s="52"/>
+      <c r="L93" s="52"/>
+      <c r="M93" s="52"/>
+      <c r="N93" s="52"/>
+      <c r="O93" s="52"/>
+      <c r="P93" s="52"/>
+      <c r="Q93" s="52"/>
+      <c r="R93" s="52"/>
+      <c r="S93" s="52"/>
+      <c r="T93" s="52"/>
+      <c r="U93" s="52"/>
+      <c r="V93" s="52"/>
+      <c r="W93" s="52"/>
+      <c r="X93" s="52"/>
+      <c r="Y93" s="52"/>
+      <c r="Z93" s="52"/>
+      <c r="AA93" s="52"/>
+      <c r="AB93" s="53"/>
       <c r="AC93" s="11"/>
     </row>
     <row r="94" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4676,27 +4700,27 @@
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
-      <c r="H94" s="49"/>
-      <c r="I94" s="50"/>
-      <c r="J94" s="50"/>
-      <c r="K94" s="50"/>
-      <c r="L94" s="50"/>
-      <c r="M94" s="50"/>
-      <c r="N94" s="50"/>
-      <c r="O94" s="50"/>
-      <c r="P94" s="50"/>
-      <c r="Q94" s="50"/>
-      <c r="R94" s="50"/>
-      <c r="S94" s="50"/>
-      <c r="T94" s="50"/>
-      <c r="U94" s="50"/>
-      <c r="V94" s="50"/>
-      <c r="W94" s="50"/>
-      <c r="X94" s="50"/>
-      <c r="Y94" s="50"/>
-      <c r="Z94" s="50"/>
-      <c r="AA94" s="50"/>
-      <c r="AB94" s="51"/>
+      <c r="H94" s="51"/>
+      <c r="I94" s="52"/>
+      <c r="J94" s="52"/>
+      <c r="K94" s="52"/>
+      <c r="L94" s="52"/>
+      <c r="M94" s="52"/>
+      <c r="N94" s="52"/>
+      <c r="O94" s="52"/>
+      <c r="P94" s="52"/>
+      <c r="Q94" s="52"/>
+      <c r="R94" s="52"/>
+      <c r="S94" s="52"/>
+      <c r="T94" s="52"/>
+      <c r="U94" s="52"/>
+      <c r="V94" s="52"/>
+      <c r="W94" s="52"/>
+      <c r="X94" s="52"/>
+      <c r="Y94" s="52"/>
+      <c r="Z94" s="52"/>
+      <c r="AA94" s="52"/>
+      <c r="AB94" s="53"/>
       <c r="AC94" s="11"/>
     </row>
     <row r="95" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4706,27 +4730,27 @@
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
-      <c r="H95" s="49"/>
-      <c r="I95" s="50"/>
-      <c r="J95" s="50"/>
-      <c r="K95" s="50"/>
-      <c r="L95" s="50"/>
-      <c r="M95" s="50"/>
-      <c r="N95" s="50"/>
-      <c r="O95" s="50"/>
-      <c r="P95" s="50"/>
-      <c r="Q95" s="50"/>
-      <c r="R95" s="50"/>
-      <c r="S95" s="50"/>
-      <c r="T95" s="50"/>
-      <c r="U95" s="50"/>
-      <c r="V95" s="50"/>
-      <c r="W95" s="50"/>
-      <c r="X95" s="50"/>
-      <c r="Y95" s="50"/>
-      <c r="Z95" s="50"/>
-      <c r="AA95" s="50"/>
-      <c r="AB95" s="51"/>
+      <c r="H95" s="51"/>
+      <c r="I95" s="52"/>
+      <c r="J95" s="52"/>
+      <c r="K95" s="52"/>
+      <c r="L95" s="52"/>
+      <c r="M95" s="52"/>
+      <c r="N95" s="52"/>
+      <c r="O95" s="52"/>
+      <c r="P95" s="52"/>
+      <c r="Q95" s="52"/>
+      <c r="R95" s="52"/>
+      <c r="S95" s="52"/>
+      <c r="T95" s="52"/>
+      <c r="U95" s="52"/>
+      <c r="V95" s="52"/>
+      <c r="W95" s="52"/>
+      <c r="X95" s="52"/>
+      <c r="Y95" s="52"/>
+      <c r="Z95" s="52"/>
+      <c r="AA95" s="52"/>
+      <c r="AB95" s="53"/>
       <c r="AC95" s="11"/>
     </row>
     <row r="96" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4736,27 +4760,27 @@
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
-      <c r="H96" s="49"/>
-      <c r="I96" s="50"/>
-      <c r="J96" s="50"/>
-      <c r="K96" s="50"/>
-      <c r="L96" s="50"/>
-      <c r="M96" s="50"/>
-      <c r="N96" s="50"/>
-      <c r="O96" s="50"/>
-      <c r="P96" s="50"/>
-      <c r="Q96" s="50"/>
-      <c r="R96" s="50"/>
-      <c r="S96" s="50"/>
-      <c r="T96" s="50"/>
-      <c r="U96" s="50"/>
-      <c r="V96" s="50"/>
-      <c r="W96" s="50"/>
-      <c r="X96" s="50"/>
-      <c r="Y96" s="50"/>
-      <c r="Z96" s="50"/>
-      <c r="AA96" s="50"/>
-      <c r="AB96" s="51"/>
+      <c r="H96" s="51"/>
+      <c r="I96" s="52"/>
+      <c r="J96" s="52"/>
+      <c r="K96" s="52"/>
+      <c r="L96" s="52"/>
+      <c r="M96" s="52"/>
+      <c r="N96" s="52"/>
+      <c r="O96" s="52"/>
+      <c r="P96" s="52"/>
+      <c r="Q96" s="52"/>
+      <c r="R96" s="52"/>
+      <c r="S96" s="52"/>
+      <c r="T96" s="52"/>
+      <c r="U96" s="52"/>
+      <c r="V96" s="52"/>
+      <c r="W96" s="52"/>
+      <c r="X96" s="52"/>
+      <c r="Y96" s="52"/>
+      <c r="Z96" s="52"/>
+      <c r="AA96" s="52"/>
+      <c r="AB96" s="53"/>
       <c r="AC96" s="11"/>
     </row>
     <row r="97" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4766,27 +4790,27 @@
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
-      <c r="H97" s="49"/>
-      <c r="I97" s="50"/>
-      <c r="J97" s="50"/>
-      <c r="K97" s="50"/>
-      <c r="L97" s="50"/>
-      <c r="M97" s="50"/>
-      <c r="N97" s="50"/>
-      <c r="O97" s="50"/>
-      <c r="P97" s="50"/>
-      <c r="Q97" s="50"/>
-      <c r="R97" s="50"/>
-      <c r="S97" s="50"/>
-      <c r="T97" s="50"/>
-      <c r="U97" s="50"/>
-      <c r="V97" s="50"/>
-      <c r="W97" s="50"/>
-      <c r="X97" s="50"/>
-      <c r="Y97" s="50"/>
-      <c r="Z97" s="50"/>
-      <c r="AA97" s="50"/>
-      <c r="AB97" s="51"/>
+      <c r="H97" s="51"/>
+      <c r="I97" s="52"/>
+      <c r="J97" s="52"/>
+      <c r="K97" s="52"/>
+      <c r="L97" s="52"/>
+      <c r="M97" s="52"/>
+      <c r="N97" s="52"/>
+      <c r="O97" s="52"/>
+      <c r="P97" s="52"/>
+      <c r="Q97" s="52"/>
+      <c r="R97" s="52"/>
+      <c r="S97" s="52"/>
+      <c r="T97" s="52"/>
+      <c r="U97" s="52"/>
+      <c r="V97" s="52"/>
+      <c r="W97" s="52"/>
+      <c r="X97" s="52"/>
+      <c r="Y97" s="52"/>
+      <c r="Z97" s="52"/>
+      <c r="AA97" s="52"/>
+      <c r="AB97" s="53"/>
       <c r="AC97" s="11"/>
     </row>
     <row r="98" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4796,27 +4820,27 @@
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="53"/>
-      <c r="J98" s="53"/>
-      <c r="K98" s="53"/>
-      <c r="L98" s="53"/>
-      <c r="M98" s="53"/>
-      <c r="N98" s="53"/>
-      <c r="O98" s="53"/>
-      <c r="P98" s="53"/>
-      <c r="Q98" s="53"/>
-      <c r="R98" s="53"/>
-      <c r="S98" s="53"/>
-      <c r="T98" s="53"/>
-      <c r="U98" s="53"/>
-      <c r="V98" s="53"/>
-      <c r="W98" s="53"/>
-      <c r="X98" s="53"/>
-      <c r="Y98" s="53"/>
-      <c r="Z98" s="53"/>
-      <c r="AA98" s="53"/>
-      <c r="AB98" s="54"/>
+      <c r="H98" s="54"/>
+      <c r="I98" s="55"/>
+      <c r="J98" s="55"/>
+      <c r="K98" s="55"/>
+      <c r="L98" s="55"/>
+      <c r="M98" s="55"/>
+      <c r="N98" s="55"/>
+      <c r="O98" s="55"/>
+      <c r="P98" s="55"/>
+      <c r="Q98" s="55"/>
+      <c r="R98" s="55"/>
+      <c r="S98" s="55"/>
+      <c r="T98" s="55"/>
+      <c r="U98" s="55"/>
+      <c r="V98" s="55"/>
+      <c r="W98" s="55"/>
+      <c r="X98" s="55"/>
+      <c r="Y98" s="55"/>
+      <c r="Z98" s="55"/>
+      <c r="AA98" s="55"/>
+      <c r="AB98" s="56"/>
       <c r="AC98" s="11"/>
     </row>
     <row r="99" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4924,27 +4948,27 @@
         <v>2</v>
       </c>
       <c r="G103" s="6"/>
-      <c r="H103" s="46"/>
-      <c r="I103" s="47"/>
-      <c r="J103" s="47"/>
-      <c r="K103" s="47"/>
-      <c r="L103" s="47"/>
-      <c r="M103" s="47"/>
-      <c r="N103" s="47"/>
-      <c r="O103" s="47"/>
-      <c r="P103" s="47"/>
-      <c r="Q103" s="47"/>
-      <c r="R103" s="47"/>
-      <c r="S103" s="47"/>
-      <c r="T103" s="47"/>
-      <c r="U103" s="47"/>
-      <c r="V103" s="47"/>
-      <c r="W103" s="47"/>
-      <c r="X103" s="47"/>
-      <c r="Y103" s="47"/>
-      <c r="Z103" s="47"/>
-      <c r="AA103" s="47"/>
-      <c r="AB103" s="48"/>
+      <c r="H103" s="48"/>
+      <c r="I103" s="49"/>
+      <c r="J103" s="49"/>
+      <c r="K103" s="49"/>
+      <c r="L103" s="49"/>
+      <c r="M103" s="49"/>
+      <c r="N103" s="49"/>
+      <c r="O103" s="49"/>
+      <c r="P103" s="49"/>
+      <c r="Q103" s="49"/>
+      <c r="R103" s="49"/>
+      <c r="S103" s="49"/>
+      <c r="T103" s="49"/>
+      <c r="U103" s="49"/>
+      <c r="V103" s="49"/>
+      <c r="W103" s="49"/>
+      <c r="X103" s="49"/>
+      <c r="Y103" s="49"/>
+      <c r="Z103" s="49"/>
+      <c r="AA103" s="49"/>
+      <c r="AB103" s="50"/>
       <c r="AC103" s="11"/>
     </row>
     <row r="104" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4954,27 +4978,27 @@
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
-      <c r="H104" s="49"/>
-      <c r="I104" s="50"/>
-      <c r="J104" s="50"/>
-      <c r="K104" s="50"/>
-      <c r="L104" s="50"/>
-      <c r="M104" s="50"/>
-      <c r="N104" s="50"/>
-      <c r="O104" s="50"/>
-      <c r="P104" s="50"/>
-      <c r="Q104" s="50"/>
-      <c r="R104" s="50"/>
-      <c r="S104" s="50"/>
-      <c r="T104" s="50"/>
-      <c r="U104" s="50"/>
-      <c r="V104" s="50"/>
-      <c r="W104" s="50"/>
-      <c r="X104" s="50"/>
-      <c r="Y104" s="50"/>
-      <c r="Z104" s="50"/>
-      <c r="AA104" s="50"/>
-      <c r="AB104" s="51"/>
+      <c r="H104" s="51"/>
+      <c r="I104" s="52"/>
+      <c r="J104" s="52"/>
+      <c r="K104" s="52"/>
+      <c r="L104" s="52"/>
+      <c r="M104" s="52"/>
+      <c r="N104" s="52"/>
+      <c r="O104" s="52"/>
+      <c r="P104" s="52"/>
+      <c r="Q104" s="52"/>
+      <c r="R104" s="52"/>
+      <c r="S104" s="52"/>
+      <c r="T104" s="52"/>
+      <c r="U104" s="52"/>
+      <c r="V104" s="52"/>
+      <c r="W104" s="52"/>
+      <c r="X104" s="52"/>
+      <c r="Y104" s="52"/>
+      <c r="Z104" s="52"/>
+      <c r="AA104" s="52"/>
+      <c r="AB104" s="53"/>
       <c r="AC104" s="11"/>
     </row>
     <row r="105" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4984,27 +5008,27 @@
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
-      <c r="H105" s="49"/>
-      <c r="I105" s="50"/>
-      <c r="J105" s="50"/>
-      <c r="K105" s="50"/>
-      <c r="L105" s="50"/>
-      <c r="M105" s="50"/>
-      <c r="N105" s="50"/>
-      <c r="O105" s="50"/>
-      <c r="P105" s="50"/>
-      <c r="Q105" s="50"/>
-      <c r="R105" s="50"/>
-      <c r="S105" s="50"/>
-      <c r="T105" s="50"/>
-      <c r="U105" s="50"/>
-      <c r="V105" s="50"/>
-      <c r="W105" s="50"/>
-      <c r="X105" s="50"/>
-      <c r="Y105" s="50"/>
-      <c r="Z105" s="50"/>
-      <c r="AA105" s="50"/>
-      <c r="AB105" s="51"/>
+      <c r="H105" s="51"/>
+      <c r="I105" s="52"/>
+      <c r="J105" s="52"/>
+      <c r="K105" s="52"/>
+      <c r="L105" s="52"/>
+      <c r="M105" s="52"/>
+      <c r="N105" s="52"/>
+      <c r="O105" s="52"/>
+      <c r="P105" s="52"/>
+      <c r="Q105" s="52"/>
+      <c r="R105" s="52"/>
+      <c r="S105" s="52"/>
+      <c r="T105" s="52"/>
+      <c r="U105" s="52"/>
+      <c r="V105" s="52"/>
+      <c r="W105" s="52"/>
+      <c r="X105" s="52"/>
+      <c r="Y105" s="52"/>
+      <c r="Z105" s="52"/>
+      <c r="AA105" s="52"/>
+      <c r="AB105" s="53"/>
       <c r="AC105" s="11"/>
     </row>
     <row r="106" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5014,27 +5038,27 @@
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
-      <c r="H106" s="49"/>
-      <c r="I106" s="50"/>
-      <c r="J106" s="50"/>
-      <c r="K106" s="50"/>
-      <c r="L106" s="50"/>
-      <c r="M106" s="50"/>
-      <c r="N106" s="50"/>
-      <c r="O106" s="50"/>
-      <c r="P106" s="50"/>
-      <c r="Q106" s="50"/>
-      <c r="R106" s="50"/>
-      <c r="S106" s="50"/>
-      <c r="T106" s="50"/>
-      <c r="U106" s="50"/>
-      <c r="V106" s="50"/>
-      <c r="W106" s="50"/>
-      <c r="X106" s="50"/>
-      <c r="Y106" s="50"/>
-      <c r="Z106" s="50"/>
-      <c r="AA106" s="50"/>
-      <c r="AB106" s="51"/>
+      <c r="H106" s="51"/>
+      <c r="I106" s="52"/>
+      <c r="J106" s="52"/>
+      <c r="K106" s="52"/>
+      <c r="L106" s="52"/>
+      <c r="M106" s="52"/>
+      <c r="N106" s="52"/>
+      <c r="O106" s="52"/>
+      <c r="P106" s="52"/>
+      <c r="Q106" s="52"/>
+      <c r="R106" s="52"/>
+      <c r="S106" s="52"/>
+      <c r="T106" s="52"/>
+      <c r="U106" s="52"/>
+      <c r="V106" s="52"/>
+      <c r="W106" s="52"/>
+      <c r="X106" s="52"/>
+      <c r="Y106" s="52"/>
+      <c r="Z106" s="52"/>
+      <c r="AA106" s="52"/>
+      <c r="AB106" s="53"/>
       <c r="AC106" s="11"/>
     </row>
     <row r="107" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5044,27 +5068,27 @@
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
-      <c r="H107" s="49"/>
-      <c r="I107" s="50"/>
-      <c r="J107" s="50"/>
-      <c r="K107" s="50"/>
-      <c r="L107" s="50"/>
-      <c r="M107" s="50"/>
-      <c r="N107" s="50"/>
-      <c r="O107" s="50"/>
-      <c r="P107" s="50"/>
-      <c r="Q107" s="50"/>
-      <c r="R107" s="50"/>
-      <c r="S107" s="50"/>
-      <c r="T107" s="50"/>
-      <c r="U107" s="50"/>
-      <c r="V107" s="50"/>
-      <c r="W107" s="50"/>
-      <c r="X107" s="50"/>
-      <c r="Y107" s="50"/>
-      <c r="Z107" s="50"/>
-      <c r="AA107" s="50"/>
-      <c r="AB107" s="51"/>
+      <c r="H107" s="51"/>
+      <c r="I107" s="52"/>
+      <c r="J107" s="52"/>
+      <c r="K107" s="52"/>
+      <c r="L107" s="52"/>
+      <c r="M107" s="52"/>
+      <c r="N107" s="52"/>
+      <c r="O107" s="52"/>
+      <c r="P107" s="52"/>
+      <c r="Q107" s="52"/>
+      <c r="R107" s="52"/>
+      <c r="S107" s="52"/>
+      <c r="T107" s="52"/>
+      <c r="U107" s="52"/>
+      <c r="V107" s="52"/>
+      <c r="W107" s="52"/>
+      <c r="X107" s="52"/>
+      <c r="Y107" s="52"/>
+      <c r="Z107" s="52"/>
+      <c r="AA107" s="52"/>
+      <c r="AB107" s="53"/>
       <c r="AC107" s="11"/>
     </row>
     <row r="108" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5074,27 +5098,27 @@
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
-      <c r="H108" s="49"/>
-      <c r="I108" s="50"/>
-      <c r="J108" s="50"/>
-      <c r="K108" s="50"/>
-      <c r="L108" s="50"/>
-      <c r="M108" s="50"/>
-      <c r="N108" s="50"/>
-      <c r="O108" s="50"/>
-      <c r="P108" s="50"/>
-      <c r="Q108" s="50"/>
-      <c r="R108" s="50"/>
-      <c r="S108" s="50"/>
-      <c r="T108" s="50"/>
-      <c r="U108" s="50"/>
-      <c r="V108" s="50"/>
-      <c r="W108" s="50"/>
-      <c r="X108" s="50"/>
-      <c r="Y108" s="50"/>
-      <c r="Z108" s="50"/>
-      <c r="AA108" s="50"/>
-      <c r="AB108" s="51"/>
+      <c r="H108" s="51"/>
+      <c r="I108" s="52"/>
+      <c r="J108" s="52"/>
+      <c r="K108" s="52"/>
+      <c r="L108" s="52"/>
+      <c r="M108" s="52"/>
+      <c r="N108" s="52"/>
+      <c r="O108" s="52"/>
+      <c r="P108" s="52"/>
+      <c r="Q108" s="52"/>
+      <c r="R108" s="52"/>
+      <c r="S108" s="52"/>
+      <c r="T108" s="52"/>
+      <c r="U108" s="52"/>
+      <c r="V108" s="52"/>
+      <c r="W108" s="52"/>
+      <c r="X108" s="52"/>
+      <c r="Y108" s="52"/>
+      <c r="Z108" s="52"/>
+      <c r="AA108" s="52"/>
+      <c r="AB108" s="53"/>
       <c r="AC108" s="11"/>
     </row>
     <row r="109" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5104,27 +5128,27 @@
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
-      <c r="H109" s="52"/>
-      <c r="I109" s="53"/>
-      <c r="J109" s="53"/>
-      <c r="K109" s="53"/>
-      <c r="L109" s="53"/>
-      <c r="M109" s="53"/>
-      <c r="N109" s="53"/>
-      <c r="O109" s="53"/>
-      <c r="P109" s="53"/>
-      <c r="Q109" s="53"/>
-      <c r="R109" s="53"/>
-      <c r="S109" s="53"/>
-      <c r="T109" s="53"/>
-      <c r="U109" s="53"/>
-      <c r="V109" s="53"/>
-      <c r="W109" s="53"/>
-      <c r="X109" s="53"/>
-      <c r="Y109" s="53"/>
-      <c r="Z109" s="53"/>
-      <c r="AA109" s="53"/>
-      <c r="AB109" s="54"/>
+      <c r="H109" s="54"/>
+      <c r="I109" s="55"/>
+      <c r="J109" s="55"/>
+      <c r="K109" s="55"/>
+      <c r="L109" s="55"/>
+      <c r="M109" s="55"/>
+      <c r="N109" s="55"/>
+      <c r="O109" s="55"/>
+      <c r="P109" s="55"/>
+      <c r="Q109" s="55"/>
+      <c r="R109" s="55"/>
+      <c r="S109" s="55"/>
+      <c r="T109" s="55"/>
+      <c r="U109" s="55"/>
+      <c r="V109" s="55"/>
+      <c r="W109" s="55"/>
+      <c r="X109" s="55"/>
+      <c r="Y109" s="55"/>
+      <c r="Z109" s="55"/>
+      <c r="AA109" s="55"/>
+      <c r="AB109" s="56"/>
       <c r="AC109" s="11"/>
     </row>
     <row r="110" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5166,27 +5190,27 @@
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
-      <c r="H111" s="46"/>
-      <c r="I111" s="47"/>
-      <c r="J111" s="47"/>
-      <c r="K111" s="47"/>
-      <c r="L111" s="47"/>
-      <c r="M111" s="47"/>
-      <c r="N111" s="47"/>
-      <c r="O111" s="47"/>
-      <c r="P111" s="47"/>
-      <c r="Q111" s="47"/>
-      <c r="R111" s="47"/>
-      <c r="S111" s="47"/>
-      <c r="T111" s="47"/>
-      <c r="U111" s="47"/>
-      <c r="V111" s="47"/>
-      <c r="W111" s="47"/>
-      <c r="X111" s="47"/>
-      <c r="Y111" s="47"/>
-      <c r="Z111" s="47"/>
-      <c r="AA111" s="47"/>
-      <c r="AB111" s="48"/>
+      <c r="H111" s="48"/>
+      <c r="I111" s="49"/>
+      <c r="J111" s="49"/>
+      <c r="K111" s="49"/>
+      <c r="L111" s="49"/>
+      <c r="M111" s="49"/>
+      <c r="N111" s="49"/>
+      <c r="O111" s="49"/>
+      <c r="P111" s="49"/>
+      <c r="Q111" s="49"/>
+      <c r="R111" s="49"/>
+      <c r="S111" s="49"/>
+      <c r="T111" s="49"/>
+      <c r="U111" s="49"/>
+      <c r="V111" s="49"/>
+      <c r="W111" s="49"/>
+      <c r="X111" s="49"/>
+      <c r="Y111" s="49"/>
+      <c r="Z111" s="49"/>
+      <c r="AA111" s="49"/>
+      <c r="AB111" s="50"/>
       <c r="AC111" s="11"/>
     </row>
     <row r="112" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5196,27 +5220,27 @@
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
-      <c r="H112" s="49"/>
-      <c r="I112" s="50"/>
-      <c r="J112" s="50"/>
-      <c r="K112" s="50"/>
-      <c r="L112" s="50"/>
-      <c r="M112" s="50"/>
-      <c r="N112" s="50"/>
-      <c r="O112" s="50"/>
-      <c r="P112" s="50"/>
-      <c r="Q112" s="50"/>
-      <c r="R112" s="50"/>
-      <c r="S112" s="50"/>
-      <c r="T112" s="50"/>
-      <c r="U112" s="50"/>
-      <c r="V112" s="50"/>
-      <c r="W112" s="50"/>
-      <c r="X112" s="50"/>
-      <c r="Y112" s="50"/>
-      <c r="Z112" s="50"/>
-      <c r="AA112" s="50"/>
-      <c r="AB112" s="51"/>
+      <c r="H112" s="51"/>
+      <c r="I112" s="52"/>
+      <c r="J112" s="52"/>
+      <c r="K112" s="52"/>
+      <c r="L112" s="52"/>
+      <c r="M112" s="52"/>
+      <c r="N112" s="52"/>
+      <c r="O112" s="52"/>
+      <c r="P112" s="52"/>
+      <c r="Q112" s="52"/>
+      <c r="R112" s="52"/>
+      <c r="S112" s="52"/>
+      <c r="T112" s="52"/>
+      <c r="U112" s="52"/>
+      <c r="V112" s="52"/>
+      <c r="W112" s="52"/>
+      <c r="X112" s="52"/>
+      <c r="Y112" s="52"/>
+      <c r="Z112" s="52"/>
+      <c r="AA112" s="52"/>
+      <c r="AB112" s="53"/>
       <c r="AC112" s="11"/>
     </row>
     <row r="113" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5226,27 +5250,27 @@
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
-      <c r="H113" s="49"/>
-      <c r="I113" s="50"/>
-      <c r="J113" s="50"/>
-      <c r="K113" s="50"/>
-      <c r="L113" s="50"/>
-      <c r="M113" s="50"/>
-      <c r="N113" s="50"/>
-      <c r="O113" s="50"/>
-      <c r="P113" s="50"/>
-      <c r="Q113" s="50"/>
-      <c r="R113" s="50"/>
-      <c r="S113" s="50"/>
-      <c r="T113" s="50"/>
-      <c r="U113" s="50"/>
-      <c r="V113" s="50"/>
-      <c r="W113" s="50"/>
-      <c r="X113" s="50"/>
-      <c r="Y113" s="50"/>
-      <c r="Z113" s="50"/>
-      <c r="AA113" s="50"/>
-      <c r="AB113" s="51"/>
+      <c r="H113" s="51"/>
+      <c r="I113" s="52"/>
+      <c r="J113" s="52"/>
+      <c r="K113" s="52"/>
+      <c r="L113" s="52"/>
+      <c r="M113" s="52"/>
+      <c r="N113" s="52"/>
+      <c r="O113" s="52"/>
+      <c r="P113" s="52"/>
+      <c r="Q113" s="52"/>
+      <c r="R113" s="52"/>
+      <c r="S113" s="52"/>
+      <c r="T113" s="52"/>
+      <c r="U113" s="52"/>
+      <c r="V113" s="52"/>
+      <c r="W113" s="52"/>
+      <c r="X113" s="52"/>
+      <c r="Y113" s="52"/>
+      <c r="Z113" s="52"/>
+      <c r="AA113" s="52"/>
+      <c r="AB113" s="53"/>
       <c r="AC113" s="11"/>
     </row>
     <row r="114" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5256,27 +5280,27 @@
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
-      <c r="H114" s="49"/>
-      <c r="I114" s="50"/>
-      <c r="J114" s="50"/>
-      <c r="K114" s="50"/>
-      <c r="L114" s="50"/>
-      <c r="M114" s="50"/>
-      <c r="N114" s="50"/>
-      <c r="O114" s="50"/>
-      <c r="P114" s="50"/>
-      <c r="Q114" s="50"/>
-      <c r="R114" s="50"/>
-      <c r="S114" s="50"/>
-      <c r="T114" s="50"/>
-      <c r="U114" s="50"/>
-      <c r="V114" s="50"/>
-      <c r="W114" s="50"/>
-      <c r="X114" s="50"/>
-      <c r="Y114" s="50"/>
-      <c r="Z114" s="50"/>
-      <c r="AA114" s="50"/>
-      <c r="AB114" s="51"/>
+      <c r="H114" s="51"/>
+      <c r="I114" s="52"/>
+      <c r="J114" s="52"/>
+      <c r="K114" s="52"/>
+      <c r="L114" s="52"/>
+      <c r="M114" s="52"/>
+      <c r="N114" s="52"/>
+      <c r="O114" s="52"/>
+      <c r="P114" s="52"/>
+      <c r="Q114" s="52"/>
+      <c r="R114" s="52"/>
+      <c r="S114" s="52"/>
+      <c r="T114" s="52"/>
+      <c r="U114" s="52"/>
+      <c r="V114" s="52"/>
+      <c r="W114" s="52"/>
+      <c r="X114" s="52"/>
+      <c r="Y114" s="52"/>
+      <c r="Z114" s="52"/>
+      <c r="AA114" s="52"/>
+      <c r="AB114" s="53"/>
       <c r="AC114" s="11"/>
     </row>
     <row r="115" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5286,27 +5310,27 @@
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
-      <c r="H115" s="49"/>
-      <c r="I115" s="50"/>
-      <c r="J115" s="50"/>
-      <c r="K115" s="50"/>
-      <c r="L115" s="50"/>
-      <c r="M115" s="50"/>
-      <c r="N115" s="50"/>
-      <c r="O115" s="50"/>
-      <c r="P115" s="50"/>
-      <c r="Q115" s="50"/>
-      <c r="R115" s="50"/>
-      <c r="S115" s="50"/>
-      <c r="T115" s="50"/>
-      <c r="U115" s="50"/>
-      <c r="V115" s="50"/>
-      <c r="W115" s="50"/>
-      <c r="X115" s="50"/>
-      <c r="Y115" s="50"/>
-      <c r="Z115" s="50"/>
-      <c r="AA115" s="50"/>
-      <c r="AB115" s="51"/>
+      <c r="H115" s="51"/>
+      <c r="I115" s="52"/>
+      <c r="J115" s="52"/>
+      <c r="K115" s="52"/>
+      <c r="L115" s="52"/>
+      <c r="M115" s="52"/>
+      <c r="N115" s="52"/>
+      <c r="O115" s="52"/>
+      <c r="P115" s="52"/>
+      <c r="Q115" s="52"/>
+      <c r="R115" s="52"/>
+      <c r="S115" s="52"/>
+      <c r="T115" s="52"/>
+      <c r="U115" s="52"/>
+      <c r="V115" s="52"/>
+      <c r="W115" s="52"/>
+      <c r="X115" s="52"/>
+      <c r="Y115" s="52"/>
+      <c r="Z115" s="52"/>
+      <c r="AA115" s="52"/>
+      <c r="AB115" s="53"/>
       <c r="AC115" s="11"/>
     </row>
     <row r="116" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5316,27 +5340,27 @@
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
-      <c r="H116" s="49"/>
-      <c r="I116" s="50"/>
-      <c r="J116" s="50"/>
-      <c r="K116" s="50"/>
-      <c r="L116" s="50"/>
-      <c r="M116" s="50"/>
-      <c r="N116" s="50"/>
-      <c r="O116" s="50"/>
-      <c r="P116" s="50"/>
-      <c r="Q116" s="50"/>
-      <c r="R116" s="50"/>
-      <c r="S116" s="50"/>
-      <c r="T116" s="50"/>
-      <c r="U116" s="50"/>
-      <c r="V116" s="50"/>
-      <c r="W116" s="50"/>
-      <c r="X116" s="50"/>
-      <c r="Y116" s="50"/>
-      <c r="Z116" s="50"/>
-      <c r="AA116" s="50"/>
-      <c r="AB116" s="51"/>
+      <c r="H116" s="51"/>
+      <c r="I116" s="52"/>
+      <c r="J116" s="52"/>
+      <c r="K116" s="52"/>
+      <c r="L116" s="52"/>
+      <c r="M116" s="52"/>
+      <c r="N116" s="52"/>
+      <c r="O116" s="52"/>
+      <c r="P116" s="52"/>
+      <c r="Q116" s="52"/>
+      <c r="R116" s="52"/>
+      <c r="S116" s="52"/>
+      <c r="T116" s="52"/>
+      <c r="U116" s="52"/>
+      <c r="V116" s="52"/>
+      <c r="W116" s="52"/>
+      <c r="X116" s="52"/>
+      <c r="Y116" s="52"/>
+      <c r="Z116" s="52"/>
+      <c r="AA116" s="52"/>
+      <c r="AB116" s="53"/>
       <c r="AC116" s="11"/>
     </row>
     <row r="117" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5346,27 +5370,27 @@
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
-      <c r="H117" s="52"/>
-      <c r="I117" s="53"/>
-      <c r="J117" s="53"/>
-      <c r="K117" s="53"/>
-      <c r="L117" s="53"/>
-      <c r="M117" s="53"/>
-      <c r="N117" s="53"/>
-      <c r="O117" s="53"/>
-      <c r="P117" s="53"/>
-      <c r="Q117" s="53"/>
-      <c r="R117" s="53"/>
-      <c r="S117" s="53"/>
-      <c r="T117" s="53"/>
-      <c r="U117" s="53"/>
-      <c r="V117" s="53"/>
-      <c r="W117" s="53"/>
-      <c r="X117" s="53"/>
-      <c r="Y117" s="53"/>
-      <c r="Z117" s="53"/>
-      <c r="AA117" s="53"/>
-      <c r="AB117" s="54"/>
+      <c r="H117" s="54"/>
+      <c r="I117" s="55"/>
+      <c r="J117" s="55"/>
+      <c r="K117" s="55"/>
+      <c r="L117" s="55"/>
+      <c r="M117" s="55"/>
+      <c r="N117" s="55"/>
+      <c r="O117" s="55"/>
+      <c r="P117" s="55"/>
+      <c r="Q117" s="55"/>
+      <c r="R117" s="55"/>
+      <c r="S117" s="55"/>
+      <c r="T117" s="55"/>
+      <c r="U117" s="55"/>
+      <c r="V117" s="55"/>
+      <c r="W117" s="55"/>
+      <c r="X117" s="55"/>
+      <c r="Y117" s="55"/>
+      <c r="Z117" s="55"/>
+      <c r="AA117" s="55"/>
+      <c r="AB117" s="56"/>
       <c r="AC117" s="11"/>
     </row>
     <row r="118" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5474,27 +5498,27 @@
         <v>2</v>
       </c>
       <c r="G122" s="6"/>
-      <c r="H122" s="46"/>
-      <c r="I122" s="47"/>
-      <c r="J122" s="47"/>
-      <c r="K122" s="47"/>
-      <c r="L122" s="47"/>
-      <c r="M122" s="47"/>
-      <c r="N122" s="47"/>
-      <c r="O122" s="47"/>
-      <c r="P122" s="47"/>
-      <c r="Q122" s="47"/>
-      <c r="R122" s="47"/>
-      <c r="S122" s="47"/>
-      <c r="T122" s="47"/>
-      <c r="U122" s="47"/>
-      <c r="V122" s="47"/>
-      <c r="W122" s="47"/>
-      <c r="X122" s="47"/>
-      <c r="Y122" s="47"/>
-      <c r="Z122" s="47"/>
-      <c r="AA122" s="47"/>
-      <c r="AB122" s="48"/>
+      <c r="H122" s="48"/>
+      <c r="I122" s="49"/>
+      <c r="J122" s="49"/>
+      <c r="K122" s="49"/>
+      <c r="L122" s="49"/>
+      <c r="M122" s="49"/>
+      <c r="N122" s="49"/>
+      <c r="O122" s="49"/>
+      <c r="P122" s="49"/>
+      <c r="Q122" s="49"/>
+      <c r="R122" s="49"/>
+      <c r="S122" s="49"/>
+      <c r="T122" s="49"/>
+      <c r="U122" s="49"/>
+      <c r="V122" s="49"/>
+      <c r="W122" s="49"/>
+      <c r="X122" s="49"/>
+      <c r="Y122" s="49"/>
+      <c r="Z122" s="49"/>
+      <c r="AA122" s="49"/>
+      <c r="AB122" s="50"/>
       <c r="AC122" s="11"/>
     </row>
     <row r="123" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5504,27 +5528,27 @@
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
-      <c r="H123" s="49"/>
-      <c r="I123" s="50"/>
-      <c r="J123" s="50"/>
-      <c r="K123" s="50"/>
-      <c r="L123" s="50"/>
-      <c r="M123" s="50"/>
-      <c r="N123" s="50"/>
-      <c r="O123" s="50"/>
-      <c r="P123" s="50"/>
-      <c r="Q123" s="50"/>
-      <c r="R123" s="50"/>
-      <c r="S123" s="50"/>
-      <c r="T123" s="50"/>
-      <c r="U123" s="50"/>
-      <c r="V123" s="50"/>
-      <c r="W123" s="50"/>
-      <c r="X123" s="50"/>
-      <c r="Y123" s="50"/>
-      <c r="Z123" s="50"/>
-      <c r="AA123" s="50"/>
-      <c r="AB123" s="51"/>
+      <c r="H123" s="51"/>
+      <c r="I123" s="52"/>
+      <c r="J123" s="52"/>
+      <c r="K123" s="52"/>
+      <c r="L123" s="52"/>
+      <c r="M123" s="52"/>
+      <c r="N123" s="52"/>
+      <c r="O123" s="52"/>
+      <c r="P123" s="52"/>
+      <c r="Q123" s="52"/>
+      <c r="R123" s="52"/>
+      <c r="S123" s="52"/>
+      <c r="T123" s="52"/>
+      <c r="U123" s="52"/>
+      <c r="V123" s="52"/>
+      <c r="W123" s="52"/>
+      <c r="X123" s="52"/>
+      <c r="Y123" s="52"/>
+      <c r="Z123" s="52"/>
+      <c r="AA123" s="52"/>
+      <c r="AB123" s="53"/>
       <c r="AC123" s="11"/>
     </row>
     <row r="124" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5534,27 +5558,27 @@
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
-      <c r="H124" s="49"/>
-      <c r="I124" s="50"/>
-      <c r="J124" s="50"/>
-      <c r="K124" s="50"/>
-      <c r="L124" s="50"/>
-      <c r="M124" s="50"/>
-      <c r="N124" s="50"/>
-      <c r="O124" s="50"/>
-      <c r="P124" s="50"/>
-      <c r="Q124" s="50"/>
-      <c r="R124" s="50"/>
-      <c r="S124" s="50"/>
-      <c r="T124" s="50"/>
-      <c r="U124" s="50"/>
-      <c r="V124" s="50"/>
-      <c r="W124" s="50"/>
-      <c r="X124" s="50"/>
-      <c r="Y124" s="50"/>
-      <c r="Z124" s="50"/>
-      <c r="AA124" s="50"/>
-      <c r="AB124" s="51"/>
+      <c r="H124" s="51"/>
+      <c r="I124" s="52"/>
+      <c r="J124" s="52"/>
+      <c r="K124" s="52"/>
+      <c r="L124" s="52"/>
+      <c r="M124" s="52"/>
+      <c r="N124" s="52"/>
+      <c r="O124" s="52"/>
+      <c r="P124" s="52"/>
+      <c r="Q124" s="52"/>
+      <c r="R124" s="52"/>
+      <c r="S124" s="52"/>
+      <c r="T124" s="52"/>
+      <c r="U124" s="52"/>
+      <c r="V124" s="52"/>
+      <c r="W124" s="52"/>
+      <c r="X124" s="52"/>
+      <c r="Y124" s="52"/>
+      <c r="Z124" s="52"/>
+      <c r="AA124" s="52"/>
+      <c r="AB124" s="53"/>
       <c r="AC124" s="11"/>
     </row>
     <row r="125" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5564,27 +5588,27 @@
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
-      <c r="H125" s="49"/>
-      <c r="I125" s="50"/>
-      <c r="J125" s="50"/>
-      <c r="K125" s="50"/>
-      <c r="L125" s="50"/>
-      <c r="M125" s="50"/>
-      <c r="N125" s="50"/>
-      <c r="O125" s="50"/>
-      <c r="P125" s="50"/>
-      <c r="Q125" s="50"/>
-      <c r="R125" s="50"/>
-      <c r="S125" s="50"/>
-      <c r="T125" s="50"/>
-      <c r="U125" s="50"/>
-      <c r="V125" s="50"/>
-      <c r="W125" s="50"/>
-      <c r="X125" s="50"/>
-      <c r="Y125" s="50"/>
-      <c r="Z125" s="50"/>
-      <c r="AA125" s="50"/>
-      <c r="AB125" s="51"/>
+      <c r="H125" s="51"/>
+      <c r="I125" s="52"/>
+      <c r="J125" s="52"/>
+      <c r="K125" s="52"/>
+      <c r="L125" s="52"/>
+      <c r="M125" s="52"/>
+      <c r="N125" s="52"/>
+      <c r="O125" s="52"/>
+      <c r="P125" s="52"/>
+      <c r="Q125" s="52"/>
+      <c r="R125" s="52"/>
+      <c r="S125" s="52"/>
+      <c r="T125" s="52"/>
+      <c r="U125" s="52"/>
+      <c r="V125" s="52"/>
+      <c r="W125" s="52"/>
+      <c r="X125" s="52"/>
+      <c r="Y125" s="52"/>
+      <c r="Z125" s="52"/>
+      <c r="AA125" s="52"/>
+      <c r="AB125" s="53"/>
       <c r="AC125" s="11"/>
     </row>
     <row r="126" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5594,27 +5618,27 @@
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
-      <c r="H126" s="49"/>
-      <c r="I126" s="50"/>
-      <c r="J126" s="50"/>
-      <c r="K126" s="50"/>
-      <c r="L126" s="50"/>
-      <c r="M126" s="50"/>
-      <c r="N126" s="50"/>
-      <c r="O126" s="50"/>
-      <c r="P126" s="50"/>
-      <c r="Q126" s="50"/>
-      <c r="R126" s="50"/>
-      <c r="S126" s="50"/>
-      <c r="T126" s="50"/>
-      <c r="U126" s="50"/>
-      <c r="V126" s="50"/>
-      <c r="W126" s="50"/>
-      <c r="X126" s="50"/>
-      <c r="Y126" s="50"/>
-      <c r="Z126" s="50"/>
-      <c r="AA126" s="50"/>
-      <c r="AB126" s="51"/>
+      <c r="H126" s="51"/>
+      <c r="I126" s="52"/>
+      <c r="J126" s="52"/>
+      <c r="K126" s="52"/>
+      <c r="L126" s="52"/>
+      <c r="M126" s="52"/>
+      <c r="N126" s="52"/>
+      <c r="O126" s="52"/>
+      <c r="P126" s="52"/>
+      <c r="Q126" s="52"/>
+      <c r="R126" s="52"/>
+      <c r="S126" s="52"/>
+      <c r="T126" s="52"/>
+      <c r="U126" s="52"/>
+      <c r="V126" s="52"/>
+      <c r="W126" s="52"/>
+      <c r="X126" s="52"/>
+      <c r="Y126" s="52"/>
+      <c r="Z126" s="52"/>
+      <c r="AA126" s="52"/>
+      <c r="AB126" s="53"/>
       <c r="AC126" s="11"/>
     </row>
     <row r="127" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5624,27 +5648,27 @@
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
-      <c r="H127" s="49"/>
-      <c r="I127" s="50"/>
-      <c r="J127" s="50"/>
-      <c r="K127" s="50"/>
-      <c r="L127" s="50"/>
-      <c r="M127" s="50"/>
-      <c r="N127" s="50"/>
-      <c r="O127" s="50"/>
-      <c r="P127" s="50"/>
-      <c r="Q127" s="50"/>
-      <c r="R127" s="50"/>
-      <c r="S127" s="50"/>
-      <c r="T127" s="50"/>
-      <c r="U127" s="50"/>
-      <c r="V127" s="50"/>
-      <c r="W127" s="50"/>
-      <c r="X127" s="50"/>
-      <c r="Y127" s="50"/>
-      <c r="Z127" s="50"/>
-      <c r="AA127" s="50"/>
-      <c r="AB127" s="51"/>
+      <c r="H127" s="51"/>
+      <c r="I127" s="52"/>
+      <c r="J127" s="52"/>
+      <c r="K127" s="52"/>
+      <c r="L127" s="52"/>
+      <c r="M127" s="52"/>
+      <c r="N127" s="52"/>
+      <c r="O127" s="52"/>
+      <c r="P127" s="52"/>
+      <c r="Q127" s="52"/>
+      <c r="R127" s="52"/>
+      <c r="S127" s="52"/>
+      <c r="T127" s="52"/>
+      <c r="U127" s="52"/>
+      <c r="V127" s="52"/>
+      <c r="W127" s="52"/>
+      <c r="X127" s="52"/>
+      <c r="Y127" s="52"/>
+      <c r="Z127" s="52"/>
+      <c r="AA127" s="52"/>
+      <c r="AB127" s="53"/>
       <c r="AC127" s="11"/>
     </row>
     <row r="128" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5654,27 +5678,27 @@
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
-      <c r="H128" s="52"/>
-      <c r="I128" s="53"/>
-      <c r="J128" s="53"/>
-      <c r="K128" s="53"/>
-      <c r="L128" s="53"/>
-      <c r="M128" s="53"/>
-      <c r="N128" s="53"/>
-      <c r="O128" s="53"/>
-      <c r="P128" s="53"/>
-      <c r="Q128" s="53"/>
-      <c r="R128" s="53"/>
-      <c r="S128" s="53"/>
-      <c r="T128" s="53"/>
-      <c r="U128" s="53"/>
-      <c r="V128" s="53"/>
-      <c r="W128" s="53"/>
-      <c r="X128" s="53"/>
-      <c r="Y128" s="53"/>
-      <c r="Z128" s="53"/>
-      <c r="AA128" s="53"/>
-      <c r="AB128" s="54"/>
+      <c r="H128" s="54"/>
+      <c r="I128" s="55"/>
+      <c r="J128" s="55"/>
+      <c r="K128" s="55"/>
+      <c r="L128" s="55"/>
+      <c r="M128" s="55"/>
+      <c r="N128" s="55"/>
+      <c r="O128" s="55"/>
+      <c r="P128" s="55"/>
+      <c r="Q128" s="55"/>
+      <c r="R128" s="55"/>
+      <c r="S128" s="55"/>
+      <c r="T128" s="55"/>
+      <c r="U128" s="55"/>
+      <c r="V128" s="55"/>
+      <c r="W128" s="55"/>
+      <c r="X128" s="55"/>
+      <c r="Y128" s="55"/>
+      <c r="Z128" s="55"/>
+      <c r="AA128" s="55"/>
+      <c r="AB128" s="56"/>
       <c r="AC128" s="11"/>
     </row>
     <row r="129" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5716,27 +5740,27 @@
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
-      <c r="H130" s="46"/>
-      <c r="I130" s="47"/>
-      <c r="J130" s="47"/>
-      <c r="K130" s="47"/>
-      <c r="L130" s="47"/>
-      <c r="M130" s="47"/>
-      <c r="N130" s="47"/>
-      <c r="O130" s="47"/>
-      <c r="P130" s="47"/>
-      <c r="Q130" s="47"/>
-      <c r="R130" s="47"/>
-      <c r="S130" s="47"/>
-      <c r="T130" s="47"/>
-      <c r="U130" s="47"/>
-      <c r="V130" s="47"/>
-      <c r="W130" s="47"/>
-      <c r="X130" s="47"/>
-      <c r="Y130" s="47"/>
-      <c r="Z130" s="47"/>
-      <c r="AA130" s="47"/>
-      <c r="AB130" s="48"/>
+      <c r="H130" s="48"/>
+      <c r="I130" s="49"/>
+      <c r="J130" s="49"/>
+      <c r="K130" s="49"/>
+      <c r="L130" s="49"/>
+      <c r="M130" s="49"/>
+      <c r="N130" s="49"/>
+      <c r="O130" s="49"/>
+      <c r="P130" s="49"/>
+      <c r="Q130" s="49"/>
+      <c r="R130" s="49"/>
+      <c r="S130" s="49"/>
+      <c r="T130" s="49"/>
+      <c r="U130" s="49"/>
+      <c r="V130" s="49"/>
+      <c r="W130" s="49"/>
+      <c r="X130" s="49"/>
+      <c r="Y130" s="49"/>
+      <c r="Z130" s="49"/>
+      <c r="AA130" s="49"/>
+      <c r="AB130" s="50"/>
       <c r="AC130" s="11"/>
     </row>
     <row r="131" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5746,27 +5770,27 @@
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
-      <c r="H131" s="49"/>
-      <c r="I131" s="50"/>
-      <c r="J131" s="50"/>
-      <c r="K131" s="50"/>
-      <c r="L131" s="50"/>
-      <c r="M131" s="50"/>
-      <c r="N131" s="50"/>
-      <c r="O131" s="50"/>
-      <c r="P131" s="50"/>
-      <c r="Q131" s="50"/>
-      <c r="R131" s="50"/>
-      <c r="S131" s="50"/>
-      <c r="T131" s="50"/>
-      <c r="U131" s="50"/>
-      <c r="V131" s="50"/>
-      <c r="W131" s="50"/>
-      <c r="X131" s="50"/>
-      <c r="Y131" s="50"/>
-      <c r="Z131" s="50"/>
-      <c r="AA131" s="50"/>
-      <c r="AB131" s="51"/>
+      <c r="H131" s="51"/>
+      <c r="I131" s="52"/>
+      <c r="J131" s="52"/>
+      <c r="K131" s="52"/>
+      <c r="L131" s="52"/>
+      <c r="M131" s="52"/>
+      <c r="N131" s="52"/>
+      <c r="O131" s="52"/>
+      <c r="P131" s="52"/>
+      <c r="Q131" s="52"/>
+      <c r="R131" s="52"/>
+      <c r="S131" s="52"/>
+      <c r="T131" s="52"/>
+      <c r="U131" s="52"/>
+      <c r="V131" s="52"/>
+      <c r="W131" s="52"/>
+      <c r="X131" s="52"/>
+      <c r="Y131" s="52"/>
+      <c r="Z131" s="52"/>
+      <c r="AA131" s="52"/>
+      <c r="AB131" s="53"/>
       <c r="AC131" s="11"/>
     </row>
     <row r="132" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5776,27 +5800,27 @@
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
-      <c r="H132" s="49"/>
-      <c r="I132" s="50"/>
-      <c r="J132" s="50"/>
-      <c r="K132" s="50"/>
-      <c r="L132" s="50"/>
-      <c r="M132" s="50"/>
-      <c r="N132" s="50"/>
-      <c r="O132" s="50"/>
-      <c r="P132" s="50"/>
-      <c r="Q132" s="50"/>
-      <c r="R132" s="50"/>
-      <c r="S132" s="50"/>
-      <c r="T132" s="50"/>
-      <c r="U132" s="50"/>
-      <c r="V132" s="50"/>
-      <c r="W132" s="50"/>
-      <c r="X132" s="50"/>
-      <c r="Y132" s="50"/>
-      <c r="Z132" s="50"/>
-      <c r="AA132" s="50"/>
-      <c r="AB132" s="51"/>
+      <c r="H132" s="51"/>
+      <c r="I132" s="52"/>
+      <c r="J132" s="52"/>
+      <c r="K132" s="52"/>
+      <c r="L132" s="52"/>
+      <c r="M132" s="52"/>
+      <c r="N132" s="52"/>
+      <c r="O132" s="52"/>
+      <c r="P132" s="52"/>
+      <c r="Q132" s="52"/>
+      <c r="R132" s="52"/>
+      <c r="S132" s="52"/>
+      <c r="T132" s="52"/>
+      <c r="U132" s="52"/>
+      <c r="V132" s="52"/>
+      <c r="W132" s="52"/>
+      <c r="X132" s="52"/>
+      <c r="Y132" s="52"/>
+      <c r="Z132" s="52"/>
+      <c r="AA132" s="52"/>
+      <c r="AB132" s="53"/>
       <c r="AC132" s="11"/>
     </row>
     <row r="133" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5806,27 +5830,27 @@
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="49"/>
-      <c r="I133" s="50"/>
-      <c r="J133" s="50"/>
-      <c r="K133" s="50"/>
-      <c r="L133" s="50"/>
-      <c r="M133" s="50"/>
-      <c r="N133" s="50"/>
-      <c r="O133" s="50"/>
-      <c r="P133" s="50"/>
-      <c r="Q133" s="50"/>
-      <c r="R133" s="50"/>
-      <c r="S133" s="50"/>
-      <c r="T133" s="50"/>
-      <c r="U133" s="50"/>
-      <c r="V133" s="50"/>
-      <c r="W133" s="50"/>
-      <c r="X133" s="50"/>
-      <c r="Y133" s="50"/>
-      <c r="Z133" s="50"/>
-      <c r="AA133" s="50"/>
-      <c r="AB133" s="51"/>
+      <c r="H133" s="51"/>
+      <c r="I133" s="52"/>
+      <c r="J133" s="52"/>
+      <c r="K133" s="52"/>
+      <c r="L133" s="52"/>
+      <c r="M133" s="52"/>
+      <c r="N133" s="52"/>
+      <c r="O133" s="52"/>
+      <c r="P133" s="52"/>
+      <c r="Q133" s="52"/>
+      <c r="R133" s="52"/>
+      <c r="S133" s="52"/>
+      <c r="T133" s="52"/>
+      <c r="U133" s="52"/>
+      <c r="V133" s="52"/>
+      <c r="W133" s="52"/>
+      <c r="X133" s="52"/>
+      <c r="Y133" s="52"/>
+      <c r="Z133" s="52"/>
+      <c r="AA133" s="52"/>
+      <c r="AB133" s="53"/>
       <c r="AC133" s="11"/>
     </row>
     <row r="134" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5836,27 +5860,27 @@
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="49"/>
-      <c r="I134" s="50"/>
-      <c r="J134" s="50"/>
-      <c r="K134" s="50"/>
-      <c r="L134" s="50"/>
-      <c r="M134" s="50"/>
-      <c r="N134" s="50"/>
-      <c r="O134" s="50"/>
-      <c r="P134" s="50"/>
-      <c r="Q134" s="50"/>
-      <c r="R134" s="50"/>
-      <c r="S134" s="50"/>
-      <c r="T134" s="50"/>
-      <c r="U134" s="50"/>
-      <c r="V134" s="50"/>
-      <c r="W134" s="50"/>
-      <c r="X134" s="50"/>
-      <c r="Y134" s="50"/>
-      <c r="Z134" s="50"/>
-      <c r="AA134" s="50"/>
-      <c r="AB134" s="51"/>
+      <c r="H134" s="51"/>
+      <c r="I134" s="52"/>
+      <c r="J134" s="52"/>
+      <c r="K134" s="52"/>
+      <c r="L134" s="52"/>
+      <c r="M134" s="52"/>
+      <c r="N134" s="52"/>
+      <c r="O134" s="52"/>
+      <c r="P134" s="52"/>
+      <c r="Q134" s="52"/>
+      <c r="R134" s="52"/>
+      <c r="S134" s="52"/>
+      <c r="T134" s="52"/>
+      <c r="U134" s="52"/>
+      <c r="V134" s="52"/>
+      <c r="W134" s="52"/>
+      <c r="X134" s="52"/>
+      <c r="Y134" s="52"/>
+      <c r="Z134" s="52"/>
+      <c r="AA134" s="52"/>
+      <c r="AB134" s="53"/>
       <c r="AC134" s="11"/>
     </row>
     <row r="135" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5866,27 +5890,27 @@
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="49"/>
-      <c r="I135" s="50"/>
-      <c r="J135" s="50"/>
-      <c r="K135" s="50"/>
-      <c r="L135" s="50"/>
-      <c r="M135" s="50"/>
-      <c r="N135" s="50"/>
-      <c r="O135" s="50"/>
-      <c r="P135" s="50"/>
-      <c r="Q135" s="50"/>
-      <c r="R135" s="50"/>
-      <c r="S135" s="50"/>
-      <c r="T135" s="50"/>
-      <c r="U135" s="50"/>
-      <c r="V135" s="50"/>
-      <c r="W135" s="50"/>
-      <c r="X135" s="50"/>
-      <c r="Y135" s="50"/>
-      <c r="Z135" s="50"/>
-      <c r="AA135" s="50"/>
-      <c r="AB135" s="51"/>
+      <c r="H135" s="51"/>
+      <c r="I135" s="52"/>
+      <c r="J135" s="52"/>
+      <c r="K135" s="52"/>
+      <c r="L135" s="52"/>
+      <c r="M135" s="52"/>
+      <c r="N135" s="52"/>
+      <c r="O135" s="52"/>
+      <c r="P135" s="52"/>
+      <c r="Q135" s="52"/>
+      <c r="R135" s="52"/>
+      <c r="S135" s="52"/>
+      <c r="T135" s="52"/>
+      <c r="U135" s="52"/>
+      <c r="V135" s="52"/>
+      <c r="W135" s="52"/>
+      <c r="X135" s="52"/>
+      <c r="Y135" s="52"/>
+      <c r="Z135" s="52"/>
+      <c r="AA135" s="52"/>
+      <c r="AB135" s="53"/>
       <c r="AC135" s="11"/>
     </row>
     <row r="136" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5896,27 +5920,27 @@
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="52"/>
-      <c r="I136" s="53"/>
-      <c r="J136" s="53"/>
-      <c r="K136" s="53"/>
-      <c r="L136" s="53"/>
-      <c r="M136" s="53"/>
-      <c r="N136" s="53"/>
-      <c r="O136" s="53"/>
-      <c r="P136" s="53"/>
-      <c r="Q136" s="53"/>
-      <c r="R136" s="53"/>
-      <c r="S136" s="53"/>
-      <c r="T136" s="53"/>
-      <c r="U136" s="53"/>
-      <c r="V136" s="53"/>
-      <c r="W136" s="53"/>
-      <c r="X136" s="53"/>
-      <c r="Y136" s="53"/>
-      <c r="Z136" s="53"/>
-      <c r="AA136" s="53"/>
-      <c r="AB136" s="54"/>
+      <c r="H136" s="54"/>
+      <c r="I136" s="55"/>
+      <c r="J136" s="55"/>
+      <c r="K136" s="55"/>
+      <c r="L136" s="55"/>
+      <c r="M136" s="55"/>
+      <c r="N136" s="55"/>
+      <c r="O136" s="55"/>
+      <c r="P136" s="55"/>
+      <c r="Q136" s="55"/>
+      <c r="R136" s="55"/>
+      <c r="S136" s="55"/>
+      <c r="T136" s="55"/>
+      <c r="U136" s="55"/>
+      <c r="V136" s="55"/>
+      <c r="W136" s="55"/>
+      <c r="X136" s="55"/>
+      <c r="Y136" s="55"/>
+      <c r="Z136" s="55"/>
+      <c r="AA136" s="55"/>
+      <c r="AB136" s="56"/>
       <c r="AC136" s="11"/>
     </row>
     <row r="137" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6024,27 +6048,27 @@
         <v>2</v>
       </c>
       <c r="G141" s="6"/>
-      <c r="H141" s="46"/>
-      <c r="I141" s="47"/>
-      <c r="J141" s="47"/>
-      <c r="K141" s="47"/>
-      <c r="L141" s="47"/>
-      <c r="M141" s="47"/>
-      <c r="N141" s="47"/>
-      <c r="O141" s="47"/>
-      <c r="P141" s="47"/>
-      <c r="Q141" s="47"/>
-      <c r="R141" s="47"/>
-      <c r="S141" s="47"/>
-      <c r="T141" s="47"/>
-      <c r="U141" s="47"/>
-      <c r="V141" s="47"/>
-      <c r="W141" s="47"/>
-      <c r="X141" s="47"/>
-      <c r="Y141" s="47"/>
-      <c r="Z141" s="47"/>
-      <c r="AA141" s="47"/>
-      <c r="AB141" s="48"/>
+      <c r="H141" s="48"/>
+      <c r="I141" s="49"/>
+      <c r="J141" s="49"/>
+      <c r="K141" s="49"/>
+      <c r="L141" s="49"/>
+      <c r="M141" s="49"/>
+      <c r="N141" s="49"/>
+      <c r="O141" s="49"/>
+      <c r="P141" s="49"/>
+      <c r="Q141" s="49"/>
+      <c r="R141" s="49"/>
+      <c r="S141" s="49"/>
+      <c r="T141" s="49"/>
+      <c r="U141" s="49"/>
+      <c r="V141" s="49"/>
+      <c r="W141" s="49"/>
+      <c r="X141" s="49"/>
+      <c r="Y141" s="49"/>
+      <c r="Z141" s="49"/>
+      <c r="AA141" s="49"/>
+      <c r="AB141" s="50"/>
       <c r="AC141" s="11"/>
     </row>
     <row r="142" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6054,27 +6078,27 @@
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
-      <c r="H142" s="49"/>
-      <c r="I142" s="50"/>
-      <c r="J142" s="50"/>
-      <c r="K142" s="50"/>
-      <c r="L142" s="50"/>
-      <c r="M142" s="50"/>
-      <c r="N142" s="50"/>
-      <c r="O142" s="50"/>
-      <c r="P142" s="50"/>
-      <c r="Q142" s="50"/>
-      <c r="R142" s="50"/>
-      <c r="S142" s="50"/>
-      <c r="T142" s="50"/>
-      <c r="U142" s="50"/>
-      <c r="V142" s="50"/>
-      <c r="W142" s="50"/>
-      <c r="X142" s="50"/>
-      <c r="Y142" s="50"/>
-      <c r="Z142" s="50"/>
-      <c r="AA142" s="50"/>
-      <c r="AB142" s="51"/>
+      <c r="H142" s="51"/>
+      <c r="I142" s="52"/>
+      <c r="J142" s="52"/>
+      <c r="K142" s="52"/>
+      <c r="L142" s="52"/>
+      <c r="M142" s="52"/>
+      <c r="N142" s="52"/>
+      <c r="O142" s="52"/>
+      <c r="P142" s="52"/>
+      <c r="Q142" s="52"/>
+      <c r="R142" s="52"/>
+      <c r="S142" s="52"/>
+      <c r="T142" s="52"/>
+      <c r="U142" s="52"/>
+      <c r="V142" s="52"/>
+      <c r="W142" s="52"/>
+      <c r="X142" s="52"/>
+      <c r="Y142" s="52"/>
+      <c r="Z142" s="52"/>
+      <c r="AA142" s="52"/>
+      <c r="AB142" s="53"/>
       <c r="AC142" s="11"/>
     </row>
     <row r="143" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6084,27 +6108,27 @@
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
-      <c r="H143" s="49"/>
-      <c r="I143" s="50"/>
-      <c r="J143" s="50"/>
-      <c r="K143" s="50"/>
-      <c r="L143" s="50"/>
-      <c r="M143" s="50"/>
-      <c r="N143" s="50"/>
-      <c r="O143" s="50"/>
-      <c r="P143" s="50"/>
-      <c r="Q143" s="50"/>
-      <c r="R143" s="50"/>
-      <c r="S143" s="50"/>
-      <c r="T143" s="50"/>
-      <c r="U143" s="50"/>
-      <c r="V143" s="50"/>
-      <c r="W143" s="50"/>
-      <c r="X143" s="50"/>
-      <c r="Y143" s="50"/>
-      <c r="Z143" s="50"/>
-      <c r="AA143" s="50"/>
-      <c r="AB143" s="51"/>
+      <c r="H143" s="51"/>
+      <c r="I143" s="52"/>
+      <c r="J143" s="52"/>
+      <c r="K143" s="52"/>
+      <c r="L143" s="52"/>
+      <c r="M143" s="52"/>
+      <c r="N143" s="52"/>
+      <c r="O143" s="52"/>
+      <c r="P143" s="52"/>
+      <c r="Q143" s="52"/>
+      <c r="R143" s="52"/>
+      <c r="S143" s="52"/>
+      <c r="T143" s="52"/>
+      <c r="U143" s="52"/>
+      <c r="V143" s="52"/>
+      <c r="W143" s="52"/>
+      <c r="X143" s="52"/>
+      <c r="Y143" s="52"/>
+      <c r="Z143" s="52"/>
+      <c r="AA143" s="52"/>
+      <c r="AB143" s="53"/>
       <c r="AC143" s="11"/>
     </row>
     <row r="144" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6114,27 +6138,27 @@
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
-      <c r="H144" s="49"/>
-      <c r="I144" s="50"/>
-      <c r="J144" s="50"/>
-      <c r="K144" s="50"/>
-      <c r="L144" s="50"/>
-      <c r="M144" s="50"/>
-      <c r="N144" s="50"/>
-      <c r="O144" s="50"/>
-      <c r="P144" s="50"/>
-      <c r="Q144" s="50"/>
-      <c r="R144" s="50"/>
-      <c r="S144" s="50"/>
-      <c r="T144" s="50"/>
-      <c r="U144" s="50"/>
-      <c r="V144" s="50"/>
-      <c r="W144" s="50"/>
-      <c r="X144" s="50"/>
-      <c r="Y144" s="50"/>
-      <c r="Z144" s="50"/>
-      <c r="AA144" s="50"/>
-      <c r="AB144" s="51"/>
+      <c r="H144" s="51"/>
+      <c r="I144" s="52"/>
+      <c r="J144" s="52"/>
+      <c r="K144" s="52"/>
+      <c r="L144" s="52"/>
+      <c r="M144" s="52"/>
+      <c r="N144" s="52"/>
+      <c r="O144" s="52"/>
+      <c r="P144" s="52"/>
+      <c r="Q144" s="52"/>
+      <c r="R144" s="52"/>
+      <c r="S144" s="52"/>
+      <c r="T144" s="52"/>
+      <c r="U144" s="52"/>
+      <c r="V144" s="52"/>
+      <c r="W144" s="52"/>
+      <c r="X144" s="52"/>
+      <c r="Y144" s="52"/>
+      <c r="Z144" s="52"/>
+      <c r="AA144" s="52"/>
+      <c r="AB144" s="53"/>
       <c r="AC144" s="11"/>
     </row>
     <row r="145" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6144,27 +6168,27 @@
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
-      <c r="H145" s="49"/>
-      <c r="I145" s="50"/>
-      <c r="J145" s="50"/>
-      <c r="K145" s="50"/>
-      <c r="L145" s="50"/>
-      <c r="M145" s="50"/>
-      <c r="N145" s="50"/>
-      <c r="O145" s="50"/>
-      <c r="P145" s="50"/>
-      <c r="Q145" s="50"/>
-      <c r="R145" s="50"/>
-      <c r="S145" s="50"/>
-      <c r="T145" s="50"/>
-      <c r="U145" s="50"/>
-      <c r="V145" s="50"/>
-      <c r="W145" s="50"/>
-      <c r="X145" s="50"/>
-      <c r="Y145" s="50"/>
-      <c r="Z145" s="50"/>
-      <c r="AA145" s="50"/>
-      <c r="AB145" s="51"/>
+      <c r="H145" s="51"/>
+      <c r="I145" s="52"/>
+      <c r="J145" s="52"/>
+      <c r="K145" s="52"/>
+      <c r="L145" s="52"/>
+      <c r="M145" s="52"/>
+      <c r="N145" s="52"/>
+      <c r="O145" s="52"/>
+      <c r="P145" s="52"/>
+      <c r="Q145" s="52"/>
+      <c r="R145" s="52"/>
+      <c r="S145" s="52"/>
+      <c r="T145" s="52"/>
+      <c r="U145" s="52"/>
+      <c r="V145" s="52"/>
+      <c r="W145" s="52"/>
+      <c r="X145" s="52"/>
+      <c r="Y145" s="52"/>
+      <c r="Z145" s="52"/>
+      <c r="AA145" s="52"/>
+      <c r="AB145" s="53"/>
       <c r="AC145" s="11"/>
     </row>
     <row r="146" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6174,27 +6198,27 @@
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
-      <c r="H146" s="49"/>
-      <c r="I146" s="50"/>
-      <c r="J146" s="50"/>
-      <c r="K146" s="50"/>
-      <c r="L146" s="50"/>
-      <c r="M146" s="50"/>
-      <c r="N146" s="50"/>
-      <c r="O146" s="50"/>
-      <c r="P146" s="50"/>
-      <c r="Q146" s="50"/>
-      <c r="R146" s="50"/>
-      <c r="S146" s="50"/>
-      <c r="T146" s="50"/>
-      <c r="U146" s="50"/>
-      <c r="V146" s="50"/>
-      <c r="W146" s="50"/>
-      <c r="X146" s="50"/>
-      <c r="Y146" s="50"/>
-      <c r="Z146" s="50"/>
-      <c r="AA146" s="50"/>
-      <c r="AB146" s="51"/>
+      <c r="H146" s="51"/>
+      <c r="I146" s="52"/>
+      <c r="J146" s="52"/>
+      <c r="K146" s="52"/>
+      <c r="L146" s="52"/>
+      <c r="M146" s="52"/>
+      <c r="N146" s="52"/>
+      <c r="O146" s="52"/>
+      <c r="P146" s="52"/>
+      <c r="Q146" s="52"/>
+      <c r="R146" s="52"/>
+      <c r="S146" s="52"/>
+      <c r="T146" s="52"/>
+      <c r="U146" s="52"/>
+      <c r="V146" s="52"/>
+      <c r="W146" s="52"/>
+      <c r="X146" s="52"/>
+      <c r="Y146" s="52"/>
+      <c r="Z146" s="52"/>
+      <c r="AA146" s="52"/>
+      <c r="AB146" s="53"/>
       <c r="AC146" s="11"/>
     </row>
     <row r="147" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6204,27 +6228,27 @@
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
-      <c r="H147" s="52"/>
-      <c r="I147" s="53"/>
-      <c r="J147" s="53"/>
-      <c r="K147" s="53"/>
-      <c r="L147" s="53"/>
-      <c r="M147" s="53"/>
-      <c r="N147" s="53"/>
-      <c r="O147" s="53"/>
-      <c r="P147" s="53"/>
-      <c r="Q147" s="53"/>
-      <c r="R147" s="53"/>
-      <c r="S147" s="53"/>
-      <c r="T147" s="53"/>
-      <c r="U147" s="53"/>
-      <c r="V147" s="53"/>
-      <c r="W147" s="53"/>
-      <c r="X147" s="53"/>
-      <c r="Y147" s="53"/>
-      <c r="Z147" s="53"/>
-      <c r="AA147" s="53"/>
-      <c r="AB147" s="54"/>
+      <c r="H147" s="54"/>
+      <c r="I147" s="55"/>
+      <c r="J147" s="55"/>
+      <c r="K147" s="55"/>
+      <c r="L147" s="55"/>
+      <c r="M147" s="55"/>
+      <c r="N147" s="55"/>
+      <c r="O147" s="55"/>
+      <c r="P147" s="55"/>
+      <c r="Q147" s="55"/>
+      <c r="R147" s="55"/>
+      <c r="S147" s="55"/>
+      <c r="T147" s="55"/>
+      <c r="U147" s="55"/>
+      <c r="V147" s="55"/>
+      <c r="W147" s="55"/>
+      <c r="X147" s="55"/>
+      <c r="Y147" s="55"/>
+      <c r="Z147" s="55"/>
+      <c r="AA147" s="55"/>
+      <c r="AB147" s="56"/>
       <c r="AC147" s="11"/>
     </row>
     <row r="148" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6266,27 +6290,27 @@
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
-      <c r="H149" s="46"/>
-      <c r="I149" s="47"/>
-      <c r="J149" s="47"/>
-      <c r="K149" s="47"/>
-      <c r="L149" s="47"/>
-      <c r="M149" s="47"/>
-      <c r="N149" s="47"/>
-      <c r="O149" s="47"/>
-      <c r="P149" s="47"/>
-      <c r="Q149" s="47"/>
-      <c r="R149" s="47"/>
-      <c r="S149" s="47"/>
-      <c r="T149" s="47"/>
-      <c r="U149" s="47"/>
-      <c r="V149" s="47"/>
-      <c r="W149" s="47"/>
-      <c r="X149" s="47"/>
-      <c r="Y149" s="47"/>
-      <c r="Z149" s="47"/>
-      <c r="AA149" s="47"/>
-      <c r="AB149" s="48"/>
+      <c r="H149" s="48"/>
+      <c r="I149" s="49"/>
+      <c r="J149" s="49"/>
+      <c r="K149" s="49"/>
+      <c r="L149" s="49"/>
+      <c r="M149" s="49"/>
+      <c r="N149" s="49"/>
+      <c r="O149" s="49"/>
+      <c r="P149" s="49"/>
+      <c r="Q149" s="49"/>
+      <c r="R149" s="49"/>
+      <c r="S149" s="49"/>
+      <c r="T149" s="49"/>
+      <c r="U149" s="49"/>
+      <c r="V149" s="49"/>
+      <c r="W149" s="49"/>
+      <c r="X149" s="49"/>
+      <c r="Y149" s="49"/>
+      <c r="Z149" s="49"/>
+      <c r="AA149" s="49"/>
+      <c r="AB149" s="50"/>
       <c r="AC149" s="11"/>
     </row>
     <row r="150" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6296,27 +6320,27 @@
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
-      <c r="H150" s="49"/>
-      <c r="I150" s="50"/>
-      <c r="J150" s="50"/>
-      <c r="K150" s="50"/>
-      <c r="L150" s="50"/>
-      <c r="M150" s="50"/>
-      <c r="N150" s="50"/>
-      <c r="O150" s="50"/>
-      <c r="P150" s="50"/>
-      <c r="Q150" s="50"/>
-      <c r="R150" s="50"/>
-      <c r="S150" s="50"/>
-      <c r="T150" s="50"/>
-      <c r="U150" s="50"/>
-      <c r="V150" s="50"/>
-      <c r="W150" s="50"/>
-      <c r="X150" s="50"/>
-      <c r="Y150" s="50"/>
-      <c r="Z150" s="50"/>
-      <c r="AA150" s="50"/>
-      <c r="AB150" s="51"/>
+      <c r="H150" s="51"/>
+      <c r="I150" s="52"/>
+      <c r="J150" s="52"/>
+      <c r="K150" s="52"/>
+      <c r="L150" s="52"/>
+      <c r="M150" s="52"/>
+      <c r="N150" s="52"/>
+      <c r="O150" s="52"/>
+      <c r="P150" s="52"/>
+      <c r="Q150" s="52"/>
+      <c r="R150" s="52"/>
+      <c r="S150" s="52"/>
+      <c r="T150" s="52"/>
+      <c r="U150" s="52"/>
+      <c r="V150" s="52"/>
+      <c r="W150" s="52"/>
+      <c r="X150" s="52"/>
+      <c r="Y150" s="52"/>
+      <c r="Z150" s="52"/>
+      <c r="AA150" s="52"/>
+      <c r="AB150" s="53"/>
       <c r="AC150" s="11"/>
     </row>
     <row r="151" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6326,27 +6350,27 @@
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
-      <c r="H151" s="49"/>
-      <c r="I151" s="50"/>
-      <c r="J151" s="50"/>
-      <c r="K151" s="50"/>
-      <c r="L151" s="50"/>
-      <c r="M151" s="50"/>
-      <c r="N151" s="50"/>
-      <c r="O151" s="50"/>
-      <c r="P151" s="50"/>
-      <c r="Q151" s="50"/>
-      <c r="R151" s="50"/>
-      <c r="S151" s="50"/>
-      <c r="T151" s="50"/>
-      <c r="U151" s="50"/>
-      <c r="V151" s="50"/>
-      <c r="W151" s="50"/>
-      <c r="X151" s="50"/>
-      <c r="Y151" s="50"/>
-      <c r="Z151" s="50"/>
-      <c r="AA151" s="50"/>
-      <c r="AB151" s="51"/>
+      <c r="H151" s="51"/>
+      <c r="I151" s="52"/>
+      <c r="J151" s="52"/>
+      <c r="K151" s="52"/>
+      <c r="L151" s="52"/>
+      <c r="M151" s="52"/>
+      <c r="N151" s="52"/>
+      <c r="O151" s="52"/>
+      <c r="P151" s="52"/>
+      <c r="Q151" s="52"/>
+      <c r="R151" s="52"/>
+      <c r="S151" s="52"/>
+      <c r="T151" s="52"/>
+      <c r="U151" s="52"/>
+      <c r="V151" s="52"/>
+      <c r="W151" s="52"/>
+      <c r="X151" s="52"/>
+      <c r="Y151" s="52"/>
+      <c r="Z151" s="52"/>
+      <c r="AA151" s="52"/>
+      <c r="AB151" s="53"/>
       <c r="AC151" s="11"/>
     </row>
     <row r="152" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6356,27 +6380,27 @@
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
-      <c r="H152" s="49"/>
-      <c r="I152" s="50"/>
-      <c r="J152" s="50"/>
-      <c r="K152" s="50"/>
-      <c r="L152" s="50"/>
-      <c r="M152" s="50"/>
-      <c r="N152" s="50"/>
-      <c r="O152" s="50"/>
-      <c r="P152" s="50"/>
-      <c r="Q152" s="50"/>
-      <c r="R152" s="50"/>
-      <c r="S152" s="50"/>
-      <c r="T152" s="50"/>
-      <c r="U152" s="50"/>
-      <c r="V152" s="50"/>
-      <c r="W152" s="50"/>
-      <c r="X152" s="50"/>
-      <c r="Y152" s="50"/>
-      <c r="Z152" s="50"/>
-      <c r="AA152" s="50"/>
-      <c r="AB152" s="51"/>
+      <c r="H152" s="51"/>
+      <c r="I152" s="52"/>
+      <c r="J152" s="52"/>
+      <c r="K152" s="52"/>
+      <c r="L152" s="52"/>
+      <c r="M152" s="52"/>
+      <c r="N152" s="52"/>
+      <c r="O152" s="52"/>
+      <c r="P152" s="52"/>
+      <c r="Q152" s="52"/>
+      <c r="R152" s="52"/>
+      <c r="S152" s="52"/>
+      <c r="T152" s="52"/>
+      <c r="U152" s="52"/>
+      <c r="V152" s="52"/>
+      <c r="W152" s="52"/>
+      <c r="X152" s="52"/>
+      <c r="Y152" s="52"/>
+      <c r="Z152" s="52"/>
+      <c r="AA152" s="52"/>
+      <c r="AB152" s="53"/>
       <c r="AC152" s="11"/>
     </row>
     <row r="153" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6386,27 +6410,27 @@
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
-      <c r="H153" s="49"/>
-      <c r="I153" s="50"/>
-      <c r="J153" s="50"/>
-      <c r="K153" s="50"/>
-      <c r="L153" s="50"/>
-      <c r="M153" s="50"/>
-      <c r="N153" s="50"/>
-      <c r="O153" s="50"/>
-      <c r="P153" s="50"/>
-      <c r="Q153" s="50"/>
-      <c r="R153" s="50"/>
-      <c r="S153" s="50"/>
-      <c r="T153" s="50"/>
-      <c r="U153" s="50"/>
-      <c r="V153" s="50"/>
-      <c r="W153" s="50"/>
-      <c r="X153" s="50"/>
-      <c r="Y153" s="50"/>
-      <c r="Z153" s="50"/>
-      <c r="AA153" s="50"/>
-      <c r="AB153" s="51"/>
+      <c r="H153" s="51"/>
+      <c r="I153" s="52"/>
+      <c r="J153" s="52"/>
+      <c r="K153" s="52"/>
+      <c r="L153" s="52"/>
+      <c r="M153" s="52"/>
+      <c r="N153" s="52"/>
+      <c r="O153" s="52"/>
+      <c r="P153" s="52"/>
+      <c r="Q153" s="52"/>
+      <c r="R153" s="52"/>
+      <c r="S153" s="52"/>
+      <c r="T153" s="52"/>
+      <c r="U153" s="52"/>
+      <c r="V153" s="52"/>
+      <c r="W153" s="52"/>
+      <c r="X153" s="52"/>
+      <c r="Y153" s="52"/>
+      <c r="Z153" s="52"/>
+      <c r="AA153" s="52"/>
+      <c r="AB153" s="53"/>
       <c r="AC153" s="11"/>
     </row>
     <row r="154" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6416,27 +6440,27 @@
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
-      <c r="H154" s="49"/>
-      <c r="I154" s="50"/>
-      <c r="J154" s="50"/>
-      <c r="K154" s="50"/>
-      <c r="L154" s="50"/>
-      <c r="M154" s="50"/>
-      <c r="N154" s="50"/>
-      <c r="O154" s="50"/>
-      <c r="P154" s="50"/>
-      <c r="Q154" s="50"/>
-      <c r="R154" s="50"/>
-      <c r="S154" s="50"/>
-      <c r="T154" s="50"/>
-      <c r="U154" s="50"/>
-      <c r="V154" s="50"/>
-      <c r="W154" s="50"/>
-      <c r="X154" s="50"/>
-      <c r="Y154" s="50"/>
-      <c r="Z154" s="50"/>
-      <c r="AA154" s="50"/>
-      <c r="AB154" s="51"/>
+      <c r="H154" s="51"/>
+      <c r="I154" s="52"/>
+      <c r="J154" s="52"/>
+      <c r="K154" s="52"/>
+      <c r="L154" s="52"/>
+      <c r="M154" s="52"/>
+      <c r="N154" s="52"/>
+      <c r="O154" s="52"/>
+      <c r="P154" s="52"/>
+      <c r="Q154" s="52"/>
+      <c r="R154" s="52"/>
+      <c r="S154" s="52"/>
+      <c r="T154" s="52"/>
+      <c r="U154" s="52"/>
+      <c r="V154" s="52"/>
+      <c r="W154" s="52"/>
+      <c r="X154" s="52"/>
+      <c r="Y154" s="52"/>
+      <c r="Z154" s="52"/>
+      <c r="AA154" s="52"/>
+      <c r="AB154" s="53"/>
       <c r="AC154" s="11"/>
     </row>
     <row r="155" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6446,27 +6470,27 @@
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
-      <c r="H155" s="52"/>
-      <c r="I155" s="53"/>
-      <c r="J155" s="53"/>
-      <c r="K155" s="53"/>
-      <c r="L155" s="53"/>
-      <c r="M155" s="53"/>
-      <c r="N155" s="53"/>
-      <c r="O155" s="53"/>
-      <c r="P155" s="53"/>
-      <c r="Q155" s="53"/>
-      <c r="R155" s="53"/>
-      <c r="S155" s="53"/>
-      <c r="T155" s="53"/>
-      <c r="U155" s="53"/>
-      <c r="V155" s="53"/>
-      <c r="W155" s="53"/>
-      <c r="X155" s="53"/>
-      <c r="Y155" s="53"/>
-      <c r="Z155" s="53"/>
-      <c r="AA155" s="53"/>
-      <c r="AB155" s="54"/>
+      <c r="H155" s="54"/>
+      <c r="I155" s="55"/>
+      <c r="J155" s="55"/>
+      <c r="K155" s="55"/>
+      <c r="L155" s="55"/>
+      <c r="M155" s="55"/>
+      <c r="N155" s="55"/>
+      <c r="O155" s="55"/>
+      <c r="P155" s="55"/>
+      <c r="Q155" s="55"/>
+      <c r="R155" s="55"/>
+      <c r="S155" s="55"/>
+      <c r="T155" s="55"/>
+      <c r="U155" s="55"/>
+      <c r="V155" s="55"/>
+      <c r="W155" s="55"/>
+      <c r="X155" s="55"/>
+      <c r="Y155" s="55"/>
+      <c r="Z155" s="55"/>
+      <c r="AA155" s="55"/>
+      <c r="AB155" s="56"/>
       <c r="AC155" s="11"/>
     </row>
     <row r="156" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6574,27 +6598,27 @@
         <v>2</v>
       </c>
       <c r="G160" s="6"/>
-      <c r="H160" s="46"/>
-      <c r="I160" s="47"/>
-      <c r="J160" s="47"/>
-      <c r="K160" s="47"/>
-      <c r="L160" s="47"/>
-      <c r="M160" s="47"/>
-      <c r="N160" s="47"/>
-      <c r="O160" s="47"/>
-      <c r="P160" s="47"/>
-      <c r="Q160" s="47"/>
-      <c r="R160" s="47"/>
-      <c r="S160" s="47"/>
-      <c r="T160" s="47"/>
-      <c r="U160" s="47"/>
-      <c r="V160" s="47"/>
-      <c r="W160" s="47"/>
-      <c r="X160" s="47"/>
-      <c r="Y160" s="47"/>
-      <c r="Z160" s="47"/>
-      <c r="AA160" s="47"/>
-      <c r="AB160" s="48"/>
+      <c r="H160" s="48"/>
+      <c r="I160" s="49"/>
+      <c r="J160" s="49"/>
+      <c r="K160" s="49"/>
+      <c r="L160" s="49"/>
+      <c r="M160" s="49"/>
+      <c r="N160" s="49"/>
+      <c r="O160" s="49"/>
+      <c r="P160" s="49"/>
+      <c r="Q160" s="49"/>
+      <c r="R160" s="49"/>
+      <c r="S160" s="49"/>
+      <c r="T160" s="49"/>
+      <c r="U160" s="49"/>
+      <c r="V160" s="49"/>
+      <c r="W160" s="49"/>
+      <c r="X160" s="49"/>
+      <c r="Y160" s="49"/>
+      <c r="Z160" s="49"/>
+      <c r="AA160" s="49"/>
+      <c r="AB160" s="50"/>
       <c r="AC160" s="11"/>
     </row>
     <row r="161" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6604,27 +6628,27 @@
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
-      <c r="H161" s="49"/>
-      <c r="I161" s="50"/>
-      <c r="J161" s="50"/>
-      <c r="K161" s="50"/>
-      <c r="L161" s="50"/>
-      <c r="M161" s="50"/>
-      <c r="N161" s="50"/>
-      <c r="O161" s="50"/>
-      <c r="P161" s="50"/>
-      <c r="Q161" s="50"/>
-      <c r="R161" s="50"/>
-      <c r="S161" s="50"/>
-      <c r="T161" s="50"/>
-      <c r="U161" s="50"/>
-      <c r="V161" s="50"/>
-      <c r="W161" s="50"/>
-      <c r="X161" s="50"/>
-      <c r="Y161" s="50"/>
-      <c r="Z161" s="50"/>
-      <c r="AA161" s="50"/>
-      <c r="AB161" s="51"/>
+      <c r="H161" s="51"/>
+      <c r="I161" s="52"/>
+      <c r="J161" s="52"/>
+      <c r="K161" s="52"/>
+      <c r="L161" s="52"/>
+      <c r="M161" s="52"/>
+      <c r="N161" s="52"/>
+      <c r="O161" s="52"/>
+      <c r="P161" s="52"/>
+      <c r="Q161" s="52"/>
+      <c r="R161" s="52"/>
+      <c r="S161" s="52"/>
+      <c r="T161" s="52"/>
+      <c r="U161" s="52"/>
+      <c r="V161" s="52"/>
+      <c r="W161" s="52"/>
+      <c r="X161" s="52"/>
+      <c r="Y161" s="52"/>
+      <c r="Z161" s="52"/>
+      <c r="AA161" s="52"/>
+      <c r="AB161" s="53"/>
       <c r="AC161" s="11"/>
     </row>
     <row r="162" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6634,27 +6658,27 @@
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
-      <c r="H162" s="49"/>
-      <c r="I162" s="50"/>
-      <c r="J162" s="50"/>
-      <c r="K162" s="50"/>
-      <c r="L162" s="50"/>
-      <c r="M162" s="50"/>
-      <c r="N162" s="50"/>
-      <c r="O162" s="50"/>
-      <c r="P162" s="50"/>
-      <c r="Q162" s="50"/>
-      <c r="R162" s="50"/>
-      <c r="S162" s="50"/>
-      <c r="T162" s="50"/>
-      <c r="U162" s="50"/>
-      <c r="V162" s="50"/>
-      <c r="W162" s="50"/>
-      <c r="X162" s="50"/>
-      <c r="Y162" s="50"/>
-      <c r="Z162" s="50"/>
-      <c r="AA162" s="50"/>
-      <c r="AB162" s="51"/>
+      <c r="H162" s="51"/>
+      <c r="I162" s="52"/>
+      <c r="J162" s="52"/>
+      <c r="K162" s="52"/>
+      <c r="L162" s="52"/>
+      <c r="M162" s="52"/>
+      <c r="N162" s="52"/>
+      <c r="O162" s="52"/>
+      <c r="P162" s="52"/>
+      <c r="Q162" s="52"/>
+      <c r="R162" s="52"/>
+      <c r="S162" s="52"/>
+      <c r="T162" s="52"/>
+      <c r="U162" s="52"/>
+      <c r="V162" s="52"/>
+      <c r="W162" s="52"/>
+      <c r="X162" s="52"/>
+      <c r="Y162" s="52"/>
+      <c r="Z162" s="52"/>
+      <c r="AA162" s="52"/>
+      <c r="AB162" s="53"/>
       <c r="AC162" s="11"/>
     </row>
     <row r="163" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6664,27 +6688,27 @@
       <c r="E163" s="6"/>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
-      <c r="H163" s="49"/>
-      <c r="I163" s="50"/>
-      <c r="J163" s="50"/>
-      <c r="K163" s="50"/>
-      <c r="L163" s="50"/>
-      <c r="M163" s="50"/>
-      <c r="N163" s="50"/>
-      <c r="O163" s="50"/>
-      <c r="P163" s="50"/>
-      <c r="Q163" s="50"/>
-      <c r="R163" s="50"/>
-      <c r="S163" s="50"/>
-      <c r="T163" s="50"/>
-      <c r="U163" s="50"/>
-      <c r="V163" s="50"/>
-      <c r="W163" s="50"/>
-      <c r="X163" s="50"/>
-      <c r="Y163" s="50"/>
-      <c r="Z163" s="50"/>
-      <c r="AA163" s="50"/>
-      <c r="AB163" s="51"/>
+      <c r="H163" s="51"/>
+      <c r="I163" s="52"/>
+      <c r="J163" s="52"/>
+      <c r="K163" s="52"/>
+      <c r="L163" s="52"/>
+      <c r="M163" s="52"/>
+      <c r="N163" s="52"/>
+      <c r="O163" s="52"/>
+      <c r="P163" s="52"/>
+      <c r="Q163" s="52"/>
+      <c r="R163" s="52"/>
+      <c r="S163" s="52"/>
+      <c r="T163" s="52"/>
+      <c r="U163" s="52"/>
+      <c r="V163" s="52"/>
+      <c r="W163" s="52"/>
+      <c r="X163" s="52"/>
+      <c r="Y163" s="52"/>
+      <c r="Z163" s="52"/>
+      <c r="AA163" s="52"/>
+      <c r="AB163" s="53"/>
       <c r="AC163" s="11"/>
     </row>
     <row r="164" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6694,27 +6718,27 @@
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
-      <c r="H164" s="49"/>
-      <c r="I164" s="50"/>
-      <c r="J164" s="50"/>
-      <c r="K164" s="50"/>
-      <c r="L164" s="50"/>
-      <c r="M164" s="50"/>
-      <c r="N164" s="50"/>
-      <c r="O164" s="50"/>
-      <c r="P164" s="50"/>
-      <c r="Q164" s="50"/>
-      <c r="R164" s="50"/>
-      <c r="S164" s="50"/>
-      <c r="T164" s="50"/>
-      <c r="U164" s="50"/>
-      <c r="V164" s="50"/>
-      <c r="W164" s="50"/>
-      <c r="X164" s="50"/>
-      <c r="Y164" s="50"/>
-      <c r="Z164" s="50"/>
-      <c r="AA164" s="50"/>
-      <c r="AB164" s="51"/>
+      <c r="H164" s="51"/>
+      <c r="I164" s="52"/>
+      <c r="J164" s="52"/>
+      <c r="K164" s="52"/>
+      <c r="L164" s="52"/>
+      <c r="M164" s="52"/>
+      <c r="N164" s="52"/>
+      <c r="O164" s="52"/>
+      <c r="P164" s="52"/>
+      <c r="Q164" s="52"/>
+      <c r="R164" s="52"/>
+      <c r="S164" s="52"/>
+      <c r="T164" s="52"/>
+      <c r="U164" s="52"/>
+      <c r="V164" s="52"/>
+      <c r="W164" s="52"/>
+      <c r="X164" s="52"/>
+      <c r="Y164" s="52"/>
+      <c r="Z164" s="52"/>
+      <c r="AA164" s="52"/>
+      <c r="AB164" s="53"/>
       <c r="AC164" s="11"/>
     </row>
     <row r="165" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6724,27 +6748,27 @@
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
-      <c r="H165" s="49"/>
-      <c r="I165" s="50"/>
-      <c r="J165" s="50"/>
-      <c r="K165" s="50"/>
-      <c r="L165" s="50"/>
-      <c r="M165" s="50"/>
-      <c r="N165" s="50"/>
-      <c r="O165" s="50"/>
-      <c r="P165" s="50"/>
-      <c r="Q165" s="50"/>
-      <c r="R165" s="50"/>
-      <c r="S165" s="50"/>
-      <c r="T165" s="50"/>
-      <c r="U165" s="50"/>
-      <c r="V165" s="50"/>
-      <c r="W165" s="50"/>
-      <c r="X165" s="50"/>
-      <c r="Y165" s="50"/>
-      <c r="Z165" s="50"/>
-      <c r="AA165" s="50"/>
-      <c r="AB165" s="51"/>
+      <c r="H165" s="51"/>
+      <c r="I165" s="52"/>
+      <c r="J165" s="52"/>
+      <c r="K165" s="52"/>
+      <c r="L165" s="52"/>
+      <c r="M165" s="52"/>
+      <c r="N165" s="52"/>
+      <c r="O165" s="52"/>
+      <c r="P165" s="52"/>
+      <c r="Q165" s="52"/>
+      <c r="R165" s="52"/>
+      <c r="S165" s="52"/>
+      <c r="T165" s="52"/>
+      <c r="U165" s="52"/>
+      <c r="V165" s="52"/>
+      <c r="W165" s="52"/>
+      <c r="X165" s="52"/>
+      <c r="Y165" s="52"/>
+      <c r="Z165" s="52"/>
+      <c r="AA165" s="52"/>
+      <c r="AB165" s="53"/>
       <c r="AC165" s="11"/>
     </row>
     <row r="166" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6754,27 +6778,27 @@
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
-      <c r="H166" s="52"/>
-      <c r="I166" s="53"/>
-      <c r="J166" s="53"/>
-      <c r="K166" s="53"/>
-      <c r="L166" s="53"/>
-      <c r="M166" s="53"/>
-      <c r="N166" s="53"/>
-      <c r="O166" s="53"/>
-      <c r="P166" s="53"/>
-      <c r="Q166" s="53"/>
-      <c r="R166" s="53"/>
-      <c r="S166" s="53"/>
-      <c r="T166" s="53"/>
-      <c r="U166" s="53"/>
-      <c r="V166" s="53"/>
-      <c r="W166" s="53"/>
-      <c r="X166" s="53"/>
-      <c r="Y166" s="53"/>
-      <c r="Z166" s="53"/>
-      <c r="AA166" s="53"/>
-      <c r="AB166" s="54"/>
+      <c r="H166" s="54"/>
+      <c r="I166" s="55"/>
+      <c r="J166" s="55"/>
+      <c r="K166" s="55"/>
+      <c r="L166" s="55"/>
+      <c r="M166" s="55"/>
+      <c r="N166" s="55"/>
+      <c r="O166" s="55"/>
+      <c r="P166" s="55"/>
+      <c r="Q166" s="55"/>
+      <c r="R166" s="55"/>
+      <c r="S166" s="55"/>
+      <c r="T166" s="55"/>
+      <c r="U166" s="55"/>
+      <c r="V166" s="55"/>
+      <c r="W166" s="55"/>
+      <c r="X166" s="55"/>
+      <c r="Y166" s="55"/>
+      <c r="Z166" s="55"/>
+      <c r="AA166" s="55"/>
+      <c r="AB166" s="56"/>
       <c r="AC166" s="11"/>
     </row>
     <row r="167" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6816,27 +6840,27 @@
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
-      <c r="H168" s="46"/>
-      <c r="I168" s="47"/>
-      <c r="J168" s="47"/>
-      <c r="K168" s="47"/>
-      <c r="L168" s="47"/>
-      <c r="M168" s="47"/>
-      <c r="N168" s="47"/>
-      <c r="O168" s="47"/>
-      <c r="P168" s="47"/>
-      <c r="Q168" s="47"/>
-      <c r="R168" s="47"/>
-      <c r="S168" s="47"/>
-      <c r="T168" s="47"/>
-      <c r="U168" s="47"/>
-      <c r="V168" s="47"/>
-      <c r="W168" s="47"/>
-      <c r="X168" s="47"/>
-      <c r="Y168" s="47"/>
-      <c r="Z168" s="47"/>
-      <c r="AA168" s="47"/>
-      <c r="AB168" s="48"/>
+      <c r="H168" s="48"/>
+      <c r="I168" s="49"/>
+      <c r="J168" s="49"/>
+      <c r="K168" s="49"/>
+      <c r="L168" s="49"/>
+      <c r="M168" s="49"/>
+      <c r="N168" s="49"/>
+      <c r="O168" s="49"/>
+      <c r="P168" s="49"/>
+      <c r="Q168" s="49"/>
+      <c r="R168" s="49"/>
+      <c r="S168" s="49"/>
+      <c r="T168" s="49"/>
+      <c r="U168" s="49"/>
+      <c r="V168" s="49"/>
+      <c r="W168" s="49"/>
+      <c r="X168" s="49"/>
+      <c r="Y168" s="49"/>
+      <c r="Z168" s="49"/>
+      <c r="AA168" s="49"/>
+      <c r="AB168" s="50"/>
       <c r="AC168" s="11"/>
     </row>
     <row r="169" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6846,27 +6870,27 @@
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
-      <c r="H169" s="49"/>
-      <c r="I169" s="50"/>
-      <c r="J169" s="50"/>
-      <c r="K169" s="50"/>
-      <c r="L169" s="50"/>
-      <c r="M169" s="50"/>
-      <c r="N169" s="50"/>
-      <c r="O169" s="50"/>
-      <c r="P169" s="50"/>
-      <c r="Q169" s="50"/>
-      <c r="R169" s="50"/>
-      <c r="S169" s="50"/>
-      <c r="T169" s="50"/>
-      <c r="U169" s="50"/>
-      <c r="V169" s="50"/>
-      <c r="W169" s="50"/>
-      <c r="X169" s="50"/>
-      <c r="Y169" s="50"/>
-      <c r="Z169" s="50"/>
-      <c r="AA169" s="50"/>
-      <c r="AB169" s="51"/>
+      <c r="H169" s="51"/>
+      <c r="I169" s="52"/>
+      <c r="J169" s="52"/>
+      <c r="K169" s="52"/>
+      <c r="L169" s="52"/>
+      <c r="M169" s="52"/>
+      <c r="N169" s="52"/>
+      <c r="O169" s="52"/>
+      <c r="P169" s="52"/>
+      <c r="Q169" s="52"/>
+      <c r="R169" s="52"/>
+      <c r="S169" s="52"/>
+      <c r="T169" s="52"/>
+      <c r="U169" s="52"/>
+      <c r="V169" s="52"/>
+      <c r="W169" s="52"/>
+      <c r="X169" s="52"/>
+      <c r="Y169" s="52"/>
+      <c r="Z169" s="52"/>
+      <c r="AA169" s="52"/>
+      <c r="AB169" s="53"/>
       <c r="AC169" s="11"/>
     </row>
     <row r="170" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6876,27 +6900,27 @@
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
-      <c r="H170" s="49"/>
-      <c r="I170" s="50"/>
-      <c r="J170" s="50"/>
-      <c r="K170" s="50"/>
-      <c r="L170" s="50"/>
-      <c r="M170" s="50"/>
-      <c r="N170" s="50"/>
-      <c r="O170" s="50"/>
-      <c r="P170" s="50"/>
-      <c r="Q170" s="50"/>
-      <c r="R170" s="50"/>
-      <c r="S170" s="50"/>
-      <c r="T170" s="50"/>
-      <c r="U170" s="50"/>
-      <c r="V170" s="50"/>
-      <c r="W170" s="50"/>
-      <c r="X170" s="50"/>
-      <c r="Y170" s="50"/>
-      <c r="Z170" s="50"/>
-      <c r="AA170" s="50"/>
-      <c r="AB170" s="51"/>
+      <c r="H170" s="51"/>
+      <c r="I170" s="52"/>
+      <c r="J170" s="52"/>
+      <c r="K170" s="52"/>
+      <c r="L170" s="52"/>
+      <c r="M170" s="52"/>
+      <c r="N170" s="52"/>
+      <c r="O170" s="52"/>
+      <c r="P170" s="52"/>
+      <c r="Q170" s="52"/>
+      <c r="R170" s="52"/>
+      <c r="S170" s="52"/>
+      <c r="T170" s="52"/>
+      <c r="U170" s="52"/>
+      <c r="V170" s="52"/>
+      <c r="W170" s="52"/>
+      <c r="X170" s="52"/>
+      <c r="Y170" s="52"/>
+      <c r="Z170" s="52"/>
+      <c r="AA170" s="52"/>
+      <c r="AB170" s="53"/>
       <c r="AC170" s="11"/>
     </row>
     <row r="171" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6906,27 +6930,27 @@
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
-      <c r="H171" s="49"/>
-      <c r="I171" s="50"/>
-      <c r="J171" s="50"/>
-      <c r="K171" s="50"/>
-      <c r="L171" s="50"/>
-      <c r="M171" s="50"/>
-      <c r="N171" s="50"/>
-      <c r="O171" s="50"/>
-      <c r="P171" s="50"/>
-      <c r="Q171" s="50"/>
-      <c r="R171" s="50"/>
-      <c r="S171" s="50"/>
-      <c r="T171" s="50"/>
-      <c r="U171" s="50"/>
-      <c r="V171" s="50"/>
-      <c r="W171" s="50"/>
-      <c r="X171" s="50"/>
-      <c r="Y171" s="50"/>
-      <c r="Z171" s="50"/>
-      <c r="AA171" s="50"/>
-      <c r="AB171" s="51"/>
+      <c r="H171" s="51"/>
+      <c r="I171" s="52"/>
+      <c r="J171" s="52"/>
+      <c r="K171" s="52"/>
+      <c r="L171" s="52"/>
+      <c r="M171" s="52"/>
+      <c r="N171" s="52"/>
+      <c r="O171" s="52"/>
+      <c r="P171" s="52"/>
+      <c r="Q171" s="52"/>
+      <c r="R171" s="52"/>
+      <c r="S171" s="52"/>
+      <c r="T171" s="52"/>
+      <c r="U171" s="52"/>
+      <c r="V171" s="52"/>
+      <c r="W171" s="52"/>
+      <c r="X171" s="52"/>
+      <c r="Y171" s="52"/>
+      <c r="Z171" s="52"/>
+      <c r="AA171" s="52"/>
+      <c r="AB171" s="53"/>
       <c r="AC171" s="11"/>
     </row>
     <row r="172" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6936,27 +6960,27 @@
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
-      <c r="H172" s="49"/>
-      <c r="I172" s="50"/>
-      <c r="J172" s="50"/>
-      <c r="K172" s="50"/>
-      <c r="L172" s="50"/>
-      <c r="M172" s="50"/>
-      <c r="N172" s="50"/>
-      <c r="O172" s="50"/>
-      <c r="P172" s="50"/>
-      <c r="Q172" s="50"/>
-      <c r="R172" s="50"/>
-      <c r="S172" s="50"/>
-      <c r="T172" s="50"/>
-      <c r="U172" s="50"/>
-      <c r="V172" s="50"/>
-      <c r="W172" s="50"/>
-      <c r="X172" s="50"/>
-      <c r="Y172" s="50"/>
-      <c r="Z172" s="50"/>
-      <c r="AA172" s="50"/>
-      <c r="AB172" s="51"/>
+      <c r="H172" s="51"/>
+      <c r="I172" s="52"/>
+      <c r="J172" s="52"/>
+      <c r="K172" s="52"/>
+      <c r="L172" s="52"/>
+      <c r="M172" s="52"/>
+      <c r="N172" s="52"/>
+      <c r="O172" s="52"/>
+      <c r="P172" s="52"/>
+      <c r="Q172" s="52"/>
+      <c r="R172" s="52"/>
+      <c r="S172" s="52"/>
+      <c r="T172" s="52"/>
+      <c r="U172" s="52"/>
+      <c r="V172" s="52"/>
+      <c r="W172" s="52"/>
+      <c r="X172" s="52"/>
+      <c r="Y172" s="52"/>
+      <c r="Z172" s="52"/>
+      <c r="AA172" s="52"/>
+      <c r="AB172" s="53"/>
       <c r="AC172" s="11"/>
     </row>
     <row r="173" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6966,27 +6990,27 @@
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
-      <c r="H173" s="49"/>
-      <c r="I173" s="50"/>
-      <c r="J173" s="50"/>
-      <c r="K173" s="50"/>
-      <c r="L173" s="50"/>
-      <c r="M173" s="50"/>
-      <c r="N173" s="50"/>
-      <c r="O173" s="50"/>
-      <c r="P173" s="50"/>
-      <c r="Q173" s="50"/>
-      <c r="R173" s="50"/>
-      <c r="S173" s="50"/>
-      <c r="T173" s="50"/>
-      <c r="U173" s="50"/>
-      <c r="V173" s="50"/>
-      <c r="W173" s="50"/>
-      <c r="X173" s="50"/>
-      <c r="Y173" s="50"/>
-      <c r="Z173" s="50"/>
-      <c r="AA173" s="50"/>
-      <c r="AB173" s="51"/>
+      <c r="H173" s="51"/>
+      <c r="I173" s="52"/>
+      <c r="J173" s="52"/>
+      <c r="K173" s="52"/>
+      <c r="L173" s="52"/>
+      <c r="M173" s="52"/>
+      <c r="N173" s="52"/>
+      <c r="O173" s="52"/>
+      <c r="P173" s="52"/>
+      <c r="Q173" s="52"/>
+      <c r="R173" s="52"/>
+      <c r="S173" s="52"/>
+      <c r="T173" s="52"/>
+      <c r="U173" s="52"/>
+      <c r="V173" s="52"/>
+      <c r="W173" s="52"/>
+      <c r="X173" s="52"/>
+      <c r="Y173" s="52"/>
+      <c r="Z173" s="52"/>
+      <c r="AA173" s="52"/>
+      <c r="AB173" s="53"/>
       <c r="AC173" s="11"/>
     </row>
     <row r="174" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6996,27 +7020,27 @@
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
-      <c r="H174" s="52"/>
-      <c r="I174" s="53"/>
-      <c r="J174" s="53"/>
-      <c r="K174" s="53"/>
-      <c r="L174" s="53"/>
-      <c r="M174" s="53"/>
-      <c r="N174" s="53"/>
-      <c r="O174" s="53"/>
-      <c r="P174" s="53"/>
-      <c r="Q174" s="53"/>
-      <c r="R174" s="53"/>
-      <c r="S174" s="53"/>
-      <c r="T174" s="53"/>
-      <c r="U174" s="53"/>
-      <c r="V174" s="53"/>
-      <c r="W174" s="53"/>
-      <c r="X174" s="53"/>
-      <c r="Y174" s="53"/>
-      <c r="Z174" s="53"/>
-      <c r="AA174" s="53"/>
-      <c r="AB174" s="54"/>
+      <c r="H174" s="54"/>
+      <c r="I174" s="55"/>
+      <c r="J174" s="55"/>
+      <c r="K174" s="55"/>
+      <c r="L174" s="55"/>
+      <c r="M174" s="55"/>
+      <c r="N174" s="55"/>
+      <c r="O174" s="55"/>
+      <c r="P174" s="55"/>
+      <c r="Q174" s="55"/>
+      <c r="R174" s="55"/>
+      <c r="S174" s="55"/>
+      <c r="T174" s="55"/>
+      <c r="U174" s="55"/>
+      <c r="V174" s="55"/>
+      <c r="W174" s="55"/>
+      <c r="X174" s="55"/>
+      <c r="Y174" s="55"/>
+      <c r="Z174" s="55"/>
+      <c r="AA174" s="55"/>
+      <c r="AB174" s="56"/>
       <c r="AC174" s="11"/>
     </row>
     <row r="175" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7124,27 +7148,27 @@
         <v>2</v>
       </c>
       <c r="G179" s="6"/>
-      <c r="H179" s="46"/>
-      <c r="I179" s="47"/>
-      <c r="J179" s="47"/>
-      <c r="K179" s="47"/>
-      <c r="L179" s="47"/>
-      <c r="M179" s="47"/>
-      <c r="N179" s="47"/>
-      <c r="O179" s="47"/>
-      <c r="P179" s="47"/>
-      <c r="Q179" s="47"/>
-      <c r="R179" s="47"/>
-      <c r="S179" s="47"/>
-      <c r="T179" s="47"/>
-      <c r="U179" s="47"/>
-      <c r="V179" s="47"/>
-      <c r="W179" s="47"/>
-      <c r="X179" s="47"/>
-      <c r="Y179" s="47"/>
-      <c r="Z179" s="47"/>
-      <c r="AA179" s="47"/>
-      <c r="AB179" s="48"/>
+      <c r="H179" s="48"/>
+      <c r="I179" s="49"/>
+      <c r="J179" s="49"/>
+      <c r="K179" s="49"/>
+      <c r="L179" s="49"/>
+      <c r="M179" s="49"/>
+      <c r="N179" s="49"/>
+      <c r="O179" s="49"/>
+      <c r="P179" s="49"/>
+      <c r="Q179" s="49"/>
+      <c r="R179" s="49"/>
+      <c r="S179" s="49"/>
+      <c r="T179" s="49"/>
+      <c r="U179" s="49"/>
+      <c r="V179" s="49"/>
+      <c r="W179" s="49"/>
+      <c r="X179" s="49"/>
+      <c r="Y179" s="49"/>
+      <c r="Z179" s="49"/>
+      <c r="AA179" s="49"/>
+      <c r="AB179" s="50"/>
       <c r="AC179" s="11"/>
     </row>
     <row r="180" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7154,27 +7178,27 @@
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
-      <c r="H180" s="49"/>
-      <c r="I180" s="50"/>
-      <c r="J180" s="50"/>
-      <c r="K180" s="50"/>
-      <c r="L180" s="50"/>
-      <c r="M180" s="50"/>
-      <c r="N180" s="50"/>
-      <c r="O180" s="50"/>
-      <c r="P180" s="50"/>
-      <c r="Q180" s="50"/>
-      <c r="R180" s="50"/>
-      <c r="S180" s="50"/>
-      <c r="T180" s="50"/>
-      <c r="U180" s="50"/>
-      <c r="V180" s="50"/>
-      <c r="W180" s="50"/>
-      <c r="X180" s="50"/>
-      <c r="Y180" s="50"/>
-      <c r="Z180" s="50"/>
-      <c r="AA180" s="50"/>
-      <c r="AB180" s="51"/>
+      <c r="H180" s="51"/>
+      <c r="I180" s="52"/>
+      <c r="J180" s="52"/>
+      <c r="K180" s="52"/>
+      <c r="L180" s="52"/>
+      <c r="M180" s="52"/>
+      <c r="N180" s="52"/>
+      <c r="O180" s="52"/>
+      <c r="P180" s="52"/>
+      <c r="Q180" s="52"/>
+      <c r="R180" s="52"/>
+      <c r="S180" s="52"/>
+      <c r="T180" s="52"/>
+      <c r="U180" s="52"/>
+      <c r="V180" s="52"/>
+      <c r="W180" s="52"/>
+      <c r="X180" s="52"/>
+      <c r="Y180" s="52"/>
+      <c r="Z180" s="52"/>
+      <c r="AA180" s="52"/>
+      <c r="AB180" s="53"/>
       <c r="AC180" s="11"/>
     </row>
     <row r="181" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7184,27 +7208,27 @@
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
-      <c r="H181" s="49"/>
-      <c r="I181" s="50"/>
-      <c r="J181" s="50"/>
-      <c r="K181" s="50"/>
-      <c r="L181" s="50"/>
-      <c r="M181" s="50"/>
-      <c r="N181" s="50"/>
-      <c r="O181" s="50"/>
-      <c r="P181" s="50"/>
-      <c r="Q181" s="50"/>
-      <c r="R181" s="50"/>
-      <c r="S181" s="50"/>
-      <c r="T181" s="50"/>
-      <c r="U181" s="50"/>
-      <c r="V181" s="50"/>
-      <c r="W181" s="50"/>
-      <c r="X181" s="50"/>
-      <c r="Y181" s="50"/>
-      <c r="Z181" s="50"/>
-      <c r="AA181" s="50"/>
-      <c r="AB181" s="51"/>
+      <c r="H181" s="51"/>
+      <c r="I181" s="52"/>
+      <c r="J181" s="52"/>
+      <c r="K181" s="52"/>
+      <c r="L181" s="52"/>
+      <c r="M181" s="52"/>
+      <c r="N181" s="52"/>
+      <c r="O181" s="52"/>
+      <c r="P181" s="52"/>
+      <c r="Q181" s="52"/>
+      <c r="R181" s="52"/>
+      <c r="S181" s="52"/>
+      <c r="T181" s="52"/>
+      <c r="U181" s="52"/>
+      <c r="V181" s="52"/>
+      <c r="W181" s="52"/>
+      <c r="X181" s="52"/>
+      <c r="Y181" s="52"/>
+      <c r="Z181" s="52"/>
+      <c r="AA181" s="52"/>
+      <c r="AB181" s="53"/>
       <c r="AC181" s="11"/>
     </row>
     <row r="182" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7214,27 +7238,27 @@
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
-      <c r="H182" s="49"/>
-      <c r="I182" s="50"/>
-      <c r="J182" s="50"/>
-      <c r="K182" s="50"/>
-      <c r="L182" s="50"/>
-      <c r="M182" s="50"/>
-      <c r="N182" s="50"/>
-      <c r="O182" s="50"/>
-      <c r="P182" s="50"/>
-      <c r="Q182" s="50"/>
-      <c r="R182" s="50"/>
-      <c r="S182" s="50"/>
-      <c r="T182" s="50"/>
-      <c r="U182" s="50"/>
-      <c r="V182" s="50"/>
-      <c r="W182" s="50"/>
-      <c r="X182" s="50"/>
-      <c r="Y182" s="50"/>
-      <c r="Z182" s="50"/>
-      <c r="AA182" s="50"/>
-      <c r="AB182" s="51"/>
+      <c r="H182" s="51"/>
+      <c r="I182" s="52"/>
+      <c r="J182" s="52"/>
+      <c r="K182" s="52"/>
+      <c r="L182" s="52"/>
+      <c r="M182" s="52"/>
+      <c r="N182" s="52"/>
+      <c r="O182" s="52"/>
+      <c r="P182" s="52"/>
+      <c r="Q182" s="52"/>
+      <c r="R182" s="52"/>
+      <c r="S182" s="52"/>
+      <c r="T182" s="52"/>
+      <c r="U182" s="52"/>
+      <c r="V182" s="52"/>
+      <c r="W182" s="52"/>
+      <c r="X182" s="52"/>
+      <c r="Y182" s="52"/>
+      <c r="Z182" s="52"/>
+      <c r="AA182" s="52"/>
+      <c r="AB182" s="53"/>
       <c r="AC182" s="11"/>
     </row>
     <row r="183" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7244,27 +7268,27 @@
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
-      <c r="H183" s="49"/>
-      <c r="I183" s="50"/>
-      <c r="J183" s="50"/>
-      <c r="K183" s="50"/>
-      <c r="L183" s="50"/>
-      <c r="M183" s="50"/>
-      <c r="N183" s="50"/>
-      <c r="O183" s="50"/>
-      <c r="P183" s="50"/>
-      <c r="Q183" s="50"/>
-      <c r="R183" s="50"/>
-      <c r="S183" s="50"/>
-      <c r="T183" s="50"/>
-      <c r="U183" s="50"/>
-      <c r="V183" s="50"/>
-      <c r="W183" s="50"/>
-      <c r="X183" s="50"/>
-      <c r="Y183" s="50"/>
-      <c r="Z183" s="50"/>
-      <c r="AA183" s="50"/>
-      <c r="AB183" s="51"/>
+      <c r="H183" s="51"/>
+      <c r="I183" s="52"/>
+      <c r="J183" s="52"/>
+      <c r="K183" s="52"/>
+      <c r="L183" s="52"/>
+      <c r="M183" s="52"/>
+      <c r="N183" s="52"/>
+      <c r="O183" s="52"/>
+      <c r="P183" s="52"/>
+      <c r="Q183" s="52"/>
+      <c r="R183" s="52"/>
+      <c r="S183" s="52"/>
+      <c r="T183" s="52"/>
+      <c r="U183" s="52"/>
+      <c r="V183" s="52"/>
+      <c r="W183" s="52"/>
+      <c r="X183" s="52"/>
+      <c r="Y183" s="52"/>
+      <c r="Z183" s="52"/>
+      <c r="AA183" s="52"/>
+      <c r="AB183" s="53"/>
       <c r="AC183" s="11"/>
     </row>
     <row r="184" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7274,27 +7298,27 @@
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
-      <c r="H184" s="49"/>
-      <c r="I184" s="50"/>
-      <c r="J184" s="50"/>
-      <c r="K184" s="50"/>
-      <c r="L184" s="50"/>
-      <c r="M184" s="50"/>
-      <c r="N184" s="50"/>
-      <c r="O184" s="50"/>
-      <c r="P184" s="50"/>
-      <c r="Q184" s="50"/>
-      <c r="R184" s="50"/>
-      <c r="S184" s="50"/>
-      <c r="T184" s="50"/>
-      <c r="U184" s="50"/>
-      <c r="V184" s="50"/>
-      <c r="W184" s="50"/>
-      <c r="X184" s="50"/>
-      <c r="Y184" s="50"/>
-      <c r="Z184" s="50"/>
-      <c r="AA184" s="50"/>
-      <c r="AB184" s="51"/>
+      <c r="H184" s="51"/>
+      <c r="I184" s="52"/>
+      <c r="J184" s="52"/>
+      <c r="K184" s="52"/>
+      <c r="L184" s="52"/>
+      <c r="M184" s="52"/>
+      <c r="N184" s="52"/>
+      <c r="O184" s="52"/>
+      <c r="P184" s="52"/>
+      <c r="Q184" s="52"/>
+      <c r="R184" s="52"/>
+      <c r="S184" s="52"/>
+      <c r="T184" s="52"/>
+      <c r="U184" s="52"/>
+      <c r="V184" s="52"/>
+      <c r="W184" s="52"/>
+      <c r="X184" s="52"/>
+      <c r="Y184" s="52"/>
+      <c r="Z184" s="52"/>
+      <c r="AA184" s="52"/>
+      <c r="AB184" s="53"/>
       <c r="AC184" s="11"/>
     </row>
     <row r="185" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7304,27 +7328,27 @@
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
-      <c r="H185" s="52"/>
-      <c r="I185" s="53"/>
-      <c r="J185" s="53"/>
-      <c r="K185" s="53"/>
-      <c r="L185" s="53"/>
-      <c r="M185" s="53"/>
-      <c r="N185" s="53"/>
-      <c r="O185" s="53"/>
-      <c r="P185" s="53"/>
-      <c r="Q185" s="53"/>
-      <c r="R185" s="53"/>
-      <c r="S185" s="53"/>
-      <c r="T185" s="53"/>
-      <c r="U185" s="53"/>
-      <c r="V185" s="53"/>
-      <c r="W185" s="53"/>
-      <c r="X185" s="53"/>
-      <c r="Y185" s="53"/>
-      <c r="Z185" s="53"/>
-      <c r="AA185" s="53"/>
-      <c r="AB185" s="54"/>
+      <c r="H185" s="54"/>
+      <c r="I185" s="55"/>
+      <c r="J185" s="55"/>
+      <c r="K185" s="55"/>
+      <c r="L185" s="55"/>
+      <c r="M185" s="55"/>
+      <c r="N185" s="55"/>
+      <c r="O185" s="55"/>
+      <c r="P185" s="55"/>
+      <c r="Q185" s="55"/>
+      <c r="R185" s="55"/>
+      <c r="S185" s="55"/>
+      <c r="T185" s="55"/>
+      <c r="U185" s="55"/>
+      <c r="V185" s="55"/>
+      <c r="W185" s="55"/>
+      <c r="X185" s="55"/>
+      <c r="Y185" s="55"/>
+      <c r="Z185" s="55"/>
+      <c r="AA185" s="55"/>
+      <c r="AB185" s="56"/>
       <c r="AC185" s="11"/>
     </row>
     <row r="186" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7366,27 +7390,27 @@
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
-      <c r="H187" s="46"/>
-      <c r="I187" s="47"/>
-      <c r="J187" s="47"/>
-      <c r="K187" s="47"/>
-      <c r="L187" s="47"/>
-      <c r="M187" s="47"/>
-      <c r="N187" s="47"/>
-      <c r="O187" s="47"/>
-      <c r="P187" s="47"/>
-      <c r="Q187" s="47"/>
-      <c r="R187" s="47"/>
-      <c r="S187" s="47"/>
-      <c r="T187" s="47"/>
-      <c r="U187" s="47"/>
-      <c r="V187" s="47"/>
-      <c r="W187" s="47"/>
-      <c r="X187" s="47"/>
-      <c r="Y187" s="47"/>
-      <c r="Z187" s="47"/>
-      <c r="AA187" s="47"/>
-      <c r="AB187" s="48"/>
+      <c r="H187" s="48"/>
+      <c r="I187" s="49"/>
+      <c r="J187" s="49"/>
+      <c r="K187" s="49"/>
+      <c r="L187" s="49"/>
+      <c r="M187" s="49"/>
+      <c r="N187" s="49"/>
+      <c r="O187" s="49"/>
+      <c r="P187" s="49"/>
+      <c r="Q187" s="49"/>
+      <c r="R187" s="49"/>
+      <c r="S187" s="49"/>
+      <c r="T187" s="49"/>
+      <c r="U187" s="49"/>
+      <c r="V187" s="49"/>
+      <c r="W187" s="49"/>
+      <c r="X187" s="49"/>
+      <c r="Y187" s="49"/>
+      <c r="Z187" s="49"/>
+      <c r="AA187" s="49"/>
+      <c r="AB187" s="50"/>
       <c r="AC187" s="11"/>
     </row>
     <row r="188" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7396,27 +7420,27 @@
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
-      <c r="H188" s="49"/>
-      <c r="I188" s="50"/>
-      <c r="J188" s="50"/>
-      <c r="K188" s="50"/>
-      <c r="L188" s="50"/>
-      <c r="M188" s="50"/>
-      <c r="N188" s="50"/>
-      <c r="O188" s="50"/>
-      <c r="P188" s="50"/>
-      <c r="Q188" s="50"/>
-      <c r="R188" s="50"/>
-      <c r="S188" s="50"/>
-      <c r="T188" s="50"/>
-      <c r="U188" s="50"/>
-      <c r="V188" s="50"/>
-      <c r="W188" s="50"/>
-      <c r="X188" s="50"/>
-      <c r="Y188" s="50"/>
-      <c r="Z188" s="50"/>
-      <c r="AA188" s="50"/>
-      <c r="AB188" s="51"/>
+      <c r="H188" s="51"/>
+      <c r="I188" s="52"/>
+      <c r="J188" s="52"/>
+      <c r="K188" s="52"/>
+      <c r="L188" s="52"/>
+      <c r="M188" s="52"/>
+      <c r="N188" s="52"/>
+      <c r="O188" s="52"/>
+      <c r="P188" s="52"/>
+      <c r="Q188" s="52"/>
+      <c r="R188" s="52"/>
+      <c r="S188" s="52"/>
+      <c r="T188" s="52"/>
+      <c r="U188" s="52"/>
+      <c r="V188" s="52"/>
+      <c r="W188" s="52"/>
+      <c r="X188" s="52"/>
+      <c r="Y188" s="52"/>
+      <c r="Z188" s="52"/>
+      <c r="AA188" s="52"/>
+      <c r="AB188" s="53"/>
       <c r="AC188" s="11"/>
     </row>
     <row r="189" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7426,27 +7450,27 @@
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
-      <c r="H189" s="49"/>
-      <c r="I189" s="50"/>
-      <c r="J189" s="50"/>
-      <c r="K189" s="50"/>
-      <c r="L189" s="50"/>
-      <c r="M189" s="50"/>
-      <c r="N189" s="50"/>
-      <c r="O189" s="50"/>
-      <c r="P189" s="50"/>
-      <c r="Q189" s="50"/>
-      <c r="R189" s="50"/>
-      <c r="S189" s="50"/>
-      <c r="T189" s="50"/>
-      <c r="U189" s="50"/>
-      <c r="V189" s="50"/>
-      <c r="W189" s="50"/>
-      <c r="X189" s="50"/>
-      <c r="Y189" s="50"/>
-      <c r="Z189" s="50"/>
-      <c r="AA189" s="50"/>
-      <c r="AB189" s="51"/>
+      <c r="H189" s="51"/>
+      <c r="I189" s="52"/>
+      <c r="J189" s="52"/>
+      <c r="K189" s="52"/>
+      <c r="L189" s="52"/>
+      <c r="M189" s="52"/>
+      <c r="N189" s="52"/>
+      <c r="O189" s="52"/>
+      <c r="P189" s="52"/>
+      <c r="Q189" s="52"/>
+      <c r="R189" s="52"/>
+      <c r="S189" s="52"/>
+      <c r="T189" s="52"/>
+      <c r="U189" s="52"/>
+      <c r="V189" s="52"/>
+      <c r="W189" s="52"/>
+      <c r="X189" s="52"/>
+      <c r="Y189" s="52"/>
+      <c r="Z189" s="52"/>
+      <c r="AA189" s="52"/>
+      <c r="AB189" s="53"/>
       <c r="AC189" s="11"/>
     </row>
     <row r="190" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7456,27 +7480,27 @@
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
-      <c r="H190" s="49"/>
-      <c r="I190" s="50"/>
-      <c r="J190" s="50"/>
-      <c r="K190" s="50"/>
-      <c r="L190" s="50"/>
-      <c r="M190" s="50"/>
-      <c r="N190" s="50"/>
-      <c r="O190" s="50"/>
-      <c r="P190" s="50"/>
-      <c r="Q190" s="50"/>
-      <c r="R190" s="50"/>
-      <c r="S190" s="50"/>
-      <c r="T190" s="50"/>
-      <c r="U190" s="50"/>
-      <c r="V190" s="50"/>
-      <c r="W190" s="50"/>
-      <c r="X190" s="50"/>
-      <c r="Y190" s="50"/>
-      <c r="Z190" s="50"/>
-      <c r="AA190" s="50"/>
-      <c r="AB190" s="51"/>
+      <c r="H190" s="51"/>
+      <c r="I190" s="52"/>
+      <c r="J190" s="52"/>
+      <c r="K190" s="52"/>
+      <c r="L190" s="52"/>
+      <c r="M190" s="52"/>
+      <c r="N190" s="52"/>
+      <c r="O190" s="52"/>
+      <c r="P190" s="52"/>
+      <c r="Q190" s="52"/>
+      <c r="R190" s="52"/>
+      <c r="S190" s="52"/>
+      <c r="T190" s="52"/>
+      <c r="U190" s="52"/>
+      <c r="V190" s="52"/>
+      <c r="W190" s="52"/>
+      <c r="X190" s="52"/>
+      <c r="Y190" s="52"/>
+      <c r="Z190" s="52"/>
+      <c r="AA190" s="52"/>
+      <c r="AB190" s="53"/>
       <c r="AC190" s="11"/>
     </row>
     <row r="191" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7486,27 +7510,27 @@
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
-      <c r="H191" s="49"/>
-      <c r="I191" s="50"/>
-      <c r="J191" s="50"/>
-      <c r="K191" s="50"/>
-      <c r="L191" s="50"/>
-      <c r="M191" s="50"/>
-      <c r="N191" s="50"/>
-      <c r="O191" s="50"/>
-      <c r="P191" s="50"/>
-      <c r="Q191" s="50"/>
-      <c r="R191" s="50"/>
-      <c r="S191" s="50"/>
-      <c r="T191" s="50"/>
-      <c r="U191" s="50"/>
-      <c r="V191" s="50"/>
-      <c r="W191" s="50"/>
-      <c r="X191" s="50"/>
-      <c r="Y191" s="50"/>
-      <c r="Z191" s="50"/>
-      <c r="AA191" s="50"/>
-      <c r="AB191" s="51"/>
+      <c r="H191" s="51"/>
+      <c r="I191" s="52"/>
+      <c r="J191" s="52"/>
+      <c r="K191" s="52"/>
+      <c r="L191" s="52"/>
+      <c r="M191" s="52"/>
+      <c r="N191" s="52"/>
+      <c r="O191" s="52"/>
+      <c r="P191" s="52"/>
+      <c r="Q191" s="52"/>
+      <c r="R191" s="52"/>
+      <c r="S191" s="52"/>
+      <c r="T191" s="52"/>
+      <c r="U191" s="52"/>
+      <c r="V191" s="52"/>
+      <c r="W191" s="52"/>
+      <c r="X191" s="52"/>
+      <c r="Y191" s="52"/>
+      <c r="Z191" s="52"/>
+      <c r="AA191" s="52"/>
+      <c r="AB191" s="53"/>
       <c r="AC191" s="11"/>
     </row>
     <row r="192" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7516,27 +7540,27 @@
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
-      <c r="H192" s="49"/>
-      <c r="I192" s="50"/>
-      <c r="J192" s="50"/>
-      <c r="K192" s="50"/>
-      <c r="L192" s="50"/>
-      <c r="M192" s="50"/>
-      <c r="N192" s="50"/>
-      <c r="O192" s="50"/>
-      <c r="P192" s="50"/>
-      <c r="Q192" s="50"/>
-      <c r="R192" s="50"/>
-      <c r="S192" s="50"/>
-      <c r="T192" s="50"/>
-      <c r="U192" s="50"/>
-      <c r="V192" s="50"/>
-      <c r="W192" s="50"/>
-      <c r="X192" s="50"/>
-      <c r="Y192" s="50"/>
-      <c r="Z192" s="50"/>
-      <c r="AA192" s="50"/>
-      <c r="AB192" s="51"/>
+      <c r="H192" s="51"/>
+      <c r="I192" s="52"/>
+      <c r="J192" s="52"/>
+      <c r="K192" s="52"/>
+      <c r="L192" s="52"/>
+      <c r="M192" s="52"/>
+      <c r="N192" s="52"/>
+      <c r="O192" s="52"/>
+      <c r="P192" s="52"/>
+      <c r="Q192" s="52"/>
+      <c r="R192" s="52"/>
+      <c r="S192" s="52"/>
+      <c r="T192" s="52"/>
+      <c r="U192" s="52"/>
+      <c r="V192" s="52"/>
+      <c r="W192" s="52"/>
+      <c r="X192" s="52"/>
+      <c r="Y192" s="52"/>
+      <c r="Z192" s="52"/>
+      <c r="AA192" s="52"/>
+      <c r="AB192" s="53"/>
       <c r="AC192" s="11"/>
     </row>
     <row r="193" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7546,27 +7570,27 @@
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
-      <c r="H193" s="52"/>
-      <c r="I193" s="53"/>
-      <c r="J193" s="53"/>
-      <c r="K193" s="53"/>
-      <c r="L193" s="53"/>
-      <c r="M193" s="53"/>
-      <c r="N193" s="53"/>
-      <c r="O193" s="53"/>
-      <c r="P193" s="53"/>
-      <c r="Q193" s="53"/>
-      <c r="R193" s="53"/>
-      <c r="S193" s="53"/>
-      <c r="T193" s="53"/>
-      <c r="U193" s="53"/>
-      <c r="V193" s="53"/>
-      <c r="W193" s="53"/>
-      <c r="X193" s="53"/>
-      <c r="Y193" s="53"/>
-      <c r="Z193" s="53"/>
-      <c r="AA193" s="53"/>
-      <c r="AB193" s="54"/>
+      <c r="H193" s="54"/>
+      <c r="I193" s="55"/>
+      <c r="J193" s="55"/>
+      <c r="K193" s="55"/>
+      <c r="L193" s="55"/>
+      <c r="M193" s="55"/>
+      <c r="N193" s="55"/>
+      <c r="O193" s="55"/>
+      <c r="P193" s="55"/>
+      <c r="Q193" s="55"/>
+      <c r="R193" s="55"/>
+      <c r="S193" s="55"/>
+      <c r="T193" s="55"/>
+      <c r="U193" s="55"/>
+      <c r="V193" s="55"/>
+      <c r="W193" s="55"/>
+      <c r="X193" s="55"/>
+      <c r="Y193" s="55"/>
+      <c r="Z193" s="55"/>
+      <c r="AA193" s="55"/>
+      <c r="AB193" s="56"/>
       <c r="AC193" s="11"/>
     </row>
     <row r="194" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7674,27 +7698,27 @@
         <v>2</v>
       </c>
       <c r="G198" s="6"/>
-      <c r="H198" s="46"/>
-      <c r="I198" s="47"/>
-      <c r="J198" s="47"/>
-      <c r="K198" s="47"/>
-      <c r="L198" s="47"/>
-      <c r="M198" s="47"/>
-      <c r="N198" s="47"/>
-      <c r="O198" s="47"/>
-      <c r="P198" s="47"/>
-      <c r="Q198" s="47"/>
-      <c r="R198" s="47"/>
-      <c r="S198" s="47"/>
-      <c r="T198" s="47"/>
-      <c r="U198" s="47"/>
-      <c r="V198" s="47"/>
-      <c r="W198" s="47"/>
-      <c r="X198" s="47"/>
-      <c r="Y198" s="47"/>
-      <c r="Z198" s="47"/>
-      <c r="AA198" s="47"/>
-      <c r="AB198" s="48"/>
+      <c r="H198" s="48"/>
+      <c r="I198" s="49"/>
+      <c r="J198" s="49"/>
+      <c r="K198" s="49"/>
+      <c r="L198" s="49"/>
+      <c r="M198" s="49"/>
+      <c r="N198" s="49"/>
+      <c r="O198" s="49"/>
+      <c r="P198" s="49"/>
+      <c r="Q198" s="49"/>
+      <c r="R198" s="49"/>
+      <c r="S198" s="49"/>
+      <c r="T198" s="49"/>
+      <c r="U198" s="49"/>
+      <c r="V198" s="49"/>
+      <c r="W198" s="49"/>
+      <c r="X198" s="49"/>
+      <c r="Y198" s="49"/>
+      <c r="Z198" s="49"/>
+      <c r="AA198" s="49"/>
+      <c r="AB198" s="50"/>
       <c r="AC198" s="11"/>
     </row>
     <row r="199" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7704,27 +7728,27 @@
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
       <c r="G199" s="6"/>
-      <c r="H199" s="49"/>
-      <c r="I199" s="50"/>
-      <c r="J199" s="50"/>
-      <c r="K199" s="50"/>
-      <c r="L199" s="50"/>
-      <c r="M199" s="50"/>
-      <c r="N199" s="50"/>
-      <c r="O199" s="50"/>
-      <c r="P199" s="50"/>
-      <c r="Q199" s="50"/>
-      <c r="R199" s="50"/>
-      <c r="S199" s="50"/>
-      <c r="T199" s="50"/>
-      <c r="U199" s="50"/>
-      <c r="V199" s="50"/>
-      <c r="W199" s="50"/>
-      <c r="X199" s="50"/>
-      <c r="Y199" s="50"/>
-      <c r="Z199" s="50"/>
-      <c r="AA199" s="50"/>
-      <c r="AB199" s="51"/>
+      <c r="H199" s="51"/>
+      <c r="I199" s="52"/>
+      <c r="J199" s="52"/>
+      <c r="K199" s="52"/>
+      <c r="L199" s="52"/>
+      <c r="M199" s="52"/>
+      <c r="N199" s="52"/>
+      <c r="O199" s="52"/>
+      <c r="P199" s="52"/>
+      <c r="Q199" s="52"/>
+      <c r="R199" s="52"/>
+      <c r="S199" s="52"/>
+      <c r="T199" s="52"/>
+      <c r="U199" s="52"/>
+      <c r="V199" s="52"/>
+      <c r="W199" s="52"/>
+      <c r="X199" s="52"/>
+      <c r="Y199" s="52"/>
+      <c r="Z199" s="52"/>
+      <c r="AA199" s="52"/>
+      <c r="AB199" s="53"/>
       <c r="AC199" s="11"/>
     </row>
     <row r="200" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7734,27 +7758,27 @@
       <c r="E200" s="6"/>
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
-      <c r="H200" s="49"/>
-      <c r="I200" s="50"/>
-      <c r="J200" s="50"/>
-      <c r="K200" s="50"/>
-      <c r="L200" s="50"/>
-      <c r="M200" s="50"/>
-      <c r="N200" s="50"/>
-      <c r="O200" s="50"/>
-      <c r="P200" s="50"/>
-      <c r="Q200" s="50"/>
-      <c r="R200" s="50"/>
-      <c r="S200" s="50"/>
-      <c r="T200" s="50"/>
-      <c r="U200" s="50"/>
-      <c r="V200" s="50"/>
-      <c r="W200" s="50"/>
-      <c r="X200" s="50"/>
-      <c r="Y200" s="50"/>
-      <c r="Z200" s="50"/>
-      <c r="AA200" s="50"/>
-      <c r="AB200" s="51"/>
+      <c r="H200" s="51"/>
+      <c r="I200" s="52"/>
+      <c r="J200" s="52"/>
+      <c r="K200" s="52"/>
+      <c r="L200" s="52"/>
+      <c r="M200" s="52"/>
+      <c r="N200" s="52"/>
+      <c r="O200" s="52"/>
+      <c r="P200" s="52"/>
+      <c r="Q200" s="52"/>
+      <c r="R200" s="52"/>
+      <c r="S200" s="52"/>
+      <c r="T200" s="52"/>
+      <c r="U200" s="52"/>
+      <c r="V200" s="52"/>
+      <c r="W200" s="52"/>
+      <c r="X200" s="52"/>
+      <c r="Y200" s="52"/>
+      <c r="Z200" s="52"/>
+      <c r="AA200" s="52"/>
+      <c r="AB200" s="53"/>
       <c r="AC200" s="11"/>
     </row>
     <row r="201" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7764,27 +7788,27 @@
       <c r="E201" s="6"/>
       <c r="F201" s="6"/>
       <c r="G201" s="6"/>
-      <c r="H201" s="49"/>
-      <c r="I201" s="50"/>
-      <c r="J201" s="50"/>
-      <c r="K201" s="50"/>
-      <c r="L201" s="50"/>
-      <c r="M201" s="50"/>
-      <c r="N201" s="50"/>
-      <c r="O201" s="50"/>
-      <c r="P201" s="50"/>
-      <c r="Q201" s="50"/>
-      <c r="R201" s="50"/>
-      <c r="S201" s="50"/>
-      <c r="T201" s="50"/>
-      <c r="U201" s="50"/>
-      <c r="V201" s="50"/>
-      <c r="W201" s="50"/>
-      <c r="X201" s="50"/>
-      <c r="Y201" s="50"/>
-      <c r="Z201" s="50"/>
-      <c r="AA201" s="50"/>
-      <c r="AB201" s="51"/>
+      <c r="H201" s="51"/>
+      <c r="I201" s="52"/>
+      <c r="J201" s="52"/>
+      <c r="K201" s="52"/>
+      <c r="L201" s="52"/>
+      <c r="M201" s="52"/>
+      <c r="N201" s="52"/>
+      <c r="O201" s="52"/>
+      <c r="P201" s="52"/>
+      <c r="Q201" s="52"/>
+      <c r="R201" s="52"/>
+      <c r="S201" s="52"/>
+      <c r="T201" s="52"/>
+      <c r="U201" s="52"/>
+      <c r="V201" s="52"/>
+      <c r="W201" s="52"/>
+      <c r="X201" s="52"/>
+      <c r="Y201" s="52"/>
+      <c r="Z201" s="52"/>
+      <c r="AA201" s="52"/>
+      <c r="AB201" s="53"/>
       <c r="AC201" s="11"/>
     </row>
     <row r="202" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7794,27 +7818,27 @@
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
-      <c r="H202" s="49"/>
-      <c r="I202" s="50"/>
-      <c r="J202" s="50"/>
-      <c r="K202" s="50"/>
-      <c r="L202" s="50"/>
-      <c r="M202" s="50"/>
-      <c r="N202" s="50"/>
-      <c r="O202" s="50"/>
-      <c r="P202" s="50"/>
-      <c r="Q202" s="50"/>
-      <c r="R202" s="50"/>
-      <c r="S202" s="50"/>
-      <c r="T202" s="50"/>
-      <c r="U202" s="50"/>
-      <c r="V202" s="50"/>
-      <c r="W202" s="50"/>
-      <c r="X202" s="50"/>
-      <c r="Y202" s="50"/>
-      <c r="Z202" s="50"/>
-      <c r="AA202" s="50"/>
-      <c r="AB202" s="51"/>
+      <c r="H202" s="51"/>
+      <c r="I202" s="52"/>
+      <c r="J202" s="52"/>
+      <c r="K202" s="52"/>
+      <c r="L202" s="52"/>
+      <c r="M202" s="52"/>
+      <c r="N202" s="52"/>
+      <c r="O202" s="52"/>
+      <c r="P202" s="52"/>
+      <c r="Q202" s="52"/>
+      <c r="R202" s="52"/>
+      <c r="S202" s="52"/>
+      <c r="T202" s="52"/>
+      <c r="U202" s="52"/>
+      <c r="V202" s="52"/>
+      <c r="W202" s="52"/>
+      <c r="X202" s="52"/>
+      <c r="Y202" s="52"/>
+      <c r="Z202" s="52"/>
+      <c r="AA202" s="52"/>
+      <c r="AB202" s="53"/>
       <c r="AC202" s="11"/>
     </row>
     <row r="203" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7824,27 +7848,27 @@
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
-      <c r="H203" s="49"/>
-      <c r="I203" s="50"/>
-      <c r="J203" s="50"/>
-      <c r="K203" s="50"/>
-      <c r="L203" s="50"/>
-      <c r="M203" s="50"/>
-      <c r="N203" s="50"/>
-      <c r="O203" s="50"/>
-      <c r="P203" s="50"/>
-      <c r="Q203" s="50"/>
-      <c r="R203" s="50"/>
-      <c r="S203" s="50"/>
-      <c r="T203" s="50"/>
-      <c r="U203" s="50"/>
-      <c r="V203" s="50"/>
-      <c r="W203" s="50"/>
-      <c r="X203" s="50"/>
-      <c r="Y203" s="50"/>
-      <c r="Z203" s="50"/>
-      <c r="AA203" s="50"/>
-      <c r="AB203" s="51"/>
+      <c r="H203" s="51"/>
+      <c r="I203" s="52"/>
+      <c r="J203" s="52"/>
+      <c r="K203" s="52"/>
+      <c r="L203" s="52"/>
+      <c r="M203" s="52"/>
+      <c r="N203" s="52"/>
+      <c r="O203" s="52"/>
+      <c r="P203" s="52"/>
+      <c r="Q203" s="52"/>
+      <c r="R203" s="52"/>
+      <c r="S203" s="52"/>
+      <c r="T203" s="52"/>
+      <c r="U203" s="52"/>
+      <c r="V203" s="52"/>
+      <c r="W203" s="52"/>
+      <c r="X203" s="52"/>
+      <c r="Y203" s="52"/>
+      <c r="Z203" s="52"/>
+      <c r="AA203" s="52"/>
+      <c r="AB203" s="53"/>
       <c r="AC203" s="11"/>
     </row>
     <row r="204" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7854,27 +7878,27 @@
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
-      <c r="H204" s="52"/>
-      <c r="I204" s="53"/>
-      <c r="J204" s="53"/>
-      <c r="K204" s="53"/>
-      <c r="L204" s="53"/>
-      <c r="M204" s="53"/>
-      <c r="N204" s="53"/>
-      <c r="O204" s="53"/>
-      <c r="P204" s="53"/>
-      <c r="Q204" s="53"/>
-      <c r="R204" s="53"/>
-      <c r="S204" s="53"/>
-      <c r="T204" s="53"/>
-      <c r="U204" s="53"/>
-      <c r="V204" s="53"/>
-      <c r="W204" s="53"/>
-      <c r="X204" s="53"/>
-      <c r="Y204" s="53"/>
-      <c r="Z204" s="53"/>
-      <c r="AA204" s="53"/>
-      <c r="AB204" s="54"/>
+      <c r="H204" s="54"/>
+      <c r="I204" s="55"/>
+      <c r="J204" s="55"/>
+      <c r="K204" s="55"/>
+      <c r="L204" s="55"/>
+      <c r="M204" s="55"/>
+      <c r="N204" s="55"/>
+      <c r="O204" s="55"/>
+      <c r="P204" s="55"/>
+      <c r="Q204" s="55"/>
+      <c r="R204" s="55"/>
+      <c r="S204" s="55"/>
+      <c r="T204" s="55"/>
+      <c r="U204" s="55"/>
+      <c r="V204" s="55"/>
+      <c r="W204" s="55"/>
+      <c r="X204" s="55"/>
+      <c r="Y204" s="55"/>
+      <c r="Z204" s="55"/>
+      <c r="AA204" s="55"/>
+      <c r="AB204" s="56"/>
       <c r="AC204" s="11"/>
     </row>
     <row r="205" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7916,27 +7940,27 @@
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
-      <c r="H206" s="46"/>
-      <c r="I206" s="47"/>
-      <c r="J206" s="47"/>
-      <c r="K206" s="47"/>
-      <c r="L206" s="47"/>
-      <c r="M206" s="47"/>
-      <c r="N206" s="47"/>
-      <c r="O206" s="47"/>
-      <c r="P206" s="47"/>
-      <c r="Q206" s="47"/>
-      <c r="R206" s="47"/>
-      <c r="S206" s="47"/>
-      <c r="T206" s="47"/>
-      <c r="U206" s="47"/>
-      <c r="V206" s="47"/>
-      <c r="W206" s="47"/>
-      <c r="X206" s="47"/>
-      <c r="Y206" s="47"/>
-      <c r="Z206" s="47"/>
-      <c r="AA206" s="47"/>
-      <c r="AB206" s="48"/>
+      <c r="H206" s="48"/>
+      <c r="I206" s="49"/>
+      <c r="J206" s="49"/>
+      <c r="K206" s="49"/>
+      <c r="L206" s="49"/>
+      <c r="M206" s="49"/>
+      <c r="N206" s="49"/>
+      <c r="O206" s="49"/>
+      <c r="P206" s="49"/>
+      <c r="Q206" s="49"/>
+      <c r="R206" s="49"/>
+      <c r="S206" s="49"/>
+      <c r="T206" s="49"/>
+      <c r="U206" s="49"/>
+      <c r="V206" s="49"/>
+      <c r="W206" s="49"/>
+      <c r="X206" s="49"/>
+      <c r="Y206" s="49"/>
+      <c r="Z206" s="49"/>
+      <c r="AA206" s="49"/>
+      <c r="AB206" s="50"/>
       <c r="AC206" s="11"/>
     </row>
     <row r="207" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7946,27 +7970,27 @@
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
-      <c r="H207" s="49"/>
-      <c r="I207" s="50"/>
-      <c r="J207" s="50"/>
-      <c r="K207" s="50"/>
-      <c r="L207" s="50"/>
-      <c r="M207" s="50"/>
-      <c r="N207" s="50"/>
-      <c r="O207" s="50"/>
-      <c r="P207" s="50"/>
-      <c r="Q207" s="50"/>
-      <c r="R207" s="50"/>
-      <c r="S207" s="50"/>
-      <c r="T207" s="50"/>
-      <c r="U207" s="50"/>
-      <c r="V207" s="50"/>
-      <c r="W207" s="50"/>
-      <c r="X207" s="50"/>
-      <c r="Y207" s="50"/>
-      <c r="Z207" s="50"/>
-      <c r="AA207" s="50"/>
-      <c r="AB207" s="51"/>
+      <c r="H207" s="51"/>
+      <c r="I207" s="52"/>
+      <c r="J207" s="52"/>
+      <c r="K207" s="52"/>
+      <c r="L207" s="52"/>
+      <c r="M207" s="52"/>
+      <c r="N207" s="52"/>
+      <c r="O207" s="52"/>
+      <c r="P207" s="52"/>
+      <c r="Q207" s="52"/>
+      <c r="R207" s="52"/>
+      <c r="S207" s="52"/>
+      <c r="T207" s="52"/>
+      <c r="U207" s="52"/>
+      <c r="V207" s="52"/>
+      <c r="W207" s="52"/>
+      <c r="X207" s="52"/>
+      <c r="Y207" s="52"/>
+      <c r="Z207" s="52"/>
+      <c r="AA207" s="52"/>
+      <c r="AB207" s="53"/>
       <c r="AC207" s="11"/>
     </row>
     <row r="208" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7976,27 +8000,27 @@
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
       <c r="G208" s="6"/>
-      <c r="H208" s="49"/>
-      <c r="I208" s="50"/>
-      <c r="J208" s="50"/>
-      <c r="K208" s="50"/>
-      <c r="L208" s="50"/>
-      <c r="M208" s="50"/>
-      <c r="N208" s="50"/>
-      <c r="O208" s="50"/>
-      <c r="P208" s="50"/>
-      <c r="Q208" s="50"/>
-      <c r="R208" s="50"/>
-      <c r="S208" s="50"/>
-      <c r="T208" s="50"/>
-      <c r="U208" s="50"/>
-      <c r="V208" s="50"/>
-      <c r="W208" s="50"/>
-      <c r="X208" s="50"/>
-      <c r="Y208" s="50"/>
-      <c r="Z208" s="50"/>
-      <c r="AA208" s="50"/>
-      <c r="AB208" s="51"/>
+      <c r="H208" s="51"/>
+      <c r="I208" s="52"/>
+      <c r="J208" s="52"/>
+      <c r="K208" s="52"/>
+      <c r="L208" s="52"/>
+      <c r="M208" s="52"/>
+      <c r="N208" s="52"/>
+      <c r="O208" s="52"/>
+      <c r="P208" s="52"/>
+      <c r="Q208" s="52"/>
+      <c r="R208" s="52"/>
+      <c r="S208" s="52"/>
+      <c r="T208" s="52"/>
+      <c r="U208" s="52"/>
+      <c r="V208" s="52"/>
+      <c r="W208" s="52"/>
+      <c r="X208" s="52"/>
+      <c r="Y208" s="52"/>
+      <c r="Z208" s="52"/>
+      <c r="AA208" s="52"/>
+      <c r="AB208" s="53"/>
       <c r="AC208" s="11"/>
     </row>
     <row r="209" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8006,27 +8030,27 @@
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
-      <c r="H209" s="49"/>
-      <c r="I209" s="50"/>
-      <c r="J209" s="50"/>
-      <c r="K209" s="50"/>
-      <c r="L209" s="50"/>
-      <c r="M209" s="50"/>
-      <c r="N209" s="50"/>
-      <c r="O209" s="50"/>
-      <c r="P209" s="50"/>
-      <c r="Q209" s="50"/>
-      <c r="R209" s="50"/>
-      <c r="S209" s="50"/>
-      <c r="T209" s="50"/>
-      <c r="U209" s="50"/>
-      <c r="V209" s="50"/>
-      <c r="W209" s="50"/>
-      <c r="X209" s="50"/>
-      <c r="Y209" s="50"/>
-      <c r="Z209" s="50"/>
-      <c r="AA209" s="50"/>
-      <c r="AB209" s="51"/>
+      <c r="H209" s="51"/>
+      <c r="I209" s="52"/>
+      <c r="J209" s="52"/>
+      <c r="K209" s="52"/>
+      <c r="L209" s="52"/>
+      <c r="M209" s="52"/>
+      <c r="N209" s="52"/>
+      <c r="O209" s="52"/>
+      <c r="P209" s="52"/>
+      <c r="Q209" s="52"/>
+      <c r="R209" s="52"/>
+      <c r="S209" s="52"/>
+      <c r="T209" s="52"/>
+      <c r="U209" s="52"/>
+      <c r="V209" s="52"/>
+      <c r="W209" s="52"/>
+      <c r="X209" s="52"/>
+      <c r="Y209" s="52"/>
+      <c r="Z209" s="52"/>
+      <c r="AA209" s="52"/>
+      <c r="AB209" s="53"/>
       <c r="AC209" s="11"/>
     </row>
     <row r="210" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8036,27 +8060,27 @@
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
-      <c r="H210" s="49"/>
-      <c r="I210" s="50"/>
-      <c r="J210" s="50"/>
-      <c r="K210" s="50"/>
-      <c r="L210" s="50"/>
-      <c r="M210" s="50"/>
-      <c r="N210" s="50"/>
-      <c r="O210" s="50"/>
-      <c r="P210" s="50"/>
-      <c r="Q210" s="50"/>
-      <c r="R210" s="50"/>
-      <c r="S210" s="50"/>
-      <c r="T210" s="50"/>
-      <c r="U210" s="50"/>
-      <c r="V210" s="50"/>
-      <c r="W210" s="50"/>
-      <c r="X210" s="50"/>
-      <c r="Y210" s="50"/>
-      <c r="Z210" s="50"/>
-      <c r="AA210" s="50"/>
-      <c r="AB210" s="51"/>
+      <c r="H210" s="51"/>
+      <c r="I210" s="52"/>
+      <c r="J210" s="52"/>
+      <c r="K210" s="52"/>
+      <c r="L210" s="52"/>
+      <c r="M210" s="52"/>
+      <c r="N210" s="52"/>
+      <c r="O210" s="52"/>
+      <c r="P210" s="52"/>
+      <c r="Q210" s="52"/>
+      <c r="R210" s="52"/>
+      <c r="S210" s="52"/>
+      <c r="T210" s="52"/>
+      <c r="U210" s="52"/>
+      <c r="V210" s="52"/>
+      <c r="W210" s="52"/>
+      <c r="X210" s="52"/>
+      <c r="Y210" s="52"/>
+      <c r="Z210" s="52"/>
+      <c r="AA210" s="52"/>
+      <c r="AB210" s="53"/>
       <c r="AC210" s="11"/>
     </row>
     <row r="211" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8066,27 +8090,27 @@
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
       <c r="G211" s="6"/>
-      <c r="H211" s="49"/>
-      <c r="I211" s="50"/>
-      <c r="J211" s="50"/>
-      <c r="K211" s="50"/>
-      <c r="L211" s="50"/>
-      <c r="M211" s="50"/>
-      <c r="N211" s="50"/>
-      <c r="O211" s="50"/>
-      <c r="P211" s="50"/>
-      <c r="Q211" s="50"/>
-      <c r="R211" s="50"/>
-      <c r="S211" s="50"/>
-      <c r="T211" s="50"/>
-      <c r="U211" s="50"/>
-      <c r="V211" s="50"/>
-      <c r="W211" s="50"/>
-      <c r="X211" s="50"/>
-      <c r="Y211" s="50"/>
-      <c r="Z211" s="50"/>
-      <c r="AA211" s="50"/>
-      <c r="AB211" s="51"/>
+      <c r="H211" s="51"/>
+      <c r="I211" s="52"/>
+      <c r="J211" s="52"/>
+      <c r="K211" s="52"/>
+      <c r="L211" s="52"/>
+      <c r="M211" s="52"/>
+      <c r="N211" s="52"/>
+      <c r="O211" s="52"/>
+      <c r="P211" s="52"/>
+      <c r="Q211" s="52"/>
+      <c r="R211" s="52"/>
+      <c r="S211" s="52"/>
+      <c r="T211" s="52"/>
+      <c r="U211" s="52"/>
+      <c r="V211" s="52"/>
+      <c r="W211" s="52"/>
+      <c r="X211" s="52"/>
+      <c r="Y211" s="52"/>
+      <c r="Z211" s="52"/>
+      <c r="AA211" s="52"/>
+      <c r="AB211" s="53"/>
       <c r="AC211" s="11"/>
     </row>
     <row r="212" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8096,27 +8120,27 @@
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
-      <c r="H212" s="52"/>
-      <c r="I212" s="53"/>
-      <c r="J212" s="53"/>
-      <c r="K212" s="53"/>
-      <c r="L212" s="53"/>
-      <c r="M212" s="53"/>
-      <c r="N212" s="53"/>
-      <c r="O212" s="53"/>
-      <c r="P212" s="53"/>
-      <c r="Q212" s="53"/>
-      <c r="R212" s="53"/>
-      <c r="S212" s="53"/>
-      <c r="T212" s="53"/>
-      <c r="U212" s="53"/>
-      <c r="V212" s="53"/>
-      <c r="W212" s="53"/>
-      <c r="X212" s="53"/>
-      <c r="Y212" s="53"/>
-      <c r="Z212" s="53"/>
-      <c r="AA212" s="53"/>
-      <c r="AB212" s="54"/>
+      <c r="H212" s="54"/>
+      <c r="I212" s="55"/>
+      <c r="J212" s="55"/>
+      <c r="K212" s="55"/>
+      <c r="L212" s="55"/>
+      <c r="M212" s="55"/>
+      <c r="N212" s="55"/>
+      <c r="O212" s="55"/>
+      <c r="P212" s="55"/>
+      <c r="Q212" s="55"/>
+      <c r="R212" s="55"/>
+      <c r="S212" s="55"/>
+      <c r="T212" s="55"/>
+      <c r="U212" s="55"/>
+      <c r="V212" s="55"/>
+      <c r="W212" s="55"/>
+      <c r="X212" s="55"/>
+      <c r="Y212" s="55"/>
+      <c r="Z212" s="55"/>
+      <c r="AA212" s="55"/>
+      <c r="AB212" s="56"/>
       <c r="AC212" s="11"/>
     </row>
     <row r="213" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8151,11 +8175,38 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B177:B194"/>
+    <mergeCell ref="D179:E179"/>
+    <mergeCell ref="H179:AB185"/>
+    <mergeCell ref="H187:AB193"/>
+    <mergeCell ref="B196:B213"/>
+    <mergeCell ref="D198:E198"/>
+    <mergeCell ref="H198:AB204"/>
+    <mergeCell ref="H206:AB212"/>
+    <mergeCell ref="B139:B156"/>
+    <mergeCell ref="D141:E141"/>
+    <mergeCell ref="H141:AB147"/>
+    <mergeCell ref="H149:AB155"/>
+    <mergeCell ref="B158:B175"/>
+    <mergeCell ref="D160:E160"/>
+    <mergeCell ref="H160:AB166"/>
+    <mergeCell ref="H168:AB174"/>
+    <mergeCell ref="B101:B118"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="H103:AB109"/>
+    <mergeCell ref="H111:AB117"/>
+    <mergeCell ref="B120:B137"/>
+    <mergeCell ref="D122:E122"/>
+    <mergeCell ref="H122:AB128"/>
+    <mergeCell ref="H130:AB136"/>
+    <mergeCell ref="B63:B80"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="H65:AB71"/>
+    <mergeCell ref="H73:AB79"/>
+    <mergeCell ref="B82:B99"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="H84:AB90"/>
+    <mergeCell ref="H92:AB98"/>
     <mergeCell ref="B25:B42"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="H27:AB33"/>
@@ -8164,38 +8215,11 @@
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="H46:AB52"/>
     <mergeCell ref="H54:AB60"/>
-    <mergeCell ref="B63:B80"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="H65:AB71"/>
-    <mergeCell ref="H73:AB79"/>
-    <mergeCell ref="B82:B99"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="H84:AB90"/>
-    <mergeCell ref="H92:AB98"/>
-    <mergeCell ref="B101:B118"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="H103:AB109"/>
-    <mergeCell ref="H111:AB117"/>
-    <mergeCell ref="B120:B137"/>
-    <mergeCell ref="D122:E122"/>
-    <mergeCell ref="H122:AB128"/>
-    <mergeCell ref="H130:AB136"/>
-    <mergeCell ref="B139:B156"/>
-    <mergeCell ref="D141:E141"/>
-    <mergeCell ref="H141:AB147"/>
-    <mergeCell ref="H149:AB155"/>
-    <mergeCell ref="B158:B175"/>
-    <mergeCell ref="D160:E160"/>
-    <mergeCell ref="H160:AB166"/>
-    <mergeCell ref="H168:AB174"/>
-    <mergeCell ref="B177:B194"/>
-    <mergeCell ref="D179:E179"/>
-    <mergeCell ref="H179:AB185"/>
-    <mergeCell ref="H187:AB193"/>
-    <mergeCell ref="B196:B213"/>
-    <mergeCell ref="D198:E198"/>
-    <mergeCell ref="H198:AB204"/>
-    <mergeCell ref="H206:AB212"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -8218,15 +8242,15 @@
       </c>
     </row>
     <row r="3" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="26">
+      <c r="B3" s="26" t="str">
         <f xml:space="preserve"> '4.2.1'!B3</f>
-        <v>0</v>
+        <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>21</v>
       </c>
@@ -9068,27 +9092,27 @@
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" s="19"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="47"/>
-      <c r="U34" s="47"/>
-      <c r="V34" s="47"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="47"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="47"/>
-      <c r="AA34" s="47"/>
-      <c r="AB34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="49"/>
+      <c r="L34" s="49"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="49"/>
+      <c r="P34" s="49"/>
+      <c r="Q34" s="49"/>
+      <c r="R34" s="49"/>
+      <c r="S34" s="49"/>
+      <c r="T34" s="49"/>
+      <c r="U34" s="49"/>
+      <c r="V34" s="49"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="49"/>
+      <c r="Y34" s="49"/>
+      <c r="Z34" s="49"/>
+      <c r="AA34" s="49"/>
+      <c r="AB34" s="50"/>
       <c r="AC34" s="16"/>
     </row>
     <row r="35" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9098,27 +9122,27 @@
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50"/>
-      <c r="S35" s="50"/>
-      <c r="T35" s="50"/>
-      <c r="U35" s="50"/>
-      <c r="V35" s="50"/>
-      <c r="W35" s="50"/>
-      <c r="X35" s="50"/>
-      <c r="Y35" s="50"/>
-      <c r="Z35" s="50"/>
-      <c r="AA35" s="50"/>
-      <c r="AB35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="52"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="52"/>
+      <c r="X35" s="52"/>
+      <c r="Y35" s="52"/>
+      <c r="Z35" s="52"/>
+      <c r="AA35" s="52"/>
+      <c r="AB35" s="53"/>
       <c r="AC35" s="16"/>
     </row>
     <row r="36" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9128,27 +9152,27 @@
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="50"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
-      <c r="Y36" s="50"/>
-      <c r="Z36" s="50"/>
-      <c r="AA36" s="50"/>
-      <c r="AB36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="52"/>
+      <c r="Q36" s="52"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="52"/>
+      <c r="T36" s="52"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="52"/>
+      <c r="W36" s="52"/>
+      <c r="X36" s="52"/>
+      <c r="Y36" s="52"/>
+      <c r="Z36" s="52"/>
+      <c r="AA36" s="52"/>
+      <c r="AB36" s="53"/>
       <c r="AC36" s="16"/>
     </row>
     <row r="37" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9158,27 +9182,27 @@
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="50"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+      <c r="O37" s="52"/>
+      <c r="P37" s="52"/>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="52"/>
+      <c r="T37" s="52"/>
+      <c r="U37" s="52"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="52"/>
+      <c r="X37" s="52"/>
+      <c r="Y37" s="52"/>
+      <c r="Z37" s="52"/>
+      <c r="AA37" s="52"/>
+      <c r="AB37" s="53"/>
       <c r="AC37" s="16"/>
     </row>
     <row r="38" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9188,27 +9212,27 @@
       <c r="E38" s="19"/>
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50"/>
-      <c r="S38" s="50"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="50"/>
-      <c r="Y38" s="50"/>
-      <c r="Z38" s="50"/>
-      <c r="AA38" s="50"/>
-      <c r="AB38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="52"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="52"/>
+      <c r="X38" s="52"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="52"/>
+      <c r="AA38" s="52"/>
+      <c r="AB38" s="53"/>
       <c r="AC38" s="16"/>
     </row>
     <row r="39" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9218,27 +9242,27 @@
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50"/>
-      <c r="Y39" s="50"/>
-      <c r="Z39" s="50"/>
-      <c r="AA39" s="50"/>
-      <c r="AB39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="52"/>
+      <c r="P39" s="52"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="52"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="52"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="52"/>
+      <c r="X39" s="52"/>
+      <c r="Y39" s="52"/>
+      <c r="Z39" s="52"/>
+      <c r="AA39" s="52"/>
+      <c r="AB39" s="53"/>
       <c r="AC39" s="16"/>
     </row>
     <row r="40" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9248,27 +9272,27 @@
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="53"/>
-      <c r="N40" s="53"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="53"/>
-      <c r="Q40" s="53"/>
-      <c r="R40" s="53"/>
-      <c r="S40" s="53"/>
-      <c r="T40" s="53"/>
-      <c r="U40" s="53"/>
-      <c r="V40" s="53"/>
-      <c r="W40" s="53"/>
-      <c r="X40" s="53"/>
-      <c r="Y40" s="53"/>
-      <c r="Z40" s="53"/>
-      <c r="AA40" s="53"/>
-      <c r="AB40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="55"/>
+      <c r="R40" s="55"/>
+      <c r="S40" s="55"/>
+      <c r="T40" s="55"/>
+      <c r="U40" s="55"/>
+      <c r="V40" s="55"/>
+      <c r="W40" s="55"/>
+      <c r="X40" s="55"/>
+      <c r="Y40" s="55"/>
+      <c r="Z40" s="55"/>
+      <c r="AA40" s="55"/>
+      <c r="AB40" s="56"/>
       <c r="AC40" s="16"/>
     </row>
     <row r="41" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9310,27 +9334,27 @@
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
       <c r="G42" s="19"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="47"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47"/>
-      <c r="S42" s="47"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="47"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="47"/>
-      <c r="X42" s="47"/>
-      <c r="Y42" s="47"/>
-      <c r="Z42" s="47"/>
-      <c r="AA42" s="47"/>
-      <c r="AB42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="49"/>
+      <c r="O42" s="49"/>
+      <c r="P42" s="49"/>
+      <c r="Q42" s="49"/>
+      <c r="R42" s="49"/>
+      <c r="S42" s="49"/>
+      <c r="T42" s="49"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="49"/>
+      <c r="W42" s="49"/>
+      <c r="X42" s="49"/>
+      <c r="Y42" s="49"/>
+      <c r="Z42" s="49"/>
+      <c r="AA42" s="49"/>
+      <c r="AB42" s="50"/>
       <c r="AC42" s="16"/>
     </row>
     <row r="43" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9340,27 +9364,27 @@
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="50"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="50"/>
-      <c r="AA43" s="50"/>
-      <c r="AB43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="52"/>
+      <c r="L43" s="52"/>
+      <c r="M43" s="52"/>
+      <c r="N43" s="52"/>
+      <c r="O43" s="52"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="52"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="52"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="52"/>
+      <c r="W43" s="52"/>
+      <c r="X43" s="52"/>
+      <c r="Y43" s="52"/>
+      <c r="Z43" s="52"/>
+      <c r="AA43" s="52"/>
+      <c r="AB43" s="53"/>
       <c r="AC43" s="16"/>
     </row>
     <row r="44" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9370,27 +9394,27 @@
       <c r="E44" s="19"/>
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="50"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50"/>
-      <c r="S44" s="50"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
-      <c r="V44" s="50"/>
-      <c r="W44" s="50"/>
-      <c r="X44" s="50"/>
-      <c r="Y44" s="50"/>
-      <c r="Z44" s="50"/>
-      <c r="AA44" s="50"/>
-      <c r="AB44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="52"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="52"/>
+      <c r="O44" s="52"/>
+      <c r="P44" s="52"/>
+      <c r="Q44" s="52"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="52"/>
+      <c r="T44" s="52"/>
+      <c r="U44" s="52"/>
+      <c r="V44" s="52"/>
+      <c r="W44" s="52"/>
+      <c r="X44" s="52"/>
+      <c r="Y44" s="52"/>
+      <c r="Z44" s="52"/>
+      <c r="AA44" s="52"/>
+      <c r="AB44" s="53"/>
       <c r="AC44" s="16"/>
     </row>
     <row r="45" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9400,27 +9424,27 @@
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="50"/>
-      <c r="O45" s="50"/>
-      <c r="P45" s="50"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50"/>
-      <c r="S45" s="50"/>
-      <c r="T45" s="50"/>
-      <c r="U45" s="50"/>
-      <c r="V45" s="50"/>
-      <c r="W45" s="50"/>
-      <c r="X45" s="50"/>
-      <c r="Y45" s="50"/>
-      <c r="Z45" s="50"/>
-      <c r="AA45" s="50"/>
-      <c r="AB45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="52"/>
+      <c r="O45" s="52"/>
+      <c r="P45" s="52"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="52"/>
+      <c r="V45" s="52"/>
+      <c r="W45" s="52"/>
+      <c r="X45" s="52"/>
+      <c r="Y45" s="52"/>
+      <c r="Z45" s="52"/>
+      <c r="AA45" s="52"/>
+      <c r="AB45" s="53"/>
       <c r="AC45" s="16"/>
     </row>
     <row r="46" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9430,27 +9454,27 @@
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="50"/>
-      <c r="J46" s="50"/>
-      <c r="K46" s="50"/>
-      <c r="L46" s="50"/>
-      <c r="M46" s="50"/>
-      <c r="N46" s="50"/>
-      <c r="O46" s="50"/>
-      <c r="P46" s="50"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50"/>
-      <c r="S46" s="50"/>
-      <c r="T46" s="50"/>
-      <c r="U46" s="50"/>
-      <c r="V46" s="50"/>
-      <c r="W46" s="50"/>
-      <c r="X46" s="50"/>
-      <c r="Y46" s="50"/>
-      <c r="Z46" s="50"/>
-      <c r="AA46" s="50"/>
-      <c r="AB46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="52"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="52"/>
+      <c r="O46" s="52"/>
+      <c r="P46" s="52"/>
+      <c r="Q46" s="52"/>
+      <c r="R46" s="52"/>
+      <c r="S46" s="52"/>
+      <c r="T46" s="52"/>
+      <c r="U46" s="52"/>
+      <c r="V46" s="52"/>
+      <c r="W46" s="52"/>
+      <c r="X46" s="52"/>
+      <c r="Y46" s="52"/>
+      <c r="Z46" s="52"/>
+      <c r="AA46" s="52"/>
+      <c r="AB46" s="53"/>
       <c r="AC46" s="16"/>
     </row>
     <row r="47" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9460,27 +9484,27 @@
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
       <c r="G47" s="19"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="50"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="50"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50"/>
-      <c r="S47" s="50"/>
-      <c r="T47" s="50"/>
-      <c r="U47" s="50"/>
-      <c r="V47" s="50"/>
-      <c r="W47" s="50"/>
-      <c r="X47" s="50"/>
-      <c r="Y47" s="50"/>
-      <c r="Z47" s="50"/>
-      <c r="AA47" s="50"/>
-      <c r="AB47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="52"/>
+      <c r="M47" s="52"/>
+      <c r="N47" s="52"/>
+      <c r="O47" s="52"/>
+      <c r="P47" s="52"/>
+      <c r="Q47" s="52"/>
+      <c r="R47" s="52"/>
+      <c r="S47" s="52"/>
+      <c r="T47" s="52"/>
+      <c r="U47" s="52"/>
+      <c r="V47" s="52"/>
+      <c r="W47" s="52"/>
+      <c r="X47" s="52"/>
+      <c r="Y47" s="52"/>
+      <c r="Z47" s="52"/>
+      <c r="AA47" s="52"/>
+      <c r="AB47" s="53"/>
       <c r="AC47" s="16"/>
     </row>
     <row r="48" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9490,27 +9514,27 @@
       <c r="E48" s="19"/>
       <c r="F48" s="19"/>
       <c r="G48" s="19"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="53"/>
-      <c r="T48" s="53"/>
-      <c r="U48" s="53"/>
-      <c r="V48" s="53"/>
-      <c r="W48" s="53"/>
-      <c r="X48" s="53"/>
-      <c r="Y48" s="53"/>
-      <c r="Z48" s="53"/>
-      <c r="AA48" s="53"/>
-      <c r="AB48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="55"/>
+      <c r="K48" s="55"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
+      <c r="O48" s="55"/>
+      <c r="P48" s="55"/>
+      <c r="Q48" s="55"/>
+      <c r="R48" s="55"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="55"/>
+      <c r="U48" s="55"/>
+      <c r="V48" s="55"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="55"/>
+      <c r="Y48" s="55"/>
+      <c r="Z48" s="55"/>
+      <c r="AA48" s="55"/>
+      <c r="AB48" s="56"/>
       <c r="AC48" s="16"/>
     </row>
     <row r="49" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9579,15 +9603,15 @@
       </c>
     </row>
     <row r="3" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="26">
+      <c r="B3" s="26" t="str">
         <f xml:space="preserve"> '4.2.1'!B3</f>
-        <v>0</v>
+        <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
@@ -10388,15 +10412,15 @@
       </c>
     </row>
     <row r="3" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="26">
+      <c r="B3" s="26" t="str">
         <f xml:space="preserve"> '4.2.1'!B3</f>
-        <v>0</v>
+        <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>33</v>
       </c>
@@ -11530,15 +11554,15 @@
       </c>
     </row>
     <row r="3" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="26">
+      <c r="B3" s="26" t="str">
         <f xml:space="preserve"> '4.2.1'!B3</f>
-        <v>0</v>
+        <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>34</v>
       </c>
@@ -14285,11 +14309,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B66:B83"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="H68:AB74"/>
+    <mergeCell ref="H76:AB82"/>
+    <mergeCell ref="B86:B103"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="H88:AB94"/>
+    <mergeCell ref="H96:AB102"/>
     <mergeCell ref="B26:B43"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="H28:AB34"/>
@@ -14298,14 +14325,11 @@
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="H48:AB54"/>
     <mergeCell ref="H56:AB62"/>
-    <mergeCell ref="B66:B83"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="H68:AB74"/>
-    <mergeCell ref="H76:AB82"/>
-    <mergeCell ref="B86:B103"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="H88:AB94"/>
-    <mergeCell ref="H96:AB102"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -14328,15 +14352,15 @@
       </c>
     </row>
     <row r="3" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="26">
+      <c r="B3" s="26" t="str">
         <f xml:space="preserve"> '4.2.1'!B3</f>
-        <v>0</v>
+        <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="I3" s="23" t="s">
         <v>41</v>
       </c>

--- a/Projekttagebuch.xlsx
+++ b/Projekttagebuch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\projects\GW.Demo.Maui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDA11E4-8C80-4135-B3C9-77B358251254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D5EFE6-298D-4E33-98C7-226B71F29150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{1DD67F99-F2FF-45C7-A69A-922EBC32F5C0}"/>
   </bookViews>
   <sheets>
     <sheet name="4.2.1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="58">
   <si>
     <t>Framework:</t>
   </si>
@@ -214,6 +214,25 @@
   </si>
   <si>
     <t>114</t>
+  </si>
+  <si>
+    <t>Durch den Einsatz von CarouselView, der sich als sinnvoll erwiesen hat, wurde die Swipe-Funktionalität bereits mit den Screeens implementiert. Eine sinnhafte Trennung ist nicht möglich.</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/dotnet/maui/fundamentals/shell/flyout
+https://learn.microsoft.com/en-us/shows/on-dotnet/enhance-dotnet-maui-desktop-apps-with-the-menu-bar
+https://stackoverflow.com/questions/73886700/net-maui-flyout-as-a-regular-sidebar
+https://www.youtube.com/watch?v=b77dEArbk9E
+https://medium.com/@cristian_lopes/net-maui-flyout-navigation-tab-navigation-ca62913c98fa</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Menü-Commands feuern nicht, mühsam,</t>
   </si>
 </sst>
 </file>
@@ -545,12 +564,6 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -577,6 +590,12 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2108,11 +2127,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>11</v>
       </c>
@@ -2742,33 +2761,35 @@
     <row r="27" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="44"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="41"/>
+      <c r="D27" s="41" t="s">
+        <v>54</v>
+      </c>
       <c r="E27" s="42"/>
       <c r="F27" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G27" s="6"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="49"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="49"/>
-      <c r="S27" s="49"/>
-      <c r="T27" s="49"/>
-      <c r="U27" s="49"/>
-      <c r="V27" s="49"/>
-      <c r="W27" s="49"/>
-      <c r="X27" s="49"/>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="49"/>
-      <c r="AA27" s="49"/>
-      <c r="AB27" s="50"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="47"/>
+      <c r="R27" s="47"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="47"/>
+      <c r="AA27" s="47"/>
+      <c r="AB27" s="48"/>
       <c r="AC27" s="11"/>
     </row>
     <row r="28" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2778,27 +2799,27 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="52"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="52"/>
-      <c r="O28" s="52"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="52"/>
-      <c r="R28" s="52"/>
-      <c r="S28" s="52"/>
-      <c r="T28" s="52"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="52"/>
-      <c r="W28" s="52"/>
-      <c r="X28" s="52"/>
-      <c r="Y28" s="52"/>
-      <c r="Z28" s="52"/>
-      <c r="AA28" s="52"/>
-      <c r="AB28" s="53"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="50"/>
+      <c r="V28" s="50"/>
+      <c r="W28" s="50"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
+      <c r="AA28" s="50"/>
+      <c r="AB28" s="51"/>
       <c r="AC28" s="11"/>
     </row>
     <row r="29" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2808,27 +2829,27 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="52"/>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
-      <c r="T29" s="52"/>
-      <c r="U29" s="52"/>
-      <c r="V29" s="52"/>
-      <c r="W29" s="52"/>
-      <c r="X29" s="52"/>
-      <c r="Y29" s="52"/>
-      <c r="Z29" s="52"/>
-      <c r="AA29" s="52"/>
-      <c r="AB29" s="53"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="50"/>
+      <c r="W29" s="50"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="50"/>
+      <c r="AA29" s="50"/>
+      <c r="AB29" s="51"/>
       <c r="AC29" s="11"/>
     </row>
     <row r="30" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2838,27 +2859,27 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="52"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="52"/>
-      <c r="R30" s="52"/>
-      <c r="S30" s="52"/>
-      <c r="T30" s="52"/>
-      <c r="U30" s="52"/>
-      <c r="V30" s="52"/>
-      <c r="W30" s="52"/>
-      <c r="X30" s="52"/>
-      <c r="Y30" s="52"/>
-      <c r="Z30" s="52"/>
-      <c r="AA30" s="52"/>
-      <c r="AB30" s="53"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="50"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="50"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="50"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="50"/>
+      <c r="V30" s="50"/>
+      <c r="W30" s="50"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="50"/>
+      <c r="AA30" s="50"/>
+      <c r="AB30" s="51"/>
       <c r="AC30" s="11"/>
     </row>
     <row r="31" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2868,27 +2889,27 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="52"/>
-      <c r="P31" s="52"/>
-      <c r="Q31" s="52"/>
-      <c r="R31" s="52"/>
-      <c r="S31" s="52"/>
-      <c r="T31" s="52"/>
-      <c r="U31" s="52"/>
-      <c r="V31" s="52"/>
-      <c r="W31" s="52"/>
-      <c r="X31" s="52"/>
-      <c r="Y31" s="52"/>
-      <c r="Z31" s="52"/>
-      <c r="AA31" s="52"/>
-      <c r="AB31" s="53"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="50"/>
+      <c r="V31" s="50"/>
+      <c r="W31" s="50"/>
+      <c r="X31" s="50"/>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="50"/>
+      <c r="AA31" s="50"/>
+      <c r="AB31" s="51"/>
       <c r="AC31" s="11"/>
     </row>
     <row r="32" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2898,27 +2919,27 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="52"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="52"/>
-      <c r="S32" s="52"/>
-      <c r="T32" s="52"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="52"/>
-      <c r="W32" s="52"/>
-      <c r="X32" s="52"/>
-      <c r="Y32" s="52"/>
-      <c r="Z32" s="52"/>
-      <c r="AA32" s="52"/>
-      <c r="AB32" s="53"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="50"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="50"/>
+      <c r="V32" s="50"/>
+      <c r="W32" s="50"/>
+      <c r="X32" s="50"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="50"/>
+      <c r="AA32" s="50"/>
+      <c r="AB32" s="51"/>
       <c r="AC32" s="11"/>
     </row>
     <row r="33" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2928,27 +2949,27 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="55"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="55"/>
-      <c r="T33" s="55"/>
-      <c r="U33" s="55"/>
-      <c r="V33" s="55"/>
-      <c r="W33" s="55"/>
-      <c r="X33" s="55"/>
-      <c r="Y33" s="55"/>
-      <c r="Z33" s="55"/>
-      <c r="AA33" s="55"/>
-      <c r="AB33" s="56"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="53"/>
+      <c r="S33" s="53"/>
+      <c r="T33" s="53"/>
+      <c r="U33" s="53"/>
+      <c r="V33" s="53"/>
+      <c r="W33" s="53"/>
+      <c r="X33" s="53"/>
+      <c r="Y33" s="53"/>
+      <c r="Z33" s="53"/>
+      <c r="AA33" s="53"/>
+      <c r="AB33" s="54"/>
       <c r="AC33" s="11"/>
     </row>
     <row r="34" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2990,27 +3011,29 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="49"/>
-      <c r="P35" s="49"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="49"/>
-      <c r="S35" s="49"/>
-      <c r="T35" s="49"/>
-      <c r="U35" s="49"/>
-      <c r="V35" s="49"/>
-      <c r="W35" s="49"/>
-      <c r="X35" s="49"/>
-      <c r="Y35" s="49"/>
-      <c r="Z35" s="49"/>
-      <c r="AA35" s="49"/>
-      <c r="AB35" s="50"/>
+      <c r="H35" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="33"/>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="34"/>
       <c r="AC35" s="11"/>
     </row>
     <row r="36" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3020,27 +3043,27 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="52"/>
-      <c r="Q36" s="52"/>
-      <c r="R36" s="52"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="52"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="52"/>
-      <c r="W36" s="52"/>
-      <c r="X36" s="52"/>
-      <c r="Y36" s="52"/>
-      <c r="Z36" s="52"/>
-      <c r="AA36" s="52"/>
-      <c r="AB36" s="53"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="36"/>
+      <c r="Z36" s="36"/>
+      <c r="AA36" s="36"/>
+      <c r="AB36" s="37"/>
       <c r="AC36" s="11"/>
     </row>
     <row r="37" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3050,27 +3073,27 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="52"/>
-      <c r="O37" s="52"/>
-      <c r="P37" s="52"/>
-      <c r="Q37" s="52"/>
-      <c r="R37" s="52"/>
-      <c r="S37" s="52"/>
-      <c r="T37" s="52"/>
-      <c r="U37" s="52"/>
-      <c r="V37" s="52"/>
-      <c r="W37" s="52"/>
-      <c r="X37" s="52"/>
-      <c r="Y37" s="52"/>
-      <c r="Z37" s="52"/>
-      <c r="AA37" s="52"/>
-      <c r="AB37" s="53"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="36"/>
+      <c r="R37" s="36"/>
+      <c r="S37" s="36"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="36"/>
+      <c r="V37" s="36"/>
+      <c r="W37" s="36"/>
+      <c r="X37" s="36"/>
+      <c r="Y37" s="36"/>
+      <c r="Z37" s="36"/>
+      <c r="AA37" s="36"/>
+      <c r="AB37" s="37"/>
       <c r="AC37" s="11"/>
     </row>
     <row r="38" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3080,27 +3103,27 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="52"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="52"/>
-      <c r="Q38" s="52"/>
-      <c r="R38" s="52"/>
-      <c r="S38" s="52"/>
-      <c r="T38" s="52"/>
-      <c r="U38" s="52"/>
-      <c r="V38" s="52"/>
-      <c r="W38" s="52"/>
-      <c r="X38" s="52"/>
-      <c r="Y38" s="52"/>
-      <c r="Z38" s="52"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="53"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="36"/>
+      <c r="V38" s="36"/>
+      <c r="W38" s="36"/>
+      <c r="X38" s="36"/>
+      <c r="Y38" s="36"/>
+      <c r="Z38" s="36"/>
+      <c r="AA38" s="36"/>
+      <c r="AB38" s="37"/>
       <c r="AC38" s="11"/>
     </row>
     <row r="39" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3110,27 +3133,27 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="52"/>
-      <c r="K39" s="52"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="52"/>
-      <c r="N39" s="52"/>
-      <c r="O39" s="52"/>
-      <c r="P39" s="52"/>
-      <c r="Q39" s="52"/>
-      <c r="R39" s="52"/>
-      <c r="S39" s="52"/>
-      <c r="T39" s="52"/>
-      <c r="U39" s="52"/>
-      <c r="V39" s="52"/>
-      <c r="W39" s="52"/>
-      <c r="X39" s="52"/>
-      <c r="Y39" s="52"/>
-      <c r="Z39" s="52"/>
-      <c r="AA39" s="52"/>
-      <c r="AB39" s="53"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="36"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36"/>
+      <c r="Q39" s="36"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="36"/>
+      <c r="W39" s="36"/>
+      <c r="X39" s="36"/>
+      <c r="Y39" s="36"/>
+      <c r="Z39" s="36"/>
+      <c r="AA39" s="36"/>
+      <c r="AB39" s="37"/>
       <c r="AC39" s="11"/>
     </row>
     <row r="40" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3140,27 +3163,27 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="52"/>
-      <c r="O40" s="52"/>
-      <c r="P40" s="52"/>
-      <c r="Q40" s="52"/>
-      <c r="R40" s="52"/>
-      <c r="S40" s="52"/>
-      <c r="T40" s="52"/>
-      <c r="U40" s="52"/>
-      <c r="V40" s="52"/>
-      <c r="W40" s="52"/>
-      <c r="X40" s="52"/>
-      <c r="Y40" s="52"/>
-      <c r="Z40" s="52"/>
-      <c r="AA40" s="52"/>
-      <c r="AB40" s="53"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+      <c r="U40" s="36"/>
+      <c r="V40" s="36"/>
+      <c r="W40" s="36"/>
+      <c r="X40" s="36"/>
+      <c r="Y40" s="36"/>
+      <c r="Z40" s="36"/>
+      <c r="AA40" s="36"/>
+      <c r="AB40" s="37"/>
       <c r="AC40" s="11"/>
     </row>
     <row r="41" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3170,27 +3193,27 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="55"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="55"/>
-      <c r="T41" s="55"/>
-      <c r="U41" s="55"/>
-      <c r="V41" s="55"/>
-      <c r="W41" s="55"/>
-      <c r="X41" s="55"/>
-      <c r="Y41" s="55"/>
-      <c r="Z41" s="55"/>
-      <c r="AA41" s="55"/>
-      <c r="AB41" s="56"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
+      <c r="R41" s="39"/>
+      <c r="S41" s="39"/>
+      <c r="T41" s="39"/>
+      <c r="U41" s="39"/>
+      <c r="V41" s="39"/>
+      <c r="W41" s="39"/>
+      <c r="X41" s="39"/>
+      <c r="Y41" s="39"/>
+      <c r="Z41" s="39"/>
+      <c r="AA41" s="39"/>
+      <c r="AB41" s="40"/>
       <c r="AC41" s="11"/>
     </row>
     <row r="42" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3292,33 +3315,37 @@
     <row r="46" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="44"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="41"/>
+      <c r="D46" s="41" t="s">
+        <v>56</v>
+      </c>
       <c r="E46" s="42"/>
       <c r="F46" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G46" s="6"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="49"/>
-      <c r="K46" s="49"/>
-      <c r="L46" s="49"/>
-      <c r="M46" s="49"/>
-      <c r="N46" s="49"/>
-      <c r="O46" s="49"/>
-      <c r="P46" s="49"/>
-      <c r="Q46" s="49"/>
-      <c r="R46" s="49"/>
-      <c r="S46" s="49"/>
-      <c r="T46" s="49"/>
-      <c r="U46" s="49"/>
-      <c r="V46" s="49"/>
-      <c r="W46" s="49"/>
-      <c r="X46" s="49"/>
-      <c r="Y46" s="49"/>
-      <c r="Z46" s="49"/>
-      <c r="AA46" s="49"/>
-      <c r="AB46" s="50"/>
+      <c r="H46" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="33"/>
+      <c r="AA46" s="33"/>
+      <c r="AB46" s="34"/>
       <c r="AC46" s="11"/>
     </row>
     <row r="47" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3328,27 +3355,27 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="52"/>
-      <c r="M47" s="52"/>
-      <c r="N47" s="52"/>
-      <c r="O47" s="52"/>
-      <c r="P47" s="52"/>
-      <c r="Q47" s="52"/>
-      <c r="R47" s="52"/>
-      <c r="S47" s="52"/>
-      <c r="T47" s="52"/>
-      <c r="U47" s="52"/>
-      <c r="V47" s="52"/>
-      <c r="W47" s="52"/>
-      <c r="X47" s="52"/>
-      <c r="Y47" s="52"/>
-      <c r="Z47" s="52"/>
-      <c r="AA47" s="52"/>
-      <c r="AB47" s="53"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="36"/>
+      <c r="P47" s="36"/>
+      <c r="Q47" s="36"/>
+      <c r="R47" s="36"/>
+      <c r="S47" s="36"/>
+      <c r="T47" s="36"/>
+      <c r="U47" s="36"/>
+      <c r="V47" s="36"/>
+      <c r="W47" s="36"/>
+      <c r="X47" s="36"/>
+      <c r="Y47" s="36"/>
+      <c r="Z47" s="36"/>
+      <c r="AA47" s="36"/>
+      <c r="AB47" s="37"/>
       <c r="AC47" s="11"/>
     </row>
     <row r="48" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3358,27 +3385,27 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="52"/>
-      <c r="L48" s="52"/>
-      <c r="M48" s="52"/>
-      <c r="N48" s="52"/>
-      <c r="O48" s="52"/>
-      <c r="P48" s="52"/>
-      <c r="Q48" s="52"/>
-      <c r="R48" s="52"/>
-      <c r="S48" s="52"/>
-      <c r="T48" s="52"/>
-      <c r="U48" s="52"/>
-      <c r="V48" s="52"/>
-      <c r="W48" s="52"/>
-      <c r="X48" s="52"/>
-      <c r="Y48" s="52"/>
-      <c r="Z48" s="52"/>
-      <c r="AA48" s="52"/>
-      <c r="AB48" s="53"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="36"/>
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="36"/>
+      <c r="P48" s="36"/>
+      <c r="Q48" s="36"/>
+      <c r="R48" s="36"/>
+      <c r="S48" s="36"/>
+      <c r="T48" s="36"/>
+      <c r="U48" s="36"/>
+      <c r="V48" s="36"/>
+      <c r="W48" s="36"/>
+      <c r="X48" s="36"/>
+      <c r="Y48" s="36"/>
+      <c r="Z48" s="36"/>
+      <c r="AA48" s="36"/>
+      <c r="AB48" s="37"/>
       <c r="AC48" s="11"/>
     </row>
     <row r="49" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3388,27 +3415,27 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="52"/>
-      <c r="K49" s="52"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="52"/>
-      <c r="N49" s="52"/>
-      <c r="O49" s="52"/>
-      <c r="P49" s="52"/>
-      <c r="Q49" s="52"/>
-      <c r="R49" s="52"/>
-      <c r="S49" s="52"/>
-      <c r="T49" s="52"/>
-      <c r="U49" s="52"/>
-      <c r="V49" s="52"/>
-      <c r="W49" s="52"/>
-      <c r="X49" s="52"/>
-      <c r="Y49" s="52"/>
-      <c r="Z49" s="52"/>
-      <c r="AA49" s="52"/>
-      <c r="AB49" s="53"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="36"/>
+      <c r="M49" s="36"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="36"/>
+      <c r="P49" s="36"/>
+      <c r="Q49" s="36"/>
+      <c r="R49" s="36"/>
+      <c r="S49" s="36"/>
+      <c r="T49" s="36"/>
+      <c r="U49" s="36"/>
+      <c r="V49" s="36"/>
+      <c r="W49" s="36"/>
+      <c r="X49" s="36"/>
+      <c r="Y49" s="36"/>
+      <c r="Z49" s="36"/>
+      <c r="AA49" s="36"/>
+      <c r="AB49" s="37"/>
       <c r="AC49" s="11"/>
     </row>
     <row r="50" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3418,27 +3445,27 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="52"/>
-      <c r="J50" s="52"/>
-      <c r="K50" s="52"/>
-      <c r="L50" s="52"/>
-      <c r="M50" s="52"/>
-      <c r="N50" s="52"/>
-      <c r="O50" s="52"/>
-      <c r="P50" s="52"/>
-      <c r="Q50" s="52"/>
-      <c r="R50" s="52"/>
-      <c r="S50" s="52"/>
-      <c r="T50" s="52"/>
-      <c r="U50" s="52"/>
-      <c r="V50" s="52"/>
-      <c r="W50" s="52"/>
-      <c r="X50" s="52"/>
-      <c r="Y50" s="52"/>
-      <c r="Z50" s="52"/>
-      <c r="AA50" s="52"/>
-      <c r="AB50" s="53"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="36"/>
+      <c r="O50" s="36"/>
+      <c r="P50" s="36"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="36"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36"/>
+      <c r="U50" s="36"/>
+      <c r="V50" s="36"/>
+      <c r="W50" s="36"/>
+      <c r="X50" s="36"/>
+      <c r="Y50" s="36"/>
+      <c r="Z50" s="36"/>
+      <c r="AA50" s="36"/>
+      <c r="AB50" s="37"/>
       <c r="AC50" s="11"/>
     </row>
     <row r="51" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3448,27 +3475,27 @@
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
-      <c r="L51" s="52"/>
-      <c r="M51" s="52"/>
-      <c r="N51" s="52"/>
-      <c r="O51" s="52"/>
-      <c r="P51" s="52"/>
-      <c r="Q51" s="52"/>
-      <c r="R51" s="52"/>
-      <c r="S51" s="52"/>
-      <c r="T51" s="52"/>
-      <c r="U51" s="52"/>
-      <c r="V51" s="52"/>
-      <c r="W51" s="52"/>
-      <c r="X51" s="52"/>
-      <c r="Y51" s="52"/>
-      <c r="Z51" s="52"/>
-      <c r="AA51" s="52"/>
-      <c r="AB51" s="53"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="36"/>
+      <c r="J51" s="36"/>
+      <c r="K51" s="36"/>
+      <c r="L51" s="36"/>
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="36"/>
+      <c r="P51" s="36"/>
+      <c r="Q51" s="36"/>
+      <c r="R51" s="36"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36"/>
+      <c r="U51" s="36"/>
+      <c r="V51" s="36"/>
+      <c r="W51" s="36"/>
+      <c r="X51" s="36"/>
+      <c r="Y51" s="36"/>
+      <c r="Z51" s="36"/>
+      <c r="AA51" s="36"/>
+      <c r="AB51" s="37"/>
       <c r="AC51" s="11"/>
     </row>
     <row r="52" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3478,27 +3505,27 @@
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="54"/>
-      <c r="I52" s="55"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="55"/>
-      <c r="L52" s="55"/>
-      <c r="M52" s="55"/>
-      <c r="N52" s="55"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="55"/>
-      <c r="Q52" s="55"/>
-      <c r="R52" s="55"/>
-      <c r="S52" s="55"/>
-      <c r="T52" s="55"/>
-      <c r="U52" s="55"/>
-      <c r="V52" s="55"/>
-      <c r="W52" s="55"/>
-      <c r="X52" s="55"/>
-      <c r="Y52" s="55"/>
-      <c r="Z52" s="55"/>
-      <c r="AA52" s="55"/>
-      <c r="AB52" s="56"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="39"/>
+      <c r="M52" s="39"/>
+      <c r="N52" s="39"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="39"/>
+      <c r="S52" s="39"/>
+      <c r="T52" s="39"/>
+      <c r="U52" s="39"/>
+      <c r="V52" s="39"/>
+      <c r="W52" s="39"/>
+      <c r="X52" s="39"/>
+      <c r="Y52" s="39"/>
+      <c r="Z52" s="39"/>
+      <c r="AA52" s="39"/>
+      <c r="AB52" s="40"/>
       <c r="AC52" s="11"/>
     </row>
     <row r="53" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3540,27 +3567,29 @@
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="49"/>
-      <c r="J54" s="49"/>
-      <c r="K54" s="49"/>
-      <c r="L54" s="49"/>
-      <c r="M54" s="49"/>
-      <c r="N54" s="49"/>
-      <c r="O54" s="49"/>
-      <c r="P54" s="49"/>
-      <c r="Q54" s="49"/>
-      <c r="R54" s="49"/>
-      <c r="S54" s="49"/>
-      <c r="T54" s="49"/>
-      <c r="U54" s="49"/>
-      <c r="V54" s="49"/>
-      <c r="W54" s="49"/>
-      <c r="X54" s="49"/>
-      <c r="Y54" s="49"/>
-      <c r="Z54" s="49"/>
-      <c r="AA54" s="49"/>
-      <c r="AB54" s="50"/>
+      <c r="H54" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="33"/>
+      <c r="M54" s="33"/>
+      <c r="N54" s="33"/>
+      <c r="O54" s="33"/>
+      <c r="P54" s="33"/>
+      <c r="Q54" s="33"/>
+      <c r="R54" s="33"/>
+      <c r="S54" s="33"/>
+      <c r="T54" s="33"/>
+      <c r="U54" s="33"/>
+      <c r="V54" s="33"/>
+      <c r="W54" s="33"/>
+      <c r="X54" s="33"/>
+      <c r="Y54" s="33"/>
+      <c r="Z54" s="33"/>
+      <c r="AA54" s="33"/>
+      <c r="AB54" s="34"/>
       <c r="AC54" s="11"/>
     </row>
     <row r="55" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3570,27 +3599,27 @@
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="52"/>
-      <c r="J55" s="52"/>
-      <c r="K55" s="52"/>
-      <c r="L55" s="52"/>
-      <c r="M55" s="52"/>
-      <c r="N55" s="52"/>
-      <c r="O55" s="52"/>
-      <c r="P55" s="52"/>
-      <c r="Q55" s="52"/>
-      <c r="R55" s="52"/>
-      <c r="S55" s="52"/>
-      <c r="T55" s="52"/>
-      <c r="U55" s="52"/>
-      <c r="V55" s="52"/>
-      <c r="W55" s="52"/>
-      <c r="X55" s="52"/>
-      <c r="Y55" s="52"/>
-      <c r="Z55" s="52"/>
-      <c r="AA55" s="52"/>
-      <c r="AB55" s="53"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
+      <c r="L55" s="36"/>
+      <c r="M55" s="36"/>
+      <c r="N55" s="36"/>
+      <c r="O55" s="36"/>
+      <c r="P55" s="36"/>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="36"/>
+      <c r="S55" s="36"/>
+      <c r="T55" s="36"/>
+      <c r="U55" s="36"/>
+      <c r="V55" s="36"/>
+      <c r="W55" s="36"/>
+      <c r="X55" s="36"/>
+      <c r="Y55" s="36"/>
+      <c r="Z55" s="36"/>
+      <c r="AA55" s="36"/>
+      <c r="AB55" s="37"/>
       <c r="AC55" s="11"/>
     </row>
     <row r="56" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3600,27 +3629,27 @@
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
-      <c r="H56" s="51"/>
-      <c r="I56" s="52"/>
-      <c r="J56" s="52"/>
-      <c r="K56" s="52"/>
-      <c r="L56" s="52"/>
-      <c r="M56" s="52"/>
-      <c r="N56" s="52"/>
-      <c r="O56" s="52"/>
-      <c r="P56" s="52"/>
-      <c r="Q56" s="52"/>
-      <c r="R56" s="52"/>
-      <c r="S56" s="52"/>
-      <c r="T56" s="52"/>
-      <c r="U56" s="52"/>
-      <c r="V56" s="52"/>
-      <c r="W56" s="52"/>
-      <c r="X56" s="52"/>
-      <c r="Y56" s="52"/>
-      <c r="Z56" s="52"/>
-      <c r="AA56" s="52"/>
-      <c r="AB56" s="53"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="36"/>
+      <c r="P56" s="36"/>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="36"/>
+      <c r="S56" s="36"/>
+      <c r="T56" s="36"/>
+      <c r="U56" s="36"/>
+      <c r="V56" s="36"/>
+      <c r="W56" s="36"/>
+      <c r="X56" s="36"/>
+      <c r="Y56" s="36"/>
+      <c r="Z56" s="36"/>
+      <c r="AA56" s="36"/>
+      <c r="AB56" s="37"/>
       <c r="AC56" s="11"/>
     </row>
     <row r="57" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3630,27 +3659,27 @@
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="52"/>
-      <c r="J57" s="52"/>
-      <c r="K57" s="52"/>
-      <c r="L57" s="52"/>
-      <c r="M57" s="52"/>
-      <c r="N57" s="52"/>
-      <c r="O57" s="52"/>
-      <c r="P57" s="52"/>
-      <c r="Q57" s="52"/>
-      <c r="R57" s="52"/>
-      <c r="S57" s="52"/>
-      <c r="T57" s="52"/>
-      <c r="U57" s="52"/>
-      <c r="V57" s="52"/>
-      <c r="W57" s="52"/>
-      <c r="X57" s="52"/>
-      <c r="Y57" s="52"/>
-      <c r="Z57" s="52"/>
-      <c r="AA57" s="52"/>
-      <c r="AB57" s="53"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="36"/>
+      <c r="K57" s="36"/>
+      <c r="L57" s="36"/>
+      <c r="M57" s="36"/>
+      <c r="N57" s="36"/>
+      <c r="O57" s="36"/>
+      <c r="P57" s="36"/>
+      <c r="Q57" s="36"/>
+      <c r="R57" s="36"/>
+      <c r="S57" s="36"/>
+      <c r="T57" s="36"/>
+      <c r="U57" s="36"/>
+      <c r="V57" s="36"/>
+      <c r="W57" s="36"/>
+      <c r="X57" s="36"/>
+      <c r="Y57" s="36"/>
+      <c r="Z57" s="36"/>
+      <c r="AA57" s="36"/>
+      <c r="AB57" s="37"/>
       <c r="AC57" s="11"/>
     </row>
     <row r="58" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3660,27 +3689,27 @@
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="L58" s="52"/>
-      <c r="M58" s="52"/>
-      <c r="N58" s="52"/>
-      <c r="O58" s="52"/>
-      <c r="P58" s="52"/>
-      <c r="Q58" s="52"/>
-      <c r="R58" s="52"/>
-      <c r="S58" s="52"/>
-      <c r="T58" s="52"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="52"/>
-      <c r="W58" s="52"/>
-      <c r="X58" s="52"/>
-      <c r="Y58" s="52"/>
-      <c r="Z58" s="52"/>
-      <c r="AA58" s="52"/>
-      <c r="AB58" s="53"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
+      <c r="K58" s="36"/>
+      <c r="L58" s="36"/>
+      <c r="M58" s="36"/>
+      <c r="N58" s="36"/>
+      <c r="O58" s="36"/>
+      <c r="P58" s="36"/>
+      <c r="Q58" s="36"/>
+      <c r="R58" s="36"/>
+      <c r="S58" s="36"/>
+      <c r="T58" s="36"/>
+      <c r="U58" s="36"/>
+      <c r="V58" s="36"/>
+      <c r="W58" s="36"/>
+      <c r="X58" s="36"/>
+      <c r="Y58" s="36"/>
+      <c r="Z58" s="36"/>
+      <c r="AA58" s="36"/>
+      <c r="AB58" s="37"/>
       <c r="AC58" s="11"/>
     </row>
     <row r="59" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3690,27 +3719,27 @@
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="52"/>
-      <c r="K59" s="52"/>
-      <c r="L59" s="52"/>
-      <c r="M59" s="52"/>
-      <c r="N59" s="52"/>
-      <c r="O59" s="52"/>
-      <c r="P59" s="52"/>
-      <c r="Q59" s="52"/>
-      <c r="R59" s="52"/>
-      <c r="S59" s="52"/>
-      <c r="T59" s="52"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="52"/>
-      <c r="W59" s="52"/>
-      <c r="X59" s="52"/>
-      <c r="Y59" s="52"/>
-      <c r="Z59" s="52"/>
-      <c r="AA59" s="52"/>
-      <c r="AB59" s="53"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36"/>
+      <c r="O59" s="36"/>
+      <c r="P59" s="36"/>
+      <c r="Q59" s="36"/>
+      <c r="R59" s="36"/>
+      <c r="S59" s="36"/>
+      <c r="T59" s="36"/>
+      <c r="U59" s="36"/>
+      <c r="V59" s="36"/>
+      <c r="W59" s="36"/>
+      <c r="X59" s="36"/>
+      <c r="Y59" s="36"/>
+      <c r="Z59" s="36"/>
+      <c r="AA59" s="36"/>
+      <c r="AB59" s="37"/>
       <c r="AC59" s="11"/>
     </row>
     <row r="60" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3720,27 +3749,27 @@
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="54"/>
-      <c r="I60" s="55"/>
-      <c r="J60" s="55"/>
-      <c r="K60" s="55"/>
-      <c r="L60" s="55"/>
-      <c r="M60" s="55"/>
-      <c r="N60" s="55"/>
-      <c r="O60" s="55"/>
-      <c r="P60" s="55"/>
-      <c r="Q60" s="55"/>
-      <c r="R60" s="55"/>
-      <c r="S60" s="55"/>
-      <c r="T60" s="55"/>
-      <c r="U60" s="55"/>
-      <c r="V60" s="55"/>
-      <c r="W60" s="55"/>
-      <c r="X60" s="55"/>
-      <c r="Y60" s="55"/>
-      <c r="Z60" s="55"/>
-      <c r="AA60" s="55"/>
-      <c r="AB60" s="56"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+      <c r="L60" s="39"/>
+      <c r="M60" s="39"/>
+      <c r="N60" s="39"/>
+      <c r="O60" s="39"/>
+      <c r="P60" s="39"/>
+      <c r="Q60" s="39"/>
+      <c r="R60" s="39"/>
+      <c r="S60" s="39"/>
+      <c r="T60" s="39"/>
+      <c r="U60" s="39"/>
+      <c r="V60" s="39"/>
+      <c r="W60" s="39"/>
+      <c r="X60" s="39"/>
+      <c r="Y60" s="39"/>
+      <c r="Z60" s="39"/>
+      <c r="AA60" s="39"/>
+      <c r="AB60" s="40"/>
       <c r="AC60" s="11"/>
     </row>
     <row r="61" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3848,27 +3877,27 @@
         <v>2</v>
       </c>
       <c r="G65" s="6"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="49"/>
-      <c r="J65" s="49"/>
-      <c r="K65" s="49"/>
-      <c r="L65" s="49"/>
-      <c r="M65" s="49"/>
-      <c r="N65" s="49"/>
-      <c r="O65" s="49"/>
-      <c r="P65" s="49"/>
-      <c r="Q65" s="49"/>
-      <c r="R65" s="49"/>
-      <c r="S65" s="49"/>
-      <c r="T65" s="49"/>
-      <c r="U65" s="49"/>
-      <c r="V65" s="49"/>
-      <c r="W65" s="49"/>
-      <c r="X65" s="49"/>
-      <c r="Y65" s="49"/>
-      <c r="Z65" s="49"/>
-      <c r="AA65" s="49"/>
-      <c r="AB65" s="50"/>
+      <c r="H65" s="46"/>
+      <c r="I65" s="47"/>
+      <c r="J65" s="47"/>
+      <c r="K65" s="47"/>
+      <c r="L65" s="47"/>
+      <c r="M65" s="47"/>
+      <c r="N65" s="47"/>
+      <c r="O65" s="47"/>
+      <c r="P65" s="47"/>
+      <c r="Q65" s="47"/>
+      <c r="R65" s="47"/>
+      <c r="S65" s="47"/>
+      <c r="T65" s="47"/>
+      <c r="U65" s="47"/>
+      <c r="V65" s="47"/>
+      <c r="W65" s="47"/>
+      <c r="X65" s="47"/>
+      <c r="Y65" s="47"/>
+      <c r="Z65" s="47"/>
+      <c r="AA65" s="47"/>
+      <c r="AB65" s="48"/>
       <c r="AC65" s="11"/>
     </row>
     <row r="66" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3878,27 +3907,27 @@
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
-      <c r="H66" s="51"/>
-      <c r="I66" s="52"/>
-      <c r="J66" s="52"/>
-      <c r="K66" s="52"/>
-      <c r="L66" s="52"/>
-      <c r="M66" s="52"/>
-      <c r="N66" s="52"/>
-      <c r="O66" s="52"/>
-      <c r="P66" s="52"/>
-      <c r="Q66" s="52"/>
-      <c r="R66" s="52"/>
-      <c r="S66" s="52"/>
-      <c r="T66" s="52"/>
-      <c r="U66" s="52"/>
-      <c r="V66" s="52"/>
-      <c r="W66" s="52"/>
-      <c r="X66" s="52"/>
-      <c r="Y66" s="52"/>
-      <c r="Z66" s="52"/>
-      <c r="AA66" s="52"/>
-      <c r="AB66" s="53"/>
+      <c r="H66" s="49"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="50"/>
+      <c r="M66" s="50"/>
+      <c r="N66" s="50"/>
+      <c r="O66" s="50"/>
+      <c r="P66" s="50"/>
+      <c r="Q66" s="50"/>
+      <c r="R66" s="50"/>
+      <c r="S66" s="50"/>
+      <c r="T66" s="50"/>
+      <c r="U66" s="50"/>
+      <c r="V66" s="50"/>
+      <c r="W66" s="50"/>
+      <c r="X66" s="50"/>
+      <c r="Y66" s="50"/>
+      <c r="Z66" s="50"/>
+      <c r="AA66" s="50"/>
+      <c r="AB66" s="51"/>
       <c r="AC66" s="11"/>
     </row>
     <row r="67" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3908,27 +3937,27 @@
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
-      <c r="H67" s="51"/>
-      <c r="I67" s="52"/>
-      <c r="J67" s="52"/>
-      <c r="K67" s="52"/>
-      <c r="L67" s="52"/>
-      <c r="M67" s="52"/>
-      <c r="N67" s="52"/>
-      <c r="O67" s="52"/>
-      <c r="P67" s="52"/>
-      <c r="Q67" s="52"/>
-      <c r="R67" s="52"/>
-      <c r="S67" s="52"/>
-      <c r="T67" s="52"/>
-      <c r="U67" s="52"/>
-      <c r="V67" s="52"/>
-      <c r="W67" s="52"/>
-      <c r="X67" s="52"/>
-      <c r="Y67" s="52"/>
-      <c r="Z67" s="52"/>
-      <c r="AA67" s="52"/>
-      <c r="AB67" s="53"/>
+      <c r="H67" s="49"/>
+      <c r="I67" s="50"/>
+      <c r="J67" s="50"/>
+      <c r="K67" s="50"/>
+      <c r="L67" s="50"/>
+      <c r="M67" s="50"/>
+      <c r="N67" s="50"/>
+      <c r="O67" s="50"/>
+      <c r="P67" s="50"/>
+      <c r="Q67" s="50"/>
+      <c r="R67" s="50"/>
+      <c r="S67" s="50"/>
+      <c r="T67" s="50"/>
+      <c r="U67" s="50"/>
+      <c r="V67" s="50"/>
+      <c r="W67" s="50"/>
+      <c r="X67" s="50"/>
+      <c r="Y67" s="50"/>
+      <c r="Z67" s="50"/>
+      <c r="AA67" s="50"/>
+      <c r="AB67" s="51"/>
       <c r="AC67" s="11"/>
     </row>
     <row r="68" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3938,27 +3967,27 @@
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
-      <c r="H68" s="51"/>
-      <c r="I68" s="52"/>
-      <c r="J68" s="52"/>
-      <c r="K68" s="52"/>
-      <c r="L68" s="52"/>
-      <c r="M68" s="52"/>
-      <c r="N68" s="52"/>
-      <c r="O68" s="52"/>
-      <c r="P68" s="52"/>
-      <c r="Q68" s="52"/>
-      <c r="R68" s="52"/>
-      <c r="S68" s="52"/>
-      <c r="T68" s="52"/>
-      <c r="U68" s="52"/>
-      <c r="V68" s="52"/>
-      <c r="W68" s="52"/>
-      <c r="X68" s="52"/>
-      <c r="Y68" s="52"/>
-      <c r="Z68" s="52"/>
-      <c r="AA68" s="52"/>
-      <c r="AB68" s="53"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="50"/>
+      <c r="J68" s="50"/>
+      <c r="K68" s="50"/>
+      <c r="L68" s="50"/>
+      <c r="M68" s="50"/>
+      <c r="N68" s="50"/>
+      <c r="O68" s="50"/>
+      <c r="P68" s="50"/>
+      <c r="Q68" s="50"/>
+      <c r="R68" s="50"/>
+      <c r="S68" s="50"/>
+      <c r="T68" s="50"/>
+      <c r="U68" s="50"/>
+      <c r="V68" s="50"/>
+      <c r="W68" s="50"/>
+      <c r="X68" s="50"/>
+      <c r="Y68" s="50"/>
+      <c r="Z68" s="50"/>
+      <c r="AA68" s="50"/>
+      <c r="AB68" s="51"/>
       <c r="AC68" s="11"/>
     </row>
     <row r="69" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3968,27 +3997,27 @@
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
-      <c r="H69" s="51"/>
-      <c r="I69" s="52"/>
-      <c r="J69" s="52"/>
-      <c r="K69" s="52"/>
-      <c r="L69" s="52"/>
-      <c r="M69" s="52"/>
-      <c r="N69" s="52"/>
-      <c r="O69" s="52"/>
-      <c r="P69" s="52"/>
-      <c r="Q69" s="52"/>
-      <c r="R69" s="52"/>
-      <c r="S69" s="52"/>
-      <c r="T69" s="52"/>
-      <c r="U69" s="52"/>
-      <c r="V69" s="52"/>
-      <c r="W69" s="52"/>
-      <c r="X69" s="52"/>
-      <c r="Y69" s="52"/>
-      <c r="Z69" s="52"/>
-      <c r="AA69" s="52"/>
-      <c r="AB69" s="53"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="50"/>
+      <c r="J69" s="50"/>
+      <c r="K69" s="50"/>
+      <c r="L69" s="50"/>
+      <c r="M69" s="50"/>
+      <c r="N69" s="50"/>
+      <c r="O69" s="50"/>
+      <c r="P69" s="50"/>
+      <c r="Q69" s="50"/>
+      <c r="R69" s="50"/>
+      <c r="S69" s="50"/>
+      <c r="T69" s="50"/>
+      <c r="U69" s="50"/>
+      <c r="V69" s="50"/>
+      <c r="W69" s="50"/>
+      <c r="X69" s="50"/>
+      <c r="Y69" s="50"/>
+      <c r="Z69" s="50"/>
+      <c r="AA69" s="50"/>
+      <c r="AB69" s="51"/>
       <c r="AC69" s="11"/>
     </row>
     <row r="70" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3998,27 +4027,27 @@
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="52"/>
-      <c r="J70" s="52"/>
-      <c r="K70" s="52"/>
-      <c r="L70" s="52"/>
-      <c r="M70" s="52"/>
-      <c r="N70" s="52"/>
-      <c r="O70" s="52"/>
-      <c r="P70" s="52"/>
-      <c r="Q70" s="52"/>
-      <c r="R70" s="52"/>
-      <c r="S70" s="52"/>
-      <c r="T70" s="52"/>
-      <c r="U70" s="52"/>
-      <c r="V70" s="52"/>
-      <c r="W70" s="52"/>
-      <c r="X70" s="52"/>
-      <c r="Y70" s="52"/>
-      <c r="Z70" s="52"/>
-      <c r="AA70" s="52"/>
-      <c r="AB70" s="53"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="50"/>
+      <c r="J70" s="50"/>
+      <c r="K70" s="50"/>
+      <c r="L70" s="50"/>
+      <c r="M70" s="50"/>
+      <c r="N70" s="50"/>
+      <c r="O70" s="50"/>
+      <c r="P70" s="50"/>
+      <c r="Q70" s="50"/>
+      <c r="R70" s="50"/>
+      <c r="S70" s="50"/>
+      <c r="T70" s="50"/>
+      <c r="U70" s="50"/>
+      <c r="V70" s="50"/>
+      <c r="W70" s="50"/>
+      <c r="X70" s="50"/>
+      <c r="Y70" s="50"/>
+      <c r="Z70" s="50"/>
+      <c r="AA70" s="50"/>
+      <c r="AB70" s="51"/>
       <c r="AC70" s="11"/>
     </row>
     <row r="71" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4028,27 +4057,27 @@
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
-      <c r="H71" s="54"/>
-      <c r="I71" s="55"/>
-      <c r="J71" s="55"/>
-      <c r="K71" s="55"/>
-      <c r="L71" s="55"/>
-      <c r="M71" s="55"/>
-      <c r="N71" s="55"/>
-      <c r="O71" s="55"/>
-      <c r="P71" s="55"/>
-      <c r="Q71" s="55"/>
-      <c r="R71" s="55"/>
-      <c r="S71" s="55"/>
-      <c r="T71" s="55"/>
-      <c r="U71" s="55"/>
-      <c r="V71" s="55"/>
-      <c r="W71" s="55"/>
-      <c r="X71" s="55"/>
-      <c r="Y71" s="55"/>
-      <c r="Z71" s="55"/>
-      <c r="AA71" s="55"/>
-      <c r="AB71" s="56"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="53"/>
+      <c r="J71" s="53"/>
+      <c r="K71" s="53"/>
+      <c r="L71" s="53"/>
+      <c r="M71" s="53"/>
+      <c r="N71" s="53"/>
+      <c r="O71" s="53"/>
+      <c r="P71" s="53"/>
+      <c r="Q71" s="53"/>
+      <c r="R71" s="53"/>
+      <c r="S71" s="53"/>
+      <c r="T71" s="53"/>
+      <c r="U71" s="53"/>
+      <c r="V71" s="53"/>
+      <c r="W71" s="53"/>
+      <c r="X71" s="53"/>
+      <c r="Y71" s="53"/>
+      <c r="Z71" s="53"/>
+      <c r="AA71" s="53"/>
+      <c r="AB71" s="54"/>
       <c r="AC71" s="11"/>
     </row>
     <row r="72" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4090,27 +4119,27 @@
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
-      <c r="H73" s="48"/>
-      <c r="I73" s="49"/>
-      <c r="J73" s="49"/>
-      <c r="K73" s="49"/>
-      <c r="L73" s="49"/>
-      <c r="M73" s="49"/>
-      <c r="N73" s="49"/>
-      <c r="O73" s="49"/>
-      <c r="P73" s="49"/>
-      <c r="Q73" s="49"/>
-      <c r="R73" s="49"/>
-      <c r="S73" s="49"/>
-      <c r="T73" s="49"/>
-      <c r="U73" s="49"/>
-      <c r="V73" s="49"/>
-      <c r="W73" s="49"/>
-      <c r="X73" s="49"/>
-      <c r="Y73" s="49"/>
-      <c r="Z73" s="49"/>
-      <c r="AA73" s="49"/>
-      <c r="AB73" s="50"/>
+      <c r="H73" s="46"/>
+      <c r="I73" s="47"/>
+      <c r="J73" s="47"/>
+      <c r="K73" s="47"/>
+      <c r="L73" s="47"/>
+      <c r="M73" s="47"/>
+      <c r="N73" s="47"/>
+      <c r="O73" s="47"/>
+      <c r="P73" s="47"/>
+      <c r="Q73" s="47"/>
+      <c r="R73" s="47"/>
+      <c r="S73" s="47"/>
+      <c r="T73" s="47"/>
+      <c r="U73" s="47"/>
+      <c r="V73" s="47"/>
+      <c r="W73" s="47"/>
+      <c r="X73" s="47"/>
+      <c r="Y73" s="47"/>
+      <c r="Z73" s="47"/>
+      <c r="AA73" s="47"/>
+      <c r="AB73" s="48"/>
       <c r="AC73" s="11"/>
     </row>
     <row r="74" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4120,27 +4149,27 @@
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
-      <c r="H74" s="51"/>
-      <c r="I74" s="52"/>
-      <c r="J74" s="52"/>
-      <c r="K74" s="52"/>
-      <c r="L74" s="52"/>
-      <c r="M74" s="52"/>
-      <c r="N74" s="52"/>
-      <c r="O74" s="52"/>
-      <c r="P74" s="52"/>
-      <c r="Q74" s="52"/>
-      <c r="R74" s="52"/>
-      <c r="S74" s="52"/>
-      <c r="T74" s="52"/>
-      <c r="U74" s="52"/>
-      <c r="V74" s="52"/>
-      <c r="W74" s="52"/>
-      <c r="X74" s="52"/>
-      <c r="Y74" s="52"/>
-      <c r="Z74" s="52"/>
-      <c r="AA74" s="52"/>
-      <c r="AB74" s="53"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="50"/>
+      <c r="J74" s="50"/>
+      <c r="K74" s="50"/>
+      <c r="L74" s="50"/>
+      <c r="M74" s="50"/>
+      <c r="N74" s="50"/>
+      <c r="O74" s="50"/>
+      <c r="P74" s="50"/>
+      <c r="Q74" s="50"/>
+      <c r="R74" s="50"/>
+      <c r="S74" s="50"/>
+      <c r="T74" s="50"/>
+      <c r="U74" s="50"/>
+      <c r="V74" s="50"/>
+      <c r="W74" s="50"/>
+      <c r="X74" s="50"/>
+      <c r="Y74" s="50"/>
+      <c r="Z74" s="50"/>
+      <c r="AA74" s="50"/>
+      <c r="AB74" s="51"/>
       <c r="AC74" s="11"/>
     </row>
     <row r="75" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4150,27 +4179,27 @@
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="52"/>
-      <c r="J75" s="52"/>
-      <c r="K75" s="52"/>
-      <c r="L75" s="52"/>
-      <c r="M75" s="52"/>
-      <c r="N75" s="52"/>
-      <c r="O75" s="52"/>
-      <c r="P75" s="52"/>
-      <c r="Q75" s="52"/>
-      <c r="R75" s="52"/>
-      <c r="S75" s="52"/>
-      <c r="T75" s="52"/>
-      <c r="U75" s="52"/>
-      <c r="V75" s="52"/>
-      <c r="W75" s="52"/>
-      <c r="X75" s="52"/>
-      <c r="Y75" s="52"/>
-      <c r="Z75" s="52"/>
-      <c r="AA75" s="52"/>
-      <c r="AB75" s="53"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="50"/>
+      <c r="J75" s="50"/>
+      <c r="K75" s="50"/>
+      <c r="L75" s="50"/>
+      <c r="M75" s="50"/>
+      <c r="N75" s="50"/>
+      <c r="O75" s="50"/>
+      <c r="P75" s="50"/>
+      <c r="Q75" s="50"/>
+      <c r="R75" s="50"/>
+      <c r="S75" s="50"/>
+      <c r="T75" s="50"/>
+      <c r="U75" s="50"/>
+      <c r="V75" s="50"/>
+      <c r="W75" s="50"/>
+      <c r="X75" s="50"/>
+      <c r="Y75" s="50"/>
+      <c r="Z75" s="50"/>
+      <c r="AA75" s="50"/>
+      <c r="AB75" s="51"/>
       <c r="AC75" s="11"/>
     </row>
     <row r="76" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4180,27 +4209,27 @@
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="52"/>
-      <c r="J76" s="52"/>
-      <c r="K76" s="52"/>
-      <c r="L76" s="52"/>
-      <c r="M76" s="52"/>
-      <c r="N76" s="52"/>
-      <c r="O76" s="52"/>
-      <c r="P76" s="52"/>
-      <c r="Q76" s="52"/>
-      <c r="R76" s="52"/>
-      <c r="S76" s="52"/>
-      <c r="T76" s="52"/>
-      <c r="U76" s="52"/>
-      <c r="V76" s="52"/>
-      <c r="W76" s="52"/>
-      <c r="X76" s="52"/>
-      <c r="Y76" s="52"/>
-      <c r="Z76" s="52"/>
-      <c r="AA76" s="52"/>
-      <c r="AB76" s="53"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="50"/>
+      <c r="J76" s="50"/>
+      <c r="K76" s="50"/>
+      <c r="L76" s="50"/>
+      <c r="M76" s="50"/>
+      <c r="N76" s="50"/>
+      <c r="O76" s="50"/>
+      <c r="P76" s="50"/>
+      <c r="Q76" s="50"/>
+      <c r="R76" s="50"/>
+      <c r="S76" s="50"/>
+      <c r="T76" s="50"/>
+      <c r="U76" s="50"/>
+      <c r="V76" s="50"/>
+      <c r="W76" s="50"/>
+      <c r="X76" s="50"/>
+      <c r="Y76" s="50"/>
+      <c r="Z76" s="50"/>
+      <c r="AA76" s="50"/>
+      <c r="AB76" s="51"/>
       <c r="AC76" s="11"/>
     </row>
     <row r="77" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4210,27 +4239,27 @@
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="51"/>
-      <c r="I77" s="52"/>
-      <c r="J77" s="52"/>
-      <c r="K77" s="52"/>
-      <c r="L77" s="52"/>
-      <c r="M77" s="52"/>
-      <c r="N77" s="52"/>
-      <c r="O77" s="52"/>
-      <c r="P77" s="52"/>
-      <c r="Q77" s="52"/>
-      <c r="R77" s="52"/>
-      <c r="S77" s="52"/>
-      <c r="T77" s="52"/>
-      <c r="U77" s="52"/>
-      <c r="V77" s="52"/>
-      <c r="W77" s="52"/>
-      <c r="X77" s="52"/>
-      <c r="Y77" s="52"/>
-      <c r="Z77" s="52"/>
-      <c r="AA77" s="52"/>
-      <c r="AB77" s="53"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="50"/>
+      <c r="J77" s="50"/>
+      <c r="K77" s="50"/>
+      <c r="L77" s="50"/>
+      <c r="M77" s="50"/>
+      <c r="N77" s="50"/>
+      <c r="O77" s="50"/>
+      <c r="P77" s="50"/>
+      <c r="Q77" s="50"/>
+      <c r="R77" s="50"/>
+      <c r="S77" s="50"/>
+      <c r="T77" s="50"/>
+      <c r="U77" s="50"/>
+      <c r="V77" s="50"/>
+      <c r="W77" s="50"/>
+      <c r="X77" s="50"/>
+      <c r="Y77" s="50"/>
+      <c r="Z77" s="50"/>
+      <c r="AA77" s="50"/>
+      <c r="AB77" s="51"/>
       <c r="AC77" s="11"/>
     </row>
     <row r="78" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4240,27 +4269,27 @@
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
-      <c r="H78" s="51"/>
-      <c r="I78" s="52"/>
-      <c r="J78" s="52"/>
-      <c r="K78" s="52"/>
-      <c r="L78" s="52"/>
-      <c r="M78" s="52"/>
-      <c r="N78" s="52"/>
-      <c r="O78" s="52"/>
-      <c r="P78" s="52"/>
-      <c r="Q78" s="52"/>
-      <c r="R78" s="52"/>
-      <c r="S78" s="52"/>
-      <c r="T78" s="52"/>
-      <c r="U78" s="52"/>
-      <c r="V78" s="52"/>
-      <c r="W78" s="52"/>
-      <c r="X78" s="52"/>
-      <c r="Y78" s="52"/>
-      <c r="Z78" s="52"/>
-      <c r="AA78" s="52"/>
-      <c r="AB78" s="53"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="50"/>
+      <c r="J78" s="50"/>
+      <c r="K78" s="50"/>
+      <c r="L78" s="50"/>
+      <c r="M78" s="50"/>
+      <c r="N78" s="50"/>
+      <c r="O78" s="50"/>
+      <c r="P78" s="50"/>
+      <c r="Q78" s="50"/>
+      <c r="R78" s="50"/>
+      <c r="S78" s="50"/>
+      <c r="T78" s="50"/>
+      <c r="U78" s="50"/>
+      <c r="V78" s="50"/>
+      <c r="W78" s="50"/>
+      <c r="X78" s="50"/>
+      <c r="Y78" s="50"/>
+      <c r="Z78" s="50"/>
+      <c r="AA78" s="50"/>
+      <c r="AB78" s="51"/>
       <c r="AC78" s="11"/>
     </row>
     <row r="79" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4270,27 +4299,27 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
-      <c r="H79" s="54"/>
-      <c r="I79" s="55"/>
-      <c r="J79" s="55"/>
-      <c r="K79" s="55"/>
-      <c r="L79" s="55"/>
-      <c r="M79" s="55"/>
-      <c r="N79" s="55"/>
-      <c r="O79" s="55"/>
-      <c r="P79" s="55"/>
-      <c r="Q79" s="55"/>
-      <c r="R79" s="55"/>
-      <c r="S79" s="55"/>
-      <c r="T79" s="55"/>
-      <c r="U79" s="55"/>
-      <c r="V79" s="55"/>
-      <c r="W79" s="55"/>
-      <c r="X79" s="55"/>
-      <c r="Y79" s="55"/>
-      <c r="Z79" s="55"/>
-      <c r="AA79" s="55"/>
-      <c r="AB79" s="56"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="53"/>
+      <c r="J79" s="53"/>
+      <c r="K79" s="53"/>
+      <c r="L79" s="53"/>
+      <c r="M79" s="53"/>
+      <c r="N79" s="53"/>
+      <c r="O79" s="53"/>
+      <c r="P79" s="53"/>
+      <c r="Q79" s="53"/>
+      <c r="R79" s="53"/>
+      <c r="S79" s="53"/>
+      <c r="T79" s="53"/>
+      <c r="U79" s="53"/>
+      <c r="V79" s="53"/>
+      <c r="W79" s="53"/>
+      <c r="X79" s="53"/>
+      <c r="Y79" s="53"/>
+      <c r="Z79" s="53"/>
+      <c r="AA79" s="53"/>
+      <c r="AB79" s="54"/>
       <c r="AC79" s="11"/>
     </row>
     <row r="80" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4398,27 +4427,27 @@
         <v>2</v>
       </c>
       <c r="G84" s="6"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="49"/>
-      <c r="J84" s="49"/>
-      <c r="K84" s="49"/>
-      <c r="L84" s="49"/>
-      <c r="M84" s="49"/>
-      <c r="N84" s="49"/>
-      <c r="O84" s="49"/>
-      <c r="P84" s="49"/>
-      <c r="Q84" s="49"/>
-      <c r="R84" s="49"/>
-      <c r="S84" s="49"/>
-      <c r="T84" s="49"/>
-      <c r="U84" s="49"/>
-      <c r="V84" s="49"/>
-      <c r="W84" s="49"/>
-      <c r="X84" s="49"/>
-      <c r="Y84" s="49"/>
-      <c r="Z84" s="49"/>
-      <c r="AA84" s="49"/>
-      <c r="AB84" s="50"/>
+      <c r="H84" s="46"/>
+      <c r="I84" s="47"/>
+      <c r="J84" s="47"/>
+      <c r="K84" s="47"/>
+      <c r="L84" s="47"/>
+      <c r="M84" s="47"/>
+      <c r="N84" s="47"/>
+      <c r="O84" s="47"/>
+      <c r="P84" s="47"/>
+      <c r="Q84" s="47"/>
+      <c r="R84" s="47"/>
+      <c r="S84" s="47"/>
+      <c r="T84" s="47"/>
+      <c r="U84" s="47"/>
+      <c r="V84" s="47"/>
+      <c r="W84" s="47"/>
+      <c r="X84" s="47"/>
+      <c r="Y84" s="47"/>
+      <c r="Z84" s="47"/>
+      <c r="AA84" s="47"/>
+      <c r="AB84" s="48"/>
       <c r="AC84" s="11"/>
     </row>
     <row r="85" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4428,27 +4457,27 @@
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
-      <c r="H85" s="51"/>
-      <c r="I85" s="52"/>
-      <c r="J85" s="52"/>
-      <c r="K85" s="52"/>
-      <c r="L85" s="52"/>
-      <c r="M85" s="52"/>
-      <c r="N85" s="52"/>
-      <c r="O85" s="52"/>
-      <c r="P85" s="52"/>
-      <c r="Q85" s="52"/>
-      <c r="R85" s="52"/>
-      <c r="S85" s="52"/>
-      <c r="T85" s="52"/>
-      <c r="U85" s="52"/>
-      <c r="V85" s="52"/>
-      <c r="W85" s="52"/>
-      <c r="X85" s="52"/>
-      <c r="Y85" s="52"/>
-      <c r="Z85" s="52"/>
-      <c r="AA85" s="52"/>
-      <c r="AB85" s="53"/>
+      <c r="H85" s="49"/>
+      <c r="I85" s="50"/>
+      <c r="J85" s="50"/>
+      <c r="K85" s="50"/>
+      <c r="L85" s="50"/>
+      <c r="M85" s="50"/>
+      <c r="N85" s="50"/>
+      <c r="O85" s="50"/>
+      <c r="P85" s="50"/>
+      <c r="Q85" s="50"/>
+      <c r="R85" s="50"/>
+      <c r="S85" s="50"/>
+      <c r="T85" s="50"/>
+      <c r="U85" s="50"/>
+      <c r="V85" s="50"/>
+      <c r="W85" s="50"/>
+      <c r="X85" s="50"/>
+      <c r="Y85" s="50"/>
+      <c r="Z85" s="50"/>
+      <c r="AA85" s="50"/>
+      <c r="AB85" s="51"/>
       <c r="AC85" s="11"/>
     </row>
     <row r="86" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4458,27 +4487,27 @@
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
-      <c r="H86" s="51"/>
-      <c r="I86" s="52"/>
-      <c r="J86" s="52"/>
-      <c r="K86" s="52"/>
-      <c r="L86" s="52"/>
-      <c r="M86" s="52"/>
-      <c r="N86" s="52"/>
-      <c r="O86" s="52"/>
-      <c r="P86" s="52"/>
-      <c r="Q86" s="52"/>
-      <c r="R86" s="52"/>
-      <c r="S86" s="52"/>
-      <c r="T86" s="52"/>
-      <c r="U86" s="52"/>
-      <c r="V86" s="52"/>
-      <c r="W86" s="52"/>
-      <c r="X86" s="52"/>
-      <c r="Y86" s="52"/>
-      <c r="Z86" s="52"/>
-      <c r="AA86" s="52"/>
-      <c r="AB86" s="53"/>
+      <c r="H86" s="49"/>
+      <c r="I86" s="50"/>
+      <c r="J86" s="50"/>
+      <c r="K86" s="50"/>
+      <c r="L86" s="50"/>
+      <c r="M86" s="50"/>
+      <c r="N86" s="50"/>
+      <c r="O86" s="50"/>
+      <c r="P86" s="50"/>
+      <c r="Q86" s="50"/>
+      <c r="R86" s="50"/>
+      <c r="S86" s="50"/>
+      <c r="T86" s="50"/>
+      <c r="U86" s="50"/>
+      <c r="V86" s="50"/>
+      <c r="W86" s="50"/>
+      <c r="X86" s="50"/>
+      <c r="Y86" s="50"/>
+      <c r="Z86" s="50"/>
+      <c r="AA86" s="50"/>
+      <c r="AB86" s="51"/>
       <c r="AC86" s="11"/>
     </row>
     <row r="87" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4488,27 +4517,27 @@
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="52"/>
-      <c r="J87" s="52"/>
-      <c r="K87" s="52"/>
-      <c r="L87" s="52"/>
-      <c r="M87" s="52"/>
-      <c r="N87" s="52"/>
-      <c r="O87" s="52"/>
-      <c r="P87" s="52"/>
-      <c r="Q87" s="52"/>
-      <c r="R87" s="52"/>
-      <c r="S87" s="52"/>
-      <c r="T87" s="52"/>
-      <c r="U87" s="52"/>
-      <c r="V87" s="52"/>
-      <c r="W87" s="52"/>
-      <c r="X87" s="52"/>
-      <c r="Y87" s="52"/>
-      <c r="Z87" s="52"/>
-      <c r="AA87" s="52"/>
-      <c r="AB87" s="53"/>
+      <c r="H87" s="49"/>
+      <c r="I87" s="50"/>
+      <c r="J87" s="50"/>
+      <c r="K87" s="50"/>
+      <c r="L87" s="50"/>
+      <c r="M87" s="50"/>
+      <c r="N87" s="50"/>
+      <c r="O87" s="50"/>
+      <c r="P87" s="50"/>
+      <c r="Q87" s="50"/>
+      <c r="R87" s="50"/>
+      <c r="S87" s="50"/>
+      <c r="T87" s="50"/>
+      <c r="U87" s="50"/>
+      <c r="V87" s="50"/>
+      <c r="W87" s="50"/>
+      <c r="X87" s="50"/>
+      <c r="Y87" s="50"/>
+      <c r="Z87" s="50"/>
+      <c r="AA87" s="50"/>
+      <c r="AB87" s="51"/>
       <c r="AC87" s="11"/>
     </row>
     <row r="88" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4518,27 +4547,27 @@
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="52"/>
-      <c r="J88" s="52"/>
-      <c r="K88" s="52"/>
-      <c r="L88" s="52"/>
-      <c r="M88" s="52"/>
-      <c r="N88" s="52"/>
-      <c r="O88" s="52"/>
-      <c r="P88" s="52"/>
-      <c r="Q88" s="52"/>
-      <c r="R88" s="52"/>
-      <c r="S88" s="52"/>
-      <c r="T88" s="52"/>
-      <c r="U88" s="52"/>
-      <c r="V88" s="52"/>
-      <c r="W88" s="52"/>
-      <c r="X88" s="52"/>
-      <c r="Y88" s="52"/>
-      <c r="Z88" s="52"/>
-      <c r="AA88" s="52"/>
-      <c r="AB88" s="53"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="50"/>
+      <c r="J88" s="50"/>
+      <c r="K88" s="50"/>
+      <c r="L88" s="50"/>
+      <c r="M88" s="50"/>
+      <c r="N88" s="50"/>
+      <c r="O88" s="50"/>
+      <c r="P88" s="50"/>
+      <c r="Q88" s="50"/>
+      <c r="R88" s="50"/>
+      <c r="S88" s="50"/>
+      <c r="T88" s="50"/>
+      <c r="U88" s="50"/>
+      <c r="V88" s="50"/>
+      <c r="W88" s="50"/>
+      <c r="X88" s="50"/>
+      <c r="Y88" s="50"/>
+      <c r="Z88" s="50"/>
+      <c r="AA88" s="50"/>
+      <c r="AB88" s="51"/>
       <c r="AC88" s="11"/>
     </row>
     <row r="89" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4548,27 +4577,27 @@
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
-      <c r="H89" s="51"/>
-      <c r="I89" s="52"/>
-      <c r="J89" s="52"/>
-      <c r="K89" s="52"/>
-      <c r="L89" s="52"/>
-      <c r="M89" s="52"/>
-      <c r="N89" s="52"/>
-      <c r="O89" s="52"/>
-      <c r="P89" s="52"/>
-      <c r="Q89" s="52"/>
-      <c r="R89" s="52"/>
-      <c r="S89" s="52"/>
-      <c r="T89" s="52"/>
-      <c r="U89" s="52"/>
-      <c r="V89" s="52"/>
-      <c r="W89" s="52"/>
-      <c r="X89" s="52"/>
-      <c r="Y89" s="52"/>
-      <c r="Z89" s="52"/>
-      <c r="AA89" s="52"/>
-      <c r="AB89" s="53"/>
+      <c r="H89" s="49"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="50"/>
+      <c r="L89" s="50"/>
+      <c r="M89" s="50"/>
+      <c r="N89" s="50"/>
+      <c r="O89" s="50"/>
+      <c r="P89" s="50"/>
+      <c r="Q89" s="50"/>
+      <c r="R89" s="50"/>
+      <c r="S89" s="50"/>
+      <c r="T89" s="50"/>
+      <c r="U89" s="50"/>
+      <c r="V89" s="50"/>
+      <c r="W89" s="50"/>
+      <c r="X89" s="50"/>
+      <c r="Y89" s="50"/>
+      <c r="Z89" s="50"/>
+      <c r="AA89" s="50"/>
+      <c r="AB89" s="51"/>
       <c r="AC89" s="11"/>
     </row>
     <row r="90" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4578,27 +4607,27 @@
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
-      <c r="H90" s="54"/>
-      <c r="I90" s="55"/>
-      <c r="J90" s="55"/>
-      <c r="K90" s="55"/>
-      <c r="L90" s="55"/>
-      <c r="M90" s="55"/>
-      <c r="N90" s="55"/>
-      <c r="O90" s="55"/>
-      <c r="P90" s="55"/>
-      <c r="Q90" s="55"/>
-      <c r="R90" s="55"/>
-      <c r="S90" s="55"/>
-      <c r="T90" s="55"/>
-      <c r="U90" s="55"/>
-      <c r="V90" s="55"/>
-      <c r="W90" s="55"/>
-      <c r="X90" s="55"/>
-      <c r="Y90" s="55"/>
-      <c r="Z90" s="55"/>
-      <c r="AA90" s="55"/>
-      <c r="AB90" s="56"/>
+      <c r="H90" s="52"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
+      <c r="M90" s="53"/>
+      <c r="N90" s="53"/>
+      <c r="O90" s="53"/>
+      <c r="P90" s="53"/>
+      <c r="Q90" s="53"/>
+      <c r="R90" s="53"/>
+      <c r="S90" s="53"/>
+      <c r="T90" s="53"/>
+      <c r="U90" s="53"/>
+      <c r="V90" s="53"/>
+      <c r="W90" s="53"/>
+      <c r="X90" s="53"/>
+      <c r="Y90" s="53"/>
+      <c r="Z90" s="53"/>
+      <c r="AA90" s="53"/>
+      <c r="AB90" s="54"/>
       <c r="AC90" s="11"/>
     </row>
     <row r="91" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4640,27 +4669,27 @@
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="49"/>
-      <c r="J92" s="49"/>
-      <c r="K92" s="49"/>
-      <c r="L92" s="49"/>
-      <c r="M92" s="49"/>
-      <c r="N92" s="49"/>
-      <c r="O92" s="49"/>
-      <c r="P92" s="49"/>
-      <c r="Q92" s="49"/>
-      <c r="R92" s="49"/>
-      <c r="S92" s="49"/>
-      <c r="T92" s="49"/>
-      <c r="U92" s="49"/>
-      <c r="V92" s="49"/>
-      <c r="W92" s="49"/>
-      <c r="X92" s="49"/>
-      <c r="Y92" s="49"/>
-      <c r="Z92" s="49"/>
-      <c r="AA92" s="49"/>
-      <c r="AB92" s="50"/>
+      <c r="H92" s="46"/>
+      <c r="I92" s="47"/>
+      <c r="J92" s="47"/>
+      <c r="K92" s="47"/>
+      <c r="L92" s="47"/>
+      <c r="M92" s="47"/>
+      <c r="N92" s="47"/>
+      <c r="O92" s="47"/>
+      <c r="P92" s="47"/>
+      <c r="Q92" s="47"/>
+      <c r="R92" s="47"/>
+      <c r="S92" s="47"/>
+      <c r="T92" s="47"/>
+      <c r="U92" s="47"/>
+      <c r="V92" s="47"/>
+      <c r="W92" s="47"/>
+      <c r="X92" s="47"/>
+      <c r="Y92" s="47"/>
+      <c r="Z92" s="47"/>
+      <c r="AA92" s="47"/>
+      <c r="AB92" s="48"/>
       <c r="AC92" s="11"/>
     </row>
     <row r="93" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4670,27 +4699,27 @@
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
-      <c r="H93" s="51"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
-      <c r="L93" s="52"/>
-      <c r="M93" s="52"/>
-      <c r="N93" s="52"/>
-      <c r="O93" s="52"/>
-      <c r="P93" s="52"/>
-      <c r="Q93" s="52"/>
-      <c r="R93" s="52"/>
-      <c r="S93" s="52"/>
-      <c r="T93" s="52"/>
-      <c r="U93" s="52"/>
-      <c r="V93" s="52"/>
-      <c r="W93" s="52"/>
-      <c r="X93" s="52"/>
-      <c r="Y93" s="52"/>
-      <c r="Z93" s="52"/>
-      <c r="AA93" s="52"/>
-      <c r="AB93" s="53"/>
+      <c r="H93" s="49"/>
+      <c r="I93" s="50"/>
+      <c r="J93" s="50"/>
+      <c r="K93" s="50"/>
+      <c r="L93" s="50"/>
+      <c r="M93" s="50"/>
+      <c r="N93" s="50"/>
+      <c r="O93" s="50"/>
+      <c r="P93" s="50"/>
+      <c r="Q93" s="50"/>
+      <c r="R93" s="50"/>
+      <c r="S93" s="50"/>
+      <c r="T93" s="50"/>
+      <c r="U93" s="50"/>
+      <c r="V93" s="50"/>
+      <c r="W93" s="50"/>
+      <c r="X93" s="50"/>
+      <c r="Y93" s="50"/>
+      <c r="Z93" s="50"/>
+      <c r="AA93" s="50"/>
+      <c r="AB93" s="51"/>
       <c r="AC93" s="11"/>
     </row>
     <row r="94" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4700,27 +4729,27 @@
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
-      <c r="H94" s="51"/>
-      <c r="I94" s="52"/>
-      <c r="J94" s="52"/>
-      <c r="K94" s="52"/>
-      <c r="L94" s="52"/>
-      <c r="M94" s="52"/>
-      <c r="N94" s="52"/>
-      <c r="O94" s="52"/>
-      <c r="P94" s="52"/>
-      <c r="Q94" s="52"/>
-      <c r="R94" s="52"/>
-      <c r="S94" s="52"/>
-      <c r="T94" s="52"/>
-      <c r="U94" s="52"/>
-      <c r="V94" s="52"/>
-      <c r="W94" s="52"/>
-      <c r="X94" s="52"/>
-      <c r="Y94" s="52"/>
-      <c r="Z94" s="52"/>
-      <c r="AA94" s="52"/>
-      <c r="AB94" s="53"/>
+      <c r="H94" s="49"/>
+      <c r="I94" s="50"/>
+      <c r="J94" s="50"/>
+      <c r="K94" s="50"/>
+      <c r="L94" s="50"/>
+      <c r="M94" s="50"/>
+      <c r="N94" s="50"/>
+      <c r="O94" s="50"/>
+      <c r="P94" s="50"/>
+      <c r="Q94" s="50"/>
+      <c r="R94" s="50"/>
+      <c r="S94" s="50"/>
+      <c r="T94" s="50"/>
+      <c r="U94" s="50"/>
+      <c r="V94" s="50"/>
+      <c r="W94" s="50"/>
+      <c r="X94" s="50"/>
+      <c r="Y94" s="50"/>
+      <c r="Z94" s="50"/>
+      <c r="AA94" s="50"/>
+      <c r="AB94" s="51"/>
       <c r="AC94" s="11"/>
     </row>
     <row r="95" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4730,27 +4759,27 @@
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
-      <c r="H95" s="51"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="52"/>
-      <c r="K95" s="52"/>
-      <c r="L95" s="52"/>
-      <c r="M95" s="52"/>
-      <c r="N95" s="52"/>
-      <c r="O95" s="52"/>
-      <c r="P95" s="52"/>
-      <c r="Q95" s="52"/>
-      <c r="R95" s="52"/>
-      <c r="S95" s="52"/>
-      <c r="T95" s="52"/>
-      <c r="U95" s="52"/>
-      <c r="V95" s="52"/>
-      <c r="W95" s="52"/>
-      <c r="X95" s="52"/>
-      <c r="Y95" s="52"/>
-      <c r="Z95" s="52"/>
-      <c r="AA95" s="52"/>
-      <c r="AB95" s="53"/>
+      <c r="H95" s="49"/>
+      <c r="I95" s="50"/>
+      <c r="J95" s="50"/>
+      <c r="K95" s="50"/>
+      <c r="L95" s="50"/>
+      <c r="M95" s="50"/>
+      <c r="N95" s="50"/>
+      <c r="O95" s="50"/>
+      <c r="P95" s="50"/>
+      <c r="Q95" s="50"/>
+      <c r="R95" s="50"/>
+      <c r="S95" s="50"/>
+      <c r="T95" s="50"/>
+      <c r="U95" s="50"/>
+      <c r="V95" s="50"/>
+      <c r="W95" s="50"/>
+      <c r="X95" s="50"/>
+      <c r="Y95" s="50"/>
+      <c r="Z95" s="50"/>
+      <c r="AA95" s="50"/>
+      <c r="AB95" s="51"/>
       <c r="AC95" s="11"/>
     </row>
     <row r="96" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4760,27 +4789,27 @@
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
-      <c r="H96" s="51"/>
-      <c r="I96" s="52"/>
-      <c r="J96" s="52"/>
-      <c r="K96" s="52"/>
-      <c r="L96" s="52"/>
-      <c r="M96" s="52"/>
-      <c r="N96" s="52"/>
-      <c r="O96" s="52"/>
-      <c r="P96" s="52"/>
-      <c r="Q96" s="52"/>
-      <c r="R96" s="52"/>
-      <c r="S96" s="52"/>
-      <c r="T96" s="52"/>
-      <c r="U96" s="52"/>
-      <c r="V96" s="52"/>
-      <c r="W96" s="52"/>
-      <c r="X96" s="52"/>
-      <c r="Y96" s="52"/>
-      <c r="Z96" s="52"/>
-      <c r="AA96" s="52"/>
-      <c r="AB96" s="53"/>
+      <c r="H96" s="49"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="50"/>
+      <c r="K96" s="50"/>
+      <c r="L96" s="50"/>
+      <c r="M96" s="50"/>
+      <c r="N96" s="50"/>
+      <c r="O96" s="50"/>
+      <c r="P96" s="50"/>
+      <c r="Q96" s="50"/>
+      <c r="R96" s="50"/>
+      <c r="S96" s="50"/>
+      <c r="T96" s="50"/>
+      <c r="U96" s="50"/>
+      <c r="V96" s="50"/>
+      <c r="W96" s="50"/>
+      <c r="X96" s="50"/>
+      <c r="Y96" s="50"/>
+      <c r="Z96" s="50"/>
+      <c r="AA96" s="50"/>
+      <c r="AB96" s="51"/>
       <c r="AC96" s="11"/>
     </row>
     <row r="97" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4790,27 +4819,27 @@
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
-      <c r="H97" s="51"/>
-      <c r="I97" s="52"/>
-      <c r="J97" s="52"/>
-      <c r="K97" s="52"/>
-      <c r="L97" s="52"/>
-      <c r="M97" s="52"/>
-      <c r="N97" s="52"/>
-      <c r="O97" s="52"/>
-      <c r="P97" s="52"/>
-      <c r="Q97" s="52"/>
-      <c r="R97" s="52"/>
-      <c r="S97" s="52"/>
-      <c r="T97" s="52"/>
-      <c r="U97" s="52"/>
-      <c r="V97" s="52"/>
-      <c r="W97" s="52"/>
-      <c r="X97" s="52"/>
-      <c r="Y97" s="52"/>
-      <c r="Z97" s="52"/>
-      <c r="AA97" s="52"/>
-      <c r="AB97" s="53"/>
+      <c r="H97" s="49"/>
+      <c r="I97" s="50"/>
+      <c r="J97" s="50"/>
+      <c r="K97" s="50"/>
+      <c r="L97" s="50"/>
+      <c r="M97" s="50"/>
+      <c r="N97" s="50"/>
+      <c r="O97" s="50"/>
+      <c r="P97" s="50"/>
+      <c r="Q97" s="50"/>
+      <c r="R97" s="50"/>
+      <c r="S97" s="50"/>
+      <c r="T97" s="50"/>
+      <c r="U97" s="50"/>
+      <c r="V97" s="50"/>
+      <c r="W97" s="50"/>
+      <c r="X97" s="50"/>
+      <c r="Y97" s="50"/>
+      <c r="Z97" s="50"/>
+      <c r="AA97" s="50"/>
+      <c r="AB97" s="51"/>
       <c r="AC97" s="11"/>
     </row>
     <row r="98" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4820,27 +4849,27 @@
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
-      <c r="H98" s="54"/>
-      <c r="I98" s="55"/>
-      <c r="J98" s="55"/>
-      <c r="K98" s="55"/>
-      <c r="L98" s="55"/>
-      <c r="M98" s="55"/>
-      <c r="N98" s="55"/>
-      <c r="O98" s="55"/>
-      <c r="P98" s="55"/>
-      <c r="Q98" s="55"/>
-      <c r="R98" s="55"/>
-      <c r="S98" s="55"/>
-      <c r="T98" s="55"/>
-      <c r="U98" s="55"/>
-      <c r="V98" s="55"/>
-      <c r="W98" s="55"/>
-      <c r="X98" s="55"/>
-      <c r="Y98" s="55"/>
-      <c r="Z98" s="55"/>
-      <c r="AA98" s="55"/>
-      <c r="AB98" s="56"/>
+      <c r="H98" s="52"/>
+      <c r="I98" s="53"/>
+      <c r="J98" s="53"/>
+      <c r="K98" s="53"/>
+      <c r="L98" s="53"/>
+      <c r="M98" s="53"/>
+      <c r="N98" s="53"/>
+      <c r="O98" s="53"/>
+      <c r="P98" s="53"/>
+      <c r="Q98" s="53"/>
+      <c r="R98" s="53"/>
+      <c r="S98" s="53"/>
+      <c r="T98" s="53"/>
+      <c r="U98" s="53"/>
+      <c r="V98" s="53"/>
+      <c r="W98" s="53"/>
+      <c r="X98" s="53"/>
+      <c r="Y98" s="53"/>
+      <c r="Z98" s="53"/>
+      <c r="AA98" s="53"/>
+      <c r="AB98" s="54"/>
       <c r="AC98" s="11"/>
     </row>
     <row r="99" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4948,27 +4977,27 @@
         <v>2</v>
       </c>
       <c r="G103" s="6"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="49"/>
-      <c r="J103" s="49"/>
-      <c r="K103" s="49"/>
-      <c r="L103" s="49"/>
-      <c r="M103" s="49"/>
-      <c r="N103" s="49"/>
-      <c r="O103" s="49"/>
-      <c r="P103" s="49"/>
-      <c r="Q103" s="49"/>
-      <c r="R103" s="49"/>
-      <c r="S103" s="49"/>
-      <c r="T103" s="49"/>
-      <c r="U103" s="49"/>
-      <c r="V103" s="49"/>
-      <c r="W103" s="49"/>
-      <c r="X103" s="49"/>
-      <c r="Y103" s="49"/>
-      <c r="Z103" s="49"/>
-      <c r="AA103" s="49"/>
-      <c r="AB103" s="50"/>
+      <c r="H103" s="46"/>
+      <c r="I103" s="47"/>
+      <c r="J103" s="47"/>
+      <c r="K103" s="47"/>
+      <c r="L103" s="47"/>
+      <c r="M103" s="47"/>
+      <c r="N103" s="47"/>
+      <c r="O103" s="47"/>
+      <c r="P103" s="47"/>
+      <c r="Q103" s="47"/>
+      <c r="R103" s="47"/>
+      <c r="S103" s="47"/>
+      <c r="T103" s="47"/>
+      <c r="U103" s="47"/>
+      <c r="V103" s="47"/>
+      <c r="W103" s="47"/>
+      <c r="X103" s="47"/>
+      <c r="Y103" s="47"/>
+      <c r="Z103" s="47"/>
+      <c r="AA103" s="47"/>
+      <c r="AB103" s="48"/>
       <c r="AC103" s="11"/>
     </row>
     <row r="104" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4978,27 +5007,27 @@
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
-      <c r="H104" s="51"/>
-      <c r="I104" s="52"/>
-      <c r="J104" s="52"/>
-      <c r="K104" s="52"/>
-      <c r="L104" s="52"/>
-      <c r="M104" s="52"/>
-      <c r="N104" s="52"/>
-      <c r="O104" s="52"/>
-      <c r="P104" s="52"/>
-      <c r="Q104" s="52"/>
-      <c r="R104" s="52"/>
-      <c r="S104" s="52"/>
-      <c r="T104" s="52"/>
-      <c r="U104" s="52"/>
-      <c r="V104" s="52"/>
-      <c r="W104" s="52"/>
-      <c r="X104" s="52"/>
-      <c r="Y104" s="52"/>
-      <c r="Z104" s="52"/>
-      <c r="AA104" s="52"/>
-      <c r="AB104" s="53"/>
+      <c r="H104" s="49"/>
+      <c r="I104" s="50"/>
+      <c r="J104" s="50"/>
+      <c r="K104" s="50"/>
+      <c r="L104" s="50"/>
+      <c r="M104" s="50"/>
+      <c r="N104" s="50"/>
+      <c r="O104" s="50"/>
+      <c r="P104" s="50"/>
+      <c r="Q104" s="50"/>
+      <c r="R104" s="50"/>
+      <c r="S104" s="50"/>
+      <c r="T104" s="50"/>
+      <c r="U104" s="50"/>
+      <c r="V104" s="50"/>
+      <c r="W104" s="50"/>
+      <c r="X104" s="50"/>
+      <c r="Y104" s="50"/>
+      <c r="Z104" s="50"/>
+      <c r="AA104" s="50"/>
+      <c r="AB104" s="51"/>
       <c r="AC104" s="11"/>
     </row>
     <row r="105" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5008,27 +5037,27 @@
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
-      <c r="H105" s="51"/>
-      <c r="I105" s="52"/>
-      <c r="J105" s="52"/>
-      <c r="K105" s="52"/>
-      <c r="L105" s="52"/>
-      <c r="M105" s="52"/>
-      <c r="N105" s="52"/>
-      <c r="O105" s="52"/>
-      <c r="P105" s="52"/>
-      <c r="Q105" s="52"/>
-      <c r="R105" s="52"/>
-      <c r="S105" s="52"/>
-      <c r="T105" s="52"/>
-      <c r="U105" s="52"/>
-      <c r="V105" s="52"/>
-      <c r="W105" s="52"/>
-      <c r="X105" s="52"/>
-      <c r="Y105" s="52"/>
-      <c r="Z105" s="52"/>
-      <c r="AA105" s="52"/>
-      <c r="AB105" s="53"/>
+      <c r="H105" s="49"/>
+      <c r="I105" s="50"/>
+      <c r="J105" s="50"/>
+      <c r="K105" s="50"/>
+      <c r="L105" s="50"/>
+      <c r="M105" s="50"/>
+      <c r="N105" s="50"/>
+      <c r="O105" s="50"/>
+      <c r="P105" s="50"/>
+      <c r="Q105" s="50"/>
+      <c r="R105" s="50"/>
+      <c r="S105" s="50"/>
+      <c r="T105" s="50"/>
+      <c r="U105" s="50"/>
+      <c r="V105" s="50"/>
+      <c r="W105" s="50"/>
+      <c r="X105" s="50"/>
+      <c r="Y105" s="50"/>
+      <c r="Z105" s="50"/>
+      <c r="AA105" s="50"/>
+      <c r="AB105" s="51"/>
       <c r="AC105" s="11"/>
     </row>
     <row r="106" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5038,27 +5067,27 @@
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
-      <c r="H106" s="51"/>
-      <c r="I106" s="52"/>
-      <c r="J106" s="52"/>
-      <c r="K106" s="52"/>
-      <c r="L106" s="52"/>
-      <c r="M106" s="52"/>
-      <c r="N106" s="52"/>
-      <c r="O106" s="52"/>
-      <c r="P106" s="52"/>
-      <c r="Q106" s="52"/>
-      <c r="R106" s="52"/>
-      <c r="S106" s="52"/>
-      <c r="T106" s="52"/>
-      <c r="U106" s="52"/>
-      <c r="V106" s="52"/>
-      <c r="W106" s="52"/>
-      <c r="X106" s="52"/>
-      <c r="Y106" s="52"/>
-      <c r="Z106" s="52"/>
-      <c r="AA106" s="52"/>
-      <c r="AB106" s="53"/>
+      <c r="H106" s="49"/>
+      <c r="I106" s="50"/>
+      <c r="J106" s="50"/>
+      <c r="K106" s="50"/>
+      <c r="L106" s="50"/>
+      <c r="M106" s="50"/>
+      <c r="N106" s="50"/>
+      <c r="O106" s="50"/>
+      <c r="P106" s="50"/>
+      <c r="Q106" s="50"/>
+      <c r="R106" s="50"/>
+      <c r="S106" s="50"/>
+      <c r="T106" s="50"/>
+      <c r="U106" s="50"/>
+      <c r="V106" s="50"/>
+      <c r="W106" s="50"/>
+      <c r="X106" s="50"/>
+      <c r="Y106" s="50"/>
+      <c r="Z106" s="50"/>
+      <c r="AA106" s="50"/>
+      <c r="AB106" s="51"/>
       <c r="AC106" s="11"/>
     </row>
     <row r="107" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5068,27 +5097,27 @@
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
-      <c r="H107" s="51"/>
-      <c r="I107" s="52"/>
-      <c r="J107" s="52"/>
-      <c r="K107" s="52"/>
-      <c r="L107" s="52"/>
-      <c r="M107" s="52"/>
-      <c r="N107" s="52"/>
-      <c r="O107" s="52"/>
-      <c r="P107" s="52"/>
-      <c r="Q107" s="52"/>
-      <c r="R107" s="52"/>
-      <c r="S107" s="52"/>
-      <c r="T107" s="52"/>
-      <c r="U107" s="52"/>
-      <c r="V107" s="52"/>
-      <c r="W107" s="52"/>
-      <c r="X107" s="52"/>
-      <c r="Y107" s="52"/>
-      <c r="Z107" s="52"/>
-      <c r="AA107" s="52"/>
-      <c r="AB107" s="53"/>
+      <c r="H107" s="49"/>
+      <c r="I107" s="50"/>
+      <c r="J107" s="50"/>
+      <c r="K107" s="50"/>
+      <c r="L107" s="50"/>
+      <c r="M107" s="50"/>
+      <c r="N107" s="50"/>
+      <c r="O107" s="50"/>
+      <c r="P107" s="50"/>
+      <c r="Q107" s="50"/>
+      <c r="R107" s="50"/>
+      <c r="S107" s="50"/>
+      <c r="T107" s="50"/>
+      <c r="U107" s="50"/>
+      <c r="V107" s="50"/>
+      <c r="W107" s="50"/>
+      <c r="X107" s="50"/>
+      <c r="Y107" s="50"/>
+      <c r="Z107" s="50"/>
+      <c r="AA107" s="50"/>
+      <c r="AB107" s="51"/>
       <c r="AC107" s="11"/>
     </row>
     <row r="108" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5098,27 +5127,27 @@
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
-      <c r="H108" s="51"/>
-      <c r="I108" s="52"/>
-      <c r="J108" s="52"/>
-      <c r="K108" s="52"/>
-      <c r="L108" s="52"/>
-      <c r="M108" s="52"/>
-      <c r="N108" s="52"/>
-      <c r="O108" s="52"/>
-      <c r="P108" s="52"/>
-      <c r="Q108" s="52"/>
-      <c r="R108" s="52"/>
-      <c r="S108" s="52"/>
-      <c r="T108" s="52"/>
-      <c r="U108" s="52"/>
-      <c r="V108" s="52"/>
-      <c r="W108" s="52"/>
-      <c r="X108" s="52"/>
-      <c r="Y108" s="52"/>
-      <c r="Z108" s="52"/>
-      <c r="AA108" s="52"/>
-      <c r="AB108" s="53"/>
+      <c r="H108" s="49"/>
+      <c r="I108" s="50"/>
+      <c r="J108" s="50"/>
+      <c r="K108" s="50"/>
+      <c r="L108" s="50"/>
+      <c r="M108" s="50"/>
+      <c r="N108" s="50"/>
+      <c r="O108" s="50"/>
+      <c r="P108" s="50"/>
+      <c r="Q108" s="50"/>
+      <c r="R108" s="50"/>
+      <c r="S108" s="50"/>
+      <c r="T108" s="50"/>
+      <c r="U108" s="50"/>
+      <c r="V108" s="50"/>
+      <c r="W108" s="50"/>
+      <c r="X108" s="50"/>
+      <c r="Y108" s="50"/>
+      <c r="Z108" s="50"/>
+      <c r="AA108" s="50"/>
+      <c r="AB108" s="51"/>
       <c r="AC108" s="11"/>
     </row>
     <row r="109" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5128,27 +5157,27 @@
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
-      <c r="H109" s="54"/>
-      <c r="I109" s="55"/>
-      <c r="J109" s="55"/>
-      <c r="K109" s="55"/>
-      <c r="L109" s="55"/>
-      <c r="M109" s="55"/>
-      <c r="N109" s="55"/>
-      <c r="O109" s="55"/>
-      <c r="P109" s="55"/>
-      <c r="Q109" s="55"/>
-      <c r="R109" s="55"/>
-      <c r="S109" s="55"/>
-      <c r="T109" s="55"/>
-      <c r="U109" s="55"/>
-      <c r="V109" s="55"/>
-      <c r="W109" s="55"/>
-      <c r="X109" s="55"/>
-      <c r="Y109" s="55"/>
-      <c r="Z109" s="55"/>
-      <c r="AA109" s="55"/>
-      <c r="AB109" s="56"/>
+      <c r="H109" s="52"/>
+      <c r="I109" s="53"/>
+      <c r="J109" s="53"/>
+      <c r="K109" s="53"/>
+      <c r="L109" s="53"/>
+      <c r="M109" s="53"/>
+      <c r="N109" s="53"/>
+      <c r="O109" s="53"/>
+      <c r="P109" s="53"/>
+      <c r="Q109" s="53"/>
+      <c r="R109" s="53"/>
+      <c r="S109" s="53"/>
+      <c r="T109" s="53"/>
+      <c r="U109" s="53"/>
+      <c r="V109" s="53"/>
+      <c r="W109" s="53"/>
+      <c r="X109" s="53"/>
+      <c r="Y109" s="53"/>
+      <c r="Z109" s="53"/>
+      <c r="AA109" s="53"/>
+      <c r="AB109" s="54"/>
       <c r="AC109" s="11"/>
     </row>
     <row r="110" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5190,27 +5219,27 @@
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
-      <c r="H111" s="48"/>
-      <c r="I111" s="49"/>
-      <c r="J111" s="49"/>
-      <c r="K111" s="49"/>
-      <c r="L111" s="49"/>
-      <c r="M111" s="49"/>
-      <c r="N111" s="49"/>
-      <c r="O111" s="49"/>
-      <c r="P111" s="49"/>
-      <c r="Q111" s="49"/>
-      <c r="R111" s="49"/>
-      <c r="S111" s="49"/>
-      <c r="T111" s="49"/>
-      <c r="U111" s="49"/>
-      <c r="V111" s="49"/>
-      <c r="W111" s="49"/>
-      <c r="X111" s="49"/>
-      <c r="Y111" s="49"/>
-      <c r="Z111" s="49"/>
-      <c r="AA111" s="49"/>
-      <c r="AB111" s="50"/>
+      <c r="H111" s="46"/>
+      <c r="I111" s="47"/>
+      <c r="J111" s="47"/>
+      <c r="K111" s="47"/>
+      <c r="L111" s="47"/>
+      <c r="M111" s="47"/>
+      <c r="N111" s="47"/>
+      <c r="O111" s="47"/>
+      <c r="P111" s="47"/>
+      <c r="Q111" s="47"/>
+      <c r="R111" s="47"/>
+      <c r="S111" s="47"/>
+      <c r="T111" s="47"/>
+      <c r="U111" s="47"/>
+      <c r="V111" s="47"/>
+      <c r="W111" s="47"/>
+      <c r="X111" s="47"/>
+      <c r="Y111" s="47"/>
+      <c r="Z111" s="47"/>
+      <c r="AA111" s="47"/>
+      <c r="AB111" s="48"/>
       <c r="AC111" s="11"/>
     </row>
     <row r="112" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5220,27 +5249,27 @@
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
-      <c r="H112" s="51"/>
-      <c r="I112" s="52"/>
-      <c r="J112" s="52"/>
-      <c r="K112" s="52"/>
-      <c r="L112" s="52"/>
-      <c r="M112" s="52"/>
-      <c r="N112" s="52"/>
-      <c r="O112" s="52"/>
-      <c r="P112" s="52"/>
-      <c r="Q112" s="52"/>
-      <c r="R112" s="52"/>
-      <c r="S112" s="52"/>
-      <c r="T112" s="52"/>
-      <c r="U112" s="52"/>
-      <c r="V112" s="52"/>
-      <c r="W112" s="52"/>
-      <c r="X112" s="52"/>
-      <c r="Y112" s="52"/>
-      <c r="Z112" s="52"/>
-      <c r="AA112" s="52"/>
-      <c r="AB112" s="53"/>
+      <c r="H112" s="49"/>
+      <c r="I112" s="50"/>
+      <c r="J112" s="50"/>
+      <c r="K112" s="50"/>
+      <c r="L112" s="50"/>
+      <c r="M112" s="50"/>
+      <c r="N112" s="50"/>
+      <c r="O112" s="50"/>
+      <c r="P112" s="50"/>
+      <c r="Q112" s="50"/>
+      <c r="R112" s="50"/>
+      <c r="S112" s="50"/>
+      <c r="T112" s="50"/>
+      <c r="U112" s="50"/>
+      <c r="V112" s="50"/>
+      <c r="W112" s="50"/>
+      <c r="X112" s="50"/>
+      <c r="Y112" s="50"/>
+      <c r="Z112" s="50"/>
+      <c r="AA112" s="50"/>
+      <c r="AB112" s="51"/>
       <c r="AC112" s="11"/>
     </row>
     <row r="113" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5250,27 +5279,27 @@
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
-      <c r="H113" s="51"/>
-      <c r="I113" s="52"/>
-      <c r="J113" s="52"/>
-      <c r="K113" s="52"/>
-      <c r="L113" s="52"/>
-      <c r="M113" s="52"/>
-      <c r="N113" s="52"/>
-      <c r="O113" s="52"/>
-      <c r="P113" s="52"/>
-      <c r="Q113" s="52"/>
-      <c r="R113" s="52"/>
-      <c r="S113" s="52"/>
-      <c r="T113" s="52"/>
-      <c r="U113" s="52"/>
-      <c r="V113" s="52"/>
-      <c r="W113" s="52"/>
-      <c r="X113" s="52"/>
-      <c r="Y113" s="52"/>
-      <c r="Z113" s="52"/>
-      <c r="AA113" s="52"/>
-      <c r="AB113" s="53"/>
+      <c r="H113" s="49"/>
+      <c r="I113" s="50"/>
+      <c r="J113" s="50"/>
+      <c r="K113" s="50"/>
+      <c r="L113" s="50"/>
+      <c r="M113" s="50"/>
+      <c r="N113" s="50"/>
+      <c r="O113" s="50"/>
+      <c r="P113" s="50"/>
+      <c r="Q113" s="50"/>
+      <c r="R113" s="50"/>
+      <c r="S113" s="50"/>
+      <c r="T113" s="50"/>
+      <c r="U113" s="50"/>
+      <c r="V113" s="50"/>
+      <c r="W113" s="50"/>
+      <c r="X113" s="50"/>
+      <c r="Y113" s="50"/>
+      <c r="Z113" s="50"/>
+      <c r="AA113" s="50"/>
+      <c r="AB113" s="51"/>
       <c r="AC113" s="11"/>
     </row>
     <row r="114" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5280,27 +5309,27 @@
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
-      <c r="H114" s="51"/>
-      <c r="I114" s="52"/>
-      <c r="J114" s="52"/>
-      <c r="K114" s="52"/>
-      <c r="L114" s="52"/>
-      <c r="M114" s="52"/>
-      <c r="N114" s="52"/>
-      <c r="O114" s="52"/>
-      <c r="P114" s="52"/>
-      <c r="Q114" s="52"/>
-      <c r="R114" s="52"/>
-      <c r="S114" s="52"/>
-      <c r="T114" s="52"/>
-      <c r="U114" s="52"/>
-      <c r="V114" s="52"/>
-      <c r="W114" s="52"/>
-      <c r="X114" s="52"/>
-      <c r="Y114" s="52"/>
-      <c r="Z114" s="52"/>
-      <c r="AA114" s="52"/>
-      <c r="AB114" s="53"/>
+      <c r="H114" s="49"/>
+      <c r="I114" s="50"/>
+      <c r="J114" s="50"/>
+      <c r="K114" s="50"/>
+      <c r="L114" s="50"/>
+      <c r="M114" s="50"/>
+      <c r="N114" s="50"/>
+      <c r="O114" s="50"/>
+      <c r="P114" s="50"/>
+      <c r="Q114" s="50"/>
+      <c r="R114" s="50"/>
+      <c r="S114" s="50"/>
+      <c r="T114" s="50"/>
+      <c r="U114" s="50"/>
+      <c r="V114" s="50"/>
+      <c r="W114" s="50"/>
+      <c r="X114" s="50"/>
+      <c r="Y114" s="50"/>
+      <c r="Z114" s="50"/>
+      <c r="AA114" s="50"/>
+      <c r="AB114" s="51"/>
       <c r="AC114" s="11"/>
     </row>
     <row r="115" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5310,27 +5339,27 @@
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
-      <c r="H115" s="51"/>
-      <c r="I115" s="52"/>
-      <c r="J115" s="52"/>
-      <c r="K115" s="52"/>
-      <c r="L115" s="52"/>
-      <c r="M115" s="52"/>
-      <c r="N115" s="52"/>
-      <c r="O115" s="52"/>
-      <c r="P115" s="52"/>
-      <c r="Q115" s="52"/>
-      <c r="R115" s="52"/>
-      <c r="S115" s="52"/>
-      <c r="T115" s="52"/>
-      <c r="U115" s="52"/>
-      <c r="V115" s="52"/>
-      <c r="W115" s="52"/>
-      <c r="X115" s="52"/>
-      <c r="Y115" s="52"/>
-      <c r="Z115" s="52"/>
-      <c r="AA115" s="52"/>
-      <c r="AB115" s="53"/>
+      <c r="H115" s="49"/>
+      <c r="I115" s="50"/>
+      <c r="J115" s="50"/>
+      <c r="K115" s="50"/>
+      <c r="L115" s="50"/>
+      <c r="M115" s="50"/>
+      <c r="N115" s="50"/>
+      <c r="O115" s="50"/>
+      <c r="P115" s="50"/>
+      <c r="Q115" s="50"/>
+      <c r="R115" s="50"/>
+      <c r="S115" s="50"/>
+      <c r="T115" s="50"/>
+      <c r="U115" s="50"/>
+      <c r="V115" s="50"/>
+      <c r="W115" s="50"/>
+      <c r="X115" s="50"/>
+      <c r="Y115" s="50"/>
+      <c r="Z115" s="50"/>
+      <c r="AA115" s="50"/>
+      <c r="AB115" s="51"/>
       <c r="AC115" s="11"/>
     </row>
     <row r="116" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5340,27 +5369,27 @@
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
-      <c r="H116" s="51"/>
-      <c r="I116" s="52"/>
-      <c r="J116" s="52"/>
-      <c r="K116" s="52"/>
-      <c r="L116" s="52"/>
-      <c r="M116" s="52"/>
-      <c r="N116" s="52"/>
-      <c r="O116" s="52"/>
-      <c r="P116" s="52"/>
-      <c r="Q116" s="52"/>
-      <c r="R116" s="52"/>
-      <c r="S116" s="52"/>
-      <c r="T116" s="52"/>
-      <c r="U116" s="52"/>
-      <c r="V116" s="52"/>
-      <c r="W116" s="52"/>
-      <c r="X116" s="52"/>
-      <c r="Y116" s="52"/>
-      <c r="Z116" s="52"/>
-      <c r="AA116" s="52"/>
-      <c r="AB116" s="53"/>
+      <c r="H116" s="49"/>
+      <c r="I116" s="50"/>
+      <c r="J116" s="50"/>
+      <c r="K116" s="50"/>
+      <c r="L116" s="50"/>
+      <c r="M116" s="50"/>
+      <c r="N116" s="50"/>
+      <c r="O116" s="50"/>
+      <c r="P116" s="50"/>
+      <c r="Q116" s="50"/>
+      <c r="R116" s="50"/>
+      <c r="S116" s="50"/>
+      <c r="T116" s="50"/>
+      <c r="U116" s="50"/>
+      <c r="V116" s="50"/>
+      <c r="W116" s="50"/>
+      <c r="X116" s="50"/>
+      <c r="Y116" s="50"/>
+      <c r="Z116" s="50"/>
+      <c r="AA116" s="50"/>
+      <c r="AB116" s="51"/>
       <c r="AC116" s="11"/>
     </row>
     <row r="117" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5370,27 +5399,27 @@
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
-      <c r="H117" s="54"/>
-      <c r="I117" s="55"/>
-      <c r="J117" s="55"/>
-      <c r="K117" s="55"/>
-      <c r="L117" s="55"/>
-      <c r="M117" s="55"/>
-      <c r="N117" s="55"/>
-      <c r="O117" s="55"/>
-      <c r="P117" s="55"/>
-      <c r="Q117" s="55"/>
-      <c r="R117" s="55"/>
-      <c r="S117" s="55"/>
-      <c r="T117" s="55"/>
-      <c r="U117" s="55"/>
-      <c r="V117" s="55"/>
-      <c r="W117" s="55"/>
-      <c r="X117" s="55"/>
-      <c r="Y117" s="55"/>
-      <c r="Z117" s="55"/>
-      <c r="AA117" s="55"/>
-      <c r="AB117" s="56"/>
+      <c r="H117" s="52"/>
+      <c r="I117" s="53"/>
+      <c r="J117" s="53"/>
+      <c r="K117" s="53"/>
+      <c r="L117" s="53"/>
+      <c r="M117" s="53"/>
+      <c r="N117" s="53"/>
+      <c r="O117" s="53"/>
+      <c r="P117" s="53"/>
+      <c r="Q117" s="53"/>
+      <c r="R117" s="53"/>
+      <c r="S117" s="53"/>
+      <c r="T117" s="53"/>
+      <c r="U117" s="53"/>
+      <c r="V117" s="53"/>
+      <c r="W117" s="53"/>
+      <c r="X117" s="53"/>
+      <c r="Y117" s="53"/>
+      <c r="Z117" s="53"/>
+      <c r="AA117" s="53"/>
+      <c r="AB117" s="54"/>
       <c r="AC117" s="11"/>
     </row>
     <row r="118" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5498,27 +5527,27 @@
         <v>2</v>
       </c>
       <c r="G122" s="6"/>
-      <c r="H122" s="48"/>
-      <c r="I122" s="49"/>
-      <c r="J122" s="49"/>
-      <c r="K122" s="49"/>
-      <c r="L122" s="49"/>
-      <c r="M122" s="49"/>
-      <c r="N122" s="49"/>
-      <c r="O122" s="49"/>
-      <c r="P122" s="49"/>
-      <c r="Q122" s="49"/>
-      <c r="R122" s="49"/>
-      <c r="S122" s="49"/>
-      <c r="T122" s="49"/>
-      <c r="U122" s="49"/>
-      <c r="V122" s="49"/>
-      <c r="W122" s="49"/>
-      <c r="X122" s="49"/>
-      <c r="Y122" s="49"/>
-      <c r="Z122" s="49"/>
-      <c r="AA122" s="49"/>
-      <c r="AB122" s="50"/>
+      <c r="H122" s="46"/>
+      <c r="I122" s="47"/>
+      <c r="J122" s="47"/>
+      <c r="K122" s="47"/>
+      <c r="L122" s="47"/>
+      <c r="M122" s="47"/>
+      <c r="N122" s="47"/>
+      <c r="O122" s="47"/>
+      <c r="P122" s="47"/>
+      <c r="Q122" s="47"/>
+      <c r="R122" s="47"/>
+      <c r="S122" s="47"/>
+      <c r="T122" s="47"/>
+      <c r="U122" s="47"/>
+      <c r="V122" s="47"/>
+      <c r="W122" s="47"/>
+      <c r="X122" s="47"/>
+      <c r="Y122" s="47"/>
+      <c r="Z122" s="47"/>
+      <c r="AA122" s="47"/>
+      <c r="AB122" s="48"/>
       <c r="AC122" s="11"/>
     </row>
     <row r="123" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5528,27 +5557,27 @@
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
-      <c r="H123" s="51"/>
-      <c r="I123" s="52"/>
-      <c r="J123" s="52"/>
-      <c r="K123" s="52"/>
-      <c r="L123" s="52"/>
-      <c r="M123" s="52"/>
-      <c r="N123" s="52"/>
-      <c r="O123" s="52"/>
-      <c r="P123" s="52"/>
-      <c r="Q123" s="52"/>
-      <c r="R123" s="52"/>
-      <c r="S123" s="52"/>
-      <c r="T123" s="52"/>
-      <c r="U123" s="52"/>
-      <c r="V123" s="52"/>
-      <c r="W123" s="52"/>
-      <c r="X123" s="52"/>
-      <c r="Y123" s="52"/>
-      <c r="Z123" s="52"/>
-      <c r="AA123" s="52"/>
-      <c r="AB123" s="53"/>
+      <c r="H123" s="49"/>
+      <c r="I123" s="50"/>
+      <c r="J123" s="50"/>
+      <c r="K123" s="50"/>
+      <c r="L123" s="50"/>
+      <c r="M123" s="50"/>
+      <c r="N123" s="50"/>
+      <c r="O123" s="50"/>
+      <c r="P123" s="50"/>
+      <c r="Q123" s="50"/>
+      <c r="R123" s="50"/>
+      <c r="S123" s="50"/>
+      <c r="T123" s="50"/>
+      <c r="U123" s="50"/>
+      <c r="V123" s="50"/>
+      <c r="W123" s="50"/>
+      <c r="X123" s="50"/>
+      <c r="Y123" s="50"/>
+      <c r="Z123" s="50"/>
+      <c r="AA123" s="50"/>
+      <c r="AB123" s="51"/>
       <c r="AC123" s="11"/>
     </row>
     <row r="124" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5558,27 +5587,27 @@
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
-      <c r="H124" s="51"/>
-      <c r="I124" s="52"/>
-      <c r="J124" s="52"/>
-      <c r="K124" s="52"/>
-      <c r="L124" s="52"/>
-      <c r="M124" s="52"/>
-      <c r="N124" s="52"/>
-      <c r="O124" s="52"/>
-      <c r="P124" s="52"/>
-      <c r="Q124" s="52"/>
-      <c r="R124" s="52"/>
-      <c r="S124" s="52"/>
-      <c r="T124" s="52"/>
-      <c r="U124" s="52"/>
-      <c r="V124" s="52"/>
-      <c r="W124" s="52"/>
-      <c r="X124" s="52"/>
-      <c r="Y124" s="52"/>
-      <c r="Z124" s="52"/>
-      <c r="AA124" s="52"/>
-      <c r="AB124" s="53"/>
+      <c r="H124" s="49"/>
+      <c r="I124" s="50"/>
+      <c r="J124" s="50"/>
+      <c r="K124" s="50"/>
+      <c r="L124" s="50"/>
+      <c r="M124" s="50"/>
+      <c r="N124" s="50"/>
+      <c r="O124" s="50"/>
+      <c r="P124" s="50"/>
+      <c r="Q124" s="50"/>
+      <c r="R124" s="50"/>
+      <c r="S124" s="50"/>
+      <c r="T124" s="50"/>
+      <c r="U124" s="50"/>
+      <c r="V124" s="50"/>
+      <c r="W124" s="50"/>
+      <c r="X124" s="50"/>
+      <c r="Y124" s="50"/>
+      <c r="Z124" s="50"/>
+      <c r="AA124" s="50"/>
+      <c r="AB124" s="51"/>
       <c r="AC124" s="11"/>
     </row>
     <row r="125" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5588,27 +5617,27 @@
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
-      <c r="H125" s="51"/>
-      <c r="I125" s="52"/>
-      <c r="J125" s="52"/>
-      <c r="K125" s="52"/>
-      <c r="L125" s="52"/>
-      <c r="M125" s="52"/>
-      <c r="N125" s="52"/>
-      <c r="O125" s="52"/>
-      <c r="P125" s="52"/>
-      <c r="Q125" s="52"/>
-      <c r="R125" s="52"/>
-      <c r="S125" s="52"/>
-      <c r="T125" s="52"/>
-      <c r="U125" s="52"/>
-      <c r="V125" s="52"/>
-      <c r="W125" s="52"/>
-      <c r="X125" s="52"/>
-      <c r="Y125" s="52"/>
-      <c r="Z125" s="52"/>
-      <c r="AA125" s="52"/>
-      <c r="AB125" s="53"/>
+      <c r="H125" s="49"/>
+      <c r="I125" s="50"/>
+      <c r="J125" s="50"/>
+      <c r="K125" s="50"/>
+      <c r="L125" s="50"/>
+      <c r="M125" s="50"/>
+      <c r="N125" s="50"/>
+      <c r="O125" s="50"/>
+      <c r="P125" s="50"/>
+      <c r="Q125" s="50"/>
+      <c r="R125" s="50"/>
+      <c r="S125" s="50"/>
+      <c r="T125" s="50"/>
+      <c r="U125" s="50"/>
+      <c r="V125" s="50"/>
+      <c r="W125" s="50"/>
+      <c r="X125" s="50"/>
+      <c r="Y125" s="50"/>
+      <c r="Z125" s="50"/>
+      <c r="AA125" s="50"/>
+      <c r="AB125" s="51"/>
       <c r="AC125" s="11"/>
     </row>
     <row r="126" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5618,27 +5647,27 @@
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
-      <c r="H126" s="51"/>
-      <c r="I126" s="52"/>
-      <c r="J126" s="52"/>
-      <c r="K126" s="52"/>
-      <c r="L126" s="52"/>
-      <c r="M126" s="52"/>
-      <c r="N126" s="52"/>
-      <c r="O126" s="52"/>
-      <c r="P126" s="52"/>
-      <c r="Q126" s="52"/>
-      <c r="R126" s="52"/>
-      <c r="S126" s="52"/>
-      <c r="T126" s="52"/>
-      <c r="U126" s="52"/>
-      <c r="V126" s="52"/>
-      <c r="W126" s="52"/>
-      <c r="X126" s="52"/>
-      <c r="Y126" s="52"/>
-      <c r="Z126" s="52"/>
-      <c r="AA126" s="52"/>
-      <c r="AB126" s="53"/>
+      <c r="H126" s="49"/>
+      <c r="I126" s="50"/>
+      <c r="J126" s="50"/>
+      <c r="K126" s="50"/>
+      <c r="L126" s="50"/>
+      <c r="M126" s="50"/>
+      <c r="N126" s="50"/>
+      <c r="O126" s="50"/>
+      <c r="P126" s="50"/>
+      <c r="Q126" s="50"/>
+      <c r="R126" s="50"/>
+      <c r="S126" s="50"/>
+      <c r="T126" s="50"/>
+      <c r="U126" s="50"/>
+      <c r="V126" s="50"/>
+      <c r="W126" s="50"/>
+      <c r="X126" s="50"/>
+      <c r="Y126" s="50"/>
+      <c r="Z126" s="50"/>
+      <c r="AA126" s="50"/>
+      <c r="AB126" s="51"/>
       <c r="AC126" s="11"/>
     </row>
     <row r="127" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5648,27 +5677,27 @@
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
-      <c r="H127" s="51"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="52"/>
-      <c r="K127" s="52"/>
-      <c r="L127" s="52"/>
-      <c r="M127" s="52"/>
-      <c r="N127" s="52"/>
-      <c r="O127" s="52"/>
-      <c r="P127" s="52"/>
-      <c r="Q127" s="52"/>
-      <c r="R127" s="52"/>
-      <c r="S127" s="52"/>
-      <c r="T127" s="52"/>
-      <c r="U127" s="52"/>
-      <c r="V127" s="52"/>
-      <c r="W127" s="52"/>
-      <c r="X127" s="52"/>
-      <c r="Y127" s="52"/>
-      <c r="Z127" s="52"/>
-      <c r="AA127" s="52"/>
-      <c r="AB127" s="53"/>
+      <c r="H127" s="49"/>
+      <c r="I127" s="50"/>
+      <c r="J127" s="50"/>
+      <c r="K127" s="50"/>
+      <c r="L127" s="50"/>
+      <c r="M127" s="50"/>
+      <c r="N127" s="50"/>
+      <c r="O127" s="50"/>
+      <c r="P127" s="50"/>
+      <c r="Q127" s="50"/>
+      <c r="R127" s="50"/>
+      <c r="S127" s="50"/>
+      <c r="T127" s="50"/>
+      <c r="U127" s="50"/>
+      <c r="V127" s="50"/>
+      <c r="W127" s="50"/>
+      <c r="X127" s="50"/>
+      <c r="Y127" s="50"/>
+      <c r="Z127" s="50"/>
+      <c r="AA127" s="50"/>
+      <c r="AB127" s="51"/>
       <c r="AC127" s="11"/>
     </row>
     <row r="128" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5678,27 +5707,27 @@
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
-      <c r="H128" s="54"/>
-      <c r="I128" s="55"/>
-      <c r="J128" s="55"/>
-      <c r="K128" s="55"/>
-      <c r="L128" s="55"/>
-      <c r="M128" s="55"/>
-      <c r="N128" s="55"/>
-      <c r="O128" s="55"/>
-      <c r="P128" s="55"/>
-      <c r="Q128" s="55"/>
-      <c r="R128" s="55"/>
-      <c r="S128" s="55"/>
-      <c r="T128" s="55"/>
-      <c r="U128" s="55"/>
-      <c r="V128" s="55"/>
-      <c r="W128" s="55"/>
-      <c r="X128" s="55"/>
-      <c r="Y128" s="55"/>
-      <c r="Z128" s="55"/>
-      <c r="AA128" s="55"/>
-      <c r="AB128" s="56"/>
+      <c r="H128" s="52"/>
+      <c r="I128" s="53"/>
+      <c r="J128" s="53"/>
+      <c r="K128" s="53"/>
+      <c r="L128" s="53"/>
+      <c r="M128" s="53"/>
+      <c r="N128" s="53"/>
+      <c r="O128" s="53"/>
+      <c r="P128" s="53"/>
+      <c r="Q128" s="53"/>
+      <c r="R128" s="53"/>
+      <c r="S128" s="53"/>
+      <c r="T128" s="53"/>
+      <c r="U128" s="53"/>
+      <c r="V128" s="53"/>
+      <c r="W128" s="53"/>
+      <c r="X128" s="53"/>
+      <c r="Y128" s="53"/>
+      <c r="Z128" s="53"/>
+      <c r="AA128" s="53"/>
+      <c r="AB128" s="54"/>
       <c r="AC128" s="11"/>
     </row>
     <row r="129" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5740,27 +5769,27 @@
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
-      <c r="H130" s="48"/>
-      <c r="I130" s="49"/>
-      <c r="J130" s="49"/>
-      <c r="K130" s="49"/>
-      <c r="L130" s="49"/>
-      <c r="M130" s="49"/>
-      <c r="N130" s="49"/>
-      <c r="O130" s="49"/>
-      <c r="P130" s="49"/>
-      <c r="Q130" s="49"/>
-      <c r="R130" s="49"/>
-      <c r="S130" s="49"/>
-      <c r="T130" s="49"/>
-      <c r="U130" s="49"/>
-      <c r="V130" s="49"/>
-      <c r="W130" s="49"/>
-      <c r="X130" s="49"/>
-      <c r="Y130" s="49"/>
-      <c r="Z130" s="49"/>
-      <c r="AA130" s="49"/>
-      <c r="AB130" s="50"/>
+      <c r="H130" s="46"/>
+      <c r="I130" s="47"/>
+      <c r="J130" s="47"/>
+      <c r="K130" s="47"/>
+      <c r="L130" s="47"/>
+      <c r="M130" s="47"/>
+      <c r="N130" s="47"/>
+      <c r="O130" s="47"/>
+      <c r="P130" s="47"/>
+      <c r="Q130" s="47"/>
+      <c r="R130" s="47"/>
+      <c r="S130" s="47"/>
+      <c r="T130" s="47"/>
+      <c r="U130" s="47"/>
+      <c r="V130" s="47"/>
+      <c r="W130" s="47"/>
+      <c r="X130" s="47"/>
+      <c r="Y130" s="47"/>
+      <c r="Z130" s="47"/>
+      <c r="AA130" s="47"/>
+      <c r="AB130" s="48"/>
       <c r="AC130" s="11"/>
     </row>
     <row r="131" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5770,27 +5799,27 @@
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
-      <c r="H131" s="51"/>
-      <c r="I131" s="52"/>
-      <c r="J131" s="52"/>
-      <c r="K131" s="52"/>
-      <c r="L131" s="52"/>
-      <c r="M131" s="52"/>
-      <c r="N131" s="52"/>
-      <c r="O131" s="52"/>
-      <c r="P131" s="52"/>
-      <c r="Q131" s="52"/>
-      <c r="R131" s="52"/>
-      <c r="S131" s="52"/>
-      <c r="T131" s="52"/>
-      <c r="U131" s="52"/>
-      <c r="V131" s="52"/>
-      <c r="W131" s="52"/>
-      <c r="X131" s="52"/>
-      <c r="Y131" s="52"/>
-      <c r="Z131" s="52"/>
-      <c r="AA131" s="52"/>
-      <c r="AB131" s="53"/>
+      <c r="H131" s="49"/>
+      <c r="I131" s="50"/>
+      <c r="J131" s="50"/>
+      <c r="K131" s="50"/>
+      <c r="L131" s="50"/>
+      <c r="M131" s="50"/>
+      <c r="N131" s="50"/>
+      <c r="O131" s="50"/>
+      <c r="P131" s="50"/>
+      <c r="Q131" s="50"/>
+      <c r="R131" s="50"/>
+      <c r="S131" s="50"/>
+      <c r="T131" s="50"/>
+      <c r="U131" s="50"/>
+      <c r="V131" s="50"/>
+      <c r="W131" s="50"/>
+      <c r="X131" s="50"/>
+      <c r="Y131" s="50"/>
+      <c r="Z131" s="50"/>
+      <c r="AA131" s="50"/>
+      <c r="AB131" s="51"/>
       <c r="AC131" s="11"/>
     </row>
     <row r="132" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5800,27 +5829,27 @@
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
-      <c r="H132" s="51"/>
-      <c r="I132" s="52"/>
-      <c r="J132" s="52"/>
-      <c r="K132" s="52"/>
-      <c r="L132" s="52"/>
-      <c r="M132" s="52"/>
-      <c r="N132" s="52"/>
-      <c r="O132" s="52"/>
-      <c r="P132" s="52"/>
-      <c r="Q132" s="52"/>
-      <c r="R132" s="52"/>
-      <c r="S132" s="52"/>
-      <c r="T132" s="52"/>
-      <c r="U132" s="52"/>
-      <c r="V132" s="52"/>
-      <c r="W132" s="52"/>
-      <c r="X132" s="52"/>
-      <c r="Y132" s="52"/>
-      <c r="Z132" s="52"/>
-      <c r="AA132" s="52"/>
-      <c r="AB132" s="53"/>
+      <c r="H132" s="49"/>
+      <c r="I132" s="50"/>
+      <c r="J132" s="50"/>
+      <c r="K132" s="50"/>
+      <c r="L132" s="50"/>
+      <c r="M132" s="50"/>
+      <c r="N132" s="50"/>
+      <c r="O132" s="50"/>
+      <c r="P132" s="50"/>
+      <c r="Q132" s="50"/>
+      <c r="R132" s="50"/>
+      <c r="S132" s="50"/>
+      <c r="T132" s="50"/>
+      <c r="U132" s="50"/>
+      <c r="V132" s="50"/>
+      <c r="W132" s="50"/>
+      <c r="X132" s="50"/>
+      <c r="Y132" s="50"/>
+      <c r="Z132" s="50"/>
+      <c r="AA132" s="50"/>
+      <c r="AB132" s="51"/>
       <c r="AC132" s="11"/>
     </row>
     <row r="133" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5830,27 +5859,27 @@
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="51"/>
-      <c r="I133" s="52"/>
-      <c r="J133" s="52"/>
-      <c r="K133" s="52"/>
-      <c r="L133" s="52"/>
-      <c r="M133" s="52"/>
-      <c r="N133" s="52"/>
-      <c r="O133" s="52"/>
-      <c r="P133" s="52"/>
-      <c r="Q133" s="52"/>
-      <c r="R133" s="52"/>
-      <c r="S133" s="52"/>
-      <c r="T133" s="52"/>
-      <c r="U133" s="52"/>
-      <c r="V133" s="52"/>
-      <c r="W133" s="52"/>
-      <c r="X133" s="52"/>
-      <c r="Y133" s="52"/>
-      <c r="Z133" s="52"/>
-      <c r="AA133" s="52"/>
-      <c r="AB133" s="53"/>
+      <c r="H133" s="49"/>
+      <c r="I133" s="50"/>
+      <c r="J133" s="50"/>
+      <c r="K133" s="50"/>
+      <c r="L133" s="50"/>
+      <c r="M133" s="50"/>
+      <c r="N133" s="50"/>
+      <c r="O133" s="50"/>
+      <c r="P133" s="50"/>
+      <c r="Q133" s="50"/>
+      <c r="R133" s="50"/>
+      <c r="S133" s="50"/>
+      <c r="T133" s="50"/>
+      <c r="U133" s="50"/>
+      <c r="V133" s="50"/>
+      <c r="W133" s="50"/>
+      <c r="X133" s="50"/>
+      <c r="Y133" s="50"/>
+      <c r="Z133" s="50"/>
+      <c r="AA133" s="50"/>
+      <c r="AB133" s="51"/>
       <c r="AC133" s="11"/>
     </row>
     <row r="134" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5860,27 +5889,27 @@
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="51"/>
-      <c r="I134" s="52"/>
-      <c r="J134" s="52"/>
-      <c r="K134" s="52"/>
-      <c r="L134" s="52"/>
-      <c r="M134" s="52"/>
-      <c r="N134" s="52"/>
-      <c r="O134" s="52"/>
-      <c r="P134" s="52"/>
-      <c r="Q134" s="52"/>
-      <c r="R134" s="52"/>
-      <c r="S134" s="52"/>
-      <c r="T134" s="52"/>
-      <c r="U134" s="52"/>
-      <c r="V134" s="52"/>
-      <c r="W134" s="52"/>
-      <c r="X134" s="52"/>
-      <c r="Y134" s="52"/>
-      <c r="Z134" s="52"/>
-      <c r="AA134" s="52"/>
-      <c r="AB134" s="53"/>
+      <c r="H134" s="49"/>
+      <c r="I134" s="50"/>
+      <c r="J134" s="50"/>
+      <c r="K134" s="50"/>
+      <c r="L134" s="50"/>
+      <c r="M134" s="50"/>
+      <c r="N134" s="50"/>
+      <c r="O134" s="50"/>
+      <c r="P134" s="50"/>
+      <c r="Q134" s="50"/>
+      <c r="R134" s="50"/>
+      <c r="S134" s="50"/>
+      <c r="T134" s="50"/>
+      <c r="U134" s="50"/>
+      <c r="V134" s="50"/>
+      <c r="W134" s="50"/>
+      <c r="X134" s="50"/>
+      <c r="Y134" s="50"/>
+      <c r="Z134" s="50"/>
+      <c r="AA134" s="50"/>
+      <c r="AB134" s="51"/>
       <c r="AC134" s="11"/>
     </row>
     <row r="135" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5890,27 +5919,27 @@
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="51"/>
-      <c r="I135" s="52"/>
-      <c r="J135" s="52"/>
-      <c r="K135" s="52"/>
-      <c r="L135" s="52"/>
-      <c r="M135" s="52"/>
-      <c r="N135" s="52"/>
-      <c r="O135" s="52"/>
-      <c r="P135" s="52"/>
-      <c r="Q135" s="52"/>
-      <c r="R135" s="52"/>
-      <c r="S135" s="52"/>
-      <c r="T135" s="52"/>
-      <c r="U135" s="52"/>
-      <c r="V135" s="52"/>
-      <c r="W135" s="52"/>
-      <c r="X135" s="52"/>
-      <c r="Y135" s="52"/>
-      <c r="Z135" s="52"/>
-      <c r="AA135" s="52"/>
-      <c r="AB135" s="53"/>
+      <c r="H135" s="49"/>
+      <c r="I135" s="50"/>
+      <c r="J135" s="50"/>
+      <c r="K135" s="50"/>
+      <c r="L135" s="50"/>
+      <c r="M135" s="50"/>
+      <c r="N135" s="50"/>
+      <c r="O135" s="50"/>
+      <c r="P135" s="50"/>
+      <c r="Q135" s="50"/>
+      <c r="R135" s="50"/>
+      <c r="S135" s="50"/>
+      <c r="T135" s="50"/>
+      <c r="U135" s="50"/>
+      <c r="V135" s="50"/>
+      <c r="W135" s="50"/>
+      <c r="X135" s="50"/>
+      <c r="Y135" s="50"/>
+      <c r="Z135" s="50"/>
+      <c r="AA135" s="50"/>
+      <c r="AB135" s="51"/>
       <c r="AC135" s="11"/>
     </row>
     <row r="136" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5920,27 +5949,27 @@
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="54"/>
-      <c r="I136" s="55"/>
-      <c r="J136" s="55"/>
-      <c r="K136" s="55"/>
-      <c r="L136" s="55"/>
-      <c r="M136" s="55"/>
-      <c r="N136" s="55"/>
-      <c r="O136" s="55"/>
-      <c r="P136" s="55"/>
-      <c r="Q136" s="55"/>
-      <c r="R136" s="55"/>
-      <c r="S136" s="55"/>
-      <c r="T136" s="55"/>
-      <c r="U136" s="55"/>
-      <c r="V136" s="55"/>
-      <c r="W136" s="55"/>
-      <c r="X136" s="55"/>
-      <c r="Y136" s="55"/>
-      <c r="Z136" s="55"/>
-      <c r="AA136" s="55"/>
-      <c r="AB136" s="56"/>
+      <c r="H136" s="52"/>
+      <c r="I136" s="53"/>
+      <c r="J136" s="53"/>
+      <c r="K136" s="53"/>
+      <c r="L136" s="53"/>
+      <c r="M136" s="53"/>
+      <c r="N136" s="53"/>
+      <c r="O136" s="53"/>
+      <c r="P136" s="53"/>
+      <c r="Q136" s="53"/>
+      <c r="R136" s="53"/>
+      <c r="S136" s="53"/>
+      <c r="T136" s="53"/>
+      <c r="U136" s="53"/>
+      <c r="V136" s="53"/>
+      <c r="W136" s="53"/>
+      <c r="X136" s="53"/>
+      <c r="Y136" s="53"/>
+      <c r="Z136" s="53"/>
+      <c r="AA136" s="53"/>
+      <c r="AB136" s="54"/>
       <c r="AC136" s="11"/>
     </row>
     <row r="137" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6048,27 +6077,27 @@
         <v>2</v>
       </c>
       <c r="G141" s="6"/>
-      <c r="H141" s="48"/>
-      <c r="I141" s="49"/>
-      <c r="J141" s="49"/>
-      <c r="K141" s="49"/>
-      <c r="L141" s="49"/>
-      <c r="M141" s="49"/>
-      <c r="N141" s="49"/>
-      <c r="O141" s="49"/>
-      <c r="P141" s="49"/>
-      <c r="Q141" s="49"/>
-      <c r="R141" s="49"/>
-      <c r="S141" s="49"/>
-      <c r="T141" s="49"/>
-      <c r="U141" s="49"/>
-      <c r="V141" s="49"/>
-      <c r="W141" s="49"/>
-      <c r="X141" s="49"/>
-      <c r="Y141" s="49"/>
-      <c r="Z141" s="49"/>
-      <c r="AA141" s="49"/>
-      <c r="AB141" s="50"/>
+      <c r="H141" s="46"/>
+      <c r="I141" s="47"/>
+      <c r="J141" s="47"/>
+      <c r="K141" s="47"/>
+      <c r="L141" s="47"/>
+      <c r="M141" s="47"/>
+      <c r="N141" s="47"/>
+      <c r="O141" s="47"/>
+      <c r="P141" s="47"/>
+      <c r="Q141" s="47"/>
+      <c r="R141" s="47"/>
+      <c r="S141" s="47"/>
+      <c r="T141" s="47"/>
+      <c r="U141" s="47"/>
+      <c r="V141" s="47"/>
+      <c r="W141" s="47"/>
+      <c r="X141" s="47"/>
+      <c r="Y141" s="47"/>
+      <c r="Z141" s="47"/>
+      <c r="AA141" s="47"/>
+      <c r="AB141" s="48"/>
       <c r="AC141" s="11"/>
     </row>
     <row r="142" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6078,27 +6107,27 @@
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
-      <c r="H142" s="51"/>
-      <c r="I142" s="52"/>
-      <c r="J142" s="52"/>
-      <c r="K142" s="52"/>
-      <c r="L142" s="52"/>
-      <c r="M142" s="52"/>
-      <c r="N142" s="52"/>
-      <c r="O142" s="52"/>
-      <c r="P142" s="52"/>
-      <c r="Q142" s="52"/>
-      <c r="R142" s="52"/>
-      <c r="S142" s="52"/>
-      <c r="T142" s="52"/>
-      <c r="U142" s="52"/>
-      <c r="V142" s="52"/>
-      <c r="W142" s="52"/>
-      <c r="X142" s="52"/>
-      <c r="Y142" s="52"/>
-      <c r="Z142" s="52"/>
-      <c r="AA142" s="52"/>
-      <c r="AB142" s="53"/>
+      <c r="H142" s="49"/>
+      <c r="I142" s="50"/>
+      <c r="J142" s="50"/>
+      <c r="K142" s="50"/>
+      <c r="L142" s="50"/>
+      <c r="M142" s="50"/>
+      <c r="N142" s="50"/>
+      <c r="O142" s="50"/>
+      <c r="P142" s="50"/>
+      <c r="Q142" s="50"/>
+      <c r="R142" s="50"/>
+      <c r="S142" s="50"/>
+      <c r="T142" s="50"/>
+      <c r="U142" s="50"/>
+      <c r="V142" s="50"/>
+      <c r="W142" s="50"/>
+      <c r="X142" s="50"/>
+      <c r="Y142" s="50"/>
+      <c r="Z142" s="50"/>
+      <c r="AA142" s="50"/>
+      <c r="AB142" s="51"/>
       <c r="AC142" s="11"/>
     </row>
     <row r="143" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6108,27 +6137,27 @@
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
-      <c r="H143" s="51"/>
-      <c r="I143" s="52"/>
-      <c r="J143" s="52"/>
-      <c r="K143" s="52"/>
-      <c r="L143" s="52"/>
-      <c r="M143" s="52"/>
-      <c r="N143" s="52"/>
-      <c r="O143" s="52"/>
-      <c r="P143" s="52"/>
-      <c r="Q143" s="52"/>
-      <c r="R143" s="52"/>
-      <c r="S143" s="52"/>
-      <c r="T143" s="52"/>
-      <c r="U143" s="52"/>
-      <c r="V143" s="52"/>
-      <c r="W143" s="52"/>
-      <c r="X143" s="52"/>
-      <c r="Y143" s="52"/>
-      <c r="Z143" s="52"/>
-      <c r="AA143" s="52"/>
-      <c r="AB143" s="53"/>
+      <c r="H143" s="49"/>
+      <c r="I143" s="50"/>
+      <c r="J143" s="50"/>
+      <c r="K143" s="50"/>
+      <c r="L143" s="50"/>
+      <c r="M143" s="50"/>
+      <c r="N143" s="50"/>
+      <c r="O143" s="50"/>
+      <c r="P143" s="50"/>
+      <c r="Q143" s="50"/>
+      <c r="R143" s="50"/>
+      <c r="S143" s="50"/>
+      <c r="T143" s="50"/>
+      <c r="U143" s="50"/>
+      <c r="V143" s="50"/>
+      <c r="W143" s="50"/>
+      <c r="X143" s="50"/>
+      <c r="Y143" s="50"/>
+      <c r="Z143" s="50"/>
+      <c r="AA143" s="50"/>
+      <c r="AB143" s="51"/>
       <c r="AC143" s="11"/>
     </row>
     <row r="144" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6138,27 +6167,27 @@
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
-      <c r="H144" s="51"/>
-      <c r="I144" s="52"/>
-      <c r="J144" s="52"/>
-      <c r="K144" s="52"/>
-      <c r="L144" s="52"/>
-      <c r="M144" s="52"/>
-      <c r="N144" s="52"/>
-      <c r="O144" s="52"/>
-      <c r="P144" s="52"/>
-      <c r="Q144" s="52"/>
-      <c r="R144" s="52"/>
-      <c r="S144" s="52"/>
-      <c r="T144" s="52"/>
-      <c r="U144" s="52"/>
-      <c r="V144" s="52"/>
-      <c r="W144" s="52"/>
-      <c r="X144" s="52"/>
-      <c r="Y144" s="52"/>
-      <c r="Z144" s="52"/>
-      <c r="AA144" s="52"/>
-      <c r="AB144" s="53"/>
+      <c r="H144" s="49"/>
+      <c r="I144" s="50"/>
+      <c r="J144" s="50"/>
+      <c r="K144" s="50"/>
+      <c r="L144" s="50"/>
+      <c r="M144" s="50"/>
+      <c r="N144" s="50"/>
+      <c r="O144" s="50"/>
+      <c r="P144" s="50"/>
+      <c r="Q144" s="50"/>
+      <c r="R144" s="50"/>
+      <c r="S144" s="50"/>
+      <c r="T144" s="50"/>
+      <c r="U144" s="50"/>
+      <c r="V144" s="50"/>
+      <c r="W144" s="50"/>
+      <c r="X144" s="50"/>
+      <c r="Y144" s="50"/>
+      <c r="Z144" s="50"/>
+      <c r="AA144" s="50"/>
+      <c r="AB144" s="51"/>
       <c r="AC144" s="11"/>
     </row>
     <row r="145" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6168,27 +6197,27 @@
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
-      <c r="H145" s="51"/>
-      <c r="I145" s="52"/>
-      <c r="J145" s="52"/>
-      <c r="K145" s="52"/>
-      <c r="L145" s="52"/>
-      <c r="M145" s="52"/>
-      <c r="N145" s="52"/>
-      <c r="O145" s="52"/>
-      <c r="P145" s="52"/>
-      <c r="Q145" s="52"/>
-      <c r="R145" s="52"/>
-      <c r="S145" s="52"/>
-      <c r="T145" s="52"/>
-      <c r="U145" s="52"/>
-      <c r="V145" s="52"/>
-      <c r="W145" s="52"/>
-      <c r="X145" s="52"/>
-      <c r="Y145" s="52"/>
-      <c r="Z145" s="52"/>
-      <c r="AA145" s="52"/>
-      <c r="AB145" s="53"/>
+      <c r="H145" s="49"/>
+      <c r="I145" s="50"/>
+      <c r="J145" s="50"/>
+      <c r="K145" s="50"/>
+      <c r="L145" s="50"/>
+      <c r="M145" s="50"/>
+      <c r="N145" s="50"/>
+      <c r="O145" s="50"/>
+      <c r="P145" s="50"/>
+      <c r="Q145" s="50"/>
+      <c r="R145" s="50"/>
+      <c r="S145" s="50"/>
+      <c r="T145" s="50"/>
+      <c r="U145" s="50"/>
+      <c r="V145" s="50"/>
+      <c r="W145" s="50"/>
+      <c r="X145" s="50"/>
+      <c r="Y145" s="50"/>
+      <c r="Z145" s="50"/>
+      <c r="AA145" s="50"/>
+      <c r="AB145" s="51"/>
       <c r="AC145" s="11"/>
     </row>
     <row r="146" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6198,27 +6227,27 @@
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
-      <c r="H146" s="51"/>
-      <c r="I146" s="52"/>
-      <c r="J146" s="52"/>
-      <c r="K146" s="52"/>
-      <c r="L146" s="52"/>
-      <c r="M146" s="52"/>
-      <c r="N146" s="52"/>
-      <c r="O146" s="52"/>
-      <c r="P146" s="52"/>
-      <c r="Q146" s="52"/>
-      <c r="R146" s="52"/>
-      <c r="S146" s="52"/>
-      <c r="T146" s="52"/>
-      <c r="U146" s="52"/>
-      <c r="V146" s="52"/>
-      <c r="W146" s="52"/>
-      <c r="X146" s="52"/>
-      <c r="Y146" s="52"/>
-      <c r="Z146" s="52"/>
-      <c r="AA146" s="52"/>
-      <c r="AB146" s="53"/>
+      <c r="H146" s="49"/>
+      <c r="I146" s="50"/>
+      <c r="J146" s="50"/>
+      <c r="K146" s="50"/>
+      <c r="L146" s="50"/>
+      <c r="M146" s="50"/>
+      <c r="N146" s="50"/>
+      <c r="O146" s="50"/>
+      <c r="P146" s="50"/>
+      <c r="Q146" s="50"/>
+      <c r="R146" s="50"/>
+      <c r="S146" s="50"/>
+      <c r="T146" s="50"/>
+      <c r="U146" s="50"/>
+      <c r="V146" s="50"/>
+      <c r="W146" s="50"/>
+      <c r="X146" s="50"/>
+      <c r="Y146" s="50"/>
+      <c r="Z146" s="50"/>
+      <c r="AA146" s="50"/>
+      <c r="AB146" s="51"/>
       <c r="AC146" s="11"/>
     </row>
     <row r="147" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6228,27 +6257,27 @@
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
-      <c r="H147" s="54"/>
-      <c r="I147" s="55"/>
-      <c r="J147" s="55"/>
-      <c r="K147" s="55"/>
-      <c r="L147" s="55"/>
-      <c r="M147" s="55"/>
-      <c r="N147" s="55"/>
-      <c r="O147" s="55"/>
-      <c r="P147" s="55"/>
-      <c r="Q147" s="55"/>
-      <c r="R147" s="55"/>
-      <c r="S147" s="55"/>
-      <c r="T147" s="55"/>
-      <c r="U147" s="55"/>
-      <c r="V147" s="55"/>
-      <c r="W147" s="55"/>
-      <c r="X147" s="55"/>
-      <c r="Y147" s="55"/>
-      <c r="Z147" s="55"/>
-      <c r="AA147" s="55"/>
-      <c r="AB147" s="56"/>
+      <c r="H147" s="52"/>
+      <c r="I147" s="53"/>
+      <c r="J147" s="53"/>
+      <c r="K147" s="53"/>
+      <c r="L147" s="53"/>
+      <c r="M147" s="53"/>
+      <c r="N147" s="53"/>
+      <c r="O147" s="53"/>
+      <c r="P147" s="53"/>
+      <c r="Q147" s="53"/>
+      <c r="R147" s="53"/>
+      <c r="S147" s="53"/>
+      <c r="T147" s="53"/>
+      <c r="U147" s="53"/>
+      <c r="V147" s="53"/>
+      <c r="W147" s="53"/>
+      <c r="X147" s="53"/>
+      <c r="Y147" s="53"/>
+      <c r="Z147" s="53"/>
+      <c r="AA147" s="53"/>
+      <c r="AB147" s="54"/>
       <c r="AC147" s="11"/>
     </row>
     <row r="148" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6290,27 +6319,27 @@
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
-      <c r="H149" s="48"/>
-      <c r="I149" s="49"/>
-      <c r="J149" s="49"/>
-      <c r="K149" s="49"/>
-      <c r="L149" s="49"/>
-      <c r="M149" s="49"/>
-      <c r="N149" s="49"/>
-      <c r="O149" s="49"/>
-      <c r="P149" s="49"/>
-      <c r="Q149" s="49"/>
-      <c r="R149" s="49"/>
-      <c r="S149" s="49"/>
-      <c r="T149" s="49"/>
-      <c r="U149" s="49"/>
-      <c r="V149" s="49"/>
-      <c r="W149" s="49"/>
-      <c r="X149" s="49"/>
-      <c r="Y149" s="49"/>
-      <c r="Z149" s="49"/>
-      <c r="AA149" s="49"/>
-      <c r="AB149" s="50"/>
+      <c r="H149" s="46"/>
+      <c r="I149" s="47"/>
+      <c r="J149" s="47"/>
+      <c r="K149" s="47"/>
+      <c r="L149" s="47"/>
+      <c r="M149" s="47"/>
+      <c r="N149" s="47"/>
+      <c r="O149" s="47"/>
+      <c r="P149" s="47"/>
+      <c r="Q149" s="47"/>
+      <c r="R149" s="47"/>
+      <c r="S149" s="47"/>
+      <c r="T149" s="47"/>
+      <c r="U149" s="47"/>
+      <c r="V149" s="47"/>
+      <c r="W149" s="47"/>
+      <c r="X149" s="47"/>
+      <c r="Y149" s="47"/>
+      <c r="Z149" s="47"/>
+      <c r="AA149" s="47"/>
+      <c r="AB149" s="48"/>
       <c r="AC149" s="11"/>
     </row>
     <row r="150" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6320,27 +6349,27 @@
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
-      <c r="H150" s="51"/>
-      <c r="I150" s="52"/>
-      <c r="J150" s="52"/>
-      <c r="K150" s="52"/>
-      <c r="L150" s="52"/>
-      <c r="M150" s="52"/>
-      <c r="N150" s="52"/>
-      <c r="O150" s="52"/>
-      <c r="P150" s="52"/>
-      <c r="Q150" s="52"/>
-      <c r="R150" s="52"/>
-      <c r="S150" s="52"/>
-      <c r="T150" s="52"/>
-      <c r="U150" s="52"/>
-      <c r="V150" s="52"/>
-      <c r="W150" s="52"/>
-      <c r="X150" s="52"/>
-      <c r="Y150" s="52"/>
-      <c r="Z150" s="52"/>
-      <c r="AA150" s="52"/>
-      <c r="AB150" s="53"/>
+      <c r="H150" s="49"/>
+      <c r="I150" s="50"/>
+      <c r="J150" s="50"/>
+      <c r="K150" s="50"/>
+      <c r="L150" s="50"/>
+      <c r="M150" s="50"/>
+      <c r="N150" s="50"/>
+      <c r="O150" s="50"/>
+      <c r="P150" s="50"/>
+      <c r="Q150" s="50"/>
+      <c r="R150" s="50"/>
+      <c r="S150" s="50"/>
+      <c r="T150" s="50"/>
+      <c r="U150" s="50"/>
+      <c r="V150" s="50"/>
+      <c r="W150" s="50"/>
+      <c r="X150" s="50"/>
+      <c r="Y150" s="50"/>
+      <c r="Z150" s="50"/>
+      <c r="AA150" s="50"/>
+      <c r="AB150" s="51"/>
       <c r="AC150" s="11"/>
     </row>
     <row r="151" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6350,27 +6379,27 @@
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
-      <c r="H151" s="51"/>
-      <c r="I151" s="52"/>
-      <c r="J151" s="52"/>
-      <c r="K151" s="52"/>
-      <c r="L151" s="52"/>
-      <c r="M151" s="52"/>
-      <c r="N151" s="52"/>
-      <c r="O151" s="52"/>
-      <c r="P151" s="52"/>
-      <c r="Q151" s="52"/>
-      <c r="R151" s="52"/>
-      <c r="S151" s="52"/>
-      <c r="T151" s="52"/>
-      <c r="U151" s="52"/>
-      <c r="V151" s="52"/>
-      <c r="W151" s="52"/>
-      <c r="X151" s="52"/>
-      <c r="Y151" s="52"/>
-      <c r="Z151" s="52"/>
-      <c r="AA151" s="52"/>
-      <c r="AB151" s="53"/>
+      <c r="H151" s="49"/>
+      <c r="I151" s="50"/>
+      <c r="J151" s="50"/>
+      <c r="K151" s="50"/>
+      <c r="L151" s="50"/>
+      <c r="M151" s="50"/>
+      <c r="N151" s="50"/>
+      <c r="O151" s="50"/>
+      <c r="P151" s="50"/>
+      <c r="Q151" s="50"/>
+      <c r="R151" s="50"/>
+      <c r="S151" s="50"/>
+      <c r="T151" s="50"/>
+      <c r="U151" s="50"/>
+      <c r="V151" s="50"/>
+      <c r="W151" s="50"/>
+      <c r="X151" s="50"/>
+      <c r="Y151" s="50"/>
+      <c r="Z151" s="50"/>
+      <c r="AA151" s="50"/>
+      <c r="AB151" s="51"/>
       <c r="AC151" s="11"/>
     </row>
     <row r="152" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6380,27 +6409,27 @@
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
-      <c r="H152" s="51"/>
-      <c r="I152" s="52"/>
-      <c r="J152" s="52"/>
-      <c r="K152" s="52"/>
-      <c r="L152" s="52"/>
-      <c r="M152" s="52"/>
-      <c r="N152" s="52"/>
-      <c r="O152" s="52"/>
-      <c r="P152" s="52"/>
-      <c r="Q152" s="52"/>
-      <c r="R152" s="52"/>
-      <c r="S152" s="52"/>
-      <c r="T152" s="52"/>
-      <c r="U152" s="52"/>
-      <c r="V152" s="52"/>
-      <c r="W152" s="52"/>
-      <c r="X152" s="52"/>
-      <c r="Y152" s="52"/>
-      <c r="Z152" s="52"/>
-      <c r="AA152" s="52"/>
-      <c r="AB152" s="53"/>
+      <c r="H152" s="49"/>
+      <c r="I152" s="50"/>
+      <c r="J152" s="50"/>
+      <c r="K152" s="50"/>
+      <c r="L152" s="50"/>
+      <c r="M152" s="50"/>
+      <c r="N152" s="50"/>
+      <c r="O152" s="50"/>
+      <c r="P152" s="50"/>
+      <c r="Q152" s="50"/>
+      <c r="R152" s="50"/>
+      <c r="S152" s="50"/>
+      <c r="T152" s="50"/>
+      <c r="U152" s="50"/>
+      <c r="V152" s="50"/>
+      <c r="W152" s="50"/>
+      <c r="X152" s="50"/>
+      <c r="Y152" s="50"/>
+      <c r="Z152" s="50"/>
+      <c r="AA152" s="50"/>
+      <c r="AB152" s="51"/>
       <c r="AC152" s="11"/>
     </row>
     <row r="153" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6410,27 +6439,27 @@
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
-      <c r="H153" s="51"/>
-      <c r="I153" s="52"/>
-      <c r="J153" s="52"/>
-      <c r="K153" s="52"/>
-      <c r="L153" s="52"/>
-      <c r="M153" s="52"/>
-      <c r="N153" s="52"/>
-      <c r="O153" s="52"/>
-      <c r="P153" s="52"/>
-      <c r="Q153" s="52"/>
-      <c r="R153" s="52"/>
-      <c r="S153" s="52"/>
-      <c r="T153" s="52"/>
-      <c r="U153" s="52"/>
-      <c r="V153" s="52"/>
-      <c r="W153" s="52"/>
-      <c r="X153" s="52"/>
-      <c r="Y153" s="52"/>
-      <c r="Z153" s="52"/>
-      <c r="AA153" s="52"/>
-      <c r="AB153" s="53"/>
+      <c r="H153" s="49"/>
+      <c r="I153" s="50"/>
+      <c r="J153" s="50"/>
+      <c r="K153" s="50"/>
+      <c r="L153" s="50"/>
+      <c r="M153" s="50"/>
+      <c r="N153" s="50"/>
+      <c r="O153" s="50"/>
+      <c r="P153" s="50"/>
+      <c r="Q153" s="50"/>
+      <c r="R153" s="50"/>
+      <c r="S153" s="50"/>
+      <c r="T153" s="50"/>
+      <c r="U153" s="50"/>
+      <c r="V153" s="50"/>
+      <c r="W153" s="50"/>
+      <c r="X153" s="50"/>
+      <c r="Y153" s="50"/>
+      <c r="Z153" s="50"/>
+      <c r="AA153" s="50"/>
+      <c r="AB153" s="51"/>
       <c r="AC153" s="11"/>
     </row>
     <row r="154" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6440,27 +6469,27 @@
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
-      <c r="H154" s="51"/>
-      <c r="I154" s="52"/>
-      <c r="J154" s="52"/>
-      <c r="K154" s="52"/>
-      <c r="L154" s="52"/>
-      <c r="M154" s="52"/>
-      <c r="N154" s="52"/>
-      <c r="O154" s="52"/>
-      <c r="P154" s="52"/>
-      <c r="Q154" s="52"/>
-      <c r="R154" s="52"/>
-      <c r="S154" s="52"/>
-      <c r="T154" s="52"/>
-      <c r="U154" s="52"/>
-      <c r="V154" s="52"/>
-      <c r="W154" s="52"/>
-      <c r="X154" s="52"/>
-      <c r="Y154" s="52"/>
-      <c r="Z154" s="52"/>
-      <c r="AA154" s="52"/>
-      <c r="AB154" s="53"/>
+      <c r="H154" s="49"/>
+      <c r="I154" s="50"/>
+      <c r="J154" s="50"/>
+      <c r="K154" s="50"/>
+      <c r="L154" s="50"/>
+      <c r="M154" s="50"/>
+      <c r="N154" s="50"/>
+      <c r="O154" s="50"/>
+      <c r="P154" s="50"/>
+      <c r="Q154" s="50"/>
+      <c r="R154" s="50"/>
+      <c r="S154" s="50"/>
+      <c r="T154" s="50"/>
+      <c r="U154" s="50"/>
+      <c r="V154" s="50"/>
+      <c r="W154" s="50"/>
+      <c r="X154" s="50"/>
+      <c r="Y154" s="50"/>
+      <c r="Z154" s="50"/>
+      <c r="AA154" s="50"/>
+      <c r="AB154" s="51"/>
       <c r="AC154" s="11"/>
     </row>
     <row r="155" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6470,27 +6499,27 @@
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
-      <c r="H155" s="54"/>
-      <c r="I155" s="55"/>
-      <c r="J155" s="55"/>
-      <c r="K155" s="55"/>
-      <c r="L155" s="55"/>
-      <c r="M155" s="55"/>
-      <c r="N155" s="55"/>
-      <c r="O155" s="55"/>
-      <c r="P155" s="55"/>
-      <c r="Q155" s="55"/>
-      <c r="R155" s="55"/>
-      <c r="S155" s="55"/>
-      <c r="T155" s="55"/>
-      <c r="U155" s="55"/>
-      <c r="V155" s="55"/>
-      <c r="W155" s="55"/>
-      <c r="X155" s="55"/>
-      <c r="Y155" s="55"/>
-      <c r="Z155" s="55"/>
-      <c r="AA155" s="55"/>
-      <c r="AB155" s="56"/>
+      <c r="H155" s="52"/>
+      <c r="I155" s="53"/>
+      <c r="J155" s="53"/>
+      <c r="K155" s="53"/>
+      <c r="L155" s="53"/>
+      <c r="M155" s="53"/>
+      <c r="N155" s="53"/>
+      <c r="O155" s="53"/>
+      <c r="P155" s="53"/>
+      <c r="Q155" s="53"/>
+      <c r="R155" s="53"/>
+      <c r="S155" s="53"/>
+      <c r="T155" s="53"/>
+      <c r="U155" s="53"/>
+      <c r="V155" s="53"/>
+      <c r="W155" s="53"/>
+      <c r="X155" s="53"/>
+      <c r="Y155" s="53"/>
+      <c r="Z155" s="53"/>
+      <c r="AA155" s="53"/>
+      <c r="AB155" s="54"/>
       <c r="AC155" s="11"/>
     </row>
     <row r="156" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6598,27 +6627,27 @@
         <v>2</v>
       </c>
       <c r="G160" s="6"/>
-      <c r="H160" s="48"/>
-      <c r="I160" s="49"/>
-      <c r="J160" s="49"/>
-      <c r="K160" s="49"/>
-      <c r="L160" s="49"/>
-      <c r="M160" s="49"/>
-      <c r="N160" s="49"/>
-      <c r="O160" s="49"/>
-      <c r="P160" s="49"/>
-      <c r="Q160" s="49"/>
-      <c r="R160" s="49"/>
-      <c r="S160" s="49"/>
-      <c r="T160" s="49"/>
-      <c r="U160" s="49"/>
-      <c r="V160" s="49"/>
-      <c r="W160" s="49"/>
-      <c r="X160" s="49"/>
-      <c r="Y160" s="49"/>
-      <c r="Z160" s="49"/>
-      <c r="AA160" s="49"/>
-      <c r="AB160" s="50"/>
+      <c r="H160" s="46"/>
+      <c r="I160" s="47"/>
+      <c r="J160" s="47"/>
+      <c r="K160" s="47"/>
+      <c r="L160" s="47"/>
+      <c r="M160" s="47"/>
+      <c r="N160" s="47"/>
+      <c r="O160" s="47"/>
+      <c r="P160" s="47"/>
+      <c r="Q160" s="47"/>
+      <c r="R160" s="47"/>
+      <c r="S160" s="47"/>
+      <c r="T160" s="47"/>
+      <c r="U160" s="47"/>
+      <c r="V160" s="47"/>
+      <c r="W160" s="47"/>
+      <c r="X160" s="47"/>
+      <c r="Y160" s="47"/>
+      <c r="Z160" s="47"/>
+      <c r="AA160" s="47"/>
+      <c r="AB160" s="48"/>
       <c r="AC160" s="11"/>
     </row>
     <row r="161" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6628,27 +6657,27 @@
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
-      <c r="H161" s="51"/>
-      <c r="I161" s="52"/>
-      <c r="J161" s="52"/>
-      <c r="K161" s="52"/>
-      <c r="L161" s="52"/>
-      <c r="M161" s="52"/>
-      <c r="N161" s="52"/>
-      <c r="O161" s="52"/>
-      <c r="P161" s="52"/>
-      <c r="Q161" s="52"/>
-      <c r="R161" s="52"/>
-      <c r="S161" s="52"/>
-      <c r="T161" s="52"/>
-      <c r="U161" s="52"/>
-      <c r="V161" s="52"/>
-      <c r="W161" s="52"/>
-      <c r="X161" s="52"/>
-      <c r="Y161" s="52"/>
-      <c r="Z161" s="52"/>
-      <c r="AA161" s="52"/>
-      <c r="AB161" s="53"/>
+      <c r="H161" s="49"/>
+      <c r="I161" s="50"/>
+      <c r="J161" s="50"/>
+      <c r="K161" s="50"/>
+      <c r="L161" s="50"/>
+      <c r="M161" s="50"/>
+      <c r="N161" s="50"/>
+      <c r="O161" s="50"/>
+      <c r="P161" s="50"/>
+      <c r="Q161" s="50"/>
+      <c r="R161" s="50"/>
+      <c r="S161" s="50"/>
+      <c r="T161" s="50"/>
+      <c r="U161" s="50"/>
+      <c r="V161" s="50"/>
+      <c r="W161" s="50"/>
+      <c r="X161" s="50"/>
+      <c r="Y161" s="50"/>
+      <c r="Z161" s="50"/>
+      <c r="AA161" s="50"/>
+      <c r="AB161" s="51"/>
       <c r="AC161" s="11"/>
     </row>
     <row r="162" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6658,27 +6687,27 @@
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
-      <c r="H162" s="51"/>
-      <c r="I162" s="52"/>
-      <c r="J162" s="52"/>
-      <c r="K162" s="52"/>
-      <c r="L162" s="52"/>
-      <c r="M162" s="52"/>
-      <c r="N162" s="52"/>
-      <c r="O162" s="52"/>
-      <c r="P162" s="52"/>
-      <c r="Q162" s="52"/>
-      <c r="R162" s="52"/>
-      <c r="S162" s="52"/>
-      <c r="T162" s="52"/>
-      <c r="U162" s="52"/>
-      <c r="V162" s="52"/>
-      <c r="W162" s="52"/>
-      <c r="X162" s="52"/>
-      <c r="Y162" s="52"/>
-      <c r="Z162" s="52"/>
-      <c r="AA162" s="52"/>
-      <c r="AB162" s="53"/>
+      <c r="H162" s="49"/>
+      <c r="I162" s="50"/>
+      <c r="J162" s="50"/>
+      <c r="K162" s="50"/>
+      <c r="L162" s="50"/>
+      <c r="M162" s="50"/>
+      <c r="N162" s="50"/>
+      <c r="O162" s="50"/>
+      <c r="P162" s="50"/>
+      <c r="Q162" s="50"/>
+      <c r="R162" s="50"/>
+      <c r="S162" s="50"/>
+      <c r="T162" s="50"/>
+      <c r="U162" s="50"/>
+      <c r="V162" s="50"/>
+      <c r="W162" s="50"/>
+      <c r="X162" s="50"/>
+      <c r="Y162" s="50"/>
+      <c r="Z162" s="50"/>
+      <c r="AA162" s="50"/>
+      <c r="AB162" s="51"/>
       <c r="AC162" s="11"/>
     </row>
     <row r="163" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6688,27 +6717,27 @@
       <c r="E163" s="6"/>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
-      <c r="H163" s="51"/>
-      <c r="I163" s="52"/>
-      <c r="J163" s="52"/>
-      <c r="K163" s="52"/>
-      <c r="L163" s="52"/>
-      <c r="M163" s="52"/>
-      <c r="N163" s="52"/>
-      <c r="O163" s="52"/>
-      <c r="P163" s="52"/>
-      <c r="Q163" s="52"/>
-      <c r="R163" s="52"/>
-      <c r="S163" s="52"/>
-      <c r="T163" s="52"/>
-      <c r="U163" s="52"/>
-      <c r="V163" s="52"/>
-      <c r="W163" s="52"/>
-      <c r="X163" s="52"/>
-      <c r="Y163" s="52"/>
-      <c r="Z163" s="52"/>
-      <c r="AA163" s="52"/>
-      <c r="AB163" s="53"/>
+      <c r="H163" s="49"/>
+      <c r="I163" s="50"/>
+      <c r="J163" s="50"/>
+      <c r="K163" s="50"/>
+      <c r="L163" s="50"/>
+      <c r="M163" s="50"/>
+      <c r="N163" s="50"/>
+      <c r="O163" s="50"/>
+      <c r="P163" s="50"/>
+      <c r="Q163" s="50"/>
+      <c r="R163" s="50"/>
+      <c r="S163" s="50"/>
+      <c r="T163" s="50"/>
+      <c r="U163" s="50"/>
+      <c r="V163" s="50"/>
+      <c r="W163" s="50"/>
+      <c r="X163" s="50"/>
+      <c r="Y163" s="50"/>
+      <c r="Z163" s="50"/>
+      <c r="AA163" s="50"/>
+      <c r="AB163" s="51"/>
       <c r="AC163" s="11"/>
     </row>
     <row r="164" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6718,27 +6747,27 @@
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
-      <c r="H164" s="51"/>
-      <c r="I164" s="52"/>
-      <c r="J164" s="52"/>
-      <c r="K164" s="52"/>
-      <c r="L164" s="52"/>
-      <c r="M164" s="52"/>
-      <c r="N164" s="52"/>
-      <c r="O164" s="52"/>
-      <c r="P164" s="52"/>
-      <c r="Q164" s="52"/>
-      <c r="R164" s="52"/>
-      <c r="S164" s="52"/>
-      <c r="T164" s="52"/>
-      <c r="U164" s="52"/>
-      <c r="V164" s="52"/>
-      <c r="W164" s="52"/>
-      <c r="X164" s="52"/>
-      <c r="Y164" s="52"/>
-      <c r="Z164" s="52"/>
-      <c r="AA164" s="52"/>
-      <c r="AB164" s="53"/>
+      <c r="H164" s="49"/>
+      <c r="I164" s="50"/>
+      <c r="J164" s="50"/>
+      <c r="K164" s="50"/>
+      <c r="L164" s="50"/>
+      <c r="M164" s="50"/>
+      <c r="N164" s="50"/>
+      <c r="O164" s="50"/>
+      <c r="P164" s="50"/>
+      <c r="Q164" s="50"/>
+      <c r="R164" s="50"/>
+      <c r="S164" s="50"/>
+      <c r="T164" s="50"/>
+      <c r="U164" s="50"/>
+      <c r="V164" s="50"/>
+      <c r="W164" s="50"/>
+      <c r="X164" s="50"/>
+      <c r="Y164" s="50"/>
+      <c r="Z164" s="50"/>
+      <c r="AA164" s="50"/>
+      <c r="AB164" s="51"/>
       <c r="AC164" s="11"/>
     </row>
     <row r="165" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6748,27 +6777,27 @@
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
-      <c r="H165" s="51"/>
-      <c r="I165" s="52"/>
-      <c r="J165" s="52"/>
-      <c r="K165" s="52"/>
-      <c r="L165" s="52"/>
-      <c r="M165" s="52"/>
-      <c r="N165" s="52"/>
-      <c r="O165" s="52"/>
-      <c r="P165" s="52"/>
-      <c r="Q165" s="52"/>
-      <c r="R165" s="52"/>
-      <c r="S165" s="52"/>
-      <c r="T165" s="52"/>
-      <c r="U165" s="52"/>
-      <c r="V165" s="52"/>
-      <c r="W165" s="52"/>
-      <c r="X165" s="52"/>
-      <c r="Y165" s="52"/>
-      <c r="Z165" s="52"/>
-      <c r="AA165" s="52"/>
-      <c r="AB165" s="53"/>
+      <c r="H165" s="49"/>
+      <c r="I165" s="50"/>
+      <c r="J165" s="50"/>
+      <c r="K165" s="50"/>
+      <c r="L165" s="50"/>
+      <c r="M165" s="50"/>
+      <c r="N165" s="50"/>
+      <c r="O165" s="50"/>
+      <c r="P165" s="50"/>
+      <c r="Q165" s="50"/>
+      <c r="R165" s="50"/>
+      <c r="S165" s="50"/>
+      <c r="T165" s="50"/>
+      <c r="U165" s="50"/>
+      <c r="V165" s="50"/>
+      <c r="W165" s="50"/>
+      <c r="X165" s="50"/>
+      <c r="Y165" s="50"/>
+      <c r="Z165" s="50"/>
+      <c r="AA165" s="50"/>
+      <c r="AB165" s="51"/>
       <c r="AC165" s="11"/>
     </row>
     <row r="166" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6778,27 +6807,27 @@
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
-      <c r="H166" s="54"/>
-      <c r="I166" s="55"/>
-      <c r="J166" s="55"/>
-      <c r="K166" s="55"/>
-      <c r="L166" s="55"/>
-      <c r="M166" s="55"/>
-      <c r="N166" s="55"/>
-      <c r="O166" s="55"/>
-      <c r="P166" s="55"/>
-      <c r="Q166" s="55"/>
-      <c r="R166" s="55"/>
-      <c r="S166" s="55"/>
-      <c r="T166" s="55"/>
-      <c r="U166" s="55"/>
-      <c r="V166" s="55"/>
-      <c r="W166" s="55"/>
-      <c r="X166" s="55"/>
-      <c r="Y166" s="55"/>
-      <c r="Z166" s="55"/>
-      <c r="AA166" s="55"/>
-      <c r="AB166" s="56"/>
+      <c r="H166" s="52"/>
+      <c r="I166" s="53"/>
+      <c r="J166" s="53"/>
+      <c r="K166" s="53"/>
+      <c r="L166" s="53"/>
+      <c r="M166" s="53"/>
+      <c r="N166" s="53"/>
+      <c r="O166" s="53"/>
+      <c r="P166" s="53"/>
+      <c r="Q166" s="53"/>
+      <c r="R166" s="53"/>
+      <c r="S166" s="53"/>
+      <c r="T166" s="53"/>
+      <c r="U166" s="53"/>
+      <c r="V166" s="53"/>
+      <c r="W166" s="53"/>
+      <c r="X166" s="53"/>
+      <c r="Y166" s="53"/>
+      <c r="Z166" s="53"/>
+      <c r="AA166" s="53"/>
+      <c r="AB166" s="54"/>
       <c r="AC166" s="11"/>
     </row>
     <row r="167" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6840,27 +6869,27 @@
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
-      <c r="H168" s="48"/>
-      <c r="I168" s="49"/>
-      <c r="J168" s="49"/>
-      <c r="K168" s="49"/>
-      <c r="L168" s="49"/>
-      <c r="M168" s="49"/>
-      <c r="N168" s="49"/>
-      <c r="O168" s="49"/>
-      <c r="P168" s="49"/>
-      <c r="Q168" s="49"/>
-      <c r="R168" s="49"/>
-      <c r="S168" s="49"/>
-      <c r="T168" s="49"/>
-      <c r="U168" s="49"/>
-      <c r="V168" s="49"/>
-      <c r="W168" s="49"/>
-      <c r="X168" s="49"/>
-      <c r="Y168" s="49"/>
-      <c r="Z168" s="49"/>
-      <c r="AA168" s="49"/>
-      <c r="AB168" s="50"/>
+      <c r="H168" s="46"/>
+      <c r="I168" s="47"/>
+      <c r="J168" s="47"/>
+      <c r="K168" s="47"/>
+      <c r="L168" s="47"/>
+      <c r="M168" s="47"/>
+      <c r="N168" s="47"/>
+      <c r="O168" s="47"/>
+      <c r="P168" s="47"/>
+      <c r="Q168" s="47"/>
+      <c r="R168" s="47"/>
+      <c r="S168" s="47"/>
+      <c r="T168" s="47"/>
+      <c r="U168" s="47"/>
+      <c r="V168" s="47"/>
+      <c r="W168" s="47"/>
+      <c r="X168" s="47"/>
+      <c r="Y168" s="47"/>
+      <c r="Z168" s="47"/>
+      <c r="AA168" s="47"/>
+      <c r="AB168" s="48"/>
       <c r="AC168" s="11"/>
     </row>
     <row r="169" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6870,27 +6899,27 @@
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
-      <c r="H169" s="51"/>
-      <c r="I169" s="52"/>
-      <c r="J169" s="52"/>
-      <c r="K169" s="52"/>
-      <c r="L169" s="52"/>
-      <c r="M169" s="52"/>
-      <c r="N169" s="52"/>
-      <c r="O169" s="52"/>
-      <c r="P169" s="52"/>
-      <c r="Q169" s="52"/>
-      <c r="R169" s="52"/>
-      <c r="S169" s="52"/>
-      <c r="T169" s="52"/>
-      <c r="U169" s="52"/>
-      <c r="V169" s="52"/>
-      <c r="W169" s="52"/>
-      <c r="X169" s="52"/>
-      <c r="Y169" s="52"/>
-      <c r="Z169" s="52"/>
-      <c r="AA169" s="52"/>
-      <c r="AB169" s="53"/>
+      <c r="H169" s="49"/>
+      <c r="I169" s="50"/>
+      <c r="J169" s="50"/>
+      <c r="K169" s="50"/>
+      <c r="L169" s="50"/>
+      <c r="M169" s="50"/>
+      <c r="N169" s="50"/>
+      <c r="O169" s="50"/>
+      <c r="P169" s="50"/>
+      <c r="Q169" s="50"/>
+      <c r="R169" s="50"/>
+      <c r="S169" s="50"/>
+      <c r="T169" s="50"/>
+      <c r="U169" s="50"/>
+      <c r="V169" s="50"/>
+      <c r="W169" s="50"/>
+      <c r="X169" s="50"/>
+      <c r="Y169" s="50"/>
+      <c r="Z169" s="50"/>
+      <c r="AA169" s="50"/>
+      <c r="AB169" s="51"/>
       <c r="AC169" s="11"/>
     </row>
     <row r="170" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6900,27 +6929,27 @@
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
-      <c r="H170" s="51"/>
-      <c r="I170" s="52"/>
-      <c r="J170" s="52"/>
-      <c r="K170" s="52"/>
-      <c r="L170" s="52"/>
-      <c r="M170" s="52"/>
-      <c r="N170" s="52"/>
-      <c r="O170" s="52"/>
-      <c r="P170" s="52"/>
-      <c r="Q170" s="52"/>
-      <c r="R170" s="52"/>
-      <c r="S170" s="52"/>
-      <c r="T170" s="52"/>
-      <c r="U170" s="52"/>
-      <c r="V170" s="52"/>
-      <c r="W170" s="52"/>
-      <c r="X170" s="52"/>
-      <c r="Y170" s="52"/>
-      <c r="Z170" s="52"/>
-      <c r="AA170" s="52"/>
-      <c r="AB170" s="53"/>
+      <c r="H170" s="49"/>
+      <c r="I170" s="50"/>
+      <c r="J170" s="50"/>
+      <c r="K170" s="50"/>
+      <c r="L170" s="50"/>
+      <c r="M170" s="50"/>
+      <c r="N170" s="50"/>
+      <c r="O170" s="50"/>
+      <c r="P170" s="50"/>
+      <c r="Q170" s="50"/>
+      <c r="R170" s="50"/>
+      <c r="S170" s="50"/>
+      <c r="T170" s="50"/>
+      <c r="U170" s="50"/>
+      <c r="V170" s="50"/>
+      <c r="W170" s="50"/>
+      <c r="X170" s="50"/>
+      <c r="Y170" s="50"/>
+      <c r="Z170" s="50"/>
+      <c r="AA170" s="50"/>
+      <c r="AB170" s="51"/>
       <c r="AC170" s="11"/>
     </row>
     <row r="171" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6930,27 +6959,27 @@
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
-      <c r="H171" s="51"/>
-      <c r="I171" s="52"/>
-      <c r="J171" s="52"/>
-      <c r="K171" s="52"/>
-      <c r="L171" s="52"/>
-      <c r="M171" s="52"/>
-      <c r="N171" s="52"/>
-      <c r="O171" s="52"/>
-      <c r="P171" s="52"/>
-      <c r="Q171" s="52"/>
-      <c r="R171" s="52"/>
-      <c r="S171" s="52"/>
-      <c r="T171" s="52"/>
-      <c r="U171" s="52"/>
-      <c r="V171" s="52"/>
-      <c r="W171" s="52"/>
-      <c r="X171" s="52"/>
-      <c r="Y171" s="52"/>
-      <c r="Z171" s="52"/>
-      <c r="AA171" s="52"/>
-      <c r="AB171" s="53"/>
+      <c r="H171" s="49"/>
+      <c r="I171" s="50"/>
+      <c r="J171" s="50"/>
+      <c r="K171" s="50"/>
+      <c r="L171" s="50"/>
+      <c r="M171" s="50"/>
+      <c r="N171" s="50"/>
+      <c r="O171" s="50"/>
+      <c r="P171" s="50"/>
+      <c r="Q171" s="50"/>
+      <c r="R171" s="50"/>
+      <c r="S171" s="50"/>
+      <c r="T171" s="50"/>
+      <c r="U171" s="50"/>
+      <c r="V171" s="50"/>
+      <c r="W171" s="50"/>
+      <c r="X171" s="50"/>
+      <c r="Y171" s="50"/>
+      <c r="Z171" s="50"/>
+      <c r="AA171" s="50"/>
+      <c r="AB171" s="51"/>
       <c r="AC171" s="11"/>
     </row>
     <row r="172" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6960,27 +6989,27 @@
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
-      <c r="H172" s="51"/>
-      <c r="I172" s="52"/>
-      <c r="J172" s="52"/>
-      <c r="K172" s="52"/>
-      <c r="L172" s="52"/>
-      <c r="M172" s="52"/>
-      <c r="N172" s="52"/>
-      <c r="O172" s="52"/>
-      <c r="P172" s="52"/>
-      <c r="Q172" s="52"/>
-      <c r="R172" s="52"/>
-      <c r="S172" s="52"/>
-      <c r="T172" s="52"/>
-      <c r="U172" s="52"/>
-      <c r="V172" s="52"/>
-      <c r="W172" s="52"/>
-      <c r="X172" s="52"/>
-      <c r="Y172" s="52"/>
-      <c r="Z172" s="52"/>
-      <c r="AA172" s="52"/>
-      <c r="AB172" s="53"/>
+      <c r="H172" s="49"/>
+      <c r="I172" s="50"/>
+      <c r="J172" s="50"/>
+      <c r="K172" s="50"/>
+      <c r="L172" s="50"/>
+      <c r="M172" s="50"/>
+      <c r="N172" s="50"/>
+      <c r="O172" s="50"/>
+      <c r="P172" s="50"/>
+      <c r="Q172" s="50"/>
+      <c r="R172" s="50"/>
+      <c r="S172" s="50"/>
+      <c r="T172" s="50"/>
+      <c r="U172" s="50"/>
+      <c r="V172" s="50"/>
+      <c r="W172" s="50"/>
+      <c r="X172" s="50"/>
+      <c r="Y172" s="50"/>
+      <c r="Z172" s="50"/>
+      <c r="AA172" s="50"/>
+      <c r="AB172" s="51"/>
       <c r="AC172" s="11"/>
     </row>
     <row r="173" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6990,27 +7019,27 @@
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
-      <c r="H173" s="51"/>
-      <c r="I173" s="52"/>
-      <c r="J173" s="52"/>
-      <c r="K173" s="52"/>
-      <c r="L173" s="52"/>
-      <c r="M173" s="52"/>
-      <c r="N173" s="52"/>
-      <c r="O173" s="52"/>
-      <c r="P173" s="52"/>
-      <c r="Q173" s="52"/>
-      <c r="R173" s="52"/>
-      <c r="S173" s="52"/>
-      <c r="T173" s="52"/>
-      <c r="U173" s="52"/>
-      <c r="V173" s="52"/>
-      <c r="W173" s="52"/>
-      <c r="X173" s="52"/>
-      <c r="Y173" s="52"/>
-      <c r="Z173" s="52"/>
-      <c r="AA173" s="52"/>
-      <c r="AB173" s="53"/>
+      <c r="H173" s="49"/>
+      <c r="I173" s="50"/>
+      <c r="J173" s="50"/>
+      <c r="K173" s="50"/>
+      <c r="L173" s="50"/>
+      <c r="M173" s="50"/>
+      <c r="N173" s="50"/>
+      <c r="O173" s="50"/>
+      <c r="P173" s="50"/>
+      <c r="Q173" s="50"/>
+      <c r="R173" s="50"/>
+      <c r="S173" s="50"/>
+      <c r="T173" s="50"/>
+      <c r="U173" s="50"/>
+      <c r="V173" s="50"/>
+      <c r="W173" s="50"/>
+      <c r="X173" s="50"/>
+      <c r="Y173" s="50"/>
+      <c r="Z173" s="50"/>
+      <c r="AA173" s="50"/>
+      <c r="AB173" s="51"/>
       <c r="AC173" s="11"/>
     </row>
     <row r="174" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7020,27 +7049,27 @@
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
-      <c r="H174" s="54"/>
-      <c r="I174" s="55"/>
-      <c r="J174" s="55"/>
-      <c r="K174" s="55"/>
-      <c r="L174" s="55"/>
-      <c r="M174" s="55"/>
-      <c r="N174" s="55"/>
-      <c r="O174" s="55"/>
-      <c r="P174" s="55"/>
-      <c r="Q174" s="55"/>
-      <c r="R174" s="55"/>
-      <c r="S174" s="55"/>
-      <c r="T174" s="55"/>
-      <c r="U174" s="55"/>
-      <c r="V174" s="55"/>
-      <c r="W174" s="55"/>
-      <c r="X174" s="55"/>
-      <c r="Y174" s="55"/>
-      <c r="Z174" s="55"/>
-      <c r="AA174" s="55"/>
-      <c r="AB174" s="56"/>
+      <c r="H174" s="52"/>
+      <c r="I174" s="53"/>
+      <c r="J174" s="53"/>
+      <c r="K174" s="53"/>
+      <c r="L174" s="53"/>
+      <c r="M174" s="53"/>
+      <c r="N174" s="53"/>
+      <c r="O174" s="53"/>
+      <c r="P174" s="53"/>
+      <c r="Q174" s="53"/>
+      <c r="R174" s="53"/>
+      <c r="S174" s="53"/>
+      <c r="T174" s="53"/>
+      <c r="U174" s="53"/>
+      <c r="V174" s="53"/>
+      <c r="W174" s="53"/>
+      <c r="X174" s="53"/>
+      <c r="Y174" s="53"/>
+      <c r="Z174" s="53"/>
+      <c r="AA174" s="53"/>
+      <c r="AB174" s="54"/>
       <c r="AC174" s="11"/>
     </row>
     <row r="175" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7148,27 +7177,27 @@
         <v>2</v>
       </c>
       <c r="G179" s="6"/>
-      <c r="H179" s="48"/>
-      <c r="I179" s="49"/>
-      <c r="J179" s="49"/>
-      <c r="K179" s="49"/>
-      <c r="L179" s="49"/>
-      <c r="M179" s="49"/>
-      <c r="N179" s="49"/>
-      <c r="O179" s="49"/>
-      <c r="P179" s="49"/>
-      <c r="Q179" s="49"/>
-      <c r="R179" s="49"/>
-      <c r="S179" s="49"/>
-      <c r="T179" s="49"/>
-      <c r="U179" s="49"/>
-      <c r="V179" s="49"/>
-      <c r="W179" s="49"/>
-      <c r="X179" s="49"/>
-      <c r="Y179" s="49"/>
-      <c r="Z179" s="49"/>
-      <c r="AA179" s="49"/>
-      <c r="AB179" s="50"/>
+      <c r="H179" s="46"/>
+      <c r="I179" s="47"/>
+      <c r="J179" s="47"/>
+      <c r="K179" s="47"/>
+      <c r="L179" s="47"/>
+      <c r="M179" s="47"/>
+      <c r="N179" s="47"/>
+      <c r="O179" s="47"/>
+      <c r="P179" s="47"/>
+      <c r="Q179" s="47"/>
+      <c r="R179" s="47"/>
+      <c r="S179" s="47"/>
+      <c r="T179" s="47"/>
+      <c r="U179" s="47"/>
+      <c r="V179" s="47"/>
+      <c r="W179" s="47"/>
+      <c r="X179" s="47"/>
+      <c r="Y179" s="47"/>
+      <c r="Z179" s="47"/>
+      <c r="AA179" s="47"/>
+      <c r="AB179" s="48"/>
       <c r="AC179" s="11"/>
     </row>
     <row r="180" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7178,27 +7207,27 @@
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
-      <c r="H180" s="51"/>
-      <c r="I180" s="52"/>
-      <c r="J180" s="52"/>
-      <c r="K180" s="52"/>
-      <c r="L180" s="52"/>
-      <c r="M180" s="52"/>
-      <c r="N180" s="52"/>
-      <c r="O180" s="52"/>
-      <c r="P180" s="52"/>
-      <c r="Q180" s="52"/>
-      <c r="R180" s="52"/>
-      <c r="S180" s="52"/>
-      <c r="T180" s="52"/>
-      <c r="U180" s="52"/>
-      <c r="V180" s="52"/>
-      <c r="W180" s="52"/>
-      <c r="X180" s="52"/>
-      <c r="Y180" s="52"/>
-      <c r="Z180" s="52"/>
-      <c r="AA180" s="52"/>
-      <c r="AB180" s="53"/>
+      <c r="H180" s="49"/>
+      <c r="I180" s="50"/>
+      <c r="J180" s="50"/>
+      <c r="K180" s="50"/>
+      <c r="L180" s="50"/>
+      <c r="M180" s="50"/>
+      <c r="N180" s="50"/>
+      <c r="O180" s="50"/>
+      <c r="P180" s="50"/>
+      <c r="Q180" s="50"/>
+      <c r="R180" s="50"/>
+      <c r="S180" s="50"/>
+      <c r="T180" s="50"/>
+      <c r="U180" s="50"/>
+      <c r="V180" s="50"/>
+      <c r="W180" s="50"/>
+      <c r="X180" s="50"/>
+      <c r="Y180" s="50"/>
+      <c r="Z180" s="50"/>
+      <c r="AA180" s="50"/>
+      <c r="AB180" s="51"/>
       <c r="AC180" s="11"/>
     </row>
     <row r="181" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7208,27 +7237,27 @@
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
-      <c r="H181" s="51"/>
-      <c r="I181" s="52"/>
-      <c r="J181" s="52"/>
-      <c r="K181" s="52"/>
-      <c r="L181" s="52"/>
-      <c r="M181" s="52"/>
-      <c r="N181" s="52"/>
-      <c r="O181" s="52"/>
-      <c r="P181" s="52"/>
-      <c r="Q181" s="52"/>
-      <c r="R181" s="52"/>
-      <c r="S181" s="52"/>
-      <c r="T181" s="52"/>
-      <c r="U181" s="52"/>
-      <c r="V181" s="52"/>
-      <c r="W181" s="52"/>
-      <c r="X181" s="52"/>
-      <c r="Y181" s="52"/>
-      <c r="Z181" s="52"/>
-      <c r="AA181" s="52"/>
-      <c r="AB181" s="53"/>
+      <c r="H181" s="49"/>
+      <c r="I181" s="50"/>
+      <c r="J181" s="50"/>
+      <c r="K181" s="50"/>
+      <c r="L181" s="50"/>
+      <c r="M181" s="50"/>
+      <c r="N181" s="50"/>
+      <c r="O181" s="50"/>
+      <c r="P181" s="50"/>
+      <c r="Q181" s="50"/>
+      <c r="R181" s="50"/>
+      <c r="S181" s="50"/>
+      <c r="T181" s="50"/>
+      <c r="U181" s="50"/>
+      <c r="V181" s="50"/>
+      <c r="W181" s="50"/>
+      <c r="X181" s="50"/>
+      <c r="Y181" s="50"/>
+      <c r="Z181" s="50"/>
+      <c r="AA181" s="50"/>
+      <c r="AB181" s="51"/>
       <c r="AC181" s="11"/>
     </row>
     <row r="182" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7238,27 +7267,27 @@
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
-      <c r="H182" s="51"/>
-      <c r="I182" s="52"/>
-      <c r="J182" s="52"/>
-      <c r="K182" s="52"/>
-      <c r="L182" s="52"/>
-      <c r="M182" s="52"/>
-      <c r="N182" s="52"/>
-      <c r="O182" s="52"/>
-      <c r="P182" s="52"/>
-      <c r="Q182" s="52"/>
-      <c r="R182" s="52"/>
-      <c r="S182" s="52"/>
-      <c r="T182" s="52"/>
-      <c r="U182" s="52"/>
-      <c r="V182" s="52"/>
-      <c r="W182" s="52"/>
-      <c r="X182" s="52"/>
-      <c r="Y182" s="52"/>
-      <c r="Z182" s="52"/>
-      <c r="AA182" s="52"/>
-      <c r="AB182" s="53"/>
+      <c r="H182" s="49"/>
+      <c r="I182" s="50"/>
+      <c r="J182" s="50"/>
+      <c r="K182" s="50"/>
+      <c r="L182" s="50"/>
+      <c r="M182" s="50"/>
+      <c r="N182" s="50"/>
+      <c r="O182" s="50"/>
+      <c r="P182" s="50"/>
+      <c r="Q182" s="50"/>
+      <c r="R182" s="50"/>
+      <c r="S182" s="50"/>
+      <c r="T182" s="50"/>
+      <c r="U182" s="50"/>
+      <c r="V182" s="50"/>
+      <c r="W182" s="50"/>
+      <c r="X182" s="50"/>
+      <c r="Y182" s="50"/>
+      <c r="Z182" s="50"/>
+      <c r="AA182" s="50"/>
+      <c r="AB182" s="51"/>
       <c r="AC182" s="11"/>
     </row>
     <row r="183" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7268,27 +7297,27 @@
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
-      <c r="H183" s="51"/>
-      <c r="I183" s="52"/>
-      <c r="J183" s="52"/>
-      <c r="K183" s="52"/>
-      <c r="L183" s="52"/>
-      <c r="M183" s="52"/>
-      <c r="N183" s="52"/>
-      <c r="O183" s="52"/>
-      <c r="P183" s="52"/>
-      <c r="Q183" s="52"/>
-      <c r="R183" s="52"/>
-      <c r="S183" s="52"/>
-      <c r="T183" s="52"/>
-      <c r="U183" s="52"/>
-      <c r="V183" s="52"/>
-      <c r="W183" s="52"/>
-      <c r="X183" s="52"/>
-      <c r="Y183" s="52"/>
-      <c r="Z183" s="52"/>
-      <c r="AA183" s="52"/>
-      <c r="AB183" s="53"/>
+      <c r="H183" s="49"/>
+      <c r="I183" s="50"/>
+      <c r="J183" s="50"/>
+      <c r="K183" s="50"/>
+      <c r="L183" s="50"/>
+      <c r="M183" s="50"/>
+      <c r="N183" s="50"/>
+      <c r="O183" s="50"/>
+      <c r="P183" s="50"/>
+      <c r="Q183" s="50"/>
+      <c r="R183" s="50"/>
+      <c r="S183" s="50"/>
+      <c r="T183" s="50"/>
+      <c r="U183" s="50"/>
+      <c r="V183" s="50"/>
+      <c r="W183" s="50"/>
+      <c r="X183" s="50"/>
+      <c r="Y183" s="50"/>
+      <c r="Z183" s="50"/>
+      <c r="AA183" s="50"/>
+      <c r="AB183" s="51"/>
       <c r="AC183" s="11"/>
     </row>
     <row r="184" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7298,27 +7327,27 @@
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
-      <c r="H184" s="51"/>
-      <c r="I184" s="52"/>
-      <c r="J184" s="52"/>
-      <c r="K184" s="52"/>
-      <c r="L184" s="52"/>
-      <c r="M184" s="52"/>
-      <c r="N184" s="52"/>
-      <c r="O184" s="52"/>
-      <c r="P184" s="52"/>
-      <c r="Q184" s="52"/>
-      <c r="R184" s="52"/>
-      <c r="S184" s="52"/>
-      <c r="T184" s="52"/>
-      <c r="U184" s="52"/>
-      <c r="V184" s="52"/>
-      <c r="W184" s="52"/>
-      <c r="X184" s="52"/>
-      <c r="Y184" s="52"/>
-      <c r="Z184" s="52"/>
-      <c r="AA184" s="52"/>
-      <c r="AB184" s="53"/>
+      <c r="H184" s="49"/>
+      <c r="I184" s="50"/>
+      <c r="J184" s="50"/>
+      <c r="K184" s="50"/>
+      <c r="L184" s="50"/>
+      <c r="M184" s="50"/>
+      <c r="N184" s="50"/>
+      <c r="O184" s="50"/>
+      <c r="P184" s="50"/>
+      <c r="Q184" s="50"/>
+      <c r="R184" s="50"/>
+      <c r="S184" s="50"/>
+      <c r="T184" s="50"/>
+      <c r="U184" s="50"/>
+      <c r="V184" s="50"/>
+      <c r="W184" s="50"/>
+      <c r="X184" s="50"/>
+      <c r="Y184" s="50"/>
+      <c r="Z184" s="50"/>
+      <c r="AA184" s="50"/>
+      <c r="AB184" s="51"/>
       <c r="AC184" s="11"/>
     </row>
     <row r="185" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7328,27 +7357,27 @@
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
-      <c r="H185" s="54"/>
-      <c r="I185" s="55"/>
-      <c r="J185" s="55"/>
-      <c r="K185" s="55"/>
-      <c r="L185" s="55"/>
-      <c r="M185" s="55"/>
-      <c r="N185" s="55"/>
-      <c r="O185" s="55"/>
-      <c r="P185" s="55"/>
-      <c r="Q185" s="55"/>
-      <c r="R185" s="55"/>
-      <c r="S185" s="55"/>
-      <c r="T185" s="55"/>
-      <c r="U185" s="55"/>
-      <c r="V185" s="55"/>
-      <c r="W185" s="55"/>
-      <c r="X185" s="55"/>
-      <c r="Y185" s="55"/>
-      <c r="Z185" s="55"/>
-      <c r="AA185" s="55"/>
-      <c r="AB185" s="56"/>
+      <c r="H185" s="52"/>
+      <c r="I185" s="53"/>
+      <c r="J185" s="53"/>
+      <c r="K185" s="53"/>
+      <c r="L185" s="53"/>
+      <c r="M185" s="53"/>
+      <c r="N185" s="53"/>
+      <c r="O185" s="53"/>
+      <c r="P185" s="53"/>
+      <c r="Q185" s="53"/>
+      <c r="R185" s="53"/>
+      <c r="S185" s="53"/>
+      <c r="T185" s="53"/>
+      <c r="U185" s="53"/>
+      <c r="V185" s="53"/>
+      <c r="W185" s="53"/>
+      <c r="X185" s="53"/>
+      <c r="Y185" s="53"/>
+      <c r="Z185" s="53"/>
+      <c r="AA185" s="53"/>
+      <c r="AB185" s="54"/>
       <c r="AC185" s="11"/>
     </row>
     <row r="186" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7390,27 +7419,27 @@
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
-      <c r="H187" s="48"/>
-      <c r="I187" s="49"/>
-      <c r="J187" s="49"/>
-      <c r="K187" s="49"/>
-      <c r="L187" s="49"/>
-      <c r="M187" s="49"/>
-      <c r="N187" s="49"/>
-      <c r="O187" s="49"/>
-      <c r="P187" s="49"/>
-      <c r="Q187" s="49"/>
-      <c r="R187" s="49"/>
-      <c r="S187" s="49"/>
-      <c r="T187" s="49"/>
-      <c r="U187" s="49"/>
-      <c r="V187" s="49"/>
-      <c r="W187" s="49"/>
-      <c r="X187" s="49"/>
-      <c r="Y187" s="49"/>
-      <c r="Z187" s="49"/>
-      <c r="AA187" s="49"/>
-      <c r="AB187" s="50"/>
+      <c r="H187" s="46"/>
+      <c r="I187" s="47"/>
+      <c r="J187" s="47"/>
+      <c r="K187" s="47"/>
+      <c r="L187" s="47"/>
+      <c r="M187" s="47"/>
+      <c r="N187" s="47"/>
+      <c r="O187" s="47"/>
+      <c r="P187" s="47"/>
+      <c r="Q187" s="47"/>
+      <c r="R187" s="47"/>
+      <c r="S187" s="47"/>
+      <c r="T187" s="47"/>
+      <c r="U187" s="47"/>
+      <c r="V187" s="47"/>
+      <c r="W187" s="47"/>
+      <c r="X187" s="47"/>
+      <c r="Y187" s="47"/>
+      <c r="Z187" s="47"/>
+      <c r="AA187" s="47"/>
+      <c r="AB187" s="48"/>
       <c r="AC187" s="11"/>
     </row>
     <row r="188" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7420,27 +7449,27 @@
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
-      <c r="H188" s="51"/>
-      <c r="I188" s="52"/>
-      <c r="J188" s="52"/>
-      <c r="K188" s="52"/>
-      <c r="L188" s="52"/>
-      <c r="M188" s="52"/>
-      <c r="N188" s="52"/>
-      <c r="O188" s="52"/>
-      <c r="P188" s="52"/>
-      <c r="Q188" s="52"/>
-      <c r="R188" s="52"/>
-      <c r="S188" s="52"/>
-      <c r="T188" s="52"/>
-      <c r="U188" s="52"/>
-      <c r="V188" s="52"/>
-      <c r="W188" s="52"/>
-      <c r="X188" s="52"/>
-      <c r="Y188" s="52"/>
-      <c r="Z188" s="52"/>
-      <c r="AA188" s="52"/>
-      <c r="AB188" s="53"/>
+      <c r="H188" s="49"/>
+      <c r="I188" s="50"/>
+      <c r="J188" s="50"/>
+      <c r="K188" s="50"/>
+      <c r="L188" s="50"/>
+      <c r="M188" s="50"/>
+      <c r="N188" s="50"/>
+      <c r="O188" s="50"/>
+      <c r="P188" s="50"/>
+      <c r="Q188" s="50"/>
+      <c r="R188" s="50"/>
+      <c r="S188" s="50"/>
+      <c r="T188" s="50"/>
+      <c r="U188" s="50"/>
+      <c r="V188" s="50"/>
+      <c r="W188" s="50"/>
+      <c r="X188" s="50"/>
+      <c r="Y188" s="50"/>
+      <c r="Z188" s="50"/>
+      <c r="AA188" s="50"/>
+      <c r="AB188" s="51"/>
       <c r="AC188" s="11"/>
     </row>
     <row r="189" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7450,27 +7479,27 @@
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
-      <c r="H189" s="51"/>
-      <c r="I189" s="52"/>
-      <c r="J189" s="52"/>
-      <c r="K189" s="52"/>
-      <c r="L189" s="52"/>
-      <c r="M189" s="52"/>
-      <c r="N189" s="52"/>
-      <c r="O189" s="52"/>
-      <c r="P189" s="52"/>
-      <c r="Q189" s="52"/>
-      <c r="R189" s="52"/>
-      <c r="S189" s="52"/>
-      <c r="T189" s="52"/>
-      <c r="U189" s="52"/>
-      <c r="V189" s="52"/>
-      <c r="W189" s="52"/>
-      <c r="X189" s="52"/>
-      <c r="Y189" s="52"/>
-      <c r="Z189" s="52"/>
-      <c r="AA189" s="52"/>
-      <c r="AB189" s="53"/>
+      <c r="H189" s="49"/>
+      <c r="I189" s="50"/>
+      <c r="J189" s="50"/>
+      <c r="K189" s="50"/>
+      <c r="L189" s="50"/>
+      <c r="M189" s="50"/>
+      <c r="N189" s="50"/>
+      <c r="O189" s="50"/>
+      <c r="P189" s="50"/>
+      <c r="Q189" s="50"/>
+      <c r="R189" s="50"/>
+      <c r="S189" s="50"/>
+      <c r="T189" s="50"/>
+      <c r="U189" s="50"/>
+      <c r="V189" s="50"/>
+      <c r="W189" s="50"/>
+      <c r="X189" s="50"/>
+      <c r="Y189" s="50"/>
+      <c r="Z189" s="50"/>
+      <c r="AA189" s="50"/>
+      <c r="AB189" s="51"/>
       <c r="AC189" s="11"/>
     </row>
     <row r="190" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7480,27 +7509,27 @@
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
-      <c r="H190" s="51"/>
-      <c r="I190" s="52"/>
-      <c r="J190" s="52"/>
-      <c r="K190" s="52"/>
-      <c r="L190" s="52"/>
-      <c r="M190" s="52"/>
-      <c r="N190" s="52"/>
-      <c r="O190" s="52"/>
-      <c r="P190" s="52"/>
-      <c r="Q190" s="52"/>
-      <c r="R190" s="52"/>
-      <c r="S190" s="52"/>
-      <c r="T190" s="52"/>
-      <c r="U190" s="52"/>
-      <c r="V190" s="52"/>
-      <c r="W190" s="52"/>
-      <c r="X190" s="52"/>
-      <c r="Y190" s="52"/>
-      <c r="Z190" s="52"/>
-      <c r="AA190" s="52"/>
-      <c r="AB190" s="53"/>
+      <c r="H190" s="49"/>
+      <c r="I190" s="50"/>
+      <c r="J190" s="50"/>
+      <c r="K190" s="50"/>
+      <c r="L190" s="50"/>
+      <c r="M190" s="50"/>
+      <c r="N190" s="50"/>
+      <c r="O190" s="50"/>
+      <c r="P190" s="50"/>
+      <c r="Q190" s="50"/>
+      <c r="R190" s="50"/>
+      <c r="S190" s="50"/>
+      <c r="T190" s="50"/>
+      <c r="U190" s="50"/>
+      <c r="V190" s="50"/>
+      <c r="W190" s="50"/>
+      <c r="X190" s="50"/>
+      <c r="Y190" s="50"/>
+      <c r="Z190" s="50"/>
+      <c r="AA190" s="50"/>
+      <c r="AB190" s="51"/>
       <c r="AC190" s="11"/>
     </row>
     <row r="191" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7510,27 +7539,27 @@
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
-      <c r="H191" s="51"/>
-      <c r="I191" s="52"/>
-      <c r="J191" s="52"/>
-      <c r="K191" s="52"/>
-      <c r="L191" s="52"/>
-      <c r="M191" s="52"/>
-      <c r="N191" s="52"/>
-      <c r="O191" s="52"/>
-      <c r="P191" s="52"/>
-      <c r="Q191" s="52"/>
-      <c r="R191" s="52"/>
-      <c r="S191" s="52"/>
-      <c r="T191" s="52"/>
-      <c r="U191" s="52"/>
-      <c r="V191" s="52"/>
-      <c r="W191" s="52"/>
-      <c r="X191" s="52"/>
-      <c r="Y191" s="52"/>
-      <c r="Z191" s="52"/>
-      <c r="AA191" s="52"/>
-      <c r="AB191" s="53"/>
+      <c r="H191" s="49"/>
+      <c r="I191" s="50"/>
+      <c r="J191" s="50"/>
+      <c r="K191" s="50"/>
+      <c r="L191" s="50"/>
+      <c r="M191" s="50"/>
+      <c r="N191" s="50"/>
+      <c r="O191" s="50"/>
+      <c r="P191" s="50"/>
+      <c r="Q191" s="50"/>
+      <c r="R191" s="50"/>
+      <c r="S191" s="50"/>
+      <c r="T191" s="50"/>
+      <c r="U191" s="50"/>
+      <c r="V191" s="50"/>
+      <c r="W191" s="50"/>
+      <c r="X191" s="50"/>
+      <c r="Y191" s="50"/>
+      <c r="Z191" s="50"/>
+      <c r="AA191" s="50"/>
+      <c r="AB191" s="51"/>
       <c r="AC191" s="11"/>
     </row>
     <row r="192" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7540,27 +7569,27 @@
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
-      <c r="H192" s="51"/>
-      <c r="I192" s="52"/>
-      <c r="J192" s="52"/>
-      <c r="K192" s="52"/>
-      <c r="L192" s="52"/>
-      <c r="M192" s="52"/>
-      <c r="N192" s="52"/>
-      <c r="O192" s="52"/>
-      <c r="P192" s="52"/>
-      <c r="Q192" s="52"/>
-      <c r="R192" s="52"/>
-      <c r="S192" s="52"/>
-      <c r="T192" s="52"/>
-      <c r="U192" s="52"/>
-      <c r="V192" s="52"/>
-      <c r="W192" s="52"/>
-      <c r="X192" s="52"/>
-      <c r="Y192" s="52"/>
-      <c r="Z192" s="52"/>
-      <c r="AA192" s="52"/>
-      <c r="AB192" s="53"/>
+      <c r="H192" s="49"/>
+      <c r="I192" s="50"/>
+      <c r="J192" s="50"/>
+      <c r="K192" s="50"/>
+      <c r="L192" s="50"/>
+      <c r="M192" s="50"/>
+      <c r="N192" s="50"/>
+      <c r="O192" s="50"/>
+      <c r="P192" s="50"/>
+      <c r="Q192" s="50"/>
+      <c r="R192" s="50"/>
+      <c r="S192" s="50"/>
+      <c r="T192" s="50"/>
+      <c r="U192" s="50"/>
+      <c r="V192" s="50"/>
+      <c r="W192" s="50"/>
+      <c r="X192" s="50"/>
+      <c r="Y192" s="50"/>
+      <c r="Z192" s="50"/>
+      <c r="AA192" s="50"/>
+      <c r="AB192" s="51"/>
       <c r="AC192" s="11"/>
     </row>
     <row r="193" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7570,27 +7599,27 @@
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
-      <c r="H193" s="54"/>
-      <c r="I193" s="55"/>
-      <c r="J193" s="55"/>
-      <c r="K193" s="55"/>
-      <c r="L193" s="55"/>
-      <c r="M193" s="55"/>
-      <c r="N193" s="55"/>
-      <c r="O193" s="55"/>
-      <c r="P193" s="55"/>
-      <c r="Q193" s="55"/>
-      <c r="R193" s="55"/>
-      <c r="S193" s="55"/>
-      <c r="T193" s="55"/>
-      <c r="U193" s="55"/>
-      <c r="V193" s="55"/>
-      <c r="W193" s="55"/>
-      <c r="X193" s="55"/>
-      <c r="Y193" s="55"/>
-      <c r="Z193" s="55"/>
-      <c r="AA193" s="55"/>
-      <c r="AB193" s="56"/>
+      <c r="H193" s="52"/>
+      <c r="I193" s="53"/>
+      <c r="J193" s="53"/>
+      <c r="K193" s="53"/>
+      <c r="L193" s="53"/>
+      <c r="M193" s="53"/>
+      <c r="N193" s="53"/>
+      <c r="O193" s="53"/>
+      <c r="P193" s="53"/>
+      <c r="Q193" s="53"/>
+      <c r="R193" s="53"/>
+      <c r="S193" s="53"/>
+      <c r="T193" s="53"/>
+      <c r="U193" s="53"/>
+      <c r="V193" s="53"/>
+      <c r="W193" s="53"/>
+      <c r="X193" s="53"/>
+      <c r="Y193" s="53"/>
+      <c r="Z193" s="53"/>
+      <c r="AA193" s="53"/>
+      <c r="AB193" s="54"/>
       <c r="AC193" s="11"/>
     </row>
     <row r="194" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7698,27 +7727,27 @@
         <v>2</v>
       </c>
       <c r="G198" s="6"/>
-      <c r="H198" s="48"/>
-      <c r="I198" s="49"/>
-      <c r="J198" s="49"/>
-      <c r="K198" s="49"/>
-      <c r="L198" s="49"/>
-      <c r="M198" s="49"/>
-      <c r="N198" s="49"/>
-      <c r="O198" s="49"/>
-      <c r="P198" s="49"/>
-      <c r="Q198" s="49"/>
-      <c r="R198" s="49"/>
-      <c r="S198" s="49"/>
-      <c r="T198" s="49"/>
-      <c r="U198" s="49"/>
-      <c r="V198" s="49"/>
-      <c r="W198" s="49"/>
-      <c r="X198" s="49"/>
-      <c r="Y198" s="49"/>
-      <c r="Z198" s="49"/>
-      <c r="AA198" s="49"/>
-      <c r="AB198" s="50"/>
+      <c r="H198" s="46"/>
+      <c r="I198" s="47"/>
+      <c r="J198" s="47"/>
+      <c r="K198" s="47"/>
+      <c r="L198" s="47"/>
+      <c r="M198" s="47"/>
+      <c r="N198" s="47"/>
+      <c r="O198" s="47"/>
+      <c r="P198" s="47"/>
+      <c r="Q198" s="47"/>
+      <c r="R198" s="47"/>
+      <c r="S198" s="47"/>
+      <c r="T198" s="47"/>
+      <c r="U198" s="47"/>
+      <c r="V198" s="47"/>
+      <c r="W198" s="47"/>
+      <c r="X198" s="47"/>
+      <c r="Y198" s="47"/>
+      <c r="Z198" s="47"/>
+      <c r="AA198" s="47"/>
+      <c r="AB198" s="48"/>
       <c r="AC198" s="11"/>
     </row>
     <row r="199" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7728,27 +7757,27 @@
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
       <c r="G199" s="6"/>
-      <c r="H199" s="51"/>
-      <c r="I199" s="52"/>
-      <c r="J199" s="52"/>
-      <c r="K199" s="52"/>
-      <c r="L199" s="52"/>
-      <c r="M199" s="52"/>
-      <c r="N199" s="52"/>
-      <c r="O199" s="52"/>
-      <c r="P199" s="52"/>
-      <c r="Q199" s="52"/>
-      <c r="R199" s="52"/>
-      <c r="S199" s="52"/>
-      <c r="T199" s="52"/>
-      <c r="U199" s="52"/>
-      <c r="V199" s="52"/>
-      <c r="W199" s="52"/>
-      <c r="X199" s="52"/>
-      <c r="Y199" s="52"/>
-      <c r="Z199" s="52"/>
-      <c r="AA199" s="52"/>
-      <c r="AB199" s="53"/>
+      <c r="H199" s="49"/>
+      <c r="I199" s="50"/>
+      <c r="J199" s="50"/>
+      <c r="K199" s="50"/>
+      <c r="L199" s="50"/>
+      <c r="M199" s="50"/>
+      <c r="N199" s="50"/>
+      <c r="O199" s="50"/>
+      <c r="P199" s="50"/>
+      <c r="Q199" s="50"/>
+      <c r="R199" s="50"/>
+      <c r="S199" s="50"/>
+      <c r="T199" s="50"/>
+      <c r="U199" s="50"/>
+      <c r="V199" s="50"/>
+      <c r="W199" s="50"/>
+      <c r="X199" s="50"/>
+      <c r="Y199" s="50"/>
+      <c r="Z199" s="50"/>
+      <c r="AA199" s="50"/>
+      <c r="AB199" s="51"/>
       <c r="AC199" s="11"/>
     </row>
     <row r="200" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7758,27 +7787,27 @@
       <c r="E200" s="6"/>
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
-      <c r="H200" s="51"/>
-      <c r="I200" s="52"/>
-      <c r="J200" s="52"/>
-      <c r="K200" s="52"/>
-      <c r="L200" s="52"/>
-      <c r="M200" s="52"/>
-      <c r="N200" s="52"/>
-      <c r="O200" s="52"/>
-      <c r="P200" s="52"/>
-      <c r="Q200" s="52"/>
-      <c r="R200" s="52"/>
-      <c r="S200" s="52"/>
-      <c r="T200" s="52"/>
-      <c r="U200" s="52"/>
-      <c r="V200" s="52"/>
-      <c r="W200" s="52"/>
-      <c r="X200" s="52"/>
-      <c r="Y200" s="52"/>
-      <c r="Z200" s="52"/>
-      <c r="AA200" s="52"/>
-      <c r="AB200" s="53"/>
+      <c r="H200" s="49"/>
+      <c r="I200" s="50"/>
+      <c r="J200" s="50"/>
+      <c r="K200" s="50"/>
+      <c r="L200" s="50"/>
+      <c r="M200" s="50"/>
+      <c r="N200" s="50"/>
+      <c r="O200" s="50"/>
+      <c r="P200" s="50"/>
+      <c r="Q200" s="50"/>
+      <c r="R200" s="50"/>
+      <c r="S200" s="50"/>
+      <c r="T200" s="50"/>
+      <c r="U200" s="50"/>
+      <c r="V200" s="50"/>
+      <c r="W200" s="50"/>
+      <c r="X200" s="50"/>
+      <c r="Y200" s="50"/>
+      <c r="Z200" s="50"/>
+      <c r="AA200" s="50"/>
+      <c r="AB200" s="51"/>
       <c r="AC200" s="11"/>
     </row>
     <row r="201" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7788,27 +7817,27 @@
       <c r="E201" s="6"/>
       <c r="F201" s="6"/>
       <c r="G201" s="6"/>
-      <c r="H201" s="51"/>
-      <c r="I201" s="52"/>
-      <c r="J201" s="52"/>
-      <c r="K201" s="52"/>
-      <c r="L201" s="52"/>
-      <c r="M201" s="52"/>
-      <c r="N201" s="52"/>
-      <c r="O201" s="52"/>
-      <c r="P201" s="52"/>
-      <c r="Q201" s="52"/>
-      <c r="R201" s="52"/>
-      <c r="S201" s="52"/>
-      <c r="T201" s="52"/>
-      <c r="U201" s="52"/>
-      <c r="V201" s="52"/>
-      <c r="W201" s="52"/>
-      <c r="X201" s="52"/>
-      <c r="Y201" s="52"/>
-      <c r="Z201" s="52"/>
-      <c r="AA201" s="52"/>
-      <c r="AB201" s="53"/>
+      <c r="H201" s="49"/>
+      <c r="I201" s="50"/>
+      <c r="J201" s="50"/>
+      <c r="K201" s="50"/>
+      <c r="L201" s="50"/>
+      <c r="M201" s="50"/>
+      <c r="N201" s="50"/>
+      <c r="O201" s="50"/>
+      <c r="P201" s="50"/>
+      <c r="Q201" s="50"/>
+      <c r="R201" s="50"/>
+      <c r="S201" s="50"/>
+      <c r="T201" s="50"/>
+      <c r="U201" s="50"/>
+      <c r="V201" s="50"/>
+      <c r="W201" s="50"/>
+      <c r="X201" s="50"/>
+      <c r="Y201" s="50"/>
+      <c r="Z201" s="50"/>
+      <c r="AA201" s="50"/>
+      <c r="AB201" s="51"/>
       <c r="AC201" s="11"/>
     </row>
     <row r="202" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7818,27 +7847,27 @@
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
-      <c r="H202" s="51"/>
-      <c r="I202" s="52"/>
-      <c r="J202" s="52"/>
-      <c r="K202" s="52"/>
-      <c r="L202" s="52"/>
-      <c r="M202" s="52"/>
-      <c r="N202" s="52"/>
-      <c r="O202" s="52"/>
-      <c r="P202" s="52"/>
-      <c r="Q202" s="52"/>
-      <c r="R202" s="52"/>
-      <c r="S202" s="52"/>
-      <c r="T202" s="52"/>
-      <c r="U202" s="52"/>
-      <c r="V202" s="52"/>
-      <c r="W202" s="52"/>
-      <c r="X202" s="52"/>
-      <c r="Y202" s="52"/>
-      <c r="Z202" s="52"/>
-      <c r="AA202" s="52"/>
-      <c r="AB202" s="53"/>
+      <c r="H202" s="49"/>
+      <c r="I202" s="50"/>
+      <c r="J202" s="50"/>
+      <c r="K202" s="50"/>
+      <c r="L202" s="50"/>
+      <c r="M202" s="50"/>
+      <c r="N202" s="50"/>
+      <c r="O202" s="50"/>
+      <c r="P202" s="50"/>
+      <c r="Q202" s="50"/>
+      <c r="R202" s="50"/>
+      <c r="S202" s="50"/>
+      <c r="T202" s="50"/>
+      <c r="U202" s="50"/>
+      <c r="V202" s="50"/>
+      <c r="W202" s="50"/>
+      <c r="X202" s="50"/>
+      <c r="Y202" s="50"/>
+      <c r="Z202" s="50"/>
+      <c r="AA202" s="50"/>
+      <c r="AB202" s="51"/>
       <c r="AC202" s="11"/>
     </row>
     <row r="203" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7848,27 +7877,27 @@
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
-      <c r="H203" s="51"/>
-      <c r="I203" s="52"/>
-      <c r="J203" s="52"/>
-      <c r="K203" s="52"/>
-      <c r="L203" s="52"/>
-      <c r="M203" s="52"/>
-      <c r="N203" s="52"/>
-      <c r="O203" s="52"/>
-      <c r="P203" s="52"/>
-      <c r="Q203" s="52"/>
-      <c r="R203" s="52"/>
-      <c r="S203" s="52"/>
-      <c r="T203" s="52"/>
-      <c r="U203" s="52"/>
-      <c r="V203" s="52"/>
-      <c r="W203" s="52"/>
-      <c r="X203" s="52"/>
-      <c r="Y203" s="52"/>
-      <c r="Z203" s="52"/>
-      <c r="AA203" s="52"/>
-      <c r="AB203" s="53"/>
+      <c r="H203" s="49"/>
+      <c r="I203" s="50"/>
+      <c r="J203" s="50"/>
+      <c r="K203" s="50"/>
+      <c r="L203" s="50"/>
+      <c r="M203" s="50"/>
+      <c r="N203" s="50"/>
+      <c r="O203" s="50"/>
+      <c r="P203" s="50"/>
+      <c r="Q203" s="50"/>
+      <c r="R203" s="50"/>
+      <c r="S203" s="50"/>
+      <c r="T203" s="50"/>
+      <c r="U203" s="50"/>
+      <c r="V203" s="50"/>
+      <c r="W203" s="50"/>
+      <c r="X203" s="50"/>
+      <c r="Y203" s="50"/>
+      <c r="Z203" s="50"/>
+      <c r="AA203" s="50"/>
+      <c r="AB203" s="51"/>
       <c r="AC203" s="11"/>
     </row>
     <row r="204" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7878,27 +7907,27 @@
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
-      <c r="H204" s="54"/>
-      <c r="I204" s="55"/>
-      <c r="J204" s="55"/>
-      <c r="K204" s="55"/>
-      <c r="L204" s="55"/>
-      <c r="M204" s="55"/>
-      <c r="N204" s="55"/>
-      <c r="O204" s="55"/>
-      <c r="P204" s="55"/>
-      <c r="Q204" s="55"/>
-      <c r="R204" s="55"/>
-      <c r="S204" s="55"/>
-      <c r="T204" s="55"/>
-      <c r="U204" s="55"/>
-      <c r="V204" s="55"/>
-      <c r="W204" s="55"/>
-      <c r="X204" s="55"/>
-      <c r="Y204" s="55"/>
-      <c r="Z204" s="55"/>
-      <c r="AA204" s="55"/>
-      <c r="AB204" s="56"/>
+      <c r="H204" s="52"/>
+      <c r="I204" s="53"/>
+      <c r="J204" s="53"/>
+      <c r="K204" s="53"/>
+      <c r="L204" s="53"/>
+      <c r="M204" s="53"/>
+      <c r="N204" s="53"/>
+      <c r="O204" s="53"/>
+      <c r="P204" s="53"/>
+      <c r="Q204" s="53"/>
+      <c r="R204" s="53"/>
+      <c r="S204" s="53"/>
+      <c r="T204" s="53"/>
+      <c r="U204" s="53"/>
+      <c r="V204" s="53"/>
+      <c r="W204" s="53"/>
+      <c r="X204" s="53"/>
+      <c r="Y204" s="53"/>
+      <c r="Z204" s="53"/>
+      <c r="AA204" s="53"/>
+      <c r="AB204" s="54"/>
       <c r="AC204" s="11"/>
     </row>
     <row r="205" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7940,27 +7969,27 @@
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
-      <c r="H206" s="48"/>
-      <c r="I206" s="49"/>
-      <c r="J206" s="49"/>
-      <c r="K206" s="49"/>
-      <c r="L206" s="49"/>
-      <c r="M206" s="49"/>
-      <c r="N206" s="49"/>
-      <c r="O206" s="49"/>
-      <c r="P206" s="49"/>
-      <c r="Q206" s="49"/>
-      <c r="R206" s="49"/>
-      <c r="S206" s="49"/>
-      <c r="T206" s="49"/>
-      <c r="U206" s="49"/>
-      <c r="V206" s="49"/>
-      <c r="W206" s="49"/>
-      <c r="X206" s="49"/>
-      <c r="Y206" s="49"/>
-      <c r="Z206" s="49"/>
-      <c r="AA206" s="49"/>
-      <c r="AB206" s="50"/>
+      <c r="H206" s="46"/>
+      <c r="I206" s="47"/>
+      <c r="J206" s="47"/>
+      <c r="K206" s="47"/>
+      <c r="L206" s="47"/>
+      <c r="M206" s="47"/>
+      <c r="N206" s="47"/>
+      <c r="O206" s="47"/>
+      <c r="P206" s="47"/>
+      <c r="Q206" s="47"/>
+      <c r="R206" s="47"/>
+      <c r="S206" s="47"/>
+      <c r="T206" s="47"/>
+      <c r="U206" s="47"/>
+      <c r="V206" s="47"/>
+      <c r="W206" s="47"/>
+      <c r="X206" s="47"/>
+      <c r="Y206" s="47"/>
+      <c r="Z206" s="47"/>
+      <c r="AA206" s="47"/>
+      <c r="AB206" s="48"/>
       <c r="AC206" s="11"/>
     </row>
     <row r="207" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -7970,27 +7999,27 @@
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
-      <c r="H207" s="51"/>
-      <c r="I207" s="52"/>
-      <c r="J207" s="52"/>
-      <c r="K207" s="52"/>
-      <c r="L207" s="52"/>
-      <c r="M207" s="52"/>
-      <c r="N207" s="52"/>
-      <c r="O207" s="52"/>
-      <c r="P207" s="52"/>
-      <c r="Q207" s="52"/>
-      <c r="R207" s="52"/>
-      <c r="S207" s="52"/>
-      <c r="T207" s="52"/>
-      <c r="U207" s="52"/>
-      <c r="V207" s="52"/>
-      <c r="W207" s="52"/>
-      <c r="X207" s="52"/>
-      <c r="Y207" s="52"/>
-      <c r="Z207" s="52"/>
-      <c r="AA207" s="52"/>
-      <c r="AB207" s="53"/>
+      <c r="H207" s="49"/>
+      <c r="I207" s="50"/>
+      <c r="J207" s="50"/>
+      <c r="K207" s="50"/>
+      <c r="L207" s="50"/>
+      <c r="M207" s="50"/>
+      <c r="N207" s="50"/>
+      <c r="O207" s="50"/>
+      <c r="P207" s="50"/>
+      <c r="Q207" s="50"/>
+      <c r="R207" s="50"/>
+      <c r="S207" s="50"/>
+      <c r="T207" s="50"/>
+      <c r="U207" s="50"/>
+      <c r="V207" s="50"/>
+      <c r="W207" s="50"/>
+      <c r="X207" s="50"/>
+      <c r="Y207" s="50"/>
+      <c r="Z207" s="50"/>
+      <c r="AA207" s="50"/>
+      <c r="AB207" s="51"/>
       <c r="AC207" s="11"/>
     </row>
     <row r="208" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8000,27 +8029,27 @@
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
       <c r="G208" s="6"/>
-      <c r="H208" s="51"/>
-      <c r="I208" s="52"/>
-      <c r="J208" s="52"/>
-      <c r="K208" s="52"/>
-      <c r="L208" s="52"/>
-      <c r="M208" s="52"/>
-      <c r="N208" s="52"/>
-      <c r="O208" s="52"/>
-      <c r="P208" s="52"/>
-      <c r="Q208" s="52"/>
-      <c r="R208" s="52"/>
-      <c r="S208" s="52"/>
-      <c r="T208" s="52"/>
-      <c r="U208" s="52"/>
-      <c r="V208" s="52"/>
-      <c r="W208" s="52"/>
-      <c r="X208" s="52"/>
-      <c r="Y208" s="52"/>
-      <c r="Z208" s="52"/>
-      <c r="AA208" s="52"/>
-      <c r="AB208" s="53"/>
+      <c r="H208" s="49"/>
+      <c r="I208" s="50"/>
+      <c r="J208" s="50"/>
+      <c r="K208" s="50"/>
+      <c r="L208" s="50"/>
+      <c r="M208" s="50"/>
+      <c r="N208" s="50"/>
+      <c r="O208" s="50"/>
+      <c r="P208" s="50"/>
+      <c r="Q208" s="50"/>
+      <c r="R208" s="50"/>
+      <c r="S208" s="50"/>
+      <c r="T208" s="50"/>
+      <c r="U208" s="50"/>
+      <c r="V208" s="50"/>
+      <c r="W208" s="50"/>
+      <c r="X208" s="50"/>
+      <c r="Y208" s="50"/>
+      <c r="Z208" s="50"/>
+      <c r="AA208" s="50"/>
+      <c r="AB208" s="51"/>
       <c r="AC208" s="11"/>
     </row>
     <row r="209" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8030,27 +8059,27 @@
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
-      <c r="H209" s="51"/>
-      <c r="I209" s="52"/>
-      <c r="J209" s="52"/>
-      <c r="K209" s="52"/>
-      <c r="L209" s="52"/>
-      <c r="M209" s="52"/>
-      <c r="N209" s="52"/>
-      <c r="O209" s="52"/>
-      <c r="P209" s="52"/>
-      <c r="Q209" s="52"/>
-      <c r="R209" s="52"/>
-      <c r="S209" s="52"/>
-      <c r="T209" s="52"/>
-      <c r="U209" s="52"/>
-      <c r="V209" s="52"/>
-      <c r="W209" s="52"/>
-      <c r="X209" s="52"/>
-      <c r="Y209" s="52"/>
-      <c r="Z209" s="52"/>
-      <c r="AA209" s="52"/>
-      <c r="AB209" s="53"/>
+      <c r="H209" s="49"/>
+      <c r="I209" s="50"/>
+      <c r="J209" s="50"/>
+      <c r="K209" s="50"/>
+      <c r="L209" s="50"/>
+      <c r="M209" s="50"/>
+      <c r="N209" s="50"/>
+      <c r="O209" s="50"/>
+      <c r="P209" s="50"/>
+      <c r="Q209" s="50"/>
+      <c r="R209" s="50"/>
+      <c r="S209" s="50"/>
+      <c r="T209" s="50"/>
+      <c r="U209" s="50"/>
+      <c r="V209" s="50"/>
+      <c r="W209" s="50"/>
+      <c r="X209" s="50"/>
+      <c r="Y209" s="50"/>
+      <c r="Z209" s="50"/>
+      <c r="AA209" s="50"/>
+      <c r="AB209" s="51"/>
       <c r="AC209" s="11"/>
     </row>
     <row r="210" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8060,27 +8089,27 @@
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
-      <c r="H210" s="51"/>
-      <c r="I210" s="52"/>
-      <c r="J210" s="52"/>
-      <c r="K210" s="52"/>
-      <c r="L210" s="52"/>
-      <c r="M210" s="52"/>
-      <c r="N210" s="52"/>
-      <c r="O210" s="52"/>
-      <c r="P210" s="52"/>
-      <c r="Q210" s="52"/>
-      <c r="R210" s="52"/>
-      <c r="S210" s="52"/>
-      <c r="T210" s="52"/>
-      <c r="U210" s="52"/>
-      <c r="V210" s="52"/>
-      <c r="W210" s="52"/>
-      <c r="X210" s="52"/>
-      <c r="Y210" s="52"/>
-      <c r="Z210" s="52"/>
-      <c r="AA210" s="52"/>
-      <c r="AB210" s="53"/>
+      <c r="H210" s="49"/>
+      <c r="I210" s="50"/>
+      <c r="J210" s="50"/>
+      <c r="K210" s="50"/>
+      <c r="L210" s="50"/>
+      <c r="M210" s="50"/>
+      <c r="N210" s="50"/>
+      <c r="O210" s="50"/>
+      <c r="P210" s="50"/>
+      <c r="Q210" s="50"/>
+      <c r="R210" s="50"/>
+      <c r="S210" s="50"/>
+      <c r="T210" s="50"/>
+      <c r="U210" s="50"/>
+      <c r="V210" s="50"/>
+      <c r="W210" s="50"/>
+      <c r="X210" s="50"/>
+      <c r="Y210" s="50"/>
+      <c r="Z210" s="50"/>
+      <c r="AA210" s="50"/>
+      <c r="AB210" s="51"/>
       <c r="AC210" s="11"/>
     </row>
     <row r="211" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8090,27 +8119,27 @@
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
       <c r="G211" s="6"/>
-      <c r="H211" s="51"/>
-      <c r="I211" s="52"/>
-      <c r="J211" s="52"/>
-      <c r="K211" s="52"/>
-      <c r="L211" s="52"/>
-      <c r="M211" s="52"/>
-      <c r="N211" s="52"/>
-      <c r="O211" s="52"/>
-      <c r="P211" s="52"/>
-      <c r="Q211" s="52"/>
-      <c r="R211" s="52"/>
-      <c r="S211" s="52"/>
-      <c r="T211" s="52"/>
-      <c r="U211" s="52"/>
-      <c r="V211" s="52"/>
-      <c r="W211" s="52"/>
-      <c r="X211" s="52"/>
-      <c r="Y211" s="52"/>
-      <c r="Z211" s="52"/>
-      <c r="AA211" s="52"/>
-      <c r="AB211" s="53"/>
+      <c r="H211" s="49"/>
+      <c r="I211" s="50"/>
+      <c r="J211" s="50"/>
+      <c r="K211" s="50"/>
+      <c r="L211" s="50"/>
+      <c r="M211" s="50"/>
+      <c r="N211" s="50"/>
+      <c r="O211" s="50"/>
+      <c r="P211" s="50"/>
+      <c r="Q211" s="50"/>
+      <c r="R211" s="50"/>
+      <c r="S211" s="50"/>
+      <c r="T211" s="50"/>
+      <c r="U211" s="50"/>
+      <c r="V211" s="50"/>
+      <c r="W211" s="50"/>
+      <c r="X211" s="50"/>
+      <c r="Y211" s="50"/>
+      <c r="Z211" s="50"/>
+      <c r="AA211" s="50"/>
+      <c r="AB211" s="51"/>
       <c r="AC211" s="11"/>
     </row>
     <row r="212" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8120,27 +8149,27 @@
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
-      <c r="H212" s="54"/>
-      <c r="I212" s="55"/>
-      <c r="J212" s="55"/>
-      <c r="K212" s="55"/>
-      <c r="L212" s="55"/>
-      <c r="M212" s="55"/>
-      <c r="N212" s="55"/>
-      <c r="O212" s="55"/>
-      <c r="P212" s="55"/>
-      <c r="Q212" s="55"/>
-      <c r="R212" s="55"/>
-      <c r="S212" s="55"/>
-      <c r="T212" s="55"/>
-      <c r="U212" s="55"/>
-      <c r="V212" s="55"/>
-      <c r="W212" s="55"/>
-      <c r="X212" s="55"/>
-      <c r="Y212" s="55"/>
-      <c r="Z212" s="55"/>
-      <c r="AA212" s="55"/>
-      <c r="AB212" s="56"/>
+      <c r="H212" s="52"/>
+      <c r="I212" s="53"/>
+      <c r="J212" s="53"/>
+      <c r="K212" s="53"/>
+      <c r="L212" s="53"/>
+      <c r="M212" s="53"/>
+      <c r="N212" s="53"/>
+      <c r="O212" s="53"/>
+      <c r="P212" s="53"/>
+      <c r="Q212" s="53"/>
+      <c r="R212" s="53"/>
+      <c r="S212" s="53"/>
+      <c r="T212" s="53"/>
+      <c r="U212" s="53"/>
+      <c r="V212" s="53"/>
+      <c r="W212" s="53"/>
+      <c r="X212" s="53"/>
+      <c r="Y212" s="53"/>
+      <c r="Z212" s="53"/>
+      <c r="AA212" s="53"/>
+      <c r="AB212" s="54"/>
       <c r="AC212" s="11"/>
     </row>
     <row r="213" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -8175,6 +8204,43 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B25:B42"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="H27:AB33"/>
+    <mergeCell ref="H35:AB41"/>
+    <mergeCell ref="B44:B61"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:AB52"/>
+    <mergeCell ref="H54:AB60"/>
+    <mergeCell ref="B63:B80"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="H65:AB71"/>
+    <mergeCell ref="H73:AB79"/>
+    <mergeCell ref="B82:B99"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="H84:AB90"/>
+    <mergeCell ref="H92:AB98"/>
+    <mergeCell ref="B101:B118"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="H103:AB109"/>
+    <mergeCell ref="H111:AB117"/>
+    <mergeCell ref="B120:B137"/>
+    <mergeCell ref="D122:E122"/>
+    <mergeCell ref="H122:AB128"/>
+    <mergeCell ref="H130:AB136"/>
+    <mergeCell ref="B139:B156"/>
+    <mergeCell ref="D141:E141"/>
+    <mergeCell ref="H141:AB147"/>
+    <mergeCell ref="H149:AB155"/>
+    <mergeCell ref="B158:B175"/>
+    <mergeCell ref="D160:E160"/>
+    <mergeCell ref="H160:AB166"/>
+    <mergeCell ref="H168:AB174"/>
     <mergeCell ref="B177:B194"/>
     <mergeCell ref="D179:E179"/>
     <mergeCell ref="H179:AB185"/>
@@ -8183,43 +8249,6 @@
     <mergeCell ref="D198:E198"/>
     <mergeCell ref="H198:AB204"/>
     <mergeCell ref="H206:AB212"/>
-    <mergeCell ref="B139:B156"/>
-    <mergeCell ref="D141:E141"/>
-    <mergeCell ref="H141:AB147"/>
-    <mergeCell ref="H149:AB155"/>
-    <mergeCell ref="B158:B175"/>
-    <mergeCell ref="D160:E160"/>
-    <mergeCell ref="H160:AB166"/>
-    <mergeCell ref="H168:AB174"/>
-    <mergeCell ref="B101:B118"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="H103:AB109"/>
-    <mergeCell ref="H111:AB117"/>
-    <mergeCell ref="B120:B137"/>
-    <mergeCell ref="D122:E122"/>
-    <mergeCell ref="H122:AB128"/>
-    <mergeCell ref="H130:AB136"/>
-    <mergeCell ref="B63:B80"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="H65:AB71"/>
-    <mergeCell ref="H73:AB79"/>
-    <mergeCell ref="B82:B99"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="H84:AB90"/>
-    <mergeCell ref="H92:AB98"/>
-    <mergeCell ref="B25:B42"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="H27:AB33"/>
-    <mergeCell ref="H35:AB41"/>
-    <mergeCell ref="B44:B61"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:AB52"/>
-    <mergeCell ref="H54:AB60"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -8246,11 +8275,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>21</v>
       </c>
@@ -9092,27 +9121,27 @@
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" s="19"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="49"/>
-      <c r="O34" s="49"/>
-      <c r="P34" s="49"/>
-      <c r="Q34" s="49"/>
-      <c r="R34" s="49"/>
-      <c r="S34" s="49"/>
-      <c r="T34" s="49"/>
-      <c r="U34" s="49"/>
-      <c r="V34" s="49"/>
-      <c r="W34" s="49"/>
-      <c r="X34" s="49"/>
-      <c r="Y34" s="49"/>
-      <c r="Z34" s="49"/>
-      <c r="AA34" s="49"/>
-      <c r="AB34" s="50"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
+      <c r="N34" s="47"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="47"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47"/>
+      <c r="S34" s="47"/>
+      <c r="T34" s="47"/>
+      <c r="U34" s="47"/>
+      <c r="V34" s="47"/>
+      <c r="W34" s="47"/>
+      <c r="X34" s="47"/>
+      <c r="Y34" s="47"/>
+      <c r="Z34" s="47"/>
+      <c r="AA34" s="47"/>
+      <c r="AB34" s="48"/>
       <c r="AC34" s="16"/>
     </row>
     <row r="35" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9122,27 +9151,27 @@
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
-      <c r="T35" s="52"/>
-      <c r="U35" s="52"/>
-      <c r="V35" s="52"/>
-      <c r="W35" s="52"/>
-      <c r="X35" s="52"/>
-      <c r="Y35" s="52"/>
-      <c r="Z35" s="52"/>
-      <c r="AA35" s="52"/>
-      <c r="AB35" s="53"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
+      <c r="P35" s="50"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="50"/>
+      <c r="S35" s="50"/>
+      <c r="T35" s="50"/>
+      <c r="U35" s="50"/>
+      <c r="V35" s="50"/>
+      <c r="W35" s="50"/>
+      <c r="X35" s="50"/>
+      <c r="Y35" s="50"/>
+      <c r="Z35" s="50"/>
+      <c r="AA35" s="50"/>
+      <c r="AB35" s="51"/>
       <c r="AC35" s="16"/>
     </row>
     <row r="36" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9152,27 +9181,27 @@
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="52"/>
-      <c r="Q36" s="52"/>
-      <c r="R36" s="52"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="52"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="52"/>
-      <c r="W36" s="52"/>
-      <c r="X36" s="52"/>
-      <c r="Y36" s="52"/>
-      <c r="Z36" s="52"/>
-      <c r="AA36" s="52"/>
-      <c r="AB36" s="53"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="50"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="50"/>
+      <c r="P36" s="50"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="50"/>
+      <c r="S36" s="50"/>
+      <c r="T36" s="50"/>
+      <c r="U36" s="50"/>
+      <c r="V36" s="50"/>
+      <c r="W36" s="50"/>
+      <c r="X36" s="50"/>
+      <c r="Y36" s="50"/>
+      <c r="Z36" s="50"/>
+      <c r="AA36" s="50"/>
+      <c r="AB36" s="51"/>
       <c r="AC36" s="16"/>
     </row>
     <row r="37" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9182,27 +9211,27 @@
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="52"/>
-      <c r="O37" s="52"/>
-      <c r="P37" s="52"/>
-      <c r="Q37" s="52"/>
-      <c r="R37" s="52"/>
-      <c r="S37" s="52"/>
-      <c r="T37" s="52"/>
-      <c r="U37" s="52"/>
-      <c r="V37" s="52"/>
-      <c r="W37" s="52"/>
-      <c r="X37" s="52"/>
-      <c r="Y37" s="52"/>
-      <c r="Z37" s="52"/>
-      <c r="AA37" s="52"/>
-      <c r="AB37" s="53"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="50"/>
+      <c r="M37" s="50"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="50"/>
+      <c r="P37" s="50"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="50"/>
+      <c r="S37" s="50"/>
+      <c r="T37" s="50"/>
+      <c r="U37" s="50"/>
+      <c r="V37" s="50"/>
+      <c r="W37" s="50"/>
+      <c r="X37" s="50"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="51"/>
       <c r="AC37" s="16"/>
     </row>
     <row r="38" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9212,27 +9241,27 @@
       <c r="E38" s="19"/>
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="52"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="52"/>
-      <c r="Q38" s="52"/>
-      <c r="R38" s="52"/>
-      <c r="S38" s="52"/>
-      <c r="T38" s="52"/>
-      <c r="U38" s="52"/>
-      <c r="V38" s="52"/>
-      <c r="W38" s="52"/>
-      <c r="X38" s="52"/>
-      <c r="Y38" s="52"/>
-      <c r="Z38" s="52"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="53"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="50"/>
+      <c r="L38" s="50"/>
+      <c r="M38" s="50"/>
+      <c r="N38" s="50"/>
+      <c r="O38" s="50"/>
+      <c r="P38" s="50"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="50"/>
+      <c r="S38" s="50"/>
+      <c r="T38" s="50"/>
+      <c r="U38" s="50"/>
+      <c r="V38" s="50"/>
+      <c r="W38" s="50"/>
+      <c r="X38" s="50"/>
+      <c r="Y38" s="50"/>
+      <c r="Z38" s="50"/>
+      <c r="AA38" s="50"/>
+      <c r="AB38" s="51"/>
       <c r="AC38" s="16"/>
     </row>
     <row r="39" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9242,27 +9271,27 @@
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="52"/>
-      <c r="K39" s="52"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="52"/>
-      <c r="N39" s="52"/>
-      <c r="O39" s="52"/>
-      <c r="P39" s="52"/>
-      <c r="Q39" s="52"/>
-      <c r="R39" s="52"/>
-      <c r="S39" s="52"/>
-      <c r="T39" s="52"/>
-      <c r="U39" s="52"/>
-      <c r="V39" s="52"/>
-      <c r="W39" s="52"/>
-      <c r="X39" s="52"/>
-      <c r="Y39" s="52"/>
-      <c r="Z39" s="52"/>
-      <c r="AA39" s="52"/>
-      <c r="AB39" s="53"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="50"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="50"/>
+      <c r="P39" s="50"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50"/>
+      <c r="S39" s="50"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="50"/>
+      <c r="V39" s="50"/>
+      <c r="W39" s="50"/>
+      <c r="X39" s="50"/>
+      <c r="Y39" s="50"/>
+      <c r="Z39" s="50"/>
+      <c r="AA39" s="50"/>
+      <c r="AB39" s="51"/>
       <c r="AC39" s="16"/>
     </row>
     <row r="40" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9272,27 +9301,27 @@
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="55"/>
-      <c r="R40" s="55"/>
-      <c r="S40" s="55"/>
-      <c r="T40" s="55"/>
-      <c r="U40" s="55"/>
-      <c r="V40" s="55"/>
-      <c r="W40" s="55"/>
-      <c r="X40" s="55"/>
-      <c r="Y40" s="55"/>
-      <c r="Z40" s="55"/>
-      <c r="AA40" s="55"/>
-      <c r="AB40" s="56"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="53"/>
+      <c r="N40" s="53"/>
+      <c r="O40" s="53"/>
+      <c r="P40" s="53"/>
+      <c r="Q40" s="53"/>
+      <c r="R40" s="53"/>
+      <c r="S40" s="53"/>
+      <c r="T40" s="53"/>
+      <c r="U40" s="53"/>
+      <c r="V40" s="53"/>
+      <c r="W40" s="53"/>
+      <c r="X40" s="53"/>
+      <c r="Y40" s="53"/>
+      <c r="Z40" s="53"/>
+      <c r="AA40" s="53"/>
+      <c r="AB40" s="54"/>
       <c r="AC40" s="16"/>
     </row>
     <row r="41" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9334,27 +9363,27 @@
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
       <c r="G42" s="19"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-      <c r="K42" s="49"/>
-      <c r="L42" s="49"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="49"/>
-      <c r="O42" s="49"/>
-      <c r="P42" s="49"/>
-      <c r="Q42" s="49"/>
-      <c r="R42" s="49"/>
-      <c r="S42" s="49"/>
-      <c r="T42" s="49"/>
-      <c r="U42" s="49"/>
-      <c r="V42" s="49"/>
-      <c r="W42" s="49"/>
-      <c r="X42" s="49"/>
-      <c r="Y42" s="49"/>
-      <c r="Z42" s="49"/>
-      <c r="AA42" s="49"/>
-      <c r="AB42" s="50"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
+      <c r="M42" s="47"/>
+      <c r="N42" s="47"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="47"/>
+      <c r="Q42" s="47"/>
+      <c r="R42" s="47"/>
+      <c r="S42" s="47"/>
+      <c r="T42" s="47"/>
+      <c r="U42" s="47"/>
+      <c r="V42" s="47"/>
+      <c r="W42" s="47"/>
+      <c r="X42" s="47"/>
+      <c r="Y42" s="47"/>
+      <c r="Z42" s="47"/>
+      <c r="AA42" s="47"/>
+      <c r="AB42" s="48"/>
       <c r="AC42" s="16"/>
     </row>
     <row r="43" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9364,27 +9393,27 @@
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="52"/>
-      <c r="L43" s="52"/>
-      <c r="M43" s="52"/>
-      <c r="N43" s="52"/>
-      <c r="O43" s="52"/>
-      <c r="P43" s="52"/>
-      <c r="Q43" s="52"/>
-      <c r="R43" s="52"/>
-      <c r="S43" s="52"/>
-      <c r="T43" s="52"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="52"/>
-      <c r="W43" s="52"/>
-      <c r="X43" s="52"/>
-      <c r="Y43" s="52"/>
-      <c r="Z43" s="52"/>
-      <c r="AA43" s="52"/>
-      <c r="AB43" s="53"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="50"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="50"/>
+      <c r="V43" s="50"/>
+      <c r="W43" s="50"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="50"/>
+      <c r="AA43" s="50"/>
+      <c r="AB43" s="51"/>
       <c r="AC43" s="16"/>
     </row>
     <row r="44" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9394,27 +9423,27 @@
       <c r="E44" s="19"/>
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="52"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="52"/>
-      <c r="O44" s="52"/>
-      <c r="P44" s="52"/>
-      <c r="Q44" s="52"/>
-      <c r="R44" s="52"/>
-      <c r="S44" s="52"/>
-      <c r="T44" s="52"/>
-      <c r="U44" s="52"/>
-      <c r="V44" s="52"/>
-      <c r="W44" s="52"/>
-      <c r="X44" s="52"/>
-      <c r="Y44" s="52"/>
-      <c r="Z44" s="52"/>
-      <c r="AA44" s="52"/>
-      <c r="AB44" s="53"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="50"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="50"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="50"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50"/>
+      <c r="S44" s="50"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="50"/>
+      <c r="W44" s="50"/>
+      <c r="X44" s="50"/>
+      <c r="Y44" s="50"/>
+      <c r="Z44" s="50"/>
+      <c r="AA44" s="50"/>
+      <c r="AB44" s="51"/>
       <c r="AC44" s="16"/>
     </row>
     <row r="45" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9424,27 +9453,27 @@
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="52"/>
-      <c r="O45" s="52"/>
-      <c r="P45" s="52"/>
-      <c r="Q45" s="52"/>
-      <c r="R45" s="52"/>
-      <c r="S45" s="52"/>
-      <c r="T45" s="52"/>
-      <c r="U45" s="52"/>
-      <c r="V45" s="52"/>
-      <c r="W45" s="52"/>
-      <c r="X45" s="52"/>
-      <c r="Y45" s="52"/>
-      <c r="Z45" s="52"/>
-      <c r="AA45" s="52"/>
-      <c r="AB45" s="53"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="L45" s="50"/>
+      <c r="M45" s="50"/>
+      <c r="N45" s="50"/>
+      <c r="O45" s="50"/>
+      <c r="P45" s="50"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50"/>
+      <c r="S45" s="50"/>
+      <c r="T45" s="50"/>
+      <c r="U45" s="50"/>
+      <c r="V45" s="50"/>
+      <c r="W45" s="50"/>
+      <c r="X45" s="50"/>
+      <c r="Y45" s="50"/>
+      <c r="Z45" s="50"/>
+      <c r="AA45" s="50"/>
+      <c r="AB45" s="51"/>
       <c r="AC45" s="16"/>
     </row>
     <row r="46" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9454,27 +9483,27 @@
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="52"/>
-      <c r="M46" s="52"/>
-      <c r="N46" s="52"/>
-      <c r="O46" s="52"/>
-      <c r="P46" s="52"/>
-      <c r="Q46" s="52"/>
-      <c r="R46" s="52"/>
-      <c r="S46" s="52"/>
-      <c r="T46" s="52"/>
-      <c r="U46" s="52"/>
-      <c r="V46" s="52"/>
-      <c r="W46" s="52"/>
-      <c r="X46" s="52"/>
-      <c r="Y46" s="52"/>
-      <c r="Z46" s="52"/>
-      <c r="AA46" s="52"/>
-      <c r="AB46" s="53"/>
+      <c r="H46" s="49"/>
+      <c r="I46" s="50"/>
+      <c r="J46" s="50"/>
+      <c r="K46" s="50"/>
+      <c r="L46" s="50"/>
+      <c r="M46" s="50"/>
+      <c r="N46" s="50"/>
+      <c r="O46" s="50"/>
+      <c r="P46" s="50"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50"/>
+      <c r="S46" s="50"/>
+      <c r="T46" s="50"/>
+      <c r="U46" s="50"/>
+      <c r="V46" s="50"/>
+      <c r="W46" s="50"/>
+      <c r="X46" s="50"/>
+      <c r="Y46" s="50"/>
+      <c r="Z46" s="50"/>
+      <c r="AA46" s="50"/>
+      <c r="AB46" s="51"/>
       <c r="AC46" s="16"/>
     </row>
     <row r="47" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9484,27 +9513,27 @@
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
       <c r="G47" s="19"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="52"/>
-      <c r="M47" s="52"/>
-      <c r="N47" s="52"/>
-      <c r="O47" s="52"/>
-      <c r="P47" s="52"/>
-      <c r="Q47" s="52"/>
-      <c r="R47" s="52"/>
-      <c r="S47" s="52"/>
-      <c r="T47" s="52"/>
-      <c r="U47" s="52"/>
-      <c r="V47" s="52"/>
-      <c r="W47" s="52"/>
-      <c r="X47" s="52"/>
-      <c r="Y47" s="52"/>
-      <c r="Z47" s="52"/>
-      <c r="AA47" s="52"/>
-      <c r="AB47" s="53"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="50"/>
+      <c r="J47" s="50"/>
+      <c r="K47" s="50"/>
+      <c r="L47" s="50"/>
+      <c r="M47" s="50"/>
+      <c r="N47" s="50"/>
+      <c r="O47" s="50"/>
+      <c r="P47" s="50"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50"/>
+      <c r="S47" s="50"/>
+      <c r="T47" s="50"/>
+      <c r="U47" s="50"/>
+      <c r="V47" s="50"/>
+      <c r="W47" s="50"/>
+      <c r="X47" s="50"/>
+      <c r="Y47" s="50"/>
+      <c r="Z47" s="50"/>
+      <c r="AA47" s="50"/>
+      <c r="AB47" s="51"/>
       <c r="AC47" s="16"/>
     </row>
     <row r="48" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9514,27 +9543,27 @@
       <c r="E48" s="19"/>
       <c r="F48" s="19"/>
       <c r="G48" s="19"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="55"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="55"/>
-      <c r="L48" s="55"/>
-      <c r="M48" s="55"/>
-      <c r="N48" s="55"/>
-      <c r="O48" s="55"/>
-      <c r="P48" s="55"/>
-      <c r="Q48" s="55"/>
-      <c r="R48" s="55"/>
-      <c r="S48" s="55"/>
-      <c r="T48" s="55"/>
-      <c r="U48" s="55"/>
-      <c r="V48" s="55"/>
-      <c r="W48" s="55"/>
-      <c r="X48" s="55"/>
-      <c r="Y48" s="55"/>
-      <c r="Z48" s="55"/>
-      <c r="AA48" s="55"/>
-      <c r="AB48" s="56"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="53"/>
+      <c r="S48" s="53"/>
+      <c r="T48" s="53"/>
+      <c r="U48" s="53"/>
+      <c r="V48" s="53"/>
+      <c r="W48" s="53"/>
+      <c r="X48" s="53"/>
+      <c r="Y48" s="53"/>
+      <c r="Z48" s="53"/>
+      <c r="AA48" s="53"/>
+      <c r="AB48" s="54"/>
       <c r="AC48" s="16"/>
     </row>
     <row r="49" spans="2:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9607,11 +9636,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
@@ -10416,11 +10445,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>33</v>
       </c>
@@ -11558,11 +11587,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>34</v>
       </c>
@@ -14309,6 +14338,19 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:B23"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="H8:AB14"/>
+    <mergeCell ref="H16:AB22"/>
+    <mergeCell ref="B26:B43"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="H28:AB34"/>
+    <mergeCell ref="H36:AB42"/>
+    <mergeCell ref="B46:B63"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="H48:AB54"/>
+    <mergeCell ref="H56:AB62"/>
     <mergeCell ref="B66:B83"/>
     <mergeCell ref="D68:F68"/>
     <mergeCell ref="H68:AB74"/>
@@ -14317,19 +14359,6 @@
     <mergeCell ref="D88:F88"/>
     <mergeCell ref="H88:AB94"/>
     <mergeCell ref="H96:AB102"/>
-    <mergeCell ref="B26:B43"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="H28:AB34"/>
-    <mergeCell ref="H36:AB42"/>
-    <mergeCell ref="B46:B63"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="H48:AB54"/>
-    <mergeCell ref="H56:AB62"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:B23"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="H8:AB14"/>
-    <mergeCell ref="H16:AB22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -14356,11 +14385,11 @@
         <f xml:space="preserve"> '4.2.1'!B3</f>
         <v>.NET MAUI</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="I3" s="23" t="s">
         <v>41</v>
       </c>
